--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1726"/>
+  <dimension ref="A1:F1727"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="C9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="D9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="E9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="C10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="D10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="E10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922460913658142</v>
       </c>
       <c r="C38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922460913658142</v>
       </c>
       <c r="D38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922460913658142</v>
       </c>
       <c r="E38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922460913658142</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800049</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997223854064941</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959037780762</v>
+        <v>3.926958560943604</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075627326965332</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045627593994</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045627593994</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045627593994</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045627593994</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="C64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="D64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="E64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -34932,19 +34932,39 @@
         <v>46276</v>
       </c>
       <c r="B1726" t="n">
-        <v>2.97</v>
+        <v>2.970000028610229</v>
       </c>
       <c r="C1726" t="n">
-        <v>2.97</v>
+        <v>2.970000028610229</v>
       </c>
       <c r="D1726" t="n">
-        <v>2.85</v>
+        <v>2.849999904632568</v>
       </c>
       <c r="E1726" t="n">
-        <v>2.89</v>
+        <v>2.890000104904175</v>
       </c>
       <c r="F1726" t="n">
         <v>3353600</v>
+      </c>
+    </row>
+    <row r="1727">
+      <c r="A1727" s="1" t="n">
+        <v>46279</v>
+      </c>
+      <c r="B1727" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="C1727" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="D1727" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E1727" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="F1727" t="n">
+        <v>6993700</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1727"/>
+  <dimension ref="A1:F1728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906559944153</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906559944153</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906559944153</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906559944153</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922460913658142</v>
+        <v>1.9224613904953</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922460913658142</v>
+        <v>1.9224613904953</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922460913658142</v>
+        <v>1.9224613904953</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922460913658142</v>
+        <v>1.9224613904953</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647352695465088</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647352695465088</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647352695465088</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647352695465088</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951084613800049</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997223854064941</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997223854064942</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997223854064942</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997223854064942</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958560943604</v>
+        <v>3.926959037780762</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489364147186279</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489364147186279</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489364147186279</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489364147186279</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489364147186279</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489364147186279</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489364147186279</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489364147186279</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075627326965332</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68732929229736</v>
       </c>
       <c r="C57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68732929229736</v>
       </c>
       <c r="D57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68732929229736</v>
       </c>
       <c r="E57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68732929229736</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="C64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="D64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="E64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -34952,19 +34952,39 @@
         <v>46279</v>
       </c>
       <c r="B1727" t="n">
-        <v>3.08</v>
+        <v>3.079999923706055</v>
       </c>
       <c r="C1727" t="n">
-        <v>3.12</v>
+        <v>3.119999885559082</v>
       </c>
       <c r="D1727" t="n">
-        <v>2.92</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="E1727" t="n">
-        <v>2.92</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="F1727" t="n">
         <v>6993700</v>
+      </c>
+    </row>
+    <row r="1728">
+      <c r="A1728" s="1" t="n">
+        <v>46280</v>
+      </c>
+      <c r="B1728" t="n">
+        <v>3.17</v>
+      </c>
+      <c r="C1728" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D1728" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="E1728" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="F1728" t="n">
+        <v>4669500</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1728"/>
+  <dimension ref="A1:F1729"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906559944153</v>
+        <v>1.553905844688416</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906559944153</v>
+        <v>1.553905844688416</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906559944153</v>
+        <v>1.553905844688416</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906559944153</v>
+        <v>1.553905844688416</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799174427986145</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799174427986145</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799174427986145</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799174427986145</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.8531334400177</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.8531334400177</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.8531334400177</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.8531334400177</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.8531334400177</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.8531334400177</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.8531334400177</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.8531334400177</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.8531334400177</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.8531334400177</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.8531334400177</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.8531334400177</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="C36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="D36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="E36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.9224613904953</v>
+        <v>1.922461867332458</v>
       </c>
       <c r="C38" t="n">
-        <v>1.9224613904953</v>
+        <v>1.922461867332458</v>
       </c>
       <c r="D38" t="n">
-        <v>1.9224613904953</v>
+        <v>1.922461867332458</v>
       </c>
       <c r="E38" t="n">
-        <v>1.9224613904953</v>
+        <v>1.922461867332458</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758487343788147</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758487343788147</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758487343788147</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758487343788147</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647352695465088</v>
+        <v>4.647353172302246</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647352695465088</v>
+        <v>4.647353172302246</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647352695465088</v>
+        <v>4.647353172302246</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647352695465088</v>
+        <v>4.647353172302246</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997223854064941</v>
+        <v>6.997223377227783</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997223377227783</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997223377227783</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997223377227783</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959037780762</v>
+        <v>3.926958560943604</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587933540344238</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587933540344238</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587933540344238</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587933540344238</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68732929229736</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68732929229736</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68732929229736</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68732929229736</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988327026367188</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988327026367188</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988327026367188</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988327026367188</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -1832,16 +1832,16 @@
         <v>43684</v>
       </c>
       <c r="B71" t="n">
-        <v>11.66787815093994</v>
+        <v>11.66787719726562</v>
       </c>
       <c r="C71" t="n">
-        <v>11.66787815093994</v>
+        <v>11.66787719726562</v>
       </c>
       <c r="D71" t="n">
-        <v>11.66787815093994</v>
+        <v>11.66787719726562</v>
       </c>
       <c r="E71" t="n">
-        <v>11.66787815093994</v>
+        <v>11.66787719726562</v>
       </c>
       <c r="F71" t="n">
         <v>755</v>
@@ -1872,16 +1872,16 @@
         <v>43741</v>
       </c>
       <c r="B73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F73" t="n">
         <v>755</v>
@@ -1892,16 +1892,16 @@
         <v>43747</v>
       </c>
       <c r="B74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F74" t="n">
         <v>755</v>
@@ -1952,16 +1952,16 @@
         <v>43773</v>
       </c>
       <c r="B77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F77" t="n">
         <v>1510</v>
@@ -2012,16 +2012,16 @@
         <v>43802</v>
       </c>
       <c r="B80" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C80" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D80" t="n">
-        <v>9.21762282756219</v>
+        <v>9.217621990355065</v>
       </c>
       <c r="E80" t="n">
-        <v>9.21762282756219</v>
+        <v>9.217621990355065</v>
       </c>
       <c r="F80" t="n">
         <v>1510</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610008239746</v>
+        <v>10.60610103607178</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448353456507</v>
+        <v>11.08448453125444</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087006568908691</v>
+        <v>8.087005615234375</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167515198324406</v>
+        <v>8.167514235155968</v>
       </c>
       <c r="D103" t="n">
-        <v>7.93415690090921</v>
+        <v>7.934155965259957</v>
       </c>
       <c r="E103" t="n">
-        <v>7.992496475263009</v>
+        <v>7.99249553273396</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759139060974121</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151755156881</v>
+        <v>7.885152239738168</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395101374897398</v>
+        <v>7.395101829362682</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759139060974121</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198310852051</v>
+        <v>6.731198787689209</v>
       </c>
       <c r="C107" t="n">
-        <v>6.78487002388751</v>
+        <v>6.784870504526766</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975251402972</v>
+        <v>6.183975689474925</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242313978574833</v>
+        <v>6.242314420779493</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642459392547607</v>
+        <v>7.642459869384766</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934156405738198</v>
+        <v>7.934156900775253</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650690051923714</v>
+        <v>6.650690466881254</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251668627103</v>
+        <v>7.242252120494039</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2632,16 +2632,16 @@
         <v>43908</v>
       </c>
       <c r="B111" t="n">
-        <v>6.985558032989502</v>
+        <v>6.98555850982666</v>
       </c>
       <c r="C111" t="n">
-        <v>8.075337993481165</v>
+        <v>8.075338544707167</v>
       </c>
       <c r="D111" t="n">
-        <v>6.710196211513576</v>
+        <v>6.71019666955442</v>
       </c>
       <c r="E111" t="n">
-        <v>7.140740982312391</v>
+        <v>7.140741469742403</v>
       </c>
       <c r="F111" t="n">
         <v>26337960</v>
@@ -2652,16 +2652,16 @@
         <v>43909</v>
       </c>
       <c r="B112" t="n">
-        <v>7.521113872528076</v>
+        <v>7.521113395690918</v>
       </c>
       <c r="C112" t="n">
-        <v>8.106842473362253</v>
+        <v>8.106841959390016</v>
       </c>
       <c r="D112" t="n">
-        <v>6.35665992385914</v>
+        <v>6.356659520848136</v>
       </c>
       <c r="E112" t="n">
-        <v>6.779037133753115</v>
+        <v>6.779036703963478</v>
       </c>
       <c r="F112" t="n">
         <v>19250108</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314575195312</v>
+        <v>7.844314098358154</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109175099531829</v>
+        <v>8.109174606594431</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235251340767977</v>
+        <v>7.235250900954319</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146673416115</v>
+        <v>7.829146197500977</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469774723052979</v>
+        <v>7.469775676727295</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746303815364229</v>
+        <v>7.746304804343318</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351929151295045</v>
+        <v>7.351930089923889</v>
       </c>
       <c r="E118" t="n">
-        <v>7.51411282735269</v>
+        <v>7.514113786687701</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2792,16 +2792,16 @@
         <v>43920</v>
       </c>
       <c r="B119" t="n">
-        <v>7.58411979675293</v>
+        <v>7.584119319915771</v>
       </c>
       <c r="C119" t="n">
-        <v>7.677463445734158</v>
+        <v>7.677462963028194</v>
       </c>
       <c r="D119" t="n">
-        <v>7.322760268800774</v>
+        <v>7.322759808396101</v>
       </c>
       <c r="E119" t="n">
-        <v>7.354263351154514</v>
+        <v>7.354262888769144</v>
       </c>
       <c r="F119" t="n">
         <v>7283457</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469932556152</v>
+        <v>7.740469455718994</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757972392701939</v>
+        <v>7.757971914786575</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2832,16 +2832,16 @@
         <v>43922</v>
       </c>
       <c r="B121" t="n">
-        <v>7.461607456207275</v>
+        <v>7.461607933044434</v>
       </c>
       <c r="C121" t="n">
-        <v>7.642459196363636</v>
+        <v>7.642459684758201</v>
       </c>
       <c r="D121" t="n">
-        <v>7.304091207587605</v>
+        <v>7.304091674358621</v>
       </c>
       <c r="E121" t="n">
-        <v>7.619123704826946</v>
+        <v>7.619124191730246</v>
       </c>
       <c r="F121" t="n">
         <v>10218288</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613289356231689</v>
+        <v>7.613289833068848</v>
       </c>
       <c r="C124" t="n">
-        <v>7.699631846045301</v>
+        <v>7.699632328290281</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497777503819842</v>
+        <v>7.497777973422238</v>
       </c>
       <c r="E124" t="n">
-        <v>7.58411915326</v>
+        <v>7.584119628270164</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672796726226807</v>
+        <v>7.672797679901123</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109174958611256</v>
+        <v>8.109175966524298</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661128980388104</v>
+        <v>7.661129932612202</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840814283200555</v>
+        <v>7.840815257758265</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798988342285</v>
+        <v>7.700798511505127</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307612995673</v>
+        <v>7.781307131173381</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430989778177</v>
+        <v>7.362430533892927</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629934591736</v>
+        <v>7.678629459127295</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -2952,16 +2952,16 @@
         <v>43930</v>
       </c>
       <c r="B127" t="n">
-        <v>7.38576602935791</v>
+        <v>7.385766506195068</v>
       </c>
       <c r="C127" t="n">
-        <v>7.778973418970338</v>
+        <v>7.778973921193609</v>
       </c>
       <c r="D127" t="n">
-        <v>7.351929231575166</v>
+        <v>7.351929706227764</v>
       </c>
       <c r="E127" t="n">
-        <v>7.778973418970338</v>
+        <v>7.778973921193609</v>
       </c>
       <c r="F127" t="n">
         <v>7590081</v>
@@ -2972,16 +2972,16 @@
         <v>43934</v>
       </c>
       <c r="B128" t="n">
-        <v>7.41493558883667</v>
+        <v>7.414936065673828</v>
       </c>
       <c r="C128" t="n">
-        <v>7.447605949093313</v>
+        <v>7.447606428031426</v>
       </c>
       <c r="D128" t="n">
-        <v>7.229416415322526</v>
+        <v>7.22941688022938</v>
       </c>
       <c r="E128" t="n">
-        <v>7.385766224588598</v>
+        <v>7.385766699549943</v>
       </c>
       <c r="F128" t="n">
         <v>8873976</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566618919372559</v>
+        <v>7.5666184425354</v>
       </c>
       <c r="C131" t="n">
-        <v>7.58878797268838</v>
+        <v>7.588787494454161</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234083960008746</v>
+        <v>7.234083504127451</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444105906916389</v>
+        <v>7.44410543779982</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3072,16 +3072,16 @@
         <v>43941</v>
       </c>
       <c r="B133" t="n">
-        <v>7.58411979675293</v>
+        <v>7.584119319915771</v>
       </c>
       <c r="C133" t="n">
-        <v>7.592288227421651</v>
+        <v>7.592287750070918</v>
       </c>
       <c r="D133" t="n">
-        <v>7.316925555412612</v>
+        <v>7.316925095374786</v>
       </c>
       <c r="E133" t="n">
-        <v>7.350763195420438</v>
+        <v>7.350762733255134</v>
       </c>
       <c r="F133" t="n">
         <v>10524157</v>
@@ -3112,16 +3112,16 @@
         <v>43944</v>
       </c>
       <c r="B135" t="n">
-        <v>8.089339256286621</v>
+        <v>8.089340209960938</v>
       </c>
       <c r="C135" t="n">
-        <v>8.57472300766133</v>
+        <v>8.574724018558863</v>
       </c>
       <c r="D135" t="n">
-        <v>7.969159966917957</v>
+        <v>7.969160906424007</v>
       </c>
       <c r="E135" t="n">
-        <v>8.481379364431731</v>
+        <v>8.481380364324728</v>
       </c>
       <c r="F135" t="n">
         <v>13472583</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852481842041016</v>
+        <v>7.852482318878174</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764051870702</v>
+        <v>7.357764498666425</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3152,16 +3152,16 @@
         <v>43948</v>
       </c>
       <c r="B137" t="n">
-        <v>8.105673789978027</v>
+        <v>8.105674743652344</v>
       </c>
       <c r="C137" t="n">
-        <v>8.16517979671254</v>
+        <v>8.165180757388045</v>
       </c>
       <c r="D137" t="n">
-        <v>7.710133516824237</v>
+        <v>7.710134423961201</v>
       </c>
       <c r="E137" t="n">
-        <v>7.937657076955135</v>
+        <v>7.93765801086142</v>
       </c>
       <c r="F137" t="n">
         <v>12260436</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484073638916</v>
+        <v>7.887483596801758</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826254468098</v>
+        <v>7.966825772834317</v>
       </c>
       <c r="D139" t="n">
-        <v>7.70079846781684</v>
+        <v>7.700798002265745</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980371125938</v>
+        <v>7.841979897039702</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726467609405518</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817412213003</v>
+        <v>7.882817898699254</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726467609405518</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311096399979</v>
+        <v>7.816311578781807</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -3252,16 +3252,16 @@
         <v>43956</v>
       </c>
       <c r="B142" t="n">
-        <v>8.114091873168945</v>
+        <v>8.114090919494629</v>
       </c>
       <c r="C142" t="n">
-        <v>8.645024731663977</v>
+        <v>8.645023715587479</v>
       </c>
       <c r="D142" t="n">
-        <v>8.069433944133035</v>
+        <v>8.069432995707503</v>
       </c>
       <c r="E142" t="n">
-        <v>8.286521173623905</v>
+        <v>8.286520199683441</v>
       </c>
       <c r="F142" t="n">
         <v>11843548</v>
@@ -3272,16 +3272,16 @@
         <v>43957</v>
       </c>
       <c r="B143" t="n">
-        <v>8.048344612121582</v>
+        <v>8.048345565795898</v>
       </c>
       <c r="C143" t="n">
-        <v>8.145103893796581</v>
+        <v>8.145104858936216</v>
       </c>
       <c r="D143" t="n">
-        <v>7.96399105383742</v>
+        <v>7.963991997516411</v>
       </c>
       <c r="E143" t="n">
-        <v>8.145103893796581</v>
+        <v>8.145104858936216</v>
       </c>
       <c r="F143" t="n">
         <v>16545622</v>
@@ -3312,16 +3312,16 @@
         <v>43959</v>
       </c>
       <c r="B145" t="n">
-        <v>8.162470817565918</v>
+        <v>8.162469863891602</v>
       </c>
       <c r="C145" t="n">
-        <v>8.184800228116485</v>
+        <v>8.184799271833279</v>
       </c>
       <c r="D145" t="n">
-        <v>7.947864739756858</v>
+        <v>7.94786381115636</v>
       </c>
       <c r="E145" t="n">
-        <v>8.156268402071278</v>
+        <v>8.15626744912163</v>
       </c>
       <c r="F145" t="n">
         <v>8818844</v>
@@ -3352,16 +3352,16 @@
         <v>43963</v>
       </c>
       <c r="B147" t="n">
-        <v>8.085559844970703</v>
+        <v>8.085558891296387</v>
       </c>
       <c r="C147" t="n">
-        <v>8.276596387736546</v>
+        <v>8.276595411529883</v>
       </c>
       <c r="D147" t="n">
-        <v>8.063230434277379</v>
+        <v>8.063229483236768</v>
       </c>
       <c r="E147" t="n">
-        <v>8.187280531887918</v>
+        <v>8.187279566215866</v>
       </c>
       <c r="F147" t="n">
         <v>9953957</v>
@@ -3372,16 +3372,16 @@
         <v>43964</v>
       </c>
       <c r="B148" t="n">
-        <v>7.926775932312012</v>
+        <v>7.926775455474854</v>
       </c>
       <c r="C148" t="n">
-        <v>8.187280049800203</v>
+        <v>8.187279557292356</v>
       </c>
       <c r="D148" t="n">
-        <v>7.885840170888542</v>
+        <v>7.885839696513885</v>
       </c>
       <c r="E148" t="n">
-        <v>8.187280049800203</v>
+        <v>8.187279557292356</v>
       </c>
       <c r="F148" t="n">
         <v>10179016</v>
@@ -3412,16 +3412,16 @@
         <v>43966</v>
       </c>
       <c r="B150" t="n">
-        <v>6.841341018676758</v>
+        <v>6.8413405418396</v>
       </c>
       <c r="C150" t="n">
-        <v>7.421893621943401</v>
+        <v>7.421893104642092</v>
       </c>
       <c r="D150" t="n">
-        <v>6.841341018676758</v>
+        <v>6.8413405418396</v>
       </c>
       <c r="E150" t="n">
-        <v>7.420653049518127</v>
+        <v>7.420652532303285</v>
       </c>
       <c r="F150" t="n">
         <v>26563775</v>
@@ -3452,16 +3452,16 @@
         <v>43970</v>
       </c>
       <c r="B152" t="n">
-        <v>6.831417560577393</v>
+        <v>6.831418037414551</v>
       </c>
       <c r="C152" t="n">
-        <v>7.018731929050585</v>
+        <v>7.018732418962401</v>
       </c>
       <c r="D152" t="n">
-        <v>6.799164018747209</v>
+        <v>6.79916449333305</v>
       </c>
       <c r="E152" t="n">
-        <v>6.966631015976597</v>
+        <v>6.966631502251738</v>
       </c>
       <c r="F152" t="n">
         <v>13463520</v>
@@ -3472,16 +3472,16 @@
         <v>43971</v>
       </c>
       <c r="B153" t="n">
-        <v>6.822733402252197</v>
+        <v>6.822733879089355</v>
       </c>
       <c r="C153" t="n">
-        <v>6.983997533970078</v>
+        <v>6.983998022077899</v>
       </c>
       <c r="D153" t="n">
-        <v>6.81032857213493</v>
+        <v>6.810329048105121</v>
       </c>
       <c r="E153" t="n">
-        <v>6.946783490349408</v>
+        <v>6.94678397585636</v>
       </c>
       <c r="F153" t="n">
         <v>11533147</v>
@@ -3552,16 +3552,16 @@
         <v>43977</v>
       </c>
       <c r="B157" t="n">
-        <v>7.423134326934814</v>
+        <v>7.423134803771973</v>
       </c>
       <c r="C157" t="n">
-        <v>7.560828925689475</v>
+        <v>7.560829411371671</v>
       </c>
       <c r="D157" t="n">
-        <v>7.275514702466858</v>
+        <v>7.275515169821428</v>
       </c>
       <c r="E157" t="n">
-        <v>7.442982144705714</v>
+        <v>7.442982622817829</v>
       </c>
       <c r="F157" t="n">
         <v>12080691</v>
@@ -3612,16 +3612,16 @@
         <v>43980</v>
       </c>
       <c r="B160" t="n">
-        <v>7.812650680541992</v>
+        <v>7.812650203704834</v>
       </c>
       <c r="C160" t="n">
-        <v>7.812650680541992</v>
+        <v>7.812650203704834</v>
       </c>
       <c r="D160" t="n">
-        <v>7.481437500239227</v>
+        <v>7.481437043617326</v>
       </c>
       <c r="E160" t="n">
-        <v>7.519893458373339</v>
+        <v>7.519892999404318</v>
       </c>
       <c r="F160" t="n">
         <v>23712019</v>
@@ -3652,16 +3652,16 @@
         <v>43984</v>
       </c>
       <c r="B162" t="n">
-        <v>8.271635055541992</v>
+        <v>8.271634101867676</v>
       </c>
       <c r="C162" t="n">
-        <v>8.286521031632221</v>
+        <v>8.286520076241633</v>
       </c>
       <c r="D162" t="n">
-        <v>7.976396678662855</v>
+        <v>7.976395759027911</v>
       </c>
       <c r="E162" t="n">
-        <v>8.063230496816454</v>
+        <v>8.063229567170044</v>
       </c>
       <c r="F162" t="n">
         <v>21348142</v>
@@ -3672,16 +3672,16 @@
         <v>43985</v>
       </c>
       <c r="B163" t="n">
-        <v>8.373353958129883</v>
+        <v>8.373354911804199</v>
       </c>
       <c r="C163" t="n">
-        <v>8.80008582291646</v>
+        <v>8.800086825192951</v>
       </c>
       <c r="D163" t="n">
-        <v>8.315051079171372</v>
+        <v>8.315052026205343</v>
       </c>
       <c r="E163" t="n">
-        <v>8.31753222383259</v>
+        <v>8.317533171149149</v>
       </c>
       <c r="F163" t="n">
         <v>31125376</v>
@@ -3752,16 +3752,16 @@
         <v>43991</v>
       </c>
       <c r="B167" t="n">
-        <v>8.296443939208984</v>
+        <v>8.296442985534668</v>
       </c>
       <c r="C167" t="n">
-        <v>8.32745691101246</v>
+        <v>8.327455953773208</v>
       </c>
       <c r="D167" t="n">
-        <v>8.0967247251524</v>
+        <v>8.096723794435762</v>
       </c>
       <c r="E167" t="n">
-        <v>8.137661383332564</v>
+        <v>8.137660447910266</v>
       </c>
       <c r="F167" t="n">
         <v>13675741</v>
@@ -3772,16 +3772,16 @@
         <v>43992</v>
       </c>
       <c r="B168" t="n">
-        <v>8.089280128479004</v>
+        <v>8.08928108215332</v>
       </c>
       <c r="C168" t="n">
-        <v>8.426696138374464</v>
+        <v>8.426697131827968</v>
       </c>
       <c r="D168" t="n">
-        <v>8.037179665656195</v>
+        <v>8.0371806131882</v>
       </c>
       <c r="E168" t="n">
-        <v>8.311329615282364</v>
+        <v>8.311330595134894</v>
       </c>
       <c r="F168" t="n">
         <v>11944749</v>
@@ -3792,16 +3792,16 @@
         <v>43994</v>
       </c>
       <c r="B169" t="n">
-        <v>7.950345516204834</v>
+        <v>7.950345993041992</v>
       </c>
       <c r="C169" t="n">
-        <v>8.084319292912509</v>
+        <v>8.084319777785</v>
       </c>
       <c r="D169" t="n">
-        <v>7.774194958703272</v>
+        <v>7.774195424975465</v>
       </c>
       <c r="E169" t="n">
-        <v>7.877156659374939</v>
+        <v>7.877157131822456</v>
       </c>
       <c r="F169" t="n">
         <v>12251373</v>
@@ -3892,16 +3892,16 @@
         <v>44001</v>
       </c>
       <c r="B174" t="n">
-        <v>8.487481117248535</v>
+        <v>8.487480163574219</v>
       </c>
       <c r="C174" t="n">
-        <v>8.58920180321846</v>
+        <v>8.589200838114557</v>
       </c>
       <c r="D174" t="n">
-        <v>8.203407450651435</v>
+        <v>8.203406528896336</v>
       </c>
       <c r="E174" t="n">
-        <v>8.203407450651435</v>
+        <v>8.203406528896336</v>
       </c>
       <c r="F174" t="n">
         <v>20750754</v>
@@ -3912,16 +3912,16 @@
         <v>44004</v>
       </c>
       <c r="B175" t="n">
-        <v>8.440341949462891</v>
+        <v>8.440342903137207</v>
       </c>
       <c r="C175" t="n">
-        <v>8.729376978500955</v>
+        <v>8.729377964833343</v>
       </c>
       <c r="D175" t="n">
-        <v>8.380797159632158</v>
+        <v>8.380798106578508</v>
       </c>
       <c r="E175" t="n">
-        <v>8.489961267461833</v>
+        <v>8.489962226742637</v>
       </c>
       <c r="F175" t="n">
         <v>12069362</v>
@@ -3952,16 +3952,16 @@
         <v>44006</v>
       </c>
       <c r="B177" t="n">
-        <v>8.59416389465332</v>
+        <v>8.594162940979004</v>
       </c>
       <c r="C177" t="n">
-        <v>8.669833897798144</v>
+        <v>8.669832935726904</v>
       </c>
       <c r="D177" t="n">
-        <v>8.422974729757115</v>
+        <v>8.422973795079262</v>
       </c>
       <c r="E177" t="n">
-        <v>8.571834484683247</v>
+        <v>8.571833533486773</v>
       </c>
       <c r="F177" t="n">
         <v>7388434</v>
@@ -4052,16 +4052,16 @@
         <v>44013</v>
       </c>
       <c r="B182" t="n">
-        <v>9.009729385375977</v>
+        <v>9.009730339050293</v>
       </c>
       <c r="C182" t="n">
-        <v>9.115171330097578</v>
+        <v>9.11517229493286</v>
       </c>
       <c r="D182" t="n">
-        <v>8.731858165462054</v>
+        <v>8.731859089723871</v>
       </c>
       <c r="E182" t="n">
-        <v>8.812490451063802</v>
+        <v>8.812491383860499</v>
       </c>
       <c r="F182" t="n">
         <v>8963093</v>
@@ -4292,16 +4292,16 @@
         <v>44029</v>
       </c>
       <c r="B194" t="n">
-        <v>8.819933891296387</v>
+        <v>8.81993293762207</v>
       </c>
       <c r="C194" t="n">
-        <v>8.919174324825571</v>
+        <v>8.919173360420668</v>
       </c>
       <c r="D194" t="n">
-        <v>8.633859641988225</v>
+        <v>8.633858708433587</v>
       </c>
       <c r="E194" t="n">
-        <v>8.633859641988225</v>
+        <v>8.633858708433587</v>
       </c>
       <c r="F194" t="n">
         <v>9678298</v>
@@ -4432,16 +4432,16 @@
         <v>44040</v>
       </c>
       <c r="B201" t="n">
-        <v>9.641142845153809</v>
+        <v>9.641143798828125</v>
       </c>
       <c r="C201" t="n">
-        <v>9.832179367263814</v>
+        <v>9.832180339834917</v>
       </c>
       <c r="D201" t="n">
-        <v>9.466232422996864</v>
+        <v>9.466233359369541</v>
       </c>
       <c r="E201" t="n">
-        <v>9.67587708316008</v>
+        <v>9.675878040270206</v>
       </c>
       <c r="F201" t="n">
         <v>30127714</v>
@@ -4472,16 +4472,16 @@
         <v>44042</v>
       </c>
       <c r="B203" t="n">
-        <v>9.143703460693359</v>
+        <v>9.143704414367676</v>
       </c>
       <c r="C203" t="n">
-        <v>9.700686938306321</v>
+        <v>9.700687950073165</v>
       </c>
       <c r="D203" t="n">
-        <v>9.097805411083952</v>
+        <v>9.097806359971171</v>
       </c>
       <c r="E203" t="n">
-        <v>9.685800070178546</v>
+        <v>9.685801080392711</v>
       </c>
       <c r="F203" t="n">
         <v>33272500</v>
@@ -4592,16 +4592,16 @@
         <v>44050</v>
       </c>
       <c r="B209" t="n">
-        <v>8.429178237915039</v>
+        <v>8.429177284240723</v>
       </c>
       <c r="C209" t="n">
-        <v>8.429178237915039</v>
+        <v>8.429177284240723</v>
       </c>
       <c r="D209" t="n">
-        <v>8.25550792408546</v>
+        <v>8.255506990060143</v>
       </c>
       <c r="E209" t="n">
-        <v>8.336141112251321</v>
+        <v>8.336140169103194</v>
       </c>
       <c r="F209" t="n">
         <v>22110172</v>
@@ -4612,16 +4612,16 @@
         <v>44053</v>
       </c>
       <c r="B210" t="n">
-        <v>8.25922966003418</v>
+        <v>8.259230613708496</v>
       </c>
       <c r="C210" t="n">
-        <v>8.468873436704216</v>
+        <v>8.468874414585619</v>
       </c>
       <c r="D210" t="n">
-        <v>8.166191645730668</v>
+        <v>8.166192588662099</v>
       </c>
       <c r="E210" t="n">
-        <v>8.435379322693057</v>
+        <v>8.435380296706972</v>
       </c>
       <c r="F210" t="n">
         <v>21920608</v>
@@ -4652,16 +4652,16 @@
         <v>44055</v>
       </c>
       <c r="B212" t="n">
-        <v>8.162470817565918</v>
+        <v>8.162469863891602</v>
       </c>
       <c r="C212" t="n">
-        <v>8.446544484992341</v>
+        <v>8.446543498127859</v>
       </c>
       <c r="D212" t="n">
-        <v>8.078116358606623</v>
+        <v>8.078115414787984</v>
       </c>
       <c r="E212" t="n">
-        <v>8.409329992024503</v>
+        <v>8.409329009508031</v>
       </c>
       <c r="F212" t="n">
         <v>20200945</v>
@@ -4732,16 +4732,16 @@
         <v>44061</v>
       </c>
       <c r="B216" t="n">
-        <v>8.101685523986816</v>
+        <v>8.101686477661133</v>
       </c>
       <c r="C216" t="n">
-        <v>8.143863198266791</v>
+        <v>8.143864156905972</v>
       </c>
       <c r="D216" t="n">
-        <v>7.978877345430011</v>
+        <v>7.9788782846482</v>
       </c>
       <c r="E216" t="n">
-        <v>8.038420352760289</v>
+        <v>8.038421298987467</v>
       </c>
       <c r="F216" t="n">
         <v>10608743</v>
@@ -4752,16 +4752,16 @@
         <v>44062</v>
       </c>
       <c r="B217" t="n">
-        <v>7.926775932312012</v>
+        <v>7.926775455474854</v>
       </c>
       <c r="C217" t="n">
-        <v>8.141381998856557</v>
+        <v>8.141381509109719</v>
       </c>
       <c r="D217" t="n">
-        <v>7.921813642791834</v>
+        <v>7.921813166253184</v>
       </c>
       <c r="E217" t="n">
-        <v>8.141381998856557</v>
+        <v>8.141381509109719</v>
       </c>
       <c r="F217" t="n">
         <v>9466833</v>
@@ -4772,16 +4772,16 @@
         <v>44063</v>
       </c>
       <c r="B218" t="n">
-        <v>7.957787990570068</v>
+        <v>7.957788467407227</v>
       </c>
       <c r="C218" t="n">
-        <v>8.033458885005254</v>
+        <v>8.033459366376674</v>
       </c>
       <c r="D218" t="n">
-        <v>7.774194893738959</v>
+        <v>7.774195359575069</v>
       </c>
       <c r="E218" t="n">
-        <v>7.915611210128628</v>
+        <v>7.915611684438519</v>
       </c>
       <c r="F218" t="n">
         <v>7652765</v>
@@ -4892,16 +4892,16 @@
         <v>44071</v>
       </c>
       <c r="B224" t="n">
-        <v>8.100444793701172</v>
+        <v>8.100445747375488</v>
       </c>
       <c r="C224" t="n">
-        <v>8.100444793701172</v>
+        <v>8.100445747375488</v>
       </c>
       <c r="D224" t="n">
-        <v>7.960268612170143</v>
+        <v>7.960269549341362</v>
       </c>
       <c r="E224" t="n">
-        <v>8.001206157737258</v>
+        <v>8.0012070997281</v>
       </c>
       <c r="F224" t="n">
         <v>5577388</v>
@@ -5012,16 +5012,16 @@
         <v>44082</v>
       </c>
       <c r="B230" t="n">
-        <v>7.751865386962891</v>
+        <v>7.751865863800049</v>
       </c>
       <c r="C230" t="n">
-        <v>7.833737802061967</v>
+        <v>7.833738283935308</v>
       </c>
       <c r="D230" t="n">
-        <v>7.691081361819436</v>
+        <v>7.691081834917614</v>
       </c>
       <c r="E230" t="n">
-        <v>7.813890431199186</v>
+        <v>7.813890911851665</v>
       </c>
       <c r="F230" t="n">
         <v>7181501</v>
@@ -5032,16 +5032,16 @@
         <v>44083</v>
       </c>
       <c r="B231" t="n">
-        <v>7.709689140319824</v>
+        <v>7.709688663482666</v>
       </c>
       <c r="C231" t="n">
-        <v>7.834980256551466</v>
+        <v>7.834979771965168</v>
       </c>
       <c r="D231" t="n">
-        <v>7.637740405675546</v>
+        <v>7.637739933288351</v>
       </c>
       <c r="E231" t="n">
-        <v>7.792802580260581</v>
+        <v>7.792802098282933</v>
       </c>
       <c r="F231" t="n">
         <v>8282629</v>
@@ -5052,16 +5052,16 @@
         <v>44084</v>
       </c>
       <c r="B232" t="n">
-        <v>8.850946426391602</v>
+        <v>8.850947380065918</v>
       </c>
       <c r="C232" t="n">
-        <v>9.197044227170217</v>
+        <v>9.197045218135978</v>
       </c>
       <c r="D232" t="n">
-        <v>8.62145438702172</v>
+        <v>8.621455315968662</v>
       </c>
       <c r="E232" t="n">
-        <v>9.197044227170217</v>
+        <v>9.197045218135978</v>
       </c>
       <c r="F232" t="n">
         <v>139609921</v>
@@ -5132,16 +5132,16 @@
         <v>44090</v>
       </c>
       <c r="B236" t="n">
-        <v>9.312411308288574</v>
+        <v>9.312410354614258</v>
       </c>
       <c r="C236" t="n">
-        <v>9.375676482213272</v>
+        <v>9.375675522060035</v>
       </c>
       <c r="D236" t="n">
-        <v>9.175957274371282</v>
+        <v>9.175956334671081</v>
       </c>
       <c r="E236" t="n">
-        <v>9.179678544963952</v>
+        <v>9.179677604882659</v>
       </c>
       <c r="F236" t="n">
         <v>13993693</v>
@@ -5212,16 +5212,16 @@
         <v>44096</v>
       </c>
       <c r="B240" t="n">
-        <v>9.326057434082031</v>
+        <v>9.326058387756348</v>
       </c>
       <c r="C240" t="n">
-        <v>9.353348239057649</v>
+        <v>9.353349195522698</v>
       </c>
       <c r="D240" t="n">
-        <v>9.182158188124824</v>
+        <v>9.182159127084132</v>
       </c>
       <c r="E240" t="n">
-        <v>9.192082766997606</v>
+        <v>9.192083706971793</v>
       </c>
       <c r="F240" t="n">
         <v>9315031</v>
@@ -5232,16 +5232,16 @@
         <v>44097</v>
       </c>
       <c r="B241" t="n">
-        <v>8.953908920288086</v>
+        <v>8.95390796661377</v>
       </c>
       <c r="C241" t="n">
-        <v>9.308690312405352</v>
+        <v>9.308689320943529</v>
       </c>
       <c r="D241" t="n">
-        <v>8.934060654104224</v>
+        <v>8.934059702543932</v>
       </c>
       <c r="E241" t="n">
-        <v>9.303728915956151</v>
+        <v>9.303727925022763</v>
       </c>
       <c r="F241" t="n">
         <v>13677251</v>
@@ -5252,16 +5252,16 @@
         <v>44098</v>
       </c>
       <c r="B242" t="n">
-        <v>9.282638549804688</v>
+        <v>9.282639503479004</v>
       </c>
       <c r="C242" t="n">
-        <v>9.463751388941567</v>
+        <v>9.46375236122295</v>
       </c>
       <c r="D242" t="n">
-        <v>8.898084356453305</v>
+        <v>8.898085270619518</v>
       </c>
       <c r="E242" t="n">
-        <v>8.906768809518589</v>
+        <v>8.906769724577019</v>
       </c>
       <c r="F242" t="n">
         <v>18607406</v>
@@ -5272,16 +5272,16 @@
         <v>44099</v>
       </c>
       <c r="B243" t="n">
-        <v>9.184639930725098</v>
+        <v>9.184640884399414</v>
       </c>
       <c r="C243" t="n">
-        <v>9.25410751328763</v>
+        <v>9.254108474175018</v>
       </c>
       <c r="D243" t="n">
-        <v>9.095324084518023</v>
+        <v>9.095325028918353</v>
       </c>
       <c r="E243" t="n">
-        <v>9.220613400863298</v>
+        <v>9.22061435827287</v>
       </c>
       <c r="F243" t="n">
         <v>8201819</v>
@@ -5312,16 +5312,16 @@
         <v>44103</v>
       </c>
       <c r="B245" t="n">
-        <v>8.760391235351562</v>
+        <v>8.760390281677246</v>
       </c>
       <c r="C245" t="n">
-        <v>8.942744221459206</v>
+        <v>8.942743247933565</v>
       </c>
       <c r="D245" t="n">
-        <v>8.68348020897627</v>
+        <v>8.683479263674647</v>
       </c>
       <c r="E245" t="n">
-        <v>8.802568019244504</v>
+        <v>8.802567060978735</v>
       </c>
       <c r="F245" t="n">
         <v>13985386</v>
@@ -5332,16 +5332,16 @@
         <v>44104</v>
       </c>
       <c r="B246" t="n">
-        <v>8.651226043701172</v>
+        <v>8.651226997375488</v>
       </c>
       <c r="C246" t="n">
-        <v>8.841022441256731</v>
+        <v>8.841023415853394</v>
       </c>
       <c r="D246" t="n">
-        <v>8.609049265013768</v>
+        <v>8.609050214038696</v>
       </c>
       <c r="E246" t="n">
-        <v>8.803807058409923</v>
+        <v>8.803808028904122</v>
       </c>
       <c r="F246" t="n">
         <v>11477260</v>
@@ -5412,16 +5412,16 @@
         <v>44110</v>
       </c>
       <c r="B250" t="n">
-        <v>8.497405052185059</v>
+        <v>8.497404098510742</v>
       </c>
       <c r="C250" t="n">
-        <v>8.520974589071102</v>
+        <v>8.520973632751547</v>
       </c>
       <c r="D250" t="n">
-        <v>8.316293085426295</v>
+        <v>8.3162921520784</v>
       </c>
       <c r="E250" t="n">
-        <v>8.488721491571129</v>
+        <v>8.48872053887138</v>
       </c>
       <c r="F250" t="n">
         <v>10544549</v>
@@ -5432,16 +5432,16 @@
         <v>44111</v>
       </c>
       <c r="B251" t="n">
-        <v>8.585480690002441</v>
+        <v>8.585479736328125</v>
       </c>
       <c r="C251" t="n">
-        <v>8.704568498874545</v>
+        <v>8.704567531971968</v>
       </c>
       <c r="D251" t="n">
-        <v>8.440343093036322</v>
+        <v>8.440342155483876</v>
       </c>
       <c r="E251" t="n">
-        <v>8.477557586577683</v>
+        <v>8.477556644891454</v>
       </c>
       <c r="F251" t="n">
         <v>12680345</v>
@@ -5552,16 +5552,16 @@
         <v>44120</v>
       </c>
       <c r="B257" t="n">
-        <v>8.25922966003418</v>
+        <v>8.259230613708496</v>
       </c>
       <c r="C257" t="n">
-        <v>8.267912326486389</v>
+        <v>8.267913281163274</v>
       </c>
       <c r="D257" t="n">
-        <v>8.097964185523827</v>
+        <v>8.097965120577188</v>
       </c>
       <c r="E257" t="n">
-        <v>8.122774739620494</v>
+        <v>8.122775677538673</v>
       </c>
       <c r="F257" t="n">
         <v>10726560</v>
@@ -5612,16 +5612,16 @@
         <v>44125</v>
       </c>
       <c r="B260" t="n">
-        <v>8.275355339050293</v>
+        <v>8.275356292724609</v>
       </c>
       <c r="C260" t="n">
-        <v>8.355987625465389</v>
+        <v>8.355988588431988</v>
       </c>
       <c r="D260" t="n">
-        <v>8.245583390421267</v>
+        <v>8.245584340664582</v>
       </c>
       <c r="E260" t="n">
-        <v>8.354747499881778</v>
+        <v>8.35474846270546</v>
       </c>
       <c r="F260" t="n">
         <v>4665068</v>
@@ -5632,16 +5632,16 @@
         <v>44126</v>
       </c>
       <c r="B261" t="n">
-        <v>8.267911911010742</v>
+        <v>8.267912864685059</v>
       </c>
       <c r="C261" t="n">
-        <v>8.337380386835774</v>
+        <v>8.337381348523031</v>
       </c>
       <c r="D261" t="n">
-        <v>8.168673273460097</v>
+        <v>8.168674215687588</v>
       </c>
       <c r="E261" t="n">
-        <v>8.30636741913896</v>
+        <v>8.306368377248981</v>
       </c>
       <c r="F261" t="n">
         <v>7908034</v>
@@ -5652,16 +5652,16 @@
         <v>44127</v>
       </c>
       <c r="B262" t="n">
-        <v>8.234419822692871</v>
+        <v>8.234420776367188</v>
       </c>
       <c r="C262" t="n">
-        <v>8.312570966783923</v>
+        <v>8.312571929509362</v>
       </c>
       <c r="D262" t="n">
-        <v>8.203406854103131</v>
+        <v>8.203407804185662</v>
       </c>
       <c r="E262" t="n">
-        <v>8.269152274680931</v>
+        <v>8.269153232377807</v>
       </c>
       <c r="F262" t="n">
         <v>5098571</v>
@@ -5712,16 +5712,16 @@
         <v>44132</v>
       </c>
       <c r="B265" t="n">
-        <v>7.825055599212646</v>
+        <v>7.825055122375488</v>
       </c>
       <c r="C265" t="n">
-        <v>8.088040873150774</v>
+        <v>8.088040380288025</v>
       </c>
       <c r="D265" t="n">
-        <v>7.817612164601516</v>
+        <v>7.81761168821794</v>
       </c>
       <c r="E265" t="n">
-        <v>8.078116293669268</v>
+        <v>8.078115801411293</v>
       </c>
       <c r="F265" t="n">
         <v>12369944</v>
@@ -5752,16 +5752,16 @@
         <v>44134</v>
       </c>
       <c r="B267" t="n">
-        <v>7.684878826141357</v>
+        <v>7.684879302978516</v>
       </c>
       <c r="C267" t="n">
-        <v>7.777915944304612</v>
+        <v>7.777916426914608</v>
       </c>
       <c r="D267" t="n">
-        <v>7.574474588649013</v>
+        <v>7.574475058635726</v>
       </c>
       <c r="E267" t="n">
-        <v>7.759308699364413</v>
+        <v>7.759309180819852</v>
       </c>
       <c r="F267" t="n">
         <v>16269207</v>
@@ -5772,16 +5772,16 @@
         <v>44138</v>
       </c>
       <c r="B268" t="n">
-        <v>7.717131614685059</v>
+        <v>7.7171311378479</v>
       </c>
       <c r="C268" t="n">
-        <v>7.852346415863062</v>
+        <v>7.852345930671059</v>
       </c>
       <c r="D268" t="n">
-        <v>7.622854363726927</v>
+        <v>7.622853892715106</v>
       </c>
       <c r="E268" t="n">
-        <v>7.821334338599661</v>
+        <v>7.821333855323877</v>
       </c>
       <c r="F268" t="n">
         <v>9901091</v>
@@ -5812,16 +5812,16 @@
         <v>44140</v>
       </c>
       <c r="B270" t="n">
-        <v>8.119053840637207</v>
+        <v>8.119052886962891</v>
       </c>
       <c r="C270" t="n">
-        <v>8.177356724487632</v>
+        <v>8.177355763964984</v>
       </c>
       <c r="D270" t="n">
-        <v>8.007408575750512</v>
+        <v>8.007407635190189</v>
       </c>
       <c r="E270" t="n">
-        <v>8.039661672128053</v>
+        <v>8.039660727779241</v>
       </c>
       <c r="F270" t="n">
         <v>9820281</v>
@@ -5892,16 +5892,16 @@
         <v>44146</v>
       </c>
       <c r="B274" t="n">
-        <v>8.193483352661133</v>
+        <v>8.193482398986816</v>
       </c>
       <c r="C274" t="n">
-        <v>8.420494274138473</v>
+        <v>8.420493294041393</v>
       </c>
       <c r="D274" t="n">
-        <v>8.193483352661133</v>
+        <v>8.193482398986816</v>
       </c>
       <c r="E274" t="n">
-        <v>8.312572059811611</v>
+        <v>8.312571092276054</v>
       </c>
       <c r="F274" t="n">
         <v>7246451</v>
@@ -5912,16 +5912,16 @@
         <v>44147</v>
       </c>
       <c r="B275" t="n">
-        <v>8.234419822692871</v>
+        <v>8.234420776367188</v>
       </c>
       <c r="C275" t="n">
-        <v>8.398164651520666</v>
+        <v>8.398165624159189</v>
       </c>
       <c r="D275" t="n">
-        <v>8.131458125037573</v>
+        <v>8.13145906678732</v>
       </c>
       <c r="E275" t="n">
-        <v>8.193482275292528</v>
+        <v>8.193483224225638</v>
       </c>
       <c r="F275" t="n">
         <v>11697033</v>
@@ -5932,16 +5932,16 @@
         <v>44148</v>
       </c>
       <c r="B276" t="n">
-        <v>8.633858680725098</v>
+        <v>8.633859634399414</v>
       </c>
       <c r="C276" t="n">
-        <v>8.646264403631776</v>
+        <v>8.646265358676397</v>
       </c>
       <c r="D276" t="n">
-        <v>8.267911744802472</v>
+        <v>8.267912658055211</v>
       </c>
       <c r="E276" t="n">
-        <v>8.322493351742979</v>
+        <v>8.322494271024663</v>
       </c>
       <c r="F276" t="n">
         <v>10854949</v>
@@ -5992,16 +5992,16 @@
         <v>44153</v>
       </c>
       <c r="B279" t="n">
-        <v>8.584239959716797</v>
+        <v>8.584240913391113</v>
       </c>
       <c r="C279" t="n">
-        <v>8.64502398560519</v>
+        <v>8.645024946032365</v>
       </c>
       <c r="D279" t="n">
-        <v>8.516012499566937</v>
+        <v>8.516013445661457</v>
       </c>
       <c r="E279" t="n">
-        <v>8.55818927999508</v>
+        <v>8.558190230775271</v>
       </c>
       <c r="F279" t="n">
         <v>8922310</v>
@@ -6072,16 +6072,16 @@
         <v>44160</v>
       </c>
       <c r="B283" t="n">
-        <v>8.739301681518555</v>
+        <v>8.739302635192871</v>
       </c>
       <c r="C283" t="n">
-        <v>8.920413624337439</v>
+        <v>8.920414597775554</v>
       </c>
       <c r="D283" t="n">
-        <v>8.616491723410208</v>
+        <v>8.616492663682914</v>
       </c>
       <c r="E283" t="n">
-        <v>8.854667312281327</v>
+        <v>8.85466827854489</v>
       </c>
       <c r="F283" t="n">
         <v>6633202</v>
@@ -6112,16 +6112,16 @@
         <v>44162</v>
       </c>
       <c r="B285" t="n">
-        <v>8.615251541137695</v>
+        <v>8.615252494812012</v>
       </c>
       <c r="C285" t="n">
-        <v>8.70828776310049</v>
+        <v>8.708288727073548</v>
       </c>
       <c r="D285" t="n">
-        <v>8.507328451506179</v>
+        <v>8.507329393233835</v>
       </c>
       <c r="E285" t="n">
-        <v>8.566871454869922</v>
+        <v>8.566872403188754</v>
       </c>
       <c r="F285" t="n">
         <v>5230736</v>
@@ -6152,16 +6152,16 @@
         <v>44166</v>
       </c>
       <c r="B287" t="n">
-        <v>8.414291381835938</v>
+        <v>8.414292335510254</v>
       </c>
       <c r="C287" t="n">
-        <v>8.672314340510058</v>
+        <v>8.672315323428652</v>
       </c>
       <c r="D287" t="n">
-        <v>8.360949006055193</v>
+        <v>8.360949953683695</v>
       </c>
       <c r="E287" t="n">
-        <v>8.636339977103933</v>
+        <v>8.636340955945199</v>
       </c>
       <c r="F287" t="n">
         <v>16096259</v>
@@ -6172,16 +6172,16 @@
         <v>44167</v>
       </c>
       <c r="B288" t="n">
-        <v>8.282797813415527</v>
+        <v>8.282798767089844</v>
       </c>
       <c r="C288" t="n">
-        <v>8.461429503764982</v>
+        <v>8.4614304780068</v>
       </c>
       <c r="D288" t="n">
-        <v>8.199685276496087</v>
+        <v>8.199686220600897</v>
       </c>
       <c r="E288" t="n">
-        <v>8.456468108007872</v>
+        <v>8.456469081678438</v>
       </c>
       <c r="F288" t="n">
         <v>15329699</v>
@@ -6212,16 +6212,16 @@
         <v>44169</v>
       </c>
       <c r="B290" t="n">
-        <v>8.772793769836426</v>
+        <v>8.772794723510742</v>
       </c>
       <c r="C290" t="n">
-        <v>8.948944312102428</v>
+        <v>8.948945284925747</v>
       </c>
       <c r="D290" t="n">
-        <v>8.683478819885265</v>
+        <v>8.683479763850318</v>
       </c>
       <c r="E290" t="n">
-        <v>8.886919271932774</v>
+        <v>8.886920238013465</v>
       </c>
       <c r="F290" t="n">
         <v>10446369</v>
@@ -6232,16 +6232,16 @@
         <v>44172</v>
       </c>
       <c r="B291" t="n">
-        <v>8.647505760192871</v>
+        <v>8.647504806518555</v>
       </c>
       <c r="C291" t="n">
-        <v>8.82737759966732</v>
+        <v>8.827376626156168</v>
       </c>
       <c r="D291" t="n">
-        <v>8.621455078573774</v>
+        <v>8.621454127772409</v>
       </c>
       <c r="E291" t="n">
-        <v>8.807529333653388</v>
+        <v>8.807528362331166</v>
       </c>
       <c r="F291" t="n">
         <v>10174485</v>
@@ -6392,16 +6392,16 @@
         <v>44182</v>
       </c>
       <c r="B299" t="n">
-        <v>9.125096321105957</v>
+        <v>9.125097274780273</v>
       </c>
       <c r="C299" t="n">
-        <v>9.233019415311725</v>
+        <v>9.233020380265208</v>
       </c>
       <c r="D299" t="n">
-        <v>9.1052480568353</v>
+        <v>9.105249008435251</v>
       </c>
       <c r="E299" t="n">
-        <v>9.230538270595108</v>
+        <v>9.230539235289285</v>
       </c>
       <c r="F299" t="n">
         <v>5262456</v>
@@ -6452,16 +6452,16 @@
         <v>44187</v>
       </c>
       <c r="B302" t="n">
-        <v>9.018413543701172</v>
+        <v>9.018414497375488</v>
       </c>
       <c r="C302" t="n">
-        <v>9.117653080233614</v>
+        <v>9.117654044402261</v>
       </c>
       <c r="D302" t="n">
-        <v>8.941503416629342</v>
+        <v>8.941504362170608</v>
       </c>
       <c r="E302" t="n">
-        <v>8.974995743895692</v>
+        <v>8.974996692978687</v>
       </c>
       <c r="F302" t="n">
         <v>3700636</v>
@@ -6572,16 +6572,16 @@
         <v>44201</v>
       </c>
       <c r="B308" t="n">
-        <v>9.097805023193359</v>
+        <v>9.097805976867676</v>
       </c>
       <c r="C308" t="n">
-        <v>9.304967640603</v>
+        <v>9.304968615993069</v>
       </c>
       <c r="D308" t="n">
-        <v>9.012210449150441</v>
+        <v>9.012211393852336</v>
       </c>
       <c r="E308" t="n">
-        <v>9.304967640603</v>
+        <v>9.304968615993069</v>
       </c>
       <c r="F308" t="n">
         <v>8306796</v>
@@ -6592,16 +6592,16 @@
         <v>44202</v>
       </c>
       <c r="B309" t="n">
-        <v>9.02337646484375</v>
+        <v>9.023375511169434</v>
       </c>
       <c r="C309" t="n">
-        <v>9.178438642419241</v>
+        <v>9.178437672356514</v>
       </c>
       <c r="D309" t="n">
-        <v>8.883200263463204</v>
+        <v>8.883199324604012</v>
       </c>
       <c r="E309" t="n">
-        <v>9.091603036730099</v>
+        <v>9.091602075844966</v>
       </c>
       <c r="F309" t="n">
         <v>6995714</v>
@@ -6632,16 +6632,16 @@
         <v>44204</v>
       </c>
       <c r="B311" t="n">
-        <v>9.494765281677246</v>
+        <v>9.49476432800293</v>
       </c>
       <c r="C311" t="n">
-        <v>9.533220794103377</v>
+        <v>9.533219836566508</v>
       </c>
       <c r="D311" t="n">
-        <v>9.077957953992263</v>
+        <v>9.077957042182957</v>
       </c>
       <c r="E311" t="n">
-        <v>9.178438515281906</v>
+        <v>9.178437593380119</v>
       </c>
       <c r="F311" t="n">
         <v>10280973</v>
@@ -6732,16 +6732,16 @@
         <v>44211</v>
       </c>
       <c r="B316" t="n">
-        <v>9.479878425598145</v>
+        <v>9.479877471923828</v>
       </c>
       <c r="C316" t="n">
-        <v>9.607649794137002</v>
+        <v>9.607648827608905</v>
       </c>
       <c r="D316" t="n">
-        <v>9.378158631904267</v>
+        <v>9.378157688462947</v>
       </c>
       <c r="E316" t="n">
-        <v>9.589042547490402</v>
+        <v>9.589041582834192</v>
       </c>
       <c r="F316" t="n">
         <v>14334303</v>
@@ -6892,16 +6892,16 @@
         <v>44224</v>
       </c>
       <c r="B324" t="n">
-        <v>9.368232727050781</v>
+        <v>9.368233680725098</v>
       </c>
       <c r="C324" t="n">
-        <v>9.399244800408228</v>
+        <v>9.399245757239534</v>
       </c>
       <c r="D324" t="n">
-        <v>9.102766341339521</v>
+        <v>9.102767267989694</v>
       </c>
       <c r="E324" t="n">
-        <v>9.180917480970056</v>
+        <v>9.180918415575915</v>
       </c>
       <c r="F324" t="n">
         <v>7429217</v>
@@ -6912,16 +6912,16 @@
         <v>44225</v>
       </c>
       <c r="B325" t="n">
-        <v>9.363271713256836</v>
+        <v>9.36327075958252</v>
       </c>
       <c r="C325" t="n">
-        <v>9.571676269761104</v>
+        <v>9.571675294860224</v>
       </c>
       <c r="D325" t="n">
-        <v>9.215652973121827</v>
+        <v>9.215652034482874</v>
       </c>
       <c r="E325" t="n">
-        <v>9.312411369945844</v>
+        <v>9.312410421451789</v>
       </c>
       <c r="F325" t="n">
         <v>11022611</v>
@@ -6952,16 +6952,16 @@
         <v>44229</v>
       </c>
       <c r="B327" t="n">
-        <v>10.13361930847168</v>
+        <v>10.133620262146</v>
       </c>
       <c r="C327" t="n">
-        <v>10.18447964681817</v>
+        <v>10.18448060527895</v>
       </c>
       <c r="D327" t="n">
-        <v>9.832179442109044</v>
+        <v>9.832180367414875</v>
       </c>
       <c r="E327" t="n">
-        <v>10.11004977442547</v>
+        <v>10.11005072588166</v>
       </c>
       <c r="F327" t="n">
         <v>20046878</v>
@@ -6992,16 +6992,16 @@
         <v>44231</v>
       </c>
       <c r="B329" t="n">
-        <v>10.38668251037598</v>
+        <v>10.38668155670166</v>
       </c>
       <c r="C329" t="n">
-        <v>10.38668251037598</v>
+        <v>10.38668155670166</v>
       </c>
       <c r="D329" t="n">
-        <v>10.11749393146458</v>
+        <v>10.11749300250636</v>
       </c>
       <c r="E329" t="n">
-        <v>10.17703872709649</v>
+        <v>10.17703779267104</v>
       </c>
       <c r="F329" t="n">
         <v>12166787</v>
@@ -7012,16 +7012,16 @@
         <v>44232</v>
       </c>
       <c r="B330" t="n">
-        <v>10.55663013458252</v>
+        <v>10.5566291809082</v>
       </c>
       <c r="C330" t="n">
-        <v>10.58144069033415</v>
+        <v>10.58143973441847</v>
       </c>
       <c r="D330" t="n">
-        <v>10.32465782656054</v>
+        <v>10.32465689384235</v>
       </c>
       <c r="E330" t="n">
-        <v>10.41893507933724</v>
+        <v>10.41893413810214</v>
       </c>
       <c r="F330" t="n">
         <v>10745440</v>
@@ -7192,16 +7192,16 @@
         <v>44249</v>
       </c>
       <c r="B339" t="n">
-        <v>11.09376525878906</v>
+        <v>11.09376621246338</v>
       </c>
       <c r="C339" t="n">
-        <v>11.20292847746345</v>
+        <v>11.20292944052197</v>
       </c>
       <c r="D339" t="n">
-        <v>10.63602131403072</v>
+        <v>10.63602222835513</v>
       </c>
       <c r="E339" t="n">
-        <v>10.9399432226141</v>
+        <v>10.93994416306512</v>
       </c>
       <c r="F339" t="n">
         <v>14982292</v>
@@ -7292,16 +7292,16 @@
         <v>44256</v>
       </c>
       <c r="B344" t="n">
-        <v>21.85701751708984</v>
+        <v>21.85701560974121</v>
       </c>
       <c r="C344" t="n">
-        <v>23.99306617161</v>
+        <v>23.99306407785948</v>
       </c>
       <c r="D344" t="n">
-        <v>16.31078752172449</v>
+        <v>16.3107860983666</v>
       </c>
       <c r="E344" t="n">
-        <v>16.86353693074166</v>
+        <v>16.8635354591482</v>
       </c>
       <c r="F344" t="n">
         <v>49361500</v>
@@ -7312,16 +7312,16 @@
         <v>44257</v>
       </c>
       <c r="B345" t="n">
-        <v>21.19184494018555</v>
+        <v>21.19184303283691</v>
       </c>
       <c r="C345" t="n">
-        <v>22.95314685108304</v>
+        <v>22.95314478521037</v>
       </c>
       <c r="D345" t="n">
-        <v>20.69530683439987</v>
+        <v>20.6953049717416</v>
       </c>
       <c r="E345" t="n">
-        <v>22.18491936483229</v>
+        <v>22.18491736810308</v>
       </c>
       <c r="F345" t="n">
         <v>20095700</v>
@@ -7352,16 +7352,16 @@
         <v>44259</v>
       </c>
       <c r="B347" t="n">
-        <v>20.86394309997559</v>
+        <v>20.86394119262695</v>
       </c>
       <c r="C347" t="n">
-        <v>21.52911508897337</v>
+        <v>21.52911312081577</v>
       </c>
       <c r="D347" t="n">
-        <v>20.0113977633286</v>
+        <v>20.01139593391831</v>
       </c>
       <c r="E347" t="n">
-        <v>20.23624470835284</v>
+        <v>20.2362428583874</v>
       </c>
       <c r="F347" t="n">
         <v>8984600</v>
@@ -7732,16 +7732,16 @@
         <v>44286</v>
       </c>
       <c r="B366" t="n">
-        <v>31.08511734008789</v>
+        <v>31.08511924743652</v>
       </c>
       <c r="C366" t="n">
-        <v>32.65904760342265</v>
+        <v>32.65904960734591</v>
       </c>
       <c r="D366" t="n">
-        <v>30.82279682081511</v>
+        <v>30.82279871206804</v>
       </c>
       <c r="E366" t="n">
-        <v>31.95640029207138</v>
+        <v>31.95640225288098</v>
       </c>
       <c r="F366" t="n">
         <v>8195900</v>
@@ -7792,16 +7792,16 @@
         <v>44292</v>
       </c>
       <c r="B369" t="n">
-        <v>30.5792121887207</v>
+        <v>30.57921028137207</v>
       </c>
       <c r="C369" t="n">
-        <v>32.19998498521812</v>
+        <v>32.19998297677536</v>
       </c>
       <c r="D369" t="n">
-        <v>30.48552730465581</v>
+        <v>30.48552540315069</v>
       </c>
       <c r="E369" t="n">
-        <v>31.01953900629401</v>
+        <v>31.01953707148042</v>
       </c>
       <c r="F369" t="n">
         <v>6923500</v>
@@ -7812,16 +7812,16 @@
         <v>44293</v>
       </c>
       <c r="B370" t="n">
-        <v>30.95395660400391</v>
+        <v>30.95395851135254</v>
       </c>
       <c r="C370" t="n">
-        <v>31.36617506706607</v>
+        <v>31.36617699981515</v>
       </c>
       <c r="D370" t="n">
-        <v>30.40120725129495</v>
+        <v>30.40120912458377</v>
       </c>
       <c r="E370" t="n">
-        <v>30.72910789533883</v>
+        <v>30.72910978883253</v>
       </c>
       <c r="F370" t="n">
         <v>4745700</v>
@@ -8012,16 +8012,16 @@
         <v>44308</v>
       </c>
       <c r="B380" t="n">
-        <v>36.30344390869141</v>
+        <v>36.30344772338867</v>
       </c>
       <c r="C380" t="n">
-        <v>38.03663915608288</v>
+        <v>38.03664315290104</v>
       </c>
       <c r="D380" t="n">
-        <v>35.88185481304648</v>
+        <v>35.88185858344396</v>
       </c>
       <c r="E380" t="n">
-        <v>37.12788440974715</v>
+        <v>37.12788831107506</v>
       </c>
       <c r="F380" t="n">
         <v>6756200</v>
@@ -8052,16 +8052,16 @@
         <v>44312</v>
       </c>
       <c r="B382" t="n">
-        <v>35.91933441162109</v>
+        <v>35.91933059692383</v>
       </c>
       <c r="C382" t="n">
-        <v>36.30344817190534</v>
+        <v>36.30344431641451</v>
       </c>
       <c r="D382" t="n">
-        <v>35.51648295890232</v>
+        <v>35.5164791869886</v>
       </c>
       <c r="E382" t="n">
-        <v>35.88185902675205</v>
+        <v>35.88185521603473</v>
       </c>
       <c r="F382" t="n">
         <v>4241900</v>
@@ -8072,16 +8072,16 @@
         <v>44313</v>
       </c>
       <c r="B383" t="n">
-        <v>35.46963500976562</v>
+        <v>35.46963882446289</v>
       </c>
       <c r="C383" t="n">
-        <v>36.2940754796825</v>
+        <v>36.29407938304689</v>
       </c>
       <c r="D383" t="n">
-        <v>35.27289463051181</v>
+        <v>35.27289842405</v>
       </c>
       <c r="E383" t="n">
-        <v>36.05985972137591</v>
+        <v>36.05986359955081</v>
       </c>
       <c r="F383" t="n">
         <v>2386900</v>
@@ -34972,19 +34972,39 @@
         <v>46280</v>
       </c>
       <c r="B1728" t="n">
-        <v>3.17</v>
+        <v>3.170000076293945</v>
       </c>
       <c r="C1728" t="n">
         <v>3.25</v>
       </c>
       <c r="D1728" t="n">
-        <v>3.04</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="E1728" t="n">
-        <v>3.09</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="F1728" t="n">
         <v>4669500</v>
+      </c>
+    </row>
+    <row r="1729">
+      <c r="A1729" s="1" t="n">
+        <v>46281</v>
+      </c>
+      <c r="B1729" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="C1729" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="D1729" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="E1729" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="F1729" t="n">
+        <v>11280400</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1729"/>
+  <dimension ref="A1:F1730"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553905844688416</v>
+        <v>1.553906559944153</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553905844688416</v>
+        <v>1.553906559944153</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553905844688416</v>
+        <v>1.553906559944153</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553905844688416</v>
+        <v>1.553906559944153</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799174427986145</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799174427986145</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799174427986145</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799174427986145</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.8531334400177</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="C4" t="n">
-        <v>1.8531334400177</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="D4" t="n">
-        <v>1.8531334400177</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8531334400177</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.8531334400177</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="C5" t="n">
-        <v>1.8531334400177</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="D5" t="n">
-        <v>1.8531334400177</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="E5" t="n">
-        <v>1.8531334400177</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.8531334400177</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="C6" t="n">
-        <v>1.8531334400177</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="D6" t="n">
-        <v>1.8531334400177</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="E6" t="n">
-        <v>1.8531334400177</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279500007629395</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279500007629395</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279500007629395</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279500007629395</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461867332458</v>
+        <v>1.92246150970459</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461867332458</v>
+        <v>1.92246150970459</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461867332458</v>
+        <v>1.92246150970459</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461867332458</v>
+        <v>1.92246150970459</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758487343788147</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758487343788147</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758487343788147</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758487343788147</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084613800049</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997223377227783</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997223377227783</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997223377227783</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997223377227783</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958560943604</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587933540344238</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587933540344238</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587933540344238</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587933540344238</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="C55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="D55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="E55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.5891432762146</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -34992,19 +34992,39 @@
         <v>46281</v>
       </c>
       <c r="B1729" t="n">
-        <v>3.29</v>
+        <v>3.289999961853027</v>
       </c>
       <c r="C1729" t="n">
-        <v>3.34</v>
+        <v>3.339999914169312</v>
       </c>
       <c r="D1729" t="n">
-        <v>3.07</v>
+        <v>3.069999933242798</v>
       </c>
       <c r="E1729" t="n">
-        <v>3.18</v>
+        <v>3.180000066757202</v>
       </c>
       <c r="F1729" t="n">
         <v>11280400</v>
+      </c>
+    </row>
+    <row r="1730">
+      <c r="A1730" s="1" t="n">
+        <v>46282</v>
+      </c>
+      <c r="B1730" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C1730" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="D1730" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E1730" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="F1730" t="n">
+        <v>10577600</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1730"/>
+  <dimension ref="A1:F1731"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906559944153</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906559944153</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906559944153</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906559944153</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500007629395</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500007629395</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500007629395</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500007629395</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922461271286011</v>
       </c>
       <c r="C38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922461271286011</v>
       </c>
       <c r="D38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922461271286011</v>
       </c>
       <c r="E38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922461271286011</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951084613800049</v>
+        <v>6.951085090637207</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951085090637208</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951085090637208</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951085090637208</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="C57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="D57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="E57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.5891432762146</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -1832,16 +1832,16 @@
         <v>43684</v>
       </c>
       <c r="B71" t="n">
-        <v>11.66787719726562</v>
+        <v>11.66787815093994</v>
       </c>
       <c r="C71" t="n">
-        <v>11.66787719726562</v>
+        <v>11.66787815093994</v>
       </c>
       <c r="D71" t="n">
-        <v>11.66787719726562</v>
+        <v>11.66787815093994</v>
       </c>
       <c r="E71" t="n">
-        <v>11.66787719726562</v>
+        <v>11.66787815093994</v>
       </c>
       <c r="F71" t="n">
         <v>755</v>
@@ -1872,16 +1872,16 @@
         <v>43741</v>
       </c>
       <c r="B73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F73" t="n">
         <v>755</v>
@@ -1892,16 +1892,16 @@
         <v>43747</v>
       </c>
       <c r="B74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F74" t="n">
         <v>755</v>
@@ -1952,16 +1952,16 @@
         <v>43773</v>
       </c>
       <c r="B77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F77" t="n">
         <v>1510</v>
@@ -2012,16 +2012,16 @@
         <v>43802</v>
       </c>
       <c r="B80" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C80" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D80" t="n">
-        <v>9.217621990355065</v>
+        <v>9.21762282756219</v>
       </c>
       <c r="E80" t="n">
-        <v>9.217621990355065</v>
+        <v>9.21762282756219</v>
       </c>
       <c r="F80" t="n">
         <v>1510</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174577261989849</v>
+        <v>7.174576363958773</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269087350174872</v>
+        <v>7.269086440314109</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759139060974121</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885152239738168</v>
+        <v>7.885151270575596</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395101829362682</v>
+        <v>7.395100920432114</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759139060974121</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198787689209</v>
+        <v>6.731198310852051</v>
       </c>
       <c r="C107" t="n">
-        <v>6.784870504526766</v>
+        <v>6.78487002388751</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975689474925</v>
+        <v>6.183975251402972</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242314420779493</v>
+        <v>6.242313978574833</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642459869384766</v>
+        <v>7.642458915710449</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934156900775253</v>
+        <v>7.934155910701143</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650690466881254</v>
+        <v>6.650689636966175</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242252120494039</v>
+        <v>7.242251216760168</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255535125732</v>
+        <v>7.277255058288574</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292731402749</v>
+        <v>7.641292230712304</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086141684674</v>
+        <v>6.70086097777741</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766202137520195</v>
+        <v>6.766201694169458</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2632,16 +2632,16 @@
         <v>43908</v>
       </c>
       <c r="B111" t="n">
-        <v>6.98555850982666</v>
+        <v>6.985558032989502</v>
       </c>
       <c r="C111" t="n">
-        <v>8.075338544707167</v>
+        <v>8.075337993481165</v>
       </c>
       <c r="D111" t="n">
-        <v>6.71019666955442</v>
+        <v>6.710196211513576</v>
       </c>
       <c r="E111" t="n">
-        <v>7.140741469742403</v>
+        <v>7.140740982312391</v>
       </c>
       <c r="F111" t="n">
         <v>26337960</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738136291503906</v>
+        <v>7.738137245178223</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145345142681279</v>
+        <v>8.145346146541403</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298031292473</v>
+        <v>7.690298979071039</v>
       </c>
       <c r="E117" t="n">
-        <v>8.138343991239532</v>
+        <v>8.13834499423681</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2832,16 +2832,16 @@
         <v>43922</v>
       </c>
       <c r="B121" t="n">
-        <v>7.461607933044434</v>
+        <v>7.461607456207275</v>
       </c>
       <c r="C121" t="n">
-        <v>7.642459684758201</v>
+        <v>7.642459196363636</v>
       </c>
       <c r="D121" t="n">
-        <v>7.304091674358621</v>
+        <v>7.304091207587605</v>
       </c>
       <c r="E121" t="n">
-        <v>7.619124191730246</v>
+        <v>7.619123704826946</v>
       </c>
       <c r="F121" t="n">
         <v>10218288</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582952976226807</v>
+        <v>7.582953929901123</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840814016199421</v>
+        <v>7.840815002303775</v>
       </c>
       <c r="D122" t="n">
-        <v>7.38109946741859</v>
+        <v>7.381100395706687</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455773374392843</v>
+        <v>7.455774312072345</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261936187744</v>
+        <v>7.340261459350586</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624921524582</v>
+        <v>7.622624426344595</v>
       </c>
       <c r="D123" t="n">
-        <v>7.215416044404066</v>
+        <v>7.21541557567713</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457642689852</v>
+        <v>7.621457147585694</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2952,16 +2952,16 @@
         <v>43930</v>
       </c>
       <c r="B127" t="n">
-        <v>7.385766506195068</v>
+        <v>7.38576602935791</v>
       </c>
       <c r="C127" t="n">
-        <v>7.778973921193609</v>
+        <v>7.778973418970338</v>
       </c>
       <c r="D127" t="n">
-        <v>7.351929706227764</v>
+        <v>7.351929231575166</v>
       </c>
       <c r="E127" t="n">
-        <v>7.778973921193609</v>
+        <v>7.778973418970338</v>
       </c>
       <c r="F127" t="n">
         <v>7590081</v>
@@ -2972,16 +2972,16 @@
         <v>43934</v>
       </c>
       <c r="B128" t="n">
-        <v>7.414936065673828</v>
+        <v>7.41493558883667</v>
       </c>
       <c r="C128" t="n">
-        <v>7.447606428031426</v>
+        <v>7.447605949093313</v>
       </c>
       <c r="D128" t="n">
-        <v>7.22941688022938</v>
+        <v>7.229416415322526</v>
       </c>
       <c r="E128" t="n">
-        <v>7.385766699549943</v>
+        <v>7.385766224588598</v>
       </c>
       <c r="F128" t="n">
         <v>8873976</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500111103057861</v>
+        <v>7.500110626220703</v>
       </c>
       <c r="C129" t="n">
-        <v>7.75097100706328</v>
+        <v>7.750970514277116</v>
       </c>
       <c r="D129" t="n">
-        <v>7.45577383571197</v>
+        <v>7.455773361693658</v>
       </c>
       <c r="E129" t="n">
-        <v>7.494278070349739</v>
+        <v>7.49427759388343</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265121459961</v>
+        <v>7.375265598297119</v>
       </c>
       <c r="C130" t="n">
-        <v>7.49427797970812</v>
+        <v>7.494278464239883</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762039125325</v>
+        <v>7.343762513925697</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935482620931</v>
+        <v>7.407935961570344</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.5666184425354</v>
+        <v>7.566619396209717</v>
       </c>
       <c r="C131" t="n">
-        <v>7.588787494454161</v>
+        <v>7.5887884509226</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234083504127451</v>
+        <v>7.234084415890043</v>
       </c>
       <c r="E131" t="n">
-        <v>7.44410543779982</v>
+        <v>7.444106376032958</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251523017883301</v>
+        <v>8.251522064208984</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431208332707222</v>
+        <v>8.431207358265677</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3112,16 +3112,16 @@
         <v>43944</v>
       </c>
       <c r="B135" t="n">
-        <v>8.089340209960938</v>
+        <v>8.089339256286621</v>
       </c>
       <c r="C135" t="n">
-        <v>8.574724018558863</v>
+        <v>8.57472300766133</v>
       </c>
       <c r="D135" t="n">
-        <v>7.969160906424007</v>
+        <v>7.969159966917957</v>
       </c>
       <c r="E135" t="n">
-        <v>8.481380364324728</v>
+        <v>8.481379364431731</v>
       </c>
       <c r="F135" t="n">
         <v>13472583</v>
@@ -3152,16 +3152,16 @@
         <v>43948</v>
       </c>
       <c r="B137" t="n">
-        <v>8.105674743652344</v>
+        <v>8.105673789978027</v>
       </c>
       <c r="C137" t="n">
-        <v>8.165180757388045</v>
+        <v>8.16517979671254</v>
       </c>
       <c r="D137" t="n">
-        <v>7.710134423961201</v>
+        <v>7.710133516824237</v>
       </c>
       <c r="E137" t="n">
-        <v>7.93765801086142</v>
+        <v>7.937657076955135</v>
       </c>
       <c r="F137" t="n">
         <v>12260436</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887483596801758</v>
+        <v>7.887484550476074</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966825772834317</v>
+        <v>7.966826736101882</v>
       </c>
       <c r="D139" t="n">
-        <v>7.700798002265745</v>
+        <v>7.700798933367937</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841979897039702</v>
+        <v>7.841980845212174</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3252,16 +3252,16 @@
         <v>43956</v>
       </c>
       <c r="B142" t="n">
-        <v>8.114090919494629</v>
+        <v>8.114091873168945</v>
       </c>
       <c r="C142" t="n">
-        <v>8.645023715587479</v>
+        <v>8.645024731663977</v>
       </c>
       <c r="D142" t="n">
-        <v>8.069432995707503</v>
+        <v>8.069433944133035</v>
       </c>
       <c r="E142" t="n">
-        <v>8.286520199683441</v>
+        <v>8.286521173623905</v>
       </c>
       <c r="F142" t="n">
         <v>11843548</v>
@@ -3272,16 +3272,16 @@
         <v>43957</v>
       </c>
       <c r="B143" t="n">
-        <v>8.048345565795898</v>
+        <v>8.048344612121582</v>
       </c>
       <c r="C143" t="n">
-        <v>8.145104858936216</v>
+        <v>8.145103893796581</v>
       </c>
       <c r="D143" t="n">
-        <v>7.963991997516411</v>
+        <v>7.96399105383742</v>
       </c>
       <c r="E143" t="n">
-        <v>8.145104858936216</v>
+        <v>8.145103893796581</v>
       </c>
       <c r="F143" t="n">
         <v>16545622</v>
@@ -3312,16 +3312,16 @@
         <v>43959</v>
       </c>
       <c r="B145" t="n">
-        <v>8.162469863891602</v>
+        <v>8.162470817565918</v>
       </c>
       <c r="C145" t="n">
-        <v>8.184799271833279</v>
+        <v>8.184800228116485</v>
       </c>
       <c r="D145" t="n">
-        <v>7.94786381115636</v>
+        <v>7.947864739756858</v>
       </c>
       <c r="E145" t="n">
-        <v>8.15626744912163</v>
+        <v>8.156268402071278</v>
       </c>
       <c r="F145" t="n">
         <v>8818844</v>
@@ -3352,16 +3352,16 @@
         <v>43963</v>
       </c>
       <c r="B147" t="n">
-        <v>8.085558891296387</v>
+        <v>8.085559844970703</v>
       </c>
       <c r="C147" t="n">
-        <v>8.276595411529883</v>
+        <v>8.276596387736546</v>
       </c>
       <c r="D147" t="n">
-        <v>8.063229483236768</v>
+        <v>8.063230434277379</v>
       </c>
       <c r="E147" t="n">
-        <v>8.187279566215866</v>
+        <v>8.187280531887918</v>
       </c>
       <c r="F147" t="n">
         <v>9953957</v>
@@ -3372,16 +3372,16 @@
         <v>43964</v>
       </c>
       <c r="B148" t="n">
-        <v>7.926775455474854</v>
+        <v>7.926775932312012</v>
       </c>
       <c r="C148" t="n">
-        <v>8.187279557292356</v>
+        <v>8.187280049800203</v>
       </c>
       <c r="D148" t="n">
-        <v>7.885839696513885</v>
+        <v>7.885840170888542</v>
       </c>
       <c r="E148" t="n">
-        <v>8.187279557292356</v>
+        <v>8.187280049800203</v>
       </c>
       <c r="F148" t="n">
         <v>10179016</v>
@@ -3412,16 +3412,16 @@
         <v>43966</v>
       </c>
       <c r="B150" t="n">
-        <v>6.8413405418396</v>
+        <v>6.841341018676758</v>
       </c>
       <c r="C150" t="n">
-        <v>7.421893104642092</v>
+        <v>7.421893621943401</v>
       </c>
       <c r="D150" t="n">
-        <v>6.8413405418396</v>
+        <v>6.841341018676758</v>
       </c>
       <c r="E150" t="n">
-        <v>7.420652532303285</v>
+        <v>7.420653049518127</v>
       </c>
       <c r="F150" t="n">
         <v>26563775</v>
@@ -3452,16 +3452,16 @@
         <v>43970</v>
       </c>
       <c r="B152" t="n">
-        <v>6.831418037414551</v>
+        <v>6.831417560577393</v>
       </c>
       <c r="C152" t="n">
-        <v>7.018732418962401</v>
+        <v>7.018731929050585</v>
       </c>
       <c r="D152" t="n">
-        <v>6.79916449333305</v>
+        <v>6.799164018747209</v>
       </c>
       <c r="E152" t="n">
-        <v>6.966631502251738</v>
+        <v>6.966631015976597</v>
       </c>
       <c r="F152" t="n">
         <v>13463520</v>
@@ -3472,16 +3472,16 @@
         <v>43971</v>
       </c>
       <c r="B153" t="n">
-        <v>6.822733879089355</v>
+        <v>6.822733402252197</v>
       </c>
       <c r="C153" t="n">
-        <v>6.983998022077899</v>
+        <v>6.983997533970078</v>
       </c>
       <c r="D153" t="n">
-        <v>6.810329048105121</v>
+        <v>6.81032857213493</v>
       </c>
       <c r="E153" t="n">
-        <v>6.94678397585636</v>
+        <v>6.946783490349408</v>
       </c>
       <c r="F153" t="n">
         <v>11533147</v>
@@ -3552,16 +3552,16 @@
         <v>43977</v>
       </c>
       <c r="B157" t="n">
-        <v>7.423134803771973</v>
+        <v>7.423134326934814</v>
       </c>
       <c r="C157" t="n">
-        <v>7.560829411371671</v>
+        <v>7.560828925689475</v>
       </c>
       <c r="D157" t="n">
-        <v>7.275515169821428</v>
+        <v>7.275514702466858</v>
       </c>
       <c r="E157" t="n">
-        <v>7.442982622817829</v>
+        <v>7.442982144705714</v>
       </c>
       <c r="F157" t="n">
         <v>12080691</v>
@@ -3612,16 +3612,16 @@
         <v>43980</v>
       </c>
       <c r="B160" t="n">
-        <v>7.812650203704834</v>
+        <v>7.812650680541992</v>
       </c>
       <c r="C160" t="n">
-        <v>7.812650203704834</v>
+        <v>7.812650680541992</v>
       </c>
       <c r="D160" t="n">
-        <v>7.481437043617326</v>
+        <v>7.481437500239227</v>
       </c>
       <c r="E160" t="n">
-        <v>7.519892999404318</v>
+        <v>7.519893458373339</v>
       </c>
       <c r="F160" t="n">
         <v>23712019</v>
@@ -3652,16 +3652,16 @@
         <v>43984</v>
       </c>
       <c r="B162" t="n">
-        <v>8.271634101867676</v>
+        <v>8.271635055541992</v>
       </c>
       <c r="C162" t="n">
-        <v>8.286520076241633</v>
+        <v>8.286521031632221</v>
       </c>
       <c r="D162" t="n">
-        <v>7.976395759027911</v>
+        <v>7.976396678662855</v>
       </c>
       <c r="E162" t="n">
-        <v>8.063229567170044</v>
+        <v>8.063230496816454</v>
       </c>
       <c r="F162" t="n">
         <v>21348142</v>
@@ -3672,16 +3672,16 @@
         <v>43985</v>
       </c>
       <c r="B163" t="n">
-        <v>8.373354911804199</v>
+        <v>8.373353958129883</v>
       </c>
       <c r="C163" t="n">
-        <v>8.800086825192951</v>
+        <v>8.80008582291646</v>
       </c>
       <c r="D163" t="n">
-        <v>8.315052026205343</v>
+        <v>8.315051079171372</v>
       </c>
       <c r="E163" t="n">
-        <v>8.317533171149149</v>
+        <v>8.31753222383259</v>
       </c>
       <c r="F163" t="n">
         <v>31125376</v>
@@ -3752,16 +3752,16 @@
         <v>43991</v>
       </c>
       <c r="B167" t="n">
-        <v>8.296442985534668</v>
+        <v>8.296443939208984</v>
       </c>
       <c r="C167" t="n">
-        <v>8.327455953773208</v>
+        <v>8.32745691101246</v>
       </c>
       <c r="D167" t="n">
-        <v>8.096723794435762</v>
+        <v>8.0967247251524</v>
       </c>
       <c r="E167" t="n">
-        <v>8.137660447910266</v>
+        <v>8.137661383332564</v>
       </c>
       <c r="F167" t="n">
         <v>13675741</v>
@@ -3772,16 +3772,16 @@
         <v>43992</v>
       </c>
       <c r="B168" t="n">
-        <v>8.08928108215332</v>
+        <v>8.089280128479004</v>
       </c>
       <c r="C168" t="n">
-        <v>8.426697131827968</v>
+        <v>8.426696138374464</v>
       </c>
       <c r="D168" t="n">
-        <v>8.0371806131882</v>
+        <v>8.037179665656195</v>
       </c>
       <c r="E168" t="n">
-        <v>8.311330595134894</v>
+        <v>8.311329615282364</v>
       </c>
       <c r="F168" t="n">
         <v>11944749</v>
@@ -3792,16 +3792,16 @@
         <v>43994</v>
       </c>
       <c r="B169" t="n">
-        <v>7.950345993041992</v>
+        <v>7.950345516204834</v>
       </c>
       <c r="C169" t="n">
-        <v>8.084319777785</v>
+        <v>8.084319292912509</v>
       </c>
       <c r="D169" t="n">
-        <v>7.774195424975465</v>
+        <v>7.774194958703272</v>
       </c>
       <c r="E169" t="n">
-        <v>7.877157131822456</v>
+        <v>7.877156659374939</v>
       </c>
       <c r="F169" t="n">
         <v>12251373</v>
@@ -3892,16 +3892,16 @@
         <v>44001</v>
       </c>
       <c r="B174" t="n">
-        <v>8.487480163574219</v>
+        <v>8.487481117248535</v>
       </c>
       <c r="C174" t="n">
-        <v>8.589200838114557</v>
+        <v>8.58920180321846</v>
       </c>
       <c r="D174" t="n">
-        <v>8.203406528896336</v>
+        <v>8.203407450651435</v>
       </c>
       <c r="E174" t="n">
-        <v>8.203406528896336</v>
+        <v>8.203407450651435</v>
       </c>
       <c r="F174" t="n">
         <v>20750754</v>
@@ -3912,16 +3912,16 @@
         <v>44004</v>
       </c>
       <c r="B175" t="n">
-        <v>8.440342903137207</v>
+        <v>8.440341949462891</v>
       </c>
       <c r="C175" t="n">
-        <v>8.729377964833343</v>
+        <v>8.729376978500955</v>
       </c>
       <c r="D175" t="n">
-        <v>8.380798106578508</v>
+        <v>8.380797159632158</v>
       </c>
       <c r="E175" t="n">
-        <v>8.489962226742637</v>
+        <v>8.489961267461833</v>
       </c>
       <c r="F175" t="n">
         <v>12069362</v>
@@ -3952,16 +3952,16 @@
         <v>44006</v>
       </c>
       <c r="B177" t="n">
-        <v>8.594162940979004</v>
+        <v>8.59416389465332</v>
       </c>
       <c r="C177" t="n">
-        <v>8.669832935726904</v>
+        <v>8.669833897798144</v>
       </c>
       <c r="D177" t="n">
-        <v>8.422973795079262</v>
+        <v>8.422974729757115</v>
       </c>
       <c r="E177" t="n">
-        <v>8.571833533486773</v>
+        <v>8.571834484683247</v>
       </c>
       <c r="F177" t="n">
         <v>7388434</v>
@@ -4052,16 +4052,16 @@
         <v>44013</v>
       </c>
       <c r="B182" t="n">
-        <v>9.009730339050293</v>
+        <v>9.009729385375977</v>
       </c>
       <c r="C182" t="n">
-        <v>9.11517229493286</v>
+        <v>9.115171330097578</v>
       </c>
       <c r="D182" t="n">
-        <v>8.731859089723871</v>
+        <v>8.731858165462054</v>
       </c>
       <c r="E182" t="n">
-        <v>8.812491383860499</v>
+        <v>8.812490451063802</v>
       </c>
       <c r="F182" t="n">
         <v>8963093</v>
@@ -4292,16 +4292,16 @@
         <v>44029</v>
       </c>
       <c r="B194" t="n">
-        <v>8.81993293762207</v>
+        <v>8.819933891296387</v>
       </c>
       <c r="C194" t="n">
-        <v>8.919173360420668</v>
+        <v>8.919174324825571</v>
       </c>
       <c r="D194" t="n">
-        <v>8.633858708433587</v>
+        <v>8.633859641988225</v>
       </c>
       <c r="E194" t="n">
-        <v>8.633858708433587</v>
+        <v>8.633859641988225</v>
       </c>
       <c r="F194" t="n">
         <v>9678298</v>
@@ -4432,16 +4432,16 @@
         <v>44040</v>
       </c>
       <c r="B201" t="n">
-        <v>9.641143798828125</v>
+        <v>9.641142845153809</v>
       </c>
       <c r="C201" t="n">
-        <v>9.832180339834917</v>
+        <v>9.832179367263814</v>
       </c>
       <c r="D201" t="n">
-        <v>9.466233359369541</v>
+        <v>9.466232422996864</v>
       </c>
       <c r="E201" t="n">
-        <v>9.675878040270206</v>
+        <v>9.67587708316008</v>
       </c>
       <c r="F201" t="n">
         <v>30127714</v>
@@ -4472,16 +4472,16 @@
         <v>44042</v>
       </c>
       <c r="B203" t="n">
-        <v>9.143704414367676</v>
+        <v>9.143703460693359</v>
       </c>
       <c r="C203" t="n">
-        <v>9.700687950073165</v>
+        <v>9.700686938306321</v>
       </c>
       <c r="D203" t="n">
-        <v>9.097806359971171</v>
+        <v>9.097805411083952</v>
       </c>
       <c r="E203" t="n">
-        <v>9.685801080392711</v>
+        <v>9.685800070178546</v>
       </c>
       <c r="F203" t="n">
         <v>33272500</v>
@@ -4592,16 +4592,16 @@
         <v>44050</v>
       </c>
       <c r="B209" t="n">
-        <v>8.429177284240723</v>
+        <v>8.429178237915039</v>
       </c>
       <c r="C209" t="n">
-        <v>8.429177284240723</v>
+        <v>8.429178237915039</v>
       </c>
       <c r="D209" t="n">
-        <v>8.255506990060143</v>
+        <v>8.25550792408546</v>
       </c>
       <c r="E209" t="n">
-        <v>8.336140169103194</v>
+        <v>8.336141112251321</v>
       </c>
       <c r="F209" t="n">
         <v>22110172</v>
@@ -4612,16 +4612,16 @@
         <v>44053</v>
       </c>
       <c r="B210" t="n">
-        <v>8.259230613708496</v>
+        <v>8.25922966003418</v>
       </c>
       <c r="C210" t="n">
-        <v>8.468874414585619</v>
+        <v>8.468873436704216</v>
       </c>
       <c r="D210" t="n">
-        <v>8.166192588662099</v>
+        <v>8.166191645730668</v>
       </c>
       <c r="E210" t="n">
-        <v>8.435380296706972</v>
+        <v>8.435379322693057</v>
       </c>
       <c r="F210" t="n">
         <v>21920608</v>
@@ -4652,16 +4652,16 @@
         <v>44055</v>
       </c>
       <c r="B212" t="n">
-        <v>8.162469863891602</v>
+        <v>8.162470817565918</v>
       </c>
       <c r="C212" t="n">
-        <v>8.446543498127859</v>
+        <v>8.446544484992341</v>
       </c>
       <c r="D212" t="n">
-        <v>8.078115414787984</v>
+        <v>8.078116358606623</v>
       </c>
       <c r="E212" t="n">
-        <v>8.409329009508031</v>
+        <v>8.409329992024503</v>
       </c>
       <c r="F212" t="n">
         <v>20200945</v>
@@ -4732,16 +4732,16 @@
         <v>44061</v>
       </c>
       <c r="B216" t="n">
-        <v>8.101686477661133</v>
+        <v>8.101685523986816</v>
       </c>
       <c r="C216" t="n">
-        <v>8.143864156905972</v>
+        <v>8.143863198266791</v>
       </c>
       <c r="D216" t="n">
-        <v>7.9788782846482</v>
+        <v>7.978877345430011</v>
       </c>
       <c r="E216" t="n">
-        <v>8.038421298987467</v>
+        <v>8.038420352760289</v>
       </c>
       <c r="F216" t="n">
         <v>10608743</v>
@@ -4752,16 +4752,16 @@
         <v>44062</v>
       </c>
       <c r="B217" t="n">
-        <v>7.926775455474854</v>
+        <v>7.926775932312012</v>
       </c>
       <c r="C217" t="n">
-        <v>8.141381509109719</v>
+        <v>8.141381998856557</v>
       </c>
       <c r="D217" t="n">
-        <v>7.921813166253184</v>
+        <v>7.921813642791834</v>
       </c>
       <c r="E217" t="n">
-        <v>8.141381509109719</v>
+        <v>8.141381998856557</v>
       </c>
       <c r="F217" t="n">
         <v>9466833</v>
@@ -4772,16 +4772,16 @@
         <v>44063</v>
       </c>
       <c r="B218" t="n">
-        <v>7.957788467407227</v>
+        <v>7.957787990570068</v>
       </c>
       <c r="C218" t="n">
-        <v>8.033459366376674</v>
+        <v>8.033458885005254</v>
       </c>
       <c r="D218" t="n">
-        <v>7.774195359575069</v>
+        <v>7.774194893738959</v>
       </c>
       <c r="E218" t="n">
-        <v>7.915611684438519</v>
+        <v>7.915611210128628</v>
       </c>
       <c r="F218" t="n">
         <v>7652765</v>
@@ -4892,16 +4892,16 @@
         <v>44071</v>
       </c>
       <c r="B224" t="n">
-        <v>8.100445747375488</v>
+        <v>8.100444793701172</v>
       </c>
       <c r="C224" t="n">
-        <v>8.100445747375488</v>
+        <v>8.100444793701172</v>
       </c>
       <c r="D224" t="n">
-        <v>7.960269549341362</v>
+        <v>7.960268612170143</v>
       </c>
       <c r="E224" t="n">
-        <v>8.0012070997281</v>
+        <v>8.001206157737258</v>
       </c>
       <c r="F224" t="n">
         <v>5577388</v>
@@ -5012,16 +5012,16 @@
         <v>44082</v>
       </c>
       <c r="B230" t="n">
-        <v>7.751865863800049</v>
+        <v>7.751865386962891</v>
       </c>
       <c r="C230" t="n">
-        <v>7.833738283935308</v>
+        <v>7.833737802061967</v>
       </c>
       <c r="D230" t="n">
-        <v>7.691081834917614</v>
+        <v>7.691081361819436</v>
       </c>
       <c r="E230" t="n">
-        <v>7.813890911851665</v>
+        <v>7.813890431199186</v>
       </c>
       <c r="F230" t="n">
         <v>7181501</v>
@@ -5032,16 +5032,16 @@
         <v>44083</v>
       </c>
       <c r="B231" t="n">
-        <v>7.709688663482666</v>
+        <v>7.709689140319824</v>
       </c>
       <c r="C231" t="n">
-        <v>7.834979771965168</v>
+        <v>7.834980256551466</v>
       </c>
       <c r="D231" t="n">
-        <v>7.637739933288351</v>
+        <v>7.637740405675546</v>
       </c>
       <c r="E231" t="n">
-        <v>7.792802098282933</v>
+        <v>7.792802580260581</v>
       </c>
       <c r="F231" t="n">
         <v>8282629</v>
@@ -5052,16 +5052,16 @@
         <v>44084</v>
       </c>
       <c r="B232" t="n">
-        <v>8.850947380065918</v>
+        <v>8.850946426391602</v>
       </c>
       <c r="C232" t="n">
-        <v>9.197045218135978</v>
+        <v>9.197044227170217</v>
       </c>
       <c r="D232" t="n">
-        <v>8.621455315968662</v>
+        <v>8.62145438702172</v>
       </c>
       <c r="E232" t="n">
-        <v>9.197045218135978</v>
+        <v>9.197044227170217</v>
       </c>
       <c r="F232" t="n">
         <v>139609921</v>
@@ -5132,16 +5132,16 @@
         <v>44090</v>
       </c>
       <c r="B236" t="n">
-        <v>9.312410354614258</v>
+        <v>9.312411308288574</v>
       </c>
       <c r="C236" t="n">
-        <v>9.375675522060035</v>
+        <v>9.375676482213272</v>
       </c>
       <c r="D236" t="n">
-        <v>9.175956334671081</v>
+        <v>9.175957274371282</v>
       </c>
       <c r="E236" t="n">
-        <v>9.179677604882659</v>
+        <v>9.179678544963952</v>
       </c>
       <c r="F236" t="n">
         <v>13993693</v>
@@ -5212,16 +5212,16 @@
         <v>44096</v>
       </c>
       <c r="B240" t="n">
-        <v>9.326058387756348</v>
+        <v>9.326057434082031</v>
       </c>
       <c r="C240" t="n">
-        <v>9.353349195522698</v>
+        <v>9.353348239057649</v>
       </c>
       <c r="D240" t="n">
-        <v>9.182159127084132</v>
+        <v>9.182158188124824</v>
       </c>
       <c r="E240" t="n">
-        <v>9.192083706971793</v>
+        <v>9.192082766997606</v>
       </c>
       <c r="F240" t="n">
         <v>9315031</v>
@@ -5232,16 +5232,16 @@
         <v>44097</v>
       </c>
       <c r="B241" t="n">
-        <v>8.95390796661377</v>
+        <v>8.953908920288086</v>
       </c>
       <c r="C241" t="n">
-        <v>9.308689320943529</v>
+        <v>9.308690312405352</v>
       </c>
       <c r="D241" t="n">
-        <v>8.934059702543932</v>
+        <v>8.934060654104224</v>
       </c>
       <c r="E241" t="n">
-        <v>9.303727925022763</v>
+        <v>9.303728915956151</v>
       </c>
       <c r="F241" t="n">
         <v>13677251</v>
@@ -5252,16 +5252,16 @@
         <v>44098</v>
       </c>
       <c r="B242" t="n">
-        <v>9.282639503479004</v>
+        <v>9.282638549804688</v>
       </c>
       <c r="C242" t="n">
-        <v>9.46375236122295</v>
+        <v>9.463751388941567</v>
       </c>
       <c r="D242" t="n">
-        <v>8.898085270619518</v>
+        <v>8.898084356453305</v>
       </c>
       <c r="E242" t="n">
-        <v>8.906769724577019</v>
+        <v>8.906768809518589</v>
       </c>
       <c r="F242" t="n">
         <v>18607406</v>
@@ -5272,16 +5272,16 @@
         <v>44099</v>
       </c>
       <c r="B243" t="n">
-        <v>9.184640884399414</v>
+        <v>9.184639930725098</v>
       </c>
       <c r="C243" t="n">
-        <v>9.254108474175018</v>
+        <v>9.25410751328763</v>
       </c>
       <c r="D243" t="n">
-        <v>9.095325028918353</v>
+        <v>9.095324084518023</v>
       </c>
       <c r="E243" t="n">
-        <v>9.22061435827287</v>
+        <v>9.220613400863298</v>
       </c>
       <c r="F243" t="n">
         <v>8201819</v>
@@ -5312,16 +5312,16 @@
         <v>44103</v>
       </c>
       <c r="B245" t="n">
-        <v>8.760390281677246</v>
+        <v>8.760391235351562</v>
       </c>
       <c r="C245" t="n">
-        <v>8.942743247933565</v>
+        <v>8.942744221459206</v>
       </c>
       <c r="D245" t="n">
-        <v>8.683479263674647</v>
+        <v>8.68348020897627</v>
       </c>
       <c r="E245" t="n">
-        <v>8.802567060978735</v>
+        <v>8.802568019244504</v>
       </c>
       <c r="F245" t="n">
         <v>13985386</v>
@@ -5332,16 +5332,16 @@
         <v>44104</v>
       </c>
       <c r="B246" t="n">
-        <v>8.651226997375488</v>
+        <v>8.651226043701172</v>
       </c>
       <c r="C246" t="n">
-        <v>8.841023415853394</v>
+        <v>8.841022441256731</v>
       </c>
       <c r="D246" t="n">
-        <v>8.609050214038696</v>
+        <v>8.609049265013768</v>
       </c>
       <c r="E246" t="n">
-        <v>8.803808028904122</v>
+        <v>8.803807058409923</v>
       </c>
       <c r="F246" t="n">
         <v>11477260</v>
@@ -5412,16 +5412,16 @@
         <v>44110</v>
       </c>
       <c r="B250" t="n">
-        <v>8.497404098510742</v>
+        <v>8.497405052185059</v>
       </c>
       <c r="C250" t="n">
-        <v>8.520973632751547</v>
+        <v>8.520974589071102</v>
       </c>
       <c r="D250" t="n">
-        <v>8.3162921520784</v>
+        <v>8.316293085426295</v>
       </c>
       <c r="E250" t="n">
-        <v>8.48872053887138</v>
+        <v>8.488721491571129</v>
       </c>
       <c r="F250" t="n">
         <v>10544549</v>
@@ -5432,16 +5432,16 @@
         <v>44111</v>
       </c>
       <c r="B251" t="n">
-        <v>8.585479736328125</v>
+        <v>8.585480690002441</v>
       </c>
       <c r="C251" t="n">
-        <v>8.704567531971968</v>
+        <v>8.704568498874545</v>
       </c>
       <c r="D251" t="n">
-        <v>8.440342155483876</v>
+        <v>8.440343093036322</v>
       </c>
       <c r="E251" t="n">
-        <v>8.477556644891454</v>
+        <v>8.477557586577683</v>
       </c>
       <c r="F251" t="n">
         <v>12680345</v>
@@ -5552,16 +5552,16 @@
         <v>44120</v>
       </c>
       <c r="B257" t="n">
-        <v>8.259230613708496</v>
+        <v>8.25922966003418</v>
       </c>
       <c r="C257" t="n">
-        <v>8.267913281163274</v>
+        <v>8.267912326486389</v>
       </c>
       <c r="D257" t="n">
-        <v>8.097965120577188</v>
+        <v>8.097964185523827</v>
       </c>
       <c r="E257" t="n">
-        <v>8.122775677538673</v>
+        <v>8.122774739620494</v>
       </c>
       <c r="F257" t="n">
         <v>10726560</v>
@@ -5612,16 +5612,16 @@
         <v>44125</v>
       </c>
       <c r="B260" t="n">
-        <v>8.275356292724609</v>
+        <v>8.275355339050293</v>
       </c>
       <c r="C260" t="n">
-        <v>8.355988588431988</v>
+        <v>8.355987625465389</v>
       </c>
       <c r="D260" t="n">
-        <v>8.245584340664582</v>
+        <v>8.245583390421267</v>
       </c>
       <c r="E260" t="n">
-        <v>8.35474846270546</v>
+        <v>8.354747499881778</v>
       </c>
       <c r="F260" t="n">
         <v>4665068</v>
@@ -5632,16 +5632,16 @@
         <v>44126</v>
       </c>
       <c r="B261" t="n">
-        <v>8.267912864685059</v>
+        <v>8.267911911010742</v>
       </c>
       <c r="C261" t="n">
-        <v>8.337381348523031</v>
+        <v>8.337380386835774</v>
       </c>
       <c r="D261" t="n">
-        <v>8.168674215687588</v>
+        <v>8.168673273460097</v>
       </c>
       <c r="E261" t="n">
-        <v>8.306368377248981</v>
+        <v>8.30636741913896</v>
       </c>
       <c r="F261" t="n">
         <v>7908034</v>
@@ -5652,16 +5652,16 @@
         <v>44127</v>
       </c>
       <c r="B262" t="n">
-        <v>8.234420776367188</v>
+        <v>8.234419822692871</v>
       </c>
       <c r="C262" t="n">
-        <v>8.312571929509362</v>
+        <v>8.312570966783923</v>
       </c>
       <c r="D262" t="n">
-        <v>8.203407804185662</v>
+        <v>8.203406854103131</v>
       </c>
       <c r="E262" t="n">
-        <v>8.269153232377807</v>
+        <v>8.269152274680931</v>
       </c>
       <c r="F262" t="n">
         <v>5098571</v>
@@ -5712,16 +5712,16 @@
         <v>44132</v>
       </c>
       <c r="B265" t="n">
-        <v>7.825055122375488</v>
+        <v>7.825055599212646</v>
       </c>
       <c r="C265" t="n">
-        <v>8.088040380288025</v>
+        <v>8.088040873150774</v>
       </c>
       <c r="D265" t="n">
-        <v>7.81761168821794</v>
+        <v>7.817612164601516</v>
       </c>
       <c r="E265" t="n">
-        <v>8.078115801411293</v>
+        <v>8.078116293669268</v>
       </c>
       <c r="F265" t="n">
         <v>12369944</v>
@@ -5752,16 +5752,16 @@
         <v>44134</v>
       </c>
       <c r="B267" t="n">
-        <v>7.684879302978516</v>
+        <v>7.684878826141357</v>
       </c>
       <c r="C267" t="n">
-        <v>7.777916426914608</v>
+        <v>7.777915944304612</v>
       </c>
       <c r="D267" t="n">
-        <v>7.574475058635726</v>
+        <v>7.574474588649013</v>
       </c>
       <c r="E267" t="n">
-        <v>7.759309180819852</v>
+        <v>7.759308699364413</v>
       </c>
       <c r="F267" t="n">
         <v>16269207</v>
@@ -5772,16 +5772,16 @@
         <v>44138</v>
       </c>
       <c r="B268" t="n">
-        <v>7.7171311378479</v>
+        <v>7.717131614685059</v>
       </c>
       <c r="C268" t="n">
-        <v>7.852345930671059</v>
+        <v>7.852346415863062</v>
       </c>
       <c r="D268" t="n">
-        <v>7.622853892715106</v>
+        <v>7.622854363726927</v>
       </c>
       <c r="E268" t="n">
-        <v>7.821333855323877</v>
+        <v>7.821334338599661</v>
       </c>
       <c r="F268" t="n">
         <v>9901091</v>
@@ -5812,16 +5812,16 @@
         <v>44140</v>
       </c>
       <c r="B270" t="n">
-        <v>8.119052886962891</v>
+        <v>8.119053840637207</v>
       </c>
       <c r="C270" t="n">
-        <v>8.177355763964984</v>
+        <v>8.177356724487632</v>
       </c>
       <c r="D270" t="n">
-        <v>8.007407635190189</v>
+        <v>8.007408575750512</v>
       </c>
       <c r="E270" t="n">
-        <v>8.039660727779241</v>
+        <v>8.039661672128053</v>
       </c>
       <c r="F270" t="n">
         <v>9820281</v>
@@ -5892,16 +5892,16 @@
         <v>44146</v>
       </c>
       <c r="B274" t="n">
-        <v>8.193482398986816</v>
+        <v>8.193483352661133</v>
       </c>
       <c r="C274" t="n">
-        <v>8.420493294041393</v>
+        <v>8.420494274138473</v>
       </c>
       <c r="D274" t="n">
-        <v>8.193482398986816</v>
+        <v>8.193483352661133</v>
       </c>
       <c r="E274" t="n">
-        <v>8.312571092276054</v>
+        <v>8.312572059811611</v>
       </c>
       <c r="F274" t="n">
         <v>7246451</v>
@@ -5912,16 +5912,16 @@
         <v>44147</v>
       </c>
       <c r="B275" t="n">
-        <v>8.234420776367188</v>
+        <v>8.234419822692871</v>
       </c>
       <c r="C275" t="n">
-        <v>8.398165624159189</v>
+        <v>8.398164651520666</v>
       </c>
       <c r="D275" t="n">
-        <v>8.13145906678732</v>
+        <v>8.131458125037573</v>
       </c>
       <c r="E275" t="n">
-        <v>8.193483224225638</v>
+        <v>8.193482275292528</v>
       </c>
       <c r="F275" t="n">
         <v>11697033</v>
@@ -5932,16 +5932,16 @@
         <v>44148</v>
       </c>
       <c r="B276" t="n">
-        <v>8.633859634399414</v>
+        <v>8.633858680725098</v>
       </c>
       <c r="C276" t="n">
-        <v>8.646265358676397</v>
+        <v>8.646264403631776</v>
       </c>
       <c r="D276" t="n">
-        <v>8.267912658055211</v>
+        <v>8.267911744802472</v>
       </c>
       <c r="E276" t="n">
-        <v>8.322494271024663</v>
+        <v>8.322493351742979</v>
       </c>
       <c r="F276" t="n">
         <v>10854949</v>
@@ -5992,16 +5992,16 @@
         <v>44153</v>
       </c>
       <c r="B279" t="n">
-        <v>8.584240913391113</v>
+        <v>8.584239959716797</v>
       </c>
       <c r="C279" t="n">
-        <v>8.645024946032365</v>
+        <v>8.64502398560519</v>
       </c>
       <c r="D279" t="n">
-        <v>8.516013445661457</v>
+        <v>8.516012499566937</v>
       </c>
       <c r="E279" t="n">
-        <v>8.558190230775271</v>
+        <v>8.55818927999508</v>
       </c>
       <c r="F279" t="n">
         <v>8922310</v>
@@ -6072,16 +6072,16 @@
         <v>44160</v>
       </c>
       <c r="B283" t="n">
-        <v>8.739302635192871</v>
+        <v>8.739301681518555</v>
       </c>
       <c r="C283" t="n">
-        <v>8.920414597775554</v>
+        <v>8.920413624337439</v>
       </c>
       <c r="D283" t="n">
-        <v>8.616492663682914</v>
+        <v>8.616491723410208</v>
       </c>
       <c r="E283" t="n">
-        <v>8.85466827854489</v>
+        <v>8.854667312281327</v>
       </c>
       <c r="F283" t="n">
         <v>6633202</v>
@@ -6112,16 +6112,16 @@
         <v>44162</v>
       </c>
       <c r="B285" t="n">
-        <v>8.615252494812012</v>
+        <v>8.615251541137695</v>
       </c>
       <c r="C285" t="n">
-        <v>8.708288727073548</v>
+        <v>8.70828776310049</v>
       </c>
       <c r="D285" t="n">
-        <v>8.507329393233835</v>
+        <v>8.507328451506179</v>
       </c>
       <c r="E285" t="n">
-        <v>8.566872403188754</v>
+        <v>8.566871454869922</v>
       </c>
       <c r="F285" t="n">
         <v>5230736</v>
@@ -6152,16 +6152,16 @@
         <v>44166</v>
       </c>
       <c r="B287" t="n">
-        <v>8.414292335510254</v>
+        <v>8.414291381835938</v>
       </c>
       <c r="C287" t="n">
-        <v>8.672315323428652</v>
+        <v>8.672314340510058</v>
       </c>
       <c r="D287" t="n">
-        <v>8.360949953683695</v>
+        <v>8.360949006055193</v>
       </c>
       <c r="E287" t="n">
-        <v>8.636340955945199</v>
+        <v>8.636339977103933</v>
       </c>
       <c r="F287" t="n">
         <v>16096259</v>
@@ -6172,16 +6172,16 @@
         <v>44167</v>
       </c>
       <c r="B288" t="n">
-        <v>8.282798767089844</v>
+        <v>8.282797813415527</v>
       </c>
       <c r="C288" t="n">
-        <v>8.4614304780068</v>
+        <v>8.461429503764982</v>
       </c>
       <c r="D288" t="n">
-        <v>8.199686220600897</v>
+        <v>8.199685276496087</v>
       </c>
       <c r="E288" t="n">
-        <v>8.456469081678438</v>
+        <v>8.456468108007872</v>
       </c>
       <c r="F288" t="n">
         <v>15329699</v>
@@ -6212,16 +6212,16 @@
         <v>44169</v>
       </c>
       <c r="B290" t="n">
-        <v>8.772794723510742</v>
+        <v>8.772793769836426</v>
       </c>
       <c r="C290" t="n">
-        <v>8.948945284925747</v>
+        <v>8.948944312102428</v>
       </c>
       <c r="D290" t="n">
-        <v>8.683479763850318</v>
+        <v>8.683478819885265</v>
       </c>
       <c r="E290" t="n">
-        <v>8.886920238013465</v>
+        <v>8.886919271932774</v>
       </c>
       <c r="F290" t="n">
         <v>10446369</v>
@@ -6232,16 +6232,16 @@
         <v>44172</v>
       </c>
       <c r="B291" t="n">
-        <v>8.647504806518555</v>
+        <v>8.647505760192871</v>
       </c>
       <c r="C291" t="n">
-        <v>8.827376626156168</v>
+        <v>8.82737759966732</v>
       </c>
       <c r="D291" t="n">
-        <v>8.621454127772409</v>
+        <v>8.621455078573774</v>
       </c>
       <c r="E291" t="n">
-        <v>8.807528362331166</v>
+        <v>8.807529333653388</v>
       </c>
       <c r="F291" t="n">
         <v>10174485</v>
@@ -6392,16 +6392,16 @@
         <v>44182</v>
       </c>
       <c r="B299" t="n">
-        <v>9.125097274780273</v>
+        <v>9.125096321105957</v>
       </c>
       <c r="C299" t="n">
-        <v>9.233020380265208</v>
+        <v>9.233019415311725</v>
       </c>
       <c r="D299" t="n">
-        <v>9.105249008435251</v>
+        <v>9.1052480568353</v>
       </c>
       <c r="E299" t="n">
-        <v>9.230539235289285</v>
+        <v>9.230538270595108</v>
       </c>
       <c r="F299" t="n">
         <v>5262456</v>
@@ -6452,16 +6452,16 @@
         <v>44187</v>
       </c>
       <c r="B302" t="n">
-        <v>9.018414497375488</v>
+        <v>9.018413543701172</v>
       </c>
       <c r="C302" t="n">
-        <v>9.117654044402261</v>
+        <v>9.117653080233614</v>
       </c>
       <c r="D302" t="n">
-        <v>8.941504362170608</v>
+        <v>8.941503416629342</v>
       </c>
       <c r="E302" t="n">
-        <v>8.974996692978687</v>
+        <v>8.974995743895692</v>
       </c>
       <c r="F302" t="n">
         <v>3700636</v>
@@ -6572,16 +6572,16 @@
         <v>44201</v>
       </c>
       <c r="B308" t="n">
-        <v>9.097805976867676</v>
+        <v>9.097805023193359</v>
       </c>
       <c r="C308" t="n">
-        <v>9.304968615993069</v>
+        <v>9.304967640603</v>
       </c>
       <c r="D308" t="n">
-        <v>9.012211393852336</v>
+        <v>9.012210449150441</v>
       </c>
       <c r="E308" t="n">
-        <v>9.304968615993069</v>
+        <v>9.304967640603</v>
       </c>
       <c r="F308" t="n">
         <v>8306796</v>
@@ -6592,16 +6592,16 @@
         <v>44202</v>
       </c>
       <c r="B309" t="n">
-        <v>9.023375511169434</v>
+        <v>9.02337646484375</v>
       </c>
       <c r="C309" t="n">
-        <v>9.178437672356514</v>
+        <v>9.178438642419241</v>
       </c>
       <c r="D309" t="n">
-        <v>8.883199324604012</v>
+        <v>8.883200263463204</v>
       </c>
       <c r="E309" t="n">
-        <v>9.091602075844966</v>
+        <v>9.091603036730099</v>
       </c>
       <c r="F309" t="n">
         <v>6995714</v>
@@ -6632,16 +6632,16 @@
         <v>44204</v>
       </c>
       <c r="B311" t="n">
-        <v>9.49476432800293</v>
+        <v>9.494765281677246</v>
       </c>
       <c r="C311" t="n">
-        <v>9.533219836566508</v>
+        <v>9.533220794103377</v>
       </c>
       <c r="D311" t="n">
-        <v>9.077957042182957</v>
+        <v>9.077957953992263</v>
       </c>
       <c r="E311" t="n">
-        <v>9.178437593380119</v>
+        <v>9.178438515281906</v>
       </c>
       <c r="F311" t="n">
         <v>10280973</v>
@@ -6732,16 +6732,16 @@
         <v>44211</v>
       </c>
       <c r="B316" t="n">
-        <v>9.479877471923828</v>
+        <v>9.479878425598145</v>
       </c>
       <c r="C316" t="n">
-        <v>9.607648827608905</v>
+        <v>9.607649794137002</v>
       </c>
       <c r="D316" t="n">
-        <v>9.378157688462947</v>
+        <v>9.378158631904267</v>
       </c>
       <c r="E316" t="n">
-        <v>9.589041582834192</v>
+        <v>9.589042547490402</v>
       </c>
       <c r="F316" t="n">
         <v>14334303</v>
@@ -6892,16 +6892,16 @@
         <v>44224</v>
       </c>
       <c r="B324" t="n">
-        <v>9.368233680725098</v>
+        <v>9.368232727050781</v>
       </c>
       <c r="C324" t="n">
-        <v>9.399245757239534</v>
+        <v>9.399244800408228</v>
       </c>
       <c r="D324" t="n">
-        <v>9.102767267989694</v>
+        <v>9.102766341339521</v>
       </c>
       <c r="E324" t="n">
-        <v>9.180918415575915</v>
+        <v>9.180917480970056</v>
       </c>
       <c r="F324" t="n">
         <v>7429217</v>
@@ -6912,16 +6912,16 @@
         <v>44225</v>
       </c>
       <c r="B325" t="n">
-        <v>9.36327075958252</v>
+        <v>9.363271713256836</v>
       </c>
       <c r="C325" t="n">
-        <v>9.571675294860224</v>
+        <v>9.571676269761104</v>
       </c>
       <c r="D325" t="n">
-        <v>9.215652034482874</v>
+        <v>9.215652973121827</v>
       </c>
       <c r="E325" t="n">
-        <v>9.312410421451789</v>
+        <v>9.312411369945844</v>
       </c>
       <c r="F325" t="n">
         <v>11022611</v>
@@ -6952,16 +6952,16 @@
         <v>44229</v>
       </c>
       <c r="B327" t="n">
-        <v>10.133620262146</v>
+        <v>10.13361930847168</v>
       </c>
       <c r="C327" t="n">
-        <v>10.18448060527895</v>
+        <v>10.18447964681817</v>
       </c>
       <c r="D327" t="n">
-        <v>9.832180367414875</v>
+        <v>9.832179442109044</v>
       </c>
       <c r="E327" t="n">
-        <v>10.11005072588166</v>
+        <v>10.11004977442547</v>
       </c>
       <c r="F327" t="n">
         <v>20046878</v>
@@ -6992,16 +6992,16 @@
         <v>44231</v>
       </c>
       <c r="B329" t="n">
-        <v>10.38668155670166</v>
+        <v>10.38668251037598</v>
       </c>
       <c r="C329" t="n">
-        <v>10.38668155670166</v>
+        <v>10.38668251037598</v>
       </c>
       <c r="D329" t="n">
-        <v>10.11749300250636</v>
+        <v>10.11749393146458</v>
       </c>
       <c r="E329" t="n">
-        <v>10.17703779267104</v>
+        <v>10.17703872709649</v>
       </c>
       <c r="F329" t="n">
         <v>12166787</v>
@@ -7012,16 +7012,16 @@
         <v>44232</v>
       </c>
       <c r="B330" t="n">
-        <v>10.5566291809082</v>
+        <v>10.55663013458252</v>
       </c>
       <c r="C330" t="n">
-        <v>10.58143973441847</v>
+        <v>10.58144069033415</v>
       </c>
       <c r="D330" t="n">
-        <v>10.32465689384235</v>
+        <v>10.32465782656054</v>
       </c>
       <c r="E330" t="n">
-        <v>10.41893413810214</v>
+        <v>10.41893507933724</v>
       </c>
       <c r="F330" t="n">
         <v>10745440</v>
@@ -7192,16 +7192,16 @@
         <v>44249</v>
       </c>
       <c r="B339" t="n">
-        <v>11.09376621246338</v>
+        <v>11.09376525878906</v>
       </c>
       <c r="C339" t="n">
-        <v>11.20292944052197</v>
+        <v>11.20292847746345</v>
       </c>
       <c r="D339" t="n">
-        <v>10.63602222835513</v>
+        <v>10.63602131403072</v>
       </c>
       <c r="E339" t="n">
-        <v>10.93994416306512</v>
+        <v>10.9399432226141</v>
       </c>
       <c r="F339" t="n">
         <v>14982292</v>
@@ -7292,16 +7292,16 @@
         <v>44256</v>
       </c>
       <c r="B344" t="n">
-        <v>21.85701560974121</v>
+        <v>21.85701751708984</v>
       </c>
       <c r="C344" t="n">
-        <v>23.99306407785948</v>
+        <v>23.99306617161</v>
       </c>
       <c r="D344" t="n">
-        <v>16.3107860983666</v>
+        <v>16.31078752172449</v>
       </c>
       <c r="E344" t="n">
-        <v>16.8635354591482</v>
+        <v>16.86353693074166</v>
       </c>
       <c r="F344" t="n">
         <v>49361500</v>
@@ -7312,16 +7312,16 @@
         <v>44257</v>
       </c>
       <c r="B345" t="n">
-        <v>21.19184303283691</v>
+        <v>21.19184494018555</v>
       </c>
       <c r="C345" t="n">
-        <v>22.95314478521037</v>
+        <v>22.95314685108304</v>
       </c>
       <c r="D345" t="n">
-        <v>20.6953049717416</v>
+        <v>20.69530683439987</v>
       </c>
       <c r="E345" t="n">
-        <v>22.18491736810308</v>
+        <v>22.18491936483229</v>
       </c>
       <c r="F345" t="n">
         <v>20095700</v>
@@ -7352,16 +7352,16 @@
         <v>44259</v>
       </c>
       <c r="B347" t="n">
-        <v>20.86394119262695</v>
+        <v>20.86394309997559</v>
       </c>
       <c r="C347" t="n">
-        <v>21.52911312081577</v>
+        <v>21.52911508897337</v>
       </c>
       <c r="D347" t="n">
-        <v>20.01139593391831</v>
+        <v>20.0113977633286</v>
       </c>
       <c r="E347" t="n">
-        <v>20.2362428583874</v>
+        <v>20.23624470835284</v>
       </c>
       <c r="F347" t="n">
         <v>8984600</v>
@@ -7732,16 +7732,16 @@
         <v>44286</v>
       </c>
       <c r="B366" t="n">
-        <v>31.08511924743652</v>
+        <v>31.08511734008789</v>
       </c>
       <c r="C366" t="n">
-        <v>32.65904960734591</v>
+        <v>32.65904760342265</v>
       </c>
       <c r="D366" t="n">
-        <v>30.82279871206804</v>
+        <v>30.82279682081511</v>
       </c>
       <c r="E366" t="n">
-        <v>31.95640225288098</v>
+        <v>31.95640029207138</v>
       </c>
       <c r="F366" t="n">
         <v>8195900</v>
@@ -7792,16 +7792,16 @@
         <v>44292</v>
       </c>
       <c r="B369" t="n">
-        <v>30.57921028137207</v>
+        <v>30.5792121887207</v>
       </c>
       <c r="C369" t="n">
-        <v>32.19998297677536</v>
+        <v>32.19998498521812</v>
       </c>
       <c r="D369" t="n">
-        <v>30.48552540315069</v>
+        <v>30.48552730465581</v>
       </c>
       <c r="E369" t="n">
-        <v>31.01953707148042</v>
+        <v>31.01953900629401</v>
       </c>
       <c r="F369" t="n">
         <v>6923500</v>
@@ -7812,16 +7812,16 @@
         <v>44293</v>
       </c>
       <c r="B370" t="n">
-        <v>30.95395851135254</v>
+        <v>30.95395660400391</v>
       </c>
       <c r="C370" t="n">
-        <v>31.36617699981515</v>
+        <v>31.36617506706607</v>
       </c>
       <c r="D370" t="n">
-        <v>30.40120912458377</v>
+        <v>30.40120725129495</v>
       </c>
       <c r="E370" t="n">
-        <v>30.72910978883253</v>
+        <v>30.72910789533883</v>
       </c>
       <c r="F370" t="n">
         <v>4745700</v>
@@ -8012,16 +8012,16 @@
         <v>44308</v>
       </c>
       <c r="B380" t="n">
-        <v>36.30344772338867</v>
+        <v>36.30344390869141</v>
       </c>
       <c r="C380" t="n">
-        <v>38.03664315290104</v>
+        <v>38.03663915608288</v>
       </c>
       <c r="D380" t="n">
-        <v>35.88185858344396</v>
+        <v>35.88185481304648</v>
       </c>
       <c r="E380" t="n">
-        <v>37.12788831107506</v>
+        <v>37.12788440974715</v>
       </c>
       <c r="F380" t="n">
         <v>6756200</v>
@@ -8052,16 +8052,16 @@
         <v>44312</v>
       </c>
       <c r="B382" t="n">
-        <v>35.91933059692383</v>
+        <v>35.91933441162109</v>
       </c>
       <c r="C382" t="n">
-        <v>36.30344431641451</v>
+        <v>36.30344817190534</v>
       </c>
       <c r="D382" t="n">
-        <v>35.5164791869886</v>
+        <v>35.51648295890232</v>
       </c>
       <c r="E382" t="n">
-        <v>35.88185521603473</v>
+        <v>35.88185902675205</v>
       </c>
       <c r="F382" t="n">
         <v>4241900</v>
@@ -8072,16 +8072,16 @@
         <v>44313</v>
       </c>
       <c r="B383" t="n">
-        <v>35.46963882446289</v>
+        <v>35.46963500976562</v>
       </c>
       <c r="C383" t="n">
-        <v>36.29407938304689</v>
+        <v>36.2940754796825</v>
       </c>
       <c r="D383" t="n">
-        <v>35.27289842405</v>
+        <v>35.27289463051181</v>
       </c>
       <c r="E383" t="n">
-        <v>36.05986359955081</v>
+        <v>36.05985972137591</v>
       </c>
       <c r="F383" t="n">
         <v>2386900</v>
@@ -35011,20 +35011,32 @@
       <c r="A1730" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B1730" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="C1730" t="n">
-        <v>3.39</v>
-      </c>
-      <c r="D1730" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="E1730" t="n">
-        <v>3.28</v>
-      </c>
+      <c r="B1730" t="inlineStr"/>
+      <c r="C1730" t="inlineStr"/>
+      <c r="D1730" t="inlineStr"/>
+      <c r="E1730" t="inlineStr"/>
       <c r="F1730" t="n">
-        <v>10577600</v>
+        <v>9170400</v>
+      </c>
+    </row>
+    <row r="1731">
+      <c r="A1731" s="1" t="n">
+        <v>46283</v>
+      </c>
+      <c r="B1731" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C1731" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="D1731" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="E1731" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="F1731" t="n">
+        <v>9177300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1731"/>
+  <dimension ref="A1:F1732"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553905844688416</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553905844688416</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553905844688416</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553905844688416</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173593521118</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173593521118</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173593521118</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173593521118</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500961303711</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500961303711</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500961303711</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500961303711</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461271286011</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461271286011</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461271286011</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461271286011</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647353172302246</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647353172302246</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647353172302246</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647353172302246</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951085090637207</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951085090637208</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951085090637208</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951085090637208</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780762</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="C55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="D55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="E55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="C64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="D64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="E64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610103607178</v>
+        <v>10.60610008239746</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448453125444</v>
+        <v>11.08448353456507</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087005615234375</v>
+        <v>8.087006568908691</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167514235155968</v>
+        <v>8.167515198324406</v>
       </c>
       <c r="D103" t="n">
-        <v>7.934155965259957</v>
+        <v>7.93415690090921</v>
       </c>
       <c r="E103" t="n">
-        <v>7.99249553273396</v>
+        <v>7.992496475263009</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174576363958773</v>
+        <v>7.174577261989849</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269086440314109</v>
+        <v>7.269087350174872</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151270575596</v>
+        <v>7.885151755156881</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395100920432114</v>
+        <v>7.395101374897398</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642458915710449</v>
+        <v>7.642459392547607</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934155910701143</v>
+        <v>7.934156405738198</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650689636966175</v>
+        <v>6.650690051923714</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251216760168</v>
+        <v>7.242251668627103</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255058288574</v>
+        <v>7.277255535125732</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292230712304</v>
+        <v>7.641292731402749</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086097777741</v>
+        <v>6.70086141684674</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766201694169458</v>
+        <v>6.766202137520195</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2652,16 +2652,16 @@
         <v>43909</v>
       </c>
       <c r="B112" t="n">
-        <v>7.521113395690918</v>
+        <v>7.521113872528076</v>
       </c>
       <c r="C112" t="n">
-        <v>8.106841959390016</v>
+        <v>8.106842473362253</v>
       </c>
       <c r="D112" t="n">
-        <v>6.356659520848136</v>
+        <v>6.35665992385914</v>
       </c>
       <c r="E112" t="n">
-        <v>6.779036703963478</v>
+        <v>6.779037133753115</v>
       </c>
       <c r="F112" t="n">
         <v>19250108</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314098358154</v>
+        <v>7.844314575195312</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109174606594431</v>
+        <v>8.109175099531829</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235250900954319</v>
+        <v>7.235251340767977</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146197500977</v>
+        <v>7.829146673416115</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738137245178223</v>
+        <v>7.738136291503906</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145346146541403</v>
+        <v>8.145345142681279</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298979071039</v>
+        <v>7.690298031292473</v>
       </c>
       <c r="E117" t="n">
-        <v>8.13834499423681</v>
+        <v>8.138343991239532</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775676727295</v>
+        <v>7.469774723052979</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304804343318</v>
+        <v>7.746303815364229</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351930089923889</v>
+        <v>7.351929151295045</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113786687701</v>
+        <v>7.51411282735269</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2792,16 +2792,16 @@
         <v>43920</v>
       </c>
       <c r="B119" t="n">
-        <v>7.584119319915771</v>
+        <v>7.58411979675293</v>
       </c>
       <c r="C119" t="n">
-        <v>7.677462963028194</v>
+        <v>7.677463445734158</v>
       </c>
       <c r="D119" t="n">
-        <v>7.322759808396101</v>
+        <v>7.322760268800774</v>
       </c>
       <c r="E119" t="n">
-        <v>7.354262888769144</v>
+        <v>7.354263351154514</v>
       </c>
       <c r="F119" t="n">
         <v>7283457</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469455718994</v>
+        <v>7.740469932556152</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757971914786575</v>
+        <v>7.757972392701939</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582953929901123</v>
+        <v>7.582952976226807</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840815002303775</v>
+        <v>7.840814016199421</v>
       </c>
       <c r="D122" t="n">
-        <v>7.381100395706687</v>
+        <v>7.38109946741859</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455774312072345</v>
+        <v>7.455773374392843</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261459350586</v>
+        <v>7.340261936187744</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624426344595</v>
+        <v>7.622624921524582</v>
       </c>
       <c r="D123" t="n">
-        <v>7.21541557567713</v>
+        <v>7.215416044404066</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457147585694</v>
+        <v>7.621457642689852</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613289833068848</v>
+        <v>7.613289356231689</v>
       </c>
       <c r="C124" t="n">
-        <v>7.699632328290281</v>
+        <v>7.699631846045301</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497777973422238</v>
+        <v>7.497777503819842</v>
       </c>
       <c r="E124" t="n">
-        <v>7.584119628270164</v>
+        <v>7.58411915326</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672797679901123</v>
+        <v>7.672796726226807</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109175966524298</v>
+        <v>8.109174958611256</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661129932612202</v>
+        <v>7.661128980388104</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840815257758265</v>
+        <v>7.840814283200555</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798511505127</v>
+        <v>7.700798988342285</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307131173381</v>
+        <v>7.781307612995673</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430533892927</v>
+        <v>7.362430989778177</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629459127295</v>
+        <v>7.678629934591736</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500110626220703</v>
+        <v>7.500111103057861</v>
       </c>
       <c r="C129" t="n">
-        <v>7.750970514277116</v>
+        <v>7.75097100706328</v>
       </c>
       <c r="D129" t="n">
-        <v>7.455773361693658</v>
+        <v>7.45577383571197</v>
       </c>
       <c r="E129" t="n">
-        <v>7.49427759388343</v>
+        <v>7.494278070349739</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265598297119</v>
+        <v>7.375265121459961</v>
       </c>
       <c r="C130" t="n">
-        <v>7.494278464239883</v>
+        <v>7.49427797970812</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762513925697</v>
+        <v>7.343762039125325</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935961570344</v>
+        <v>7.407935482620931</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566619396209717</v>
+        <v>7.566618919372559</v>
       </c>
       <c r="C131" t="n">
-        <v>7.5887884509226</v>
+        <v>7.58878797268838</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234084415890043</v>
+        <v>7.234083960008746</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444106376032958</v>
+        <v>7.444105906916389</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3072,16 +3072,16 @@
         <v>43941</v>
       </c>
       <c r="B133" t="n">
-        <v>7.584119319915771</v>
+        <v>7.58411979675293</v>
       </c>
       <c r="C133" t="n">
-        <v>7.592287750070918</v>
+        <v>7.592288227421651</v>
       </c>
       <c r="D133" t="n">
-        <v>7.316925095374786</v>
+        <v>7.316925555412612</v>
       </c>
       <c r="E133" t="n">
-        <v>7.350762733255134</v>
+        <v>7.350763195420438</v>
       </c>
       <c r="F133" t="n">
         <v>10524157</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251522064208984</v>
+        <v>8.251523017883301</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431207358265677</v>
+        <v>8.431208332707222</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852482318878174</v>
+        <v>7.852481842041016</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764498666425</v>
+        <v>7.357764051870702</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484550476074</v>
+        <v>7.887484073638916</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826736101882</v>
+        <v>7.966826254468098</v>
       </c>
       <c r="D139" t="n">
-        <v>7.700798933367937</v>
+        <v>7.70079846781684</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980845212174</v>
+        <v>7.841980371125938</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726467609405518</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817898699254</v>
+        <v>7.882817412213003</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726467609405518</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311578781807</v>
+        <v>7.816311096399979</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -35011,12 +35011,20 @@
       <c r="A1730" s="1" t="n">
         <v>46282</v>
       </c>
-      <c r="B1730" t="inlineStr"/>
-      <c r="C1730" t="inlineStr"/>
-      <c r="D1730" t="inlineStr"/>
-      <c r="E1730" t="inlineStr"/>
+      <c r="B1730" t="n">
+        <v>3.299999952316284</v>
+      </c>
+      <c r="C1730" t="n">
+        <v>3.390000104904175</v>
+      </c>
+      <c r="D1730" t="n">
+        <v>3.210000038146973</v>
+      </c>
+      <c r="E1730" t="n">
+        <v>3.279999971389771</v>
+      </c>
       <c r="F1730" t="n">
-        <v>9170400</v>
+        <v>10577600</v>
       </c>
     </row>
     <row r="1731">
@@ -35024,19 +35032,39 @@
         <v>46283</v>
       </c>
       <c r="B1731" t="n">
-        <v>3.05</v>
+        <v>3.049999952316284</v>
       </c>
       <c r="C1731" t="n">
-        <v>3.23</v>
+        <v>3.230000019073486</v>
       </c>
       <c r="D1731" t="n">
-        <v>3.02</v>
+        <v>3.019999980926514</v>
       </c>
       <c r="E1731" t="n">
-        <v>3.23</v>
+        <v>3.230000019073486</v>
       </c>
       <c r="F1731" t="n">
         <v>9177300</v>
+      </c>
+    </row>
+    <row r="1732">
+      <c r="A1732" s="1" t="n">
+        <v>46286</v>
+      </c>
+      <c r="B1732" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C1732" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="D1732" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="E1732" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="F1732" t="n">
+        <v>9207300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1732"/>
+  <dimension ref="A1:F1733"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553905844688416</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553905844688416</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553905844688416</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553905844688416</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173593521118</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173593521118</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173593521118</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173593521118</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725194931030273</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725194931030273</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725194931030273</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725194931030273</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725194931030273</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725194931030273</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725194931030273</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725194931030273</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500961303711</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500961303711</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500961303711</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500961303711</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152358293533325</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152358293533325</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152358293533325</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152358293533325</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.12565279006958</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.12565279006958</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.12565279006958</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.12565279006958</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.922461271286011</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.922461271286011</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.922461271286011</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.922461271286011</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486270904541</v>
       </c>
       <c r="C39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486270904541</v>
       </c>
       <c r="D39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486270904541</v>
       </c>
       <c r="E39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486270904541</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222900390625</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959037780762</v>
+        <v>3.926958560943604</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075627326965332</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294585227966309</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294585227966309</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294585227966309</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294585227966309</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.5891432762146</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156005859375</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156005859375</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156005859375</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156005859375</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014761924743652</v>
       </c>
       <c r="C64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014761924743652</v>
       </c>
       <c r="D64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014761924743652</v>
       </c>
       <c r="E64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014761924743652</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610008239746</v>
+        <v>10.60610103607178</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448353456507</v>
+        <v>11.08448453125444</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087006568908691</v>
+        <v>8.087005615234375</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167515198324406</v>
+        <v>8.167514235155968</v>
       </c>
       <c r="D103" t="n">
-        <v>7.93415690090921</v>
+        <v>7.934155965259957</v>
       </c>
       <c r="E103" t="n">
-        <v>7.992496475263009</v>
+        <v>7.99249553273396</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174577261989849</v>
+        <v>7.174576363958773</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269087350174872</v>
+        <v>7.269086440314109</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151755156881</v>
+        <v>7.885151270575596</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395101374897398</v>
+        <v>7.395100920432114</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642459392547607</v>
+        <v>7.642458915710449</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934156405738198</v>
+        <v>7.934155910701143</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650690051923714</v>
+        <v>6.650689636966175</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251668627103</v>
+        <v>7.242251216760168</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255535125732</v>
+        <v>7.277255058288574</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292731402749</v>
+        <v>7.641292230712304</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086141684674</v>
+        <v>6.70086097777741</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766202137520195</v>
+        <v>6.766201694169458</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2652,16 +2652,16 @@
         <v>43909</v>
       </c>
       <c r="B112" t="n">
-        <v>7.521113872528076</v>
+        <v>7.521113395690918</v>
       </c>
       <c r="C112" t="n">
-        <v>8.106842473362253</v>
+        <v>8.106841959390016</v>
       </c>
       <c r="D112" t="n">
-        <v>6.35665992385914</v>
+        <v>6.356659520848136</v>
       </c>
       <c r="E112" t="n">
-        <v>6.779037133753115</v>
+        <v>6.779036703963478</v>
       </c>
       <c r="F112" t="n">
         <v>19250108</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314575195312</v>
+        <v>7.844314098358154</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109175099531829</v>
+        <v>8.109174606594431</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235251340767977</v>
+        <v>7.235250900954319</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146673416115</v>
+        <v>7.829146197500977</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738136291503906</v>
+        <v>7.738137245178223</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145345142681279</v>
+        <v>8.145346146541403</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298031292473</v>
+        <v>7.690298979071039</v>
       </c>
       <c r="E117" t="n">
-        <v>8.138343991239532</v>
+        <v>8.13834499423681</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469774723052979</v>
+        <v>7.469775676727295</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746303815364229</v>
+        <v>7.746304804343318</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351929151295045</v>
+        <v>7.351930089923889</v>
       </c>
       <c r="E118" t="n">
-        <v>7.51411282735269</v>
+        <v>7.514113786687701</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2792,16 +2792,16 @@
         <v>43920</v>
       </c>
       <c r="B119" t="n">
-        <v>7.58411979675293</v>
+        <v>7.584119319915771</v>
       </c>
       <c r="C119" t="n">
-        <v>7.677463445734158</v>
+        <v>7.677462963028194</v>
       </c>
       <c r="D119" t="n">
-        <v>7.322760268800774</v>
+        <v>7.322759808396101</v>
       </c>
       <c r="E119" t="n">
-        <v>7.354263351154514</v>
+        <v>7.354262888769144</v>
       </c>
       <c r="F119" t="n">
         <v>7283457</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469932556152</v>
+        <v>7.740469455718994</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757972392701939</v>
+        <v>7.757971914786575</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582952976226807</v>
+        <v>7.582953929901123</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840814016199421</v>
+        <v>7.840815002303775</v>
       </c>
       <c r="D122" t="n">
-        <v>7.38109946741859</v>
+        <v>7.381100395706687</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455773374392843</v>
+        <v>7.455774312072345</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261936187744</v>
+        <v>7.340261459350586</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624921524582</v>
+        <v>7.622624426344595</v>
       </c>
       <c r="D123" t="n">
-        <v>7.215416044404066</v>
+        <v>7.21541557567713</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457642689852</v>
+        <v>7.621457147585694</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613289356231689</v>
+        <v>7.613289833068848</v>
       </c>
       <c r="C124" t="n">
-        <v>7.699631846045301</v>
+        <v>7.699632328290281</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497777503819842</v>
+        <v>7.497777973422238</v>
       </c>
       <c r="E124" t="n">
-        <v>7.58411915326</v>
+        <v>7.584119628270164</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672796726226807</v>
+        <v>7.672797679901123</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109174958611256</v>
+        <v>8.109175966524298</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661128980388104</v>
+        <v>7.661129932612202</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840814283200555</v>
+        <v>7.840815257758265</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798988342285</v>
+        <v>7.700798511505127</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307612995673</v>
+        <v>7.781307131173381</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430989778177</v>
+        <v>7.362430533892927</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629934591736</v>
+        <v>7.678629459127295</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500111103057861</v>
+        <v>7.500110626220703</v>
       </c>
       <c r="C129" t="n">
-        <v>7.75097100706328</v>
+        <v>7.750970514277116</v>
       </c>
       <c r="D129" t="n">
-        <v>7.45577383571197</v>
+        <v>7.455773361693658</v>
       </c>
       <c r="E129" t="n">
-        <v>7.494278070349739</v>
+        <v>7.49427759388343</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265121459961</v>
+        <v>7.375265598297119</v>
       </c>
       <c r="C130" t="n">
-        <v>7.49427797970812</v>
+        <v>7.494278464239883</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762039125325</v>
+        <v>7.343762513925697</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935482620931</v>
+        <v>7.407935961570344</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566618919372559</v>
+        <v>7.566619396209717</v>
       </c>
       <c r="C131" t="n">
-        <v>7.58878797268838</v>
+        <v>7.5887884509226</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234083960008746</v>
+        <v>7.234084415890043</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444105906916389</v>
+        <v>7.444106376032958</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3072,16 +3072,16 @@
         <v>43941</v>
       </c>
       <c r="B133" t="n">
-        <v>7.58411979675293</v>
+        <v>7.584119319915771</v>
       </c>
       <c r="C133" t="n">
-        <v>7.592288227421651</v>
+        <v>7.592287750070918</v>
       </c>
       <c r="D133" t="n">
-        <v>7.316925555412612</v>
+        <v>7.316925095374786</v>
       </c>
       <c r="E133" t="n">
-        <v>7.350763195420438</v>
+        <v>7.350762733255134</v>
       </c>
       <c r="F133" t="n">
         <v>10524157</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251523017883301</v>
+        <v>8.251522064208984</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431208332707222</v>
+        <v>8.431207358265677</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852481842041016</v>
+        <v>7.852482318878174</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764051870702</v>
+        <v>7.357764498666425</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484073638916</v>
+        <v>7.887484550476074</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826254468098</v>
+        <v>7.966826736101882</v>
       </c>
       <c r="D139" t="n">
-        <v>7.70079846781684</v>
+        <v>7.700798933367937</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980371125938</v>
+        <v>7.841980845212174</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726467609405518</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817412213003</v>
+        <v>7.882817898699254</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726467609405518</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311096399979</v>
+        <v>7.816311578781807</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -35052,19 +35052,39 @@
         <v>46286</v>
       </c>
       <c r="B1732" t="n">
-        <v>2.9</v>
+        <v>2.900000095367432</v>
       </c>
       <c r="C1732" t="n">
-        <v>3.09</v>
+        <v>3.089999914169312</v>
       </c>
       <c r="D1732" t="n">
-        <v>2.9</v>
+        <v>2.900000095367432</v>
       </c>
       <c r="E1732" t="n">
-        <v>3.08</v>
+        <v>3.079999923706055</v>
       </c>
       <c r="F1732" t="n">
         <v>9207300</v>
+      </c>
+    </row>
+    <row r="1733">
+      <c r="A1733" s="1" t="n">
+        <v>46287</v>
+      </c>
+      <c r="B1733" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C1733" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="D1733" t="n">
+        <v>2.81</v>
+      </c>
+      <c r="E1733" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="F1733" t="n">
+        <v>3362800</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1733"/>
+  <dimension ref="A1:F1734"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616733074188232</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616733074188232</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616733074188232</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616733074188232</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725194931030273</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725194931030273</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725194931030273</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725194931030273</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725194931030273</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725194931030273</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725194931030273</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725194931030273</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152358293533325</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152358293533325</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152358293533325</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152358293533325</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.12565279006958</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="C37" t="n">
-        <v>2.12565279006958</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="D37" t="n">
-        <v>2.12565279006958</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="E37" t="n">
-        <v>2.12565279006958</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486270904541</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486270904541</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486270904541</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486270904541</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647353172302246</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647353172302246</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647353172302246</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647353172302246</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997222900390625</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958560943604</v>
+        <v>3.926959037780762</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294585227966309</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294585227966309</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294585227966309</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294585227966309</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.5891432762146</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.014761924743652</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="C64" t="n">
-        <v>9.014761924743652</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="D64" t="n">
-        <v>9.014761924743652</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="E64" t="n">
-        <v>9.014761924743652</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -35072,19 +35072,39 @@
         <v>46287</v>
       </c>
       <c r="B1733" t="n">
-        <v>2.91</v>
+        <v>2.910000085830688</v>
       </c>
       <c r="C1733" t="n">
-        <v>2.96</v>
+        <v>2.960000038146973</v>
       </c>
       <c r="D1733" t="n">
-        <v>2.81</v>
+        <v>2.809999942779541</v>
       </c>
       <c r="E1733" t="n">
-        <v>2.9</v>
+        <v>2.900000095367432</v>
       </c>
       <c r="F1733" t="n">
         <v>3362800</v>
+      </c>
+    </row>
+    <row r="1734">
+      <c r="A1734" s="1" t="n">
+        <v>46288</v>
+      </c>
+      <c r="B1734" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C1734" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="D1734" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E1734" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="F1734" t="n">
+        <v>1346100</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1734"/>
+  <dimension ref="A1:F1735"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799173712730408</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799173712730408</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799173712730408</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799173712730408</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853133201599121</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853133201599121</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853133201599121</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853133201599121</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853133201599121</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853133201599121</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853133201599121</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853133201599121</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853133201599121</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853133201599121</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853133201599121</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853133201599121</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725196599960327</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461271286011</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461271286011</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461271286011</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461271286011</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951085567474365</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951085567474365</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951085567474365</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951085567474365</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.99722146987915</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.99722146987915</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.99722146987915</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.99722146987915</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075627326965332</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="C57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="D57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="E57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589143753051758</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589143753051758</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589143753051758</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589143753051758</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156005859375</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156005859375</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156005859375</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156005859375</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257293701172</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257293701172</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257293701172</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257293701172</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="C64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="D64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="E64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -1872,16 +1872,16 @@
         <v>43741</v>
       </c>
       <c r="B73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F73" t="n">
         <v>755</v>
@@ -1892,16 +1892,16 @@
         <v>43747</v>
       </c>
       <c r="B74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F74" t="n">
         <v>755</v>
@@ -1952,16 +1952,16 @@
         <v>43773</v>
       </c>
       <c r="B77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F77" t="n">
         <v>1510</v>
@@ -2012,16 +2012,16 @@
         <v>43802</v>
       </c>
       <c r="B80" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C80" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D80" t="n">
-        <v>9.21762282756219</v>
+        <v>9.217621990355065</v>
       </c>
       <c r="E80" t="n">
-        <v>9.21762282756219</v>
+        <v>9.217621990355065</v>
       </c>
       <c r="F80" t="n">
         <v>1510</v>
@@ -2032,16 +2032,16 @@
         <v>43809</v>
       </c>
       <c r="B81" t="n">
-        <v>10.37040996551514</v>
+        <v>10.37040901184082</v>
       </c>
       <c r="C81" t="n">
-        <v>10.37040996551514</v>
+        <v>10.37040901184082</v>
       </c>
       <c r="D81" t="n">
-        <v>9.685505554677158</v>
+        <v>9.685504663987407</v>
       </c>
       <c r="E81" t="n">
-        <v>9.685505554677158</v>
+        <v>9.685504663987407</v>
       </c>
       <c r="F81" t="n">
         <v>1510</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610103607178</v>
+        <v>10.60610008239746</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448453125444</v>
+        <v>11.08448353456507</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2392,16 +2392,16 @@
         <v>43892</v>
       </c>
       <c r="B99" t="n">
-        <v>8.602725982666016</v>
+        <v>8.602726936340332</v>
       </c>
       <c r="C99" t="n">
-        <v>8.865252774798098</v>
+        <v>8.865253757575406</v>
       </c>
       <c r="D99" t="n">
-        <v>8.459211201840722</v>
+        <v>8.459212139605388</v>
       </c>
       <c r="E99" t="n">
-        <v>8.721737993972804</v>
+        <v>8.72173896084046</v>
       </c>
       <c r="F99" t="n">
         <v>11103420</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174576363958773</v>
+        <v>7.174577261989849</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269086440314109</v>
+        <v>7.269087350174872</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151270575596</v>
+        <v>7.885151755156881</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395100920432114</v>
+        <v>7.395101374897398</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642458915710449</v>
+        <v>7.642459392547607</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934155910701143</v>
+        <v>7.934156405738198</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650689636966175</v>
+        <v>6.650690051923714</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251216760168</v>
+        <v>7.242251668627103</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255058288574</v>
+        <v>7.277256011962891</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292230712304</v>
+        <v>7.641293232093194</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086097777741</v>
+        <v>6.70086185591607</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766201694169458</v>
+        <v>6.766202580870931</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2632,16 +2632,16 @@
         <v>43908</v>
       </c>
       <c r="B111" t="n">
-        <v>6.985558032989502</v>
+        <v>6.98555850982666</v>
       </c>
       <c r="C111" t="n">
-        <v>8.075337993481165</v>
+        <v>8.075338544707167</v>
       </c>
       <c r="D111" t="n">
-        <v>6.710196211513576</v>
+        <v>6.71019666955442</v>
       </c>
       <c r="E111" t="n">
-        <v>7.140740982312391</v>
+        <v>7.140741469742403</v>
       </c>
       <c r="F111" t="n">
         <v>26337960</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314098358154</v>
+        <v>7.844314575195312</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109174606594431</v>
+        <v>8.109175099531829</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235250900954319</v>
+        <v>7.235251340767977</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146197500977</v>
+        <v>7.829146673416115</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738137245178223</v>
+        <v>7.738136291503906</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145346146541403</v>
+        <v>8.145345142681279</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298979071039</v>
+        <v>7.690298031292473</v>
       </c>
       <c r="E117" t="n">
-        <v>8.13834499423681</v>
+        <v>8.138343991239532</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775676727295</v>
+        <v>7.469774723052979</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304804343318</v>
+        <v>7.746303815364229</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351930089923889</v>
+        <v>7.351929151295045</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113786687701</v>
+        <v>7.51411282735269</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2792,16 +2792,16 @@
         <v>43920</v>
       </c>
       <c r="B119" t="n">
-        <v>7.584119319915771</v>
+        <v>7.58411979675293</v>
       </c>
       <c r="C119" t="n">
-        <v>7.677462963028194</v>
+        <v>7.677463445734158</v>
       </c>
       <c r="D119" t="n">
-        <v>7.322759808396101</v>
+        <v>7.322760268800774</v>
       </c>
       <c r="E119" t="n">
-        <v>7.354262888769144</v>
+        <v>7.354263351154514</v>
       </c>
       <c r="F119" t="n">
         <v>7283457</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582953929901123</v>
+        <v>7.582952976226807</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840815002303775</v>
+        <v>7.840814016199421</v>
       </c>
       <c r="D122" t="n">
-        <v>7.381100395706687</v>
+        <v>7.38109946741859</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455774312072345</v>
+        <v>7.455773374392843</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261459350586</v>
+        <v>7.340261936187744</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624426344595</v>
+        <v>7.622624921524582</v>
       </c>
       <c r="D123" t="n">
-        <v>7.21541557567713</v>
+        <v>7.215416044404066</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457147585694</v>
+        <v>7.621457642689852</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672797679901123</v>
+        <v>7.672796726226807</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109175966524298</v>
+        <v>8.109174958611256</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661129932612202</v>
+        <v>7.661128980388104</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840815257758265</v>
+        <v>7.840814283200555</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798511505127</v>
+        <v>7.700798988342285</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307131173381</v>
+        <v>7.781307612995673</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430533892927</v>
+        <v>7.362430989778177</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629459127295</v>
+        <v>7.678629934591736</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500110626220703</v>
+        <v>7.500111103057861</v>
       </c>
       <c r="C129" t="n">
-        <v>7.750970514277116</v>
+        <v>7.75097100706328</v>
       </c>
       <c r="D129" t="n">
-        <v>7.455773361693658</v>
+        <v>7.45577383571197</v>
       </c>
       <c r="E129" t="n">
-        <v>7.49427759388343</v>
+        <v>7.494278070349739</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265598297119</v>
+        <v>7.375264644622803</v>
       </c>
       <c r="C130" t="n">
-        <v>7.494278464239883</v>
+        <v>7.494277495176356</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762513925697</v>
+        <v>7.343761564324954</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935961570344</v>
+        <v>7.407935003671517</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566619396209717</v>
+        <v>7.566618919372559</v>
       </c>
       <c r="C131" t="n">
-        <v>7.5887884509226</v>
+        <v>7.58878797268838</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234084415890043</v>
+        <v>7.234083960008746</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444106376032958</v>
+        <v>7.444105906916389</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3052,16 +3052,16 @@
         <v>43938</v>
       </c>
       <c r="B132" t="n">
-        <v>7.467442512512207</v>
+        <v>7.467442035675049</v>
       </c>
       <c r="C132" t="n">
-        <v>7.640126670488972</v>
+        <v>7.640126182624983</v>
       </c>
       <c r="D132" t="n">
-        <v>7.396267915457998</v>
+        <v>7.396267443165728</v>
       </c>
       <c r="E132" t="n">
-        <v>7.640126670488972</v>
+        <v>7.640126182624983</v>
       </c>
       <c r="F132" t="n">
         <v>7733575</v>
@@ -3072,16 +3072,16 @@
         <v>43941</v>
       </c>
       <c r="B133" t="n">
-        <v>7.584119319915771</v>
+        <v>7.58411979675293</v>
       </c>
       <c r="C133" t="n">
-        <v>7.592287750070918</v>
+        <v>7.592288227421651</v>
       </c>
       <c r="D133" t="n">
-        <v>7.316925095374786</v>
+        <v>7.316925555412612</v>
       </c>
       <c r="E133" t="n">
-        <v>7.350762733255134</v>
+        <v>7.350763195420438</v>
       </c>
       <c r="F133" t="n">
         <v>10524157</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251522064208984</v>
+        <v>8.251523017883301</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431207358265677</v>
+        <v>8.431208332707222</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3112,16 +3112,16 @@
         <v>43944</v>
       </c>
       <c r="B135" t="n">
-        <v>8.089339256286621</v>
+        <v>8.089340209960938</v>
       </c>
       <c r="C135" t="n">
-        <v>8.57472300766133</v>
+        <v>8.574724018558863</v>
       </c>
       <c r="D135" t="n">
-        <v>7.969159966917957</v>
+        <v>7.969160906424007</v>
       </c>
       <c r="E135" t="n">
-        <v>8.481379364431731</v>
+        <v>8.481380364324728</v>
       </c>
       <c r="F135" t="n">
         <v>13472583</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852482318878174</v>
+        <v>7.852481842041016</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764498666425</v>
+        <v>7.357764051870702</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484550476074</v>
+        <v>7.887484073638916</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826736101882</v>
+        <v>7.966826254468098</v>
       </c>
       <c r="D139" t="n">
-        <v>7.700798933367937</v>
+        <v>7.70079846781684</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980845212174</v>
+        <v>7.841980371125938</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726467609405518</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817898699254</v>
+        <v>7.882817412213003</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726467609405518</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311578781807</v>
+        <v>7.816311096399979</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -3252,16 +3252,16 @@
         <v>43956</v>
       </c>
       <c r="B142" t="n">
-        <v>8.114091873168945</v>
+        <v>8.114090919494629</v>
       </c>
       <c r="C142" t="n">
-        <v>8.645024731663977</v>
+        <v>8.645023715587479</v>
       </c>
       <c r="D142" t="n">
-        <v>8.069433944133035</v>
+        <v>8.069432995707503</v>
       </c>
       <c r="E142" t="n">
-        <v>8.286521173623905</v>
+        <v>8.286520199683441</v>
       </c>
       <c r="F142" t="n">
         <v>11843548</v>
@@ -3272,16 +3272,16 @@
         <v>43957</v>
       </c>
       <c r="B143" t="n">
-        <v>8.048344612121582</v>
+        <v>8.048345565795898</v>
       </c>
       <c r="C143" t="n">
-        <v>8.145103893796581</v>
+        <v>8.145104858936216</v>
       </c>
       <c r="D143" t="n">
-        <v>7.96399105383742</v>
+        <v>7.963991997516411</v>
       </c>
       <c r="E143" t="n">
-        <v>8.145103893796581</v>
+        <v>8.145104858936216</v>
       </c>
       <c r="F143" t="n">
         <v>16545622</v>
@@ -3312,16 +3312,16 @@
         <v>43959</v>
       </c>
       <c r="B145" t="n">
-        <v>8.162470817565918</v>
+        <v>8.162469863891602</v>
       </c>
       <c r="C145" t="n">
-        <v>8.184800228116485</v>
+        <v>8.184799271833279</v>
       </c>
       <c r="D145" t="n">
-        <v>7.947864739756858</v>
+        <v>7.94786381115636</v>
       </c>
       <c r="E145" t="n">
-        <v>8.156268402071278</v>
+        <v>8.15626744912163</v>
       </c>
       <c r="F145" t="n">
         <v>8818844</v>
@@ -3352,16 +3352,16 @@
         <v>43963</v>
       </c>
       <c r="B147" t="n">
-        <v>8.085559844970703</v>
+        <v>8.085558891296387</v>
       </c>
       <c r="C147" t="n">
-        <v>8.276596387736546</v>
+        <v>8.276595411529883</v>
       </c>
       <c r="D147" t="n">
-        <v>8.063230434277379</v>
+        <v>8.063229483236768</v>
       </c>
       <c r="E147" t="n">
-        <v>8.187280531887918</v>
+        <v>8.187279566215866</v>
       </c>
       <c r="F147" t="n">
         <v>9953957</v>
@@ -3372,16 +3372,16 @@
         <v>43964</v>
       </c>
       <c r="B148" t="n">
-        <v>7.926775932312012</v>
+        <v>7.926775455474854</v>
       </c>
       <c r="C148" t="n">
-        <v>8.187280049800203</v>
+        <v>8.187279557292356</v>
       </c>
       <c r="D148" t="n">
-        <v>7.885840170888542</v>
+        <v>7.885839696513885</v>
       </c>
       <c r="E148" t="n">
-        <v>8.187280049800203</v>
+        <v>8.187279557292356</v>
       </c>
       <c r="F148" t="n">
         <v>10179016</v>
@@ -3412,16 +3412,16 @@
         <v>43966</v>
       </c>
       <c r="B150" t="n">
-        <v>6.841341018676758</v>
+        <v>6.8413405418396</v>
       </c>
       <c r="C150" t="n">
-        <v>7.421893621943401</v>
+        <v>7.421893104642092</v>
       </c>
       <c r="D150" t="n">
-        <v>6.841341018676758</v>
+        <v>6.8413405418396</v>
       </c>
       <c r="E150" t="n">
-        <v>7.420653049518127</v>
+        <v>7.420652532303285</v>
       </c>
       <c r="F150" t="n">
         <v>26563775</v>
@@ -3452,16 +3452,16 @@
         <v>43970</v>
       </c>
       <c r="B152" t="n">
-        <v>6.831417560577393</v>
+        <v>6.831418037414551</v>
       </c>
       <c r="C152" t="n">
-        <v>7.018731929050585</v>
+        <v>7.018732418962401</v>
       </c>
       <c r="D152" t="n">
-        <v>6.799164018747209</v>
+        <v>6.79916449333305</v>
       </c>
       <c r="E152" t="n">
-        <v>6.966631015976597</v>
+        <v>6.966631502251738</v>
       </c>
       <c r="F152" t="n">
         <v>13463520</v>
@@ -3472,16 +3472,16 @@
         <v>43971</v>
       </c>
       <c r="B153" t="n">
-        <v>6.822733402252197</v>
+        <v>6.822733879089355</v>
       </c>
       <c r="C153" t="n">
-        <v>6.983997533970078</v>
+        <v>6.983998022077899</v>
       </c>
       <c r="D153" t="n">
-        <v>6.81032857213493</v>
+        <v>6.810329048105121</v>
       </c>
       <c r="E153" t="n">
-        <v>6.946783490349408</v>
+        <v>6.94678397585636</v>
       </c>
       <c r="F153" t="n">
         <v>11533147</v>
@@ -3552,16 +3552,16 @@
         <v>43977</v>
       </c>
       <c r="B157" t="n">
-        <v>7.423134326934814</v>
+        <v>7.423134803771973</v>
       </c>
       <c r="C157" t="n">
-        <v>7.560828925689475</v>
+        <v>7.560829411371671</v>
       </c>
       <c r="D157" t="n">
-        <v>7.275514702466858</v>
+        <v>7.275515169821428</v>
       </c>
       <c r="E157" t="n">
-        <v>7.442982144705714</v>
+        <v>7.442982622817829</v>
       </c>
       <c r="F157" t="n">
         <v>12080691</v>
@@ -3612,16 +3612,16 @@
         <v>43980</v>
       </c>
       <c r="B160" t="n">
-        <v>7.812650680541992</v>
+        <v>7.812650203704834</v>
       </c>
       <c r="C160" t="n">
-        <v>7.812650680541992</v>
+        <v>7.812650203704834</v>
       </c>
       <c r="D160" t="n">
-        <v>7.481437500239227</v>
+        <v>7.481437043617326</v>
       </c>
       <c r="E160" t="n">
-        <v>7.519893458373339</v>
+        <v>7.519892999404318</v>
       </c>
       <c r="F160" t="n">
         <v>23712019</v>
@@ -3652,16 +3652,16 @@
         <v>43984</v>
       </c>
       <c r="B162" t="n">
-        <v>8.271635055541992</v>
+        <v>8.271634101867676</v>
       </c>
       <c r="C162" t="n">
-        <v>8.286521031632221</v>
+        <v>8.286520076241633</v>
       </c>
       <c r="D162" t="n">
-        <v>7.976396678662855</v>
+        <v>7.976395759027911</v>
       </c>
       <c r="E162" t="n">
-        <v>8.063230496816454</v>
+        <v>8.063229567170044</v>
       </c>
       <c r="F162" t="n">
         <v>21348142</v>
@@ -3672,16 +3672,16 @@
         <v>43985</v>
       </c>
       <c r="B163" t="n">
-        <v>8.373353958129883</v>
+        <v>8.373354911804199</v>
       </c>
       <c r="C163" t="n">
-        <v>8.80008582291646</v>
+        <v>8.800086825192951</v>
       </c>
       <c r="D163" t="n">
-        <v>8.315051079171372</v>
+        <v>8.315052026205343</v>
       </c>
       <c r="E163" t="n">
-        <v>8.31753222383259</v>
+        <v>8.317533171149149</v>
       </c>
       <c r="F163" t="n">
         <v>31125376</v>
@@ -3752,16 +3752,16 @@
         <v>43991</v>
       </c>
       <c r="B167" t="n">
-        <v>8.296443939208984</v>
+        <v>8.296442985534668</v>
       </c>
       <c r="C167" t="n">
-        <v>8.32745691101246</v>
+        <v>8.327455953773208</v>
       </c>
       <c r="D167" t="n">
-        <v>8.0967247251524</v>
+        <v>8.096723794435762</v>
       </c>
       <c r="E167" t="n">
-        <v>8.137661383332564</v>
+        <v>8.137660447910266</v>
       </c>
       <c r="F167" t="n">
         <v>13675741</v>
@@ -3772,16 +3772,16 @@
         <v>43992</v>
       </c>
       <c r="B168" t="n">
-        <v>8.089280128479004</v>
+        <v>8.08928108215332</v>
       </c>
       <c r="C168" t="n">
-        <v>8.426696138374464</v>
+        <v>8.426697131827968</v>
       </c>
       <c r="D168" t="n">
-        <v>8.037179665656195</v>
+        <v>8.0371806131882</v>
       </c>
       <c r="E168" t="n">
-        <v>8.311329615282364</v>
+        <v>8.311330595134894</v>
       </c>
       <c r="F168" t="n">
         <v>11944749</v>
@@ -3792,16 +3792,16 @@
         <v>43994</v>
       </c>
       <c r="B169" t="n">
-        <v>7.950345516204834</v>
+        <v>7.950345993041992</v>
       </c>
       <c r="C169" t="n">
-        <v>8.084319292912509</v>
+        <v>8.084319777785</v>
       </c>
       <c r="D169" t="n">
-        <v>7.774194958703272</v>
+        <v>7.774195424975465</v>
       </c>
       <c r="E169" t="n">
-        <v>7.877156659374939</v>
+        <v>7.877157131822456</v>
       </c>
       <c r="F169" t="n">
         <v>12251373</v>
@@ -3892,16 +3892,16 @@
         <v>44001</v>
       </c>
       <c r="B174" t="n">
-        <v>8.487481117248535</v>
+        <v>8.487480163574219</v>
       </c>
       <c r="C174" t="n">
-        <v>8.58920180321846</v>
+        <v>8.589200838114557</v>
       </c>
       <c r="D174" t="n">
-        <v>8.203407450651435</v>
+        <v>8.203406528896336</v>
       </c>
       <c r="E174" t="n">
-        <v>8.203407450651435</v>
+        <v>8.203406528896336</v>
       </c>
       <c r="F174" t="n">
         <v>20750754</v>
@@ -3912,16 +3912,16 @@
         <v>44004</v>
       </c>
       <c r="B175" t="n">
-        <v>8.440341949462891</v>
+        <v>8.440342903137207</v>
       </c>
       <c r="C175" t="n">
-        <v>8.729376978500955</v>
+        <v>8.729377964833343</v>
       </c>
       <c r="D175" t="n">
-        <v>8.380797159632158</v>
+        <v>8.380798106578508</v>
       </c>
       <c r="E175" t="n">
-        <v>8.489961267461833</v>
+        <v>8.489962226742637</v>
       </c>
       <c r="F175" t="n">
         <v>12069362</v>
@@ -3952,16 +3952,16 @@
         <v>44006</v>
       </c>
       <c r="B177" t="n">
-        <v>8.59416389465332</v>
+        <v>8.594162940979004</v>
       </c>
       <c r="C177" t="n">
-        <v>8.669833897798144</v>
+        <v>8.669832935726904</v>
       </c>
       <c r="D177" t="n">
-        <v>8.422974729757115</v>
+        <v>8.422973795079262</v>
       </c>
       <c r="E177" t="n">
-        <v>8.571834484683247</v>
+        <v>8.571833533486773</v>
       </c>
       <c r="F177" t="n">
         <v>7388434</v>
@@ -4052,16 +4052,16 @@
         <v>44013</v>
       </c>
       <c r="B182" t="n">
-        <v>9.009729385375977</v>
+        <v>9.009730339050293</v>
       </c>
       <c r="C182" t="n">
-        <v>9.115171330097578</v>
+        <v>9.11517229493286</v>
       </c>
       <c r="D182" t="n">
-        <v>8.731858165462054</v>
+        <v>8.731859089723871</v>
       </c>
       <c r="E182" t="n">
-        <v>8.812490451063802</v>
+        <v>8.812491383860499</v>
       </c>
       <c r="F182" t="n">
         <v>8963093</v>
@@ -4292,16 +4292,16 @@
         <v>44029</v>
       </c>
       <c r="B194" t="n">
-        <v>8.819933891296387</v>
+        <v>8.81993293762207</v>
       </c>
       <c r="C194" t="n">
-        <v>8.919174324825571</v>
+        <v>8.919173360420668</v>
       </c>
       <c r="D194" t="n">
-        <v>8.633859641988225</v>
+        <v>8.633858708433587</v>
       </c>
       <c r="E194" t="n">
-        <v>8.633859641988225</v>
+        <v>8.633858708433587</v>
       </c>
       <c r="F194" t="n">
         <v>9678298</v>
@@ -4432,16 +4432,16 @@
         <v>44040</v>
       </c>
       <c r="B201" t="n">
-        <v>9.641142845153809</v>
+        <v>9.641143798828125</v>
       </c>
       <c r="C201" t="n">
-        <v>9.832179367263814</v>
+        <v>9.832180339834917</v>
       </c>
       <c r="D201" t="n">
-        <v>9.466232422996864</v>
+        <v>9.466233359369541</v>
       </c>
       <c r="E201" t="n">
-        <v>9.67587708316008</v>
+        <v>9.675878040270206</v>
       </c>
       <c r="F201" t="n">
         <v>30127714</v>
@@ -4472,16 +4472,16 @@
         <v>44042</v>
       </c>
       <c r="B203" t="n">
-        <v>9.143703460693359</v>
+        <v>9.143704414367676</v>
       </c>
       <c r="C203" t="n">
-        <v>9.700686938306321</v>
+        <v>9.700687950073165</v>
       </c>
       <c r="D203" t="n">
-        <v>9.097805411083952</v>
+        <v>9.097806359971171</v>
       </c>
       <c r="E203" t="n">
-        <v>9.685800070178546</v>
+        <v>9.685801080392711</v>
       </c>
       <c r="F203" t="n">
         <v>33272500</v>
@@ -4592,16 +4592,16 @@
         <v>44050</v>
       </c>
       <c r="B209" t="n">
-        <v>8.429178237915039</v>
+        <v>8.429177284240723</v>
       </c>
       <c r="C209" t="n">
-        <v>8.429178237915039</v>
+        <v>8.429177284240723</v>
       </c>
       <c r="D209" t="n">
-        <v>8.25550792408546</v>
+        <v>8.255506990060143</v>
       </c>
       <c r="E209" t="n">
-        <v>8.336141112251321</v>
+        <v>8.336140169103194</v>
       </c>
       <c r="F209" t="n">
         <v>22110172</v>
@@ -4612,16 +4612,16 @@
         <v>44053</v>
       </c>
       <c r="B210" t="n">
-        <v>8.25922966003418</v>
+        <v>8.259230613708496</v>
       </c>
       <c r="C210" t="n">
-        <v>8.468873436704216</v>
+        <v>8.468874414585619</v>
       </c>
       <c r="D210" t="n">
-        <v>8.166191645730668</v>
+        <v>8.166192588662099</v>
       </c>
       <c r="E210" t="n">
-        <v>8.435379322693057</v>
+        <v>8.435380296706972</v>
       </c>
       <c r="F210" t="n">
         <v>21920608</v>
@@ -4652,16 +4652,16 @@
         <v>44055</v>
       </c>
       <c r="B212" t="n">
-        <v>8.162470817565918</v>
+        <v>8.162469863891602</v>
       </c>
       <c r="C212" t="n">
-        <v>8.446544484992341</v>
+        <v>8.446543498127859</v>
       </c>
       <c r="D212" t="n">
-        <v>8.078116358606623</v>
+        <v>8.078115414787984</v>
       </c>
       <c r="E212" t="n">
-        <v>8.409329992024503</v>
+        <v>8.409329009508031</v>
       </c>
       <c r="F212" t="n">
         <v>20200945</v>
@@ -4732,16 +4732,16 @@
         <v>44061</v>
       </c>
       <c r="B216" t="n">
-        <v>8.101685523986816</v>
+        <v>8.101686477661133</v>
       </c>
       <c r="C216" t="n">
-        <v>8.143863198266791</v>
+        <v>8.143864156905972</v>
       </c>
       <c r="D216" t="n">
-        <v>7.978877345430011</v>
+        <v>7.9788782846482</v>
       </c>
       <c r="E216" t="n">
-        <v>8.038420352760289</v>
+        <v>8.038421298987467</v>
       </c>
       <c r="F216" t="n">
         <v>10608743</v>
@@ -4752,16 +4752,16 @@
         <v>44062</v>
       </c>
       <c r="B217" t="n">
-        <v>7.926775932312012</v>
+        <v>7.926775455474854</v>
       </c>
       <c r="C217" t="n">
-        <v>8.141381998856557</v>
+        <v>8.141381509109719</v>
       </c>
       <c r="D217" t="n">
-        <v>7.921813642791834</v>
+        <v>7.921813166253184</v>
       </c>
       <c r="E217" t="n">
-        <v>8.141381998856557</v>
+        <v>8.141381509109719</v>
       </c>
       <c r="F217" t="n">
         <v>9466833</v>
@@ -4772,16 +4772,16 @@
         <v>44063</v>
       </c>
       <c r="B218" t="n">
-        <v>7.957787990570068</v>
+        <v>7.957788467407227</v>
       </c>
       <c r="C218" t="n">
-        <v>8.033458885005254</v>
+        <v>8.033459366376674</v>
       </c>
       <c r="D218" t="n">
-        <v>7.774194893738959</v>
+        <v>7.774195359575069</v>
       </c>
       <c r="E218" t="n">
-        <v>7.915611210128628</v>
+        <v>7.915611684438519</v>
       </c>
       <c r="F218" t="n">
         <v>7652765</v>
@@ -4892,16 +4892,16 @@
         <v>44071</v>
       </c>
       <c r="B224" t="n">
-        <v>8.100444793701172</v>
+        <v>8.100445747375488</v>
       </c>
       <c r="C224" t="n">
-        <v>8.100444793701172</v>
+        <v>8.100445747375488</v>
       </c>
       <c r="D224" t="n">
-        <v>7.960268612170143</v>
+        <v>7.960269549341362</v>
       </c>
       <c r="E224" t="n">
-        <v>8.001206157737258</v>
+        <v>8.0012070997281</v>
       </c>
       <c r="F224" t="n">
         <v>5577388</v>
@@ -5012,16 +5012,16 @@
         <v>44082</v>
       </c>
       <c r="B230" t="n">
-        <v>7.751865386962891</v>
+        <v>7.751865863800049</v>
       </c>
       <c r="C230" t="n">
-        <v>7.833737802061967</v>
+        <v>7.833738283935308</v>
       </c>
       <c r="D230" t="n">
-        <v>7.691081361819436</v>
+        <v>7.691081834917614</v>
       </c>
       <c r="E230" t="n">
-        <v>7.813890431199186</v>
+        <v>7.813890911851665</v>
       </c>
       <c r="F230" t="n">
         <v>7181501</v>
@@ -5032,16 +5032,16 @@
         <v>44083</v>
       </c>
       <c r="B231" t="n">
-        <v>7.709689140319824</v>
+        <v>7.709688663482666</v>
       </c>
       <c r="C231" t="n">
-        <v>7.834980256551466</v>
+        <v>7.834979771965168</v>
       </c>
       <c r="D231" t="n">
-        <v>7.637740405675546</v>
+        <v>7.637739933288351</v>
       </c>
       <c r="E231" t="n">
-        <v>7.792802580260581</v>
+        <v>7.792802098282933</v>
       </c>
       <c r="F231" t="n">
         <v>8282629</v>
@@ -5052,16 +5052,16 @@
         <v>44084</v>
       </c>
       <c r="B232" t="n">
-        <v>8.850946426391602</v>
+        <v>8.850947380065918</v>
       </c>
       <c r="C232" t="n">
-        <v>9.197044227170217</v>
+        <v>9.197045218135978</v>
       </c>
       <c r="D232" t="n">
-        <v>8.62145438702172</v>
+        <v>8.621455315968662</v>
       </c>
       <c r="E232" t="n">
-        <v>9.197044227170217</v>
+        <v>9.197045218135978</v>
       </c>
       <c r="F232" t="n">
         <v>139609921</v>
@@ -5132,16 +5132,16 @@
         <v>44090</v>
       </c>
       <c r="B236" t="n">
-        <v>9.312411308288574</v>
+        <v>9.312410354614258</v>
       </c>
       <c r="C236" t="n">
-        <v>9.375676482213272</v>
+        <v>9.375675522060035</v>
       </c>
       <c r="D236" t="n">
-        <v>9.175957274371282</v>
+        <v>9.175956334671081</v>
       </c>
       <c r="E236" t="n">
-        <v>9.179678544963952</v>
+        <v>9.179677604882659</v>
       </c>
       <c r="F236" t="n">
         <v>13993693</v>
@@ -5212,16 +5212,16 @@
         <v>44096</v>
       </c>
       <c r="B240" t="n">
-        <v>9.326057434082031</v>
+        <v>9.326058387756348</v>
       </c>
       <c r="C240" t="n">
-        <v>9.353348239057649</v>
+        <v>9.353349195522698</v>
       </c>
       <c r="D240" t="n">
-        <v>9.182158188124824</v>
+        <v>9.182159127084132</v>
       </c>
       <c r="E240" t="n">
-        <v>9.192082766997606</v>
+        <v>9.192083706971793</v>
       </c>
       <c r="F240" t="n">
         <v>9315031</v>
@@ -5232,16 +5232,16 @@
         <v>44097</v>
       </c>
       <c r="B241" t="n">
-        <v>8.953908920288086</v>
+        <v>8.95390796661377</v>
       </c>
       <c r="C241" t="n">
-        <v>9.308690312405352</v>
+        <v>9.308689320943529</v>
       </c>
       <c r="D241" t="n">
-        <v>8.934060654104224</v>
+        <v>8.934059702543932</v>
       </c>
       <c r="E241" t="n">
-        <v>9.303728915956151</v>
+        <v>9.303727925022763</v>
       </c>
       <c r="F241" t="n">
         <v>13677251</v>
@@ -5252,16 +5252,16 @@
         <v>44098</v>
       </c>
       <c r="B242" t="n">
-        <v>9.282638549804688</v>
+        <v>9.282639503479004</v>
       </c>
       <c r="C242" t="n">
-        <v>9.463751388941567</v>
+        <v>9.46375236122295</v>
       </c>
       <c r="D242" t="n">
-        <v>8.898084356453305</v>
+        <v>8.898085270619518</v>
       </c>
       <c r="E242" t="n">
-        <v>8.906768809518589</v>
+        <v>8.906769724577019</v>
       </c>
       <c r="F242" t="n">
         <v>18607406</v>
@@ -5272,16 +5272,16 @@
         <v>44099</v>
       </c>
       <c r="B243" t="n">
-        <v>9.184639930725098</v>
+        <v>9.184640884399414</v>
       </c>
       <c r="C243" t="n">
-        <v>9.25410751328763</v>
+        <v>9.254108474175018</v>
       </c>
       <c r="D243" t="n">
-        <v>9.095324084518023</v>
+        <v>9.095325028918353</v>
       </c>
       <c r="E243" t="n">
-        <v>9.220613400863298</v>
+        <v>9.22061435827287</v>
       </c>
       <c r="F243" t="n">
         <v>8201819</v>
@@ -5312,16 +5312,16 @@
         <v>44103</v>
       </c>
       <c r="B245" t="n">
-        <v>8.760391235351562</v>
+        <v>8.760390281677246</v>
       </c>
       <c r="C245" t="n">
-        <v>8.942744221459206</v>
+        <v>8.942743247933565</v>
       </c>
       <c r="D245" t="n">
-        <v>8.68348020897627</v>
+        <v>8.683479263674647</v>
       </c>
       <c r="E245" t="n">
-        <v>8.802568019244504</v>
+        <v>8.802567060978735</v>
       </c>
       <c r="F245" t="n">
         <v>13985386</v>
@@ -5332,16 +5332,16 @@
         <v>44104</v>
       </c>
       <c r="B246" t="n">
-        <v>8.651226043701172</v>
+        <v>8.651226997375488</v>
       </c>
       <c r="C246" t="n">
-        <v>8.841022441256731</v>
+        <v>8.841023415853394</v>
       </c>
       <c r="D246" t="n">
-        <v>8.609049265013768</v>
+        <v>8.609050214038696</v>
       </c>
       <c r="E246" t="n">
-        <v>8.803807058409923</v>
+        <v>8.803808028904122</v>
       </c>
       <c r="F246" t="n">
         <v>11477260</v>
@@ -5412,16 +5412,16 @@
         <v>44110</v>
       </c>
       <c r="B250" t="n">
-        <v>8.497405052185059</v>
+        <v>8.497404098510742</v>
       </c>
       <c r="C250" t="n">
-        <v>8.520974589071102</v>
+        <v>8.520973632751547</v>
       </c>
       <c r="D250" t="n">
-        <v>8.316293085426295</v>
+        <v>8.3162921520784</v>
       </c>
       <c r="E250" t="n">
-        <v>8.488721491571129</v>
+        <v>8.48872053887138</v>
       </c>
       <c r="F250" t="n">
         <v>10544549</v>
@@ -5432,16 +5432,16 @@
         <v>44111</v>
       </c>
       <c r="B251" t="n">
-        <v>8.585480690002441</v>
+        <v>8.585479736328125</v>
       </c>
       <c r="C251" t="n">
-        <v>8.704568498874545</v>
+        <v>8.704567531971968</v>
       </c>
       <c r="D251" t="n">
-        <v>8.440343093036322</v>
+        <v>8.440342155483876</v>
       </c>
       <c r="E251" t="n">
-        <v>8.477557586577683</v>
+        <v>8.477556644891454</v>
       </c>
       <c r="F251" t="n">
         <v>12680345</v>
@@ -5552,16 +5552,16 @@
         <v>44120</v>
       </c>
       <c r="B257" t="n">
-        <v>8.25922966003418</v>
+        <v>8.259230613708496</v>
       </c>
       <c r="C257" t="n">
-        <v>8.267912326486389</v>
+        <v>8.267913281163274</v>
       </c>
       <c r="D257" t="n">
-        <v>8.097964185523827</v>
+        <v>8.097965120577188</v>
       </c>
       <c r="E257" t="n">
-        <v>8.122774739620494</v>
+        <v>8.122775677538673</v>
       </c>
       <c r="F257" t="n">
         <v>10726560</v>
@@ -5612,16 +5612,16 @@
         <v>44125</v>
       </c>
       <c r="B260" t="n">
-        <v>8.275355339050293</v>
+        <v>8.275356292724609</v>
       </c>
       <c r="C260" t="n">
-        <v>8.355987625465389</v>
+        <v>8.355988588431988</v>
       </c>
       <c r="D260" t="n">
-        <v>8.245583390421267</v>
+        <v>8.245584340664582</v>
       </c>
       <c r="E260" t="n">
-        <v>8.354747499881778</v>
+        <v>8.35474846270546</v>
       </c>
       <c r="F260" t="n">
         <v>4665068</v>
@@ -5632,16 +5632,16 @@
         <v>44126</v>
       </c>
       <c r="B261" t="n">
-        <v>8.267911911010742</v>
+        <v>8.267912864685059</v>
       </c>
       <c r="C261" t="n">
-        <v>8.337380386835774</v>
+        <v>8.337381348523031</v>
       </c>
       <c r="D261" t="n">
-        <v>8.168673273460097</v>
+        <v>8.168674215687588</v>
       </c>
       <c r="E261" t="n">
-        <v>8.30636741913896</v>
+        <v>8.306368377248981</v>
       </c>
       <c r="F261" t="n">
         <v>7908034</v>
@@ -5652,16 +5652,16 @@
         <v>44127</v>
       </c>
       <c r="B262" t="n">
-        <v>8.234419822692871</v>
+        <v>8.234420776367188</v>
       </c>
       <c r="C262" t="n">
-        <v>8.312570966783923</v>
+        <v>8.312571929509362</v>
       </c>
       <c r="D262" t="n">
-        <v>8.203406854103131</v>
+        <v>8.203407804185662</v>
       </c>
       <c r="E262" t="n">
-        <v>8.269152274680931</v>
+        <v>8.269153232377807</v>
       </c>
       <c r="F262" t="n">
         <v>5098571</v>
@@ -5712,16 +5712,16 @@
         <v>44132</v>
       </c>
       <c r="B265" t="n">
-        <v>7.825055599212646</v>
+        <v>7.825055122375488</v>
       </c>
       <c r="C265" t="n">
-        <v>8.088040873150774</v>
+        <v>8.088040380288025</v>
       </c>
       <c r="D265" t="n">
-        <v>7.817612164601516</v>
+        <v>7.81761168821794</v>
       </c>
       <c r="E265" t="n">
-        <v>8.078116293669268</v>
+        <v>8.078115801411293</v>
       </c>
       <c r="F265" t="n">
         <v>12369944</v>
@@ -5752,16 +5752,16 @@
         <v>44134</v>
       </c>
       <c r="B267" t="n">
-        <v>7.684878826141357</v>
+        <v>7.684879302978516</v>
       </c>
       <c r="C267" t="n">
-        <v>7.777915944304612</v>
+        <v>7.777916426914608</v>
       </c>
       <c r="D267" t="n">
-        <v>7.574474588649013</v>
+        <v>7.574475058635726</v>
       </c>
       <c r="E267" t="n">
-        <v>7.759308699364413</v>
+        <v>7.759309180819852</v>
       </c>
       <c r="F267" t="n">
         <v>16269207</v>
@@ -5772,16 +5772,16 @@
         <v>44138</v>
       </c>
       <c r="B268" t="n">
-        <v>7.717131614685059</v>
+        <v>7.7171311378479</v>
       </c>
       <c r="C268" t="n">
-        <v>7.852346415863062</v>
+        <v>7.852345930671059</v>
       </c>
       <c r="D268" t="n">
-        <v>7.622854363726927</v>
+        <v>7.622853892715106</v>
       </c>
       <c r="E268" t="n">
-        <v>7.821334338599661</v>
+        <v>7.821333855323877</v>
       </c>
       <c r="F268" t="n">
         <v>9901091</v>
@@ -5812,16 +5812,16 @@
         <v>44140</v>
       </c>
       <c r="B270" t="n">
-        <v>8.119053840637207</v>
+        <v>8.119052886962891</v>
       </c>
       <c r="C270" t="n">
-        <v>8.177356724487632</v>
+        <v>8.177355763964984</v>
       </c>
       <c r="D270" t="n">
-        <v>8.007408575750512</v>
+        <v>8.007407635190189</v>
       </c>
       <c r="E270" t="n">
-        <v>8.039661672128053</v>
+        <v>8.039660727779241</v>
       </c>
       <c r="F270" t="n">
         <v>9820281</v>
@@ -5892,16 +5892,16 @@
         <v>44146</v>
       </c>
       <c r="B274" t="n">
-        <v>8.193483352661133</v>
+        <v>8.193482398986816</v>
       </c>
       <c r="C274" t="n">
-        <v>8.420494274138473</v>
+        <v>8.420493294041393</v>
       </c>
       <c r="D274" t="n">
-        <v>8.193483352661133</v>
+        <v>8.193482398986816</v>
       </c>
       <c r="E274" t="n">
-        <v>8.312572059811611</v>
+        <v>8.312571092276054</v>
       </c>
       <c r="F274" t="n">
         <v>7246451</v>
@@ -5912,16 +5912,16 @@
         <v>44147</v>
       </c>
       <c r="B275" t="n">
-        <v>8.234419822692871</v>
+        <v>8.234420776367188</v>
       </c>
       <c r="C275" t="n">
-        <v>8.398164651520666</v>
+        <v>8.398165624159189</v>
       </c>
       <c r="D275" t="n">
-        <v>8.131458125037573</v>
+        <v>8.13145906678732</v>
       </c>
       <c r="E275" t="n">
-        <v>8.193482275292528</v>
+        <v>8.193483224225638</v>
       </c>
       <c r="F275" t="n">
         <v>11697033</v>
@@ -5932,16 +5932,16 @@
         <v>44148</v>
       </c>
       <c r="B276" t="n">
-        <v>8.633858680725098</v>
+        <v>8.633859634399414</v>
       </c>
       <c r="C276" t="n">
-        <v>8.646264403631776</v>
+        <v>8.646265358676397</v>
       </c>
       <c r="D276" t="n">
-        <v>8.267911744802472</v>
+        <v>8.267912658055211</v>
       </c>
       <c r="E276" t="n">
-        <v>8.322493351742979</v>
+        <v>8.322494271024663</v>
       </c>
       <c r="F276" t="n">
         <v>10854949</v>
@@ -5992,16 +5992,16 @@
         <v>44153</v>
       </c>
       <c r="B279" t="n">
-        <v>8.584239959716797</v>
+        <v>8.584240913391113</v>
       </c>
       <c r="C279" t="n">
-        <v>8.64502398560519</v>
+        <v>8.645024946032365</v>
       </c>
       <c r="D279" t="n">
-        <v>8.516012499566937</v>
+        <v>8.516013445661457</v>
       </c>
       <c r="E279" t="n">
-        <v>8.55818927999508</v>
+        <v>8.558190230775271</v>
       </c>
       <c r="F279" t="n">
         <v>8922310</v>
@@ -6072,16 +6072,16 @@
         <v>44160</v>
       </c>
       <c r="B283" t="n">
-        <v>8.739301681518555</v>
+        <v>8.739302635192871</v>
       </c>
       <c r="C283" t="n">
-        <v>8.920413624337439</v>
+        <v>8.920414597775554</v>
       </c>
       <c r="D283" t="n">
-        <v>8.616491723410208</v>
+        <v>8.616492663682914</v>
       </c>
       <c r="E283" t="n">
-        <v>8.854667312281327</v>
+        <v>8.85466827854489</v>
       </c>
       <c r="F283" t="n">
         <v>6633202</v>
@@ -6112,16 +6112,16 @@
         <v>44162</v>
       </c>
       <c r="B285" t="n">
-        <v>8.615251541137695</v>
+        <v>8.615252494812012</v>
       </c>
       <c r="C285" t="n">
-        <v>8.70828776310049</v>
+        <v>8.708288727073548</v>
       </c>
       <c r="D285" t="n">
-        <v>8.507328451506179</v>
+        <v>8.507329393233835</v>
       </c>
       <c r="E285" t="n">
-        <v>8.566871454869922</v>
+        <v>8.566872403188754</v>
       </c>
       <c r="F285" t="n">
         <v>5230736</v>
@@ -6152,16 +6152,16 @@
         <v>44166</v>
       </c>
       <c r="B287" t="n">
-        <v>8.414291381835938</v>
+        <v>8.414292335510254</v>
       </c>
       <c r="C287" t="n">
-        <v>8.672314340510058</v>
+        <v>8.672315323428652</v>
       </c>
       <c r="D287" t="n">
-        <v>8.360949006055193</v>
+        <v>8.360949953683695</v>
       </c>
       <c r="E287" t="n">
-        <v>8.636339977103933</v>
+        <v>8.636340955945199</v>
       </c>
       <c r="F287" t="n">
         <v>16096259</v>
@@ -6172,16 +6172,16 @@
         <v>44167</v>
       </c>
       <c r="B288" t="n">
-        <v>8.282797813415527</v>
+        <v>8.282798767089844</v>
       </c>
       <c r="C288" t="n">
-        <v>8.461429503764982</v>
+        <v>8.4614304780068</v>
       </c>
       <c r="D288" t="n">
-        <v>8.199685276496087</v>
+        <v>8.199686220600897</v>
       </c>
       <c r="E288" t="n">
-        <v>8.456468108007872</v>
+        <v>8.456469081678438</v>
       </c>
       <c r="F288" t="n">
         <v>15329699</v>
@@ -6212,16 +6212,16 @@
         <v>44169</v>
       </c>
       <c r="B290" t="n">
-        <v>8.772793769836426</v>
+        <v>8.772794723510742</v>
       </c>
       <c r="C290" t="n">
-        <v>8.948944312102428</v>
+        <v>8.948945284925747</v>
       </c>
       <c r="D290" t="n">
-        <v>8.683478819885265</v>
+        <v>8.683479763850318</v>
       </c>
       <c r="E290" t="n">
-        <v>8.886919271932774</v>
+        <v>8.886920238013465</v>
       </c>
       <c r="F290" t="n">
         <v>10446369</v>
@@ -6232,16 +6232,16 @@
         <v>44172</v>
       </c>
       <c r="B291" t="n">
-        <v>8.647505760192871</v>
+        <v>8.647504806518555</v>
       </c>
       <c r="C291" t="n">
-        <v>8.82737759966732</v>
+        <v>8.827376626156168</v>
       </c>
       <c r="D291" t="n">
-        <v>8.621455078573774</v>
+        <v>8.621454127772409</v>
       </c>
       <c r="E291" t="n">
-        <v>8.807529333653388</v>
+        <v>8.807528362331166</v>
       </c>
       <c r="F291" t="n">
         <v>10174485</v>
@@ -6392,16 +6392,16 @@
         <v>44182</v>
       </c>
       <c r="B299" t="n">
-        <v>9.125096321105957</v>
+        <v>9.125097274780273</v>
       </c>
       <c r="C299" t="n">
-        <v>9.233019415311725</v>
+        <v>9.233020380265208</v>
       </c>
       <c r="D299" t="n">
-        <v>9.1052480568353</v>
+        <v>9.105249008435251</v>
       </c>
       <c r="E299" t="n">
-        <v>9.230538270595108</v>
+        <v>9.230539235289285</v>
       </c>
       <c r="F299" t="n">
         <v>5262456</v>
@@ -6452,16 +6452,16 @@
         <v>44187</v>
       </c>
       <c r="B302" t="n">
-        <v>9.018413543701172</v>
+        <v>9.018414497375488</v>
       </c>
       <c r="C302" t="n">
-        <v>9.117653080233614</v>
+        <v>9.117654044402261</v>
       </c>
       <c r="D302" t="n">
-        <v>8.941503416629342</v>
+        <v>8.941504362170608</v>
       </c>
       <c r="E302" t="n">
-        <v>8.974995743895692</v>
+        <v>8.974996692978687</v>
       </c>
       <c r="F302" t="n">
         <v>3700636</v>
@@ -6572,16 +6572,16 @@
         <v>44201</v>
       </c>
       <c r="B308" t="n">
-        <v>9.097805023193359</v>
+        <v>9.097805976867676</v>
       </c>
       <c r="C308" t="n">
-        <v>9.304967640603</v>
+        <v>9.304968615993069</v>
       </c>
       <c r="D308" t="n">
-        <v>9.012210449150441</v>
+        <v>9.012211393852336</v>
       </c>
       <c r="E308" t="n">
-        <v>9.304967640603</v>
+        <v>9.304968615993069</v>
       </c>
       <c r="F308" t="n">
         <v>8306796</v>
@@ -6592,16 +6592,16 @@
         <v>44202</v>
       </c>
       <c r="B309" t="n">
-        <v>9.02337646484375</v>
+        <v>9.023375511169434</v>
       </c>
       <c r="C309" t="n">
-        <v>9.178438642419241</v>
+        <v>9.178437672356514</v>
       </c>
       <c r="D309" t="n">
-        <v>8.883200263463204</v>
+        <v>8.883199324604012</v>
       </c>
       <c r="E309" t="n">
-        <v>9.091603036730099</v>
+        <v>9.091602075844966</v>
       </c>
       <c r="F309" t="n">
         <v>6995714</v>
@@ -6632,16 +6632,16 @@
         <v>44204</v>
       </c>
       <c r="B311" t="n">
-        <v>9.494765281677246</v>
+        <v>9.49476432800293</v>
       </c>
       <c r="C311" t="n">
-        <v>9.533220794103377</v>
+        <v>9.533219836566508</v>
       </c>
       <c r="D311" t="n">
-        <v>9.077957953992263</v>
+        <v>9.077957042182957</v>
       </c>
       <c r="E311" t="n">
-        <v>9.178438515281906</v>
+        <v>9.178437593380119</v>
       </c>
       <c r="F311" t="n">
         <v>10280973</v>
@@ -6732,16 +6732,16 @@
         <v>44211</v>
       </c>
       <c r="B316" t="n">
-        <v>9.479878425598145</v>
+        <v>9.479877471923828</v>
       </c>
       <c r="C316" t="n">
-        <v>9.607649794137002</v>
+        <v>9.607648827608905</v>
       </c>
       <c r="D316" t="n">
-        <v>9.378158631904267</v>
+        <v>9.378157688462947</v>
       </c>
       <c r="E316" t="n">
-        <v>9.589042547490402</v>
+        <v>9.589041582834192</v>
       </c>
       <c r="F316" t="n">
         <v>14334303</v>
@@ -6892,16 +6892,16 @@
         <v>44224</v>
       </c>
       <c r="B324" t="n">
-        <v>9.368232727050781</v>
+        <v>9.368233680725098</v>
       </c>
       <c r="C324" t="n">
-        <v>9.399244800408228</v>
+        <v>9.399245757239534</v>
       </c>
       <c r="D324" t="n">
-        <v>9.102766341339521</v>
+        <v>9.102767267989694</v>
       </c>
       <c r="E324" t="n">
-        <v>9.180917480970056</v>
+        <v>9.180918415575915</v>
       </c>
       <c r="F324" t="n">
         <v>7429217</v>
@@ -6912,16 +6912,16 @@
         <v>44225</v>
       </c>
       <c r="B325" t="n">
-        <v>9.363271713256836</v>
+        <v>9.36327075958252</v>
       </c>
       <c r="C325" t="n">
-        <v>9.571676269761104</v>
+        <v>9.571675294860224</v>
       </c>
       <c r="D325" t="n">
-        <v>9.215652973121827</v>
+        <v>9.215652034482874</v>
       </c>
       <c r="E325" t="n">
-        <v>9.312411369945844</v>
+        <v>9.312410421451789</v>
       </c>
       <c r="F325" t="n">
         <v>11022611</v>
@@ -6952,16 +6952,16 @@
         <v>44229</v>
       </c>
       <c r="B327" t="n">
-        <v>10.13361930847168</v>
+        <v>10.133620262146</v>
       </c>
       <c r="C327" t="n">
-        <v>10.18447964681817</v>
+        <v>10.18448060527895</v>
       </c>
       <c r="D327" t="n">
-        <v>9.832179442109044</v>
+        <v>9.832180367414875</v>
       </c>
       <c r="E327" t="n">
-        <v>10.11004977442547</v>
+        <v>10.11005072588166</v>
       </c>
       <c r="F327" t="n">
         <v>20046878</v>
@@ -6992,16 +6992,16 @@
         <v>44231</v>
       </c>
       <c r="B329" t="n">
-        <v>10.38668251037598</v>
+        <v>10.38668155670166</v>
       </c>
       <c r="C329" t="n">
-        <v>10.38668251037598</v>
+        <v>10.38668155670166</v>
       </c>
       <c r="D329" t="n">
-        <v>10.11749393146458</v>
+        <v>10.11749300250636</v>
       </c>
       <c r="E329" t="n">
-        <v>10.17703872709649</v>
+        <v>10.17703779267104</v>
       </c>
       <c r="F329" t="n">
         <v>12166787</v>
@@ -7012,16 +7012,16 @@
         <v>44232</v>
       </c>
       <c r="B330" t="n">
-        <v>10.55663013458252</v>
+        <v>10.5566291809082</v>
       </c>
       <c r="C330" t="n">
-        <v>10.58144069033415</v>
+        <v>10.58143973441847</v>
       </c>
       <c r="D330" t="n">
-        <v>10.32465782656054</v>
+        <v>10.32465689384235</v>
       </c>
       <c r="E330" t="n">
-        <v>10.41893507933724</v>
+        <v>10.41893413810214</v>
       </c>
       <c r="F330" t="n">
         <v>10745440</v>
@@ -7192,16 +7192,16 @@
         <v>44249</v>
       </c>
       <c r="B339" t="n">
-        <v>11.09376525878906</v>
+        <v>11.09376621246338</v>
       </c>
       <c r="C339" t="n">
-        <v>11.20292847746345</v>
+        <v>11.20292944052197</v>
       </c>
       <c r="D339" t="n">
-        <v>10.63602131403072</v>
+        <v>10.63602222835513</v>
       </c>
       <c r="E339" t="n">
-        <v>10.9399432226141</v>
+        <v>10.93994416306512</v>
       </c>
       <c r="F339" t="n">
         <v>14982292</v>
@@ -7292,16 +7292,16 @@
         <v>44256</v>
       </c>
       <c r="B344" t="n">
-        <v>21.85701751708984</v>
+        <v>21.85701560974121</v>
       </c>
       <c r="C344" t="n">
-        <v>23.99306617161</v>
+        <v>23.99306407785948</v>
       </c>
       <c r="D344" t="n">
-        <v>16.31078752172449</v>
+        <v>16.3107860983666</v>
       </c>
       <c r="E344" t="n">
-        <v>16.86353693074166</v>
+        <v>16.8635354591482</v>
       </c>
       <c r="F344" t="n">
         <v>49361500</v>
@@ -7312,16 +7312,16 @@
         <v>44257</v>
       </c>
       <c r="B345" t="n">
-        <v>21.19184494018555</v>
+        <v>21.19184303283691</v>
       </c>
       <c r="C345" t="n">
-        <v>22.95314685108304</v>
+        <v>22.95314478521037</v>
       </c>
       <c r="D345" t="n">
-        <v>20.69530683439987</v>
+        <v>20.6953049717416</v>
       </c>
       <c r="E345" t="n">
-        <v>22.18491936483229</v>
+        <v>22.18491736810308</v>
       </c>
       <c r="F345" t="n">
         <v>20095700</v>
@@ -7352,16 +7352,16 @@
         <v>44259</v>
       </c>
       <c r="B347" t="n">
-        <v>20.86394309997559</v>
+        <v>20.86394119262695</v>
       </c>
       <c r="C347" t="n">
-        <v>21.52911508897337</v>
+        <v>21.52911312081577</v>
       </c>
       <c r="D347" t="n">
-        <v>20.0113977633286</v>
+        <v>20.01139593391831</v>
       </c>
       <c r="E347" t="n">
-        <v>20.23624470835284</v>
+        <v>20.2362428583874</v>
       </c>
       <c r="F347" t="n">
         <v>8984600</v>
@@ -7732,16 +7732,16 @@
         <v>44286</v>
       </c>
       <c r="B366" t="n">
-        <v>31.08511734008789</v>
+        <v>31.08511924743652</v>
       </c>
       <c r="C366" t="n">
-        <v>32.65904760342265</v>
+        <v>32.65904960734591</v>
       </c>
       <c r="D366" t="n">
-        <v>30.82279682081511</v>
+        <v>30.82279871206804</v>
       </c>
       <c r="E366" t="n">
-        <v>31.95640029207138</v>
+        <v>31.95640225288098</v>
       </c>
       <c r="F366" t="n">
         <v>8195900</v>
@@ -7792,16 +7792,16 @@
         <v>44292</v>
       </c>
       <c r="B369" t="n">
-        <v>30.5792121887207</v>
+        <v>30.57921028137207</v>
       </c>
       <c r="C369" t="n">
-        <v>32.19998498521812</v>
+        <v>32.19998297677536</v>
       </c>
       <c r="D369" t="n">
-        <v>30.48552730465581</v>
+        <v>30.48552540315069</v>
       </c>
       <c r="E369" t="n">
-        <v>31.01953900629401</v>
+        <v>31.01953707148042</v>
       </c>
       <c r="F369" t="n">
         <v>6923500</v>
@@ -7812,16 +7812,16 @@
         <v>44293</v>
       </c>
       <c r="B370" t="n">
-        <v>30.95395660400391</v>
+        <v>30.95395851135254</v>
       </c>
       <c r="C370" t="n">
-        <v>31.36617506706607</v>
+        <v>31.36617699981515</v>
       </c>
       <c r="D370" t="n">
-        <v>30.40120725129495</v>
+        <v>30.40120912458377</v>
       </c>
       <c r="E370" t="n">
-        <v>30.72910789533883</v>
+        <v>30.72910978883253</v>
       </c>
       <c r="F370" t="n">
         <v>4745700</v>
@@ -8012,16 +8012,16 @@
         <v>44308</v>
       </c>
       <c r="B380" t="n">
-        <v>36.30344390869141</v>
+        <v>36.30344772338867</v>
       </c>
       <c r="C380" t="n">
-        <v>38.03663915608288</v>
+        <v>38.03664315290104</v>
       </c>
       <c r="D380" t="n">
-        <v>35.88185481304648</v>
+        <v>35.88185858344396</v>
       </c>
       <c r="E380" t="n">
-        <v>37.12788440974715</v>
+        <v>37.12788831107506</v>
       </c>
       <c r="F380" t="n">
         <v>6756200</v>
@@ -8052,16 +8052,16 @@
         <v>44312</v>
       </c>
       <c r="B382" t="n">
-        <v>35.91933441162109</v>
+        <v>35.91933059692383</v>
       </c>
       <c r="C382" t="n">
-        <v>36.30344817190534</v>
+        <v>36.30344431641451</v>
       </c>
       <c r="D382" t="n">
-        <v>35.51648295890232</v>
+        <v>35.5164791869886</v>
       </c>
       <c r="E382" t="n">
-        <v>35.88185902675205</v>
+        <v>35.88185521603473</v>
       </c>
       <c r="F382" t="n">
         <v>4241900</v>
@@ -8072,16 +8072,16 @@
         <v>44313</v>
       </c>
       <c r="B383" t="n">
-        <v>35.46963500976562</v>
+        <v>35.46963882446289</v>
       </c>
       <c r="C383" t="n">
-        <v>36.2940754796825</v>
+        <v>36.29407938304689</v>
       </c>
       <c r="D383" t="n">
-        <v>35.27289463051181</v>
+        <v>35.27289842405</v>
       </c>
       <c r="E383" t="n">
-        <v>36.05985972137591</v>
+        <v>36.05986359955081</v>
       </c>
       <c r="F383" t="n">
         <v>2386900</v>
@@ -35092,19 +35092,39 @@
         <v>46288</v>
       </c>
       <c r="B1734" t="n">
-        <v>2.85</v>
+        <v>2.849999904632568</v>
       </c>
       <c r="C1734" t="n">
-        <v>2.93</v>
+        <v>2.930000066757202</v>
       </c>
       <c r="D1734" t="n">
-        <v>2.85</v>
+        <v>2.849999904632568</v>
       </c>
       <c r="E1734" t="n">
-        <v>2.88</v>
+        <v>2.880000114440918</v>
       </c>
       <c r="F1734" t="n">
         <v>1346100</v>
+      </c>
+    </row>
+    <row r="1735">
+      <c r="A1735" s="1" t="n">
+        <v>46289</v>
+      </c>
+      <c r="B1735" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="C1735" t="n">
+        <v>3</v>
+      </c>
+      <c r="D1735" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="E1735" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="F1735" t="n">
+        <v>3627000</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1735"/>
+  <dimension ref="A1:F1736"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173712730408</v>
+        <v>1.799173474311829</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173712730408</v>
+        <v>1.799173474311829</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173712730408</v>
+        <v>1.799173474311829</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173712730408</v>
+        <v>1.799173474311829</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853133201599121</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853133201599121</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853133201599121</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853133201599121</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853133201599121</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853133201599121</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853133201599121</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853133201599121</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853133201599121</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853133201599121</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853133201599121</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853133201599121</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725196361541748</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725196361541748</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725196361541748</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725196361541748</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725196361541748</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725196361541748</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725196361541748</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725196599960327</v>
+        <v>2.725196361541748</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279499292373657</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279499292373657</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279499292373657</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279499292373657</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461867332458</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461867332458</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461867332458</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461867332458</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647353172302246</v>
+        <v>4.647355556488037</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647353172302246</v>
+        <v>4.647355556488037</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647353172302246</v>
+        <v>4.647355556488037</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647353172302246</v>
+        <v>4.647355556488037</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951085567474365</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951085567474365</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951085567474365</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951085567474365</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.99722146987915</v>
+        <v>6.997223854064941</v>
       </c>
       <c r="C44" t="n">
-        <v>6.99722146987915</v>
+        <v>6.997223854064942</v>
       </c>
       <c r="D44" t="n">
-        <v>6.99722146987915</v>
+        <v>6.997223854064942</v>
       </c>
       <c r="E44" t="n">
-        <v>6.99722146987915</v>
+        <v>6.997223854064942</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959037780762</v>
+        <v>3.926958560943604</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045627593994</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045627593994</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045627593994</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045627593994</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.68732929229736</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.68732929229736</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.68732929229736</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.68732929229736</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589143753051758</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589143753051758</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589143753051758</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589143753051758</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257293701172</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257293701172</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257293701172</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257293701172</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -2032,16 +2032,16 @@
         <v>43809</v>
       </c>
       <c r="B81" t="n">
-        <v>10.37040901184082</v>
+        <v>10.37040996551514</v>
       </c>
       <c r="C81" t="n">
-        <v>10.37040901184082</v>
+        <v>10.37040996551514</v>
       </c>
       <c r="D81" t="n">
-        <v>9.685504663987407</v>
+        <v>9.685505554677158</v>
       </c>
       <c r="E81" t="n">
-        <v>9.685504663987407</v>
+        <v>9.685505554677158</v>
       </c>
       <c r="F81" t="n">
         <v>1510</v>
@@ -2392,16 +2392,16 @@
         <v>43892</v>
       </c>
       <c r="B99" t="n">
-        <v>8.602726936340332</v>
+        <v>8.602725982666016</v>
       </c>
       <c r="C99" t="n">
-        <v>8.865253757575406</v>
+        <v>8.865252774798098</v>
       </c>
       <c r="D99" t="n">
-        <v>8.459212139605388</v>
+        <v>8.459211201840722</v>
       </c>
       <c r="E99" t="n">
-        <v>8.72173896084046</v>
+        <v>8.721737993972804</v>
       </c>
       <c r="F99" t="n">
         <v>11103420</v>
@@ -2432,16 +2432,16 @@
         <v>43894</v>
       </c>
       <c r="B101" t="n">
-        <v>8.692568778991699</v>
+        <v>8.692569732666016</v>
       </c>
       <c r="C101" t="n">
-        <v>8.80224676394379</v>
+        <v>8.802247729651036</v>
       </c>
       <c r="D101" t="n">
-        <v>8.564221896891393</v>
+        <v>8.564222836484587</v>
       </c>
       <c r="E101" t="n">
-        <v>8.734572326921571</v>
+        <v>8.734573285204156</v>
       </c>
       <c r="F101" t="n">
         <v>7583284</v>
@@ -2532,16 +2532,16 @@
         <v>43901</v>
       </c>
       <c r="B106" t="n">
-        <v>7.280755043029785</v>
+        <v>7.280755519866943</v>
       </c>
       <c r="C106" t="n">
-        <v>7.652960679612288</v>
+        <v>7.652961180826241</v>
       </c>
       <c r="D106" t="n">
-        <v>6.825708745737296</v>
+        <v>6.825709192772189</v>
       </c>
       <c r="E106" t="n">
-        <v>7.467442341108447</v>
+        <v>7.467442830172282</v>
       </c>
       <c r="F106" t="n">
         <v>14927915</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198310852051</v>
+        <v>6.731198787689209</v>
       </c>
       <c r="C107" t="n">
-        <v>6.78487002388751</v>
+        <v>6.784870504526766</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975251402972</v>
+        <v>6.183975689474925</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242313978574833</v>
+        <v>6.242314420779493</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277256011962891</v>
+        <v>7.277255535125732</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641293232093194</v>
+        <v>7.641292731402749</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086185591607</v>
+        <v>6.70086141684674</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766202580870931</v>
+        <v>6.766202137520195</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2692,16 +2692,16 @@
         <v>43913</v>
       </c>
       <c r="B114" t="n">
-        <v>8.386870384216309</v>
+        <v>8.386871337890625</v>
       </c>
       <c r="C114" t="n">
-        <v>8.386870384216309</v>
+        <v>8.386871337890625</v>
       </c>
       <c r="D114" t="n">
-        <v>7.48377644845884</v>
+        <v>7.483777299441991</v>
       </c>
       <c r="E114" t="n">
-        <v>8.050835275027762</v>
+        <v>8.050836190491395</v>
       </c>
       <c r="F114" t="n">
         <v>25091072</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469774723052979</v>
+        <v>7.469775199890137</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746303815364229</v>
+        <v>7.746304309853773</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351929151295045</v>
+        <v>7.351929620609467</v>
       </c>
       <c r="E118" t="n">
-        <v>7.51411282735269</v>
+        <v>7.514113307020195</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2792,16 +2792,16 @@
         <v>43920</v>
       </c>
       <c r="B119" t="n">
-        <v>7.58411979675293</v>
+        <v>7.584119319915771</v>
       </c>
       <c r="C119" t="n">
-        <v>7.677463445734158</v>
+        <v>7.677462963028194</v>
       </c>
       <c r="D119" t="n">
-        <v>7.322760268800774</v>
+        <v>7.322759808396101</v>
       </c>
       <c r="E119" t="n">
-        <v>7.354263351154514</v>
+        <v>7.354262888769144</v>
       </c>
       <c r="F119" t="n">
         <v>7283457</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672796726226807</v>
+        <v>7.672797203063965</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109174958611256</v>
+        <v>8.109175462567777</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661128980388104</v>
+        <v>7.661129456500152</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840814283200555</v>
+        <v>7.84081477047941</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798988342285</v>
+        <v>7.700798511505127</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307612995673</v>
+        <v>7.781307131173381</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430989778177</v>
+        <v>7.362430533892927</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629934591736</v>
+        <v>7.678629459127295</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -2952,16 +2952,16 @@
         <v>43930</v>
       </c>
       <c r="B127" t="n">
-        <v>7.38576602935791</v>
+        <v>7.385766506195068</v>
       </c>
       <c r="C127" t="n">
-        <v>7.778973418970338</v>
+        <v>7.778973921193609</v>
       </c>
       <c r="D127" t="n">
-        <v>7.351929231575166</v>
+        <v>7.351929706227764</v>
       </c>
       <c r="E127" t="n">
-        <v>7.778973418970338</v>
+        <v>7.778973921193609</v>
       </c>
       <c r="F127" t="n">
         <v>7590081</v>
@@ -2972,16 +2972,16 @@
         <v>43934</v>
       </c>
       <c r="B128" t="n">
-        <v>7.41493558883667</v>
+        <v>7.414936065673828</v>
       </c>
       <c r="C128" t="n">
-        <v>7.447605949093313</v>
+        <v>7.447606428031426</v>
       </c>
       <c r="D128" t="n">
-        <v>7.229416415322526</v>
+        <v>7.22941688022938</v>
       </c>
       <c r="E128" t="n">
-        <v>7.385766224588598</v>
+        <v>7.385766699549943</v>
       </c>
       <c r="F128" t="n">
         <v>8873976</v>
@@ -3052,16 +3052,16 @@
         <v>43938</v>
       </c>
       <c r="B132" t="n">
-        <v>7.467442035675049</v>
+        <v>7.467442512512207</v>
       </c>
       <c r="C132" t="n">
-        <v>7.640126182624983</v>
+        <v>7.640126670488972</v>
       </c>
       <c r="D132" t="n">
-        <v>7.396267443165728</v>
+        <v>7.396267915457998</v>
       </c>
       <c r="E132" t="n">
-        <v>7.640126182624983</v>
+        <v>7.640126670488972</v>
       </c>
       <c r="F132" t="n">
         <v>7733575</v>
@@ -3072,16 +3072,16 @@
         <v>43941</v>
       </c>
       <c r="B133" t="n">
-        <v>7.58411979675293</v>
+        <v>7.584119319915771</v>
       </c>
       <c r="C133" t="n">
-        <v>7.592288227421651</v>
+        <v>7.592287750070918</v>
       </c>
       <c r="D133" t="n">
-        <v>7.316925555412612</v>
+        <v>7.316925095374786</v>
       </c>
       <c r="E133" t="n">
-        <v>7.350763195420438</v>
+        <v>7.350762733255134</v>
       </c>
       <c r="F133" t="n">
         <v>10524157</v>
@@ -3152,16 +3152,16 @@
         <v>43948</v>
       </c>
       <c r="B137" t="n">
-        <v>8.105673789978027</v>
+        <v>8.105674743652344</v>
       </c>
       <c r="C137" t="n">
-        <v>8.16517979671254</v>
+        <v>8.165180757388045</v>
       </c>
       <c r="D137" t="n">
-        <v>7.710133516824237</v>
+        <v>7.710134423961201</v>
       </c>
       <c r="E137" t="n">
-        <v>7.937657076955135</v>
+        <v>7.93765801086142</v>
       </c>
       <c r="F137" t="n">
         <v>12260436</v>
@@ -3172,16 +3172,16 @@
         <v>43949</v>
       </c>
       <c r="B138" t="n">
-        <v>7.822145462036133</v>
+        <v>7.822145938873291</v>
       </c>
       <c r="C138" t="n">
-        <v>8.301695367155927</v>
+        <v>8.301695873226397</v>
       </c>
       <c r="D138" t="n">
-        <v>7.804643843107134</v>
+        <v>7.804644318877395</v>
       </c>
       <c r="E138" t="n">
-        <v>8.167514607953231</v>
+        <v>8.167515105844055</v>
       </c>
       <c r="F138" t="n">
         <v>14579753</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726467609405518</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817412213003</v>
+        <v>7.882817898699254</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726467609405518</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311096399979</v>
+        <v>7.816311578781807</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -35112,19 +35112,39 @@
         <v>46289</v>
       </c>
       <c r="B1735" t="n">
-        <v>2.86</v>
+        <v>2.859999895095825</v>
       </c>
       <c r="C1735" t="n">
         <v>3</v>
       </c>
       <c r="D1735" t="n">
-        <v>2.8</v>
+        <v>2.799999952316284</v>
       </c>
       <c r="E1735" t="n">
-        <v>2.85</v>
+        <v>2.849999904632568</v>
       </c>
       <c r="F1735" t="n">
         <v>3627000</v>
+      </c>
+    </row>
+    <row r="1736">
+      <c r="A1736" s="1" t="n">
+        <v>46290</v>
+      </c>
+      <c r="B1736" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="C1736" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="D1736" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E1736" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="F1736" t="n">
+        <v>1454500</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1736"/>
+  <dimension ref="A1:F1737"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173474311829</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173474311829</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173474311829</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173474311829</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725196361541748</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725196361541748</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725196361541748</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725196361541748</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725196361541748</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725196361541748</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725196361541748</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725196361541748</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279499292373657</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279499292373657</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279499292373657</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279499292373657</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461867332458</v>
+        <v>1.9224613904953</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461867332458</v>
+        <v>1.9224613904953</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461867332458</v>
+        <v>1.9224613904953</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461867332458</v>
+        <v>1.9224613904953</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647355556488037</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647355556488037</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647355556488037</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647355556488037</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997223854064941</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958560943604</v>
+        <v>3.92695951461792</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.92695951461792</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.92695951461792</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.92695951461792</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045627593994</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045627593994</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045627593994</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045627593994</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68732929229736</v>
+        <v>12.687331199646</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68732929229736</v>
+        <v>12.687331199646</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68732929229736</v>
+        <v>12.687331199646</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68732929229736</v>
+        <v>12.687331199646</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -35132,19 +35132,39 @@
         <v>46290</v>
       </c>
       <c r="B1736" t="n">
-        <v>2.92</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="C1736" t="n">
-        <v>2.94</v>
+        <v>2.940000057220459</v>
       </c>
       <c r="D1736" t="n">
-        <v>2.82</v>
+        <v>2.819999933242798</v>
       </c>
       <c r="E1736" t="n">
-        <v>2.86</v>
+        <v>2.859999895095825</v>
       </c>
       <c r="F1736" t="n">
         <v>1454500</v>
+      </c>
+    </row>
+    <row r="1737">
+      <c r="A1737" s="1" t="n">
+        <v>46293</v>
+      </c>
+      <c r="B1737" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C1737" t="n">
+        <v>2.99</v>
+      </c>
+      <c r="D1737" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="E1737" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="F1737" t="n">
+        <v>3124100</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1737"/>
+  <dimension ref="A1:F1738"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500961303711</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500961303711</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500961303711</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500961303711</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.12565279006958</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.12565279006958</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.12565279006958</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.12565279006958</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.9224613904953</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="C38" t="n">
-        <v>1.9224613904953</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="D38" t="n">
-        <v>1.9224613904953</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="E38" t="n">
-        <v>1.9224613904953</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800049</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222900390625</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.92695951461792</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="C48" t="n">
-        <v>3.92695951461792</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="D48" t="n">
-        <v>3.92695951461792</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="E48" t="n">
-        <v>3.92695951461792</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988324165344238</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988324165344238</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988324165344238</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988324165344238</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -2032,16 +2032,16 @@
         <v>43809</v>
       </c>
       <c r="B81" t="n">
-        <v>10.37040996551514</v>
+        <v>10.37040901184082</v>
       </c>
       <c r="C81" t="n">
-        <v>10.37040996551514</v>
+        <v>10.37040901184082</v>
       </c>
       <c r="D81" t="n">
-        <v>9.685505554677158</v>
+        <v>9.685504663987407</v>
       </c>
       <c r="E81" t="n">
-        <v>9.685505554677158</v>
+        <v>9.685504663987407</v>
       </c>
       <c r="F81" t="n">
         <v>1510</v>
@@ -2392,16 +2392,16 @@
         <v>43892</v>
       </c>
       <c r="B99" t="n">
-        <v>8.602725982666016</v>
+        <v>8.602726936340332</v>
       </c>
       <c r="C99" t="n">
-        <v>8.865252774798098</v>
+        <v>8.865253757575406</v>
       </c>
       <c r="D99" t="n">
-        <v>8.459211201840722</v>
+        <v>8.459212139605388</v>
       </c>
       <c r="E99" t="n">
-        <v>8.721737993972804</v>
+        <v>8.72173896084046</v>
       </c>
       <c r="F99" t="n">
         <v>11103420</v>
@@ -2432,16 +2432,16 @@
         <v>43894</v>
       </c>
       <c r="B101" t="n">
-        <v>8.692569732666016</v>
+        <v>8.692568778991699</v>
       </c>
       <c r="C101" t="n">
-        <v>8.802247729651036</v>
+        <v>8.80224676394379</v>
       </c>
       <c r="D101" t="n">
-        <v>8.564222836484587</v>
+        <v>8.564221896891393</v>
       </c>
       <c r="E101" t="n">
-        <v>8.734573285204156</v>
+        <v>8.734572326921571</v>
       </c>
       <c r="F101" t="n">
         <v>7583284</v>
@@ -2532,16 +2532,16 @@
         <v>43901</v>
       </c>
       <c r="B106" t="n">
-        <v>7.280755519866943</v>
+        <v>7.280755043029785</v>
       </c>
       <c r="C106" t="n">
-        <v>7.652961180826241</v>
+        <v>7.652960679612288</v>
       </c>
       <c r="D106" t="n">
-        <v>6.825709192772189</v>
+        <v>6.825708745737296</v>
       </c>
       <c r="E106" t="n">
-        <v>7.467442830172282</v>
+        <v>7.467442341108447</v>
       </c>
       <c r="F106" t="n">
         <v>14927915</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198787689209</v>
+        <v>6.731198310852051</v>
       </c>
       <c r="C107" t="n">
-        <v>6.784870504526766</v>
+        <v>6.78487002388751</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975689474925</v>
+        <v>6.183975251402972</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242314420779493</v>
+        <v>6.242313978574833</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255535125732</v>
+        <v>7.277256011962891</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292731402749</v>
+        <v>7.641293232093194</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086141684674</v>
+        <v>6.70086185591607</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766202137520195</v>
+        <v>6.766202580870931</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2692,16 +2692,16 @@
         <v>43913</v>
       </c>
       <c r="B114" t="n">
-        <v>8.386871337890625</v>
+        <v>8.386870384216309</v>
       </c>
       <c r="C114" t="n">
-        <v>8.386871337890625</v>
+        <v>8.386870384216309</v>
       </c>
       <c r="D114" t="n">
-        <v>7.483777299441991</v>
+        <v>7.48377644845884</v>
       </c>
       <c r="E114" t="n">
-        <v>8.050836190491395</v>
+        <v>8.050835275027762</v>
       </c>
       <c r="F114" t="n">
         <v>25091072</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775199890137</v>
+        <v>7.469774723052979</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304309853773</v>
+        <v>7.746303815364229</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351929620609467</v>
+        <v>7.351929151295045</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113307020195</v>
+        <v>7.51411282735269</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2792,16 +2792,16 @@
         <v>43920</v>
       </c>
       <c r="B119" t="n">
-        <v>7.584119319915771</v>
+        <v>7.58411979675293</v>
       </c>
       <c r="C119" t="n">
-        <v>7.677462963028194</v>
+        <v>7.677463445734158</v>
       </c>
       <c r="D119" t="n">
-        <v>7.322759808396101</v>
+        <v>7.322760268800774</v>
       </c>
       <c r="E119" t="n">
-        <v>7.354262888769144</v>
+        <v>7.354263351154514</v>
       </c>
       <c r="F119" t="n">
         <v>7283457</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672797203063965</v>
+        <v>7.672796726226807</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109175462567777</v>
+        <v>8.109174958611256</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661129456500152</v>
+        <v>7.661128980388104</v>
       </c>
       <c r="E125" t="n">
-        <v>7.84081477047941</v>
+        <v>7.840814283200555</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798511505127</v>
+        <v>7.700798988342285</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307131173381</v>
+        <v>7.781307612995673</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430533892927</v>
+        <v>7.362430989778177</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629459127295</v>
+        <v>7.678629934591736</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -2952,16 +2952,16 @@
         <v>43930</v>
       </c>
       <c r="B127" t="n">
-        <v>7.385766506195068</v>
+        <v>7.38576602935791</v>
       </c>
       <c r="C127" t="n">
-        <v>7.778973921193609</v>
+        <v>7.778973418970338</v>
       </c>
       <c r="D127" t="n">
-        <v>7.351929706227764</v>
+        <v>7.351929231575166</v>
       </c>
       <c r="E127" t="n">
-        <v>7.778973921193609</v>
+        <v>7.778973418970338</v>
       </c>
       <c r="F127" t="n">
         <v>7590081</v>
@@ -2972,16 +2972,16 @@
         <v>43934</v>
       </c>
       <c r="B128" t="n">
-        <v>7.414936065673828</v>
+        <v>7.41493558883667</v>
       </c>
       <c r="C128" t="n">
-        <v>7.447606428031426</v>
+        <v>7.447605949093313</v>
       </c>
       <c r="D128" t="n">
-        <v>7.22941688022938</v>
+        <v>7.229416415322526</v>
       </c>
       <c r="E128" t="n">
-        <v>7.385766699549943</v>
+        <v>7.385766224588598</v>
       </c>
       <c r="F128" t="n">
         <v>8873976</v>
@@ -3052,16 +3052,16 @@
         <v>43938</v>
       </c>
       <c r="B132" t="n">
-        <v>7.467442512512207</v>
+        <v>7.467442035675049</v>
       </c>
       <c r="C132" t="n">
-        <v>7.640126670488972</v>
+        <v>7.640126182624983</v>
       </c>
       <c r="D132" t="n">
-        <v>7.396267915457998</v>
+        <v>7.396267443165728</v>
       </c>
       <c r="E132" t="n">
-        <v>7.640126670488972</v>
+        <v>7.640126182624983</v>
       </c>
       <c r="F132" t="n">
         <v>7733575</v>
@@ -3072,16 +3072,16 @@
         <v>43941</v>
       </c>
       <c r="B133" t="n">
-        <v>7.584119319915771</v>
+        <v>7.58411979675293</v>
       </c>
       <c r="C133" t="n">
-        <v>7.592287750070918</v>
+        <v>7.592288227421651</v>
       </c>
       <c r="D133" t="n">
-        <v>7.316925095374786</v>
+        <v>7.316925555412612</v>
       </c>
       <c r="E133" t="n">
-        <v>7.350762733255134</v>
+        <v>7.350763195420438</v>
       </c>
       <c r="F133" t="n">
         <v>10524157</v>
@@ -3152,16 +3152,16 @@
         <v>43948</v>
       </c>
       <c r="B137" t="n">
-        <v>8.105674743652344</v>
+        <v>8.105673789978027</v>
       </c>
       <c r="C137" t="n">
-        <v>8.165180757388045</v>
+        <v>8.16517979671254</v>
       </c>
       <c r="D137" t="n">
-        <v>7.710134423961201</v>
+        <v>7.710133516824237</v>
       </c>
       <c r="E137" t="n">
-        <v>7.93765801086142</v>
+        <v>7.937657076955135</v>
       </c>
       <c r="F137" t="n">
         <v>12260436</v>
@@ -3172,16 +3172,16 @@
         <v>43949</v>
       </c>
       <c r="B138" t="n">
-        <v>7.822145938873291</v>
+        <v>7.822145462036133</v>
       </c>
       <c r="C138" t="n">
-        <v>8.301695873226397</v>
+        <v>8.301695367155927</v>
       </c>
       <c r="D138" t="n">
-        <v>7.804644318877395</v>
+        <v>7.804643843107134</v>
       </c>
       <c r="E138" t="n">
-        <v>8.167515105844055</v>
+        <v>8.167514607953231</v>
       </c>
       <c r="F138" t="n">
         <v>14579753</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726467609405518</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817898699254</v>
+        <v>7.882817412213003</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726467609405518</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311578781807</v>
+        <v>7.816311096399979</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -35152,19 +35152,39 @@
         <v>46293</v>
       </c>
       <c r="B1737" t="n">
-        <v>2.91</v>
+        <v>2.910000085830688</v>
       </c>
       <c r="C1737" t="n">
-        <v>2.99</v>
+        <v>2.990000009536743</v>
       </c>
       <c r="D1737" t="n">
-        <v>2.89</v>
+        <v>2.890000104904175</v>
       </c>
       <c r="E1737" t="n">
-        <v>2.93</v>
+        <v>2.930000066757202</v>
       </c>
       <c r="F1737" t="n">
         <v>3124100</v>
+      </c>
+    </row>
+    <row r="1738">
+      <c r="A1738" s="1" t="n">
+        <v>46294</v>
+      </c>
+      <c r="B1738" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1738" t="n">
+        <v>3.01</v>
+      </c>
+      <c r="D1738" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="E1738" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="F1738" t="n">
+        <v>3587200</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1738"/>
+  <dimension ref="A1:F1739"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500961303711</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500961303711</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500961303711</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500961303711</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="C36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="D36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="E36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.12565279006958</v>
+        <v>2.125653028488159</v>
       </c>
       <c r="C37" t="n">
-        <v>2.12565279006958</v>
+        <v>2.125653028488159</v>
       </c>
       <c r="D37" t="n">
-        <v>2.12565279006958</v>
+        <v>2.125653028488159</v>
       </c>
       <c r="E37" t="n">
-        <v>2.12565279006958</v>
+        <v>2.125653028488159</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212013244629</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997222900390625</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294834613800049</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294834613800049</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294834613800049</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294834613800049</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587933540344238</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587933540344238</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587933540344238</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587933540344238</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543548583984</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543548583984</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543548583984</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543548583984</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589141845703125</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988324165344238</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988324165344238</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988324165344238</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988324165344238</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="C64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="D64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="E64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -1872,16 +1872,16 @@
         <v>43741</v>
       </c>
       <c r="B73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F73" t="n">
         <v>755</v>
@@ -1892,16 +1892,16 @@
         <v>43747</v>
       </c>
       <c r="B74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F74" t="n">
         <v>755</v>
@@ -1952,16 +1952,16 @@
         <v>43773</v>
       </c>
       <c r="B77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F77" t="n">
         <v>1510</v>
@@ -2012,16 +2012,16 @@
         <v>43802</v>
       </c>
       <c r="B80" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C80" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D80" t="n">
-        <v>9.217621990355065</v>
+        <v>9.21762282756219</v>
       </c>
       <c r="E80" t="n">
-        <v>9.217621990355065</v>
+        <v>9.21762282756219</v>
       </c>
       <c r="F80" t="n">
         <v>1510</v>
@@ -2032,16 +2032,16 @@
         <v>43809</v>
       </c>
       <c r="B81" t="n">
-        <v>10.37040901184082</v>
+        <v>10.37040996551514</v>
       </c>
       <c r="C81" t="n">
-        <v>10.37040901184082</v>
+        <v>10.37040996551514</v>
       </c>
       <c r="D81" t="n">
-        <v>9.685504663987407</v>
+        <v>9.685505554677158</v>
       </c>
       <c r="E81" t="n">
-        <v>9.685504663987407</v>
+        <v>9.685505554677158</v>
       </c>
       <c r="F81" t="n">
         <v>1510</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2392,16 +2392,16 @@
         <v>43892</v>
       </c>
       <c r="B99" t="n">
-        <v>8.602726936340332</v>
+        <v>8.602725982666016</v>
       </c>
       <c r="C99" t="n">
-        <v>8.865253757575406</v>
+        <v>8.865252774798098</v>
       </c>
       <c r="D99" t="n">
-        <v>8.459212139605388</v>
+        <v>8.459211201840722</v>
       </c>
       <c r="E99" t="n">
-        <v>8.72173896084046</v>
+        <v>8.721737993972804</v>
       </c>
       <c r="F99" t="n">
         <v>11103420</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087005615234375</v>
+        <v>8.087006568908691</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167514235155968</v>
+        <v>8.167515198324406</v>
       </c>
       <c r="D103" t="n">
-        <v>7.934155965259957</v>
+        <v>7.93415690090921</v>
       </c>
       <c r="E103" t="n">
-        <v>7.99249553273396</v>
+        <v>7.992496475263009</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277256011962891</v>
+        <v>7.277255535125732</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641293232093194</v>
+        <v>7.641292731402749</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086185591607</v>
+        <v>6.70086141684674</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766202580870931</v>
+        <v>6.766202137520195</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2632,16 +2632,16 @@
         <v>43908</v>
       </c>
       <c r="B111" t="n">
-        <v>6.98555850982666</v>
+        <v>6.985558032989502</v>
       </c>
       <c r="C111" t="n">
-        <v>8.075338544707167</v>
+        <v>8.075337993481165</v>
       </c>
       <c r="D111" t="n">
-        <v>6.71019666955442</v>
+        <v>6.710196211513576</v>
       </c>
       <c r="E111" t="n">
-        <v>7.140741469742403</v>
+        <v>7.140740982312391</v>
       </c>
       <c r="F111" t="n">
         <v>26337960</v>
@@ -2652,16 +2652,16 @@
         <v>43909</v>
       </c>
       <c r="B112" t="n">
-        <v>7.521113395690918</v>
+        <v>7.521113872528076</v>
       </c>
       <c r="C112" t="n">
-        <v>8.106841959390016</v>
+        <v>8.106842473362253</v>
       </c>
       <c r="D112" t="n">
-        <v>6.356659520848136</v>
+        <v>6.35665992385914</v>
       </c>
       <c r="E112" t="n">
-        <v>6.779036703963478</v>
+        <v>6.779037133753115</v>
       </c>
       <c r="F112" t="n">
         <v>19250108</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469455718994</v>
+        <v>7.740469932556152</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757971914786575</v>
+        <v>7.757972392701939</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613289833068848</v>
+        <v>7.613289356231689</v>
       </c>
       <c r="C124" t="n">
-        <v>7.699632328290281</v>
+        <v>7.699631846045301</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497777973422238</v>
+        <v>7.497777503819842</v>
       </c>
       <c r="E124" t="n">
-        <v>7.584119628270164</v>
+        <v>7.58411915326</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375264644622803</v>
+        <v>7.375265121459961</v>
       </c>
       <c r="C130" t="n">
-        <v>7.494277495176356</v>
+        <v>7.49427797970812</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343761564324954</v>
+        <v>7.343762039125325</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935003671517</v>
+        <v>7.407935482620931</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3052,16 +3052,16 @@
         <v>43938</v>
       </c>
       <c r="B132" t="n">
-        <v>7.467442035675049</v>
+        <v>7.467442512512207</v>
       </c>
       <c r="C132" t="n">
-        <v>7.640126182624983</v>
+        <v>7.640126670488972</v>
       </c>
       <c r="D132" t="n">
-        <v>7.396267443165728</v>
+        <v>7.396267915457998</v>
       </c>
       <c r="E132" t="n">
-        <v>7.640126182624983</v>
+        <v>7.640126670488972</v>
       </c>
       <c r="F132" t="n">
         <v>7733575</v>
@@ -3112,16 +3112,16 @@
         <v>43944</v>
       </c>
       <c r="B135" t="n">
-        <v>8.089340209960938</v>
+        <v>8.089339256286621</v>
       </c>
       <c r="C135" t="n">
-        <v>8.574724018558863</v>
+        <v>8.57472300766133</v>
       </c>
       <c r="D135" t="n">
-        <v>7.969160906424007</v>
+        <v>7.969159966917957</v>
       </c>
       <c r="E135" t="n">
-        <v>8.481380364324728</v>
+        <v>8.481379364431731</v>
       </c>
       <c r="F135" t="n">
         <v>13472583</v>
@@ -3252,16 +3252,16 @@
         <v>43956</v>
       </c>
       <c r="B142" t="n">
-        <v>8.114090919494629</v>
+        <v>8.114091873168945</v>
       </c>
       <c r="C142" t="n">
-        <v>8.645023715587479</v>
+        <v>8.645024731663977</v>
       </c>
       <c r="D142" t="n">
-        <v>8.069432995707503</v>
+        <v>8.069433944133035</v>
       </c>
       <c r="E142" t="n">
-        <v>8.286520199683441</v>
+        <v>8.286521173623905</v>
       </c>
       <c r="F142" t="n">
         <v>11843548</v>
@@ -3272,16 +3272,16 @@
         <v>43957</v>
       </c>
       <c r="B143" t="n">
-        <v>8.048345565795898</v>
+        <v>8.048344612121582</v>
       </c>
       <c r="C143" t="n">
-        <v>8.145104858936216</v>
+        <v>8.145103893796581</v>
       </c>
       <c r="D143" t="n">
-        <v>7.963991997516411</v>
+        <v>7.96399105383742</v>
       </c>
       <c r="E143" t="n">
-        <v>8.145104858936216</v>
+        <v>8.145103893796581</v>
       </c>
       <c r="F143" t="n">
         <v>16545622</v>
@@ -3312,16 +3312,16 @@
         <v>43959</v>
       </c>
       <c r="B145" t="n">
-        <v>8.162469863891602</v>
+        <v>8.162470817565918</v>
       </c>
       <c r="C145" t="n">
-        <v>8.184799271833279</v>
+        <v>8.184800228116485</v>
       </c>
       <c r="D145" t="n">
-        <v>7.94786381115636</v>
+        <v>7.947864739756858</v>
       </c>
       <c r="E145" t="n">
-        <v>8.15626744912163</v>
+        <v>8.156268402071278</v>
       </c>
       <c r="F145" t="n">
         <v>8818844</v>
@@ -3352,16 +3352,16 @@
         <v>43963</v>
       </c>
       <c r="B147" t="n">
-        <v>8.085558891296387</v>
+        <v>8.085559844970703</v>
       </c>
       <c r="C147" t="n">
-        <v>8.276595411529883</v>
+        <v>8.276596387736546</v>
       </c>
       <c r="D147" t="n">
-        <v>8.063229483236768</v>
+        <v>8.063230434277379</v>
       </c>
       <c r="E147" t="n">
-        <v>8.187279566215866</v>
+        <v>8.187280531887918</v>
       </c>
       <c r="F147" t="n">
         <v>9953957</v>
@@ -3372,16 +3372,16 @@
         <v>43964</v>
       </c>
       <c r="B148" t="n">
-        <v>7.926775455474854</v>
+        <v>7.926775932312012</v>
       </c>
       <c r="C148" t="n">
-        <v>8.187279557292356</v>
+        <v>8.187280049800203</v>
       </c>
       <c r="D148" t="n">
-        <v>7.885839696513885</v>
+        <v>7.885840170888542</v>
       </c>
       <c r="E148" t="n">
-        <v>8.187279557292356</v>
+        <v>8.187280049800203</v>
       </c>
       <c r="F148" t="n">
         <v>10179016</v>
@@ -3412,16 +3412,16 @@
         <v>43966</v>
       </c>
       <c r="B150" t="n">
-        <v>6.8413405418396</v>
+        <v>6.841341018676758</v>
       </c>
       <c r="C150" t="n">
-        <v>7.421893104642092</v>
+        <v>7.421893621943401</v>
       </c>
       <c r="D150" t="n">
-        <v>6.8413405418396</v>
+        <v>6.841341018676758</v>
       </c>
       <c r="E150" t="n">
-        <v>7.420652532303285</v>
+        <v>7.420653049518127</v>
       </c>
       <c r="F150" t="n">
         <v>26563775</v>
@@ -3452,16 +3452,16 @@
         <v>43970</v>
       </c>
       <c r="B152" t="n">
-        <v>6.831418037414551</v>
+        <v>6.831417560577393</v>
       </c>
       <c r="C152" t="n">
-        <v>7.018732418962401</v>
+        <v>7.018731929050585</v>
       </c>
       <c r="D152" t="n">
-        <v>6.79916449333305</v>
+        <v>6.799164018747209</v>
       </c>
       <c r="E152" t="n">
-        <v>6.966631502251738</v>
+        <v>6.966631015976597</v>
       </c>
       <c r="F152" t="n">
         <v>13463520</v>
@@ -3472,16 +3472,16 @@
         <v>43971</v>
       </c>
       <c r="B153" t="n">
-        <v>6.822733879089355</v>
+        <v>6.822733402252197</v>
       </c>
       <c r="C153" t="n">
-        <v>6.983998022077899</v>
+        <v>6.983997533970078</v>
       </c>
       <c r="D153" t="n">
-        <v>6.810329048105121</v>
+        <v>6.81032857213493</v>
       </c>
       <c r="E153" t="n">
-        <v>6.94678397585636</v>
+        <v>6.946783490349408</v>
       </c>
       <c r="F153" t="n">
         <v>11533147</v>
@@ -3552,16 +3552,16 @@
         <v>43977</v>
       </c>
       <c r="B157" t="n">
-        <v>7.423134803771973</v>
+        <v>7.423134326934814</v>
       </c>
       <c r="C157" t="n">
-        <v>7.560829411371671</v>
+        <v>7.560828925689475</v>
       </c>
       <c r="D157" t="n">
-        <v>7.275515169821428</v>
+        <v>7.275514702466858</v>
       </c>
       <c r="E157" t="n">
-        <v>7.442982622817829</v>
+        <v>7.442982144705714</v>
       </c>
       <c r="F157" t="n">
         <v>12080691</v>
@@ -3612,16 +3612,16 @@
         <v>43980</v>
       </c>
       <c r="B160" t="n">
-        <v>7.812650203704834</v>
+        <v>7.812650680541992</v>
       </c>
       <c r="C160" t="n">
-        <v>7.812650203704834</v>
+        <v>7.812650680541992</v>
       </c>
       <c r="D160" t="n">
-        <v>7.481437043617326</v>
+        <v>7.481437500239227</v>
       </c>
       <c r="E160" t="n">
-        <v>7.519892999404318</v>
+        <v>7.519893458373339</v>
       </c>
       <c r="F160" t="n">
         <v>23712019</v>
@@ -3652,16 +3652,16 @@
         <v>43984</v>
       </c>
       <c r="B162" t="n">
-        <v>8.271634101867676</v>
+        <v>8.271635055541992</v>
       </c>
       <c r="C162" t="n">
-        <v>8.286520076241633</v>
+        <v>8.286521031632221</v>
       </c>
       <c r="D162" t="n">
-        <v>7.976395759027911</v>
+        <v>7.976396678662855</v>
       </c>
       <c r="E162" t="n">
-        <v>8.063229567170044</v>
+        <v>8.063230496816454</v>
       </c>
       <c r="F162" t="n">
         <v>21348142</v>
@@ -3672,16 +3672,16 @@
         <v>43985</v>
       </c>
       <c r="B163" t="n">
-        <v>8.373354911804199</v>
+        <v>8.373353958129883</v>
       </c>
       <c r="C163" t="n">
-        <v>8.800086825192951</v>
+        <v>8.80008582291646</v>
       </c>
       <c r="D163" t="n">
-        <v>8.315052026205343</v>
+        <v>8.315051079171372</v>
       </c>
       <c r="E163" t="n">
-        <v>8.317533171149149</v>
+        <v>8.31753222383259</v>
       </c>
       <c r="F163" t="n">
         <v>31125376</v>
@@ -3752,16 +3752,16 @@
         <v>43991</v>
       </c>
       <c r="B167" t="n">
-        <v>8.296442985534668</v>
+        <v>8.296443939208984</v>
       </c>
       <c r="C167" t="n">
-        <v>8.327455953773208</v>
+        <v>8.32745691101246</v>
       </c>
       <c r="D167" t="n">
-        <v>8.096723794435762</v>
+        <v>8.0967247251524</v>
       </c>
       <c r="E167" t="n">
-        <v>8.137660447910266</v>
+        <v>8.137661383332564</v>
       </c>
       <c r="F167" t="n">
         <v>13675741</v>
@@ -3772,16 +3772,16 @@
         <v>43992</v>
       </c>
       <c r="B168" t="n">
-        <v>8.08928108215332</v>
+        <v>8.089280128479004</v>
       </c>
       <c r="C168" t="n">
-        <v>8.426697131827968</v>
+        <v>8.426696138374464</v>
       </c>
       <c r="D168" t="n">
-        <v>8.0371806131882</v>
+        <v>8.037179665656195</v>
       </c>
       <c r="E168" t="n">
-        <v>8.311330595134894</v>
+        <v>8.311329615282364</v>
       </c>
       <c r="F168" t="n">
         <v>11944749</v>
@@ -3792,16 +3792,16 @@
         <v>43994</v>
       </c>
       <c r="B169" t="n">
-        <v>7.950345993041992</v>
+        <v>7.950345516204834</v>
       </c>
       <c r="C169" t="n">
-        <v>8.084319777785</v>
+        <v>8.084319292912509</v>
       </c>
       <c r="D169" t="n">
-        <v>7.774195424975465</v>
+        <v>7.774194958703272</v>
       </c>
       <c r="E169" t="n">
-        <v>7.877157131822456</v>
+        <v>7.877156659374939</v>
       </c>
       <c r="F169" t="n">
         <v>12251373</v>
@@ -3892,16 +3892,16 @@
         <v>44001</v>
       </c>
       <c r="B174" t="n">
-        <v>8.487480163574219</v>
+        <v>8.487481117248535</v>
       </c>
       <c r="C174" t="n">
-        <v>8.589200838114557</v>
+        <v>8.58920180321846</v>
       </c>
       <c r="D174" t="n">
-        <v>8.203406528896336</v>
+        <v>8.203407450651435</v>
       </c>
       <c r="E174" t="n">
-        <v>8.203406528896336</v>
+        <v>8.203407450651435</v>
       </c>
       <c r="F174" t="n">
         <v>20750754</v>
@@ -3912,16 +3912,16 @@
         <v>44004</v>
       </c>
       <c r="B175" t="n">
-        <v>8.440342903137207</v>
+        <v>8.440341949462891</v>
       </c>
       <c r="C175" t="n">
-        <v>8.729377964833343</v>
+        <v>8.729376978500955</v>
       </c>
       <c r="D175" t="n">
-        <v>8.380798106578508</v>
+        <v>8.380797159632158</v>
       </c>
       <c r="E175" t="n">
-        <v>8.489962226742637</v>
+        <v>8.489961267461833</v>
       </c>
       <c r="F175" t="n">
         <v>12069362</v>
@@ -3952,16 +3952,16 @@
         <v>44006</v>
       </c>
       <c r="B177" t="n">
-        <v>8.594162940979004</v>
+        <v>8.59416389465332</v>
       </c>
       <c r="C177" t="n">
-        <v>8.669832935726904</v>
+        <v>8.669833897798144</v>
       </c>
       <c r="D177" t="n">
-        <v>8.422973795079262</v>
+        <v>8.422974729757115</v>
       </c>
       <c r="E177" t="n">
-        <v>8.571833533486773</v>
+        <v>8.571834484683247</v>
       </c>
       <c r="F177" t="n">
         <v>7388434</v>
@@ -4052,16 +4052,16 @@
         <v>44013</v>
       </c>
       <c r="B182" t="n">
-        <v>9.009730339050293</v>
+        <v>9.009729385375977</v>
       </c>
       <c r="C182" t="n">
-        <v>9.11517229493286</v>
+        <v>9.115171330097578</v>
       </c>
       <c r="D182" t="n">
-        <v>8.731859089723871</v>
+        <v>8.731858165462054</v>
       </c>
       <c r="E182" t="n">
-        <v>8.812491383860499</v>
+        <v>8.812490451063802</v>
       </c>
       <c r="F182" t="n">
         <v>8963093</v>
@@ -4292,16 +4292,16 @@
         <v>44029</v>
       </c>
       <c r="B194" t="n">
-        <v>8.81993293762207</v>
+        <v>8.819933891296387</v>
       </c>
       <c r="C194" t="n">
-        <v>8.919173360420668</v>
+        <v>8.919174324825571</v>
       </c>
       <c r="D194" t="n">
-        <v>8.633858708433587</v>
+        <v>8.633859641988225</v>
       </c>
       <c r="E194" t="n">
-        <v>8.633858708433587</v>
+        <v>8.633859641988225</v>
       </c>
       <c r="F194" t="n">
         <v>9678298</v>
@@ -4432,16 +4432,16 @@
         <v>44040</v>
       </c>
       <c r="B201" t="n">
-        <v>9.641143798828125</v>
+        <v>9.641142845153809</v>
       </c>
       <c r="C201" t="n">
-        <v>9.832180339834917</v>
+        <v>9.832179367263814</v>
       </c>
       <c r="D201" t="n">
-        <v>9.466233359369541</v>
+        <v>9.466232422996864</v>
       </c>
       <c r="E201" t="n">
-        <v>9.675878040270206</v>
+        <v>9.67587708316008</v>
       </c>
       <c r="F201" t="n">
         <v>30127714</v>
@@ -4472,16 +4472,16 @@
         <v>44042</v>
       </c>
       <c r="B203" t="n">
-        <v>9.143704414367676</v>
+        <v>9.143703460693359</v>
       </c>
       <c r="C203" t="n">
-        <v>9.700687950073165</v>
+        <v>9.700686938306321</v>
       </c>
       <c r="D203" t="n">
-        <v>9.097806359971171</v>
+        <v>9.097805411083952</v>
       </c>
       <c r="E203" t="n">
-        <v>9.685801080392711</v>
+        <v>9.685800070178546</v>
       </c>
       <c r="F203" t="n">
         <v>33272500</v>
@@ -4592,16 +4592,16 @@
         <v>44050</v>
       </c>
       <c r="B209" t="n">
-        <v>8.429177284240723</v>
+        <v>8.429178237915039</v>
       </c>
       <c r="C209" t="n">
-        <v>8.429177284240723</v>
+        <v>8.429178237915039</v>
       </c>
       <c r="D209" t="n">
-        <v>8.255506990060143</v>
+        <v>8.25550792408546</v>
       </c>
       <c r="E209" t="n">
-        <v>8.336140169103194</v>
+        <v>8.336141112251321</v>
       </c>
       <c r="F209" t="n">
         <v>22110172</v>
@@ -4612,16 +4612,16 @@
         <v>44053</v>
       </c>
       <c r="B210" t="n">
-        <v>8.259230613708496</v>
+        <v>8.25922966003418</v>
       </c>
       <c r="C210" t="n">
-        <v>8.468874414585619</v>
+        <v>8.468873436704216</v>
       </c>
       <c r="D210" t="n">
-        <v>8.166192588662099</v>
+        <v>8.166191645730668</v>
       </c>
       <c r="E210" t="n">
-        <v>8.435380296706972</v>
+        <v>8.435379322693057</v>
       </c>
       <c r="F210" t="n">
         <v>21920608</v>
@@ -4652,16 +4652,16 @@
         <v>44055</v>
       </c>
       <c r="B212" t="n">
-        <v>8.162469863891602</v>
+        <v>8.162470817565918</v>
       </c>
       <c r="C212" t="n">
-        <v>8.446543498127859</v>
+        <v>8.446544484992341</v>
       </c>
       <c r="D212" t="n">
-        <v>8.078115414787984</v>
+        <v>8.078116358606623</v>
       </c>
       <c r="E212" t="n">
-        <v>8.409329009508031</v>
+        <v>8.409329992024503</v>
       </c>
       <c r="F212" t="n">
         <v>20200945</v>
@@ -4732,16 +4732,16 @@
         <v>44061</v>
       </c>
       <c r="B216" t="n">
-        <v>8.101686477661133</v>
+        <v>8.101685523986816</v>
       </c>
       <c r="C216" t="n">
-        <v>8.143864156905972</v>
+        <v>8.143863198266791</v>
       </c>
       <c r="D216" t="n">
-        <v>7.9788782846482</v>
+        <v>7.978877345430011</v>
       </c>
       <c r="E216" t="n">
-        <v>8.038421298987467</v>
+        <v>8.038420352760289</v>
       </c>
       <c r="F216" t="n">
         <v>10608743</v>
@@ -4752,16 +4752,16 @@
         <v>44062</v>
       </c>
       <c r="B217" t="n">
-        <v>7.926775455474854</v>
+        <v>7.926775932312012</v>
       </c>
       <c r="C217" t="n">
-        <v>8.141381509109719</v>
+        <v>8.141381998856557</v>
       </c>
       <c r="D217" t="n">
-        <v>7.921813166253184</v>
+        <v>7.921813642791834</v>
       </c>
       <c r="E217" t="n">
-        <v>8.141381509109719</v>
+        <v>8.141381998856557</v>
       </c>
       <c r="F217" t="n">
         <v>9466833</v>
@@ -4772,16 +4772,16 @@
         <v>44063</v>
       </c>
       <c r="B218" t="n">
-        <v>7.957788467407227</v>
+        <v>7.957787990570068</v>
       </c>
       <c r="C218" t="n">
-        <v>8.033459366376674</v>
+        <v>8.033458885005254</v>
       </c>
       <c r="D218" t="n">
-        <v>7.774195359575069</v>
+        <v>7.774194893738959</v>
       </c>
       <c r="E218" t="n">
-        <v>7.915611684438519</v>
+        <v>7.915611210128628</v>
       </c>
       <c r="F218" t="n">
         <v>7652765</v>
@@ -4892,16 +4892,16 @@
         <v>44071</v>
       </c>
       <c r="B224" t="n">
-        <v>8.100445747375488</v>
+        <v>8.100444793701172</v>
       </c>
       <c r="C224" t="n">
-        <v>8.100445747375488</v>
+        <v>8.100444793701172</v>
       </c>
       <c r="D224" t="n">
-        <v>7.960269549341362</v>
+        <v>7.960268612170143</v>
       </c>
       <c r="E224" t="n">
-        <v>8.0012070997281</v>
+        <v>8.001206157737258</v>
       </c>
       <c r="F224" t="n">
         <v>5577388</v>
@@ -5012,16 +5012,16 @@
         <v>44082</v>
       </c>
       <c r="B230" t="n">
-        <v>7.751865863800049</v>
+        <v>7.751865386962891</v>
       </c>
       <c r="C230" t="n">
-        <v>7.833738283935308</v>
+        <v>7.833737802061967</v>
       </c>
       <c r="D230" t="n">
-        <v>7.691081834917614</v>
+        <v>7.691081361819436</v>
       </c>
       <c r="E230" t="n">
-        <v>7.813890911851665</v>
+        <v>7.813890431199186</v>
       </c>
       <c r="F230" t="n">
         <v>7181501</v>
@@ -5032,16 +5032,16 @@
         <v>44083</v>
       </c>
       <c r="B231" t="n">
-        <v>7.709688663482666</v>
+        <v>7.709689140319824</v>
       </c>
       <c r="C231" t="n">
-        <v>7.834979771965168</v>
+        <v>7.834980256551466</v>
       </c>
       <c r="D231" t="n">
-        <v>7.637739933288351</v>
+        <v>7.637740405675546</v>
       </c>
       <c r="E231" t="n">
-        <v>7.792802098282933</v>
+        <v>7.792802580260581</v>
       </c>
       <c r="F231" t="n">
         <v>8282629</v>
@@ -5052,16 +5052,16 @@
         <v>44084</v>
       </c>
       <c r="B232" t="n">
-        <v>8.850947380065918</v>
+        <v>8.850946426391602</v>
       </c>
       <c r="C232" t="n">
-        <v>9.197045218135978</v>
+        <v>9.197044227170217</v>
       </c>
       <c r="D232" t="n">
-        <v>8.621455315968662</v>
+        <v>8.62145438702172</v>
       </c>
       <c r="E232" t="n">
-        <v>9.197045218135978</v>
+        <v>9.197044227170217</v>
       </c>
       <c r="F232" t="n">
         <v>139609921</v>
@@ -5132,16 +5132,16 @@
         <v>44090</v>
       </c>
       <c r="B236" t="n">
-        <v>9.312410354614258</v>
+        <v>9.312411308288574</v>
       </c>
       <c r="C236" t="n">
-        <v>9.375675522060035</v>
+        <v>9.375676482213272</v>
       </c>
       <c r="D236" t="n">
-        <v>9.175956334671081</v>
+        <v>9.175957274371282</v>
       </c>
       <c r="E236" t="n">
-        <v>9.179677604882659</v>
+        <v>9.179678544963952</v>
       </c>
       <c r="F236" t="n">
         <v>13993693</v>
@@ -5212,16 +5212,16 @@
         <v>44096</v>
       </c>
       <c r="B240" t="n">
-        <v>9.326058387756348</v>
+        <v>9.326057434082031</v>
       </c>
       <c r="C240" t="n">
-        <v>9.353349195522698</v>
+        <v>9.353348239057649</v>
       </c>
       <c r="D240" t="n">
-        <v>9.182159127084132</v>
+        <v>9.182158188124824</v>
       </c>
       <c r="E240" t="n">
-        <v>9.192083706971793</v>
+        <v>9.192082766997606</v>
       </c>
       <c r="F240" t="n">
         <v>9315031</v>
@@ -5232,16 +5232,16 @@
         <v>44097</v>
       </c>
       <c r="B241" t="n">
-        <v>8.95390796661377</v>
+        <v>8.953908920288086</v>
       </c>
       <c r="C241" t="n">
-        <v>9.308689320943529</v>
+        <v>9.308690312405352</v>
       </c>
       <c r="D241" t="n">
-        <v>8.934059702543932</v>
+        <v>8.934060654104224</v>
       </c>
       <c r="E241" t="n">
-        <v>9.303727925022763</v>
+        <v>9.303728915956151</v>
       </c>
       <c r="F241" t="n">
         <v>13677251</v>
@@ -5252,16 +5252,16 @@
         <v>44098</v>
       </c>
       <c r="B242" t="n">
-        <v>9.282639503479004</v>
+        <v>9.282638549804688</v>
       </c>
       <c r="C242" t="n">
-        <v>9.46375236122295</v>
+        <v>9.463751388941567</v>
       </c>
       <c r="D242" t="n">
-        <v>8.898085270619518</v>
+        <v>8.898084356453305</v>
       </c>
       <c r="E242" t="n">
-        <v>8.906769724577019</v>
+        <v>8.906768809518589</v>
       </c>
       <c r="F242" t="n">
         <v>18607406</v>
@@ -5272,16 +5272,16 @@
         <v>44099</v>
       </c>
       <c r="B243" t="n">
-        <v>9.184640884399414</v>
+        <v>9.184639930725098</v>
       </c>
       <c r="C243" t="n">
-        <v>9.254108474175018</v>
+        <v>9.25410751328763</v>
       </c>
       <c r="D243" t="n">
-        <v>9.095325028918353</v>
+        <v>9.095324084518023</v>
       </c>
       <c r="E243" t="n">
-        <v>9.22061435827287</v>
+        <v>9.220613400863298</v>
       </c>
       <c r="F243" t="n">
         <v>8201819</v>
@@ -5312,16 +5312,16 @@
         <v>44103</v>
       </c>
       <c r="B245" t="n">
-        <v>8.760390281677246</v>
+        <v>8.760391235351562</v>
       </c>
       <c r="C245" t="n">
-        <v>8.942743247933565</v>
+        <v>8.942744221459206</v>
       </c>
       <c r="D245" t="n">
-        <v>8.683479263674647</v>
+        <v>8.68348020897627</v>
       </c>
       <c r="E245" t="n">
-        <v>8.802567060978735</v>
+        <v>8.802568019244504</v>
       </c>
       <c r="F245" t="n">
         <v>13985386</v>
@@ -5332,16 +5332,16 @@
         <v>44104</v>
       </c>
       <c r="B246" t="n">
-        <v>8.651226997375488</v>
+        <v>8.651226043701172</v>
       </c>
       <c r="C246" t="n">
-        <v>8.841023415853394</v>
+        <v>8.841022441256731</v>
       </c>
       <c r="D246" t="n">
-        <v>8.609050214038696</v>
+        <v>8.609049265013768</v>
       </c>
       <c r="E246" t="n">
-        <v>8.803808028904122</v>
+        <v>8.803807058409923</v>
       </c>
       <c r="F246" t="n">
         <v>11477260</v>
@@ -5412,16 +5412,16 @@
         <v>44110</v>
       </c>
       <c r="B250" t="n">
-        <v>8.497404098510742</v>
+        <v>8.497405052185059</v>
       </c>
       <c r="C250" t="n">
-        <v>8.520973632751547</v>
+        <v>8.520974589071102</v>
       </c>
       <c r="D250" t="n">
-        <v>8.3162921520784</v>
+        <v>8.316293085426295</v>
       </c>
       <c r="E250" t="n">
-        <v>8.48872053887138</v>
+        <v>8.488721491571129</v>
       </c>
       <c r="F250" t="n">
         <v>10544549</v>
@@ -5432,16 +5432,16 @@
         <v>44111</v>
       </c>
       <c r="B251" t="n">
-        <v>8.585479736328125</v>
+        <v>8.585480690002441</v>
       </c>
       <c r="C251" t="n">
-        <v>8.704567531971968</v>
+        <v>8.704568498874545</v>
       </c>
       <c r="D251" t="n">
-        <v>8.440342155483876</v>
+        <v>8.440343093036322</v>
       </c>
       <c r="E251" t="n">
-        <v>8.477556644891454</v>
+        <v>8.477557586577683</v>
       </c>
       <c r="F251" t="n">
         <v>12680345</v>
@@ -5552,16 +5552,16 @@
         <v>44120</v>
       </c>
       <c r="B257" t="n">
-        <v>8.259230613708496</v>
+        <v>8.25922966003418</v>
       </c>
       <c r="C257" t="n">
-        <v>8.267913281163274</v>
+        <v>8.267912326486389</v>
       </c>
       <c r="D257" t="n">
-        <v>8.097965120577188</v>
+        <v>8.097964185523827</v>
       </c>
       <c r="E257" t="n">
-        <v>8.122775677538673</v>
+        <v>8.122774739620494</v>
       </c>
       <c r="F257" t="n">
         <v>10726560</v>
@@ -5612,16 +5612,16 @@
         <v>44125</v>
       </c>
       <c r="B260" t="n">
-        <v>8.275356292724609</v>
+        <v>8.275355339050293</v>
       </c>
       <c r="C260" t="n">
-        <v>8.355988588431988</v>
+        <v>8.355987625465389</v>
       </c>
       <c r="D260" t="n">
-        <v>8.245584340664582</v>
+        <v>8.245583390421267</v>
       </c>
       <c r="E260" t="n">
-        <v>8.35474846270546</v>
+        <v>8.354747499881778</v>
       </c>
       <c r="F260" t="n">
         <v>4665068</v>
@@ -5632,16 +5632,16 @@
         <v>44126</v>
       </c>
       <c r="B261" t="n">
-        <v>8.267912864685059</v>
+        <v>8.267911911010742</v>
       </c>
       <c r="C261" t="n">
-        <v>8.337381348523031</v>
+        <v>8.337380386835774</v>
       </c>
       <c r="D261" t="n">
-        <v>8.168674215687588</v>
+        <v>8.168673273460097</v>
       </c>
       <c r="E261" t="n">
-        <v>8.306368377248981</v>
+        <v>8.30636741913896</v>
       </c>
       <c r="F261" t="n">
         <v>7908034</v>
@@ -5652,16 +5652,16 @@
         <v>44127</v>
       </c>
       <c r="B262" t="n">
-        <v>8.234420776367188</v>
+        <v>8.234419822692871</v>
       </c>
       <c r="C262" t="n">
-        <v>8.312571929509362</v>
+        <v>8.312570966783923</v>
       </c>
       <c r="D262" t="n">
-        <v>8.203407804185662</v>
+        <v>8.203406854103131</v>
       </c>
       <c r="E262" t="n">
-        <v>8.269153232377807</v>
+        <v>8.269152274680931</v>
       </c>
       <c r="F262" t="n">
         <v>5098571</v>
@@ -5712,16 +5712,16 @@
         <v>44132</v>
       </c>
       <c r="B265" t="n">
-        <v>7.825055122375488</v>
+        <v>7.825055599212646</v>
       </c>
       <c r="C265" t="n">
-        <v>8.088040380288025</v>
+        <v>8.088040873150774</v>
       </c>
       <c r="D265" t="n">
-        <v>7.81761168821794</v>
+        <v>7.817612164601516</v>
       </c>
       <c r="E265" t="n">
-        <v>8.078115801411293</v>
+        <v>8.078116293669268</v>
       </c>
       <c r="F265" t="n">
         <v>12369944</v>
@@ -5752,16 +5752,16 @@
         <v>44134</v>
       </c>
       <c r="B267" t="n">
-        <v>7.684879302978516</v>
+        <v>7.684878826141357</v>
       </c>
       <c r="C267" t="n">
-        <v>7.777916426914608</v>
+        <v>7.777915944304612</v>
       </c>
       <c r="D267" t="n">
-        <v>7.574475058635726</v>
+        <v>7.574474588649013</v>
       </c>
       <c r="E267" t="n">
-        <v>7.759309180819852</v>
+        <v>7.759308699364413</v>
       </c>
       <c r="F267" t="n">
         <v>16269207</v>
@@ -5772,16 +5772,16 @@
         <v>44138</v>
       </c>
       <c r="B268" t="n">
-        <v>7.7171311378479</v>
+        <v>7.717131614685059</v>
       </c>
       <c r="C268" t="n">
-        <v>7.852345930671059</v>
+        <v>7.852346415863062</v>
       </c>
       <c r="D268" t="n">
-        <v>7.622853892715106</v>
+        <v>7.622854363726927</v>
       </c>
       <c r="E268" t="n">
-        <v>7.821333855323877</v>
+        <v>7.821334338599661</v>
       </c>
       <c r="F268" t="n">
         <v>9901091</v>
@@ -5812,16 +5812,16 @@
         <v>44140</v>
       </c>
       <c r="B270" t="n">
-        <v>8.119052886962891</v>
+        <v>8.119053840637207</v>
       </c>
       <c r="C270" t="n">
-        <v>8.177355763964984</v>
+        <v>8.177356724487632</v>
       </c>
       <c r="D270" t="n">
-        <v>8.007407635190189</v>
+        <v>8.007408575750512</v>
       </c>
       <c r="E270" t="n">
-        <v>8.039660727779241</v>
+        <v>8.039661672128053</v>
       </c>
       <c r="F270" t="n">
         <v>9820281</v>
@@ -5892,16 +5892,16 @@
         <v>44146</v>
       </c>
       <c r="B274" t="n">
-        <v>8.193482398986816</v>
+        <v>8.193483352661133</v>
       </c>
       <c r="C274" t="n">
-        <v>8.420493294041393</v>
+        <v>8.420494274138473</v>
       </c>
       <c r="D274" t="n">
-        <v>8.193482398986816</v>
+        <v>8.193483352661133</v>
       </c>
       <c r="E274" t="n">
-        <v>8.312571092276054</v>
+        <v>8.312572059811611</v>
       </c>
       <c r="F274" t="n">
         <v>7246451</v>
@@ -5912,16 +5912,16 @@
         <v>44147</v>
       </c>
       <c r="B275" t="n">
-        <v>8.234420776367188</v>
+        <v>8.234419822692871</v>
       </c>
       <c r="C275" t="n">
-        <v>8.398165624159189</v>
+        <v>8.398164651520666</v>
       </c>
       <c r="D275" t="n">
-        <v>8.13145906678732</v>
+        <v>8.131458125037573</v>
       </c>
       <c r="E275" t="n">
-        <v>8.193483224225638</v>
+        <v>8.193482275292528</v>
       </c>
       <c r="F275" t="n">
         <v>11697033</v>
@@ -5932,16 +5932,16 @@
         <v>44148</v>
       </c>
       <c r="B276" t="n">
-        <v>8.633859634399414</v>
+        <v>8.633858680725098</v>
       </c>
       <c r="C276" t="n">
-        <v>8.646265358676397</v>
+        <v>8.646264403631776</v>
       </c>
       <c r="D276" t="n">
-        <v>8.267912658055211</v>
+        <v>8.267911744802472</v>
       </c>
       <c r="E276" t="n">
-        <v>8.322494271024663</v>
+        <v>8.322493351742979</v>
       </c>
       <c r="F276" t="n">
         <v>10854949</v>
@@ -5992,16 +5992,16 @@
         <v>44153</v>
       </c>
       <c r="B279" t="n">
-        <v>8.584240913391113</v>
+        <v>8.584239959716797</v>
       </c>
       <c r="C279" t="n">
-        <v>8.645024946032365</v>
+        <v>8.64502398560519</v>
       </c>
       <c r="D279" t="n">
-        <v>8.516013445661457</v>
+        <v>8.516012499566937</v>
       </c>
       <c r="E279" t="n">
-        <v>8.558190230775271</v>
+        <v>8.55818927999508</v>
       </c>
       <c r="F279" t="n">
         <v>8922310</v>
@@ -6072,16 +6072,16 @@
         <v>44160</v>
       </c>
       <c r="B283" t="n">
-        <v>8.739302635192871</v>
+        <v>8.739301681518555</v>
       </c>
       <c r="C283" t="n">
-        <v>8.920414597775554</v>
+        <v>8.920413624337439</v>
       </c>
       <c r="D283" t="n">
-        <v>8.616492663682914</v>
+        <v>8.616491723410208</v>
       </c>
       <c r="E283" t="n">
-        <v>8.85466827854489</v>
+        <v>8.854667312281327</v>
       </c>
       <c r="F283" t="n">
         <v>6633202</v>
@@ -6112,16 +6112,16 @@
         <v>44162</v>
       </c>
       <c r="B285" t="n">
-        <v>8.615252494812012</v>
+        <v>8.615251541137695</v>
       </c>
       <c r="C285" t="n">
-        <v>8.708288727073548</v>
+        <v>8.70828776310049</v>
       </c>
       <c r="D285" t="n">
-        <v>8.507329393233835</v>
+        <v>8.507328451506179</v>
       </c>
       <c r="E285" t="n">
-        <v>8.566872403188754</v>
+        <v>8.566871454869922</v>
       </c>
       <c r="F285" t="n">
         <v>5230736</v>
@@ -6152,16 +6152,16 @@
         <v>44166</v>
       </c>
       <c r="B287" t="n">
-        <v>8.414292335510254</v>
+        <v>8.414291381835938</v>
       </c>
       <c r="C287" t="n">
-        <v>8.672315323428652</v>
+        <v>8.672314340510058</v>
       </c>
       <c r="D287" t="n">
-        <v>8.360949953683695</v>
+        <v>8.360949006055193</v>
       </c>
       <c r="E287" t="n">
-        <v>8.636340955945199</v>
+        <v>8.636339977103933</v>
       </c>
       <c r="F287" t="n">
         <v>16096259</v>
@@ -6172,16 +6172,16 @@
         <v>44167</v>
       </c>
       <c r="B288" t="n">
-        <v>8.282798767089844</v>
+        <v>8.282797813415527</v>
       </c>
       <c r="C288" t="n">
-        <v>8.4614304780068</v>
+        <v>8.461429503764982</v>
       </c>
       <c r="D288" t="n">
-        <v>8.199686220600897</v>
+        <v>8.199685276496087</v>
       </c>
       <c r="E288" t="n">
-        <v>8.456469081678438</v>
+        <v>8.456468108007872</v>
       </c>
       <c r="F288" t="n">
         <v>15329699</v>
@@ -6212,16 +6212,16 @@
         <v>44169</v>
       </c>
       <c r="B290" t="n">
-        <v>8.772794723510742</v>
+        <v>8.772793769836426</v>
       </c>
       <c r="C290" t="n">
-        <v>8.948945284925747</v>
+        <v>8.948944312102428</v>
       </c>
       <c r="D290" t="n">
-        <v>8.683479763850318</v>
+        <v>8.683478819885265</v>
       </c>
       <c r="E290" t="n">
-        <v>8.886920238013465</v>
+        <v>8.886919271932774</v>
       </c>
       <c r="F290" t="n">
         <v>10446369</v>
@@ -6232,16 +6232,16 @@
         <v>44172</v>
       </c>
       <c r="B291" t="n">
-        <v>8.647504806518555</v>
+        <v>8.647505760192871</v>
       </c>
       <c r="C291" t="n">
-        <v>8.827376626156168</v>
+        <v>8.82737759966732</v>
       </c>
       <c r="D291" t="n">
-        <v>8.621454127772409</v>
+        <v>8.621455078573774</v>
       </c>
       <c r="E291" t="n">
-        <v>8.807528362331166</v>
+        <v>8.807529333653388</v>
       </c>
       <c r="F291" t="n">
         <v>10174485</v>
@@ -6392,16 +6392,16 @@
         <v>44182</v>
       </c>
       <c r="B299" t="n">
-        <v>9.125097274780273</v>
+        <v>9.125096321105957</v>
       </c>
       <c r="C299" t="n">
-        <v>9.233020380265208</v>
+        <v>9.233019415311725</v>
       </c>
       <c r="D299" t="n">
-        <v>9.105249008435251</v>
+        <v>9.1052480568353</v>
       </c>
       <c r="E299" t="n">
-        <v>9.230539235289285</v>
+        <v>9.230538270595108</v>
       </c>
       <c r="F299" t="n">
         <v>5262456</v>
@@ -6452,16 +6452,16 @@
         <v>44187</v>
       </c>
       <c r="B302" t="n">
-        <v>9.018414497375488</v>
+        <v>9.018413543701172</v>
       </c>
       <c r="C302" t="n">
-        <v>9.117654044402261</v>
+        <v>9.117653080233614</v>
       </c>
       <c r="D302" t="n">
-        <v>8.941504362170608</v>
+        <v>8.941503416629342</v>
       </c>
       <c r="E302" t="n">
-        <v>8.974996692978687</v>
+        <v>8.974995743895692</v>
       </c>
       <c r="F302" t="n">
         <v>3700636</v>
@@ -6572,16 +6572,16 @@
         <v>44201</v>
       </c>
       <c r="B308" t="n">
-        <v>9.097805976867676</v>
+        <v>9.097805023193359</v>
       </c>
       <c r="C308" t="n">
-        <v>9.304968615993069</v>
+        <v>9.304967640603</v>
       </c>
       <c r="D308" t="n">
-        <v>9.012211393852336</v>
+        <v>9.012210449150441</v>
       </c>
       <c r="E308" t="n">
-        <v>9.304968615993069</v>
+        <v>9.304967640603</v>
       </c>
       <c r="F308" t="n">
         <v>8306796</v>
@@ -6592,16 +6592,16 @@
         <v>44202</v>
       </c>
       <c r="B309" t="n">
-        <v>9.023375511169434</v>
+        <v>9.02337646484375</v>
       </c>
       <c r="C309" t="n">
-        <v>9.178437672356514</v>
+        <v>9.178438642419241</v>
       </c>
       <c r="D309" t="n">
-        <v>8.883199324604012</v>
+        <v>8.883200263463204</v>
       </c>
       <c r="E309" t="n">
-        <v>9.091602075844966</v>
+        <v>9.091603036730099</v>
       </c>
       <c r="F309" t="n">
         <v>6995714</v>
@@ -6632,16 +6632,16 @@
         <v>44204</v>
       </c>
       <c r="B311" t="n">
-        <v>9.49476432800293</v>
+        <v>9.494765281677246</v>
       </c>
       <c r="C311" t="n">
-        <v>9.533219836566508</v>
+        <v>9.533220794103377</v>
       </c>
       <c r="D311" t="n">
-        <v>9.077957042182957</v>
+        <v>9.077957953992263</v>
       </c>
       <c r="E311" t="n">
-        <v>9.178437593380119</v>
+        <v>9.178438515281906</v>
       </c>
       <c r="F311" t="n">
         <v>10280973</v>
@@ -6732,16 +6732,16 @@
         <v>44211</v>
       </c>
       <c r="B316" t="n">
-        <v>9.479877471923828</v>
+        <v>9.479878425598145</v>
       </c>
       <c r="C316" t="n">
-        <v>9.607648827608905</v>
+        <v>9.607649794137002</v>
       </c>
       <c r="D316" t="n">
-        <v>9.378157688462947</v>
+        <v>9.378158631904267</v>
       </c>
       <c r="E316" t="n">
-        <v>9.589041582834192</v>
+        <v>9.589042547490402</v>
       </c>
       <c r="F316" t="n">
         <v>14334303</v>
@@ -6892,16 +6892,16 @@
         <v>44224</v>
       </c>
       <c r="B324" t="n">
-        <v>9.368233680725098</v>
+        <v>9.368232727050781</v>
       </c>
       <c r="C324" t="n">
-        <v>9.399245757239534</v>
+        <v>9.399244800408228</v>
       </c>
       <c r="D324" t="n">
-        <v>9.102767267989694</v>
+        <v>9.102766341339521</v>
       </c>
       <c r="E324" t="n">
-        <v>9.180918415575915</v>
+        <v>9.180917480970056</v>
       </c>
       <c r="F324" t="n">
         <v>7429217</v>
@@ -6912,16 +6912,16 @@
         <v>44225</v>
       </c>
       <c r="B325" t="n">
-        <v>9.36327075958252</v>
+        <v>9.363271713256836</v>
       </c>
       <c r="C325" t="n">
-        <v>9.571675294860224</v>
+        <v>9.571676269761104</v>
       </c>
       <c r="D325" t="n">
-        <v>9.215652034482874</v>
+        <v>9.215652973121827</v>
       </c>
       <c r="E325" t="n">
-        <v>9.312410421451789</v>
+        <v>9.312411369945844</v>
       </c>
       <c r="F325" t="n">
         <v>11022611</v>
@@ -6952,16 +6952,16 @@
         <v>44229</v>
       </c>
       <c r="B327" t="n">
-        <v>10.133620262146</v>
+        <v>10.13361930847168</v>
       </c>
       <c r="C327" t="n">
-        <v>10.18448060527895</v>
+        <v>10.18447964681817</v>
       </c>
       <c r="D327" t="n">
-        <v>9.832180367414875</v>
+        <v>9.832179442109044</v>
       </c>
       <c r="E327" t="n">
-        <v>10.11005072588166</v>
+        <v>10.11004977442547</v>
       </c>
       <c r="F327" t="n">
         <v>20046878</v>
@@ -6992,16 +6992,16 @@
         <v>44231</v>
       </c>
       <c r="B329" t="n">
-        <v>10.38668155670166</v>
+        <v>10.38668251037598</v>
       </c>
       <c r="C329" t="n">
-        <v>10.38668155670166</v>
+        <v>10.38668251037598</v>
       </c>
       <c r="D329" t="n">
-        <v>10.11749300250636</v>
+        <v>10.11749393146458</v>
       </c>
       <c r="E329" t="n">
-        <v>10.17703779267104</v>
+        <v>10.17703872709649</v>
       </c>
       <c r="F329" t="n">
         <v>12166787</v>
@@ -7012,16 +7012,16 @@
         <v>44232</v>
       </c>
       <c r="B330" t="n">
-        <v>10.5566291809082</v>
+        <v>10.55663013458252</v>
       </c>
       <c r="C330" t="n">
-        <v>10.58143973441847</v>
+        <v>10.58144069033415</v>
       </c>
       <c r="D330" t="n">
-        <v>10.32465689384235</v>
+        <v>10.32465782656054</v>
       </c>
       <c r="E330" t="n">
-        <v>10.41893413810214</v>
+        <v>10.41893507933724</v>
       </c>
       <c r="F330" t="n">
         <v>10745440</v>
@@ -7192,16 +7192,16 @@
         <v>44249</v>
       </c>
       <c r="B339" t="n">
-        <v>11.09376621246338</v>
+        <v>11.09376525878906</v>
       </c>
       <c r="C339" t="n">
-        <v>11.20292944052197</v>
+        <v>11.20292847746345</v>
       </c>
       <c r="D339" t="n">
-        <v>10.63602222835513</v>
+        <v>10.63602131403072</v>
       </c>
       <c r="E339" t="n">
-        <v>10.93994416306512</v>
+        <v>10.9399432226141</v>
       </c>
       <c r="F339" t="n">
         <v>14982292</v>
@@ -7292,16 +7292,16 @@
         <v>44256</v>
       </c>
       <c r="B344" t="n">
-        <v>21.85701560974121</v>
+        <v>21.85701751708984</v>
       </c>
       <c r="C344" t="n">
-        <v>23.99306407785948</v>
+        <v>23.99306617161</v>
       </c>
       <c r="D344" t="n">
-        <v>16.3107860983666</v>
+        <v>16.31078752172449</v>
       </c>
       <c r="E344" t="n">
-        <v>16.8635354591482</v>
+        <v>16.86353693074166</v>
       </c>
       <c r="F344" t="n">
         <v>49361500</v>
@@ -7312,16 +7312,16 @@
         <v>44257</v>
       </c>
       <c r="B345" t="n">
-        <v>21.19184303283691</v>
+        <v>21.19184494018555</v>
       </c>
       <c r="C345" t="n">
-        <v>22.95314478521037</v>
+        <v>22.95314685108304</v>
       </c>
       <c r="D345" t="n">
-        <v>20.6953049717416</v>
+        <v>20.69530683439987</v>
       </c>
       <c r="E345" t="n">
-        <v>22.18491736810308</v>
+        <v>22.18491936483229</v>
       </c>
       <c r="F345" t="n">
         <v>20095700</v>
@@ -7352,16 +7352,16 @@
         <v>44259</v>
       </c>
       <c r="B347" t="n">
-        <v>20.86394119262695</v>
+        <v>20.86394309997559</v>
       </c>
       <c r="C347" t="n">
-        <v>21.52911312081577</v>
+        <v>21.52911508897337</v>
       </c>
       <c r="D347" t="n">
-        <v>20.01139593391831</v>
+        <v>20.0113977633286</v>
       </c>
       <c r="E347" t="n">
-        <v>20.2362428583874</v>
+        <v>20.23624470835284</v>
       </c>
       <c r="F347" t="n">
         <v>8984600</v>
@@ -7732,16 +7732,16 @@
         <v>44286</v>
       </c>
       <c r="B366" t="n">
-        <v>31.08511924743652</v>
+        <v>31.08511734008789</v>
       </c>
       <c r="C366" t="n">
-        <v>32.65904960734591</v>
+        <v>32.65904760342265</v>
       </c>
       <c r="D366" t="n">
-        <v>30.82279871206804</v>
+        <v>30.82279682081511</v>
       </c>
       <c r="E366" t="n">
-        <v>31.95640225288098</v>
+        <v>31.95640029207138</v>
       </c>
       <c r="F366" t="n">
         <v>8195900</v>
@@ -7792,16 +7792,16 @@
         <v>44292</v>
       </c>
       <c r="B369" t="n">
-        <v>30.57921028137207</v>
+        <v>30.5792121887207</v>
       </c>
       <c r="C369" t="n">
-        <v>32.19998297677536</v>
+        <v>32.19998498521812</v>
       </c>
       <c r="D369" t="n">
-        <v>30.48552540315069</v>
+        <v>30.48552730465581</v>
       </c>
       <c r="E369" t="n">
-        <v>31.01953707148042</v>
+        <v>31.01953900629401</v>
       </c>
       <c r="F369" t="n">
         <v>6923500</v>
@@ -7812,16 +7812,16 @@
         <v>44293</v>
       </c>
       <c r="B370" t="n">
-        <v>30.95395851135254</v>
+        <v>30.95395660400391</v>
       </c>
       <c r="C370" t="n">
-        <v>31.36617699981515</v>
+        <v>31.36617506706607</v>
       </c>
       <c r="D370" t="n">
-        <v>30.40120912458377</v>
+        <v>30.40120725129495</v>
       </c>
       <c r="E370" t="n">
-        <v>30.72910978883253</v>
+        <v>30.72910789533883</v>
       </c>
       <c r="F370" t="n">
         <v>4745700</v>
@@ -8012,16 +8012,16 @@
         <v>44308</v>
       </c>
       <c r="B380" t="n">
-        <v>36.30344772338867</v>
+        <v>36.30344390869141</v>
       </c>
       <c r="C380" t="n">
-        <v>38.03664315290104</v>
+        <v>38.03663915608288</v>
       </c>
       <c r="D380" t="n">
-        <v>35.88185858344396</v>
+        <v>35.88185481304648</v>
       </c>
       <c r="E380" t="n">
-        <v>37.12788831107506</v>
+        <v>37.12788440974715</v>
       </c>
       <c r="F380" t="n">
         <v>6756200</v>
@@ -8052,16 +8052,16 @@
         <v>44312</v>
       </c>
       <c r="B382" t="n">
-        <v>35.91933059692383</v>
+        <v>35.91933441162109</v>
       </c>
       <c r="C382" t="n">
-        <v>36.30344431641451</v>
+        <v>36.30344817190534</v>
       </c>
       <c r="D382" t="n">
-        <v>35.5164791869886</v>
+        <v>35.51648295890232</v>
       </c>
       <c r="E382" t="n">
-        <v>35.88185521603473</v>
+        <v>35.88185902675205</v>
       </c>
       <c r="F382" t="n">
         <v>4241900</v>
@@ -8072,16 +8072,16 @@
         <v>44313</v>
       </c>
       <c r="B383" t="n">
-        <v>35.46963882446289</v>
+        <v>35.46963500976562</v>
       </c>
       <c r="C383" t="n">
-        <v>36.29407938304689</v>
+        <v>36.2940754796825</v>
       </c>
       <c r="D383" t="n">
-        <v>35.27289842405</v>
+        <v>35.27289463051181</v>
       </c>
       <c r="E383" t="n">
-        <v>36.05986359955081</v>
+        <v>36.05985972137591</v>
       </c>
       <c r="F383" t="n">
         <v>2386900</v>
@@ -35175,16 +35175,36 @@
         <v>3</v>
       </c>
       <c r="C1738" t="n">
-        <v>3.01</v>
+        <v>3.009999990463257</v>
       </c>
       <c r="D1738" t="n">
-        <v>2.84</v>
+        <v>2.839999914169312</v>
       </c>
       <c r="E1738" t="n">
-        <v>2.93</v>
+        <v>2.930000066757202</v>
       </c>
       <c r="F1738" t="n">
         <v>3587200</v>
+      </c>
+    </row>
+    <row r="1739">
+      <c r="A1739" s="1" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B1739" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="C1739" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="D1739" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="E1739" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="F1739" t="n">
+        <v>9735700</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1739"/>
+  <dimension ref="A1:F1740"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906440734863</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906440734863</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906440734863</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906440734863</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799173712730408</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799173712730408</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799173712730408</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799173712730408</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125653028488159</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125653028488159</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125653028488159</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125653028488159</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="C39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="D39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="E39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212013244629</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951084613800049</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294834613800049</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294834613800049</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294834613800049</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294834613800049</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780762</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587933540344238</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587933540344238</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587933540344238</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587933540344238</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543548583984</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543548583984</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543548583984</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543548583984</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.075628280639648</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.075628280639648</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.075628280639648</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.075628280639648</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="C57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="D57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="E57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589141368865967</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589141368865967</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589141368865967</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589141368865967</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="C64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="D64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="E64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610008239746</v>
+        <v>10.60610103607178</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448353456507</v>
+        <v>11.08448453125444</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087006568908691</v>
+        <v>8.087005615234375</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167515198324406</v>
+        <v>8.167514235155968</v>
       </c>
       <c r="D103" t="n">
-        <v>7.93415690090921</v>
+        <v>7.934155965259957</v>
       </c>
       <c r="E103" t="n">
-        <v>7.992496475263009</v>
+        <v>7.99249553273396</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174577261989849</v>
+        <v>7.174576363958773</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269087350174872</v>
+        <v>7.269086440314109</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151755156881</v>
+        <v>7.885151270575596</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395101374897398</v>
+        <v>7.395100920432114</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642459392547607</v>
+        <v>7.642458915710449</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934156405738198</v>
+        <v>7.934155910701143</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650690051923714</v>
+        <v>6.650689636966175</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251668627103</v>
+        <v>7.242251216760168</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255535125732</v>
+        <v>7.277255058288574</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292731402749</v>
+        <v>7.641292230712304</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086141684674</v>
+        <v>6.70086097777741</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766202137520195</v>
+        <v>6.766201694169458</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2652,16 +2652,16 @@
         <v>43909</v>
       </c>
       <c r="B112" t="n">
-        <v>7.521113872528076</v>
+        <v>7.521113395690918</v>
       </c>
       <c r="C112" t="n">
-        <v>8.106842473362253</v>
+        <v>8.106841959390016</v>
       </c>
       <c r="D112" t="n">
-        <v>6.35665992385914</v>
+        <v>6.356659520848136</v>
       </c>
       <c r="E112" t="n">
-        <v>6.779037133753115</v>
+        <v>6.779036703963478</v>
       </c>
       <c r="F112" t="n">
         <v>19250108</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314575195312</v>
+        <v>7.844314098358154</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109175099531829</v>
+        <v>8.109174606594431</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235251340767977</v>
+        <v>7.235250900954319</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146673416115</v>
+        <v>7.829146197500977</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738136291503906</v>
+        <v>7.738137245178223</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145345142681279</v>
+        <v>8.145346146541403</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298031292473</v>
+        <v>7.690298979071039</v>
       </c>
       <c r="E117" t="n">
-        <v>8.138343991239532</v>
+        <v>8.13834499423681</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469774723052979</v>
+        <v>7.469775676727295</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746303815364229</v>
+        <v>7.746304804343318</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351929151295045</v>
+        <v>7.351930089923889</v>
       </c>
       <c r="E118" t="n">
-        <v>7.51411282735269</v>
+        <v>7.514113786687701</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2792,16 +2792,16 @@
         <v>43920</v>
       </c>
       <c r="B119" t="n">
-        <v>7.58411979675293</v>
+        <v>7.584119319915771</v>
       </c>
       <c r="C119" t="n">
-        <v>7.677463445734158</v>
+        <v>7.677462963028194</v>
       </c>
       <c r="D119" t="n">
-        <v>7.322760268800774</v>
+        <v>7.322759808396101</v>
       </c>
       <c r="E119" t="n">
-        <v>7.354263351154514</v>
+        <v>7.354262888769144</v>
       </c>
       <c r="F119" t="n">
         <v>7283457</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469932556152</v>
+        <v>7.740469455718994</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757972392701939</v>
+        <v>7.757971914786575</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582952976226807</v>
+        <v>7.582953929901123</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840814016199421</v>
+        <v>7.840815002303775</v>
       </c>
       <c r="D122" t="n">
-        <v>7.38109946741859</v>
+        <v>7.381100395706687</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455773374392843</v>
+        <v>7.455774312072345</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261936187744</v>
+        <v>7.340261459350586</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624921524582</v>
+        <v>7.622624426344595</v>
       </c>
       <c r="D123" t="n">
-        <v>7.215416044404066</v>
+        <v>7.21541557567713</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457642689852</v>
+        <v>7.621457147585694</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613289356231689</v>
+        <v>7.613289833068848</v>
       </c>
       <c r="C124" t="n">
-        <v>7.699631846045301</v>
+        <v>7.699632328290281</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497777503819842</v>
+        <v>7.497777973422238</v>
       </c>
       <c r="E124" t="n">
-        <v>7.58411915326</v>
+        <v>7.584119628270164</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672796726226807</v>
+        <v>7.672797679901123</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109174958611256</v>
+        <v>8.109175966524298</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661128980388104</v>
+        <v>7.661129932612202</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840814283200555</v>
+        <v>7.840815257758265</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798988342285</v>
+        <v>7.700798511505127</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307612995673</v>
+        <v>7.781307131173381</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430989778177</v>
+        <v>7.362430533892927</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629934591736</v>
+        <v>7.678629459127295</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500111103057861</v>
+        <v>7.500110626220703</v>
       </c>
       <c r="C129" t="n">
-        <v>7.75097100706328</v>
+        <v>7.750970514277116</v>
       </c>
       <c r="D129" t="n">
-        <v>7.45577383571197</v>
+        <v>7.455773361693658</v>
       </c>
       <c r="E129" t="n">
-        <v>7.494278070349739</v>
+        <v>7.49427759388343</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265121459961</v>
+        <v>7.375265598297119</v>
       </c>
       <c r="C130" t="n">
-        <v>7.49427797970812</v>
+        <v>7.494278464239883</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762039125325</v>
+        <v>7.343762513925697</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935482620931</v>
+        <v>7.407935961570344</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566618919372559</v>
+        <v>7.566619396209717</v>
       </c>
       <c r="C131" t="n">
-        <v>7.58878797268838</v>
+        <v>7.5887884509226</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234083960008746</v>
+        <v>7.234084415890043</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444105906916389</v>
+        <v>7.444106376032958</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3072,16 +3072,16 @@
         <v>43941</v>
       </c>
       <c r="B133" t="n">
-        <v>7.58411979675293</v>
+        <v>7.584119319915771</v>
       </c>
       <c r="C133" t="n">
-        <v>7.592288227421651</v>
+        <v>7.592287750070918</v>
       </c>
       <c r="D133" t="n">
-        <v>7.316925555412612</v>
+        <v>7.316925095374786</v>
       </c>
       <c r="E133" t="n">
-        <v>7.350763195420438</v>
+        <v>7.350762733255134</v>
       </c>
       <c r="F133" t="n">
         <v>10524157</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251523017883301</v>
+        <v>8.251522064208984</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431208332707222</v>
+        <v>8.431207358265677</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852481842041016</v>
+        <v>7.852482318878174</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764051870702</v>
+        <v>7.357764498666425</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484073638916</v>
+        <v>7.887484550476074</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826254468098</v>
+        <v>7.966826736101882</v>
       </c>
       <c r="D139" t="n">
-        <v>7.70079846781684</v>
+        <v>7.700798933367937</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980371125938</v>
+        <v>7.841980845212174</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726467609405518</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817412213003</v>
+        <v>7.882817898699254</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726467609405518</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311096399979</v>
+        <v>7.816311578781807</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -35192,19 +35192,39 @@
         <v>46295</v>
       </c>
       <c r="B1739" t="n">
-        <v>3.35</v>
+        <v>3.349999904632568</v>
       </c>
       <c r="C1739" t="n">
-        <v>3.35</v>
+        <v>3.349999904632568</v>
       </c>
       <c r="D1739" t="n">
-        <v>2.97</v>
+        <v>2.970000028610229</v>
       </c>
       <c r="E1739" t="n">
-        <v>3.03</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="F1739" t="n">
         <v>9735700</v>
+      </c>
+    </row>
+    <row r="1740">
+      <c r="A1740" s="1" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B1740" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="C1740" t="n">
+        <v>3.49</v>
+      </c>
+      <c r="D1740" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="E1740" t="n">
+        <v>3.33</v>
+      </c>
+      <c r="F1740" t="n">
+        <v>14350000</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1740"/>
+  <dimension ref="A1:F1741"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906440734863</v>
+        <v>1.553905963897705</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906440734863</v>
+        <v>1.553905963897705</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906440734863</v>
+        <v>1.553905963897705</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906440734863</v>
+        <v>1.553905963897705</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173712730408</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173712730408</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173712730408</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173712730408</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616731882095337</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616731882095337</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616731882095337</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616731882095337</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212728500366</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212728500366</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212728500366</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212728500366</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212728500366</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212728500366</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212728500366</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212728500366</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959037780762</v>
+        <v>3.926959753036499</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926959753036499</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926959753036499</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926959753036499</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587933540344238</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587933540344238</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587933540344238</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587933540344238</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075628280639648</v>
+        <v>7.075627326965332</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075628280639648</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075628280639648</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075628280639648</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589141368865967</v>
+        <v>7.589144706726074</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589141368865967</v>
+        <v>7.589144706726074</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589141368865967</v>
+        <v>7.589144706726074</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589141368865967</v>
+        <v>7.589144706726074</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988327026367188</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988327026367188</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988327026367188</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988327026367188</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="C64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="D64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="E64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27652168273926</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27652168273926</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27652168273926</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27652168273926</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -2032,16 +2032,16 @@
         <v>43809</v>
       </c>
       <c r="B81" t="n">
-        <v>10.37040996551514</v>
+        <v>10.37041091918945</v>
       </c>
       <c r="C81" t="n">
-        <v>10.37040996551514</v>
+        <v>10.37041091918945</v>
       </c>
       <c r="D81" t="n">
-        <v>9.685505554677158</v>
+        <v>9.685506445366912</v>
       </c>
       <c r="E81" t="n">
-        <v>9.685505554677158</v>
+        <v>9.685506445366912</v>
       </c>
       <c r="F81" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610103607178</v>
+        <v>10.60610008239746</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448453125444</v>
+        <v>11.08448353456507</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2412,16 +2412,16 @@
         <v>43893</v>
       </c>
       <c r="B100" t="n">
-        <v>8.707736968994141</v>
+        <v>8.707737922668457</v>
       </c>
       <c r="C100" t="n">
-        <v>8.750908637511316</v>
+        <v>8.750909595913809</v>
       </c>
       <c r="D100" t="n">
-        <v>8.496548582064067</v>
+        <v>8.496549512608961</v>
       </c>
       <c r="E100" t="n">
-        <v>8.692569067314889</v>
+        <v>8.692570019328013</v>
       </c>
       <c r="F100" t="n">
         <v>7099936</v>
@@ -2452,16 +2452,16 @@
         <v>43895</v>
       </c>
       <c r="B102" t="n">
-        <v>8.294693946838379</v>
+        <v>8.294694900512695</v>
       </c>
       <c r="C102" t="n">
-        <v>8.675067158673277</v>
+        <v>8.675068156080631</v>
       </c>
       <c r="D102" t="n">
-        <v>8.054335362649853</v>
+        <v>8.054336288689177</v>
       </c>
       <c r="E102" t="n">
-        <v>8.588723824522271</v>
+        <v>8.588724812002386</v>
       </c>
       <c r="F102" t="n">
         <v>11131364</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087005615234375</v>
+        <v>8.087006568908691</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167514235155968</v>
+        <v>8.167515198324406</v>
       </c>
       <c r="D103" t="n">
-        <v>7.934155965259957</v>
+        <v>7.93415690090921</v>
       </c>
       <c r="E103" t="n">
-        <v>7.99249553273396</v>
+        <v>7.992496475263009</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151270575596</v>
+        <v>7.885151755156881</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395100920432114</v>
+        <v>7.395101374897398</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198310852051</v>
+        <v>6.731198787689209</v>
       </c>
       <c r="C107" t="n">
-        <v>6.78487002388751</v>
+        <v>6.784870504526766</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975251402972</v>
+        <v>6.183975689474925</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242313978574833</v>
+        <v>6.242314420779493</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642458915710449</v>
+        <v>7.642459392547607</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934155910701143</v>
+        <v>7.934156405738198</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650689636966175</v>
+        <v>6.650690051923714</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251216760168</v>
+        <v>7.242251668627103</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775676727295</v>
+        <v>7.469775199890137</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304804343318</v>
+        <v>7.746304309853773</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351930089923889</v>
+        <v>7.351929620609467</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113786687701</v>
+        <v>7.514113307020195</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469455718994</v>
+        <v>7.740469932556152</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757971914786575</v>
+        <v>7.757972392701939</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2832,16 +2832,16 @@
         <v>43922</v>
       </c>
       <c r="B121" t="n">
-        <v>7.461607456207275</v>
+        <v>7.461606979370117</v>
       </c>
       <c r="C121" t="n">
-        <v>7.642459196363636</v>
+        <v>7.642458707969071</v>
       </c>
       <c r="D121" t="n">
-        <v>7.304091207587605</v>
+        <v>7.304090740816589</v>
       </c>
       <c r="E121" t="n">
-        <v>7.619123704826946</v>
+        <v>7.619123217923645</v>
       </c>
       <c r="F121" t="n">
         <v>10218288</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613289833068848</v>
+        <v>7.613290309906006</v>
       </c>
       <c r="C124" t="n">
-        <v>7.699632328290281</v>
+        <v>7.69963281053526</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497777973422238</v>
+        <v>7.497778443024633</v>
       </c>
       <c r="E124" t="n">
-        <v>7.584119628270164</v>
+        <v>7.584120103280328</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672797679901123</v>
+        <v>7.672796726226807</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109175966524298</v>
+        <v>8.109174958611256</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661129932612202</v>
+        <v>7.661128980388104</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840815257758265</v>
+        <v>7.840814283200555</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798511505127</v>
+        <v>7.700798988342285</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307131173381</v>
+        <v>7.781307612995673</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430533892927</v>
+        <v>7.362430989778177</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629459127295</v>
+        <v>7.678629934591736</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265598297119</v>
+        <v>7.375265121459961</v>
       </c>
       <c r="C130" t="n">
-        <v>7.494278464239883</v>
+        <v>7.49427797970812</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762513925697</v>
+        <v>7.343762039125325</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935961570344</v>
+        <v>7.407935482620931</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852482318878174</v>
+        <v>7.852481842041016</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764498666425</v>
+        <v>7.357764051870702</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484550476074</v>
+        <v>7.887484073638916</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826736101882</v>
+        <v>7.966826254468098</v>
       </c>
       <c r="D139" t="n">
-        <v>7.700798933367937</v>
+        <v>7.70079846781684</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980845212174</v>
+        <v>7.841980371125938</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726468563079834</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817898699254</v>
+        <v>7.882818385185504</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726468563079834</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311578781807</v>
+        <v>7.816312061163636</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -35212,19 +35212,39 @@
         <v>46296</v>
       </c>
       <c r="B1740" t="n">
-        <v>3.3</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="C1740" t="n">
-        <v>3.49</v>
+        <v>3.490000009536743</v>
       </c>
       <c r="D1740" t="n">
-        <v>3.21</v>
+        <v>3.210000038146973</v>
       </c>
       <c r="E1740" t="n">
-        <v>3.33</v>
+        <v>3.329999923706055</v>
       </c>
       <c r="F1740" t="n">
         <v>14350000</v>
+      </c>
+    </row>
+    <row r="1741">
+      <c r="A1741" s="1" t="n">
+        <v>46297</v>
+      </c>
+      <c r="B1741" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C1741" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D1741" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E1741" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F1741" t="n">
+        <v>10018100</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1741"/>
+  <dimension ref="A1:F1742"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553905963897705</v>
+        <v>1.553906440734863</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553905963897705</v>
+        <v>1.553906440734863</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553905963897705</v>
+        <v>1.553906440734863</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553905963897705</v>
+        <v>1.553906440734863</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616731882095337</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616731882095337</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616731882095337</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616731882095337</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.152358293533325</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.152358293533325</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.152358293533325</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.152358293533325</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.9224613904953</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.9224613904953</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.9224613904953</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.9224613904953</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212728500366</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959753036499</v>
+        <v>3.926958560943604</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959753036499</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959753036499</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959753036499</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587933540344238</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587933540344238</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587933540344238</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587933540344238</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="C57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="D57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="E57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589144706726074</v>
+        <v>7.5891432762146</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589144706726074</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589144706726074</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589144706726074</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257579803467</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257579803467</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257579803467</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257579803467</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27652168273926</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27652168273926</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27652168273926</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27652168273926</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -2032,16 +2032,16 @@
         <v>43809</v>
       </c>
       <c r="B81" t="n">
-        <v>10.37041091918945</v>
+        <v>10.37040996551514</v>
       </c>
       <c r="C81" t="n">
-        <v>10.37041091918945</v>
+        <v>10.37040996551514</v>
       </c>
       <c r="D81" t="n">
-        <v>9.685506445366912</v>
+        <v>9.685505554677158</v>
       </c>
       <c r="E81" t="n">
-        <v>9.685506445366912</v>
+        <v>9.685505554677158</v>
       </c>
       <c r="F81" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610008239746</v>
+        <v>10.60610103607178</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448353456507</v>
+        <v>11.08448453125444</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2412,16 +2412,16 @@
         <v>43893</v>
       </c>
       <c r="B100" t="n">
-        <v>8.707737922668457</v>
+        <v>8.707736968994141</v>
       </c>
       <c r="C100" t="n">
-        <v>8.750909595913809</v>
+        <v>8.750908637511316</v>
       </c>
       <c r="D100" t="n">
-        <v>8.496549512608961</v>
+        <v>8.496548582064067</v>
       </c>
       <c r="E100" t="n">
-        <v>8.692570019328013</v>
+        <v>8.692569067314889</v>
       </c>
       <c r="F100" t="n">
         <v>7099936</v>
@@ -2452,16 +2452,16 @@
         <v>43895</v>
       </c>
       <c r="B102" t="n">
-        <v>8.294694900512695</v>
+        <v>8.294693946838379</v>
       </c>
       <c r="C102" t="n">
-        <v>8.675068156080631</v>
+        <v>8.675067158673277</v>
       </c>
       <c r="D102" t="n">
-        <v>8.054336288689177</v>
+        <v>8.054335362649853</v>
       </c>
       <c r="E102" t="n">
-        <v>8.588724812002386</v>
+        <v>8.588723824522271</v>
       </c>
       <c r="F102" t="n">
         <v>11131364</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087006568908691</v>
+        <v>8.087005615234375</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167515198324406</v>
+        <v>8.167514235155968</v>
       </c>
       <c r="D103" t="n">
-        <v>7.93415690090921</v>
+        <v>7.934155965259957</v>
       </c>
       <c r="E103" t="n">
-        <v>7.992496475263009</v>
+        <v>7.99249553273396</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151755156881</v>
+        <v>7.885151270575596</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395101374897398</v>
+        <v>7.395100920432114</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198787689209</v>
+        <v>6.731198310852051</v>
       </c>
       <c r="C107" t="n">
-        <v>6.784870504526766</v>
+        <v>6.78487002388751</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975689474925</v>
+        <v>6.183975251402972</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242314420779493</v>
+        <v>6.242313978574833</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642459392547607</v>
+        <v>7.642458915710449</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934156405738198</v>
+        <v>7.934155910701143</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650690051923714</v>
+        <v>6.650689636966175</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251668627103</v>
+        <v>7.242251216760168</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775199890137</v>
+        <v>7.469775676727295</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304309853773</v>
+        <v>7.746304804343318</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351929620609467</v>
+        <v>7.351930089923889</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113307020195</v>
+        <v>7.514113786687701</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469932556152</v>
+        <v>7.740469455718994</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757972392701939</v>
+        <v>7.757971914786575</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2832,16 +2832,16 @@
         <v>43922</v>
       </c>
       <c r="B121" t="n">
-        <v>7.461606979370117</v>
+        <v>7.461607456207275</v>
       </c>
       <c r="C121" t="n">
-        <v>7.642458707969071</v>
+        <v>7.642459196363636</v>
       </c>
       <c r="D121" t="n">
-        <v>7.304090740816589</v>
+        <v>7.304091207587605</v>
       </c>
       <c r="E121" t="n">
-        <v>7.619123217923645</v>
+        <v>7.619123704826946</v>
       </c>
       <c r="F121" t="n">
         <v>10218288</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613290309906006</v>
+        <v>7.613289833068848</v>
       </c>
       <c r="C124" t="n">
-        <v>7.69963281053526</v>
+        <v>7.699632328290281</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497778443024633</v>
+        <v>7.497777973422238</v>
       </c>
       <c r="E124" t="n">
-        <v>7.584120103280328</v>
+        <v>7.584119628270164</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672796726226807</v>
+        <v>7.672797679901123</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109174958611256</v>
+        <v>8.109175966524298</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661128980388104</v>
+        <v>7.661129932612202</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840814283200555</v>
+        <v>7.840815257758265</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798988342285</v>
+        <v>7.700798511505127</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307612995673</v>
+        <v>7.781307131173381</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430989778177</v>
+        <v>7.362430533892927</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629934591736</v>
+        <v>7.678629459127295</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265121459961</v>
+        <v>7.375265598297119</v>
       </c>
       <c r="C130" t="n">
-        <v>7.49427797970812</v>
+        <v>7.494278464239883</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762039125325</v>
+        <v>7.343762513925697</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935482620931</v>
+        <v>7.407935961570344</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852481842041016</v>
+        <v>7.852482318878174</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764051870702</v>
+        <v>7.357764498666425</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484073638916</v>
+        <v>7.887484550476074</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826254468098</v>
+        <v>7.966826736101882</v>
       </c>
       <c r="D139" t="n">
-        <v>7.70079846781684</v>
+        <v>7.700798933367937</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980371125938</v>
+        <v>7.841980845212174</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726468563079834</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882818385185504</v>
+        <v>7.882817898699254</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726468563079834</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816312061163636</v>
+        <v>7.816311578781807</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -35232,19 +35232,39 @@
         <v>46297</v>
       </c>
       <c r="B1741" t="n">
-        <v>3.1</v>
+        <v>3.099999904632568</v>
       </c>
       <c r="C1741" t="n">
-        <v>3.3</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="D1741" t="n">
-        <v>3.1</v>
+        <v>3.099999904632568</v>
       </c>
       <c r="E1741" t="n">
-        <v>3.3</v>
+        <v>3.299999952316284</v>
       </c>
       <c r="F1741" t="n">
         <v>10018100</v>
+      </c>
+    </row>
+    <row r="1742">
+      <c r="A1742" s="1" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B1742" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="C1742" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="D1742" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="E1742" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="F1742" t="n">
+        <v>11343300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1742"/>
+  <dimension ref="A1:F1743"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906440734863</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906440734863</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906440734863</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906440734863</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799174427986145</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799174427986145</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799174427986145</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799174427986145</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132247924805</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C7" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D7" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E7" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C12" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D12" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E12" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C13" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D13" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E13" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C14" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D14" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E14" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C15" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D15" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E15" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C16" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D16" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E16" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C17" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D17" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E17" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C18" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D18" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E18" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C19" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D19" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E19" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C20" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D20" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E20" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C21" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D21" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E21" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C22" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D22" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E22" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C23" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D23" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E23" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C24" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D24" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E24" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C25" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D25" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E25" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C26" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D26" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E26" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C27" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D27" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E27" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C28" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D28" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E28" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C29" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D29" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E29" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C30" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D30" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E30" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C31" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D31" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E31" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C32" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D32" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E32" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C33" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D33" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E33" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C34" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D34" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E34" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C35" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D35" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E35" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152358293533325</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152358293533325</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152358293533325</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152358293533325</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.9224613904953</v>
+        <v>1.922460675239563</v>
       </c>
       <c r="C38" t="n">
-        <v>1.9224613904953</v>
+        <v>1.922460675239563</v>
       </c>
       <c r="D38" t="n">
-        <v>1.9224613904953</v>
+        <v>1.922460675239563</v>
       </c>
       <c r="E38" t="n">
-        <v>1.9224613904953</v>
+        <v>1.922460675239563</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997222900390625</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958560943604</v>
+        <v>3.926959037780762</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075627326965332</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.5891432762146</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257579803467</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257579803467</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257579803467</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257579803467</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="C64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="D64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="E64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610103607178</v>
+        <v>10.60610008239746</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448453125444</v>
+        <v>11.08448353456507</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087005615234375</v>
+        <v>8.087006568908691</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167514235155968</v>
+        <v>8.167515198324406</v>
       </c>
       <c r="D103" t="n">
-        <v>7.934155965259957</v>
+        <v>7.93415690090921</v>
       </c>
       <c r="E103" t="n">
-        <v>7.99249553273396</v>
+        <v>7.992496475263009</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174576363958773</v>
+        <v>7.174577261989849</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269086440314109</v>
+        <v>7.269087350174872</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151270575596</v>
+        <v>7.885151755156881</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395100920432114</v>
+        <v>7.395101374897398</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642458915710449</v>
+        <v>7.642459392547607</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934155910701143</v>
+        <v>7.934156405738198</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650689636966175</v>
+        <v>6.650690051923714</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251216760168</v>
+        <v>7.242251668627103</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255058288574</v>
+        <v>7.277255535125732</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292230712304</v>
+        <v>7.641292731402749</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086097777741</v>
+        <v>6.70086141684674</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766201694169458</v>
+        <v>6.766202137520195</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2652,16 +2652,16 @@
         <v>43909</v>
       </c>
       <c r="B112" t="n">
-        <v>7.521113395690918</v>
+        <v>7.521113872528076</v>
       </c>
       <c r="C112" t="n">
-        <v>8.106841959390016</v>
+        <v>8.106842473362253</v>
       </c>
       <c r="D112" t="n">
-        <v>6.356659520848136</v>
+        <v>6.35665992385914</v>
       </c>
       <c r="E112" t="n">
-        <v>6.779036703963478</v>
+        <v>6.779037133753115</v>
       </c>
       <c r="F112" t="n">
         <v>19250108</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314098358154</v>
+        <v>7.844314575195312</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109174606594431</v>
+        <v>8.109175099531829</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235250900954319</v>
+        <v>7.235251340767977</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146197500977</v>
+        <v>7.829146673416115</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738137245178223</v>
+        <v>7.738136291503906</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145346146541403</v>
+        <v>8.145345142681279</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298979071039</v>
+        <v>7.690298031292473</v>
       </c>
       <c r="E117" t="n">
-        <v>8.13834499423681</v>
+        <v>8.138343991239532</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775676727295</v>
+        <v>7.469774723052979</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304804343318</v>
+        <v>7.746303815364229</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351930089923889</v>
+        <v>7.351929151295045</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113786687701</v>
+        <v>7.51411282735269</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2792,16 +2792,16 @@
         <v>43920</v>
       </c>
       <c r="B119" t="n">
-        <v>7.584119319915771</v>
+        <v>7.58411979675293</v>
       </c>
       <c r="C119" t="n">
-        <v>7.677462963028194</v>
+        <v>7.677463445734158</v>
       </c>
       <c r="D119" t="n">
-        <v>7.322759808396101</v>
+        <v>7.322760268800774</v>
       </c>
       <c r="E119" t="n">
-        <v>7.354262888769144</v>
+        <v>7.354263351154514</v>
       </c>
       <c r="F119" t="n">
         <v>7283457</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469455718994</v>
+        <v>7.740469932556152</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757971914786575</v>
+        <v>7.757972392701939</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582953929901123</v>
+        <v>7.582952976226807</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840815002303775</v>
+        <v>7.840814016199421</v>
       </c>
       <c r="D122" t="n">
-        <v>7.381100395706687</v>
+        <v>7.38109946741859</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455774312072345</v>
+        <v>7.455773374392843</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261459350586</v>
+        <v>7.340261936187744</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624426344595</v>
+        <v>7.622624921524582</v>
       </c>
       <c r="D123" t="n">
-        <v>7.21541557567713</v>
+        <v>7.215416044404066</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457147585694</v>
+        <v>7.621457642689852</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613289833068848</v>
+        <v>7.613289356231689</v>
       </c>
       <c r="C124" t="n">
-        <v>7.699632328290281</v>
+        <v>7.699631846045301</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497777973422238</v>
+        <v>7.497777503819842</v>
       </c>
       <c r="E124" t="n">
-        <v>7.584119628270164</v>
+        <v>7.58411915326</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672797679901123</v>
+        <v>7.672796726226807</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109175966524298</v>
+        <v>8.109174958611256</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661129932612202</v>
+        <v>7.661128980388104</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840815257758265</v>
+        <v>7.840814283200555</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798511505127</v>
+        <v>7.700798988342285</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307131173381</v>
+        <v>7.781307612995673</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430533892927</v>
+        <v>7.362430989778177</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629459127295</v>
+        <v>7.678629934591736</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500110626220703</v>
+        <v>7.500111103057861</v>
       </c>
       <c r="C129" t="n">
-        <v>7.750970514277116</v>
+        <v>7.75097100706328</v>
       </c>
       <c r="D129" t="n">
-        <v>7.455773361693658</v>
+        <v>7.45577383571197</v>
       </c>
       <c r="E129" t="n">
-        <v>7.49427759388343</v>
+        <v>7.494278070349739</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265598297119</v>
+        <v>7.375265121459961</v>
       </c>
       <c r="C130" t="n">
-        <v>7.494278464239883</v>
+        <v>7.49427797970812</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762513925697</v>
+        <v>7.343762039125325</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935961570344</v>
+        <v>7.407935482620931</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566619396209717</v>
+        <v>7.566618919372559</v>
       </c>
       <c r="C131" t="n">
-        <v>7.5887884509226</v>
+        <v>7.58878797268838</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234084415890043</v>
+        <v>7.234083960008746</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444106376032958</v>
+        <v>7.444105906916389</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3072,16 +3072,16 @@
         <v>43941</v>
       </c>
       <c r="B133" t="n">
-        <v>7.584119319915771</v>
+        <v>7.58411979675293</v>
       </c>
       <c r="C133" t="n">
-        <v>7.592287750070918</v>
+        <v>7.592288227421651</v>
       </c>
       <c r="D133" t="n">
-        <v>7.316925095374786</v>
+        <v>7.316925555412612</v>
       </c>
       <c r="E133" t="n">
-        <v>7.350762733255134</v>
+        <v>7.350763195420438</v>
       </c>
       <c r="F133" t="n">
         <v>10524157</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251522064208984</v>
+        <v>8.251523017883301</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431207358265677</v>
+        <v>8.431208332707222</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852482318878174</v>
+        <v>7.852481842041016</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764498666425</v>
+        <v>7.357764051870702</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484550476074</v>
+        <v>7.887484073638916</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826736101882</v>
+        <v>7.966826254468098</v>
       </c>
       <c r="D139" t="n">
-        <v>7.700798933367937</v>
+        <v>7.70079846781684</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980845212174</v>
+        <v>7.841980371125938</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726467609405518</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817898699254</v>
+        <v>7.882817412213003</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726467609405518</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311578781807</v>
+        <v>7.816311096399979</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -35252,19 +35252,39 @@
         <v>46300</v>
       </c>
       <c r="B1742" t="n">
-        <v>3.28</v>
+        <v>3.279999971389771</v>
       </c>
       <c r="C1742" t="n">
-        <v>3.41</v>
+        <v>3.410000085830688</v>
       </c>
       <c r="D1742" t="n">
-        <v>3.16</v>
+        <v>3.160000085830688</v>
       </c>
       <c r="E1742" t="n">
-        <v>3.26</v>
+        <v>3.259999990463257</v>
       </c>
       <c r="F1742" t="n">
         <v>11343300</v>
+      </c>
+    </row>
+    <row r="1743">
+      <c r="A1743" s="1" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B1743" t="n">
+        <v>3.37</v>
+      </c>
+      <c r="C1743" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D1743" t="n">
+        <v>3.16</v>
+      </c>
+      <c r="E1743" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="F1743" t="n">
+        <v>9348400</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1743"/>
+  <dimension ref="A1:F1744"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799174427986145</v>
+        <v>1.799173593521118</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799174427986145</v>
+        <v>1.799173593521118</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799174427986145</v>
+        <v>1.799173593521118</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799174427986145</v>
+        <v>1.799173593521118</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132247924805</v>
+        <v>1.853132843971252</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="C9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="D9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="E9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="C10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="D10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="E10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922460675239563</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922460675239563</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922460675239563</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922460675239563</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959037780762</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.58793306350708</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.58793306350708</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.58793306350708</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.58793306350708</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075627326965332</v>
       </c>
       <c r="C55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="D55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="E55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.5891432762146</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27652168273926</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27652168273926</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27652168273926</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27652168273926</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -2032,16 +2032,16 @@
         <v>43809</v>
       </c>
       <c r="B81" t="n">
-        <v>10.37040996551514</v>
+        <v>10.37041091918945</v>
       </c>
       <c r="C81" t="n">
-        <v>10.37040996551514</v>
+        <v>10.37041091918945</v>
       </c>
       <c r="D81" t="n">
-        <v>9.685505554677158</v>
+        <v>9.685506445366912</v>
       </c>
       <c r="E81" t="n">
-        <v>9.685505554677158</v>
+        <v>9.685506445366912</v>
       </c>
       <c r="F81" t="n">
         <v>1510</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2412,16 +2412,16 @@
         <v>43893</v>
       </c>
       <c r="B100" t="n">
-        <v>8.707736968994141</v>
+        <v>8.707737922668457</v>
       </c>
       <c r="C100" t="n">
-        <v>8.750908637511316</v>
+        <v>8.750909595913809</v>
       </c>
       <c r="D100" t="n">
-        <v>8.496548582064067</v>
+        <v>8.496549512608961</v>
       </c>
       <c r="E100" t="n">
-        <v>8.692569067314889</v>
+        <v>8.692570019328013</v>
       </c>
       <c r="F100" t="n">
         <v>7099936</v>
@@ -2452,16 +2452,16 @@
         <v>43895</v>
       </c>
       <c r="B102" t="n">
-        <v>8.294693946838379</v>
+        <v>8.294694900512695</v>
       </c>
       <c r="C102" t="n">
-        <v>8.675067158673277</v>
+        <v>8.675068156080631</v>
       </c>
       <c r="D102" t="n">
-        <v>8.054335362649853</v>
+        <v>8.054336288689177</v>
       </c>
       <c r="E102" t="n">
-        <v>8.588723824522271</v>
+        <v>8.588724812002386</v>
       </c>
       <c r="F102" t="n">
         <v>11131364</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174577261989849</v>
+        <v>7.174576363958773</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269087350174872</v>
+        <v>7.269086440314109</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198310852051</v>
+        <v>6.731198787689209</v>
       </c>
       <c r="C107" t="n">
-        <v>6.78487002388751</v>
+        <v>6.784870504526766</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975251402972</v>
+        <v>6.183975689474925</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242313978574833</v>
+        <v>6.242314420779493</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255535125732</v>
+        <v>7.277255058288574</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292731402749</v>
+        <v>7.641292230712304</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086141684674</v>
+        <v>6.70086097777741</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766202137520195</v>
+        <v>6.766201694169458</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2652,16 +2652,16 @@
         <v>43909</v>
       </c>
       <c r="B112" t="n">
-        <v>7.521113872528076</v>
+        <v>7.521113395690918</v>
       </c>
       <c r="C112" t="n">
-        <v>8.106842473362253</v>
+        <v>8.106841959390016</v>
       </c>
       <c r="D112" t="n">
-        <v>6.35665992385914</v>
+        <v>6.356659520848136</v>
       </c>
       <c r="E112" t="n">
-        <v>6.779037133753115</v>
+        <v>6.779036703963478</v>
       </c>
       <c r="F112" t="n">
         <v>19250108</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314575195312</v>
+        <v>7.844314098358154</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109175099531829</v>
+        <v>8.109174606594431</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235251340767977</v>
+        <v>7.235250900954319</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146673416115</v>
+        <v>7.829146197500977</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738136291503906</v>
+        <v>7.738137245178223</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145345142681279</v>
+        <v>8.145346146541403</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298031292473</v>
+        <v>7.690298979071039</v>
       </c>
       <c r="E117" t="n">
-        <v>8.138343991239532</v>
+        <v>8.13834499423681</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469774723052979</v>
+        <v>7.469775199890137</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746303815364229</v>
+        <v>7.746304309853773</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351929151295045</v>
+        <v>7.351929620609467</v>
       </c>
       <c r="E118" t="n">
-        <v>7.51411282735269</v>
+        <v>7.514113307020195</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2792,16 +2792,16 @@
         <v>43920</v>
       </c>
       <c r="B119" t="n">
-        <v>7.58411979675293</v>
+        <v>7.584119319915771</v>
       </c>
       <c r="C119" t="n">
-        <v>7.677463445734158</v>
+        <v>7.677462963028194</v>
       </c>
       <c r="D119" t="n">
-        <v>7.322760268800774</v>
+        <v>7.322759808396101</v>
       </c>
       <c r="E119" t="n">
-        <v>7.354263351154514</v>
+        <v>7.354262888769144</v>
       </c>
       <c r="F119" t="n">
         <v>7283457</v>
@@ -2832,16 +2832,16 @@
         <v>43922</v>
       </c>
       <c r="B121" t="n">
-        <v>7.461607456207275</v>
+        <v>7.461606979370117</v>
       </c>
       <c r="C121" t="n">
-        <v>7.642459196363636</v>
+        <v>7.642458707969071</v>
       </c>
       <c r="D121" t="n">
-        <v>7.304091207587605</v>
+        <v>7.304090740816589</v>
       </c>
       <c r="E121" t="n">
-        <v>7.619123704826946</v>
+        <v>7.619123217923645</v>
       </c>
       <c r="F121" t="n">
         <v>10218288</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582952976226807</v>
+        <v>7.582953929901123</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840814016199421</v>
+        <v>7.840815002303775</v>
       </c>
       <c r="D122" t="n">
-        <v>7.38109946741859</v>
+        <v>7.381100395706687</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455773374392843</v>
+        <v>7.455774312072345</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261936187744</v>
+        <v>7.340261459350586</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624921524582</v>
+        <v>7.622624426344595</v>
       </c>
       <c r="D123" t="n">
-        <v>7.215416044404066</v>
+        <v>7.21541557567713</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457642689852</v>
+        <v>7.621457147585694</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613289356231689</v>
+        <v>7.613290309906006</v>
       </c>
       <c r="C124" t="n">
-        <v>7.699631846045301</v>
+        <v>7.69963281053526</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497777503819842</v>
+        <v>7.497778443024633</v>
       </c>
       <c r="E124" t="n">
-        <v>7.58411915326</v>
+        <v>7.584120103280328</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500111103057861</v>
+        <v>7.500110626220703</v>
       </c>
       <c r="C129" t="n">
-        <v>7.75097100706328</v>
+        <v>7.750970514277116</v>
       </c>
       <c r="D129" t="n">
-        <v>7.45577383571197</v>
+        <v>7.455773361693658</v>
       </c>
       <c r="E129" t="n">
-        <v>7.494278070349739</v>
+        <v>7.49427759388343</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566618919372559</v>
+        <v>7.566619396209717</v>
       </c>
       <c r="C131" t="n">
-        <v>7.58878797268838</v>
+        <v>7.5887884509226</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234083960008746</v>
+        <v>7.234084415890043</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444105906916389</v>
+        <v>7.444106376032958</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3072,16 +3072,16 @@
         <v>43941</v>
       </c>
       <c r="B133" t="n">
-        <v>7.58411979675293</v>
+        <v>7.584119319915771</v>
       </c>
       <c r="C133" t="n">
-        <v>7.592288227421651</v>
+        <v>7.592287750070918</v>
       </c>
       <c r="D133" t="n">
-        <v>7.316925555412612</v>
+        <v>7.316925095374786</v>
       </c>
       <c r="E133" t="n">
-        <v>7.350763195420438</v>
+        <v>7.350762733255134</v>
       </c>
       <c r="F133" t="n">
         <v>10524157</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251523017883301</v>
+        <v>8.251522064208984</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431208332707222</v>
+        <v>8.431207358265677</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726467609405518</v>
+        <v>7.726468563079834</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817412213003</v>
+        <v>7.882818385185504</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726467609405518</v>
+        <v>7.726468563079834</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311096399979</v>
+        <v>7.816312061163636</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -35272,19 +35272,39 @@
         <v>46301</v>
       </c>
       <c r="B1743" t="n">
-        <v>3.37</v>
+        <v>3.369999885559082</v>
       </c>
       <c r="C1743" t="n">
-        <v>3.45</v>
+        <v>3.440000057220459</v>
       </c>
       <c r="D1743" t="n">
-        <v>3.16</v>
+        <v>3.170000076293945</v>
       </c>
       <c r="E1743" t="n">
-        <v>3.28</v>
+        <v>3.279999971389771</v>
       </c>
       <c r="F1743" t="n">
         <v>9348400</v>
+      </c>
+    </row>
+    <row r="1744">
+      <c r="A1744" s="1" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B1744" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="C1744" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="D1744" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="E1744" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F1744" t="n">
+        <v>15985900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1744"/>
+  <dimension ref="A1:F1745"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553905844688416</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553905844688416</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553905844688416</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553905844688416</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173593521118</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173593521118</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173593521118</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173593521118</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211536407471</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211536407471</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211536407471</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211536407471</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211536407471</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211536407471</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211536407471</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211536407471</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997222900390625</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997221946716309</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.58793306350708</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="C49" t="n">
-        <v>4.58793306350708</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="D49" t="n">
-        <v>4.58793306350708</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="E49" t="n">
-        <v>4.58793306350708</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075627326965332</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="C57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="D57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="E57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.5891432762146</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988327026367188</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988327026367188</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988327026367188</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988327026367188</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="C64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="D64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="E64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -35292,19 +35292,39 @@
         <v>46302</v>
       </c>
       <c r="B1744" t="n">
-        <v>3.51</v>
+        <v>3.509999990463257</v>
       </c>
       <c r="C1744" t="n">
-        <v>3.85</v>
+        <v>3.849999904632568</v>
       </c>
       <c r="D1744" t="n">
-        <v>3.35</v>
+        <v>3.349999904632568</v>
       </c>
       <c r="E1744" t="n">
-        <v>3.4</v>
+        <v>3.400000095367432</v>
       </c>
       <c r="F1744" t="n">
         <v>15985900</v>
+      </c>
+    </row>
+    <row r="1745">
+      <c r="A1745" s="1" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B1745" t="n">
+        <v>3.42</v>
+      </c>
+      <c r="C1745" t="n">
+        <v>3.63</v>
+      </c>
+      <c r="D1745" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="E1745" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F1745" t="n">
+        <v>12761800</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1745"/>
+  <dimension ref="A1:F1746"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553905844688416</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553905844688416</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553905844688416</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553905844688416</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180155754089355</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838211536407471</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838211536407471</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838211536407471</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838211536407471</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838211536407471</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838211536407471</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838211536407471</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838211536407471</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647352695465088</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647352695465088</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647352695465088</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647352695465088</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800049</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="C55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="D55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="E55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27652168273926</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27652168273926</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27652168273926</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27652168273926</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -2032,16 +2032,16 @@
         <v>43809</v>
       </c>
       <c r="B81" t="n">
-        <v>10.37041091918945</v>
+        <v>10.37040996551514</v>
       </c>
       <c r="C81" t="n">
-        <v>10.37041091918945</v>
+        <v>10.37040996551514</v>
       </c>
       <c r="D81" t="n">
-        <v>9.685506445366912</v>
+        <v>9.685505554677158</v>
       </c>
       <c r="E81" t="n">
-        <v>9.685506445366912</v>
+        <v>9.685505554677158</v>
       </c>
       <c r="F81" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610008239746</v>
+        <v>10.60610103607178</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448353456507</v>
+        <v>11.08448453125444</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2412,16 +2412,16 @@
         <v>43893</v>
       </c>
       <c r="B100" t="n">
-        <v>8.707737922668457</v>
+        <v>8.707736968994141</v>
       </c>
       <c r="C100" t="n">
-        <v>8.750909595913809</v>
+        <v>8.750908637511316</v>
       </c>
       <c r="D100" t="n">
-        <v>8.496549512608961</v>
+        <v>8.496548582064067</v>
       </c>
       <c r="E100" t="n">
-        <v>8.692570019328013</v>
+        <v>8.692569067314889</v>
       </c>
       <c r="F100" t="n">
         <v>7099936</v>
@@ -2452,16 +2452,16 @@
         <v>43895</v>
       </c>
       <c r="B102" t="n">
-        <v>8.294694900512695</v>
+        <v>8.294693946838379</v>
       </c>
       <c r="C102" t="n">
-        <v>8.675068156080631</v>
+        <v>8.675067158673277</v>
       </c>
       <c r="D102" t="n">
-        <v>8.054336288689177</v>
+        <v>8.054335362649853</v>
       </c>
       <c r="E102" t="n">
-        <v>8.588724812002386</v>
+        <v>8.588723824522271</v>
       </c>
       <c r="F102" t="n">
         <v>11131364</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087006568908691</v>
+        <v>8.087005615234375</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167515198324406</v>
+        <v>8.167514235155968</v>
       </c>
       <c r="D103" t="n">
-        <v>7.93415690090921</v>
+        <v>7.934155965259957</v>
       </c>
       <c r="E103" t="n">
-        <v>7.992496475263009</v>
+        <v>7.99249553273396</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151755156881</v>
+        <v>7.885151270575596</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395101374897398</v>
+        <v>7.395100920432114</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198787689209</v>
+        <v>6.731198310852051</v>
       </c>
       <c r="C107" t="n">
-        <v>6.784870504526766</v>
+        <v>6.78487002388751</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975689474925</v>
+        <v>6.183975251402972</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242314420779493</v>
+        <v>6.242313978574833</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642459392547607</v>
+        <v>7.642458915710449</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934156405738198</v>
+        <v>7.934155910701143</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650690051923714</v>
+        <v>6.650689636966175</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251668627103</v>
+        <v>7.242251216760168</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775199890137</v>
+        <v>7.469775676727295</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304309853773</v>
+        <v>7.746304804343318</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351929620609467</v>
+        <v>7.351930089923889</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113307020195</v>
+        <v>7.514113786687701</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469932556152</v>
+        <v>7.740469455718994</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757972392701939</v>
+        <v>7.757971914786575</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2832,16 +2832,16 @@
         <v>43922</v>
       </c>
       <c r="B121" t="n">
-        <v>7.461606979370117</v>
+        <v>7.461607456207275</v>
       </c>
       <c r="C121" t="n">
-        <v>7.642458707969071</v>
+        <v>7.642459196363636</v>
       </c>
       <c r="D121" t="n">
-        <v>7.304090740816589</v>
+        <v>7.304091207587605</v>
       </c>
       <c r="E121" t="n">
-        <v>7.619123217923645</v>
+        <v>7.619123704826946</v>
       </c>
       <c r="F121" t="n">
         <v>10218288</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613290309906006</v>
+        <v>7.613289833068848</v>
       </c>
       <c r="C124" t="n">
-        <v>7.69963281053526</v>
+        <v>7.699632328290281</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497778443024633</v>
+        <v>7.497777973422238</v>
       </c>
       <c r="E124" t="n">
-        <v>7.584120103280328</v>
+        <v>7.584119628270164</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672796726226807</v>
+        <v>7.672797679901123</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109174958611256</v>
+        <v>8.109175966524298</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661128980388104</v>
+        <v>7.661129932612202</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840814283200555</v>
+        <v>7.840815257758265</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798988342285</v>
+        <v>7.700798511505127</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307612995673</v>
+        <v>7.781307131173381</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430989778177</v>
+        <v>7.362430533892927</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629934591736</v>
+        <v>7.678629459127295</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265121459961</v>
+        <v>7.375265598297119</v>
       </c>
       <c r="C130" t="n">
-        <v>7.49427797970812</v>
+        <v>7.494278464239883</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762039125325</v>
+        <v>7.343762513925697</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935482620931</v>
+        <v>7.407935961570344</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852481842041016</v>
+        <v>7.852482318878174</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764051870702</v>
+        <v>7.357764498666425</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484073638916</v>
+        <v>7.887484550476074</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826254468098</v>
+        <v>7.966826736101882</v>
       </c>
       <c r="D139" t="n">
-        <v>7.70079846781684</v>
+        <v>7.700798933367937</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980371125938</v>
+        <v>7.841980845212174</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726468563079834</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882818385185504</v>
+        <v>7.882817898699254</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726468563079834</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816312061163636</v>
+        <v>7.816311578781807</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -35312,19 +35312,39 @@
         <v>46303</v>
       </c>
       <c r="B1745" t="n">
-        <v>3.42</v>
+        <v>3.420000076293945</v>
       </c>
       <c r="C1745" t="n">
-        <v>3.63</v>
+        <v>3.630000114440918</v>
       </c>
       <c r="D1745" t="n">
-        <v>3.38</v>
+        <v>3.380000114440918</v>
       </c>
       <c r="E1745" t="n">
-        <v>3.6</v>
+        <v>3.599999904632568</v>
       </c>
       <c r="F1745" t="n">
         <v>12761800</v>
+      </c>
+    </row>
+    <row r="1746">
+      <c r="A1746" s="1" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B1746" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="C1746" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="D1746" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="E1746" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="F1746" t="n">
+        <v>6714600</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132843971252</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180155754089355</v>
+        <v>2.180155992507935</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="C36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="D36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="E36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212490081787</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647352695465088</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647352695465088</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647352695465088</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647352695465088</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951084613800049</v>
+        <v>6.951085090637207</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951085090637208</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951085090637208</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951085090637208</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222900390625</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997221946716309</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="C46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="D46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="E46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="C47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="D47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="E47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543262481689</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.075627326965332</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -2032,16 +2032,16 @@
         <v>43809</v>
       </c>
       <c r="B81" t="n">
-        <v>10.37040996551514</v>
+        <v>10.37041091918945</v>
       </c>
       <c r="C81" t="n">
-        <v>10.37040996551514</v>
+        <v>10.37041091918945</v>
       </c>
       <c r="D81" t="n">
-        <v>9.685505554677158</v>
+        <v>9.685506445366912</v>
       </c>
       <c r="E81" t="n">
-        <v>9.685505554677158</v>
+        <v>9.685506445366912</v>
       </c>
       <c r="F81" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610103607178</v>
+        <v>10.60610008239746</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448453125444</v>
+        <v>11.08448353456507</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2412,16 +2412,16 @@
         <v>43893</v>
       </c>
       <c r="B100" t="n">
-        <v>8.707736968994141</v>
+        <v>8.707737922668457</v>
       </c>
       <c r="C100" t="n">
-        <v>8.750908637511316</v>
+        <v>8.750909595913809</v>
       </c>
       <c r="D100" t="n">
-        <v>8.496548582064067</v>
+        <v>8.496549512608961</v>
       </c>
       <c r="E100" t="n">
-        <v>8.692569067314889</v>
+        <v>8.692570019328013</v>
       </c>
       <c r="F100" t="n">
         <v>7099936</v>
@@ -2452,16 +2452,16 @@
         <v>43895</v>
       </c>
       <c r="B102" t="n">
-        <v>8.294693946838379</v>
+        <v>8.294694900512695</v>
       </c>
       <c r="C102" t="n">
-        <v>8.675067158673277</v>
+        <v>8.675068156080631</v>
       </c>
       <c r="D102" t="n">
-        <v>8.054335362649853</v>
+        <v>8.054336288689177</v>
       </c>
       <c r="E102" t="n">
-        <v>8.588723824522271</v>
+        <v>8.588724812002386</v>
       </c>
       <c r="F102" t="n">
         <v>11131364</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087005615234375</v>
+        <v>8.087006568908691</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167514235155968</v>
+        <v>8.167515198324406</v>
       </c>
       <c r="D103" t="n">
-        <v>7.934155965259957</v>
+        <v>7.93415690090921</v>
       </c>
       <c r="E103" t="n">
-        <v>7.99249553273396</v>
+        <v>7.992496475263009</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151270575596</v>
+        <v>7.885151755156881</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395100920432114</v>
+        <v>7.395101374897398</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198310852051</v>
+        <v>6.731198787689209</v>
       </c>
       <c r="C107" t="n">
-        <v>6.78487002388751</v>
+        <v>6.784870504526766</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975251402972</v>
+        <v>6.183975689474925</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242313978574833</v>
+        <v>6.242314420779493</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642458915710449</v>
+        <v>7.642459392547607</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934155910701143</v>
+        <v>7.934156405738198</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650689636966175</v>
+        <v>6.650690051923714</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251216760168</v>
+        <v>7.242251668627103</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775676727295</v>
+        <v>7.469775199890137</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304804343318</v>
+        <v>7.746304309853773</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351930089923889</v>
+        <v>7.351929620609467</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113786687701</v>
+        <v>7.514113307020195</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469455718994</v>
+        <v>7.740469932556152</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757971914786575</v>
+        <v>7.757972392701939</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2832,16 +2832,16 @@
         <v>43922</v>
       </c>
       <c r="B121" t="n">
-        <v>7.461607456207275</v>
+        <v>7.461606979370117</v>
       </c>
       <c r="C121" t="n">
-        <v>7.642459196363636</v>
+        <v>7.642458707969071</v>
       </c>
       <c r="D121" t="n">
-        <v>7.304091207587605</v>
+        <v>7.304090740816589</v>
       </c>
       <c r="E121" t="n">
-        <v>7.619123704826946</v>
+        <v>7.619123217923645</v>
       </c>
       <c r="F121" t="n">
         <v>10218288</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613289833068848</v>
+        <v>7.613290309906006</v>
       </c>
       <c r="C124" t="n">
-        <v>7.699632328290281</v>
+        <v>7.69963281053526</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497777973422238</v>
+        <v>7.497778443024633</v>
       </c>
       <c r="E124" t="n">
-        <v>7.584119628270164</v>
+        <v>7.584120103280328</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672797679901123</v>
+        <v>7.672796726226807</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109175966524298</v>
+        <v>8.109174958611256</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661129932612202</v>
+        <v>7.661128980388104</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840815257758265</v>
+        <v>7.840814283200555</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798511505127</v>
+        <v>7.700798988342285</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307131173381</v>
+        <v>7.781307612995673</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430533892927</v>
+        <v>7.362430989778177</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629459127295</v>
+        <v>7.678629934591736</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265598297119</v>
+        <v>7.375265121459961</v>
       </c>
       <c r="C130" t="n">
-        <v>7.494278464239883</v>
+        <v>7.49427797970812</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762513925697</v>
+        <v>7.343762039125325</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935961570344</v>
+        <v>7.407935482620931</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852482318878174</v>
+        <v>7.852481842041016</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764498666425</v>
+        <v>7.357764051870702</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484550476074</v>
+        <v>7.887484073638916</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826736101882</v>
+        <v>7.966826254468098</v>
       </c>
       <c r="D139" t="n">
-        <v>7.700798933367937</v>
+        <v>7.70079846781684</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980845212174</v>
+        <v>7.841980371125938</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726468563079834</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817898699254</v>
+        <v>7.882818385185504</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726468563079834</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311578781807</v>
+        <v>7.816312061163636</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -35332,16 +35332,16 @@
         <v>46304</v>
       </c>
       <c r="B1746" t="n">
-        <v>3.58</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="C1746" t="n">
-        <v>3.58</v>
+        <v>3.579999923706055</v>
       </c>
       <c r="D1746" t="n">
-        <v>3.38</v>
+        <v>3.380000114440918</v>
       </c>
       <c r="E1746" t="n">
-        <v>3.43</v>
+        <v>3.430000066757202</v>
       </c>
       <c r="F1746" t="n">
         <v>6714600</v>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1746"/>
+  <dimension ref="A1:F1747"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616732120513916</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279499769210815</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279499769210815</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279499769210815</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279499769210815</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180155992507935</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125651836395264</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.758486986160278</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951085090637207</v>
+        <v>6.951085567474365</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951085090637208</v>
+        <v>6.951085567474365</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951085090637208</v>
+        <v>6.951085567474365</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951085090637208</v>
+        <v>6.951085567474365</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543262481689</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733310699463</v>
       </c>
       <c r="C57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733310699463</v>
       </c>
       <c r="D57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733310699463</v>
       </c>
       <c r="E57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733310699463</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014761924743652</v>
       </c>
       <c r="C64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014761924743652</v>
       </c>
       <c r="D64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014761924743652</v>
       </c>
       <c r="E64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014761924743652</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1832,16 +1832,16 @@
         <v>43684</v>
       </c>
       <c r="B71" t="n">
-        <v>11.66787815093994</v>
+        <v>11.66787719726562</v>
       </c>
       <c r="C71" t="n">
-        <v>11.66787815093994</v>
+        <v>11.66787719726562</v>
       </c>
       <c r="D71" t="n">
-        <v>11.66787815093994</v>
+        <v>11.66787719726562</v>
       </c>
       <c r="E71" t="n">
-        <v>11.66787815093994</v>
+        <v>11.66787719726562</v>
       </c>
       <c r="F71" t="n">
         <v>755</v>
@@ -1872,16 +1872,16 @@
         <v>43741</v>
       </c>
       <c r="B73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F73" t="n">
         <v>755</v>
@@ -1892,16 +1892,16 @@
         <v>43747</v>
       </c>
       <c r="B74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F74" t="n">
         <v>755</v>
@@ -1952,16 +1952,16 @@
         <v>43773</v>
       </c>
       <c r="B77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F77" t="n">
         <v>1510</v>
@@ -2012,16 +2012,16 @@
         <v>43802</v>
       </c>
       <c r="B80" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C80" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D80" t="n">
-        <v>9.21762282756219</v>
+        <v>9.217621990355065</v>
       </c>
       <c r="E80" t="n">
-        <v>9.21762282756219</v>
+        <v>9.217621990355065</v>
       </c>
       <c r="F80" t="n">
         <v>1510</v>
@@ -2032,16 +2032,16 @@
         <v>43809</v>
       </c>
       <c r="B81" t="n">
-        <v>10.37041091918945</v>
+        <v>10.37040996551514</v>
       </c>
       <c r="C81" t="n">
-        <v>10.37041091918945</v>
+        <v>10.37040996551514</v>
       </c>
       <c r="D81" t="n">
-        <v>9.685506445366912</v>
+        <v>9.685505554677158</v>
       </c>
       <c r="E81" t="n">
-        <v>9.685506445366912</v>
+        <v>9.685505554677158</v>
       </c>
       <c r="F81" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610008239746</v>
+        <v>10.60610103607178</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448353456507</v>
+        <v>11.08448453125444</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2412,16 +2412,16 @@
         <v>43893</v>
       </c>
       <c r="B100" t="n">
-        <v>8.707737922668457</v>
+        <v>8.707736968994141</v>
       </c>
       <c r="C100" t="n">
-        <v>8.750909595913809</v>
+        <v>8.750908637511316</v>
       </c>
       <c r="D100" t="n">
-        <v>8.496549512608961</v>
+        <v>8.496548582064067</v>
       </c>
       <c r="E100" t="n">
-        <v>8.692570019328013</v>
+        <v>8.692569067314889</v>
       </c>
       <c r="F100" t="n">
         <v>7099936</v>
@@ -2452,16 +2452,16 @@
         <v>43895</v>
       </c>
       <c r="B102" t="n">
-        <v>8.294694900512695</v>
+        <v>8.294693946838379</v>
       </c>
       <c r="C102" t="n">
-        <v>8.675068156080631</v>
+        <v>8.675067158673277</v>
       </c>
       <c r="D102" t="n">
-        <v>8.054336288689177</v>
+        <v>8.054335362649853</v>
       </c>
       <c r="E102" t="n">
-        <v>8.588724812002386</v>
+        <v>8.588723824522271</v>
       </c>
       <c r="F102" t="n">
         <v>11131364</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087006568908691</v>
+        <v>8.087005615234375</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167515198324406</v>
+        <v>8.167514235155968</v>
       </c>
       <c r="D103" t="n">
-        <v>7.93415690090921</v>
+        <v>7.934155965259957</v>
       </c>
       <c r="E103" t="n">
-        <v>7.992496475263009</v>
+        <v>7.99249553273396</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174576363958773</v>
+        <v>7.174577261989849</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269086440314109</v>
+        <v>7.269087350174872</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759139060974121</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151755156881</v>
+        <v>7.885152239738168</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395101374897398</v>
+        <v>7.395101829362682</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759139060974121</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642459392547607</v>
+        <v>7.642459869384766</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934156405738198</v>
+        <v>7.934156900775253</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650690051923714</v>
+        <v>6.650690466881254</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251668627103</v>
+        <v>7.242252120494039</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255058288574</v>
+        <v>7.277255535125732</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292230712304</v>
+        <v>7.641292731402749</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086097777741</v>
+        <v>6.70086141684674</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766201694169458</v>
+        <v>6.766202137520195</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2632,16 +2632,16 @@
         <v>43908</v>
       </c>
       <c r="B111" t="n">
-        <v>6.985558032989502</v>
+        <v>6.98555850982666</v>
       </c>
       <c r="C111" t="n">
-        <v>8.075337993481165</v>
+        <v>8.075338544707167</v>
       </c>
       <c r="D111" t="n">
-        <v>6.710196211513576</v>
+        <v>6.71019666955442</v>
       </c>
       <c r="E111" t="n">
-        <v>7.140740982312391</v>
+        <v>7.140741469742403</v>
       </c>
       <c r="F111" t="n">
         <v>26337960</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738137245178223</v>
+        <v>7.738136291503906</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145346146541403</v>
+        <v>8.145345142681279</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298979071039</v>
+        <v>7.690298031292473</v>
       </c>
       <c r="E117" t="n">
-        <v>8.13834499423681</v>
+        <v>8.138343991239532</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775199890137</v>
+        <v>7.469775676727295</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304309853773</v>
+        <v>7.746304804343318</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351929620609467</v>
+        <v>7.351930089923889</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113307020195</v>
+        <v>7.514113786687701</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469932556152</v>
+        <v>7.740469455718994</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757972392701939</v>
+        <v>7.757971914786575</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2832,16 +2832,16 @@
         <v>43922</v>
       </c>
       <c r="B121" t="n">
-        <v>7.461606979370117</v>
+        <v>7.461607933044434</v>
       </c>
       <c r="C121" t="n">
-        <v>7.642458707969071</v>
+        <v>7.642459684758201</v>
       </c>
       <c r="D121" t="n">
-        <v>7.304090740816589</v>
+        <v>7.304091674358621</v>
       </c>
       <c r="E121" t="n">
-        <v>7.619123217923645</v>
+        <v>7.619124191730246</v>
       </c>
       <c r="F121" t="n">
         <v>10218288</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582953929901123</v>
+        <v>7.582952976226807</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840815002303775</v>
+        <v>7.840814016199421</v>
       </c>
       <c r="D122" t="n">
-        <v>7.381100395706687</v>
+        <v>7.38109946741859</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455774312072345</v>
+        <v>7.455773374392843</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261459350586</v>
+        <v>7.340261936187744</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624426344595</v>
+        <v>7.622624921524582</v>
       </c>
       <c r="D123" t="n">
-        <v>7.21541557567713</v>
+        <v>7.215416044404066</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457147585694</v>
+        <v>7.621457642689852</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613290309906006</v>
+        <v>7.613289833068848</v>
       </c>
       <c r="C124" t="n">
-        <v>7.69963281053526</v>
+        <v>7.699632328290281</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497778443024633</v>
+        <v>7.497777973422238</v>
       </c>
       <c r="E124" t="n">
-        <v>7.584120103280328</v>
+        <v>7.584119628270164</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672796726226807</v>
+        <v>7.672797679901123</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109174958611256</v>
+        <v>8.109175966524298</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661128980388104</v>
+        <v>7.661129932612202</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840814283200555</v>
+        <v>7.840815257758265</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798988342285</v>
+        <v>7.700798511505127</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307612995673</v>
+        <v>7.781307131173381</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430989778177</v>
+        <v>7.362430533892927</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629934591736</v>
+        <v>7.678629459127295</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -2952,16 +2952,16 @@
         <v>43930</v>
       </c>
       <c r="B127" t="n">
-        <v>7.38576602935791</v>
+        <v>7.385766506195068</v>
       </c>
       <c r="C127" t="n">
-        <v>7.778973418970338</v>
+        <v>7.778973921193609</v>
       </c>
       <c r="D127" t="n">
-        <v>7.351929231575166</v>
+        <v>7.351929706227764</v>
       </c>
       <c r="E127" t="n">
-        <v>7.778973418970338</v>
+        <v>7.778973921193609</v>
       </c>
       <c r="F127" t="n">
         <v>7590081</v>
@@ -2972,16 +2972,16 @@
         <v>43934</v>
       </c>
       <c r="B128" t="n">
-        <v>7.41493558883667</v>
+        <v>7.414936065673828</v>
       </c>
       <c r="C128" t="n">
-        <v>7.447605949093313</v>
+        <v>7.447606428031426</v>
       </c>
       <c r="D128" t="n">
-        <v>7.229416415322526</v>
+        <v>7.22941688022938</v>
       </c>
       <c r="E128" t="n">
-        <v>7.385766224588598</v>
+        <v>7.385766699549943</v>
       </c>
       <c r="F128" t="n">
         <v>8873976</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500110626220703</v>
+        <v>7.500111103057861</v>
       </c>
       <c r="C129" t="n">
-        <v>7.750970514277116</v>
+        <v>7.75097100706328</v>
       </c>
       <c r="D129" t="n">
-        <v>7.455773361693658</v>
+        <v>7.45577383571197</v>
       </c>
       <c r="E129" t="n">
-        <v>7.49427759388343</v>
+        <v>7.494278070349739</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566619396209717</v>
+        <v>7.5666184425354</v>
       </c>
       <c r="C131" t="n">
-        <v>7.5887884509226</v>
+        <v>7.588787494454161</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234084415890043</v>
+        <v>7.234083504127451</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444106376032958</v>
+        <v>7.44410543779982</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251522064208984</v>
+        <v>8.251523017883301</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431207358265677</v>
+        <v>8.431208332707222</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3112,16 +3112,16 @@
         <v>43944</v>
       </c>
       <c r="B135" t="n">
-        <v>8.089339256286621</v>
+        <v>8.089340209960938</v>
       </c>
       <c r="C135" t="n">
-        <v>8.57472300766133</v>
+        <v>8.574724018558863</v>
       </c>
       <c r="D135" t="n">
-        <v>7.969159966917957</v>
+        <v>7.969160906424007</v>
       </c>
       <c r="E135" t="n">
-        <v>8.481379364431731</v>
+        <v>8.481380364324728</v>
       </c>
       <c r="F135" t="n">
         <v>13472583</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852481842041016</v>
+        <v>7.852482318878174</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764051870702</v>
+        <v>7.357764498666425</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3152,16 +3152,16 @@
         <v>43948</v>
       </c>
       <c r="B137" t="n">
-        <v>8.105673789978027</v>
+        <v>8.105674743652344</v>
       </c>
       <c r="C137" t="n">
-        <v>8.16517979671254</v>
+        <v>8.165180757388045</v>
       </c>
       <c r="D137" t="n">
-        <v>7.710133516824237</v>
+        <v>7.710134423961201</v>
       </c>
       <c r="E137" t="n">
-        <v>7.937657076955135</v>
+        <v>7.93765801086142</v>
       </c>
       <c r="F137" t="n">
         <v>12260436</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484073638916</v>
+        <v>7.887483596801758</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826254468098</v>
+        <v>7.966825772834317</v>
       </c>
       <c r="D139" t="n">
-        <v>7.70079846781684</v>
+        <v>7.700798002265745</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980371125938</v>
+        <v>7.841979897039702</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726468563079834</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882818385185504</v>
+        <v>7.882817898699254</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726468563079834</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816312061163636</v>
+        <v>7.816311578781807</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -3252,16 +3252,16 @@
         <v>43956</v>
       </c>
       <c r="B142" t="n">
-        <v>8.114091873168945</v>
+        <v>8.114090919494629</v>
       </c>
       <c r="C142" t="n">
-        <v>8.645024731663977</v>
+        <v>8.645023715587479</v>
       </c>
       <c r="D142" t="n">
-        <v>8.069433944133035</v>
+        <v>8.069432995707503</v>
       </c>
       <c r="E142" t="n">
-        <v>8.286521173623905</v>
+        <v>8.286520199683441</v>
       </c>
       <c r="F142" t="n">
         <v>11843548</v>
@@ -3272,16 +3272,16 @@
         <v>43957</v>
       </c>
       <c r="B143" t="n">
-        <v>8.048344612121582</v>
+        <v>8.048345565795898</v>
       </c>
       <c r="C143" t="n">
-        <v>8.145103893796581</v>
+        <v>8.145104858936216</v>
       </c>
       <c r="D143" t="n">
-        <v>7.96399105383742</v>
+        <v>7.963991997516411</v>
       </c>
       <c r="E143" t="n">
-        <v>8.145103893796581</v>
+        <v>8.145104858936216</v>
       </c>
       <c r="F143" t="n">
         <v>16545622</v>
@@ -3312,16 +3312,16 @@
         <v>43959</v>
       </c>
       <c r="B145" t="n">
-        <v>8.162470817565918</v>
+        <v>8.162469863891602</v>
       </c>
       <c r="C145" t="n">
-        <v>8.184800228116485</v>
+        <v>8.184799271833279</v>
       </c>
       <c r="D145" t="n">
-        <v>7.947864739756858</v>
+        <v>7.94786381115636</v>
       </c>
       <c r="E145" t="n">
-        <v>8.156268402071278</v>
+        <v>8.15626744912163</v>
       </c>
       <c r="F145" t="n">
         <v>8818844</v>
@@ -3352,16 +3352,16 @@
         <v>43963</v>
       </c>
       <c r="B147" t="n">
-        <v>8.085559844970703</v>
+        <v>8.085558891296387</v>
       </c>
       <c r="C147" t="n">
-        <v>8.276596387736546</v>
+        <v>8.276595411529883</v>
       </c>
       <c r="D147" t="n">
-        <v>8.063230434277379</v>
+        <v>8.063229483236768</v>
       </c>
       <c r="E147" t="n">
-        <v>8.187280531887918</v>
+        <v>8.187279566215866</v>
       </c>
       <c r="F147" t="n">
         <v>9953957</v>
@@ -3372,16 +3372,16 @@
         <v>43964</v>
       </c>
       <c r="B148" t="n">
-        <v>7.926775932312012</v>
+        <v>7.926775455474854</v>
       </c>
       <c r="C148" t="n">
-        <v>8.187280049800203</v>
+        <v>8.187279557292356</v>
       </c>
       <c r="D148" t="n">
-        <v>7.885840170888542</v>
+        <v>7.885839696513885</v>
       </c>
       <c r="E148" t="n">
-        <v>8.187280049800203</v>
+        <v>8.187279557292356</v>
       </c>
       <c r="F148" t="n">
         <v>10179016</v>
@@ -3412,16 +3412,16 @@
         <v>43966</v>
       </c>
       <c r="B150" t="n">
-        <v>6.841341018676758</v>
+        <v>6.8413405418396</v>
       </c>
       <c r="C150" t="n">
-        <v>7.421893621943401</v>
+        <v>7.421893104642092</v>
       </c>
       <c r="D150" t="n">
-        <v>6.841341018676758</v>
+        <v>6.8413405418396</v>
       </c>
       <c r="E150" t="n">
-        <v>7.420653049518127</v>
+        <v>7.420652532303285</v>
       </c>
       <c r="F150" t="n">
         <v>26563775</v>
@@ -3452,16 +3452,16 @@
         <v>43970</v>
       </c>
       <c r="B152" t="n">
-        <v>6.831417560577393</v>
+        <v>6.831418037414551</v>
       </c>
       <c r="C152" t="n">
-        <v>7.018731929050585</v>
+        <v>7.018732418962401</v>
       </c>
       <c r="D152" t="n">
-        <v>6.799164018747209</v>
+        <v>6.79916449333305</v>
       </c>
       <c r="E152" t="n">
-        <v>6.966631015976597</v>
+        <v>6.966631502251738</v>
       </c>
       <c r="F152" t="n">
         <v>13463520</v>
@@ -3472,16 +3472,16 @@
         <v>43971</v>
       </c>
       <c r="B153" t="n">
-        <v>6.822733402252197</v>
+        <v>6.822733879089355</v>
       </c>
       <c r="C153" t="n">
-        <v>6.983997533970078</v>
+        <v>6.983998022077899</v>
       </c>
       <c r="D153" t="n">
-        <v>6.81032857213493</v>
+        <v>6.810329048105121</v>
       </c>
       <c r="E153" t="n">
-        <v>6.946783490349408</v>
+        <v>6.94678397585636</v>
       </c>
       <c r="F153" t="n">
         <v>11533147</v>
@@ -3552,16 +3552,16 @@
         <v>43977</v>
       </c>
       <c r="B157" t="n">
-        <v>7.423134326934814</v>
+        <v>7.423134803771973</v>
       </c>
       <c r="C157" t="n">
-        <v>7.560828925689475</v>
+        <v>7.560829411371671</v>
       </c>
       <c r="D157" t="n">
-        <v>7.275514702466858</v>
+        <v>7.275515169821428</v>
       </c>
       <c r="E157" t="n">
-        <v>7.442982144705714</v>
+        <v>7.442982622817829</v>
       </c>
       <c r="F157" t="n">
         <v>12080691</v>
@@ -3612,16 +3612,16 @@
         <v>43980</v>
       </c>
       <c r="B160" t="n">
-        <v>7.812650680541992</v>
+        <v>7.812650203704834</v>
       </c>
       <c r="C160" t="n">
-        <v>7.812650680541992</v>
+        <v>7.812650203704834</v>
       </c>
       <c r="D160" t="n">
-        <v>7.481437500239227</v>
+        <v>7.481437043617326</v>
       </c>
       <c r="E160" t="n">
-        <v>7.519893458373339</v>
+        <v>7.519892999404318</v>
       </c>
       <c r="F160" t="n">
         <v>23712019</v>
@@ -3652,16 +3652,16 @@
         <v>43984</v>
       </c>
       <c r="B162" t="n">
-        <v>8.271635055541992</v>
+        <v>8.271634101867676</v>
       </c>
       <c r="C162" t="n">
-        <v>8.286521031632221</v>
+        <v>8.286520076241633</v>
       </c>
       <c r="D162" t="n">
-        <v>7.976396678662855</v>
+        <v>7.976395759027911</v>
       </c>
       <c r="E162" t="n">
-        <v>8.063230496816454</v>
+        <v>8.063229567170044</v>
       </c>
       <c r="F162" t="n">
         <v>21348142</v>
@@ -3672,16 +3672,16 @@
         <v>43985</v>
       </c>
       <c r="B163" t="n">
-        <v>8.373353958129883</v>
+        <v>8.373354911804199</v>
       </c>
       <c r="C163" t="n">
-        <v>8.80008582291646</v>
+        <v>8.800086825192951</v>
       </c>
       <c r="D163" t="n">
-        <v>8.315051079171372</v>
+        <v>8.315052026205343</v>
       </c>
       <c r="E163" t="n">
-        <v>8.31753222383259</v>
+        <v>8.317533171149149</v>
       </c>
       <c r="F163" t="n">
         <v>31125376</v>
@@ -3752,16 +3752,16 @@
         <v>43991</v>
       </c>
       <c r="B167" t="n">
-        <v>8.296443939208984</v>
+        <v>8.296442985534668</v>
       </c>
       <c r="C167" t="n">
-        <v>8.32745691101246</v>
+        <v>8.327455953773208</v>
       </c>
       <c r="D167" t="n">
-        <v>8.0967247251524</v>
+        <v>8.096723794435762</v>
       </c>
       <c r="E167" t="n">
-        <v>8.137661383332564</v>
+        <v>8.137660447910266</v>
       </c>
       <c r="F167" t="n">
         <v>13675741</v>
@@ -3772,16 +3772,16 @@
         <v>43992</v>
       </c>
       <c r="B168" t="n">
-        <v>8.089280128479004</v>
+        <v>8.08928108215332</v>
       </c>
       <c r="C168" t="n">
-        <v>8.426696138374464</v>
+        <v>8.426697131827968</v>
       </c>
       <c r="D168" t="n">
-        <v>8.037179665656195</v>
+        <v>8.0371806131882</v>
       </c>
       <c r="E168" t="n">
-        <v>8.311329615282364</v>
+        <v>8.311330595134894</v>
       </c>
       <c r="F168" t="n">
         <v>11944749</v>
@@ -3792,16 +3792,16 @@
         <v>43994</v>
       </c>
       <c r="B169" t="n">
-        <v>7.950345516204834</v>
+        <v>7.950345993041992</v>
       </c>
       <c r="C169" t="n">
-        <v>8.084319292912509</v>
+        <v>8.084319777785</v>
       </c>
       <c r="D169" t="n">
-        <v>7.774194958703272</v>
+        <v>7.774195424975465</v>
       </c>
       <c r="E169" t="n">
-        <v>7.877156659374939</v>
+        <v>7.877157131822456</v>
       </c>
       <c r="F169" t="n">
         <v>12251373</v>
@@ -3892,16 +3892,16 @@
         <v>44001</v>
       </c>
       <c r="B174" t="n">
-        <v>8.487481117248535</v>
+        <v>8.487480163574219</v>
       </c>
       <c r="C174" t="n">
-        <v>8.58920180321846</v>
+        <v>8.589200838114557</v>
       </c>
       <c r="D174" t="n">
-        <v>8.203407450651435</v>
+        <v>8.203406528896336</v>
       </c>
       <c r="E174" t="n">
-        <v>8.203407450651435</v>
+        <v>8.203406528896336</v>
       </c>
       <c r="F174" t="n">
         <v>20750754</v>
@@ -3912,16 +3912,16 @@
         <v>44004</v>
       </c>
       <c r="B175" t="n">
-        <v>8.440341949462891</v>
+        <v>8.440342903137207</v>
       </c>
       <c r="C175" t="n">
-        <v>8.729376978500955</v>
+        <v>8.729377964833343</v>
       </c>
       <c r="D175" t="n">
-        <v>8.380797159632158</v>
+        <v>8.380798106578508</v>
       </c>
       <c r="E175" t="n">
-        <v>8.489961267461833</v>
+        <v>8.489962226742637</v>
       </c>
       <c r="F175" t="n">
         <v>12069362</v>
@@ -3952,16 +3952,16 @@
         <v>44006</v>
       </c>
       <c r="B177" t="n">
-        <v>8.59416389465332</v>
+        <v>8.594162940979004</v>
       </c>
       <c r="C177" t="n">
-        <v>8.669833897798144</v>
+        <v>8.669832935726904</v>
       </c>
       <c r="D177" t="n">
-        <v>8.422974729757115</v>
+        <v>8.422973795079262</v>
       </c>
       <c r="E177" t="n">
-        <v>8.571834484683247</v>
+        <v>8.571833533486773</v>
       </c>
       <c r="F177" t="n">
         <v>7388434</v>
@@ -4052,16 +4052,16 @@
         <v>44013</v>
       </c>
       <c r="B182" t="n">
-        <v>9.009729385375977</v>
+        <v>9.009730339050293</v>
       </c>
       <c r="C182" t="n">
-        <v>9.115171330097578</v>
+        <v>9.11517229493286</v>
       </c>
       <c r="D182" t="n">
-        <v>8.731858165462054</v>
+        <v>8.731859089723871</v>
       </c>
       <c r="E182" t="n">
-        <v>8.812490451063802</v>
+        <v>8.812491383860499</v>
       </c>
       <c r="F182" t="n">
         <v>8963093</v>
@@ -4292,16 +4292,16 @@
         <v>44029</v>
       </c>
       <c r="B194" t="n">
-        <v>8.819933891296387</v>
+        <v>8.81993293762207</v>
       </c>
       <c r="C194" t="n">
-        <v>8.919174324825571</v>
+        <v>8.919173360420668</v>
       </c>
       <c r="D194" t="n">
-        <v>8.633859641988225</v>
+        <v>8.633858708433587</v>
       </c>
       <c r="E194" t="n">
-        <v>8.633859641988225</v>
+        <v>8.633858708433587</v>
       </c>
       <c r="F194" t="n">
         <v>9678298</v>
@@ -4432,16 +4432,16 @@
         <v>44040</v>
       </c>
       <c r="B201" t="n">
-        <v>9.641142845153809</v>
+        <v>9.641143798828125</v>
       </c>
       <c r="C201" t="n">
-        <v>9.832179367263814</v>
+        <v>9.832180339834917</v>
       </c>
       <c r="D201" t="n">
-        <v>9.466232422996864</v>
+        <v>9.466233359369541</v>
       </c>
       <c r="E201" t="n">
-        <v>9.67587708316008</v>
+        <v>9.675878040270206</v>
       </c>
       <c r="F201" t="n">
         <v>30127714</v>
@@ -4472,16 +4472,16 @@
         <v>44042</v>
       </c>
       <c r="B203" t="n">
-        <v>9.143703460693359</v>
+        <v>9.143704414367676</v>
       </c>
       <c r="C203" t="n">
-        <v>9.700686938306321</v>
+        <v>9.700687950073165</v>
       </c>
       <c r="D203" t="n">
-        <v>9.097805411083952</v>
+        <v>9.097806359971171</v>
       </c>
       <c r="E203" t="n">
-        <v>9.685800070178546</v>
+        <v>9.685801080392711</v>
       </c>
       <c r="F203" t="n">
         <v>33272500</v>
@@ -4592,16 +4592,16 @@
         <v>44050</v>
       </c>
       <c r="B209" t="n">
-        <v>8.429178237915039</v>
+        <v>8.429177284240723</v>
       </c>
       <c r="C209" t="n">
-        <v>8.429178237915039</v>
+        <v>8.429177284240723</v>
       </c>
       <c r="D209" t="n">
-        <v>8.25550792408546</v>
+        <v>8.255506990060143</v>
       </c>
       <c r="E209" t="n">
-        <v>8.336141112251321</v>
+        <v>8.336140169103194</v>
       </c>
       <c r="F209" t="n">
         <v>22110172</v>
@@ -4612,16 +4612,16 @@
         <v>44053</v>
       </c>
       <c r="B210" t="n">
-        <v>8.25922966003418</v>
+        <v>8.259230613708496</v>
       </c>
       <c r="C210" t="n">
-        <v>8.468873436704216</v>
+        <v>8.468874414585619</v>
       </c>
       <c r="D210" t="n">
-        <v>8.166191645730668</v>
+        <v>8.166192588662099</v>
       </c>
       <c r="E210" t="n">
-        <v>8.435379322693057</v>
+        <v>8.435380296706972</v>
       </c>
       <c r="F210" t="n">
         <v>21920608</v>
@@ -4652,16 +4652,16 @@
         <v>44055</v>
       </c>
       <c r="B212" t="n">
-        <v>8.162470817565918</v>
+        <v>8.162469863891602</v>
       </c>
       <c r="C212" t="n">
-        <v>8.446544484992341</v>
+        <v>8.446543498127859</v>
       </c>
       <c r="D212" t="n">
-        <v>8.078116358606623</v>
+        <v>8.078115414787984</v>
       </c>
       <c r="E212" t="n">
-        <v>8.409329992024503</v>
+        <v>8.409329009508031</v>
       </c>
       <c r="F212" t="n">
         <v>20200945</v>
@@ -4732,16 +4732,16 @@
         <v>44061</v>
       </c>
       <c r="B216" t="n">
-        <v>8.101685523986816</v>
+        <v>8.101686477661133</v>
       </c>
       <c r="C216" t="n">
-        <v>8.143863198266791</v>
+        <v>8.143864156905972</v>
       </c>
       <c r="D216" t="n">
-        <v>7.978877345430011</v>
+        <v>7.9788782846482</v>
       </c>
       <c r="E216" t="n">
-        <v>8.038420352760289</v>
+        <v>8.038421298987467</v>
       </c>
       <c r="F216" t="n">
         <v>10608743</v>
@@ -4752,16 +4752,16 @@
         <v>44062</v>
       </c>
       <c r="B217" t="n">
-        <v>7.926775932312012</v>
+        <v>7.926775455474854</v>
       </c>
       <c r="C217" t="n">
-        <v>8.141381998856557</v>
+        <v>8.141381509109719</v>
       </c>
       <c r="D217" t="n">
-        <v>7.921813642791834</v>
+        <v>7.921813166253184</v>
       </c>
       <c r="E217" t="n">
-        <v>8.141381998856557</v>
+        <v>8.141381509109719</v>
       </c>
       <c r="F217" t="n">
         <v>9466833</v>
@@ -4772,16 +4772,16 @@
         <v>44063</v>
       </c>
       <c r="B218" t="n">
-        <v>7.957787990570068</v>
+        <v>7.957788467407227</v>
       </c>
       <c r="C218" t="n">
-        <v>8.033458885005254</v>
+        <v>8.033459366376674</v>
       </c>
       <c r="D218" t="n">
-        <v>7.774194893738959</v>
+        <v>7.774195359575069</v>
       </c>
       <c r="E218" t="n">
-        <v>7.915611210128628</v>
+        <v>7.915611684438519</v>
       </c>
       <c r="F218" t="n">
         <v>7652765</v>
@@ -4892,16 +4892,16 @@
         <v>44071</v>
       </c>
       <c r="B224" t="n">
-        <v>8.100444793701172</v>
+        <v>8.100445747375488</v>
       </c>
       <c r="C224" t="n">
-        <v>8.100444793701172</v>
+        <v>8.100445747375488</v>
       </c>
       <c r="D224" t="n">
-        <v>7.960268612170143</v>
+        <v>7.960269549341362</v>
       </c>
       <c r="E224" t="n">
-        <v>8.001206157737258</v>
+        <v>8.0012070997281</v>
       </c>
       <c r="F224" t="n">
         <v>5577388</v>
@@ -5012,16 +5012,16 @@
         <v>44082</v>
       </c>
       <c r="B230" t="n">
-        <v>7.751865386962891</v>
+        <v>7.751865863800049</v>
       </c>
       <c r="C230" t="n">
-        <v>7.833737802061967</v>
+        <v>7.833738283935308</v>
       </c>
       <c r="D230" t="n">
-        <v>7.691081361819436</v>
+        <v>7.691081834917614</v>
       </c>
       <c r="E230" t="n">
-        <v>7.813890431199186</v>
+        <v>7.813890911851665</v>
       </c>
       <c r="F230" t="n">
         <v>7181501</v>
@@ -5032,16 +5032,16 @@
         <v>44083</v>
       </c>
       <c r="B231" t="n">
-        <v>7.709689140319824</v>
+        <v>7.709688663482666</v>
       </c>
       <c r="C231" t="n">
-        <v>7.834980256551466</v>
+        <v>7.834979771965168</v>
       </c>
       <c r="D231" t="n">
-        <v>7.637740405675546</v>
+        <v>7.637739933288351</v>
       </c>
       <c r="E231" t="n">
-        <v>7.792802580260581</v>
+        <v>7.792802098282933</v>
       </c>
       <c r="F231" t="n">
         <v>8282629</v>
@@ -5052,16 +5052,16 @@
         <v>44084</v>
       </c>
       <c r="B232" t="n">
-        <v>8.850946426391602</v>
+        <v>8.850947380065918</v>
       </c>
       <c r="C232" t="n">
-        <v>9.197044227170217</v>
+        <v>9.197045218135978</v>
       </c>
       <c r="D232" t="n">
-        <v>8.62145438702172</v>
+        <v>8.621455315968662</v>
       </c>
       <c r="E232" t="n">
-        <v>9.197044227170217</v>
+        <v>9.197045218135978</v>
       </c>
       <c r="F232" t="n">
         <v>139609921</v>
@@ -5132,16 +5132,16 @@
         <v>44090</v>
       </c>
       <c r="B236" t="n">
-        <v>9.312411308288574</v>
+        <v>9.312410354614258</v>
       </c>
       <c r="C236" t="n">
-        <v>9.375676482213272</v>
+        <v>9.375675522060035</v>
       </c>
       <c r="D236" t="n">
-        <v>9.175957274371282</v>
+        <v>9.175956334671081</v>
       </c>
       <c r="E236" t="n">
-        <v>9.179678544963952</v>
+        <v>9.179677604882659</v>
       </c>
       <c r="F236" t="n">
         <v>13993693</v>
@@ -5212,16 +5212,16 @@
         <v>44096</v>
       </c>
       <c r="B240" t="n">
-        <v>9.326057434082031</v>
+        <v>9.326058387756348</v>
       </c>
       <c r="C240" t="n">
-        <v>9.353348239057649</v>
+        <v>9.353349195522698</v>
       </c>
       <c r="D240" t="n">
-        <v>9.182158188124824</v>
+        <v>9.182159127084132</v>
       </c>
       <c r="E240" t="n">
-        <v>9.192082766997606</v>
+        <v>9.192083706971793</v>
       </c>
       <c r="F240" t="n">
         <v>9315031</v>
@@ -5232,16 +5232,16 @@
         <v>44097</v>
       </c>
       <c r="B241" t="n">
-        <v>8.953908920288086</v>
+        <v>8.95390796661377</v>
       </c>
       <c r="C241" t="n">
-        <v>9.308690312405352</v>
+        <v>9.308689320943529</v>
       </c>
       <c r="D241" t="n">
-        <v>8.934060654104224</v>
+        <v>8.934059702543932</v>
       </c>
       <c r="E241" t="n">
-        <v>9.303728915956151</v>
+        <v>9.303727925022763</v>
       </c>
       <c r="F241" t="n">
         <v>13677251</v>
@@ -5252,16 +5252,16 @@
         <v>44098</v>
       </c>
       <c r="B242" t="n">
-        <v>9.282638549804688</v>
+        <v>9.282639503479004</v>
       </c>
       <c r="C242" t="n">
-        <v>9.463751388941567</v>
+        <v>9.46375236122295</v>
       </c>
       <c r="D242" t="n">
-        <v>8.898084356453305</v>
+        <v>8.898085270619518</v>
       </c>
       <c r="E242" t="n">
-        <v>8.906768809518589</v>
+        <v>8.906769724577019</v>
       </c>
       <c r="F242" t="n">
         <v>18607406</v>
@@ -5272,16 +5272,16 @@
         <v>44099</v>
       </c>
       <c r="B243" t="n">
-        <v>9.184639930725098</v>
+        <v>9.184640884399414</v>
       </c>
       <c r="C243" t="n">
-        <v>9.25410751328763</v>
+        <v>9.254108474175018</v>
       </c>
       <c r="D243" t="n">
-        <v>9.095324084518023</v>
+        <v>9.095325028918353</v>
       </c>
       <c r="E243" t="n">
-        <v>9.220613400863298</v>
+        <v>9.22061435827287</v>
       </c>
       <c r="F243" t="n">
         <v>8201819</v>
@@ -5312,16 +5312,16 @@
         <v>44103</v>
       </c>
       <c r="B245" t="n">
-        <v>8.760391235351562</v>
+        <v>8.760390281677246</v>
       </c>
       <c r="C245" t="n">
-        <v>8.942744221459206</v>
+        <v>8.942743247933565</v>
       </c>
       <c r="D245" t="n">
-        <v>8.68348020897627</v>
+        <v>8.683479263674647</v>
       </c>
       <c r="E245" t="n">
-        <v>8.802568019244504</v>
+        <v>8.802567060978735</v>
       </c>
       <c r="F245" t="n">
         <v>13985386</v>
@@ -5332,16 +5332,16 @@
         <v>44104</v>
       </c>
       <c r="B246" t="n">
-        <v>8.651226043701172</v>
+        <v>8.651226997375488</v>
       </c>
       <c r="C246" t="n">
-        <v>8.841022441256731</v>
+        <v>8.841023415853394</v>
       </c>
       <c r="D246" t="n">
-        <v>8.609049265013768</v>
+        <v>8.609050214038696</v>
       </c>
       <c r="E246" t="n">
-        <v>8.803807058409923</v>
+        <v>8.803808028904122</v>
       </c>
       <c r="F246" t="n">
         <v>11477260</v>
@@ -5412,16 +5412,16 @@
         <v>44110</v>
       </c>
       <c r="B250" t="n">
-        <v>8.497405052185059</v>
+        <v>8.497404098510742</v>
       </c>
       <c r="C250" t="n">
-        <v>8.520974589071102</v>
+        <v>8.520973632751547</v>
       </c>
       <c r="D250" t="n">
-        <v>8.316293085426295</v>
+        <v>8.3162921520784</v>
       </c>
       <c r="E250" t="n">
-        <v>8.488721491571129</v>
+        <v>8.48872053887138</v>
       </c>
       <c r="F250" t="n">
         <v>10544549</v>
@@ -5432,16 +5432,16 @@
         <v>44111</v>
       </c>
       <c r="B251" t="n">
-        <v>8.585480690002441</v>
+        <v>8.585479736328125</v>
       </c>
       <c r="C251" t="n">
-        <v>8.704568498874545</v>
+        <v>8.704567531971968</v>
       </c>
       <c r="D251" t="n">
-        <v>8.440343093036322</v>
+        <v>8.440342155483876</v>
       </c>
       <c r="E251" t="n">
-        <v>8.477557586577683</v>
+        <v>8.477556644891454</v>
       </c>
       <c r="F251" t="n">
         <v>12680345</v>
@@ -5552,16 +5552,16 @@
         <v>44120</v>
       </c>
       <c r="B257" t="n">
-        <v>8.25922966003418</v>
+        <v>8.259230613708496</v>
       </c>
       <c r="C257" t="n">
-        <v>8.267912326486389</v>
+        <v>8.267913281163274</v>
       </c>
       <c r="D257" t="n">
-        <v>8.097964185523827</v>
+        <v>8.097965120577188</v>
       </c>
       <c r="E257" t="n">
-        <v>8.122774739620494</v>
+        <v>8.122775677538673</v>
       </c>
       <c r="F257" t="n">
         <v>10726560</v>
@@ -5612,16 +5612,16 @@
         <v>44125</v>
       </c>
       <c r="B260" t="n">
-        <v>8.275355339050293</v>
+        <v>8.275356292724609</v>
       </c>
       <c r="C260" t="n">
-        <v>8.355987625465389</v>
+        <v>8.355988588431988</v>
       </c>
       <c r="D260" t="n">
-        <v>8.245583390421267</v>
+        <v>8.245584340664582</v>
       </c>
       <c r="E260" t="n">
-        <v>8.354747499881778</v>
+        <v>8.35474846270546</v>
       </c>
       <c r="F260" t="n">
         <v>4665068</v>
@@ -5632,16 +5632,16 @@
         <v>44126</v>
       </c>
       <c r="B261" t="n">
-        <v>8.267911911010742</v>
+        <v>8.267912864685059</v>
       </c>
       <c r="C261" t="n">
-        <v>8.337380386835774</v>
+        <v>8.337381348523031</v>
       </c>
       <c r="D261" t="n">
-        <v>8.168673273460097</v>
+        <v>8.168674215687588</v>
       </c>
       <c r="E261" t="n">
-        <v>8.30636741913896</v>
+        <v>8.306368377248981</v>
       </c>
       <c r="F261" t="n">
         <v>7908034</v>
@@ -5652,16 +5652,16 @@
         <v>44127</v>
       </c>
       <c r="B262" t="n">
-        <v>8.234419822692871</v>
+        <v>8.234420776367188</v>
       </c>
       <c r="C262" t="n">
-        <v>8.312570966783923</v>
+        <v>8.312571929509362</v>
       </c>
       <c r="D262" t="n">
-        <v>8.203406854103131</v>
+        <v>8.203407804185662</v>
       </c>
       <c r="E262" t="n">
-        <v>8.269152274680931</v>
+        <v>8.269153232377807</v>
       </c>
       <c r="F262" t="n">
         <v>5098571</v>
@@ -5712,16 +5712,16 @@
         <v>44132</v>
       </c>
       <c r="B265" t="n">
-        <v>7.825055599212646</v>
+        <v>7.825055122375488</v>
       </c>
       <c r="C265" t="n">
-        <v>8.088040873150774</v>
+        <v>8.088040380288025</v>
       </c>
       <c r="D265" t="n">
-        <v>7.817612164601516</v>
+        <v>7.81761168821794</v>
       </c>
       <c r="E265" t="n">
-        <v>8.078116293669268</v>
+        <v>8.078115801411293</v>
       </c>
       <c r="F265" t="n">
         <v>12369944</v>
@@ -5752,16 +5752,16 @@
         <v>44134</v>
       </c>
       <c r="B267" t="n">
-        <v>7.684878826141357</v>
+        <v>7.684879302978516</v>
       </c>
       <c r="C267" t="n">
-        <v>7.777915944304612</v>
+        <v>7.777916426914608</v>
       </c>
       <c r="D267" t="n">
-        <v>7.574474588649013</v>
+        <v>7.574475058635726</v>
       </c>
       <c r="E267" t="n">
-        <v>7.759308699364413</v>
+        <v>7.759309180819852</v>
       </c>
       <c r="F267" t="n">
         <v>16269207</v>
@@ -5772,16 +5772,16 @@
         <v>44138</v>
       </c>
       <c r="B268" t="n">
-        <v>7.717131614685059</v>
+        <v>7.7171311378479</v>
       </c>
       <c r="C268" t="n">
-        <v>7.852346415863062</v>
+        <v>7.852345930671059</v>
       </c>
       <c r="D268" t="n">
-        <v>7.622854363726927</v>
+        <v>7.622853892715106</v>
       </c>
       <c r="E268" t="n">
-        <v>7.821334338599661</v>
+        <v>7.821333855323877</v>
       </c>
       <c r="F268" t="n">
         <v>9901091</v>
@@ -5812,16 +5812,16 @@
         <v>44140</v>
       </c>
       <c r="B270" t="n">
-        <v>8.119053840637207</v>
+        <v>8.119052886962891</v>
       </c>
       <c r="C270" t="n">
-        <v>8.177356724487632</v>
+        <v>8.177355763964984</v>
       </c>
       <c r="D270" t="n">
-        <v>8.007408575750512</v>
+        <v>8.007407635190189</v>
       </c>
       <c r="E270" t="n">
-        <v>8.039661672128053</v>
+        <v>8.039660727779241</v>
       </c>
       <c r="F270" t="n">
         <v>9820281</v>
@@ -5892,16 +5892,16 @@
         <v>44146</v>
       </c>
       <c r="B274" t="n">
-        <v>8.193483352661133</v>
+        <v>8.193482398986816</v>
       </c>
       <c r="C274" t="n">
-        <v>8.420494274138473</v>
+        <v>8.420493294041393</v>
       </c>
       <c r="D274" t="n">
-        <v>8.193483352661133</v>
+        <v>8.193482398986816</v>
       </c>
       <c r="E274" t="n">
-        <v>8.312572059811611</v>
+        <v>8.312571092276054</v>
       </c>
       <c r="F274" t="n">
         <v>7246451</v>
@@ -5912,16 +5912,16 @@
         <v>44147</v>
       </c>
       <c r="B275" t="n">
-        <v>8.234419822692871</v>
+        <v>8.234420776367188</v>
       </c>
       <c r="C275" t="n">
-        <v>8.398164651520666</v>
+        <v>8.398165624159189</v>
       </c>
       <c r="D275" t="n">
-        <v>8.131458125037573</v>
+        <v>8.13145906678732</v>
       </c>
       <c r="E275" t="n">
-        <v>8.193482275292528</v>
+        <v>8.193483224225638</v>
       </c>
       <c r="F275" t="n">
         <v>11697033</v>
@@ -5932,16 +5932,16 @@
         <v>44148</v>
       </c>
       <c r="B276" t="n">
-        <v>8.633858680725098</v>
+        <v>8.633859634399414</v>
       </c>
       <c r="C276" t="n">
-        <v>8.646264403631776</v>
+        <v>8.646265358676397</v>
       </c>
       <c r="D276" t="n">
-        <v>8.267911744802472</v>
+        <v>8.267912658055211</v>
       </c>
       <c r="E276" t="n">
-        <v>8.322493351742979</v>
+        <v>8.322494271024663</v>
       </c>
       <c r="F276" t="n">
         <v>10854949</v>
@@ -5992,16 +5992,16 @@
         <v>44153</v>
       </c>
       <c r="B279" t="n">
-        <v>8.584239959716797</v>
+        <v>8.584240913391113</v>
       </c>
       <c r="C279" t="n">
-        <v>8.64502398560519</v>
+        <v>8.645024946032365</v>
       </c>
       <c r="D279" t="n">
-        <v>8.516012499566937</v>
+        <v>8.516013445661457</v>
       </c>
       <c r="E279" t="n">
-        <v>8.55818927999508</v>
+        <v>8.558190230775271</v>
       </c>
       <c r="F279" t="n">
         <v>8922310</v>
@@ -6072,16 +6072,16 @@
         <v>44160</v>
       </c>
       <c r="B283" t="n">
-        <v>8.739301681518555</v>
+        <v>8.739302635192871</v>
       </c>
       <c r="C283" t="n">
-        <v>8.920413624337439</v>
+        <v>8.920414597775554</v>
       </c>
       <c r="D283" t="n">
-        <v>8.616491723410208</v>
+        <v>8.616492663682914</v>
       </c>
       <c r="E283" t="n">
-        <v>8.854667312281327</v>
+        <v>8.85466827854489</v>
       </c>
       <c r="F283" t="n">
         <v>6633202</v>
@@ -6112,16 +6112,16 @@
         <v>44162</v>
       </c>
       <c r="B285" t="n">
-        <v>8.615251541137695</v>
+        <v>8.615252494812012</v>
       </c>
       <c r="C285" t="n">
-        <v>8.70828776310049</v>
+        <v>8.708288727073548</v>
       </c>
       <c r="D285" t="n">
-        <v>8.507328451506179</v>
+        <v>8.507329393233835</v>
       </c>
       <c r="E285" t="n">
-        <v>8.566871454869922</v>
+        <v>8.566872403188754</v>
       </c>
       <c r="F285" t="n">
         <v>5230736</v>
@@ -6152,16 +6152,16 @@
         <v>44166</v>
       </c>
       <c r="B287" t="n">
-        <v>8.414291381835938</v>
+        <v>8.414292335510254</v>
       </c>
       <c r="C287" t="n">
-        <v>8.672314340510058</v>
+        <v>8.672315323428652</v>
       </c>
       <c r="D287" t="n">
-        <v>8.360949006055193</v>
+        <v>8.360949953683695</v>
       </c>
       <c r="E287" t="n">
-        <v>8.636339977103933</v>
+        <v>8.636340955945199</v>
       </c>
       <c r="F287" t="n">
         <v>16096259</v>
@@ -6172,16 +6172,16 @@
         <v>44167</v>
       </c>
       <c r="B288" t="n">
-        <v>8.282797813415527</v>
+        <v>8.282798767089844</v>
       </c>
       <c r="C288" t="n">
-        <v>8.461429503764982</v>
+        <v>8.4614304780068</v>
       </c>
       <c r="D288" t="n">
-        <v>8.199685276496087</v>
+        <v>8.199686220600897</v>
       </c>
       <c r="E288" t="n">
-        <v>8.456468108007872</v>
+        <v>8.456469081678438</v>
       </c>
       <c r="F288" t="n">
         <v>15329699</v>
@@ -6212,16 +6212,16 @@
         <v>44169</v>
       </c>
       <c r="B290" t="n">
-        <v>8.772793769836426</v>
+        <v>8.772794723510742</v>
       </c>
       <c r="C290" t="n">
-        <v>8.948944312102428</v>
+        <v>8.948945284925747</v>
       </c>
       <c r="D290" t="n">
-        <v>8.683478819885265</v>
+        <v>8.683479763850318</v>
       </c>
       <c r="E290" t="n">
-        <v>8.886919271932774</v>
+        <v>8.886920238013465</v>
       </c>
       <c r="F290" t="n">
         <v>10446369</v>
@@ -6232,16 +6232,16 @@
         <v>44172</v>
       </c>
       <c r="B291" t="n">
-        <v>8.647505760192871</v>
+        <v>8.647504806518555</v>
       </c>
       <c r="C291" t="n">
-        <v>8.82737759966732</v>
+        <v>8.827376626156168</v>
       </c>
       <c r="D291" t="n">
-        <v>8.621455078573774</v>
+        <v>8.621454127772409</v>
       </c>
       <c r="E291" t="n">
-        <v>8.807529333653388</v>
+        <v>8.807528362331166</v>
       </c>
       <c r="F291" t="n">
         <v>10174485</v>
@@ -6392,16 +6392,16 @@
         <v>44182</v>
       </c>
       <c r="B299" t="n">
-        <v>9.125096321105957</v>
+        <v>9.125097274780273</v>
       </c>
       <c r="C299" t="n">
-        <v>9.233019415311725</v>
+        <v>9.233020380265208</v>
       </c>
       <c r="D299" t="n">
-        <v>9.1052480568353</v>
+        <v>9.105249008435251</v>
       </c>
       <c r="E299" t="n">
-        <v>9.230538270595108</v>
+        <v>9.230539235289285</v>
       </c>
       <c r="F299" t="n">
         <v>5262456</v>
@@ -6452,16 +6452,16 @@
         <v>44187</v>
       </c>
       <c r="B302" t="n">
-        <v>9.018413543701172</v>
+        <v>9.018414497375488</v>
       </c>
       <c r="C302" t="n">
-        <v>9.117653080233614</v>
+        <v>9.117654044402261</v>
       </c>
       <c r="D302" t="n">
-        <v>8.941503416629342</v>
+        <v>8.941504362170608</v>
       </c>
       <c r="E302" t="n">
-        <v>8.974995743895692</v>
+        <v>8.974996692978687</v>
       </c>
       <c r="F302" t="n">
         <v>3700636</v>
@@ -6572,16 +6572,16 @@
         <v>44201</v>
       </c>
       <c r="B308" t="n">
-        <v>9.097805023193359</v>
+        <v>9.097805976867676</v>
       </c>
       <c r="C308" t="n">
-        <v>9.304967640603</v>
+        <v>9.304968615993069</v>
       </c>
       <c r="D308" t="n">
-        <v>9.012210449150441</v>
+        <v>9.012211393852336</v>
       </c>
       <c r="E308" t="n">
-        <v>9.304967640603</v>
+        <v>9.304968615993069</v>
       </c>
       <c r="F308" t="n">
         <v>8306796</v>
@@ -6592,16 +6592,16 @@
         <v>44202</v>
       </c>
       <c r="B309" t="n">
-        <v>9.02337646484375</v>
+        <v>9.023375511169434</v>
       </c>
       <c r="C309" t="n">
-        <v>9.178438642419241</v>
+        <v>9.178437672356514</v>
       </c>
       <c r="D309" t="n">
-        <v>8.883200263463204</v>
+        <v>8.883199324604012</v>
       </c>
       <c r="E309" t="n">
-        <v>9.091603036730099</v>
+        <v>9.091602075844966</v>
       </c>
       <c r="F309" t="n">
         <v>6995714</v>
@@ -6632,16 +6632,16 @@
         <v>44204</v>
       </c>
       <c r="B311" t="n">
-        <v>9.494765281677246</v>
+        <v>9.49476432800293</v>
       </c>
       <c r="C311" t="n">
-        <v>9.533220794103377</v>
+        <v>9.533219836566508</v>
       </c>
       <c r="D311" t="n">
-        <v>9.077957953992263</v>
+        <v>9.077957042182957</v>
       </c>
       <c r="E311" t="n">
-        <v>9.178438515281906</v>
+        <v>9.178437593380119</v>
       </c>
       <c r="F311" t="n">
         <v>10280973</v>
@@ -6732,16 +6732,16 @@
         <v>44211</v>
       </c>
       <c r="B316" t="n">
-        <v>9.479878425598145</v>
+        <v>9.479877471923828</v>
       </c>
       <c r="C316" t="n">
-        <v>9.607649794137002</v>
+        <v>9.607648827608905</v>
       </c>
       <c r="D316" t="n">
-        <v>9.378158631904267</v>
+        <v>9.378157688462947</v>
       </c>
       <c r="E316" t="n">
-        <v>9.589042547490402</v>
+        <v>9.589041582834192</v>
       </c>
       <c r="F316" t="n">
         <v>14334303</v>
@@ -6892,16 +6892,16 @@
         <v>44224</v>
       </c>
       <c r="B324" t="n">
-        <v>9.368232727050781</v>
+        <v>9.368233680725098</v>
       </c>
       <c r="C324" t="n">
-        <v>9.399244800408228</v>
+        <v>9.399245757239534</v>
       </c>
       <c r="D324" t="n">
-        <v>9.102766341339521</v>
+        <v>9.102767267989694</v>
       </c>
       <c r="E324" t="n">
-        <v>9.180917480970056</v>
+        <v>9.180918415575915</v>
       </c>
       <c r="F324" t="n">
         <v>7429217</v>
@@ -6912,16 +6912,16 @@
         <v>44225</v>
       </c>
       <c r="B325" t="n">
-        <v>9.363271713256836</v>
+        <v>9.36327075958252</v>
       </c>
       <c r="C325" t="n">
-        <v>9.571676269761104</v>
+        <v>9.571675294860224</v>
       </c>
       <c r="D325" t="n">
-        <v>9.215652973121827</v>
+        <v>9.215652034482874</v>
       </c>
       <c r="E325" t="n">
-        <v>9.312411369945844</v>
+        <v>9.312410421451789</v>
       </c>
       <c r="F325" t="n">
         <v>11022611</v>
@@ -6952,16 +6952,16 @@
         <v>44229</v>
       </c>
       <c r="B327" t="n">
-        <v>10.13361930847168</v>
+        <v>10.133620262146</v>
       </c>
       <c r="C327" t="n">
-        <v>10.18447964681817</v>
+        <v>10.18448060527895</v>
       </c>
       <c r="D327" t="n">
-        <v>9.832179442109044</v>
+        <v>9.832180367414875</v>
       </c>
       <c r="E327" t="n">
-        <v>10.11004977442547</v>
+        <v>10.11005072588166</v>
       </c>
       <c r="F327" t="n">
         <v>20046878</v>
@@ -6992,16 +6992,16 @@
         <v>44231</v>
       </c>
       <c r="B329" t="n">
-        <v>10.38668251037598</v>
+        <v>10.38668155670166</v>
       </c>
       <c r="C329" t="n">
-        <v>10.38668251037598</v>
+        <v>10.38668155670166</v>
       </c>
       <c r="D329" t="n">
-        <v>10.11749393146458</v>
+        <v>10.11749300250636</v>
       </c>
       <c r="E329" t="n">
-        <v>10.17703872709649</v>
+        <v>10.17703779267104</v>
       </c>
       <c r="F329" t="n">
         <v>12166787</v>
@@ -7012,16 +7012,16 @@
         <v>44232</v>
       </c>
       <c r="B330" t="n">
-        <v>10.55663013458252</v>
+        <v>10.5566291809082</v>
       </c>
       <c r="C330" t="n">
-        <v>10.58144069033415</v>
+        <v>10.58143973441847</v>
       </c>
       <c r="D330" t="n">
-        <v>10.32465782656054</v>
+        <v>10.32465689384235</v>
       </c>
       <c r="E330" t="n">
-        <v>10.41893507933724</v>
+        <v>10.41893413810214</v>
       </c>
       <c r="F330" t="n">
         <v>10745440</v>
@@ -7192,16 +7192,16 @@
         <v>44249</v>
       </c>
       <c r="B339" t="n">
-        <v>11.09376525878906</v>
+        <v>11.09376621246338</v>
       </c>
       <c r="C339" t="n">
-        <v>11.20292847746345</v>
+        <v>11.20292944052197</v>
       </c>
       <c r="D339" t="n">
-        <v>10.63602131403072</v>
+        <v>10.63602222835513</v>
       </c>
       <c r="E339" t="n">
-        <v>10.9399432226141</v>
+        <v>10.93994416306512</v>
       </c>
       <c r="F339" t="n">
         <v>14982292</v>
@@ -7292,16 +7292,16 @@
         <v>44256</v>
       </c>
       <c r="B344" t="n">
-        <v>21.85701751708984</v>
+        <v>21.85701560974121</v>
       </c>
       <c r="C344" t="n">
-        <v>23.99306617161</v>
+        <v>23.99306407785948</v>
       </c>
       <c r="D344" t="n">
-        <v>16.31078752172449</v>
+        <v>16.3107860983666</v>
       </c>
       <c r="E344" t="n">
-        <v>16.86353693074166</v>
+        <v>16.8635354591482</v>
       </c>
       <c r="F344" t="n">
         <v>49361500</v>
@@ -7312,16 +7312,16 @@
         <v>44257</v>
       </c>
       <c r="B345" t="n">
-        <v>21.19184494018555</v>
+        <v>21.19184303283691</v>
       </c>
       <c r="C345" t="n">
-        <v>22.95314685108304</v>
+        <v>22.95314478521037</v>
       </c>
       <c r="D345" t="n">
-        <v>20.69530683439987</v>
+        <v>20.6953049717416</v>
       </c>
       <c r="E345" t="n">
-        <v>22.18491936483229</v>
+        <v>22.18491736810308</v>
       </c>
       <c r="F345" t="n">
         <v>20095700</v>
@@ -7352,16 +7352,16 @@
         <v>44259</v>
       </c>
       <c r="B347" t="n">
-        <v>20.86394309997559</v>
+        <v>20.86394119262695</v>
       </c>
       <c r="C347" t="n">
-        <v>21.52911508897337</v>
+        <v>21.52911312081577</v>
       </c>
       <c r="D347" t="n">
-        <v>20.0113977633286</v>
+        <v>20.01139593391831</v>
       </c>
       <c r="E347" t="n">
-        <v>20.23624470835284</v>
+        <v>20.2362428583874</v>
       </c>
       <c r="F347" t="n">
         <v>8984600</v>
@@ -7732,16 +7732,16 @@
         <v>44286</v>
       </c>
       <c r="B366" t="n">
-        <v>31.08511734008789</v>
+        <v>31.08511924743652</v>
       </c>
       <c r="C366" t="n">
-        <v>32.65904760342265</v>
+        <v>32.65904960734591</v>
       </c>
       <c r="D366" t="n">
-        <v>30.82279682081511</v>
+        <v>30.82279871206804</v>
       </c>
       <c r="E366" t="n">
-        <v>31.95640029207138</v>
+        <v>31.95640225288098</v>
       </c>
       <c r="F366" t="n">
         <v>8195900</v>
@@ -7792,16 +7792,16 @@
         <v>44292</v>
       </c>
       <c r="B369" t="n">
-        <v>30.5792121887207</v>
+        <v>30.57921028137207</v>
       </c>
       <c r="C369" t="n">
-        <v>32.19998498521812</v>
+        <v>32.19998297677536</v>
       </c>
       <c r="D369" t="n">
-        <v>30.48552730465581</v>
+        <v>30.48552540315069</v>
       </c>
       <c r="E369" t="n">
-        <v>31.01953900629401</v>
+        <v>31.01953707148042</v>
       </c>
       <c r="F369" t="n">
         <v>6923500</v>
@@ -7812,16 +7812,16 @@
         <v>44293</v>
       </c>
       <c r="B370" t="n">
-        <v>30.95395660400391</v>
+        <v>30.95395851135254</v>
       </c>
       <c r="C370" t="n">
-        <v>31.36617506706607</v>
+        <v>31.36617699981515</v>
       </c>
       <c r="D370" t="n">
-        <v>30.40120725129495</v>
+        <v>30.40120912458377</v>
       </c>
       <c r="E370" t="n">
-        <v>30.72910789533883</v>
+        <v>30.72910978883253</v>
       </c>
       <c r="F370" t="n">
         <v>4745700</v>
@@ -8012,16 +8012,16 @@
         <v>44308</v>
       </c>
       <c r="B380" t="n">
-        <v>36.30344390869141</v>
+        <v>36.30344772338867</v>
       </c>
       <c r="C380" t="n">
-        <v>38.03663915608288</v>
+        <v>38.03664315290104</v>
       </c>
       <c r="D380" t="n">
-        <v>35.88185481304648</v>
+        <v>35.88185858344396</v>
       </c>
       <c r="E380" t="n">
-        <v>37.12788440974715</v>
+        <v>37.12788831107506</v>
       </c>
       <c r="F380" t="n">
         <v>6756200</v>
@@ -8052,16 +8052,16 @@
         <v>44312</v>
       </c>
       <c r="B382" t="n">
-        <v>35.91933441162109</v>
+        <v>35.91933059692383</v>
       </c>
       <c r="C382" t="n">
-        <v>36.30344817190534</v>
+        <v>36.30344431641451</v>
       </c>
       <c r="D382" t="n">
-        <v>35.51648295890232</v>
+        <v>35.5164791869886</v>
       </c>
       <c r="E382" t="n">
-        <v>35.88185902675205</v>
+        <v>35.88185521603473</v>
       </c>
       <c r="F382" t="n">
         <v>4241900</v>
@@ -8072,16 +8072,16 @@
         <v>44313</v>
       </c>
       <c r="B383" t="n">
-        <v>35.46963500976562</v>
+        <v>35.46963882446289</v>
       </c>
       <c r="C383" t="n">
-        <v>36.2940754796825</v>
+        <v>36.29407938304689</v>
       </c>
       <c r="D383" t="n">
-        <v>35.27289463051181</v>
+        <v>35.27289842405</v>
       </c>
       <c r="E383" t="n">
-        <v>36.05985972137591</v>
+        <v>36.05986359955081</v>
       </c>
       <c r="F383" t="n">
         <v>2386900</v>
@@ -35345,6 +35345,26 @@
       </c>
       <c r="F1746" t="n">
         <v>6714600</v>
+      </c>
+    </row>
+    <row r="1747">
+      <c r="A1747" s="1" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B1747" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="C1747" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="D1747" t="n">
+        <v>3.39</v>
+      </c>
+      <c r="E1747" t="n">
+        <v>3.52</v>
+      </c>
+      <c r="F1747" t="n">
+        <v>8844900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1747"/>
+  <dimension ref="A1:F1748"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799174308776855</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799174308776855</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799174308776855</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799174308776855</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732120513916</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279499769210815</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279499769210815</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279499769210815</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279499769210815</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125653028488159</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125653028488159</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125653028488159</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125651836395264</v>
+        <v>2.125653028488159</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486986160278</v>
+        <v>1.758487105369568</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.83821177482605</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.83821177482605</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.83821177482605</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.83821177482605</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.83821177482605</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.83821177482605</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.83821177482605</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.83821177482605</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647355556488037</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647355556488037</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647355556488037</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647355556488037</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951085567474365</v>
+        <v>6.951085090637207</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951085567474365</v>
+        <v>6.951085090637208</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951085567474365</v>
+        <v>6.951085090637208</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951085567474365</v>
+        <v>6.951085090637208</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780762</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68733310699463</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68733310699463</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68733310699463</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68733310699463</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.014761924743652</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="C64" t="n">
-        <v>9.014761924743652</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="D64" t="n">
-        <v>9.014761924743652</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="E64" t="n">
-        <v>9.014761924743652</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -35352,19 +35352,39 @@
         <v>46308</v>
       </c>
       <c r="B1747" t="n">
-        <v>3.39</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="C1747" t="n">
-        <v>3.72</v>
+        <v>3.720000028610229</v>
       </c>
       <c r="D1747" t="n">
-        <v>3.39</v>
+        <v>3.390000104904175</v>
       </c>
       <c r="E1747" t="n">
-        <v>3.52</v>
+        <v>3.519999980926514</v>
       </c>
       <c r="F1747" t="n">
         <v>8844900</v>
+      </c>
+    </row>
+    <row r="1748">
+      <c r="A1748" s="1" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B1748" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C1748" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="D1748" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="E1748" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="F1748" t="n">
+        <v>6643700</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1748"/>
+  <dimension ref="A1:F1749"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799174308776855</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799174308776855</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799174308776855</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799174308776855</v>
+        <v>1.799173831939697</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132128715515</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132128715515</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132128715515</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132128715515</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132128715515</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132128715515</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132128715515</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132128715515</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132128715515</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132128715515</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132128715515</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132128715515</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616733312606812</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616733312606812</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616733312606812</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616733312606812</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.1523597240448</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125653028488159</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125653028488159</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125653028488159</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125653028488159</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.922460794448853</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.922460794448853</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.922460794448853</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.922460794448853</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.75848650932312</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.75848650932312</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.75848650932312</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758487105369568</v>
+        <v>1.75848650932312</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.83821177482605</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="C40" t="n">
-        <v>1.83821177482605</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="D40" t="n">
-        <v>1.83821177482605</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="E40" t="n">
-        <v>1.83821177482605</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.83821177482605</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="C41" t="n">
-        <v>1.83821177482605</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="D41" t="n">
-        <v>1.83821177482605</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="E41" t="n">
-        <v>1.83821177482605</v>
+        <v>1.838211894035339</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647355556488037</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647355556488037</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647355556488037</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647355556488037</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951085090637207</v>
+        <v>6.951083660125732</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951085090637208</v>
+        <v>6.951083660125732</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951085090637208</v>
+        <v>6.951083660125732</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951085090637208</v>
+        <v>6.951083660125732</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997222900390625</v>
+        <v>6.997223377227783</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997223377227783</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997223377227783</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997223377227783</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370967388153076</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370967388153076</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370967388153076</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370967388153076</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370967388153076</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370967388153076</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370967388153076</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370967388153076</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959037780762</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075627326965332</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988325119018555</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="C64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="D64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="E64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -1832,16 +1832,16 @@
         <v>43684</v>
       </c>
       <c r="B71" t="n">
-        <v>11.66787719726562</v>
+        <v>11.66787815093994</v>
       </c>
       <c r="C71" t="n">
-        <v>11.66787719726562</v>
+        <v>11.66787815093994</v>
       </c>
       <c r="D71" t="n">
-        <v>11.66787719726562</v>
+        <v>11.66787815093994</v>
       </c>
       <c r="E71" t="n">
-        <v>11.66787719726562</v>
+        <v>11.66787815093994</v>
       </c>
       <c r="F71" t="n">
         <v>755</v>
@@ -1872,16 +1872,16 @@
         <v>43741</v>
       </c>
       <c r="B73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F73" t="n">
         <v>755</v>
@@ -1892,16 +1892,16 @@
         <v>43747</v>
       </c>
       <c r="B74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F74" t="n">
         <v>755</v>
@@ -1952,16 +1952,16 @@
         <v>43773</v>
       </c>
       <c r="B77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F77" t="n">
         <v>1510</v>
@@ -2012,16 +2012,16 @@
         <v>43802</v>
       </c>
       <c r="B80" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C80" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D80" t="n">
-        <v>9.217621990355065</v>
+        <v>9.21762282756219</v>
       </c>
       <c r="E80" t="n">
-        <v>9.217621990355065</v>
+        <v>9.21762282756219</v>
       </c>
       <c r="F80" t="n">
         <v>1510</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174577261989849</v>
+        <v>7.174576363958773</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269087350174872</v>
+        <v>7.269086440314109</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759139060974121</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885152239738168</v>
+        <v>7.885151270575596</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395101829362682</v>
+        <v>7.395100920432114</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759139060974121</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198787689209</v>
+        <v>6.731198310852051</v>
       </c>
       <c r="C107" t="n">
-        <v>6.784870504526766</v>
+        <v>6.78487002388751</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975689474925</v>
+        <v>6.183975251402972</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242314420779493</v>
+        <v>6.242313978574833</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642459869384766</v>
+        <v>7.642458915710449</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934156900775253</v>
+        <v>7.934155910701143</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650690466881254</v>
+        <v>6.650689636966175</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242252120494039</v>
+        <v>7.242251216760168</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255535125732</v>
+        <v>7.277255058288574</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292731402749</v>
+        <v>7.641292230712304</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086141684674</v>
+        <v>6.70086097777741</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766202137520195</v>
+        <v>6.766201694169458</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2632,16 +2632,16 @@
         <v>43908</v>
       </c>
       <c r="B111" t="n">
-        <v>6.98555850982666</v>
+        <v>6.985558032989502</v>
       </c>
       <c r="C111" t="n">
-        <v>8.075338544707167</v>
+        <v>8.075337993481165</v>
       </c>
       <c r="D111" t="n">
-        <v>6.71019666955442</v>
+        <v>6.710196211513576</v>
       </c>
       <c r="E111" t="n">
-        <v>7.140741469742403</v>
+        <v>7.140740982312391</v>
       </c>
       <c r="F111" t="n">
         <v>26337960</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738136291503906</v>
+        <v>7.738137245178223</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145345142681279</v>
+        <v>8.145346146541403</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298031292473</v>
+        <v>7.690298979071039</v>
       </c>
       <c r="E117" t="n">
-        <v>8.138343991239532</v>
+        <v>8.13834499423681</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2832,16 +2832,16 @@
         <v>43922</v>
       </c>
       <c r="B121" t="n">
-        <v>7.461607933044434</v>
+        <v>7.461607456207275</v>
       </c>
       <c r="C121" t="n">
-        <v>7.642459684758201</v>
+        <v>7.642459196363636</v>
       </c>
       <c r="D121" t="n">
-        <v>7.304091674358621</v>
+        <v>7.304091207587605</v>
       </c>
       <c r="E121" t="n">
-        <v>7.619124191730246</v>
+        <v>7.619123704826946</v>
       </c>
       <c r="F121" t="n">
         <v>10218288</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582952976226807</v>
+        <v>7.582953929901123</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840814016199421</v>
+        <v>7.840815002303775</v>
       </c>
       <c r="D122" t="n">
-        <v>7.38109946741859</v>
+        <v>7.381100395706687</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455773374392843</v>
+        <v>7.455774312072345</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261936187744</v>
+        <v>7.340261459350586</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624921524582</v>
+        <v>7.622624426344595</v>
       </c>
       <c r="D123" t="n">
-        <v>7.215416044404066</v>
+        <v>7.21541557567713</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457642689852</v>
+        <v>7.621457147585694</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2952,16 +2952,16 @@
         <v>43930</v>
       </c>
       <c r="B127" t="n">
-        <v>7.385766506195068</v>
+        <v>7.38576602935791</v>
       </c>
       <c r="C127" t="n">
-        <v>7.778973921193609</v>
+        <v>7.778973418970338</v>
       </c>
       <c r="D127" t="n">
-        <v>7.351929706227764</v>
+        <v>7.351929231575166</v>
       </c>
       <c r="E127" t="n">
-        <v>7.778973921193609</v>
+        <v>7.778973418970338</v>
       </c>
       <c r="F127" t="n">
         <v>7590081</v>
@@ -2972,16 +2972,16 @@
         <v>43934</v>
       </c>
       <c r="B128" t="n">
-        <v>7.414936065673828</v>
+        <v>7.41493558883667</v>
       </c>
       <c r="C128" t="n">
-        <v>7.447606428031426</v>
+        <v>7.447605949093313</v>
       </c>
       <c r="D128" t="n">
-        <v>7.22941688022938</v>
+        <v>7.229416415322526</v>
       </c>
       <c r="E128" t="n">
-        <v>7.385766699549943</v>
+        <v>7.385766224588598</v>
       </c>
       <c r="F128" t="n">
         <v>8873976</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500111103057861</v>
+        <v>7.500110626220703</v>
       </c>
       <c r="C129" t="n">
-        <v>7.75097100706328</v>
+        <v>7.750970514277116</v>
       </c>
       <c r="D129" t="n">
-        <v>7.45577383571197</v>
+        <v>7.455773361693658</v>
       </c>
       <c r="E129" t="n">
-        <v>7.494278070349739</v>
+        <v>7.49427759388343</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265121459961</v>
+        <v>7.375265598297119</v>
       </c>
       <c r="C130" t="n">
-        <v>7.49427797970812</v>
+        <v>7.494278464239883</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762039125325</v>
+        <v>7.343762513925697</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935482620931</v>
+        <v>7.407935961570344</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.5666184425354</v>
+        <v>7.566619396209717</v>
       </c>
       <c r="C131" t="n">
-        <v>7.588787494454161</v>
+        <v>7.5887884509226</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234083504127451</v>
+        <v>7.234084415890043</v>
       </c>
       <c r="E131" t="n">
-        <v>7.44410543779982</v>
+        <v>7.444106376032958</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251523017883301</v>
+        <v>8.251522064208984</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431208332707222</v>
+        <v>8.431207358265677</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3112,16 +3112,16 @@
         <v>43944</v>
       </c>
       <c r="B135" t="n">
-        <v>8.089340209960938</v>
+        <v>8.089339256286621</v>
       </c>
       <c r="C135" t="n">
-        <v>8.574724018558863</v>
+        <v>8.57472300766133</v>
       </c>
       <c r="D135" t="n">
-        <v>7.969160906424007</v>
+        <v>7.969159966917957</v>
       </c>
       <c r="E135" t="n">
-        <v>8.481380364324728</v>
+        <v>8.481379364431731</v>
       </c>
       <c r="F135" t="n">
         <v>13472583</v>
@@ -3152,16 +3152,16 @@
         <v>43948</v>
       </c>
       <c r="B137" t="n">
-        <v>8.105674743652344</v>
+        <v>8.105673789978027</v>
       </c>
       <c r="C137" t="n">
-        <v>8.165180757388045</v>
+        <v>8.16517979671254</v>
       </c>
       <c r="D137" t="n">
-        <v>7.710134423961201</v>
+        <v>7.710133516824237</v>
       </c>
       <c r="E137" t="n">
-        <v>7.93765801086142</v>
+        <v>7.937657076955135</v>
       </c>
       <c r="F137" t="n">
         <v>12260436</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887483596801758</v>
+        <v>7.887484550476074</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966825772834317</v>
+        <v>7.966826736101882</v>
       </c>
       <c r="D139" t="n">
-        <v>7.700798002265745</v>
+        <v>7.700798933367937</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841979897039702</v>
+        <v>7.841980845212174</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3252,16 +3252,16 @@
         <v>43956</v>
       </c>
       <c r="B142" t="n">
-        <v>8.114090919494629</v>
+        <v>8.114091873168945</v>
       </c>
       <c r="C142" t="n">
-        <v>8.645023715587479</v>
+        <v>8.645024731663977</v>
       </c>
       <c r="D142" t="n">
-        <v>8.069432995707503</v>
+        <v>8.069433944133035</v>
       </c>
       <c r="E142" t="n">
-        <v>8.286520199683441</v>
+        <v>8.286521173623905</v>
       </c>
       <c r="F142" t="n">
         <v>11843548</v>
@@ -3272,16 +3272,16 @@
         <v>43957</v>
       </c>
       <c r="B143" t="n">
-        <v>8.048345565795898</v>
+        <v>8.048344612121582</v>
       </c>
       <c r="C143" t="n">
-        <v>8.145104858936216</v>
+        <v>8.145103893796581</v>
       </c>
       <c r="D143" t="n">
-        <v>7.963991997516411</v>
+        <v>7.96399105383742</v>
       </c>
       <c r="E143" t="n">
-        <v>8.145104858936216</v>
+        <v>8.145103893796581</v>
       </c>
       <c r="F143" t="n">
         <v>16545622</v>
@@ -3312,16 +3312,16 @@
         <v>43959</v>
       </c>
       <c r="B145" t="n">
-        <v>8.162469863891602</v>
+        <v>8.162470817565918</v>
       </c>
       <c r="C145" t="n">
-        <v>8.184799271833279</v>
+        <v>8.184800228116485</v>
       </c>
       <c r="D145" t="n">
-        <v>7.94786381115636</v>
+        <v>7.947864739756858</v>
       </c>
       <c r="E145" t="n">
-        <v>8.15626744912163</v>
+        <v>8.156268402071278</v>
       </c>
       <c r="F145" t="n">
         <v>8818844</v>
@@ -3352,16 +3352,16 @@
         <v>43963</v>
       </c>
       <c r="B147" t="n">
-        <v>8.085558891296387</v>
+        <v>8.085559844970703</v>
       </c>
       <c r="C147" t="n">
-        <v>8.276595411529883</v>
+        <v>8.276596387736546</v>
       </c>
       <c r="D147" t="n">
-        <v>8.063229483236768</v>
+        <v>8.063230434277379</v>
       </c>
       <c r="E147" t="n">
-        <v>8.187279566215866</v>
+        <v>8.187280531887918</v>
       </c>
       <c r="F147" t="n">
         <v>9953957</v>
@@ -3372,16 +3372,16 @@
         <v>43964</v>
       </c>
       <c r="B148" t="n">
-        <v>7.926775455474854</v>
+        <v>7.926775932312012</v>
       </c>
       <c r="C148" t="n">
-        <v>8.187279557292356</v>
+        <v>8.187280049800203</v>
       </c>
       <c r="D148" t="n">
-        <v>7.885839696513885</v>
+        <v>7.885840170888542</v>
       </c>
       <c r="E148" t="n">
-        <v>8.187279557292356</v>
+        <v>8.187280049800203</v>
       </c>
       <c r="F148" t="n">
         <v>10179016</v>
@@ -3412,16 +3412,16 @@
         <v>43966</v>
       </c>
       <c r="B150" t="n">
-        <v>6.8413405418396</v>
+        <v>6.841341018676758</v>
       </c>
       <c r="C150" t="n">
-        <v>7.421893104642092</v>
+        <v>7.421893621943401</v>
       </c>
       <c r="D150" t="n">
-        <v>6.8413405418396</v>
+        <v>6.841341018676758</v>
       </c>
       <c r="E150" t="n">
-        <v>7.420652532303285</v>
+        <v>7.420653049518127</v>
       </c>
       <c r="F150" t="n">
         <v>26563775</v>
@@ -3452,16 +3452,16 @@
         <v>43970</v>
       </c>
       <c r="B152" t="n">
-        <v>6.831418037414551</v>
+        <v>6.831417560577393</v>
       </c>
       <c r="C152" t="n">
-        <v>7.018732418962401</v>
+        <v>7.018731929050585</v>
       </c>
       <c r="D152" t="n">
-        <v>6.79916449333305</v>
+        <v>6.799164018747209</v>
       </c>
       <c r="E152" t="n">
-        <v>6.966631502251738</v>
+        <v>6.966631015976597</v>
       </c>
       <c r="F152" t="n">
         <v>13463520</v>
@@ -3472,16 +3472,16 @@
         <v>43971</v>
       </c>
       <c r="B153" t="n">
-        <v>6.822733879089355</v>
+        <v>6.822733402252197</v>
       </c>
       <c r="C153" t="n">
-        <v>6.983998022077899</v>
+        <v>6.983997533970078</v>
       </c>
       <c r="D153" t="n">
-        <v>6.810329048105121</v>
+        <v>6.81032857213493</v>
       </c>
       <c r="E153" t="n">
-        <v>6.94678397585636</v>
+        <v>6.946783490349408</v>
       </c>
       <c r="F153" t="n">
         <v>11533147</v>
@@ -3552,16 +3552,16 @@
         <v>43977</v>
       </c>
       <c r="B157" t="n">
-        <v>7.423134803771973</v>
+        <v>7.423134326934814</v>
       </c>
       <c r="C157" t="n">
-        <v>7.560829411371671</v>
+        <v>7.560828925689475</v>
       </c>
       <c r="D157" t="n">
-        <v>7.275515169821428</v>
+        <v>7.275514702466858</v>
       </c>
       <c r="E157" t="n">
-        <v>7.442982622817829</v>
+        <v>7.442982144705714</v>
       </c>
       <c r="F157" t="n">
         <v>12080691</v>
@@ -3612,16 +3612,16 @@
         <v>43980</v>
       </c>
       <c r="B160" t="n">
-        <v>7.812650203704834</v>
+        <v>7.812650680541992</v>
       </c>
       <c r="C160" t="n">
-        <v>7.812650203704834</v>
+        <v>7.812650680541992</v>
       </c>
       <c r="D160" t="n">
-        <v>7.481437043617326</v>
+        <v>7.481437500239227</v>
       </c>
       <c r="E160" t="n">
-        <v>7.519892999404318</v>
+        <v>7.519893458373339</v>
       </c>
       <c r="F160" t="n">
         <v>23712019</v>
@@ -3652,16 +3652,16 @@
         <v>43984</v>
       </c>
       <c r="B162" t="n">
-        <v>8.271634101867676</v>
+        <v>8.271635055541992</v>
       </c>
       <c r="C162" t="n">
-        <v>8.286520076241633</v>
+        <v>8.286521031632221</v>
       </c>
       <c r="D162" t="n">
-        <v>7.976395759027911</v>
+        <v>7.976396678662855</v>
       </c>
       <c r="E162" t="n">
-        <v>8.063229567170044</v>
+        <v>8.063230496816454</v>
       </c>
       <c r="F162" t="n">
         <v>21348142</v>
@@ -3672,16 +3672,16 @@
         <v>43985</v>
       </c>
       <c r="B163" t="n">
-        <v>8.373354911804199</v>
+        <v>8.373353958129883</v>
       </c>
       <c r="C163" t="n">
-        <v>8.800086825192951</v>
+        <v>8.80008582291646</v>
       </c>
       <c r="D163" t="n">
-        <v>8.315052026205343</v>
+        <v>8.315051079171372</v>
       </c>
       <c r="E163" t="n">
-        <v>8.317533171149149</v>
+        <v>8.31753222383259</v>
       </c>
       <c r="F163" t="n">
         <v>31125376</v>
@@ -3752,16 +3752,16 @@
         <v>43991</v>
       </c>
       <c r="B167" t="n">
-        <v>8.296442985534668</v>
+        <v>8.296443939208984</v>
       </c>
       <c r="C167" t="n">
-        <v>8.327455953773208</v>
+        <v>8.32745691101246</v>
       </c>
       <c r="D167" t="n">
-        <v>8.096723794435762</v>
+        <v>8.0967247251524</v>
       </c>
       <c r="E167" t="n">
-        <v>8.137660447910266</v>
+        <v>8.137661383332564</v>
       </c>
       <c r="F167" t="n">
         <v>13675741</v>
@@ -3772,16 +3772,16 @@
         <v>43992</v>
       </c>
       <c r="B168" t="n">
-        <v>8.08928108215332</v>
+        <v>8.089280128479004</v>
       </c>
       <c r="C168" t="n">
-        <v>8.426697131827968</v>
+        <v>8.426696138374464</v>
       </c>
       <c r="D168" t="n">
-        <v>8.0371806131882</v>
+        <v>8.037179665656195</v>
       </c>
       <c r="E168" t="n">
-        <v>8.311330595134894</v>
+        <v>8.311329615282364</v>
       </c>
       <c r="F168" t="n">
         <v>11944749</v>
@@ -3792,16 +3792,16 @@
         <v>43994</v>
       </c>
       <c r="B169" t="n">
-        <v>7.950345993041992</v>
+        <v>7.950345516204834</v>
       </c>
       <c r="C169" t="n">
-        <v>8.084319777785</v>
+        <v>8.084319292912509</v>
       </c>
       <c r="D169" t="n">
-        <v>7.774195424975465</v>
+        <v>7.774194958703272</v>
       </c>
       <c r="E169" t="n">
-        <v>7.877157131822456</v>
+        <v>7.877156659374939</v>
       </c>
       <c r="F169" t="n">
         <v>12251373</v>
@@ -3892,16 +3892,16 @@
         <v>44001</v>
       </c>
       <c r="B174" t="n">
-        <v>8.487480163574219</v>
+        <v>8.487481117248535</v>
       </c>
       <c r="C174" t="n">
-        <v>8.589200838114557</v>
+        <v>8.58920180321846</v>
       </c>
       <c r="D174" t="n">
-        <v>8.203406528896336</v>
+        <v>8.203407450651435</v>
       </c>
       <c r="E174" t="n">
-        <v>8.203406528896336</v>
+        <v>8.203407450651435</v>
       </c>
       <c r="F174" t="n">
         <v>20750754</v>
@@ -3912,16 +3912,16 @@
         <v>44004</v>
       </c>
       <c r="B175" t="n">
-        <v>8.440342903137207</v>
+        <v>8.440341949462891</v>
       </c>
       <c r="C175" t="n">
-        <v>8.729377964833343</v>
+        <v>8.729376978500955</v>
       </c>
       <c r="D175" t="n">
-        <v>8.380798106578508</v>
+        <v>8.380797159632158</v>
       </c>
       <c r="E175" t="n">
-        <v>8.489962226742637</v>
+        <v>8.489961267461833</v>
       </c>
       <c r="F175" t="n">
         <v>12069362</v>
@@ -3952,16 +3952,16 @@
         <v>44006</v>
       </c>
       <c r="B177" t="n">
-        <v>8.594162940979004</v>
+        <v>8.59416389465332</v>
       </c>
       <c r="C177" t="n">
-        <v>8.669832935726904</v>
+        <v>8.669833897798144</v>
       </c>
       <c r="D177" t="n">
-        <v>8.422973795079262</v>
+        <v>8.422974729757115</v>
       </c>
       <c r="E177" t="n">
-        <v>8.571833533486773</v>
+        <v>8.571834484683247</v>
       </c>
       <c r="F177" t="n">
         <v>7388434</v>
@@ -4052,16 +4052,16 @@
         <v>44013</v>
       </c>
       <c r="B182" t="n">
-        <v>9.009730339050293</v>
+        <v>9.009729385375977</v>
       </c>
       <c r="C182" t="n">
-        <v>9.11517229493286</v>
+        <v>9.115171330097578</v>
       </c>
       <c r="D182" t="n">
-        <v>8.731859089723871</v>
+        <v>8.731858165462054</v>
       </c>
       <c r="E182" t="n">
-        <v>8.812491383860499</v>
+        <v>8.812490451063802</v>
       </c>
       <c r="F182" t="n">
         <v>8963093</v>
@@ -4292,16 +4292,16 @@
         <v>44029</v>
       </c>
       <c r="B194" t="n">
-        <v>8.81993293762207</v>
+        <v>8.819933891296387</v>
       </c>
       <c r="C194" t="n">
-        <v>8.919173360420668</v>
+        <v>8.919174324825571</v>
       </c>
       <c r="D194" t="n">
-        <v>8.633858708433587</v>
+        <v>8.633859641988225</v>
       </c>
       <c r="E194" t="n">
-        <v>8.633858708433587</v>
+        <v>8.633859641988225</v>
       </c>
       <c r="F194" t="n">
         <v>9678298</v>
@@ -4432,16 +4432,16 @@
         <v>44040</v>
       </c>
       <c r="B201" t="n">
-        <v>9.641143798828125</v>
+        <v>9.641142845153809</v>
       </c>
       <c r="C201" t="n">
-        <v>9.832180339834917</v>
+        <v>9.832179367263814</v>
       </c>
       <c r="D201" t="n">
-        <v>9.466233359369541</v>
+        <v>9.466232422996864</v>
       </c>
       <c r="E201" t="n">
-        <v>9.675878040270206</v>
+        <v>9.67587708316008</v>
       </c>
       <c r="F201" t="n">
         <v>30127714</v>
@@ -4472,16 +4472,16 @@
         <v>44042</v>
       </c>
       <c r="B203" t="n">
-        <v>9.143704414367676</v>
+        <v>9.143703460693359</v>
       </c>
       <c r="C203" t="n">
-        <v>9.700687950073165</v>
+        <v>9.700686938306321</v>
       </c>
       <c r="D203" t="n">
-        <v>9.097806359971171</v>
+        <v>9.097805411083952</v>
       </c>
       <c r="E203" t="n">
-        <v>9.685801080392711</v>
+        <v>9.685800070178546</v>
       </c>
       <c r="F203" t="n">
         <v>33272500</v>
@@ -4592,16 +4592,16 @@
         <v>44050</v>
       </c>
       <c r="B209" t="n">
-        <v>8.429177284240723</v>
+        <v>8.429178237915039</v>
       </c>
       <c r="C209" t="n">
-        <v>8.429177284240723</v>
+        <v>8.429178237915039</v>
       </c>
       <c r="D209" t="n">
-        <v>8.255506990060143</v>
+        <v>8.25550792408546</v>
       </c>
       <c r="E209" t="n">
-        <v>8.336140169103194</v>
+        <v>8.336141112251321</v>
       </c>
       <c r="F209" t="n">
         <v>22110172</v>
@@ -4612,16 +4612,16 @@
         <v>44053</v>
       </c>
       <c r="B210" t="n">
-        <v>8.259230613708496</v>
+        <v>8.25922966003418</v>
       </c>
       <c r="C210" t="n">
-        <v>8.468874414585619</v>
+        <v>8.468873436704216</v>
       </c>
       <c r="D210" t="n">
-        <v>8.166192588662099</v>
+        <v>8.166191645730668</v>
       </c>
       <c r="E210" t="n">
-        <v>8.435380296706972</v>
+        <v>8.435379322693057</v>
       </c>
       <c r="F210" t="n">
         <v>21920608</v>
@@ -4652,16 +4652,16 @@
         <v>44055</v>
       </c>
       <c r="B212" t="n">
-        <v>8.162469863891602</v>
+        <v>8.162470817565918</v>
       </c>
       <c r="C212" t="n">
-        <v>8.446543498127859</v>
+        <v>8.446544484992341</v>
       </c>
       <c r="D212" t="n">
-        <v>8.078115414787984</v>
+        <v>8.078116358606623</v>
       </c>
       <c r="E212" t="n">
-        <v>8.409329009508031</v>
+        <v>8.409329992024503</v>
       </c>
       <c r="F212" t="n">
         <v>20200945</v>
@@ -4732,16 +4732,16 @@
         <v>44061</v>
       </c>
       <c r="B216" t="n">
-        <v>8.101686477661133</v>
+        <v>8.101685523986816</v>
       </c>
       <c r="C216" t="n">
-        <v>8.143864156905972</v>
+        <v>8.143863198266791</v>
       </c>
       <c r="D216" t="n">
-        <v>7.9788782846482</v>
+        <v>7.978877345430011</v>
       </c>
       <c r="E216" t="n">
-        <v>8.038421298987467</v>
+        <v>8.038420352760289</v>
       </c>
       <c r="F216" t="n">
         <v>10608743</v>
@@ -4752,16 +4752,16 @@
         <v>44062</v>
       </c>
       <c r="B217" t="n">
-        <v>7.926775455474854</v>
+        <v>7.926775932312012</v>
       </c>
       <c r="C217" t="n">
-        <v>8.141381509109719</v>
+        <v>8.141381998856557</v>
       </c>
       <c r="D217" t="n">
-        <v>7.921813166253184</v>
+        <v>7.921813642791834</v>
       </c>
       <c r="E217" t="n">
-        <v>8.141381509109719</v>
+        <v>8.141381998856557</v>
       </c>
       <c r="F217" t="n">
         <v>9466833</v>
@@ -4772,16 +4772,16 @@
         <v>44063</v>
       </c>
       <c r="B218" t="n">
-        <v>7.957788467407227</v>
+        <v>7.957787990570068</v>
       </c>
       <c r="C218" t="n">
-        <v>8.033459366376674</v>
+        <v>8.033458885005254</v>
       </c>
       <c r="D218" t="n">
-        <v>7.774195359575069</v>
+        <v>7.774194893738959</v>
       </c>
       <c r="E218" t="n">
-        <v>7.915611684438519</v>
+        <v>7.915611210128628</v>
       </c>
       <c r="F218" t="n">
         <v>7652765</v>
@@ -4892,16 +4892,16 @@
         <v>44071</v>
       </c>
       <c r="B224" t="n">
-        <v>8.100445747375488</v>
+        <v>8.100444793701172</v>
       </c>
       <c r="C224" t="n">
-        <v>8.100445747375488</v>
+        <v>8.100444793701172</v>
       </c>
       <c r="D224" t="n">
-        <v>7.960269549341362</v>
+        <v>7.960268612170143</v>
       </c>
       <c r="E224" t="n">
-        <v>8.0012070997281</v>
+        <v>8.001206157737258</v>
       </c>
       <c r="F224" t="n">
         <v>5577388</v>
@@ -5012,16 +5012,16 @@
         <v>44082</v>
       </c>
       <c r="B230" t="n">
-        <v>7.751865863800049</v>
+        <v>7.751865386962891</v>
       </c>
       <c r="C230" t="n">
-        <v>7.833738283935308</v>
+        <v>7.833737802061967</v>
       </c>
       <c r="D230" t="n">
-        <v>7.691081834917614</v>
+        <v>7.691081361819436</v>
       </c>
       <c r="E230" t="n">
-        <v>7.813890911851665</v>
+        <v>7.813890431199186</v>
       </c>
       <c r="F230" t="n">
         <v>7181501</v>
@@ -5032,16 +5032,16 @@
         <v>44083</v>
       </c>
       <c r="B231" t="n">
-        <v>7.709688663482666</v>
+        <v>7.709689140319824</v>
       </c>
       <c r="C231" t="n">
-        <v>7.834979771965168</v>
+        <v>7.834980256551466</v>
       </c>
       <c r="D231" t="n">
-        <v>7.637739933288351</v>
+        <v>7.637740405675546</v>
       </c>
       <c r="E231" t="n">
-        <v>7.792802098282933</v>
+        <v>7.792802580260581</v>
       </c>
       <c r="F231" t="n">
         <v>8282629</v>
@@ -5052,16 +5052,16 @@
         <v>44084</v>
       </c>
       <c r="B232" t="n">
-        <v>8.850947380065918</v>
+        <v>8.850946426391602</v>
       </c>
       <c r="C232" t="n">
-        <v>9.197045218135978</v>
+        <v>9.197044227170217</v>
       </c>
       <c r="D232" t="n">
-        <v>8.621455315968662</v>
+        <v>8.62145438702172</v>
       </c>
       <c r="E232" t="n">
-        <v>9.197045218135978</v>
+        <v>9.197044227170217</v>
       </c>
       <c r="F232" t="n">
         <v>139609921</v>
@@ -5132,16 +5132,16 @@
         <v>44090</v>
       </c>
       <c r="B236" t="n">
-        <v>9.312410354614258</v>
+        <v>9.312411308288574</v>
       </c>
       <c r="C236" t="n">
-        <v>9.375675522060035</v>
+        <v>9.375676482213272</v>
       </c>
       <c r="D236" t="n">
-        <v>9.175956334671081</v>
+        <v>9.175957274371282</v>
       </c>
       <c r="E236" t="n">
-        <v>9.179677604882659</v>
+        <v>9.179678544963952</v>
       </c>
       <c r="F236" t="n">
         <v>13993693</v>
@@ -5212,16 +5212,16 @@
         <v>44096</v>
       </c>
       <c r="B240" t="n">
-        <v>9.326058387756348</v>
+        <v>9.326057434082031</v>
       </c>
       <c r="C240" t="n">
-        <v>9.353349195522698</v>
+        <v>9.353348239057649</v>
       </c>
       <c r="D240" t="n">
-        <v>9.182159127084132</v>
+        <v>9.182158188124824</v>
       </c>
       <c r="E240" t="n">
-        <v>9.192083706971793</v>
+        <v>9.192082766997606</v>
       </c>
       <c r="F240" t="n">
         <v>9315031</v>
@@ -5232,16 +5232,16 @@
         <v>44097</v>
       </c>
       <c r="B241" t="n">
-        <v>8.95390796661377</v>
+        <v>8.953908920288086</v>
       </c>
       <c r="C241" t="n">
-        <v>9.308689320943529</v>
+        <v>9.308690312405352</v>
       </c>
       <c r="D241" t="n">
-        <v>8.934059702543932</v>
+        <v>8.934060654104224</v>
       </c>
       <c r="E241" t="n">
-        <v>9.303727925022763</v>
+        <v>9.303728915956151</v>
       </c>
       <c r="F241" t="n">
         <v>13677251</v>
@@ -5252,16 +5252,16 @@
         <v>44098</v>
       </c>
       <c r="B242" t="n">
-        <v>9.282639503479004</v>
+        <v>9.282638549804688</v>
       </c>
       <c r="C242" t="n">
-        <v>9.46375236122295</v>
+        <v>9.463751388941567</v>
       </c>
       <c r="D242" t="n">
-        <v>8.898085270619518</v>
+        <v>8.898084356453305</v>
       </c>
       <c r="E242" t="n">
-        <v>8.906769724577019</v>
+        <v>8.906768809518589</v>
       </c>
       <c r="F242" t="n">
         <v>18607406</v>
@@ -5272,16 +5272,16 @@
         <v>44099</v>
       </c>
       <c r="B243" t="n">
-        <v>9.184640884399414</v>
+        <v>9.184639930725098</v>
       </c>
       <c r="C243" t="n">
-        <v>9.254108474175018</v>
+        <v>9.25410751328763</v>
       </c>
       <c r="D243" t="n">
-        <v>9.095325028918353</v>
+        <v>9.095324084518023</v>
       </c>
       <c r="E243" t="n">
-        <v>9.22061435827287</v>
+        <v>9.220613400863298</v>
       </c>
       <c r="F243" t="n">
         <v>8201819</v>
@@ -5312,16 +5312,16 @@
         <v>44103</v>
       </c>
       <c r="B245" t="n">
-        <v>8.760390281677246</v>
+        <v>8.760391235351562</v>
       </c>
       <c r="C245" t="n">
-        <v>8.942743247933565</v>
+        <v>8.942744221459206</v>
       </c>
       <c r="D245" t="n">
-        <v>8.683479263674647</v>
+        <v>8.68348020897627</v>
       </c>
       <c r="E245" t="n">
-        <v>8.802567060978735</v>
+        <v>8.802568019244504</v>
       </c>
       <c r="F245" t="n">
         <v>13985386</v>
@@ -5332,16 +5332,16 @@
         <v>44104</v>
       </c>
       <c r="B246" t="n">
-        <v>8.651226997375488</v>
+        <v>8.651226043701172</v>
       </c>
       <c r="C246" t="n">
-        <v>8.841023415853394</v>
+        <v>8.841022441256731</v>
       </c>
       <c r="D246" t="n">
-        <v>8.609050214038696</v>
+        <v>8.609049265013768</v>
       </c>
       <c r="E246" t="n">
-        <v>8.803808028904122</v>
+        <v>8.803807058409923</v>
       </c>
       <c r="F246" t="n">
         <v>11477260</v>
@@ -5412,16 +5412,16 @@
         <v>44110</v>
       </c>
       <c r="B250" t="n">
-        <v>8.497404098510742</v>
+        <v>8.497405052185059</v>
       </c>
       <c r="C250" t="n">
-        <v>8.520973632751547</v>
+        <v>8.520974589071102</v>
       </c>
       <c r="D250" t="n">
-        <v>8.3162921520784</v>
+        <v>8.316293085426295</v>
       </c>
       <c r="E250" t="n">
-        <v>8.48872053887138</v>
+        <v>8.488721491571129</v>
       </c>
       <c r="F250" t="n">
         <v>10544549</v>
@@ -5432,16 +5432,16 @@
         <v>44111</v>
       </c>
       <c r="B251" t="n">
-        <v>8.585479736328125</v>
+        <v>8.585480690002441</v>
       </c>
       <c r="C251" t="n">
-        <v>8.704567531971968</v>
+        <v>8.704568498874545</v>
       </c>
       <c r="D251" t="n">
-        <v>8.440342155483876</v>
+        <v>8.440343093036322</v>
       </c>
       <c r="E251" t="n">
-        <v>8.477556644891454</v>
+        <v>8.477557586577683</v>
       </c>
       <c r="F251" t="n">
         <v>12680345</v>
@@ -5552,16 +5552,16 @@
         <v>44120</v>
       </c>
       <c r="B257" t="n">
-        <v>8.259230613708496</v>
+        <v>8.25922966003418</v>
       </c>
       <c r="C257" t="n">
-        <v>8.267913281163274</v>
+        <v>8.267912326486389</v>
       </c>
       <c r="D257" t="n">
-        <v>8.097965120577188</v>
+        <v>8.097964185523827</v>
       </c>
       <c r="E257" t="n">
-        <v>8.122775677538673</v>
+        <v>8.122774739620494</v>
       </c>
       <c r="F257" t="n">
         <v>10726560</v>
@@ -5612,16 +5612,16 @@
         <v>44125</v>
       </c>
       <c r="B260" t="n">
-        <v>8.275356292724609</v>
+        <v>8.275355339050293</v>
       </c>
       <c r="C260" t="n">
-        <v>8.355988588431988</v>
+        <v>8.355987625465389</v>
       </c>
       <c r="D260" t="n">
-        <v>8.245584340664582</v>
+        <v>8.245583390421267</v>
       </c>
       <c r="E260" t="n">
-        <v>8.35474846270546</v>
+        <v>8.354747499881778</v>
       </c>
       <c r="F260" t="n">
         <v>4665068</v>
@@ -5632,16 +5632,16 @@
         <v>44126</v>
       </c>
       <c r="B261" t="n">
-        <v>8.267912864685059</v>
+        <v>8.267911911010742</v>
       </c>
       <c r="C261" t="n">
-        <v>8.337381348523031</v>
+        <v>8.337380386835774</v>
       </c>
       <c r="D261" t="n">
-        <v>8.168674215687588</v>
+        <v>8.168673273460097</v>
       </c>
       <c r="E261" t="n">
-        <v>8.306368377248981</v>
+        <v>8.30636741913896</v>
       </c>
       <c r="F261" t="n">
         <v>7908034</v>
@@ -5652,16 +5652,16 @@
         <v>44127</v>
       </c>
       <c r="B262" t="n">
-        <v>8.234420776367188</v>
+        <v>8.234419822692871</v>
       </c>
       <c r="C262" t="n">
-        <v>8.312571929509362</v>
+        <v>8.312570966783923</v>
       </c>
       <c r="D262" t="n">
-        <v>8.203407804185662</v>
+        <v>8.203406854103131</v>
       </c>
       <c r="E262" t="n">
-        <v>8.269153232377807</v>
+        <v>8.269152274680931</v>
       </c>
       <c r="F262" t="n">
         <v>5098571</v>
@@ -5712,16 +5712,16 @@
         <v>44132</v>
       </c>
       <c r="B265" t="n">
-        <v>7.825055122375488</v>
+        <v>7.825055599212646</v>
       </c>
       <c r="C265" t="n">
-        <v>8.088040380288025</v>
+        <v>8.088040873150774</v>
       </c>
       <c r="D265" t="n">
-        <v>7.81761168821794</v>
+        <v>7.817612164601516</v>
       </c>
       <c r="E265" t="n">
-        <v>8.078115801411293</v>
+        <v>8.078116293669268</v>
       </c>
       <c r="F265" t="n">
         <v>12369944</v>
@@ -5752,16 +5752,16 @@
         <v>44134</v>
       </c>
       <c r="B267" t="n">
-        <v>7.684879302978516</v>
+        <v>7.684878826141357</v>
       </c>
       <c r="C267" t="n">
-        <v>7.777916426914608</v>
+        <v>7.777915944304612</v>
       </c>
       <c r="D267" t="n">
-        <v>7.574475058635726</v>
+        <v>7.574474588649013</v>
       </c>
       <c r="E267" t="n">
-        <v>7.759309180819852</v>
+        <v>7.759308699364413</v>
       </c>
       <c r="F267" t="n">
         <v>16269207</v>
@@ -5772,16 +5772,16 @@
         <v>44138</v>
       </c>
       <c r="B268" t="n">
-        <v>7.7171311378479</v>
+        <v>7.717131614685059</v>
       </c>
       <c r="C268" t="n">
-        <v>7.852345930671059</v>
+        <v>7.852346415863062</v>
       </c>
       <c r="D268" t="n">
-        <v>7.622853892715106</v>
+        <v>7.622854363726927</v>
       </c>
       <c r="E268" t="n">
-        <v>7.821333855323877</v>
+        <v>7.821334338599661</v>
       </c>
       <c r="F268" t="n">
         <v>9901091</v>
@@ -5812,16 +5812,16 @@
         <v>44140</v>
       </c>
       <c r="B270" t="n">
-        <v>8.119052886962891</v>
+        <v>8.119053840637207</v>
       </c>
       <c r="C270" t="n">
-        <v>8.177355763964984</v>
+        <v>8.177356724487632</v>
       </c>
       <c r="D270" t="n">
-        <v>8.007407635190189</v>
+        <v>8.007408575750512</v>
       </c>
       <c r="E270" t="n">
-        <v>8.039660727779241</v>
+        <v>8.039661672128053</v>
       </c>
       <c r="F270" t="n">
         <v>9820281</v>
@@ -5892,16 +5892,16 @@
         <v>44146</v>
       </c>
       <c r="B274" t="n">
-        <v>8.193482398986816</v>
+        <v>8.193483352661133</v>
       </c>
       <c r="C274" t="n">
-        <v>8.420493294041393</v>
+        <v>8.420494274138473</v>
       </c>
       <c r="D274" t="n">
-        <v>8.193482398986816</v>
+        <v>8.193483352661133</v>
       </c>
       <c r="E274" t="n">
-        <v>8.312571092276054</v>
+        <v>8.312572059811611</v>
       </c>
       <c r="F274" t="n">
         <v>7246451</v>
@@ -5912,16 +5912,16 @@
         <v>44147</v>
       </c>
       <c r="B275" t="n">
-        <v>8.234420776367188</v>
+        <v>8.234419822692871</v>
       </c>
       <c r="C275" t="n">
-        <v>8.398165624159189</v>
+        <v>8.398164651520666</v>
       </c>
       <c r="D275" t="n">
-        <v>8.13145906678732</v>
+        <v>8.131458125037573</v>
       </c>
       <c r="E275" t="n">
-        <v>8.193483224225638</v>
+        <v>8.193482275292528</v>
       </c>
       <c r="F275" t="n">
         <v>11697033</v>
@@ -5932,16 +5932,16 @@
         <v>44148</v>
       </c>
       <c r="B276" t="n">
-        <v>8.633859634399414</v>
+        <v>8.633858680725098</v>
       </c>
       <c r="C276" t="n">
-        <v>8.646265358676397</v>
+        <v>8.646264403631776</v>
       </c>
       <c r="D276" t="n">
-        <v>8.267912658055211</v>
+        <v>8.267911744802472</v>
       </c>
       <c r="E276" t="n">
-        <v>8.322494271024663</v>
+        <v>8.322493351742979</v>
       </c>
       <c r="F276" t="n">
         <v>10854949</v>
@@ -5992,16 +5992,16 @@
         <v>44153</v>
       </c>
       <c r="B279" t="n">
-        <v>8.584240913391113</v>
+        <v>8.584239959716797</v>
       </c>
       <c r="C279" t="n">
-        <v>8.645024946032365</v>
+        <v>8.64502398560519</v>
       </c>
       <c r="D279" t="n">
-        <v>8.516013445661457</v>
+        <v>8.516012499566937</v>
       </c>
       <c r="E279" t="n">
-        <v>8.558190230775271</v>
+        <v>8.55818927999508</v>
       </c>
       <c r="F279" t="n">
         <v>8922310</v>
@@ -6072,16 +6072,16 @@
         <v>44160</v>
       </c>
       <c r="B283" t="n">
-        <v>8.739302635192871</v>
+        <v>8.739301681518555</v>
       </c>
       <c r="C283" t="n">
-        <v>8.920414597775554</v>
+        <v>8.920413624337439</v>
       </c>
       <c r="D283" t="n">
-        <v>8.616492663682914</v>
+        <v>8.616491723410208</v>
       </c>
       <c r="E283" t="n">
-        <v>8.85466827854489</v>
+        <v>8.854667312281327</v>
       </c>
       <c r="F283" t="n">
         <v>6633202</v>
@@ -6112,16 +6112,16 @@
         <v>44162</v>
       </c>
       <c r="B285" t="n">
-        <v>8.615252494812012</v>
+        <v>8.615251541137695</v>
       </c>
       <c r="C285" t="n">
-        <v>8.708288727073548</v>
+        <v>8.70828776310049</v>
       </c>
       <c r="D285" t="n">
-        <v>8.507329393233835</v>
+        <v>8.507328451506179</v>
       </c>
       <c r="E285" t="n">
-        <v>8.566872403188754</v>
+        <v>8.566871454869922</v>
       </c>
       <c r="F285" t="n">
         <v>5230736</v>
@@ -6152,16 +6152,16 @@
         <v>44166</v>
       </c>
       <c r="B287" t="n">
-        <v>8.414292335510254</v>
+        <v>8.414291381835938</v>
       </c>
       <c r="C287" t="n">
-        <v>8.672315323428652</v>
+        <v>8.672314340510058</v>
       </c>
       <c r="D287" t="n">
-        <v>8.360949953683695</v>
+        <v>8.360949006055193</v>
       </c>
       <c r="E287" t="n">
-        <v>8.636340955945199</v>
+        <v>8.636339977103933</v>
       </c>
       <c r="F287" t="n">
         <v>16096259</v>
@@ -6172,16 +6172,16 @@
         <v>44167</v>
       </c>
       <c r="B288" t="n">
-        <v>8.282798767089844</v>
+        <v>8.282797813415527</v>
       </c>
       <c r="C288" t="n">
-        <v>8.4614304780068</v>
+        <v>8.461429503764982</v>
       </c>
       <c r="D288" t="n">
-        <v>8.199686220600897</v>
+        <v>8.199685276496087</v>
       </c>
       <c r="E288" t="n">
-        <v>8.456469081678438</v>
+        <v>8.456468108007872</v>
       </c>
       <c r="F288" t="n">
         <v>15329699</v>
@@ -6212,16 +6212,16 @@
         <v>44169</v>
       </c>
       <c r="B290" t="n">
-        <v>8.772794723510742</v>
+        <v>8.772793769836426</v>
       </c>
       <c r="C290" t="n">
-        <v>8.948945284925747</v>
+        <v>8.948944312102428</v>
       </c>
       <c r="D290" t="n">
-        <v>8.683479763850318</v>
+        <v>8.683478819885265</v>
       </c>
       <c r="E290" t="n">
-        <v>8.886920238013465</v>
+        <v>8.886919271932774</v>
       </c>
       <c r="F290" t="n">
         <v>10446369</v>
@@ -6232,16 +6232,16 @@
         <v>44172</v>
       </c>
       <c r="B291" t="n">
-        <v>8.647504806518555</v>
+        <v>8.647505760192871</v>
       </c>
       <c r="C291" t="n">
-        <v>8.827376626156168</v>
+        <v>8.82737759966732</v>
       </c>
       <c r="D291" t="n">
-        <v>8.621454127772409</v>
+        <v>8.621455078573774</v>
       </c>
       <c r="E291" t="n">
-        <v>8.807528362331166</v>
+        <v>8.807529333653388</v>
       </c>
       <c r="F291" t="n">
         <v>10174485</v>
@@ -6392,16 +6392,16 @@
         <v>44182</v>
       </c>
       <c r="B299" t="n">
-        <v>9.125097274780273</v>
+        <v>9.125096321105957</v>
       </c>
       <c r="C299" t="n">
-        <v>9.233020380265208</v>
+        <v>9.233019415311725</v>
       </c>
       <c r="D299" t="n">
-        <v>9.105249008435251</v>
+        <v>9.1052480568353</v>
       </c>
       <c r="E299" t="n">
-        <v>9.230539235289285</v>
+        <v>9.230538270595108</v>
       </c>
       <c r="F299" t="n">
         <v>5262456</v>
@@ -6452,16 +6452,16 @@
         <v>44187</v>
       </c>
       <c r="B302" t="n">
-        <v>9.018414497375488</v>
+        <v>9.018413543701172</v>
       </c>
       <c r="C302" t="n">
-        <v>9.117654044402261</v>
+        <v>9.117653080233614</v>
       </c>
       <c r="D302" t="n">
-        <v>8.941504362170608</v>
+        <v>8.941503416629342</v>
       </c>
       <c r="E302" t="n">
-        <v>8.974996692978687</v>
+        <v>8.974995743895692</v>
       </c>
       <c r="F302" t="n">
         <v>3700636</v>
@@ -6572,16 +6572,16 @@
         <v>44201</v>
       </c>
       <c r="B308" t="n">
-        <v>9.097805976867676</v>
+        <v>9.097805023193359</v>
       </c>
       <c r="C308" t="n">
-        <v>9.304968615993069</v>
+        <v>9.304967640603</v>
       </c>
       <c r="D308" t="n">
-        <v>9.012211393852336</v>
+        <v>9.012210449150441</v>
       </c>
       <c r="E308" t="n">
-        <v>9.304968615993069</v>
+        <v>9.304967640603</v>
       </c>
       <c r="F308" t="n">
         <v>8306796</v>
@@ -6592,16 +6592,16 @@
         <v>44202</v>
       </c>
       <c r="B309" t="n">
-        <v>9.023375511169434</v>
+        <v>9.02337646484375</v>
       </c>
       <c r="C309" t="n">
-        <v>9.178437672356514</v>
+        <v>9.178438642419241</v>
       </c>
       <c r="D309" t="n">
-        <v>8.883199324604012</v>
+        <v>8.883200263463204</v>
       </c>
       <c r="E309" t="n">
-        <v>9.091602075844966</v>
+        <v>9.091603036730099</v>
       </c>
       <c r="F309" t="n">
         <v>6995714</v>
@@ -6632,16 +6632,16 @@
         <v>44204</v>
       </c>
       <c r="B311" t="n">
-        <v>9.49476432800293</v>
+        <v>9.494765281677246</v>
       </c>
       <c r="C311" t="n">
-        <v>9.533219836566508</v>
+        <v>9.533220794103377</v>
       </c>
       <c r="D311" t="n">
-        <v>9.077957042182957</v>
+        <v>9.077957953992263</v>
       </c>
       <c r="E311" t="n">
-        <v>9.178437593380119</v>
+        <v>9.178438515281906</v>
       </c>
       <c r="F311" t="n">
         <v>10280973</v>
@@ -6732,16 +6732,16 @@
         <v>44211</v>
       </c>
       <c r="B316" t="n">
-        <v>9.479877471923828</v>
+        <v>9.479878425598145</v>
       </c>
       <c r="C316" t="n">
-        <v>9.607648827608905</v>
+        <v>9.607649794137002</v>
       </c>
       <c r="D316" t="n">
-        <v>9.378157688462947</v>
+        <v>9.378158631904267</v>
       </c>
       <c r="E316" t="n">
-        <v>9.589041582834192</v>
+        <v>9.589042547490402</v>
       </c>
       <c r="F316" t="n">
         <v>14334303</v>
@@ -6892,16 +6892,16 @@
         <v>44224</v>
       </c>
       <c r="B324" t="n">
-        <v>9.368233680725098</v>
+        <v>9.368232727050781</v>
       </c>
       <c r="C324" t="n">
-        <v>9.399245757239534</v>
+        <v>9.399244800408228</v>
       </c>
       <c r="D324" t="n">
-        <v>9.102767267989694</v>
+        <v>9.102766341339521</v>
       </c>
       <c r="E324" t="n">
-        <v>9.180918415575915</v>
+        <v>9.180917480970056</v>
       </c>
       <c r="F324" t="n">
         <v>7429217</v>
@@ -6912,16 +6912,16 @@
         <v>44225</v>
       </c>
       <c r="B325" t="n">
-        <v>9.36327075958252</v>
+        <v>9.363271713256836</v>
       </c>
       <c r="C325" t="n">
-        <v>9.571675294860224</v>
+        <v>9.571676269761104</v>
       </c>
       <c r="D325" t="n">
-        <v>9.215652034482874</v>
+        <v>9.215652973121827</v>
       </c>
       <c r="E325" t="n">
-        <v>9.312410421451789</v>
+        <v>9.312411369945844</v>
       </c>
       <c r="F325" t="n">
         <v>11022611</v>
@@ -6952,16 +6952,16 @@
         <v>44229</v>
       </c>
       <c r="B327" t="n">
-        <v>10.133620262146</v>
+        <v>10.13361930847168</v>
       </c>
       <c r="C327" t="n">
-        <v>10.18448060527895</v>
+        <v>10.18447964681817</v>
       </c>
       <c r="D327" t="n">
-        <v>9.832180367414875</v>
+        <v>9.832179442109044</v>
       </c>
       <c r="E327" t="n">
-        <v>10.11005072588166</v>
+        <v>10.11004977442547</v>
       </c>
       <c r="F327" t="n">
         <v>20046878</v>
@@ -6992,16 +6992,16 @@
         <v>44231</v>
       </c>
       <c r="B329" t="n">
-        <v>10.38668155670166</v>
+        <v>10.38668251037598</v>
       </c>
       <c r="C329" t="n">
-        <v>10.38668155670166</v>
+        <v>10.38668251037598</v>
       </c>
       <c r="D329" t="n">
-        <v>10.11749300250636</v>
+        <v>10.11749393146458</v>
       </c>
       <c r="E329" t="n">
-        <v>10.17703779267104</v>
+        <v>10.17703872709649</v>
       </c>
       <c r="F329" t="n">
         <v>12166787</v>
@@ -7012,16 +7012,16 @@
         <v>44232</v>
       </c>
       <c r="B330" t="n">
-        <v>10.5566291809082</v>
+        <v>10.55663013458252</v>
       </c>
       <c r="C330" t="n">
-        <v>10.58143973441847</v>
+        <v>10.58144069033415</v>
       </c>
       <c r="D330" t="n">
-        <v>10.32465689384235</v>
+        <v>10.32465782656054</v>
       </c>
       <c r="E330" t="n">
-        <v>10.41893413810214</v>
+        <v>10.41893507933724</v>
       </c>
       <c r="F330" t="n">
         <v>10745440</v>
@@ -7192,16 +7192,16 @@
         <v>44249</v>
       </c>
       <c r="B339" t="n">
-        <v>11.09376621246338</v>
+        <v>11.09376525878906</v>
       </c>
       <c r="C339" t="n">
-        <v>11.20292944052197</v>
+        <v>11.20292847746345</v>
       </c>
       <c r="D339" t="n">
-        <v>10.63602222835513</v>
+        <v>10.63602131403072</v>
       </c>
       <c r="E339" t="n">
-        <v>10.93994416306512</v>
+        <v>10.9399432226141</v>
       </c>
       <c r="F339" t="n">
         <v>14982292</v>
@@ -7292,16 +7292,16 @@
         <v>44256</v>
       </c>
       <c r="B344" t="n">
-        <v>21.85701560974121</v>
+        <v>21.85701751708984</v>
       </c>
       <c r="C344" t="n">
-        <v>23.99306407785948</v>
+        <v>23.99306617161</v>
       </c>
       <c r="D344" t="n">
-        <v>16.3107860983666</v>
+        <v>16.31078752172449</v>
       </c>
       <c r="E344" t="n">
-        <v>16.8635354591482</v>
+        <v>16.86353693074166</v>
       </c>
       <c r="F344" t="n">
         <v>49361500</v>
@@ -7312,16 +7312,16 @@
         <v>44257</v>
       </c>
       <c r="B345" t="n">
-        <v>21.19184303283691</v>
+        <v>21.19184494018555</v>
       </c>
       <c r="C345" t="n">
-        <v>22.95314478521037</v>
+        <v>22.95314685108304</v>
       </c>
       <c r="D345" t="n">
-        <v>20.6953049717416</v>
+        <v>20.69530683439987</v>
       </c>
       <c r="E345" t="n">
-        <v>22.18491736810308</v>
+        <v>22.18491936483229</v>
       </c>
       <c r="F345" t="n">
         <v>20095700</v>
@@ -7352,16 +7352,16 @@
         <v>44259</v>
       </c>
       <c r="B347" t="n">
-        <v>20.86394119262695</v>
+        <v>20.86394309997559</v>
       </c>
       <c r="C347" t="n">
-        <v>21.52911312081577</v>
+        <v>21.52911508897337</v>
       </c>
       <c r="D347" t="n">
-        <v>20.01139593391831</v>
+        <v>20.0113977633286</v>
       </c>
       <c r="E347" t="n">
-        <v>20.2362428583874</v>
+        <v>20.23624470835284</v>
       </c>
       <c r="F347" t="n">
         <v>8984600</v>
@@ -7732,16 +7732,16 @@
         <v>44286</v>
       </c>
       <c r="B366" t="n">
-        <v>31.08511924743652</v>
+        <v>31.08511734008789</v>
       </c>
       <c r="C366" t="n">
-        <v>32.65904960734591</v>
+        <v>32.65904760342265</v>
       </c>
       <c r="D366" t="n">
-        <v>30.82279871206804</v>
+        <v>30.82279682081511</v>
       </c>
       <c r="E366" t="n">
-        <v>31.95640225288098</v>
+        <v>31.95640029207138</v>
       </c>
       <c r="F366" t="n">
         <v>8195900</v>
@@ -7792,16 +7792,16 @@
         <v>44292</v>
       </c>
       <c r="B369" t="n">
-        <v>30.57921028137207</v>
+        <v>30.5792121887207</v>
       </c>
       <c r="C369" t="n">
-        <v>32.19998297677536</v>
+        <v>32.19998498521812</v>
       </c>
       <c r="D369" t="n">
-        <v>30.48552540315069</v>
+        <v>30.48552730465581</v>
       </c>
       <c r="E369" t="n">
-        <v>31.01953707148042</v>
+        <v>31.01953900629401</v>
       </c>
       <c r="F369" t="n">
         <v>6923500</v>
@@ -7812,16 +7812,16 @@
         <v>44293</v>
       </c>
       <c r="B370" t="n">
-        <v>30.95395851135254</v>
+        <v>30.95395660400391</v>
       </c>
       <c r="C370" t="n">
-        <v>31.36617699981515</v>
+        <v>31.36617506706607</v>
       </c>
       <c r="D370" t="n">
-        <v>30.40120912458377</v>
+        <v>30.40120725129495</v>
       </c>
       <c r="E370" t="n">
-        <v>30.72910978883253</v>
+        <v>30.72910789533883</v>
       </c>
       <c r="F370" t="n">
         <v>4745700</v>
@@ -8012,16 +8012,16 @@
         <v>44308</v>
       </c>
       <c r="B380" t="n">
-        <v>36.30344772338867</v>
+        <v>36.30344390869141</v>
       </c>
       <c r="C380" t="n">
-        <v>38.03664315290104</v>
+        <v>38.03663915608288</v>
       </c>
       <c r="D380" t="n">
-        <v>35.88185858344396</v>
+        <v>35.88185481304648</v>
       </c>
       <c r="E380" t="n">
-        <v>37.12788831107506</v>
+        <v>37.12788440974715</v>
       </c>
       <c r="F380" t="n">
         <v>6756200</v>
@@ -8052,16 +8052,16 @@
         <v>44312</v>
       </c>
       <c r="B382" t="n">
-        <v>35.91933059692383</v>
+        <v>35.91933441162109</v>
       </c>
       <c r="C382" t="n">
-        <v>36.30344431641451</v>
+        <v>36.30344817190534</v>
       </c>
       <c r="D382" t="n">
-        <v>35.5164791869886</v>
+        <v>35.51648295890232</v>
       </c>
       <c r="E382" t="n">
-        <v>35.88185521603473</v>
+        <v>35.88185902675205</v>
       </c>
       <c r="F382" t="n">
         <v>4241900</v>
@@ -8072,16 +8072,16 @@
         <v>44313</v>
       </c>
       <c r="B383" t="n">
-        <v>35.46963882446289</v>
+        <v>35.46963500976562</v>
       </c>
       <c r="C383" t="n">
-        <v>36.29407938304689</v>
+        <v>36.2940754796825</v>
       </c>
       <c r="D383" t="n">
-        <v>35.27289842405</v>
+        <v>35.27289463051181</v>
       </c>
       <c r="E383" t="n">
-        <v>36.05986359955081</v>
+        <v>36.05985972137591</v>
       </c>
       <c r="F383" t="n">
         <v>2386900</v>
@@ -35372,19 +35372,39 @@
         <v>46309</v>
       </c>
       <c r="B1748" t="n">
-        <v>3.1</v>
+        <v>3.099999904632568</v>
       </c>
       <c r="C1748" t="n">
-        <v>3.35</v>
+        <v>3.349999904632568</v>
       </c>
       <c r="D1748" t="n">
-        <v>3.1</v>
+        <v>3.099999904632568</v>
       </c>
       <c r="E1748" t="n">
-        <v>3.35</v>
+        <v>3.349999904632568</v>
       </c>
       <c r="F1748" t="n">
         <v>6643700</v>
+      </c>
+    </row>
+    <row r="1749">
+      <c r="A1749" s="1" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B1749" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="C1749" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="D1749" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="E1749" t="n">
+        <v>3.08</v>
+      </c>
+      <c r="F1749" t="n">
+        <v>6668400</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1749"/>
+  <dimension ref="A1:F1750"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132128715515</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132128715515</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132128715515</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132128715515</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132128715515</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132128715515</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132128715515</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132128715515</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132128715515</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132128715515</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132128715515</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132128715515</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616733312606812</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616733312606812</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616733312606812</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616733312606812</v>
+        <v>2.616732358932495</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180155515670776</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="C36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="D36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="E36" t="n">
-        <v>2.1523597240448</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922460794448853</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922460794448853</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922460794448853</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922460794448853</v>
+        <v>1.922461628913879</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.75848650932312</v>
+        <v>1.758487701416016</v>
       </c>
       <c r="C39" t="n">
-        <v>1.75848650932312</v>
+        <v>1.758487701416016</v>
       </c>
       <c r="D39" t="n">
-        <v>1.75848650932312</v>
+        <v>1.758487701416016</v>
       </c>
       <c r="E39" t="n">
-        <v>1.75848650932312</v>
+        <v>1.758487701416016</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838211894035339</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951083660125732</v>
+        <v>6.951085090637207</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951083660125732</v>
+        <v>6.951085090637208</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951083660125732</v>
+        <v>6.951085090637208</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951083660125732</v>
+        <v>6.951085090637208</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="C46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="D46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="E46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="C47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="D47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="E47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370967388153076</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780762</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.58793306350708</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.58793306350708</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.58793306350708</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.58793306350708</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="C55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="D55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="E55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56046009063721</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56046009063721</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56046009063721</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56046009063721</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="C57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="D57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="E57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589143753051758</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589143753051758</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589143753051758</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589143753051758</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988325119018555</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="C64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="D64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="E64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -1872,16 +1872,16 @@
         <v>43741</v>
       </c>
       <c r="B73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F73" t="n">
         <v>755</v>
@@ -1892,16 +1892,16 @@
         <v>43747</v>
       </c>
       <c r="B74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F74" t="n">
         <v>755</v>
@@ -1952,16 +1952,16 @@
         <v>43773</v>
       </c>
       <c r="B77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F77" t="n">
         <v>1510</v>
@@ -2012,16 +2012,16 @@
         <v>43802</v>
       </c>
       <c r="B80" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C80" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D80" t="n">
-        <v>9.21762282756219</v>
+        <v>9.217621990355065</v>
       </c>
       <c r="E80" t="n">
-        <v>9.21762282756219</v>
+        <v>9.217621990355065</v>
       </c>
       <c r="F80" t="n">
         <v>1510</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610103607178</v>
+        <v>10.60610008239746</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448453125444</v>
+        <v>11.08448353456507</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2432,16 +2432,16 @@
         <v>43894</v>
       </c>
       <c r="B101" t="n">
-        <v>8.692568778991699</v>
+        <v>8.692569732666016</v>
       </c>
       <c r="C101" t="n">
-        <v>8.80224676394379</v>
+        <v>8.802247729651036</v>
       </c>
       <c r="D101" t="n">
-        <v>8.564221896891393</v>
+        <v>8.564222836484587</v>
       </c>
       <c r="E101" t="n">
-        <v>8.734572326921571</v>
+        <v>8.734573285204156</v>
       </c>
       <c r="F101" t="n">
         <v>7583284</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174576363958773</v>
+        <v>7.174577261989849</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269086440314109</v>
+        <v>7.269087350174872</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151270575596</v>
+        <v>7.885151755156881</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395100920432114</v>
+        <v>7.395101374897398</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2532,16 +2532,16 @@
         <v>43901</v>
       </c>
       <c r="B106" t="n">
-        <v>7.280755043029785</v>
+        <v>7.280755519866943</v>
       </c>
       <c r="C106" t="n">
-        <v>7.652960679612288</v>
+        <v>7.652961180826241</v>
       </c>
       <c r="D106" t="n">
-        <v>6.825708745737296</v>
+        <v>6.825709192772189</v>
       </c>
       <c r="E106" t="n">
-        <v>7.467442341108447</v>
+        <v>7.467442830172282</v>
       </c>
       <c r="F106" t="n">
         <v>14927915</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198310852051</v>
+        <v>6.731198787689209</v>
       </c>
       <c r="C107" t="n">
-        <v>6.78487002388751</v>
+        <v>6.784870504526766</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975251402972</v>
+        <v>6.183975689474925</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242313978574833</v>
+        <v>6.242314420779493</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642458915710449</v>
+        <v>7.642459392547607</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934155910701143</v>
+        <v>7.934156405738198</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650689636966175</v>
+        <v>6.650690051923714</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251216760168</v>
+        <v>7.242251668627103</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255058288574</v>
+        <v>7.277255535125732</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292230712304</v>
+        <v>7.641292731402749</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086097777741</v>
+        <v>6.70086141684674</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766201694169458</v>
+        <v>6.766202137520195</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2632,16 +2632,16 @@
         <v>43908</v>
       </c>
       <c r="B111" t="n">
-        <v>6.985558032989502</v>
+        <v>6.98555850982666</v>
       </c>
       <c r="C111" t="n">
-        <v>8.075337993481165</v>
+        <v>8.075338544707167</v>
       </c>
       <c r="D111" t="n">
-        <v>6.710196211513576</v>
+        <v>6.71019666955442</v>
       </c>
       <c r="E111" t="n">
-        <v>7.140740982312391</v>
+        <v>7.140741469742403</v>
       </c>
       <c r="F111" t="n">
         <v>26337960</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314098358154</v>
+        <v>7.844314575195312</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109174606594431</v>
+        <v>8.109175099531829</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235250900954319</v>
+        <v>7.235251340767977</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146197500977</v>
+        <v>7.829146673416115</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2692,16 +2692,16 @@
         <v>43913</v>
       </c>
       <c r="B114" t="n">
-        <v>8.386870384216309</v>
+        <v>8.386871337890625</v>
       </c>
       <c r="C114" t="n">
-        <v>8.386870384216309</v>
+        <v>8.386871337890625</v>
       </c>
       <c r="D114" t="n">
-        <v>7.48377644845884</v>
+        <v>7.483777299441991</v>
       </c>
       <c r="E114" t="n">
-        <v>8.050835275027762</v>
+        <v>8.050836190491395</v>
       </c>
       <c r="F114" t="n">
         <v>25091072</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738137245178223</v>
+        <v>7.738136291503906</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145346146541403</v>
+        <v>8.145345142681279</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298979071039</v>
+        <v>7.690298031292473</v>
       </c>
       <c r="E117" t="n">
-        <v>8.13834499423681</v>
+        <v>8.138343991239532</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775676727295</v>
+        <v>7.469775199890137</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304804343318</v>
+        <v>7.746304309853773</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351930089923889</v>
+        <v>7.351929620609467</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113786687701</v>
+        <v>7.514113307020195</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582953929901123</v>
+        <v>7.582952976226807</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840815002303775</v>
+        <v>7.840814016199421</v>
       </c>
       <c r="D122" t="n">
-        <v>7.381100395706687</v>
+        <v>7.38109946741859</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455774312072345</v>
+        <v>7.455773374392843</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261459350586</v>
+        <v>7.340261936187744</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624426344595</v>
+        <v>7.622624921524582</v>
       </c>
       <c r="D123" t="n">
-        <v>7.21541557567713</v>
+        <v>7.215416044404066</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457147585694</v>
+        <v>7.621457642689852</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672797679901123</v>
+        <v>7.672797203063965</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109175966524298</v>
+        <v>8.109175462567777</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661129932612202</v>
+        <v>7.661129456500152</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840815257758265</v>
+        <v>7.84081477047941</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2952,16 +2952,16 @@
         <v>43930</v>
       </c>
       <c r="B127" t="n">
-        <v>7.38576602935791</v>
+        <v>7.385766506195068</v>
       </c>
       <c r="C127" t="n">
-        <v>7.778973418970338</v>
+        <v>7.778973921193609</v>
       </c>
       <c r="D127" t="n">
-        <v>7.351929231575166</v>
+        <v>7.351929706227764</v>
       </c>
       <c r="E127" t="n">
-        <v>7.778973418970338</v>
+        <v>7.778973921193609</v>
       </c>
       <c r="F127" t="n">
         <v>7590081</v>
@@ -2972,16 +2972,16 @@
         <v>43934</v>
       </c>
       <c r="B128" t="n">
-        <v>7.41493558883667</v>
+        <v>7.414936065673828</v>
       </c>
       <c r="C128" t="n">
-        <v>7.447605949093313</v>
+        <v>7.447606428031426</v>
       </c>
       <c r="D128" t="n">
-        <v>7.229416415322526</v>
+        <v>7.22941688022938</v>
       </c>
       <c r="E128" t="n">
-        <v>7.385766224588598</v>
+        <v>7.385766699549943</v>
       </c>
       <c r="F128" t="n">
         <v>8873976</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500110626220703</v>
+        <v>7.500111103057861</v>
       </c>
       <c r="C129" t="n">
-        <v>7.750970514277116</v>
+        <v>7.75097100706328</v>
       </c>
       <c r="D129" t="n">
-        <v>7.455773361693658</v>
+        <v>7.45577383571197</v>
       </c>
       <c r="E129" t="n">
-        <v>7.49427759388343</v>
+        <v>7.494278070349739</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265598297119</v>
+        <v>7.375264644622803</v>
       </c>
       <c r="C130" t="n">
-        <v>7.494278464239883</v>
+        <v>7.494277495176356</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762513925697</v>
+        <v>7.343761564324954</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935961570344</v>
+        <v>7.407935003671517</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566619396209717</v>
+        <v>7.566618919372559</v>
       </c>
       <c r="C131" t="n">
-        <v>7.5887884509226</v>
+        <v>7.58878797268838</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234084415890043</v>
+        <v>7.234083960008746</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444106376032958</v>
+        <v>7.444105906916389</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251522064208984</v>
+        <v>8.251523017883301</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431207358265677</v>
+        <v>8.431208332707222</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3112,16 +3112,16 @@
         <v>43944</v>
       </c>
       <c r="B135" t="n">
-        <v>8.089339256286621</v>
+        <v>8.089340209960938</v>
       </c>
       <c r="C135" t="n">
-        <v>8.57472300766133</v>
+        <v>8.574724018558863</v>
       </c>
       <c r="D135" t="n">
-        <v>7.969159966917957</v>
+        <v>7.969160906424007</v>
       </c>
       <c r="E135" t="n">
-        <v>8.481379364431731</v>
+        <v>8.481380364324728</v>
       </c>
       <c r="F135" t="n">
         <v>13472583</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852482318878174</v>
+        <v>7.852481842041016</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764498666425</v>
+        <v>7.357764051870702</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3152,16 +3152,16 @@
         <v>43948</v>
       </c>
       <c r="B137" t="n">
-        <v>8.105673789978027</v>
+        <v>8.105674743652344</v>
       </c>
       <c r="C137" t="n">
-        <v>8.16517979671254</v>
+        <v>8.165180757388045</v>
       </c>
       <c r="D137" t="n">
-        <v>7.710133516824237</v>
+        <v>7.710134423961201</v>
       </c>
       <c r="E137" t="n">
-        <v>7.937657076955135</v>
+        <v>7.93765801086142</v>
       </c>
       <c r="F137" t="n">
         <v>12260436</v>
@@ -3172,16 +3172,16 @@
         <v>43949</v>
       </c>
       <c r="B138" t="n">
-        <v>7.822145462036133</v>
+        <v>7.822145938873291</v>
       </c>
       <c r="C138" t="n">
-        <v>8.301695367155927</v>
+        <v>8.301695873226397</v>
       </c>
       <c r="D138" t="n">
-        <v>7.804643843107134</v>
+        <v>7.804644318877395</v>
       </c>
       <c r="E138" t="n">
-        <v>8.167514607953231</v>
+        <v>8.167515105844055</v>
       </c>
       <c r="F138" t="n">
         <v>14579753</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484550476074</v>
+        <v>7.887484073638916</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826736101882</v>
+        <v>7.966826254468098</v>
       </c>
       <c r="D139" t="n">
-        <v>7.700798933367937</v>
+        <v>7.70079846781684</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980845212174</v>
+        <v>7.841980371125938</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3252,16 +3252,16 @@
         <v>43956</v>
       </c>
       <c r="B142" t="n">
-        <v>8.114091873168945</v>
+        <v>8.114090919494629</v>
       </c>
       <c r="C142" t="n">
-        <v>8.645024731663977</v>
+        <v>8.645023715587479</v>
       </c>
       <c r="D142" t="n">
-        <v>8.069433944133035</v>
+        <v>8.069432995707503</v>
       </c>
       <c r="E142" t="n">
-        <v>8.286521173623905</v>
+        <v>8.286520199683441</v>
       </c>
       <c r="F142" t="n">
         <v>11843548</v>
@@ -3272,16 +3272,16 @@
         <v>43957</v>
       </c>
       <c r="B143" t="n">
-        <v>8.048344612121582</v>
+        <v>8.048345565795898</v>
       </c>
       <c r="C143" t="n">
-        <v>8.145103893796581</v>
+        <v>8.145104858936216</v>
       </c>
       <c r="D143" t="n">
-        <v>7.96399105383742</v>
+        <v>7.963991997516411</v>
       </c>
       <c r="E143" t="n">
-        <v>8.145103893796581</v>
+        <v>8.145104858936216</v>
       </c>
       <c r="F143" t="n">
         <v>16545622</v>
@@ -3312,16 +3312,16 @@
         <v>43959</v>
       </c>
       <c r="B145" t="n">
-        <v>8.162470817565918</v>
+        <v>8.162469863891602</v>
       </c>
       <c r="C145" t="n">
-        <v>8.184800228116485</v>
+        <v>8.184799271833279</v>
       </c>
       <c r="D145" t="n">
-        <v>7.947864739756858</v>
+        <v>7.94786381115636</v>
       </c>
       <c r="E145" t="n">
-        <v>8.156268402071278</v>
+        <v>8.15626744912163</v>
       </c>
       <c r="F145" t="n">
         <v>8818844</v>
@@ -3352,16 +3352,16 @@
         <v>43963</v>
       </c>
       <c r="B147" t="n">
-        <v>8.085559844970703</v>
+        <v>8.085558891296387</v>
       </c>
       <c r="C147" t="n">
-        <v>8.276596387736546</v>
+        <v>8.276595411529883</v>
       </c>
       <c r="D147" t="n">
-        <v>8.063230434277379</v>
+        <v>8.063229483236768</v>
       </c>
       <c r="E147" t="n">
-        <v>8.187280531887918</v>
+        <v>8.187279566215866</v>
       </c>
       <c r="F147" t="n">
         <v>9953957</v>
@@ -3372,16 +3372,16 @@
         <v>43964</v>
       </c>
       <c r="B148" t="n">
-        <v>7.926775932312012</v>
+        <v>7.926775455474854</v>
       </c>
       <c r="C148" t="n">
-        <v>8.187280049800203</v>
+        <v>8.187279557292356</v>
       </c>
       <c r="D148" t="n">
-        <v>7.885840170888542</v>
+        <v>7.885839696513885</v>
       </c>
       <c r="E148" t="n">
-        <v>8.187280049800203</v>
+        <v>8.187279557292356</v>
       </c>
       <c r="F148" t="n">
         <v>10179016</v>
@@ -3412,16 +3412,16 @@
         <v>43966</v>
       </c>
       <c r="B150" t="n">
-        <v>6.841341018676758</v>
+        <v>6.8413405418396</v>
       </c>
       <c r="C150" t="n">
-        <v>7.421893621943401</v>
+        <v>7.421893104642092</v>
       </c>
       <c r="D150" t="n">
-        <v>6.841341018676758</v>
+        <v>6.8413405418396</v>
       </c>
       <c r="E150" t="n">
-        <v>7.420653049518127</v>
+        <v>7.420652532303285</v>
       </c>
       <c r="F150" t="n">
         <v>26563775</v>
@@ -3452,16 +3452,16 @@
         <v>43970</v>
       </c>
       <c r="B152" t="n">
-        <v>6.831417560577393</v>
+        <v>6.831418037414551</v>
       </c>
       <c r="C152" t="n">
-        <v>7.018731929050585</v>
+        <v>7.018732418962401</v>
       </c>
       <c r="D152" t="n">
-        <v>6.799164018747209</v>
+        <v>6.79916449333305</v>
       </c>
       <c r="E152" t="n">
-        <v>6.966631015976597</v>
+        <v>6.966631502251738</v>
       </c>
       <c r="F152" t="n">
         <v>13463520</v>
@@ -3472,16 +3472,16 @@
         <v>43971</v>
       </c>
       <c r="B153" t="n">
-        <v>6.822733402252197</v>
+        <v>6.822733879089355</v>
       </c>
       <c r="C153" t="n">
-        <v>6.983997533970078</v>
+        <v>6.983998022077899</v>
       </c>
       <c r="D153" t="n">
-        <v>6.81032857213493</v>
+        <v>6.810329048105121</v>
       </c>
       <c r="E153" t="n">
-        <v>6.946783490349408</v>
+        <v>6.94678397585636</v>
       </c>
       <c r="F153" t="n">
         <v>11533147</v>
@@ -3552,16 +3552,16 @@
         <v>43977</v>
       </c>
       <c r="B157" t="n">
-        <v>7.423134326934814</v>
+        <v>7.423134803771973</v>
       </c>
       <c r="C157" t="n">
-        <v>7.560828925689475</v>
+        <v>7.560829411371671</v>
       </c>
       <c r="D157" t="n">
-        <v>7.275514702466858</v>
+        <v>7.275515169821428</v>
       </c>
       <c r="E157" t="n">
-        <v>7.442982144705714</v>
+        <v>7.442982622817829</v>
       </c>
       <c r="F157" t="n">
         <v>12080691</v>
@@ -3612,16 +3612,16 @@
         <v>43980</v>
       </c>
       <c r="B160" t="n">
-        <v>7.812650680541992</v>
+        <v>7.812650203704834</v>
       </c>
       <c r="C160" t="n">
-        <v>7.812650680541992</v>
+        <v>7.812650203704834</v>
       </c>
       <c r="D160" t="n">
-        <v>7.481437500239227</v>
+        <v>7.481437043617326</v>
       </c>
       <c r="E160" t="n">
-        <v>7.519893458373339</v>
+        <v>7.519892999404318</v>
       </c>
       <c r="F160" t="n">
         <v>23712019</v>
@@ -3652,16 +3652,16 @@
         <v>43984</v>
       </c>
       <c r="B162" t="n">
-        <v>8.271635055541992</v>
+        <v>8.271634101867676</v>
       </c>
       <c r="C162" t="n">
-        <v>8.286521031632221</v>
+        <v>8.286520076241633</v>
       </c>
       <c r="D162" t="n">
-        <v>7.976396678662855</v>
+        <v>7.976395759027911</v>
       </c>
       <c r="E162" t="n">
-        <v>8.063230496816454</v>
+        <v>8.063229567170044</v>
       </c>
       <c r="F162" t="n">
         <v>21348142</v>
@@ -3672,16 +3672,16 @@
         <v>43985</v>
       </c>
       <c r="B163" t="n">
-        <v>8.373353958129883</v>
+        <v>8.373354911804199</v>
       </c>
       <c r="C163" t="n">
-        <v>8.80008582291646</v>
+        <v>8.800086825192951</v>
       </c>
       <c r="D163" t="n">
-        <v>8.315051079171372</v>
+        <v>8.315052026205343</v>
       </c>
       <c r="E163" t="n">
-        <v>8.31753222383259</v>
+        <v>8.317533171149149</v>
       </c>
       <c r="F163" t="n">
         <v>31125376</v>
@@ -3752,16 +3752,16 @@
         <v>43991</v>
       </c>
       <c r="B167" t="n">
-        <v>8.296443939208984</v>
+        <v>8.296442985534668</v>
       </c>
       <c r="C167" t="n">
-        <v>8.32745691101246</v>
+        <v>8.327455953773208</v>
       </c>
       <c r="D167" t="n">
-        <v>8.0967247251524</v>
+        <v>8.096723794435762</v>
       </c>
       <c r="E167" t="n">
-        <v>8.137661383332564</v>
+        <v>8.137660447910266</v>
       </c>
       <c r="F167" t="n">
         <v>13675741</v>
@@ -3772,16 +3772,16 @@
         <v>43992</v>
       </c>
       <c r="B168" t="n">
-        <v>8.089280128479004</v>
+        <v>8.08928108215332</v>
       </c>
       <c r="C168" t="n">
-        <v>8.426696138374464</v>
+        <v>8.426697131827968</v>
       </c>
       <c r="D168" t="n">
-        <v>8.037179665656195</v>
+        <v>8.0371806131882</v>
       </c>
       <c r="E168" t="n">
-        <v>8.311329615282364</v>
+        <v>8.311330595134894</v>
       </c>
       <c r="F168" t="n">
         <v>11944749</v>
@@ -3792,16 +3792,16 @@
         <v>43994</v>
       </c>
       <c r="B169" t="n">
-        <v>7.950345516204834</v>
+        <v>7.950345993041992</v>
       </c>
       <c r="C169" t="n">
-        <v>8.084319292912509</v>
+        <v>8.084319777785</v>
       </c>
       <c r="D169" t="n">
-        <v>7.774194958703272</v>
+        <v>7.774195424975465</v>
       </c>
       <c r="E169" t="n">
-        <v>7.877156659374939</v>
+        <v>7.877157131822456</v>
       </c>
       <c r="F169" t="n">
         <v>12251373</v>
@@ -3892,16 +3892,16 @@
         <v>44001</v>
       </c>
       <c r="B174" t="n">
-        <v>8.487481117248535</v>
+        <v>8.487480163574219</v>
       </c>
       <c r="C174" t="n">
-        <v>8.58920180321846</v>
+        <v>8.589200838114557</v>
       </c>
       <c r="D174" t="n">
-        <v>8.203407450651435</v>
+        <v>8.203406528896336</v>
       </c>
       <c r="E174" t="n">
-        <v>8.203407450651435</v>
+        <v>8.203406528896336</v>
       </c>
       <c r="F174" t="n">
         <v>20750754</v>
@@ -3912,16 +3912,16 @@
         <v>44004</v>
       </c>
       <c r="B175" t="n">
-        <v>8.440341949462891</v>
+        <v>8.440342903137207</v>
       </c>
       <c r="C175" t="n">
-        <v>8.729376978500955</v>
+        <v>8.729377964833343</v>
       </c>
       <c r="D175" t="n">
-        <v>8.380797159632158</v>
+        <v>8.380798106578508</v>
       </c>
       <c r="E175" t="n">
-        <v>8.489961267461833</v>
+        <v>8.489962226742637</v>
       </c>
       <c r="F175" t="n">
         <v>12069362</v>
@@ -3952,16 +3952,16 @@
         <v>44006</v>
       </c>
       <c r="B177" t="n">
-        <v>8.59416389465332</v>
+        <v>8.594162940979004</v>
       </c>
       <c r="C177" t="n">
-        <v>8.669833897798144</v>
+        <v>8.669832935726904</v>
       </c>
       <c r="D177" t="n">
-        <v>8.422974729757115</v>
+        <v>8.422973795079262</v>
       </c>
       <c r="E177" t="n">
-        <v>8.571834484683247</v>
+        <v>8.571833533486773</v>
       </c>
       <c r="F177" t="n">
         <v>7388434</v>
@@ -4052,16 +4052,16 @@
         <v>44013</v>
       </c>
       <c r="B182" t="n">
-        <v>9.009729385375977</v>
+        <v>9.009730339050293</v>
       </c>
       <c r="C182" t="n">
-        <v>9.115171330097578</v>
+        <v>9.11517229493286</v>
       </c>
       <c r="D182" t="n">
-        <v>8.731858165462054</v>
+        <v>8.731859089723871</v>
       </c>
       <c r="E182" t="n">
-        <v>8.812490451063802</v>
+        <v>8.812491383860499</v>
       </c>
       <c r="F182" t="n">
         <v>8963093</v>
@@ -4292,16 +4292,16 @@
         <v>44029</v>
       </c>
       <c r="B194" t="n">
-        <v>8.819933891296387</v>
+        <v>8.81993293762207</v>
       </c>
       <c r="C194" t="n">
-        <v>8.919174324825571</v>
+        <v>8.919173360420668</v>
       </c>
       <c r="D194" t="n">
-        <v>8.633859641988225</v>
+        <v>8.633858708433587</v>
       </c>
       <c r="E194" t="n">
-        <v>8.633859641988225</v>
+        <v>8.633858708433587</v>
       </c>
       <c r="F194" t="n">
         <v>9678298</v>
@@ -4432,16 +4432,16 @@
         <v>44040</v>
       </c>
       <c r="B201" t="n">
-        <v>9.641142845153809</v>
+        <v>9.641143798828125</v>
       </c>
       <c r="C201" t="n">
-        <v>9.832179367263814</v>
+        <v>9.832180339834917</v>
       </c>
       <c r="D201" t="n">
-        <v>9.466232422996864</v>
+        <v>9.466233359369541</v>
       </c>
       <c r="E201" t="n">
-        <v>9.67587708316008</v>
+        <v>9.675878040270206</v>
       </c>
       <c r="F201" t="n">
         <v>30127714</v>
@@ -4472,16 +4472,16 @@
         <v>44042</v>
       </c>
       <c r="B203" t="n">
-        <v>9.143703460693359</v>
+        <v>9.143704414367676</v>
       </c>
       <c r="C203" t="n">
-        <v>9.700686938306321</v>
+        <v>9.700687950073165</v>
       </c>
       <c r="D203" t="n">
-        <v>9.097805411083952</v>
+        <v>9.097806359971171</v>
       </c>
       <c r="E203" t="n">
-        <v>9.685800070178546</v>
+        <v>9.685801080392711</v>
       </c>
       <c r="F203" t="n">
         <v>33272500</v>
@@ -4592,16 +4592,16 @@
         <v>44050</v>
       </c>
       <c r="B209" t="n">
-        <v>8.429178237915039</v>
+        <v>8.429177284240723</v>
       </c>
       <c r="C209" t="n">
-        <v>8.429178237915039</v>
+        <v>8.429177284240723</v>
       </c>
       <c r="D209" t="n">
-        <v>8.25550792408546</v>
+        <v>8.255506990060143</v>
       </c>
       <c r="E209" t="n">
-        <v>8.336141112251321</v>
+        <v>8.336140169103194</v>
       </c>
       <c r="F209" t="n">
         <v>22110172</v>
@@ -4612,16 +4612,16 @@
         <v>44053</v>
       </c>
       <c r="B210" t="n">
-        <v>8.25922966003418</v>
+        <v>8.259230613708496</v>
       </c>
       <c r="C210" t="n">
-        <v>8.468873436704216</v>
+        <v>8.468874414585619</v>
       </c>
       <c r="D210" t="n">
-        <v>8.166191645730668</v>
+        <v>8.166192588662099</v>
       </c>
       <c r="E210" t="n">
-        <v>8.435379322693057</v>
+        <v>8.435380296706972</v>
       </c>
       <c r="F210" t="n">
         <v>21920608</v>
@@ -4652,16 +4652,16 @@
         <v>44055</v>
       </c>
       <c r="B212" t="n">
-        <v>8.162470817565918</v>
+        <v>8.162469863891602</v>
       </c>
       <c r="C212" t="n">
-        <v>8.446544484992341</v>
+        <v>8.446543498127859</v>
       </c>
       <c r="D212" t="n">
-        <v>8.078116358606623</v>
+        <v>8.078115414787984</v>
       </c>
       <c r="E212" t="n">
-        <v>8.409329992024503</v>
+        <v>8.409329009508031</v>
       </c>
       <c r="F212" t="n">
         <v>20200945</v>
@@ -4732,16 +4732,16 @@
         <v>44061</v>
       </c>
       <c r="B216" t="n">
-        <v>8.101685523986816</v>
+        <v>8.101686477661133</v>
       </c>
       <c r="C216" t="n">
-        <v>8.143863198266791</v>
+        <v>8.143864156905972</v>
       </c>
       <c r="D216" t="n">
-        <v>7.978877345430011</v>
+        <v>7.9788782846482</v>
       </c>
       <c r="E216" t="n">
-        <v>8.038420352760289</v>
+        <v>8.038421298987467</v>
       </c>
       <c r="F216" t="n">
         <v>10608743</v>
@@ -4752,16 +4752,16 @@
         <v>44062</v>
       </c>
       <c r="B217" t="n">
-        <v>7.926775932312012</v>
+        <v>7.926775455474854</v>
       </c>
       <c r="C217" t="n">
-        <v>8.141381998856557</v>
+        <v>8.141381509109719</v>
       </c>
       <c r="D217" t="n">
-        <v>7.921813642791834</v>
+        <v>7.921813166253184</v>
       </c>
       <c r="E217" t="n">
-        <v>8.141381998856557</v>
+        <v>8.141381509109719</v>
       </c>
       <c r="F217" t="n">
         <v>9466833</v>
@@ -4772,16 +4772,16 @@
         <v>44063</v>
       </c>
       <c r="B218" t="n">
-        <v>7.957787990570068</v>
+        <v>7.957788467407227</v>
       </c>
       <c r="C218" t="n">
-        <v>8.033458885005254</v>
+        <v>8.033459366376674</v>
       </c>
       <c r="D218" t="n">
-        <v>7.774194893738959</v>
+        <v>7.774195359575069</v>
       </c>
       <c r="E218" t="n">
-        <v>7.915611210128628</v>
+        <v>7.915611684438519</v>
       </c>
       <c r="F218" t="n">
         <v>7652765</v>
@@ -4892,16 +4892,16 @@
         <v>44071</v>
       </c>
       <c r="B224" t="n">
-        <v>8.100444793701172</v>
+        <v>8.100445747375488</v>
       </c>
       <c r="C224" t="n">
-        <v>8.100444793701172</v>
+        <v>8.100445747375488</v>
       </c>
       <c r="D224" t="n">
-        <v>7.960268612170143</v>
+        <v>7.960269549341362</v>
       </c>
       <c r="E224" t="n">
-        <v>8.001206157737258</v>
+        <v>8.0012070997281</v>
       </c>
       <c r="F224" t="n">
         <v>5577388</v>
@@ -5012,16 +5012,16 @@
         <v>44082</v>
       </c>
       <c r="B230" t="n">
-        <v>7.751865386962891</v>
+        <v>7.751865863800049</v>
       </c>
       <c r="C230" t="n">
-        <v>7.833737802061967</v>
+        <v>7.833738283935308</v>
       </c>
       <c r="D230" t="n">
-        <v>7.691081361819436</v>
+        <v>7.691081834917614</v>
       </c>
       <c r="E230" t="n">
-        <v>7.813890431199186</v>
+        <v>7.813890911851665</v>
       </c>
       <c r="F230" t="n">
         <v>7181501</v>
@@ -5032,16 +5032,16 @@
         <v>44083</v>
       </c>
       <c r="B231" t="n">
-        <v>7.709689140319824</v>
+        <v>7.709688663482666</v>
       </c>
       <c r="C231" t="n">
-        <v>7.834980256551466</v>
+        <v>7.834979771965168</v>
       </c>
       <c r="D231" t="n">
-        <v>7.637740405675546</v>
+        <v>7.637739933288351</v>
       </c>
       <c r="E231" t="n">
-        <v>7.792802580260581</v>
+        <v>7.792802098282933</v>
       </c>
       <c r="F231" t="n">
         <v>8282629</v>
@@ -5052,16 +5052,16 @@
         <v>44084</v>
       </c>
       <c r="B232" t="n">
-        <v>8.850946426391602</v>
+        <v>8.850947380065918</v>
       </c>
       <c r="C232" t="n">
-        <v>9.197044227170217</v>
+        <v>9.197045218135978</v>
       </c>
       <c r="D232" t="n">
-        <v>8.62145438702172</v>
+        <v>8.621455315968662</v>
       </c>
       <c r="E232" t="n">
-        <v>9.197044227170217</v>
+        <v>9.197045218135978</v>
       </c>
       <c r="F232" t="n">
         <v>139609921</v>
@@ -5132,16 +5132,16 @@
         <v>44090</v>
       </c>
       <c r="B236" t="n">
-        <v>9.312411308288574</v>
+        <v>9.312410354614258</v>
       </c>
       <c r="C236" t="n">
-        <v>9.375676482213272</v>
+        <v>9.375675522060035</v>
       </c>
       <c r="D236" t="n">
-        <v>9.175957274371282</v>
+        <v>9.175956334671081</v>
       </c>
       <c r="E236" t="n">
-        <v>9.179678544963952</v>
+        <v>9.179677604882659</v>
       </c>
       <c r="F236" t="n">
         <v>13993693</v>
@@ -5212,16 +5212,16 @@
         <v>44096</v>
       </c>
       <c r="B240" t="n">
-        <v>9.326057434082031</v>
+        <v>9.326058387756348</v>
       </c>
       <c r="C240" t="n">
-        <v>9.353348239057649</v>
+        <v>9.353349195522698</v>
       </c>
       <c r="D240" t="n">
-        <v>9.182158188124824</v>
+        <v>9.182159127084132</v>
       </c>
       <c r="E240" t="n">
-        <v>9.192082766997606</v>
+        <v>9.192083706971793</v>
       </c>
       <c r="F240" t="n">
         <v>9315031</v>
@@ -5232,16 +5232,16 @@
         <v>44097</v>
       </c>
       <c r="B241" t="n">
-        <v>8.953908920288086</v>
+        <v>8.95390796661377</v>
       </c>
       <c r="C241" t="n">
-        <v>9.308690312405352</v>
+        <v>9.308689320943529</v>
       </c>
       <c r="D241" t="n">
-        <v>8.934060654104224</v>
+        <v>8.934059702543932</v>
       </c>
       <c r="E241" t="n">
-        <v>9.303728915956151</v>
+        <v>9.303727925022763</v>
       </c>
       <c r="F241" t="n">
         <v>13677251</v>
@@ -5252,16 +5252,16 @@
         <v>44098</v>
       </c>
       <c r="B242" t="n">
-        <v>9.282638549804688</v>
+        <v>9.282639503479004</v>
       </c>
       <c r="C242" t="n">
-        <v>9.463751388941567</v>
+        <v>9.46375236122295</v>
       </c>
       <c r="D242" t="n">
-        <v>8.898084356453305</v>
+        <v>8.898085270619518</v>
       </c>
       <c r="E242" t="n">
-        <v>8.906768809518589</v>
+        <v>8.906769724577019</v>
       </c>
       <c r="F242" t="n">
         <v>18607406</v>
@@ -5272,16 +5272,16 @@
         <v>44099</v>
       </c>
       <c r="B243" t="n">
-        <v>9.184639930725098</v>
+        <v>9.184640884399414</v>
       </c>
       <c r="C243" t="n">
-        <v>9.25410751328763</v>
+        <v>9.254108474175018</v>
       </c>
       <c r="D243" t="n">
-        <v>9.095324084518023</v>
+        <v>9.095325028918353</v>
       </c>
       <c r="E243" t="n">
-        <v>9.220613400863298</v>
+        <v>9.22061435827287</v>
       </c>
       <c r="F243" t="n">
         <v>8201819</v>
@@ -5312,16 +5312,16 @@
         <v>44103</v>
       </c>
       <c r="B245" t="n">
-        <v>8.760391235351562</v>
+        <v>8.760390281677246</v>
       </c>
       <c r="C245" t="n">
-        <v>8.942744221459206</v>
+        <v>8.942743247933565</v>
       </c>
       <c r="D245" t="n">
-        <v>8.68348020897627</v>
+        <v>8.683479263674647</v>
       </c>
       <c r="E245" t="n">
-        <v>8.802568019244504</v>
+        <v>8.802567060978735</v>
       </c>
       <c r="F245" t="n">
         <v>13985386</v>
@@ -5332,16 +5332,16 @@
         <v>44104</v>
       </c>
       <c r="B246" t="n">
-        <v>8.651226043701172</v>
+        <v>8.651226997375488</v>
       </c>
       <c r="C246" t="n">
-        <v>8.841022441256731</v>
+        <v>8.841023415853394</v>
       </c>
       <c r="D246" t="n">
-        <v>8.609049265013768</v>
+        <v>8.609050214038696</v>
       </c>
       <c r="E246" t="n">
-        <v>8.803807058409923</v>
+        <v>8.803808028904122</v>
       </c>
       <c r="F246" t="n">
         <v>11477260</v>
@@ -5412,16 +5412,16 @@
         <v>44110</v>
       </c>
       <c r="B250" t="n">
-        <v>8.497405052185059</v>
+        <v>8.497404098510742</v>
       </c>
       <c r="C250" t="n">
-        <v>8.520974589071102</v>
+        <v>8.520973632751547</v>
       </c>
       <c r="D250" t="n">
-        <v>8.316293085426295</v>
+        <v>8.3162921520784</v>
       </c>
       <c r="E250" t="n">
-        <v>8.488721491571129</v>
+        <v>8.48872053887138</v>
       </c>
       <c r="F250" t="n">
         <v>10544549</v>
@@ -5432,16 +5432,16 @@
         <v>44111</v>
       </c>
       <c r="B251" t="n">
-        <v>8.585480690002441</v>
+        <v>8.585479736328125</v>
       </c>
       <c r="C251" t="n">
-        <v>8.704568498874545</v>
+        <v>8.704567531971968</v>
       </c>
       <c r="D251" t="n">
-        <v>8.440343093036322</v>
+        <v>8.440342155483876</v>
       </c>
       <c r="E251" t="n">
-        <v>8.477557586577683</v>
+        <v>8.477556644891454</v>
       </c>
       <c r="F251" t="n">
         <v>12680345</v>
@@ -5552,16 +5552,16 @@
         <v>44120</v>
       </c>
       <c r="B257" t="n">
-        <v>8.25922966003418</v>
+        <v>8.259230613708496</v>
       </c>
       <c r="C257" t="n">
-        <v>8.267912326486389</v>
+        <v>8.267913281163274</v>
       </c>
       <c r="D257" t="n">
-        <v>8.097964185523827</v>
+        <v>8.097965120577188</v>
       </c>
       <c r="E257" t="n">
-        <v>8.122774739620494</v>
+        <v>8.122775677538673</v>
       </c>
       <c r="F257" t="n">
         <v>10726560</v>
@@ -5612,16 +5612,16 @@
         <v>44125</v>
       </c>
       <c r="B260" t="n">
-        <v>8.275355339050293</v>
+        <v>8.275356292724609</v>
       </c>
       <c r="C260" t="n">
-        <v>8.355987625465389</v>
+        <v>8.355988588431988</v>
       </c>
       <c r="D260" t="n">
-        <v>8.245583390421267</v>
+        <v>8.245584340664582</v>
       </c>
       <c r="E260" t="n">
-        <v>8.354747499881778</v>
+        <v>8.35474846270546</v>
       </c>
       <c r="F260" t="n">
         <v>4665068</v>
@@ -5632,16 +5632,16 @@
         <v>44126</v>
       </c>
       <c r="B261" t="n">
-        <v>8.267911911010742</v>
+        <v>8.267912864685059</v>
       </c>
       <c r="C261" t="n">
-        <v>8.337380386835774</v>
+        <v>8.337381348523031</v>
       </c>
       <c r="D261" t="n">
-        <v>8.168673273460097</v>
+        <v>8.168674215687588</v>
       </c>
       <c r="E261" t="n">
-        <v>8.30636741913896</v>
+        <v>8.306368377248981</v>
       </c>
       <c r="F261" t="n">
         <v>7908034</v>
@@ -5652,16 +5652,16 @@
         <v>44127</v>
       </c>
       <c r="B262" t="n">
-        <v>8.234419822692871</v>
+        <v>8.234420776367188</v>
       </c>
       <c r="C262" t="n">
-        <v>8.312570966783923</v>
+        <v>8.312571929509362</v>
       </c>
       <c r="D262" t="n">
-        <v>8.203406854103131</v>
+        <v>8.203407804185662</v>
       </c>
       <c r="E262" t="n">
-        <v>8.269152274680931</v>
+        <v>8.269153232377807</v>
       </c>
       <c r="F262" t="n">
         <v>5098571</v>
@@ -5712,16 +5712,16 @@
         <v>44132</v>
       </c>
       <c r="B265" t="n">
-        <v>7.825055599212646</v>
+        <v>7.825055122375488</v>
       </c>
       <c r="C265" t="n">
-        <v>8.088040873150774</v>
+        <v>8.088040380288025</v>
       </c>
       <c r="D265" t="n">
-        <v>7.817612164601516</v>
+        <v>7.81761168821794</v>
       </c>
       <c r="E265" t="n">
-        <v>8.078116293669268</v>
+        <v>8.078115801411293</v>
       </c>
       <c r="F265" t="n">
         <v>12369944</v>
@@ -5752,16 +5752,16 @@
         <v>44134</v>
       </c>
       <c r="B267" t="n">
-        <v>7.684878826141357</v>
+        <v>7.684879302978516</v>
       </c>
       <c r="C267" t="n">
-        <v>7.777915944304612</v>
+        <v>7.777916426914608</v>
       </c>
       <c r="D267" t="n">
-        <v>7.574474588649013</v>
+        <v>7.574475058635726</v>
       </c>
       <c r="E267" t="n">
-        <v>7.759308699364413</v>
+        <v>7.759309180819852</v>
       </c>
       <c r="F267" t="n">
         <v>16269207</v>
@@ -5772,16 +5772,16 @@
         <v>44138</v>
       </c>
       <c r="B268" t="n">
-        <v>7.717131614685059</v>
+        <v>7.7171311378479</v>
       </c>
       <c r="C268" t="n">
-        <v>7.852346415863062</v>
+        <v>7.852345930671059</v>
       </c>
       <c r="D268" t="n">
-        <v>7.622854363726927</v>
+        <v>7.622853892715106</v>
       </c>
       <c r="E268" t="n">
-        <v>7.821334338599661</v>
+        <v>7.821333855323877</v>
       </c>
       <c r="F268" t="n">
         <v>9901091</v>
@@ -5812,16 +5812,16 @@
         <v>44140</v>
       </c>
       <c r="B270" t="n">
-        <v>8.119053840637207</v>
+        <v>8.119052886962891</v>
       </c>
       <c r="C270" t="n">
-        <v>8.177356724487632</v>
+        <v>8.177355763964984</v>
       </c>
       <c r="D270" t="n">
-        <v>8.007408575750512</v>
+        <v>8.007407635190189</v>
       </c>
       <c r="E270" t="n">
-        <v>8.039661672128053</v>
+        <v>8.039660727779241</v>
       </c>
       <c r="F270" t="n">
         <v>9820281</v>
@@ -5892,16 +5892,16 @@
         <v>44146</v>
       </c>
       <c r="B274" t="n">
-        <v>8.193483352661133</v>
+        <v>8.193482398986816</v>
       </c>
       <c r="C274" t="n">
-        <v>8.420494274138473</v>
+        <v>8.420493294041393</v>
       </c>
       <c r="D274" t="n">
-        <v>8.193483352661133</v>
+        <v>8.193482398986816</v>
       </c>
       <c r="E274" t="n">
-        <v>8.312572059811611</v>
+        <v>8.312571092276054</v>
       </c>
       <c r="F274" t="n">
         <v>7246451</v>
@@ -5912,16 +5912,16 @@
         <v>44147</v>
       </c>
       <c r="B275" t="n">
-        <v>8.234419822692871</v>
+        <v>8.234420776367188</v>
       </c>
       <c r="C275" t="n">
-        <v>8.398164651520666</v>
+        <v>8.398165624159189</v>
       </c>
       <c r="D275" t="n">
-        <v>8.131458125037573</v>
+        <v>8.13145906678732</v>
       </c>
       <c r="E275" t="n">
-        <v>8.193482275292528</v>
+        <v>8.193483224225638</v>
       </c>
       <c r="F275" t="n">
         <v>11697033</v>
@@ -5932,16 +5932,16 @@
         <v>44148</v>
       </c>
       <c r="B276" t="n">
-        <v>8.633858680725098</v>
+        <v>8.633859634399414</v>
       </c>
       <c r="C276" t="n">
-        <v>8.646264403631776</v>
+        <v>8.646265358676397</v>
       </c>
       <c r="D276" t="n">
-        <v>8.267911744802472</v>
+        <v>8.267912658055211</v>
       </c>
       <c r="E276" t="n">
-        <v>8.322493351742979</v>
+        <v>8.322494271024663</v>
       </c>
       <c r="F276" t="n">
         <v>10854949</v>
@@ -5992,16 +5992,16 @@
         <v>44153</v>
       </c>
       <c r="B279" t="n">
-        <v>8.584239959716797</v>
+        <v>8.584240913391113</v>
       </c>
       <c r="C279" t="n">
-        <v>8.64502398560519</v>
+        <v>8.645024946032365</v>
       </c>
       <c r="D279" t="n">
-        <v>8.516012499566937</v>
+        <v>8.516013445661457</v>
       </c>
       <c r="E279" t="n">
-        <v>8.55818927999508</v>
+        <v>8.558190230775271</v>
       </c>
       <c r="F279" t="n">
         <v>8922310</v>
@@ -6072,16 +6072,16 @@
         <v>44160</v>
       </c>
       <c r="B283" t="n">
-        <v>8.739301681518555</v>
+        <v>8.739302635192871</v>
       </c>
       <c r="C283" t="n">
-        <v>8.920413624337439</v>
+        <v>8.920414597775554</v>
       </c>
       <c r="D283" t="n">
-        <v>8.616491723410208</v>
+        <v>8.616492663682914</v>
       </c>
       <c r="E283" t="n">
-        <v>8.854667312281327</v>
+        <v>8.85466827854489</v>
       </c>
       <c r="F283" t="n">
         <v>6633202</v>
@@ -6112,16 +6112,16 @@
         <v>44162</v>
       </c>
       <c r="B285" t="n">
-        <v>8.615251541137695</v>
+        <v>8.615252494812012</v>
       </c>
       <c r="C285" t="n">
-        <v>8.70828776310049</v>
+        <v>8.708288727073548</v>
       </c>
       <c r="D285" t="n">
-        <v>8.507328451506179</v>
+        <v>8.507329393233835</v>
       </c>
       <c r="E285" t="n">
-        <v>8.566871454869922</v>
+        <v>8.566872403188754</v>
       </c>
       <c r="F285" t="n">
         <v>5230736</v>
@@ -6152,16 +6152,16 @@
         <v>44166</v>
       </c>
       <c r="B287" t="n">
-        <v>8.414291381835938</v>
+        <v>8.414292335510254</v>
       </c>
       <c r="C287" t="n">
-        <v>8.672314340510058</v>
+        <v>8.672315323428652</v>
       </c>
       <c r="D287" t="n">
-        <v>8.360949006055193</v>
+        <v>8.360949953683695</v>
       </c>
       <c r="E287" t="n">
-        <v>8.636339977103933</v>
+        <v>8.636340955945199</v>
       </c>
       <c r="F287" t="n">
         <v>16096259</v>
@@ -6172,16 +6172,16 @@
         <v>44167</v>
       </c>
       <c r="B288" t="n">
-        <v>8.282797813415527</v>
+        <v>8.282798767089844</v>
       </c>
       <c r="C288" t="n">
-        <v>8.461429503764982</v>
+        <v>8.4614304780068</v>
       </c>
       <c r="D288" t="n">
-        <v>8.199685276496087</v>
+        <v>8.199686220600897</v>
       </c>
       <c r="E288" t="n">
-        <v>8.456468108007872</v>
+        <v>8.456469081678438</v>
       </c>
       <c r="F288" t="n">
         <v>15329699</v>
@@ -6212,16 +6212,16 @@
         <v>44169</v>
       </c>
       <c r="B290" t="n">
-        <v>8.772793769836426</v>
+        <v>8.772794723510742</v>
       </c>
       <c r="C290" t="n">
-        <v>8.948944312102428</v>
+        <v>8.948945284925747</v>
       </c>
       <c r="D290" t="n">
-        <v>8.683478819885265</v>
+        <v>8.683479763850318</v>
       </c>
       <c r="E290" t="n">
-        <v>8.886919271932774</v>
+        <v>8.886920238013465</v>
       </c>
       <c r="F290" t="n">
         <v>10446369</v>
@@ -6232,16 +6232,16 @@
         <v>44172</v>
       </c>
       <c r="B291" t="n">
-        <v>8.647505760192871</v>
+        <v>8.647504806518555</v>
       </c>
       <c r="C291" t="n">
-        <v>8.82737759966732</v>
+        <v>8.827376626156168</v>
       </c>
       <c r="D291" t="n">
-        <v>8.621455078573774</v>
+        <v>8.621454127772409</v>
       </c>
       <c r="E291" t="n">
-        <v>8.807529333653388</v>
+        <v>8.807528362331166</v>
       </c>
       <c r="F291" t="n">
         <v>10174485</v>
@@ -6392,16 +6392,16 @@
         <v>44182</v>
       </c>
       <c r="B299" t="n">
-        <v>9.125096321105957</v>
+        <v>9.125097274780273</v>
       </c>
       <c r="C299" t="n">
-        <v>9.233019415311725</v>
+        <v>9.233020380265208</v>
       </c>
       <c r="D299" t="n">
-        <v>9.1052480568353</v>
+        <v>9.105249008435251</v>
       </c>
       <c r="E299" t="n">
-        <v>9.230538270595108</v>
+        <v>9.230539235289285</v>
       </c>
       <c r="F299" t="n">
         <v>5262456</v>
@@ -6452,16 +6452,16 @@
         <v>44187</v>
       </c>
       <c r="B302" t="n">
-        <v>9.018413543701172</v>
+        <v>9.018414497375488</v>
       </c>
       <c r="C302" t="n">
-        <v>9.117653080233614</v>
+        <v>9.117654044402261</v>
       </c>
       <c r="D302" t="n">
-        <v>8.941503416629342</v>
+        <v>8.941504362170608</v>
       </c>
       <c r="E302" t="n">
-        <v>8.974995743895692</v>
+        <v>8.974996692978687</v>
       </c>
       <c r="F302" t="n">
         <v>3700636</v>
@@ -6572,16 +6572,16 @@
         <v>44201</v>
       </c>
       <c r="B308" t="n">
-        <v>9.097805023193359</v>
+        <v>9.097805976867676</v>
       </c>
       <c r="C308" t="n">
-        <v>9.304967640603</v>
+        <v>9.304968615993069</v>
       </c>
       <c r="D308" t="n">
-        <v>9.012210449150441</v>
+        <v>9.012211393852336</v>
       </c>
       <c r="E308" t="n">
-        <v>9.304967640603</v>
+        <v>9.304968615993069</v>
       </c>
       <c r="F308" t="n">
         <v>8306796</v>
@@ -6592,16 +6592,16 @@
         <v>44202</v>
       </c>
       <c r="B309" t="n">
-        <v>9.02337646484375</v>
+        <v>9.023375511169434</v>
       </c>
       <c r="C309" t="n">
-        <v>9.178438642419241</v>
+        <v>9.178437672356514</v>
       </c>
       <c r="D309" t="n">
-        <v>8.883200263463204</v>
+        <v>8.883199324604012</v>
       </c>
       <c r="E309" t="n">
-        <v>9.091603036730099</v>
+        <v>9.091602075844966</v>
       </c>
       <c r="F309" t="n">
         <v>6995714</v>
@@ -6632,16 +6632,16 @@
         <v>44204</v>
       </c>
       <c r="B311" t="n">
-        <v>9.494765281677246</v>
+        <v>9.49476432800293</v>
       </c>
       <c r="C311" t="n">
-        <v>9.533220794103377</v>
+        <v>9.533219836566508</v>
       </c>
       <c r="D311" t="n">
-        <v>9.077957953992263</v>
+        <v>9.077957042182957</v>
       </c>
       <c r="E311" t="n">
-        <v>9.178438515281906</v>
+        <v>9.178437593380119</v>
       </c>
       <c r="F311" t="n">
         <v>10280973</v>
@@ -6732,16 +6732,16 @@
         <v>44211</v>
       </c>
       <c r="B316" t="n">
-        <v>9.479878425598145</v>
+        <v>9.479877471923828</v>
       </c>
       <c r="C316" t="n">
-        <v>9.607649794137002</v>
+        <v>9.607648827608905</v>
       </c>
       <c r="D316" t="n">
-        <v>9.378158631904267</v>
+        <v>9.378157688462947</v>
       </c>
       <c r="E316" t="n">
-        <v>9.589042547490402</v>
+        <v>9.589041582834192</v>
       </c>
       <c r="F316" t="n">
         <v>14334303</v>
@@ -6892,16 +6892,16 @@
         <v>44224</v>
       </c>
       <c r="B324" t="n">
-        <v>9.368232727050781</v>
+        <v>9.368233680725098</v>
       </c>
       <c r="C324" t="n">
-        <v>9.399244800408228</v>
+        <v>9.399245757239534</v>
       </c>
       <c r="D324" t="n">
-        <v>9.102766341339521</v>
+        <v>9.102767267989694</v>
       </c>
       <c r="E324" t="n">
-        <v>9.180917480970056</v>
+        <v>9.180918415575915</v>
       </c>
       <c r="F324" t="n">
         <v>7429217</v>
@@ -6912,16 +6912,16 @@
         <v>44225</v>
       </c>
       <c r="B325" t="n">
-        <v>9.363271713256836</v>
+        <v>9.36327075958252</v>
       </c>
       <c r="C325" t="n">
-        <v>9.571676269761104</v>
+        <v>9.571675294860224</v>
       </c>
       <c r="D325" t="n">
-        <v>9.215652973121827</v>
+        <v>9.215652034482874</v>
       </c>
       <c r="E325" t="n">
-        <v>9.312411369945844</v>
+        <v>9.312410421451789</v>
       </c>
       <c r="F325" t="n">
         <v>11022611</v>
@@ -6952,16 +6952,16 @@
         <v>44229</v>
       </c>
       <c r="B327" t="n">
-        <v>10.13361930847168</v>
+        <v>10.133620262146</v>
       </c>
       <c r="C327" t="n">
-        <v>10.18447964681817</v>
+        <v>10.18448060527895</v>
       </c>
       <c r="D327" t="n">
-        <v>9.832179442109044</v>
+        <v>9.832180367414875</v>
       </c>
       <c r="E327" t="n">
-        <v>10.11004977442547</v>
+        <v>10.11005072588166</v>
       </c>
       <c r="F327" t="n">
         <v>20046878</v>
@@ -6992,16 +6992,16 @@
         <v>44231</v>
       </c>
       <c r="B329" t="n">
-        <v>10.38668251037598</v>
+        <v>10.38668155670166</v>
       </c>
       <c r="C329" t="n">
-        <v>10.38668251037598</v>
+        <v>10.38668155670166</v>
       </c>
       <c r="D329" t="n">
-        <v>10.11749393146458</v>
+        <v>10.11749300250636</v>
       </c>
       <c r="E329" t="n">
-        <v>10.17703872709649</v>
+        <v>10.17703779267104</v>
       </c>
       <c r="F329" t="n">
         <v>12166787</v>
@@ -7012,16 +7012,16 @@
         <v>44232</v>
       </c>
       <c r="B330" t="n">
-        <v>10.55663013458252</v>
+        <v>10.5566291809082</v>
       </c>
       <c r="C330" t="n">
-        <v>10.58144069033415</v>
+        <v>10.58143973441847</v>
       </c>
       <c r="D330" t="n">
-        <v>10.32465782656054</v>
+        <v>10.32465689384235</v>
       </c>
       <c r="E330" t="n">
-        <v>10.41893507933724</v>
+        <v>10.41893413810214</v>
       </c>
       <c r="F330" t="n">
         <v>10745440</v>
@@ -7192,16 +7192,16 @@
         <v>44249</v>
       </c>
       <c r="B339" t="n">
-        <v>11.09376525878906</v>
+        <v>11.09376621246338</v>
       </c>
       <c r="C339" t="n">
-        <v>11.20292847746345</v>
+        <v>11.20292944052197</v>
       </c>
       <c r="D339" t="n">
-        <v>10.63602131403072</v>
+        <v>10.63602222835513</v>
       </c>
       <c r="E339" t="n">
-        <v>10.9399432226141</v>
+        <v>10.93994416306512</v>
       </c>
       <c r="F339" t="n">
         <v>14982292</v>
@@ -7292,16 +7292,16 @@
         <v>44256</v>
       </c>
       <c r="B344" t="n">
-        <v>21.85701751708984</v>
+        <v>21.85701560974121</v>
       </c>
       <c r="C344" t="n">
-        <v>23.99306617161</v>
+        <v>23.99306407785948</v>
       </c>
       <c r="D344" t="n">
-        <v>16.31078752172449</v>
+        <v>16.3107860983666</v>
       </c>
       <c r="E344" t="n">
-        <v>16.86353693074166</v>
+        <v>16.8635354591482</v>
       </c>
       <c r="F344" t="n">
         <v>49361500</v>
@@ -7312,16 +7312,16 @@
         <v>44257</v>
       </c>
       <c r="B345" t="n">
-        <v>21.19184494018555</v>
+        <v>21.19184303283691</v>
       </c>
       <c r="C345" t="n">
-        <v>22.95314685108304</v>
+        <v>22.95314478521037</v>
       </c>
       <c r="D345" t="n">
-        <v>20.69530683439987</v>
+        <v>20.6953049717416</v>
       </c>
       <c r="E345" t="n">
-        <v>22.18491936483229</v>
+        <v>22.18491736810308</v>
       </c>
       <c r="F345" t="n">
         <v>20095700</v>
@@ -7352,16 +7352,16 @@
         <v>44259</v>
       </c>
       <c r="B347" t="n">
-        <v>20.86394309997559</v>
+        <v>20.86394119262695</v>
       </c>
       <c r="C347" t="n">
-        <v>21.52911508897337</v>
+        <v>21.52911312081577</v>
       </c>
       <c r="D347" t="n">
-        <v>20.0113977633286</v>
+        <v>20.01139593391831</v>
       </c>
       <c r="E347" t="n">
-        <v>20.23624470835284</v>
+        <v>20.2362428583874</v>
       </c>
       <c r="F347" t="n">
         <v>8984600</v>
@@ -7732,16 +7732,16 @@
         <v>44286</v>
       </c>
       <c r="B366" t="n">
-        <v>31.08511734008789</v>
+        <v>31.08511924743652</v>
       </c>
       <c r="C366" t="n">
-        <v>32.65904760342265</v>
+        <v>32.65904960734591</v>
       </c>
       <c r="D366" t="n">
-        <v>30.82279682081511</v>
+        <v>30.82279871206804</v>
       </c>
       <c r="E366" t="n">
-        <v>31.95640029207138</v>
+        <v>31.95640225288098</v>
       </c>
       <c r="F366" t="n">
         <v>8195900</v>
@@ -7792,16 +7792,16 @@
         <v>44292</v>
       </c>
       <c r="B369" t="n">
-        <v>30.5792121887207</v>
+        <v>30.57921028137207</v>
       </c>
       <c r="C369" t="n">
-        <v>32.19998498521812</v>
+        <v>32.19998297677536</v>
       </c>
       <c r="D369" t="n">
-        <v>30.48552730465581</v>
+        <v>30.48552540315069</v>
       </c>
       <c r="E369" t="n">
-        <v>31.01953900629401</v>
+        <v>31.01953707148042</v>
       </c>
       <c r="F369" t="n">
         <v>6923500</v>
@@ -7812,16 +7812,16 @@
         <v>44293</v>
       </c>
       <c r="B370" t="n">
-        <v>30.95395660400391</v>
+        <v>30.95395851135254</v>
       </c>
       <c r="C370" t="n">
-        <v>31.36617506706607</v>
+        <v>31.36617699981515</v>
       </c>
       <c r="D370" t="n">
-        <v>30.40120725129495</v>
+        <v>30.40120912458377</v>
       </c>
       <c r="E370" t="n">
-        <v>30.72910789533883</v>
+        <v>30.72910978883253</v>
       </c>
       <c r="F370" t="n">
         <v>4745700</v>
@@ -8012,16 +8012,16 @@
         <v>44308</v>
       </c>
       <c r="B380" t="n">
-        <v>36.30344390869141</v>
+        <v>36.30344772338867</v>
       </c>
       <c r="C380" t="n">
-        <v>38.03663915608288</v>
+        <v>38.03664315290104</v>
       </c>
       <c r="D380" t="n">
-        <v>35.88185481304648</v>
+        <v>35.88185858344396</v>
       </c>
       <c r="E380" t="n">
-        <v>37.12788440974715</v>
+        <v>37.12788831107506</v>
       </c>
       <c r="F380" t="n">
         <v>6756200</v>
@@ -8052,16 +8052,16 @@
         <v>44312</v>
       </c>
       <c r="B382" t="n">
-        <v>35.91933441162109</v>
+        <v>35.91933059692383</v>
       </c>
       <c r="C382" t="n">
-        <v>36.30344817190534</v>
+        <v>36.30344431641451</v>
       </c>
       <c r="D382" t="n">
-        <v>35.51648295890232</v>
+        <v>35.5164791869886</v>
       </c>
       <c r="E382" t="n">
-        <v>35.88185902675205</v>
+        <v>35.88185521603473</v>
       </c>
       <c r="F382" t="n">
         <v>4241900</v>
@@ -8072,16 +8072,16 @@
         <v>44313</v>
       </c>
       <c r="B383" t="n">
-        <v>35.46963500976562</v>
+        <v>35.46963882446289</v>
       </c>
       <c r="C383" t="n">
-        <v>36.2940754796825</v>
+        <v>36.29407938304689</v>
       </c>
       <c r="D383" t="n">
-        <v>35.27289463051181</v>
+        <v>35.27289842405</v>
       </c>
       <c r="E383" t="n">
-        <v>36.05985972137591</v>
+        <v>36.05986359955081</v>
       </c>
       <c r="F383" t="n">
         <v>2386900</v>
@@ -35392,19 +35392,39 @@
         <v>46310</v>
       </c>
       <c r="B1749" t="n">
-        <v>2.91</v>
+        <v>2.910000085830688</v>
       </c>
       <c r="C1749" t="n">
-        <v>3.08</v>
+        <v>3.079999923706055</v>
       </c>
       <c r="D1749" t="n">
-        <v>2.85</v>
+        <v>2.849999904632568</v>
       </c>
       <c r="E1749" t="n">
-        <v>3.08</v>
+        <v>3.079999923706055</v>
       </c>
       <c r="F1749" t="n">
         <v>6668400</v>
+      </c>
+    </row>
+    <row r="1750">
+      <c r="A1750" s="1" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B1750" t="n">
+        <v>2.93</v>
+      </c>
+      <c r="C1750" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="D1750" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="E1750" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="F1750" t="n">
+        <v>5502800</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1750"/>
+  <dimension ref="A1:F1751"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173831939697</v>
+        <v>1.799174189567566</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732358932495</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180155515670776</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.92246150970459</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.92246150970459</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.92246150970459</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461628913879</v>
+        <v>1.92246150970459</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758487701416016</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758487701416016</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758487701416016</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758487701416016</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951085090637207</v>
+        <v>6.951085567474365</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951085090637208</v>
+        <v>6.951085567474365</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951085090637208</v>
+        <v>6.951085567474365</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951085090637208</v>
+        <v>6.951085567474365</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997223377227783</v>
+        <v>6.997222900390625</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997223377227783</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997223377227783</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997223377227783</v>
+        <v>6.997222900390624</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370967388153076</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959037780762</v>
+        <v>3.926958560943604</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.58793306350708</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="C49" t="n">
-        <v>4.58793306350708</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="D49" t="n">
-        <v>4.58793306350708</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="E49" t="n">
-        <v>4.58793306350708</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295563697814941</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.07562780380249</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56046009063721</v>
+        <v>12.56045627593994</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56046009063721</v>
+        <v>12.56045627593994</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56046009063721</v>
+        <v>12.56045627593994</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56046009063721</v>
+        <v>12.56045627593994</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.687331199646</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296536445617676</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296536445617676</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296536445617676</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296536445617676</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589143753051758</v>
+        <v>7.5891432762146</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589143753051758</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589143753051758</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589143753051758</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1832,16 +1832,16 @@
         <v>43684</v>
       </c>
       <c r="B71" t="n">
-        <v>11.66787815093994</v>
+        <v>11.66787719726562</v>
       </c>
       <c r="C71" t="n">
-        <v>11.66787815093994</v>
+        <v>11.66787719726562</v>
       </c>
       <c r="D71" t="n">
-        <v>11.66787815093994</v>
+        <v>11.66787719726562</v>
       </c>
       <c r="E71" t="n">
-        <v>11.66787815093994</v>
+        <v>11.66787719726562</v>
       </c>
       <c r="F71" t="n">
         <v>755</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610008239746</v>
+        <v>10.60610103607178</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448353456507</v>
+        <v>11.08448453125444</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2432,16 +2432,16 @@
         <v>43894</v>
       </c>
       <c r="B101" t="n">
-        <v>8.692569732666016</v>
+        <v>8.692568778991699</v>
       </c>
       <c r="C101" t="n">
-        <v>8.802247729651036</v>
+        <v>8.80224676394379</v>
       </c>
       <c r="D101" t="n">
-        <v>8.564222836484587</v>
+        <v>8.564221896891393</v>
       </c>
       <c r="E101" t="n">
-        <v>8.734573285204156</v>
+        <v>8.734572326921571</v>
       </c>
       <c r="F101" t="n">
         <v>7583284</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759139060974121</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151755156881</v>
+        <v>7.885152239738168</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395101374897398</v>
+        <v>7.395101829362682</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759139060974121</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2532,16 +2532,16 @@
         <v>43901</v>
       </c>
       <c r="B106" t="n">
-        <v>7.280755519866943</v>
+        <v>7.280755043029785</v>
       </c>
       <c r="C106" t="n">
-        <v>7.652961180826241</v>
+        <v>7.652960679612288</v>
       </c>
       <c r="D106" t="n">
-        <v>6.825709192772189</v>
+        <v>6.825708745737296</v>
       </c>
       <c r="E106" t="n">
-        <v>7.467442830172282</v>
+        <v>7.467442341108447</v>
       </c>
       <c r="F106" t="n">
         <v>14927915</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642459392547607</v>
+        <v>7.642459869384766</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934156405738198</v>
+        <v>7.934156900775253</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650690051923714</v>
+        <v>6.650690466881254</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251668627103</v>
+        <v>7.242252120494039</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314575195312</v>
+        <v>7.844314098358154</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109175099531829</v>
+        <v>8.109174606594431</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235251340767977</v>
+        <v>7.235250900954319</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146673416115</v>
+        <v>7.829146197500977</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2692,16 +2692,16 @@
         <v>43913</v>
       </c>
       <c r="B114" t="n">
-        <v>8.386871337890625</v>
+        <v>8.386870384216309</v>
       </c>
       <c r="C114" t="n">
-        <v>8.386871337890625</v>
+        <v>8.386870384216309</v>
       </c>
       <c r="D114" t="n">
-        <v>7.483777299441991</v>
+        <v>7.48377644845884</v>
       </c>
       <c r="E114" t="n">
-        <v>8.050836190491395</v>
+        <v>8.050835275027762</v>
       </c>
       <c r="F114" t="n">
         <v>25091072</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775199890137</v>
+        <v>7.469775676727295</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304309853773</v>
+        <v>7.746304804343318</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351929620609467</v>
+        <v>7.351930089923889</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113307020195</v>
+        <v>7.514113786687701</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2832,16 +2832,16 @@
         <v>43922</v>
       </c>
       <c r="B121" t="n">
-        <v>7.461607456207275</v>
+        <v>7.461607933044434</v>
       </c>
       <c r="C121" t="n">
-        <v>7.642459196363636</v>
+        <v>7.642459684758201</v>
       </c>
       <c r="D121" t="n">
-        <v>7.304091207587605</v>
+        <v>7.304091674358621</v>
       </c>
       <c r="E121" t="n">
-        <v>7.619123704826946</v>
+        <v>7.619124191730246</v>
       </c>
       <c r="F121" t="n">
         <v>10218288</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672797203063965</v>
+        <v>7.672797679901123</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109175462567777</v>
+        <v>8.109175966524298</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661129456500152</v>
+        <v>7.661129932612202</v>
       </c>
       <c r="E125" t="n">
-        <v>7.84081477047941</v>
+        <v>7.840815257758265</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375264644622803</v>
+        <v>7.375265121459961</v>
       </c>
       <c r="C130" t="n">
-        <v>7.494277495176356</v>
+        <v>7.49427797970812</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343761564324954</v>
+        <v>7.343762039125325</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935003671517</v>
+        <v>7.407935482620931</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566618919372559</v>
+        <v>7.5666184425354</v>
       </c>
       <c r="C131" t="n">
-        <v>7.58878797268838</v>
+        <v>7.588787494454161</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234083960008746</v>
+        <v>7.234083504127451</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444105906916389</v>
+        <v>7.44410543779982</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852481842041016</v>
+        <v>7.852482318878174</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764051870702</v>
+        <v>7.357764498666425</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3172,16 +3172,16 @@
         <v>43949</v>
       </c>
       <c r="B138" t="n">
-        <v>7.822145938873291</v>
+        <v>7.822145462036133</v>
       </c>
       <c r="C138" t="n">
-        <v>8.301695873226397</v>
+        <v>8.301695367155927</v>
       </c>
       <c r="D138" t="n">
-        <v>7.804644318877395</v>
+        <v>7.804643843107134</v>
       </c>
       <c r="E138" t="n">
-        <v>8.167515105844055</v>
+        <v>8.167514607953231</v>
       </c>
       <c r="F138" t="n">
         <v>14579753</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484073638916</v>
+        <v>7.887483596801758</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826254468098</v>
+        <v>7.966825772834317</v>
       </c>
       <c r="D139" t="n">
-        <v>7.70079846781684</v>
+        <v>7.700798002265745</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980371125938</v>
+        <v>7.841979897039702</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -35412,19 +35412,39 @@
         <v>46311</v>
       </c>
       <c r="B1750" t="n">
-        <v>2.93</v>
+        <v>2.930000066757202</v>
       </c>
       <c r="C1750" t="n">
-        <v>2.95</v>
+        <v>2.950000047683716</v>
       </c>
       <c r="D1750" t="n">
-        <v>2.82</v>
+        <v>2.819999933242798</v>
       </c>
       <c r="E1750" t="n">
+        <v>2.920000076293945</v>
+      </c>
+      <c r="F1750" t="n">
+        <v>5421900</v>
+      </c>
+    </row>
+    <row r="1751">
+      <c r="A1751" s="1" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B1751" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1751" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="D1751" t="n">
         <v>2.92</v>
       </c>
-      <c r="F1750" t="n">
-        <v>5502800</v>
+      <c r="E1751" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="F1751" t="n">
+        <v>10083700</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1751"/>
+  <dimension ref="A1:F1752"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799174189567566</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616733074188232</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616733074188232</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616733074188232</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616733074188232</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.72519588470459</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500722885132</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.18015718460083</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359485626221</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="C38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="D38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="E38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758487224578857</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758487224578857</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758487224578857</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758487224578857</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951085567474365</v>
+        <v>6.951082706451416</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951085567474365</v>
+        <v>6.951082706451416</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951085567474365</v>
+        <v>6.951082706451416</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951085567474365</v>
+        <v>6.951082706451416</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958560943604</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295563697814941</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075628280639648</v>
       </c>
       <c r="C55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075628280639648</v>
       </c>
       <c r="D55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075628280639648</v>
       </c>
       <c r="E55" t="n">
-        <v>7.07562780380249</v>
+        <v>7.075628280639648</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045627593994</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045627593994</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045627593994</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045627593994</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296536445617676</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296536445617676</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296536445617676</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296536445617676</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.5891432762146</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.014761924743652</v>
       </c>
       <c r="C64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.014761924743652</v>
       </c>
       <c r="D64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.014761924743652</v>
       </c>
       <c r="E64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.014761924743652</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -1832,16 +1832,16 @@
         <v>43684</v>
       </c>
       <c r="B71" t="n">
-        <v>11.66787719726562</v>
+        <v>11.66787815093994</v>
       </c>
       <c r="C71" t="n">
-        <v>11.66787719726562</v>
+        <v>11.66787815093994</v>
       </c>
       <c r="D71" t="n">
-        <v>11.66787719726562</v>
+        <v>11.66787815093994</v>
       </c>
       <c r="E71" t="n">
-        <v>11.66787719726562</v>
+        <v>11.66787815093994</v>
       </c>
       <c r="F71" t="n">
         <v>755</v>
@@ -1872,16 +1872,16 @@
         <v>43741</v>
       </c>
       <c r="B73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F73" t="n">
         <v>755</v>
@@ -1892,16 +1892,16 @@
         <v>43747</v>
       </c>
       <c r="B74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F74" t="n">
         <v>755</v>
@@ -1952,16 +1952,16 @@
         <v>43773</v>
       </c>
       <c r="B77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F77" t="n">
         <v>1510</v>
@@ -2012,16 +2012,16 @@
         <v>43802</v>
       </c>
       <c r="B80" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C80" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D80" t="n">
-        <v>9.217621990355065</v>
+        <v>9.21762282756219</v>
       </c>
       <c r="E80" t="n">
-        <v>9.217621990355065</v>
+        <v>9.21762282756219</v>
       </c>
       <c r="F80" t="n">
         <v>1510</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174577261989849</v>
+        <v>7.174576363958773</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269087350174872</v>
+        <v>7.269086440314109</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759139060974121</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885152239738168</v>
+        <v>7.885151270575596</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395101829362682</v>
+        <v>7.395100920432114</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759139060974121</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198787689209</v>
+        <v>6.731198310852051</v>
       </c>
       <c r="C107" t="n">
-        <v>6.784870504526766</v>
+        <v>6.78487002388751</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975689474925</v>
+        <v>6.183975251402972</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242314420779493</v>
+        <v>6.242313978574833</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642459869384766</v>
+        <v>7.642458915710449</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934156900775253</v>
+        <v>7.934155910701143</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650690466881254</v>
+        <v>6.650689636966175</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242252120494039</v>
+        <v>7.242251216760168</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255535125732</v>
+        <v>7.277255058288574</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292731402749</v>
+        <v>7.641292230712304</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086141684674</v>
+        <v>6.70086097777741</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766202137520195</v>
+        <v>6.766201694169458</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2632,16 +2632,16 @@
         <v>43908</v>
       </c>
       <c r="B111" t="n">
-        <v>6.98555850982666</v>
+        <v>6.985558032989502</v>
       </c>
       <c r="C111" t="n">
-        <v>8.075338544707167</v>
+        <v>8.075337993481165</v>
       </c>
       <c r="D111" t="n">
-        <v>6.71019666955442</v>
+        <v>6.710196211513576</v>
       </c>
       <c r="E111" t="n">
-        <v>7.140741469742403</v>
+        <v>7.140740982312391</v>
       </c>
       <c r="F111" t="n">
         <v>26337960</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738136291503906</v>
+        <v>7.738137245178223</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145345142681279</v>
+        <v>8.145346146541403</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298031292473</v>
+        <v>7.690298979071039</v>
       </c>
       <c r="E117" t="n">
-        <v>8.138343991239532</v>
+        <v>8.13834499423681</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2832,16 +2832,16 @@
         <v>43922</v>
       </c>
       <c r="B121" t="n">
-        <v>7.461607933044434</v>
+        <v>7.461607456207275</v>
       </c>
       <c r="C121" t="n">
-        <v>7.642459684758201</v>
+        <v>7.642459196363636</v>
       </c>
       <c r="D121" t="n">
-        <v>7.304091674358621</v>
+        <v>7.304091207587605</v>
       </c>
       <c r="E121" t="n">
-        <v>7.619124191730246</v>
+        <v>7.619123704826946</v>
       </c>
       <c r="F121" t="n">
         <v>10218288</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582952976226807</v>
+        <v>7.582953929901123</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840814016199421</v>
+        <v>7.840815002303775</v>
       </c>
       <c r="D122" t="n">
-        <v>7.38109946741859</v>
+        <v>7.381100395706687</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455773374392843</v>
+        <v>7.455774312072345</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261936187744</v>
+        <v>7.340261459350586</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624921524582</v>
+        <v>7.622624426344595</v>
       </c>
       <c r="D123" t="n">
-        <v>7.215416044404066</v>
+        <v>7.21541557567713</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457642689852</v>
+        <v>7.621457147585694</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2952,16 +2952,16 @@
         <v>43930</v>
       </c>
       <c r="B127" t="n">
-        <v>7.385766506195068</v>
+        <v>7.38576602935791</v>
       </c>
       <c r="C127" t="n">
-        <v>7.778973921193609</v>
+        <v>7.778973418970338</v>
       </c>
       <c r="D127" t="n">
-        <v>7.351929706227764</v>
+        <v>7.351929231575166</v>
       </c>
       <c r="E127" t="n">
-        <v>7.778973921193609</v>
+        <v>7.778973418970338</v>
       </c>
       <c r="F127" t="n">
         <v>7590081</v>
@@ -2972,16 +2972,16 @@
         <v>43934</v>
       </c>
       <c r="B128" t="n">
-        <v>7.414936065673828</v>
+        <v>7.41493558883667</v>
       </c>
       <c r="C128" t="n">
-        <v>7.447606428031426</v>
+        <v>7.447605949093313</v>
       </c>
       <c r="D128" t="n">
-        <v>7.22941688022938</v>
+        <v>7.229416415322526</v>
       </c>
       <c r="E128" t="n">
-        <v>7.385766699549943</v>
+        <v>7.385766224588598</v>
       </c>
       <c r="F128" t="n">
         <v>8873976</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500111103057861</v>
+        <v>7.500110626220703</v>
       </c>
       <c r="C129" t="n">
-        <v>7.75097100706328</v>
+        <v>7.750970514277116</v>
       </c>
       <c r="D129" t="n">
-        <v>7.45577383571197</v>
+        <v>7.455773361693658</v>
       </c>
       <c r="E129" t="n">
-        <v>7.494278070349739</v>
+        <v>7.49427759388343</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265121459961</v>
+        <v>7.375265598297119</v>
       </c>
       <c r="C130" t="n">
-        <v>7.49427797970812</v>
+        <v>7.494278464239883</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762039125325</v>
+        <v>7.343762513925697</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935482620931</v>
+        <v>7.407935961570344</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.5666184425354</v>
+        <v>7.566619396209717</v>
       </c>
       <c r="C131" t="n">
-        <v>7.588787494454161</v>
+        <v>7.5887884509226</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234083504127451</v>
+        <v>7.234084415890043</v>
       </c>
       <c r="E131" t="n">
-        <v>7.44410543779982</v>
+        <v>7.444106376032958</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251523017883301</v>
+        <v>8.251522064208984</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431208332707222</v>
+        <v>8.431207358265677</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3112,16 +3112,16 @@
         <v>43944</v>
       </c>
       <c r="B135" t="n">
-        <v>8.089340209960938</v>
+        <v>8.089339256286621</v>
       </c>
       <c r="C135" t="n">
-        <v>8.574724018558863</v>
+        <v>8.57472300766133</v>
       </c>
       <c r="D135" t="n">
-        <v>7.969160906424007</v>
+        <v>7.969159966917957</v>
       </c>
       <c r="E135" t="n">
-        <v>8.481380364324728</v>
+        <v>8.481379364431731</v>
       </c>
       <c r="F135" t="n">
         <v>13472583</v>
@@ -3152,16 +3152,16 @@
         <v>43948</v>
       </c>
       <c r="B137" t="n">
-        <v>8.105674743652344</v>
+        <v>8.105673789978027</v>
       </c>
       <c r="C137" t="n">
-        <v>8.165180757388045</v>
+        <v>8.16517979671254</v>
       </c>
       <c r="D137" t="n">
-        <v>7.710134423961201</v>
+        <v>7.710133516824237</v>
       </c>
       <c r="E137" t="n">
-        <v>7.93765801086142</v>
+        <v>7.937657076955135</v>
       </c>
       <c r="F137" t="n">
         <v>12260436</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887483596801758</v>
+        <v>7.887484550476074</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966825772834317</v>
+        <v>7.966826736101882</v>
       </c>
       <c r="D139" t="n">
-        <v>7.700798002265745</v>
+        <v>7.700798933367937</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841979897039702</v>
+        <v>7.841980845212174</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3252,16 +3252,16 @@
         <v>43956</v>
       </c>
       <c r="B142" t="n">
-        <v>8.114090919494629</v>
+        <v>8.114091873168945</v>
       </c>
       <c r="C142" t="n">
-        <v>8.645023715587479</v>
+        <v>8.645024731663977</v>
       </c>
       <c r="D142" t="n">
-        <v>8.069432995707503</v>
+        <v>8.069433944133035</v>
       </c>
       <c r="E142" t="n">
-        <v>8.286520199683441</v>
+        <v>8.286521173623905</v>
       </c>
       <c r="F142" t="n">
         <v>11843548</v>
@@ -3272,16 +3272,16 @@
         <v>43957</v>
       </c>
       <c r="B143" t="n">
-        <v>8.048345565795898</v>
+        <v>8.048344612121582</v>
       </c>
       <c r="C143" t="n">
-        <v>8.145104858936216</v>
+        <v>8.145103893796581</v>
       </c>
       <c r="D143" t="n">
-        <v>7.963991997516411</v>
+        <v>7.96399105383742</v>
       </c>
       <c r="E143" t="n">
-        <v>8.145104858936216</v>
+        <v>8.145103893796581</v>
       </c>
       <c r="F143" t="n">
         <v>16545622</v>
@@ -3312,16 +3312,16 @@
         <v>43959</v>
       </c>
       <c r="B145" t="n">
-        <v>8.162469863891602</v>
+        <v>8.162470817565918</v>
       </c>
       <c r="C145" t="n">
-        <v>8.184799271833279</v>
+        <v>8.184800228116485</v>
       </c>
       <c r="D145" t="n">
-        <v>7.94786381115636</v>
+        <v>7.947864739756858</v>
       </c>
       <c r="E145" t="n">
-        <v>8.15626744912163</v>
+        <v>8.156268402071278</v>
       </c>
       <c r="F145" t="n">
         <v>8818844</v>
@@ -3352,16 +3352,16 @@
         <v>43963</v>
       </c>
       <c r="B147" t="n">
-        <v>8.085558891296387</v>
+        <v>8.085559844970703</v>
       </c>
       <c r="C147" t="n">
-        <v>8.276595411529883</v>
+        <v>8.276596387736546</v>
       </c>
       <c r="D147" t="n">
-        <v>8.063229483236768</v>
+        <v>8.063230434277379</v>
       </c>
       <c r="E147" t="n">
-        <v>8.187279566215866</v>
+        <v>8.187280531887918</v>
       </c>
       <c r="F147" t="n">
         <v>9953957</v>
@@ -3372,16 +3372,16 @@
         <v>43964</v>
       </c>
       <c r="B148" t="n">
-        <v>7.926775455474854</v>
+        <v>7.926775932312012</v>
       </c>
       <c r="C148" t="n">
-        <v>8.187279557292356</v>
+        <v>8.187280049800203</v>
       </c>
       <c r="D148" t="n">
-        <v>7.885839696513885</v>
+        <v>7.885840170888542</v>
       </c>
       <c r="E148" t="n">
-        <v>8.187279557292356</v>
+        <v>8.187280049800203</v>
       </c>
       <c r="F148" t="n">
         <v>10179016</v>
@@ -3412,16 +3412,16 @@
         <v>43966</v>
       </c>
       <c r="B150" t="n">
-        <v>6.8413405418396</v>
+        <v>6.841341018676758</v>
       </c>
       <c r="C150" t="n">
-        <v>7.421893104642092</v>
+        <v>7.421893621943401</v>
       </c>
       <c r="D150" t="n">
-        <v>6.8413405418396</v>
+        <v>6.841341018676758</v>
       </c>
       <c r="E150" t="n">
-        <v>7.420652532303285</v>
+        <v>7.420653049518127</v>
       </c>
       <c r="F150" t="n">
         <v>26563775</v>
@@ -3452,16 +3452,16 @@
         <v>43970</v>
       </c>
       <c r="B152" t="n">
-        <v>6.831418037414551</v>
+        <v>6.831417560577393</v>
       </c>
       <c r="C152" t="n">
-        <v>7.018732418962401</v>
+        <v>7.018731929050585</v>
       </c>
       <c r="D152" t="n">
-        <v>6.79916449333305</v>
+        <v>6.799164018747209</v>
       </c>
       <c r="E152" t="n">
-        <v>6.966631502251738</v>
+        <v>6.966631015976597</v>
       </c>
       <c r="F152" t="n">
         <v>13463520</v>
@@ -3472,16 +3472,16 @@
         <v>43971</v>
       </c>
       <c r="B153" t="n">
-        <v>6.822733879089355</v>
+        <v>6.822733402252197</v>
       </c>
       <c r="C153" t="n">
-        <v>6.983998022077899</v>
+        <v>6.983997533970078</v>
       </c>
       <c r="D153" t="n">
-        <v>6.810329048105121</v>
+        <v>6.81032857213493</v>
       </c>
       <c r="E153" t="n">
-        <v>6.94678397585636</v>
+        <v>6.946783490349408</v>
       </c>
       <c r="F153" t="n">
         <v>11533147</v>
@@ -3552,16 +3552,16 @@
         <v>43977</v>
       </c>
       <c r="B157" t="n">
-        <v>7.423134803771973</v>
+        <v>7.423134326934814</v>
       </c>
       <c r="C157" t="n">
-        <v>7.560829411371671</v>
+        <v>7.560828925689475</v>
       </c>
       <c r="D157" t="n">
-        <v>7.275515169821428</v>
+        <v>7.275514702466858</v>
       </c>
       <c r="E157" t="n">
-        <v>7.442982622817829</v>
+        <v>7.442982144705714</v>
       </c>
       <c r="F157" t="n">
         <v>12080691</v>
@@ -3612,16 +3612,16 @@
         <v>43980</v>
       </c>
       <c r="B160" t="n">
-        <v>7.812650203704834</v>
+        <v>7.812650680541992</v>
       </c>
       <c r="C160" t="n">
-        <v>7.812650203704834</v>
+        <v>7.812650680541992</v>
       </c>
       <c r="D160" t="n">
-        <v>7.481437043617326</v>
+        <v>7.481437500239227</v>
       </c>
       <c r="E160" t="n">
-        <v>7.519892999404318</v>
+        <v>7.519893458373339</v>
       </c>
       <c r="F160" t="n">
         <v>23712019</v>
@@ -3652,16 +3652,16 @@
         <v>43984</v>
       </c>
       <c r="B162" t="n">
-        <v>8.271634101867676</v>
+        <v>8.271635055541992</v>
       </c>
       <c r="C162" t="n">
-        <v>8.286520076241633</v>
+        <v>8.286521031632221</v>
       </c>
       <c r="D162" t="n">
-        <v>7.976395759027911</v>
+        <v>7.976396678662855</v>
       </c>
       <c r="E162" t="n">
-        <v>8.063229567170044</v>
+        <v>8.063230496816454</v>
       </c>
       <c r="F162" t="n">
         <v>21348142</v>
@@ -3672,16 +3672,16 @@
         <v>43985</v>
       </c>
       <c r="B163" t="n">
-        <v>8.373354911804199</v>
+        <v>8.373353958129883</v>
       </c>
       <c r="C163" t="n">
-        <v>8.800086825192951</v>
+        <v>8.80008582291646</v>
       </c>
       <c r="D163" t="n">
-        <v>8.315052026205343</v>
+        <v>8.315051079171372</v>
       </c>
       <c r="E163" t="n">
-        <v>8.317533171149149</v>
+        <v>8.31753222383259</v>
       </c>
       <c r="F163" t="n">
         <v>31125376</v>
@@ -3752,16 +3752,16 @@
         <v>43991</v>
       </c>
       <c r="B167" t="n">
-        <v>8.296442985534668</v>
+        <v>8.296443939208984</v>
       </c>
       <c r="C167" t="n">
-        <v>8.327455953773208</v>
+        <v>8.32745691101246</v>
       </c>
       <c r="D167" t="n">
-        <v>8.096723794435762</v>
+        <v>8.0967247251524</v>
       </c>
       <c r="E167" t="n">
-        <v>8.137660447910266</v>
+        <v>8.137661383332564</v>
       </c>
       <c r="F167" t="n">
         <v>13675741</v>
@@ -3772,16 +3772,16 @@
         <v>43992</v>
       </c>
       <c r="B168" t="n">
-        <v>8.08928108215332</v>
+        <v>8.089280128479004</v>
       </c>
       <c r="C168" t="n">
-        <v>8.426697131827968</v>
+        <v>8.426696138374464</v>
       </c>
       <c r="D168" t="n">
-        <v>8.0371806131882</v>
+        <v>8.037179665656195</v>
       </c>
       <c r="E168" t="n">
-        <v>8.311330595134894</v>
+        <v>8.311329615282364</v>
       </c>
       <c r="F168" t="n">
         <v>11944749</v>
@@ -3792,16 +3792,16 @@
         <v>43994</v>
       </c>
       <c r="B169" t="n">
-        <v>7.950345993041992</v>
+        <v>7.950345516204834</v>
       </c>
       <c r="C169" t="n">
-        <v>8.084319777785</v>
+        <v>8.084319292912509</v>
       </c>
       <c r="D169" t="n">
-        <v>7.774195424975465</v>
+        <v>7.774194958703272</v>
       </c>
       <c r="E169" t="n">
-        <v>7.877157131822456</v>
+        <v>7.877156659374939</v>
       </c>
       <c r="F169" t="n">
         <v>12251373</v>
@@ -3892,16 +3892,16 @@
         <v>44001</v>
       </c>
       <c r="B174" t="n">
-        <v>8.487480163574219</v>
+        <v>8.487481117248535</v>
       </c>
       <c r="C174" t="n">
-        <v>8.589200838114557</v>
+        <v>8.58920180321846</v>
       </c>
       <c r="D174" t="n">
-        <v>8.203406528896336</v>
+        <v>8.203407450651435</v>
       </c>
       <c r="E174" t="n">
-        <v>8.203406528896336</v>
+        <v>8.203407450651435</v>
       </c>
       <c r="F174" t="n">
         <v>20750754</v>
@@ -3912,16 +3912,16 @@
         <v>44004</v>
       </c>
       <c r="B175" t="n">
-        <v>8.440342903137207</v>
+        <v>8.440341949462891</v>
       </c>
       <c r="C175" t="n">
-        <v>8.729377964833343</v>
+        <v>8.729376978500955</v>
       </c>
       <c r="D175" t="n">
-        <v>8.380798106578508</v>
+        <v>8.380797159632158</v>
       </c>
       <c r="E175" t="n">
-        <v>8.489962226742637</v>
+        <v>8.489961267461833</v>
       </c>
       <c r="F175" t="n">
         <v>12069362</v>
@@ -3952,16 +3952,16 @@
         <v>44006</v>
       </c>
       <c r="B177" t="n">
-        <v>8.594162940979004</v>
+        <v>8.59416389465332</v>
       </c>
       <c r="C177" t="n">
-        <v>8.669832935726904</v>
+        <v>8.669833897798144</v>
       </c>
       <c r="D177" t="n">
-        <v>8.422973795079262</v>
+        <v>8.422974729757115</v>
       </c>
       <c r="E177" t="n">
-        <v>8.571833533486773</v>
+        <v>8.571834484683247</v>
       </c>
       <c r="F177" t="n">
         <v>7388434</v>
@@ -4052,16 +4052,16 @@
         <v>44013</v>
       </c>
       <c r="B182" t="n">
-        <v>9.009730339050293</v>
+        <v>9.009729385375977</v>
       </c>
       <c r="C182" t="n">
-        <v>9.11517229493286</v>
+        <v>9.115171330097578</v>
       </c>
       <c r="D182" t="n">
-        <v>8.731859089723871</v>
+        <v>8.731858165462054</v>
       </c>
       <c r="E182" t="n">
-        <v>8.812491383860499</v>
+        <v>8.812490451063802</v>
       </c>
       <c r="F182" t="n">
         <v>8963093</v>
@@ -4292,16 +4292,16 @@
         <v>44029</v>
       </c>
       <c r="B194" t="n">
-        <v>8.81993293762207</v>
+        <v>8.819933891296387</v>
       </c>
       <c r="C194" t="n">
-        <v>8.919173360420668</v>
+        <v>8.919174324825571</v>
       </c>
       <c r="D194" t="n">
-        <v>8.633858708433587</v>
+        <v>8.633859641988225</v>
       </c>
       <c r="E194" t="n">
-        <v>8.633858708433587</v>
+        <v>8.633859641988225</v>
       </c>
       <c r="F194" t="n">
         <v>9678298</v>
@@ -4432,16 +4432,16 @@
         <v>44040</v>
       </c>
       <c r="B201" t="n">
-        <v>9.641143798828125</v>
+        <v>9.641142845153809</v>
       </c>
       <c r="C201" t="n">
-        <v>9.832180339834917</v>
+        <v>9.832179367263814</v>
       </c>
       <c r="D201" t="n">
-        <v>9.466233359369541</v>
+        <v>9.466232422996864</v>
       </c>
       <c r="E201" t="n">
-        <v>9.675878040270206</v>
+        <v>9.67587708316008</v>
       </c>
       <c r="F201" t="n">
         <v>30127714</v>
@@ -4472,16 +4472,16 @@
         <v>44042</v>
       </c>
       <c r="B203" t="n">
-        <v>9.143704414367676</v>
+        <v>9.143703460693359</v>
       </c>
       <c r="C203" t="n">
-        <v>9.700687950073165</v>
+        <v>9.700686938306321</v>
       </c>
       <c r="D203" t="n">
-        <v>9.097806359971171</v>
+        <v>9.097805411083952</v>
       </c>
       <c r="E203" t="n">
-        <v>9.685801080392711</v>
+        <v>9.685800070178546</v>
       </c>
       <c r="F203" t="n">
         <v>33272500</v>
@@ -4592,16 +4592,16 @@
         <v>44050</v>
       </c>
       <c r="B209" t="n">
-        <v>8.429177284240723</v>
+        <v>8.429178237915039</v>
       </c>
       <c r="C209" t="n">
-        <v>8.429177284240723</v>
+        <v>8.429178237915039</v>
       </c>
       <c r="D209" t="n">
-        <v>8.255506990060143</v>
+        <v>8.25550792408546</v>
       </c>
       <c r="E209" t="n">
-        <v>8.336140169103194</v>
+        <v>8.336141112251321</v>
       </c>
       <c r="F209" t="n">
         <v>22110172</v>
@@ -4612,16 +4612,16 @@
         <v>44053</v>
       </c>
       <c r="B210" t="n">
-        <v>8.259230613708496</v>
+        <v>8.25922966003418</v>
       </c>
       <c r="C210" t="n">
-        <v>8.468874414585619</v>
+        <v>8.468873436704216</v>
       </c>
       <c r="D210" t="n">
-        <v>8.166192588662099</v>
+        <v>8.166191645730668</v>
       </c>
       <c r="E210" t="n">
-        <v>8.435380296706972</v>
+        <v>8.435379322693057</v>
       </c>
       <c r="F210" t="n">
         <v>21920608</v>
@@ -4652,16 +4652,16 @@
         <v>44055</v>
       </c>
       <c r="B212" t="n">
-        <v>8.162469863891602</v>
+        <v>8.162470817565918</v>
       </c>
       <c r="C212" t="n">
-        <v>8.446543498127859</v>
+        <v>8.446544484992341</v>
       </c>
       <c r="D212" t="n">
-        <v>8.078115414787984</v>
+        <v>8.078116358606623</v>
       </c>
       <c r="E212" t="n">
-        <v>8.409329009508031</v>
+        <v>8.409329992024503</v>
       </c>
       <c r="F212" t="n">
         <v>20200945</v>
@@ -4732,16 +4732,16 @@
         <v>44061</v>
       </c>
       <c r="B216" t="n">
-        <v>8.101686477661133</v>
+        <v>8.101685523986816</v>
       </c>
       <c r="C216" t="n">
-        <v>8.143864156905972</v>
+        <v>8.143863198266791</v>
       </c>
       <c r="D216" t="n">
-        <v>7.9788782846482</v>
+        <v>7.978877345430011</v>
       </c>
       <c r="E216" t="n">
-        <v>8.038421298987467</v>
+        <v>8.038420352760289</v>
       </c>
       <c r="F216" t="n">
         <v>10608743</v>
@@ -4752,16 +4752,16 @@
         <v>44062</v>
       </c>
       <c r="B217" t="n">
-        <v>7.926775455474854</v>
+        <v>7.926775932312012</v>
       </c>
       <c r="C217" t="n">
-        <v>8.141381509109719</v>
+        <v>8.141381998856557</v>
       </c>
       <c r="D217" t="n">
-        <v>7.921813166253184</v>
+        <v>7.921813642791834</v>
       </c>
       <c r="E217" t="n">
-        <v>8.141381509109719</v>
+        <v>8.141381998856557</v>
       </c>
       <c r="F217" t="n">
         <v>9466833</v>
@@ -4772,16 +4772,16 @@
         <v>44063</v>
       </c>
       <c r="B218" t="n">
-        <v>7.957788467407227</v>
+        <v>7.957787990570068</v>
       </c>
       <c r="C218" t="n">
-        <v>8.033459366376674</v>
+        <v>8.033458885005254</v>
       </c>
       <c r="D218" t="n">
-        <v>7.774195359575069</v>
+        <v>7.774194893738959</v>
       </c>
       <c r="E218" t="n">
-        <v>7.915611684438519</v>
+        <v>7.915611210128628</v>
       </c>
       <c r="F218" t="n">
         <v>7652765</v>
@@ -4892,16 +4892,16 @@
         <v>44071</v>
       </c>
       <c r="B224" t="n">
-        <v>8.100445747375488</v>
+        <v>8.100444793701172</v>
       </c>
       <c r="C224" t="n">
-        <v>8.100445747375488</v>
+        <v>8.100444793701172</v>
       </c>
       <c r="D224" t="n">
-        <v>7.960269549341362</v>
+        <v>7.960268612170143</v>
       </c>
       <c r="E224" t="n">
-        <v>8.0012070997281</v>
+        <v>8.001206157737258</v>
       </c>
       <c r="F224" t="n">
         <v>5577388</v>
@@ -5012,16 +5012,16 @@
         <v>44082</v>
       </c>
       <c r="B230" t="n">
-        <v>7.751865863800049</v>
+        <v>7.751865386962891</v>
       </c>
       <c r="C230" t="n">
-        <v>7.833738283935308</v>
+        <v>7.833737802061967</v>
       </c>
       <c r="D230" t="n">
-        <v>7.691081834917614</v>
+        <v>7.691081361819436</v>
       </c>
       <c r="E230" t="n">
-        <v>7.813890911851665</v>
+        <v>7.813890431199186</v>
       </c>
       <c r="F230" t="n">
         <v>7181501</v>
@@ -5032,16 +5032,16 @@
         <v>44083</v>
       </c>
       <c r="B231" t="n">
-        <v>7.709688663482666</v>
+        <v>7.709689140319824</v>
       </c>
       <c r="C231" t="n">
-        <v>7.834979771965168</v>
+        <v>7.834980256551466</v>
       </c>
       <c r="D231" t="n">
-        <v>7.637739933288351</v>
+        <v>7.637740405675546</v>
       </c>
       <c r="E231" t="n">
-        <v>7.792802098282933</v>
+        <v>7.792802580260581</v>
       </c>
       <c r="F231" t="n">
         <v>8282629</v>
@@ -5052,16 +5052,16 @@
         <v>44084</v>
       </c>
       <c r="B232" t="n">
-        <v>8.850947380065918</v>
+        <v>8.850946426391602</v>
       </c>
       <c r="C232" t="n">
-        <v>9.197045218135978</v>
+        <v>9.197044227170217</v>
       </c>
       <c r="D232" t="n">
-        <v>8.621455315968662</v>
+        <v>8.62145438702172</v>
       </c>
       <c r="E232" t="n">
-        <v>9.197045218135978</v>
+        <v>9.197044227170217</v>
       </c>
       <c r="F232" t="n">
         <v>139609921</v>
@@ -5132,16 +5132,16 @@
         <v>44090</v>
       </c>
       <c r="B236" t="n">
-        <v>9.312410354614258</v>
+        <v>9.312411308288574</v>
       </c>
       <c r="C236" t="n">
-        <v>9.375675522060035</v>
+        <v>9.375676482213272</v>
       </c>
       <c r="D236" t="n">
-        <v>9.175956334671081</v>
+        <v>9.175957274371282</v>
       </c>
       <c r="E236" t="n">
-        <v>9.179677604882659</v>
+        <v>9.179678544963952</v>
       </c>
       <c r="F236" t="n">
         <v>13993693</v>
@@ -5212,16 +5212,16 @@
         <v>44096</v>
       </c>
       <c r="B240" t="n">
-        <v>9.326058387756348</v>
+        <v>9.326057434082031</v>
       </c>
       <c r="C240" t="n">
-        <v>9.353349195522698</v>
+        <v>9.353348239057649</v>
       </c>
       <c r="D240" t="n">
-        <v>9.182159127084132</v>
+        <v>9.182158188124824</v>
       </c>
       <c r="E240" t="n">
-        <v>9.192083706971793</v>
+        <v>9.192082766997606</v>
       </c>
       <c r="F240" t="n">
         <v>9315031</v>
@@ -5232,16 +5232,16 @@
         <v>44097</v>
       </c>
       <c r="B241" t="n">
-        <v>8.95390796661377</v>
+        <v>8.953908920288086</v>
       </c>
       <c r="C241" t="n">
-        <v>9.308689320943529</v>
+        <v>9.308690312405352</v>
       </c>
       <c r="D241" t="n">
-        <v>8.934059702543932</v>
+        <v>8.934060654104224</v>
       </c>
       <c r="E241" t="n">
-        <v>9.303727925022763</v>
+        <v>9.303728915956151</v>
       </c>
       <c r="F241" t="n">
         <v>13677251</v>
@@ -5252,16 +5252,16 @@
         <v>44098</v>
       </c>
       <c r="B242" t="n">
-        <v>9.282639503479004</v>
+        <v>9.282638549804688</v>
       </c>
       <c r="C242" t="n">
-        <v>9.46375236122295</v>
+        <v>9.463751388941567</v>
       </c>
       <c r="D242" t="n">
-        <v>8.898085270619518</v>
+        <v>8.898084356453305</v>
       </c>
       <c r="E242" t="n">
-        <v>8.906769724577019</v>
+        <v>8.906768809518589</v>
       </c>
       <c r="F242" t="n">
         <v>18607406</v>
@@ -5272,16 +5272,16 @@
         <v>44099</v>
       </c>
       <c r="B243" t="n">
-        <v>9.184640884399414</v>
+        <v>9.184639930725098</v>
       </c>
       <c r="C243" t="n">
-        <v>9.254108474175018</v>
+        <v>9.25410751328763</v>
       </c>
       <c r="D243" t="n">
-        <v>9.095325028918353</v>
+        <v>9.095324084518023</v>
       </c>
       <c r="E243" t="n">
-        <v>9.22061435827287</v>
+        <v>9.220613400863298</v>
       </c>
       <c r="F243" t="n">
         <v>8201819</v>
@@ -5312,16 +5312,16 @@
         <v>44103</v>
       </c>
       <c r="B245" t="n">
-        <v>8.760390281677246</v>
+        <v>8.760391235351562</v>
       </c>
       <c r="C245" t="n">
-        <v>8.942743247933565</v>
+        <v>8.942744221459206</v>
       </c>
       <c r="D245" t="n">
-        <v>8.683479263674647</v>
+        <v>8.68348020897627</v>
       </c>
       <c r="E245" t="n">
-        <v>8.802567060978735</v>
+        <v>8.802568019244504</v>
       </c>
       <c r="F245" t="n">
         <v>13985386</v>
@@ -5332,16 +5332,16 @@
         <v>44104</v>
       </c>
       <c r="B246" t="n">
-        <v>8.651226997375488</v>
+        <v>8.651226043701172</v>
       </c>
       <c r="C246" t="n">
-        <v>8.841023415853394</v>
+        <v>8.841022441256731</v>
       </c>
       <c r="D246" t="n">
-        <v>8.609050214038696</v>
+        <v>8.609049265013768</v>
       </c>
       <c r="E246" t="n">
-        <v>8.803808028904122</v>
+        <v>8.803807058409923</v>
       </c>
       <c r="F246" t="n">
         <v>11477260</v>
@@ -5412,16 +5412,16 @@
         <v>44110</v>
       </c>
       <c r="B250" t="n">
-        <v>8.497404098510742</v>
+        <v>8.497405052185059</v>
       </c>
       <c r="C250" t="n">
-        <v>8.520973632751547</v>
+        <v>8.520974589071102</v>
       </c>
       <c r="D250" t="n">
-        <v>8.3162921520784</v>
+        <v>8.316293085426295</v>
       </c>
       <c r="E250" t="n">
-        <v>8.48872053887138</v>
+        <v>8.488721491571129</v>
       </c>
       <c r="F250" t="n">
         <v>10544549</v>
@@ -5432,16 +5432,16 @@
         <v>44111</v>
       </c>
       <c r="B251" t="n">
-        <v>8.585479736328125</v>
+        <v>8.585480690002441</v>
       </c>
       <c r="C251" t="n">
-        <v>8.704567531971968</v>
+        <v>8.704568498874545</v>
       </c>
       <c r="D251" t="n">
-        <v>8.440342155483876</v>
+        <v>8.440343093036322</v>
       </c>
       <c r="E251" t="n">
-        <v>8.477556644891454</v>
+        <v>8.477557586577683</v>
       </c>
       <c r="F251" t="n">
         <v>12680345</v>
@@ -5552,16 +5552,16 @@
         <v>44120</v>
       </c>
       <c r="B257" t="n">
-        <v>8.259230613708496</v>
+        <v>8.25922966003418</v>
       </c>
       <c r="C257" t="n">
-        <v>8.267913281163274</v>
+        <v>8.267912326486389</v>
       </c>
       <c r="D257" t="n">
-        <v>8.097965120577188</v>
+        <v>8.097964185523827</v>
       </c>
       <c r="E257" t="n">
-        <v>8.122775677538673</v>
+        <v>8.122774739620494</v>
       </c>
       <c r="F257" t="n">
         <v>10726560</v>
@@ -5612,16 +5612,16 @@
         <v>44125</v>
       </c>
       <c r="B260" t="n">
-        <v>8.275356292724609</v>
+        <v>8.275355339050293</v>
       </c>
       <c r="C260" t="n">
-        <v>8.355988588431988</v>
+        <v>8.355987625465389</v>
       </c>
       <c r="D260" t="n">
-        <v>8.245584340664582</v>
+        <v>8.245583390421267</v>
       </c>
       <c r="E260" t="n">
-        <v>8.35474846270546</v>
+        <v>8.354747499881778</v>
       </c>
       <c r="F260" t="n">
         <v>4665068</v>
@@ -5632,16 +5632,16 @@
         <v>44126</v>
       </c>
       <c r="B261" t="n">
-        <v>8.267912864685059</v>
+        <v>8.267911911010742</v>
       </c>
       <c r="C261" t="n">
-        <v>8.337381348523031</v>
+        <v>8.337380386835774</v>
       </c>
       <c r="D261" t="n">
-        <v>8.168674215687588</v>
+        <v>8.168673273460097</v>
       </c>
       <c r="E261" t="n">
-        <v>8.306368377248981</v>
+        <v>8.30636741913896</v>
       </c>
       <c r="F261" t="n">
         <v>7908034</v>
@@ -5652,16 +5652,16 @@
         <v>44127</v>
       </c>
       <c r="B262" t="n">
-        <v>8.234420776367188</v>
+        <v>8.234419822692871</v>
       </c>
       <c r="C262" t="n">
-        <v>8.312571929509362</v>
+        <v>8.312570966783923</v>
       </c>
       <c r="D262" t="n">
-        <v>8.203407804185662</v>
+        <v>8.203406854103131</v>
       </c>
       <c r="E262" t="n">
-        <v>8.269153232377807</v>
+        <v>8.269152274680931</v>
       </c>
       <c r="F262" t="n">
         <v>5098571</v>
@@ -5712,16 +5712,16 @@
         <v>44132</v>
       </c>
       <c r="B265" t="n">
-        <v>7.825055122375488</v>
+        <v>7.825055599212646</v>
       </c>
       <c r="C265" t="n">
-        <v>8.088040380288025</v>
+        <v>8.088040873150774</v>
       </c>
       <c r="D265" t="n">
-        <v>7.81761168821794</v>
+        <v>7.817612164601516</v>
       </c>
       <c r="E265" t="n">
-        <v>8.078115801411293</v>
+        <v>8.078116293669268</v>
       </c>
       <c r="F265" t="n">
         <v>12369944</v>
@@ -5752,16 +5752,16 @@
         <v>44134</v>
       </c>
       <c r="B267" t="n">
-        <v>7.684879302978516</v>
+        <v>7.684878826141357</v>
       </c>
       <c r="C267" t="n">
-        <v>7.777916426914608</v>
+        <v>7.777915944304612</v>
       </c>
       <c r="D267" t="n">
-        <v>7.574475058635726</v>
+        <v>7.574474588649013</v>
       </c>
       <c r="E267" t="n">
-        <v>7.759309180819852</v>
+        <v>7.759308699364413</v>
       </c>
       <c r="F267" t="n">
         <v>16269207</v>
@@ -5772,16 +5772,16 @@
         <v>44138</v>
       </c>
       <c r="B268" t="n">
-        <v>7.7171311378479</v>
+        <v>7.717131614685059</v>
       </c>
       <c r="C268" t="n">
-        <v>7.852345930671059</v>
+        <v>7.852346415863062</v>
       </c>
       <c r="D268" t="n">
-        <v>7.622853892715106</v>
+        <v>7.622854363726927</v>
       </c>
       <c r="E268" t="n">
-        <v>7.821333855323877</v>
+        <v>7.821334338599661</v>
       </c>
       <c r="F268" t="n">
         <v>9901091</v>
@@ -5812,16 +5812,16 @@
         <v>44140</v>
       </c>
       <c r="B270" t="n">
-        <v>8.119052886962891</v>
+        <v>8.119053840637207</v>
       </c>
       <c r="C270" t="n">
-        <v>8.177355763964984</v>
+        <v>8.177356724487632</v>
       </c>
       <c r="D270" t="n">
-        <v>8.007407635190189</v>
+        <v>8.007408575750512</v>
       </c>
       <c r="E270" t="n">
-        <v>8.039660727779241</v>
+        <v>8.039661672128053</v>
       </c>
       <c r="F270" t="n">
         <v>9820281</v>
@@ -5892,16 +5892,16 @@
         <v>44146</v>
       </c>
       <c r="B274" t="n">
-        <v>8.193482398986816</v>
+        <v>8.193483352661133</v>
       </c>
       <c r="C274" t="n">
-        <v>8.420493294041393</v>
+        <v>8.420494274138473</v>
       </c>
       <c r="D274" t="n">
-        <v>8.193482398986816</v>
+        <v>8.193483352661133</v>
       </c>
       <c r="E274" t="n">
-        <v>8.312571092276054</v>
+        <v>8.312572059811611</v>
       </c>
       <c r="F274" t="n">
         <v>7246451</v>
@@ -5912,16 +5912,16 @@
         <v>44147</v>
       </c>
       <c r="B275" t="n">
-        <v>8.234420776367188</v>
+        <v>8.234419822692871</v>
       </c>
       <c r="C275" t="n">
-        <v>8.398165624159189</v>
+        <v>8.398164651520666</v>
       </c>
       <c r="D275" t="n">
-        <v>8.13145906678732</v>
+        <v>8.131458125037573</v>
       </c>
       <c r="E275" t="n">
-        <v>8.193483224225638</v>
+        <v>8.193482275292528</v>
       </c>
       <c r="F275" t="n">
         <v>11697033</v>
@@ -5932,16 +5932,16 @@
         <v>44148</v>
       </c>
       <c r="B276" t="n">
-        <v>8.633859634399414</v>
+        <v>8.633858680725098</v>
       </c>
       <c r="C276" t="n">
-        <v>8.646265358676397</v>
+        <v>8.646264403631776</v>
       </c>
       <c r="D276" t="n">
-        <v>8.267912658055211</v>
+        <v>8.267911744802472</v>
       </c>
       <c r="E276" t="n">
-        <v>8.322494271024663</v>
+        <v>8.322493351742979</v>
       </c>
       <c r="F276" t="n">
         <v>10854949</v>
@@ -5992,16 +5992,16 @@
         <v>44153</v>
       </c>
       <c r="B279" t="n">
-        <v>8.584240913391113</v>
+        <v>8.584239959716797</v>
       </c>
       <c r="C279" t="n">
-        <v>8.645024946032365</v>
+        <v>8.64502398560519</v>
       </c>
       <c r="D279" t="n">
-        <v>8.516013445661457</v>
+        <v>8.516012499566937</v>
       </c>
       <c r="E279" t="n">
-        <v>8.558190230775271</v>
+        <v>8.55818927999508</v>
       </c>
       <c r="F279" t="n">
         <v>8922310</v>
@@ -6072,16 +6072,16 @@
         <v>44160</v>
       </c>
       <c r="B283" t="n">
-        <v>8.739302635192871</v>
+        <v>8.739301681518555</v>
       </c>
       <c r="C283" t="n">
-        <v>8.920414597775554</v>
+        <v>8.920413624337439</v>
       </c>
       <c r="D283" t="n">
-        <v>8.616492663682914</v>
+        <v>8.616491723410208</v>
       </c>
       <c r="E283" t="n">
-        <v>8.85466827854489</v>
+        <v>8.854667312281327</v>
       </c>
       <c r="F283" t="n">
         <v>6633202</v>
@@ -6112,16 +6112,16 @@
         <v>44162</v>
       </c>
       <c r="B285" t="n">
-        <v>8.615252494812012</v>
+        <v>8.615251541137695</v>
       </c>
       <c r="C285" t="n">
-        <v>8.708288727073548</v>
+        <v>8.70828776310049</v>
       </c>
       <c r="D285" t="n">
-        <v>8.507329393233835</v>
+        <v>8.507328451506179</v>
       </c>
       <c r="E285" t="n">
-        <v>8.566872403188754</v>
+        <v>8.566871454869922</v>
       </c>
       <c r="F285" t="n">
         <v>5230736</v>
@@ -6152,16 +6152,16 @@
         <v>44166</v>
       </c>
       <c r="B287" t="n">
-        <v>8.414292335510254</v>
+        <v>8.414291381835938</v>
       </c>
       <c r="C287" t="n">
-        <v>8.672315323428652</v>
+        <v>8.672314340510058</v>
       </c>
       <c r="D287" t="n">
-        <v>8.360949953683695</v>
+        <v>8.360949006055193</v>
       </c>
       <c r="E287" t="n">
-        <v>8.636340955945199</v>
+        <v>8.636339977103933</v>
       </c>
       <c r="F287" t="n">
         <v>16096259</v>
@@ -6172,16 +6172,16 @@
         <v>44167</v>
       </c>
       <c r="B288" t="n">
-        <v>8.282798767089844</v>
+        <v>8.282797813415527</v>
       </c>
       <c r="C288" t="n">
-        <v>8.4614304780068</v>
+        <v>8.461429503764982</v>
       </c>
       <c r="D288" t="n">
-        <v>8.199686220600897</v>
+        <v>8.199685276496087</v>
       </c>
       <c r="E288" t="n">
-        <v>8.456469081678438</v>
+        <v>8.456468108007872</v>
       </c>
       <c r="F288" t="n">
         <v>15329699</v>
@@ -6212,16 +6212,16 @@
         <v>44169</v>
       </c>
       <c r="B290" t="n">
-        <v>8.772794723510742</v>
+        <v>8.772793769836426</v>
       </c>
       <c r="C290" t="n">
-        <v>8.948945284925747</v>
+        <v>8.948944312102428</v>
       </c>
       <c r="D290" t="n">
-        <v>8.683479763850318</v>
+        <v>8.683478819885265</v>
       </c>
       <c r="E290" t="n">
-        <v>8.886920238013465</v>
+        <v>8.886919271932774</v>
       </c>
       <c r="F290" t="n">
         <v>10446369</v>
@@ -6232,16 +6232,16 @@
         <v>44172</v>
       </c>
       <c r="B291" t="n">
-        <v>8.647504806518555</v>
+        <v>8.647505760192871</v>
       </c>
       <c r="C291" t="n">
-        <v>8.827376626156168</v>
+        <v>8.82737759966732</v>
       </c>
       <c r="D291" t="n">
-        <v>8.621454127772409</v>
+        <v>8.621455078573774</v>
       </c>
       <c r="E291" t="n">
-        <v>8.807528362331166</v>
+        <v>8.807529333653388</v>
       </c>
       <c r="F291" t="n">
         <v>10174485</v>
@@ -6392,16 +6392,16 @@
         <v>44182</v>
       </c>
       <c r="B299" t="n">
-        <v>9.125097274780273</v>
+        <v>9.125096321105957</v>
       </c>
       <c r="C299" t="n">
-        <v>9.233020380265208</v>
+        <v>9.233019415311725</v>
       </c>
       <c r="D299" t="n">
-        <v>9.105249008435251</v>
+        <v>9.1052480568353</v>
       </c>
       <c r="E299" t="n">
-        <v>9.230539235289285</v>
+        <v>9.230538270595108</v>
       </c>
       <c r="F299" t="n">
         <v>5262456</v>
@@ -6452,16 +6452,16 @@
         <v>44187</v>
       </c>
       <c r="B302" t="n">
-        <v>9.018414497375488</v>
+        <v>9.018413543701172</v>
       </c>
       <c r="C302" t="n">
-        <v>9.117654044402261</v>
+        <v>9.117653080233614</v>
       </c>
       <c r="D302" t="n">
-        <v>8.941504362170608</v>
+        <v>8.941503416629342</v>
       </c>
       <c r="E302" t="n">
-        <v>8.974996692978687</v>
+        <v>8.974995743895692</v>
       </c>
       <c r="F302" t="n">
         <v>3700636</v>
@@ -6572,16 +6572,16 @@
         <v>44201</v>
       </c>
       <c r="B308" t="n">
-        <v>9.097805976867676</v>
+        <v>9.097805023193359</v>
       </c>
       <c r="C308" t="n">
-        <v>9.304968615993069</v>
+        <v>9.304967640603</v>
       </c>
       <c r="D308" t="n">
-        <v>9.012211393852336</v>
+        <v>9.012210449150441</v>
       </c>
       <c r="E308" t="n">
-        <v>9.304968615993069</v>
+        <v>9.304967640603</v>
       </c>
       <c r="F308" t="n">
         <v>8306796</v>
@@ -6592,16 +6592,16 @@
         <v>44202</v>
       </c>
       <c r="B309" t="n">
-        <v>9.023375511169434</v>
+        <v>9.02337646484375</v>
       </c>
       <c r="C309" t="n">
-        <v>9.178437672356514</v>
+        <v>9.178438642419241</v>
       </c>
       <c r="D309" t="n">
-        <v>8.883199324604012</v>
+        <v>8.883200263463204</v>
       </c>
       <c r="E309" t="n">
-        <v>9.091602075844966</v>
+        <v>9.091603036730099</v>
       </c>
       <c r="F309" t="n">
         <v>6995714</v>
@@ -6632,16 +6632,16 @@
         <v>44204</v>
       </c>
       <c r="B311" t="n">
-        <v>9.49476432800293</v>
+        <v>9.494765281677246</v>
       </c>
       <c r="C311" t="n">
-        <v>9.533219836566508</v>
+        <v>9.533220794103377</v>
       </c>
       <c r="D311" t="n">
-        <v>9.077957042182957</v>
+        <v>9.077957953992263</v>
       </c>
       <c r="E311" t="n">
-        <v>9.178437593380119</v>
+        <v>9.178438515281906</v>
       </c>
       <c r="F311" t="n">
         <v>10280973</v>
@@ -6732,16 +6732,16 @@
         <v>44211</v>
       </c>
       <c r="B316" t="n">
-        <v>9.479877471923828</v>
+        <v>9.479878425598145</v>
       </c>
       <c r="C316" t="n">
-        <v>9.607648827608905</v>
+        <v>9.607649794137002</v>
       </c>
       <c r="D316" t="n">
-        <v>9.378157688462947</v>
+        <v>9.378158631904267</v>
       </c>
       <c r="E316" t="n">
-        <v>9.589041582834192</v>
+        <v>9.589042547490402</v>
       </c>
       <c r="F316" t="n">
         <v>14334303</v>
@@ -6892,16 +6892,16 @@
         <v>44224</v>
       </c>
       <c r="B324" t="n">
-        <v>9.368233680725098</v>
+        <v>9.368232727050781</v>
       </c>
       <c r="C324" t="n">
-        <v>9.399245757239534</v>
+        <v>9.399244800408228</v>
       </c>
       <c r="D324" t="n">
-        <v>9.102767267989694</v>
+        <v>9.102766341339521</v>
       </c>
       <c r="E324" t="n">
-        <v>9.180918415575915</v>
+        <v>9.180917480970056</v>
       </c>
       <c r="F324" t="n">
         <v>7429217</v>
@@ -6912,16 +6912,16 @@
         <v>44225</v>
       </c>
       <c r="B325" t="n">
-        <v>9.36327075958252</v>
+        <v>9.363271713256836</v>
       </c>
       <c r="C325" t="n">
-        <v>9.571675294860224</v>
+        <v>9.571676269761104</v>
       </c>
       <c r="D325" t="n">
-        <v>9.215652034482874</v>
+        <v>9.215652973121827</v>
       </c>
       <c r="E325" t="n">
-        <v>9.312410421451789</v>
+        <v>9.312411369945844</v>
       </c>
       <c r="F325" t="n">
         <v>11022611</v>
@@ -6952,16 +6952,16 @@
         <v>44229</v>
       </c>
       <c r="B327" t="n">
-        <v>10.133620262146</v>
+        <v>10.13361930847168</v>
       </c>
       <c r="C327" t="n">
-        <v>10.18448060527895</v>
+        <v>10.18447964681817</v>
       </c>
       <c r="D327" t="n">
-        <v>9.832180367414875</v>
+        <v>9.832179442109044</v>
       </c>
       <c r="E327" t="n">
-        <v>10.11005072588166</v>
+        <v>10.11004977442547</v>
       </c>
       <c r="F327" t="n">
         <v>20046878</v>
@@ -6992,16 +6992,16 @@
         <v>44231</v>
       </c>
       <c r="B329" t="n">
-        <v>10.38668155670166</v>
+        <v>10.38668251037598</v>
       </c>
       <c r="C329" t="n">
-        <v>10.38668155670166</v>
+        <v>10.38668251037598</v>
       </c>
       <c r="D329" t="n">
-        <v>10.11749300250636</v>
+        <v>10.11749393146458</v>
       </c>
       <c r="E329" t="n">
-        <v>10.17703779267104</v>
+        <v>10.17703872709649</v>
       </c>
       <c r="F329" t="n">
         <v>12166787</v>
@@ -7012,16 +7012,16 @@
         <v>44232</v>
       </c>
       <c r="B330" t="n">
-        <v>10.5566291809082</v>
+        <v>10.55663013458252</v>
       </c>
       <c r="C330" t="n">
-        <v>10.58143973441847</v>
+        <v>10.58144069033415</v>
       </c>
       <c r="D330" t="n">
-        <v>10.32465689384235</v>
+        <v>10.32465782656054</v>
       </c>
       <c r="E330" t="n">
-        <v>10.41893413810214</v>
+        <v>10.41893507933724</v>
       </c>
       <c r="F330" t="n">
         <v>10745440</v>
@@ -7192,16 +7192,16 @@
         <v>44249</v>
       </c>
       <c r="B339" t="n">
-        <v>11.09376621246338</v>
+        <v>11.09376525878906</v>
       </c>
       <c r="C339" t="n">
-        <v>11.20292944052197</v>
+        <v>11.20292847746345</v>
       </c>
       <c r="D339" t="n">
-        <v>10.63602222835513</v>
+        <v>10.63602131403072</v>
       </c>
       <c r="E339" t="n">
-        <v>10.93994416306512</v>
+        <v>10.9399432226141</v>
       </c>
       <c r="F339" t="n">
         <v>14982292</v>
@@ -7292,16 +7292,16 @@
         <v>44256</v>
       </c>
       <c r="B344" t="n">
-        <v>21.85701560974121</v>
+        <v>21.85701751708984</v>
       </c>
       <c r="C344" t="n">
-        <v>23.99306407785948</v>
+        <v>23.99306617161</v>
       </c>
       <c r="D344" t="n">
-        <v>16.3107860983666</v>
+        <v>16.31078752172449</v>
       </c>
       <c r="E344" t="n">
-        <v>16.8635354591482</v>
+        <v>16.86353693074166</v>
       </c>
       <c r="F344" t="n">
         <v>49361500</v>
@@ -7312,16 +7312,16 @@
         <v>44257</v>
       </c>
       <c r="B345" t="n">
-        <v>21.19184303283691</v>
+        <v>21.19184494018555</v>
       </c>
       <c r="C345" t="n">
-        <v>22.95314478521037</v>
+        <v>22.95314685108304</v>
       </c>
       <c r="D345" t="n">
-        <v>20.6953049717416</v>
+        <v>20.69530683439987</v>
       </c>
       <c r="E345" t="n">
-        <v>22.18491736810308</v>
+        <v>22.18491936483229</v>
       </c>
       <c r="F345" t="n">
         <v>20095700</v>
@@ -7352,16 +7352,16 @@
         <v>44259</v>
       </c>
       <c r="B347" t="n">
-        <v>20.86394119262695</v>
+        <v>20.86394309997559</v>
       </c>
       <c r="C347" t="n">
-        <v>21.52911312081577</v>
+        <v>21.52911508897337</v>
       </c>
       <c r="D347" t="n">
-        <v>20.01139593391831</v>
+        <v>20.0113977633286</v>
       </c>
       <c r="E347" t="n">
-        <v>20.2362428583874</v>
+        <v>20.23624470835284</v>
       </c>
       <c r="F347" t="n">
         <v>8984600</v>
@@ -7732,16 +7732,16 @@
         <v>44286</v>
       </c>
       <c r="B366" t="n">
-        <v>31.08511924743652</v>
+        <v>31.08511734008789</v>
       </c>
       <c r="C366" t="n">
-        <v>32.65904960734591</v>
+        <v>32.65904760342265</v>
       </c>
       <c r="D366" t="n">
-        <v>30.82279871206804</v>
+        <v>30.82279682081511</v>
       </c>
       <c r="E366" t="n">
-        <v>31.95640225288098</v>
+        <v>31.95640029207138</v>
       </c>
       <c r="F366" t="n">
         <v>8195900</v>
@@ -7792,16 +7792,16 @@
         <v>44292</v>
       </c>
       <c r="B369" t="n">
-        <v>30.57921028137207</v>
+        <v>30.5792121887207</v>
       </c>
       <c r="C369" t="n">
-        <v>32.19998297677536</v>
+        <v>32.19998498521812</v>
       </c>
       <c r="D369" t="n">
-        <v>30.48552540315069</v>
+        <v>30.48552730465581</v>
       </c>
       <c r="E369" t="n">
-        <v>31.01953707148042</v>
+        <v>31.01953900629401</v>
       </c>
       <c r="F369" t="n">
         <v>6923500</v>
@@ -7812,16 +7812,16 @@
         <v>44293</v>
       </c>
       <c r="B370" t="n">
-        <v>30.95395851135254</v>
+        <v>30.95395660400391</v>
       </c>
       <c r="C370" t="n">
-        <v>31.36617699981515</v>
+        <v>31.36617506706607</v>
       </c>
       <c r="D370" t="n">
-        <v>30.40120912458377</v>
+        <v>30.40120725129495</v>
       </c>
       <c r="E370" t="n">
-        <v>30.72910978883253</v>
+        <v>30.72910789533883</v>
       </c>
       <c r="F370" t="n">
         <v>4745700</v>
@@ -8012,16 +8012,16 @@
         <v>44308</v>
       </c>
       <c r="B380" t="n">
-        <v>36.30344772338867</v>
+        <v>36.30344390869141</v>
       </c>
       <c r="C380" t="n">
-        <v>38.03664315290104</v>
+        <v>38.03663915608288</v>
       </c>
       <c r="D380" t="n">
-        <v>35.88185858344396</v>
+        <v>35.88185481304648</v>
       </c>
       <c r="E380" t="n">
-        <v>37.12788831107506</v>
+        <v>37.12788440974715</v>
       </c>
       <c r="F380" t="n">
         <v>6756200</v>
@@ -8052,16 +8052,16 @@
         <v>44312</v>
       </c>
       <c r="B382" t="n">
-        <v>35.91933059692383</v>
+        <v>35.91933441162109</v>
       </c>
       <c r="C382" t="n">
-        <v>36.30344431641451</v>
+        <v>36.30344817190534</v>
       </c>
       <c r="D382" t="n">
-        <v>35.5164791869886</v>
+        <v>35.51648295890232</v>
       </c>
       <c r="E382" t="n">
-        <v>35.88185521603473</v>
+        <v>35.88185902675205</v>
       </c>
       <c r="F382" t="n">
         <v>4241900</v>
@@ -8072,16 +8072,16 @@
         <v>44313</v>
       </c>
       <c r="B383" t="n">
-        <v>35.46963882446289</v>
+        <v>35.46963500976562</v>
       </c>
       <c r="C383" t="n">
-        <v>36.29407938304689</v>
+        <v>36.2940754796825</v>
       </c>
       <c r="D383" t="n">
-        <v>35.27289842405</v>
+        <v>35.27289463051181</v>
       </c>
       <c r="E383" t="n">
-        <v>36.05986359955081</v>
+        <v>36.05985972137591</v>
       </c>
       <c r="F383" t="n">
         <v>2386900</v>
@@ -35435,16 +35435,36 @@
         <v>3</v>
       </c>
       <c r="C1751" t="n">
-        <v>3.07</v>
+        <v>3.069999933242798</v>
       </c>
       <c r="D1751" t="n">
-        <v>2.92</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="E1751" t="n">
-        <v>2.96</v>
+        <v>2.960000038146973</v>
       </c>
       <c r="F1751" t="n">
         <v>10083700</v>
+      </c>
+    </row>
+    <row r="1752">
+      <c r="A1752" s="1" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B1752" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="C1752" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="D1752" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="E1752" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="F1752" t="n">
+        <v>6363900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1752"/>
+  <dimension ref="A1:F1753"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799173355102539</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799173355102539</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799173355102539</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799173355102539</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C7" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D7" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E7" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616732597351074</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500722885132</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C12" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D12" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E12" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C13" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D13" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E13" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C14" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D14" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E14" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C15" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D15" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E15" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C16" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D16" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E16" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C17" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D17" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E17" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C18" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D18" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E18" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C19" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D19" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E19" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C20" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D20" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E20" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C21" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D21" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E21" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C22" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D22" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E22" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C23" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D23" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E23" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C24" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D24" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E24" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C25" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D25" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E25" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C26" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D26" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E26" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C27" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D27" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E27" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C28" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D28" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E28" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C29" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D29" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E29" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C30" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D30" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E30" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C31" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D31" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E31" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C32" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D32" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E32" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C33" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D33" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E33" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C34" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D34" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E34" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="C35" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="D35" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="E35" t="n">
-        <v>2.18015718460083</v>
+        <v>2.180156946182251</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758487224578857</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758487224578857</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758487224578857</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758487224578857</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951082706451416</v>
+        <v>6.951083660125732</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951082706451416</v>
+        <v>6.951083660125732</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951082706451416</v>
+        <v>6.951083660125732</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951082706451416</v>
+        <v>6.951083660125732</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958560943604</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958560943603</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.58793306350708</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.58793306350708</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.58793306350708</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.58793306350708</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075628280639648</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075628280639648</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075628280639648</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075628280639648</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296539306640625</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988324165344238</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988324165344238</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988324165344238</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988324165344238</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.014761924743652</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="C64" t="n">
-        <v>9.014761924743652</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="D64" t="n">
-        <v>9.014761924743652</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="E64" t="n">
-        <v>9.014761924743652</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -1872,16 +1872,16 @@
         <v>43741</v>
       </c>
       <c r="B73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F73" t="n">
         <v>755</v>
@@ -1892,16 +1892,16 @@
         <v>43747</v>
       </c>
       <c r="B74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F74" t="n">
         <v>755</v>
@@ -1952,16 +1952,16 @@
         <v>43773</v>
       </c>
       <c r="B77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F77" t="n">
         <v>1510</v>
@@ -2012,16 +2012,16 @@
         <v>43802</v>
       </c>
       <c r="B80" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C80" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D80" t="n">
-        <v>9.21762282756219</v>
+        <v>9.217621990355065</v>
       </c>
       <c r="E80" t="n">
-        <v>9.21762282756219</v>
+        <v>9.217621990355065</v>
       </c>
       <c r="F80" t="n">
         <v>1510</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610103607178</v>
+        <v>10.60610008239746</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448453125444</v>
+        <v>11.08448353456507</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2432,16 +2432,16 @@
         <v>43894</v>
       </c>
       <c r="B101" t="n">
-        <v>8.692568778991699</v>
+        <v>8.692569732666016</v>
       </c>
       <c r="C101" t="n">
-        <v>8.80224676394379</v>
+        <v>8.802247729651036</v>
       </c>
       <c r="D101" t="n">
-        <v>8.564221896891393</v>
+        <v>8.564222836484587</v>
       </c>
       <c r="E101" t="n">
-        <v>8.734572326921571</v>
+        <v>8.734573285204156</v>
       </c>
       <c r="F101" t="n">
         <v>7583284</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174576363958773</v>
+        <v>7.174577261989849</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269086440314109</v>
+        <v>7.269087350174872</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151270575596</v>
+        <v>7.885151755156881</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395100920432114</v>
+        <v>7.395101374897398</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2532,16 +2532,16 @@
         <v>43901</v>
       </c>
       <c r="B106" t="n">
-        <v>7.280755043029785</v>
+        <v>7.280755519866943</v>
       </c>
       <c r="C106" t="n">
-        <v>7.652960679612288</v>
+        <v>7.652961180826241</v>
       </c>
       <c r="D106" t="n">
-        <v>6.825708745737296</v>
+        <v>6.825709192772189</v>
       </c>
       <c r="E106" t="n">
-        <v>7.467442341108447</v>
+        <v>7.467442830172282</v>
       </c>
       <c r="F106" t="n">
         <v>14927915</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198310852051</v>
+        <v>6.731198787689209</v>
       </c>
       <c r="C107" t="n">
-        <v>6.78487002388751</v>
+        <v>6.784870504526766</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975251402972</v>
+        <v>6.183975689474925</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242313978574833</v>
+        <v>6.242314420779493</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642458915710449</v>
+        <v>7.642459392547607</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934155910701143</v>
+        <v>7.934156405738198</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650689636966175</v>
+        <v>6.650690051923714</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251216760168</v>
+        <v>7.242251668627103</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255058288574</v>
+        <v>7.277255535125732</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292230712304</v>
+        <v>7.641292731402749</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086097777741</v>
+        <v>6.70086141684674</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766201694169458</v>
+        <v>6.766202137520195</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2632,16 +2632,16 @@
         <v>43908</v>
       </c>
       <c r="B111" t="n">
-        <v>6.985558032989502</v>
+        <v>6.98555850982666</v>
       </c>
       <c r="C111" t="n">
-        <v>8.075337993481165</v>
+        <v>8.075338544707167</v>
       </c>
       <c r="D111" t="n">
-        <v>6.710196211513576</v>
+        <v>6.71019666955442</v>
       </c>
       <c r="E111" t="n">
-        <v>7.140740982312391</v>
+        <v>7.140741469742403</v>
       </c>
       <c r="F111" t="n">
         <v>26337960</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314098358154</v>
+        <v>7.844314575195312</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109174606594431</v>
+        <v>8.109175099531829</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235250900954319</v>
+        <v>7.235251340767977</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146197500977</v>
+        <v>7.829146673416115</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2692,16 +2692,16 @@
         <v>43913</v>
       </c>
       <c r="B114" t="n">
-        <v>8.386870384216309</v>
+        <v>8.386871337890625</v>
       </c>
       <c r="C114" t="n">
-        <v>8.386870384216309</v>
+        <v>8.386871337890625</v>
       </c>
       <c r="D114" t="n">
-        <v>7.48377644845884</v>
+        <v>7.483777299441991</v>
       </c>
       <c r="E114" t="n">
-        <v>8.050835275027762</v>
+        <v>8.050836190491395</v>
       </c>
       <c r="F114" t="n">
         <v>25091072</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738137245178223</v>
+        <v>7.738136291503906</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145346146541403</v>
+        <v>8.145345142681279</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298979071039</v>
+        <v>7.690298031292473</v>
       </c>
       <c r="E117" t="n">
-        <v>8.13834499423681</v>
+        <v>8.138343991239532</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775676727295</v>
+        <v>7.469775199890137</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304804343318</v>
+        <v>7.746304309853773</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351930089923889</v>
+        <v>7.351929620609467</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113786687701</v>
+        <v>7.514113307020195</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582953929901123</v>
+        <v>7.582952976226807</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840815002303775</v>
+        <v>7.840814016199421</v>
       </c>
       <c r="D122" t="n">
-        <v>7.381100395706687</v>
+        <v>7.38109946741859</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455774312072345</v>
+        <v>7.455773374392843</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261459350586</v>
+        <v>7.340261936187744</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624426344595</v>
+        <v>7.622624921524582</v>
       </c>
       <c r="D123" t="n">
-        <v>7.21541557567713</v>
+        <v>7.215416044404066</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457147585694</v>
+        <v>7.621457642689852</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672797679901123</v>
+        <v>7.672797203063965</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109175966524298</v>
+        <v>8.109175462567777</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661129932612202</v>
+        <v>7.661129456500152</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840815257758265</v>
+        <v>7.84081477047941</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2952,16 +2952,16 @@
         <v>43930</v>
       </c>
       <c r="B127" t="n">
-        <v>7.38576602935791</v>
+        <v>7.385766506195068</v>
       </c>
       <c r="C127" t="n">
-        <v>7.778973418970338</v>
+        <v>7.778973921193609</v>
       </c>
       <c r="D127" t="n">
-        <v>7.351929231575166</v>
+        <v>7.351929706227764</v>
       </c>
       <c r="E127" t="n">
-        <v>7.778973418970338</v>
+        <v>7.778973921193609</v>
       </c>
       <c r="F127" t="n">
         <v>7590081</v>
@@ -2972,16 +2972,16 @@
         <v>43934</v>
       </c>
       <c r="B128" t="n">
-        <v>7.41493558883667</v>
+        <v>7.414936065673828</v>
       </c>
       <c r="C128" t="n">
-        <v>7.447605949093313</v>
+        <v>7.447606428031426</v>
       </c>
       <c r="D128" t="n">
-        <v>7.229416415322526</v>
+        <v>7.22941688022938</v>
       </c>
       <c r="E128" t="n">
-        <v>7.385766224588598</v>
+        <v>7.385766699549943</v>
       </c>
       <c r="F128" t="n">
         <v>8873976</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500110626220703</v>
+        <v>7.500111103057861</v>
       </c>
       <c r="C129" t="n">
-        <v>7.750970514277116</v>
+        <v>7.75097100706328</v>
       </c>
       <c r="D129" t="n">
-        <v>7.455773361693658</v>
+        <v>7.45577383571197</v>
       </c>
       <c r="E129" t="n">
-        <v>7.49427759388343</v>
+        <v>7.494278070349739</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265598297119</v>
+        <v>7.375264644622803</v>
       </c>
       <c r="C130" t="n">
-        <v>7.494278464239883</v>
+        <v>7.494277495176356</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762513925697</v>
+        <v>7.343761564324954</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935961570344</v>
+        <v>7.407935003671517</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566619396209717</v>
+        <v>7.566618919372559</v>
       </c>
       <c r="C131" t="n">
-        <v>7.5887884509226</v>
+        <v>7.58878797268838</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234084415890043</v>
+        <v>7.234083960008746</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444106376032958</v>
+        <v>7.444105906916389</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251522064208984</v>
+        <v>8.251523017883301</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431207358265677</v>
+        <v>8.431208332707222</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3112,16 +3112,16 @@
         <v>43944</v>
       </c>
       <c r="B135" t="n">
-        <v>8.089339256286621</v>
+        <v>8.089340209960938</v>
       </c>
       <c r="C135" t="n">
-        <v>8.57472300766133</v>
+        <v>8.574724018558863</v>
       </c>
       <c r="D135" t="n">
-        <v>7.969159966917957</v>
+        <v>7.969160906424007</v>
       </c>
       <c r="E135" t="n">
-        <v>8.481379364431731</v>
+        <v>8.481380364324728</v>
       </c>
       <c r="F135" t="n">
         <v>13472583</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852482318878174</v>
+        <v>7.852481842041016</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764498666425</v>
+        <v>7.357764051870702</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3152,16 +3152,16 @@
         <v>43948</v>
       </c>
       <c r="B137" t="n">
-        <v>8.105673789978027</v>
+        <v>8.105674743652344</v>
       </c>
       <c r="C137" t="n">
-        <v>8.16517979671254</v>
+        <v>8.165180757388045</v>
       </c>
       <c r="D137" t="n">
-        <v>7.710133516824237</v>
+        <v>7.710134423961201</v>
       </c>
       <c r="E137" t="n">
-        <v>7.937657076955135</v>
+        <v>7.93765801086142</v>
       </c>
       <c r="F137" t="n">
         <v>12260436</v>
@@ -3172,16 +3172,16 @@
         <v>43949</v>
       </c>
       <c r="B138" t="n">
-        <v>7.822145462036133</v>
+        <v>7.822145938873291</v>
       </c>
       <c r="C138" t="n">
-        <v>8.301695367155927</v>
+        <v>8.301695873226397</v>
       </c>
       <c r="D138" t="n">
-        <v>7.804643843107134</v>
+        <v>7.804644318877395</v>
       </c>
       <c r="E138" t="n">
-        <v>8.167514607953231</v>
+        <v>8.167515105844055</v>
       </c>
       <c r="F138" t="n">
         <v>14579753</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484550476074</v>
+        <v>7.887484073638916</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826736101882</v>
+        <v>7.966826254468098</v>
       </c>
       <c r="D139" t="n">
-        <v>7.700798933367937</v>
+        <v>7.70079846781684</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980845212174</v>
+        <v>7.841980371125938</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3252,16 +3252,16 @@
         <v>43956</v>
       </c>
       <c r="B142" t="n">
-        <v>8.114091873168945</v>
+        <v>8.114090919494629</v>
       </c>
       <c r="C142" t="n">
-        <v>8.645024731663977</v>
+        <v>8.645023715587479</v>
       </c>
       <c r="D142" t="n">
-        <v>8.069433944133035</v>
+        <v>8.069432995707503</v>
       </c>
       <c r="E142" t="n">
-        <v>8.286521173623905</v>
+        <v>8.286520199683441</v>
       </c>
       <c r="F142" t="n">
         <v>11843548</v>
@@ -3272,16 +3272,16 @@
         <v>43957</v>
       </c>
       <c r="B143" t="n">
-        <v>8.048344612121582</v>
+        <v>8.048345565795898</v>
       </c>
       <c r="C143" t="n">
-        <v>8.145103893796581</v>
+        <v>8.145104858936216</v>
       </c>
       <c r="D143" t="n">
-        <v>7.96399105383742</v>
+        <v>7.963991997516411</v>
       </c>
       <c r="E143" t="n">
-        <v>8.145103893796581</v>
+        <v>8.145104858936216</v>
       </c>
       <c r="F143" t="n">
         <v>16545622</v>
@@ -3312,16 +3312,16 @@
         <v>43959</v>
       </c>
       <c r="B145" t="n">
-        <v>8.162470817565918</v>
+        <v>8.162469863891602</v>
       </c>
       <c r="C145" t="n">
-        <v>8.184800228116485</v>
+        <v>8.184799271833279</v>
       </c>
       <c r="D145" t="n">
-        <v>7.947864739756858</v>
+        <v>7.94786381115636</v>
       </c>
       <c r="E145" t="n">
-        <v>8.156268402071278</v>
+        <v>8.15626744912163</v>
       </c>
       <c r="F145" t="n">
         <v>8818844</v>
@@ -3352,16 +3352,16 @@
         <v>43963</v>
       </c>
       <c r="B147" t="n">
-        <v>8.085559844970703</v>
+        <v>8.085558891296387</v>
       </c>
       <c r="C147" t="n">
-        <v>8.276596387736546</v>
+        <v>8.276595411529883</v>
       </c>
       <c r="D147" t="n">
-        <v>8.063230434277379</v>
+        <v>8.063229483236768</v>
       </c>
       <c r="E147" t="n">
-        <v>8.187280531887918</v>
+        <v>8.187279566215866</v>
       </c>
       <c r="F147" t="n">
         <v>9953957</v>
@@ -3372,16 +3372,16 @@
         <v>43964</v>
       </c>
       <c r="B148" t="n">
-        <v>7.926775932312012</v>
+        <v>7.926775455474854</v>
       </c>
       <c r="C148" t="n">
-        <v>8.187280049800203</v>
+        <v>8.187279557292356</v>
       </c>
       <c r="D148" t="n">
-        <v>7.885840170888542</v>
+        <v>7.885839696513885</v>
       </c>
       <c r="E148" t="n">
-        <v>8.187280049800203</v>
+        <v>8.187279557292356</v>
       </c>
       <c r="F148" t="n">
         <v>10179016</v>
@@ -3412,16 +3412,16 @@
         <v>43966</v>
       </c>
       <c r="B150" t="n">
-        <v>6.841341018676758</v>
+        <v>6.8413405418396</v>
       </c>
       <c r="C150" t="n">
-        <v>7.421893621943401</v>
+        <v>7.421893104642092</v>
       </c>
       <c r="D150" t="n">
-        <v>6.841341018676758</v>
+        <v>6.8413405418396</v>
       </c>
       <c r="E150" t="n">
-        <v>7.420653049518127</v>
+        <v>7.420652532303285</v>
       </c>
       <c r="F150" t="n">
         <v>26563775</v>
@@ -3452,16 +3452,16 @@
         <v>43970</v>
       </c>
       <c r="B152" t="n">
-        <v>6.831417560577393</v>
+        <v>6.831418037414551</v>
       </c>
       <c r="C152" t="n">
-        <v>7.018731929050585</v>
+        <v>7.018732418962401</v>
       </c>
       <c r="D152" t="n">
-        <v>6.799164018747209</v>
+        <v>6.79916449333305</v>
       </c>
       <c r="E152" t="n">
-        <v>6.966631015976597</v>
+        <v>6.966631502251738</v>
       </c>
       <c r="F152" t="n">
         <v>13463520</v>
@@ -3472,16 +3472,16 @@
         <v>43971</v>
       </c>
       <c r="B153" t="n">
-        <v>6.822733402252197</v>
+        <v>6.822733879089355</v>
       </c>
       <c r="C153" t="n">
-        <v>6.983997533970078</v>
+        <v>6.983998022077899</v>
       </c>
       <c r="D153" t="n">
-        <v>6.81032857213493</v>
+        <v>6.810329048105121</v>
       </c>
       <c r="E153" t="n">
-        <v>6.946783490349408</v>
+        <v>6.94678397585636</v>
       </c>
       <c r="F153" t="n">
         <v>11533147</v>
@@ -3552,16 +3552,16 @@
         <v>43977</v>
       </c>
       <c r="B157" t="n">
-        <v>7.423134326934814</v>
+        <v>7.423134803771973</v>
       </c>
       <c r="C157" t="n">
-        <v>7.560828925689475</v>
+        <v>7.560829411371671</v>
       </c>
       <c r="D157" t="n">
-        <v>7.275514702466858</v>
+        <v>7.275515169821428</v>
       </c>
       <c r="E157" t="n">
-        <v>7.442982144705714</v>
+        <v>7.442982622817829</v>
       </c>
       <c r="F157" t="n">
         <v>12080691</v>
@@ -3612,16 +3612,16 @@
         <v>43980</v>
       </c>
       <c r="B160" t="n">
-        <v>7.812650680541992</v>
+        <v>7.812650203704834</v>
       </c>
       <c r="C160" t="n">
-        <v>7.812650680541992</v>
+        <v>7.812650203704834</v>
       </c>
       <c r="D160" t="n">
-        <v>7.481437500239227</v>
+        <v>7.481437043617326</v>
       </c>
       <c r="E160" t="n">
-        <v>7.519893458373339</v>
+        <v>7.519892999404318</v>
       </c>
       <c r="F160" t="n">
         <v>23712019</v>
@@ -3652,16 +3652,16 @@
         <v>43984</v>
       </c>
       <c r="B162" t="n">
-        <v>8.271635055541992</v>
+        <v>8.271634101867676</v>
       </c>
       <c r="C162" t="n">
-        <v>8.286521031632221</v>
+        <v>8.286520076241633</v>
       </c>
       <c r="D162" t="n">
-        <v>7.976396678662855</v>
+        <v>7.976395759027911</v>
       </c>
       <c r="E162" t="n">
-        <v>8.063230496816454</v>
+        <v>8.063229567170044</v>
       </c>
       <c r="F162" t="n">
         <v>21348142</v>
@@ -3672,16 +3672,16 @@
         <v>43985</v>
       </c>
       <c r="B163" t="n">
-        <v>8.373353958129883</v>
+        <v>8.373354911804199</v>
       </c>
       <c r="C163" t="n">
-        <v>8.80008582291646</v>
+        <v>8.800086825192951</v>
       </c>
       <c r="D163" t="n">
-        <v>8.315051079171372</v>
+        <v>8.315052026205343</v>
       </c>
       <c r="E163" t="n">
-        <v>8.31753222383259</v>
+        <v>8.317533171149149</v>
       </c>
       <c r="F163" t="n">
         <v>31125376</v>
@@ -3752,16 +3752,16 @@
         <v>43991</v>
       </c>
       <c r="B167" t="n">
-        <v>8.296443939208984</v>
+        <v>8.296442985534668</v>
       </c>
       <c r="C167" t="n">
-        <v>8.32745691101246</v>
+        <v>8.327455953773208</v>
       </c>
       <c r="D167" t="n">
-        <v>8.0967247251524</v>
+        <v>8.096723794435762</v>
       </c>
       <c r="E167" t="n">
-        <v>8.137661383332564</v>
+        <v>8.137660447910266</v>
       </c>
       <c r="F167" t="n">
         <v>13675741</v>
@@ -3772,16 +3772,16 @@
         <v>43992</v>
       </c>
       <c r="B168" t="n">
-        <v>8.089280128479004</v>
+        <v>8.08928108215332</v>
       </c>
       <c r="C168" t="n">
-        <v>8.426696138374464</v>
+        <v>8.426697131827968</v>
       </c>
       <c r="D168" t="n">
-        <v>8.037179665656195</v>
+        <v>8.0371806131882</v>
       </c>
       <c r="E168" t="n">
-        <v>8.311329615282364</v>
+        <v>8.311330595134894</v>
       </c>
       <c r="F168" t="n">
         <v>11944749</v>
@@ -3792,16 +3792,16 @@
         <v>43994</v>
       </c>
       <c r="B169" t="n">
-        <v>7.950345516204834</v>
+        <v>7.950345993041992</v>
       </c>
       <c r="C169" t="n">
-        <v>8.084319292912509</v>
+        <v>8.084319777785</v>
       </c>
       <c r="D169" t="n">
-        <v>7.774194958703272</v>
+        <v>7.774195424975465</v>
       </c>
       <c r="E169" t="n">
-        <v>7.877156659374939</v>
+        <v>7.877157131822456</v>
       </c>
       <c r="F169" t="n">
         <v>12251373</v>
@@ -3892,16 +3892,16 @@
         <v>44001</v>
       </c>
       <c r="B174" t="n">
-        <v>8.487481117248535</v>
+        <v>8.487480163574219</v>
       </c>
       <c r="C174" t="n">
-        <v>8.58920180321846</v>
+        <v>8.589200838114557</v>
       </c>
       <c r="D174" t="n">
-        <v>8.203407450651435</v>
+        <v>8.203406528896336</v>
       </c>
       <c r="E174" t="n">
-        <v>8.203407450651435</v>
+        <v>8.203406528896336</v>
       </c>
       <c r="F174" t="n">
         <v>20750754</v>
@@ -3912,16 +3912,16 @@
         <v>44004</v>
       </c>
       <c r="B175" t="n">
-        <v>8.440341949462891</v>
+        <v>8.440342903137207</v>
       </c>
       <c r="C175" t="n">
-        <v>8.729376978500955</v>
+        <v>8.729377964833343</v>
       </c>
       <c r="D175" t="n">
-        <v>8.380797159632158</v>
+        <v>8.380798106578508</v>
       </c>
       <c r="E175" t="n">
-        <v>8.489961267461833</v>
+        <v>8.489962226742637</v>
       </c>
       <c r="F175" t="n">
         <v>12069362</v>
@@ -3952,16 +3952,16 @@
         <v>44006</v>
       </c>
       <c r="B177" t="n">
-        <v>8.59416389465332</v>
+        <v>8.594162940979004</v>
       </c>
       <c r="C177" t="n">
-        <v>8.669833897798144</v>
+        <v>8.669832935726904</v>
       </c>
       <c r="D177" t="n">
-        <v>8.422974729757115</v>
+        <v>8.422973795079262</v>
       </c>
       <c r="E177" t="n">
-        <v>8.571834484683247</v>
+        <v>8.571833533486773</v>
       </c>
       <c r="F177" t="n">
         <v>7388434</v>
@@ -4052,16 +4052,16 @@
         <v>44013</v>
       </c>
       <c r="B182" t="n">
-        <v>9.009729385375977</v>
+        <v>9.009730339050293</v>
       </c>
       <c r="C182" t="n">
-        <v>9.115171330097578</v>
+        <v>9.11517229493286</v>
       </c>
       <c r="D182" t="n">
-        <v>8.731858165462054</v>
+        <v>8.731859089723871</v>
       </c>
       <c r="E182" t="n">
-        <v>8.812490451063802</v>
+        <v>8.812491383860499</v>
       </c>
       <c r="F182" t="n">
         <v>8963093</v>
@@ -4292,16 +4292,16 @@
         <v>44029</v>
       </c>
       <c r="B194" t="n">
-        <v>8.819933891296387</v>
+        <v>8.81993293762207</v>
       </c>
       <c r="C194" t="n">
-        <v>8.919174324825571</v>
+        <v>8.919173360420668</v>
       </c>
       <c r="D194" t="n">
-        <v>8.633859641988225</v>
+        <v>8.633858708433587</v>
       </c>
       <c r="E194" t="n">
-        <v>8.633859641988225</v>
+        <v>8.633858708433587</v>
       </c>
       <c r="F194" t="n">
         <v>9678298</v>
@@ -4432,16 +4432,16 @@
         <v>44040</v>
       </c>
       <c r="B201" t="n">
-        <v>9.641142845153809</v>
+        <v>9.641143798828125</v>
       </c>
       <c r="C201" t="n">
-        <v>9.832179367263814</v>
+        <v>9.832180339834917</v>
       </c>
       <c r="D201" t="n">
-        <v>9.466232422996864</v>
+        <v>9.466233359369541</v>
       </c>
       <c r="E201" t="n">
-        <v>9.67587708316008</v>
+        <v>9.675878040270206</v>
       </c>
       <c r="F201" t="n">
         <v>30127714</v>
@@ -4472,16 +4472,16 @@
         <v>44042</v>
       </c>
       <c r="B203" t="n">
-        <v>9.143703460693359</v>
+        <v>9.143704414367676</v>
       </c>
       <c r="C203" t="n">
-        <v>9.700686938306321</v>
+        <v>9.700687950073165</v>
       </c>
       <c r="D203" t="n">
-        <v>9.097805411083952</v>
+        <v>9.097806359971171</v>
       </c>
       <c r="E203" t="n">
-        <v>9.685800070178546</v>
+        <v>9.685801080392711</v>
       </c>
       <c r="F203" t="n">
         <v>33272500</v>
@@ -4592,16 +4592,16 @@
         <v>44050</v>
       </c>
       <c r="B209" t="n">
-        <v>8.429178237915039</v>
+        <v>8.429177284240723</v>
       </c>
       <c r="C209" t="n">
-        <v>8.429178237915039</v>
+        <v>8.429177284240723</v>
       </c>
       <c r="D209" t="n">
-        <v>8.25550792408546</v>
+        <v>8.255506990060143</v>
       </c>
       <c r="E209" t="n">
-        <v>8.336141112251321</v>
+        <v>8.336140169103194</v>
       </c>
       <c r="F209" t="n">
         <v>22110172</v>
@@ -4612,16 +4612,16 @@
         <v>44053</v>
       </c>
       <c r="B210" t="n">
-        <v>8.25922966003418</v>
+        <v>8.259230613708496</v>
       </c>
       <c r="C210" t="n">
-        <v>8.468873436704216</v>
+        <v>8.468874414585619</v>
       </c>
       <c r="D210" t="n">
-        <v>8.166191645730668</v>
+        <v>8.166192588662099</v>
       </c>
       <c r="E210" t="n">
-        <v>8.435379322693057</v>
+        <v>8.435380296706972</v>
       </c>
       <c r="F210" t="n">
         <v>21920608</v>
@@ -4652,16 +4652,16 @@
         <v>44055</v>
       </c>
       <c r="B212" t="n">
-        <v>8.162470817565918</v>
+        <v>8.162469863891602</v>
       </c>
       <c r="C212" t="n">
-        <v>8.446544484992341</v>
+        <v>8.446543498127859</v>
       </c>
       <c r="D212" t="n">
-        <v>8.078116358606623</v>
+        <v>8.078115414787984</v>
       </c>
       <c r="E212" t="n">
-        <v>8.409329992024503</v>
+        <v>8.409329009508031</v>
       </c>
       <c r="F212" t="n">
         <v>20200945</v>
@@ -4732,16 +4732,16 @@
         <v>44061</v>
       </c>
       <c r="B216" t="n">
-        <v>8.101685523986816</v>
+        <v>8.101686477661133</v>
       </c>
       <c r="C216" t="n">
-        <v>8.143863198266791</v>
+        <v>8.143864156905972</v>
       </c>
       <c r="D216" t="n">
-        <v>7.978877345430011</v>
+        <v>7.9788782846482</v>
       </c>
       <c r="E216" t="n">
-        <v>8.038420352760289</v>
+        <v>8.038421298987467</v>
       </c>
       <c r="F216" t="n">
         <v>10608743</v>
@@ -4752,16 +4752,16 @@
         <v>44062</v>
       </c>
       <c r="B217" t="n">
-        <v>7.926775932312012</v>
+        <v>7.926775455474854</v>
       </c>
       <c r="C217" t="n">
-        <v>8.141381998856557</v>
+        <v>8.141381509109719</v>
       </c>
       <c r="D217" t="n">
-        <v>7.921813642791834</v>
+        <v>7.921813166253184</v>
       </c>
       <c r="E217" t="n">
-        <v>8.141381998856557</v>
+        <v>8.141381509109719</v>
       </c>
       <c r="F217" t="n">
         <v>9466833</v>
@@ -4772,16 +4772,16 @@
         <v>44063</v>
       </c>
       <c r="B218" t="n">
-        <v>7.957787990570068</v>
+        <v>7.957788467407227</v>
       </c>
       <c r="C218" t="n">
-        <v>8.033458885005254</v>
+        <v>8.033459366376674</v>
       </c>
       <c r="D218" t="n">
-        <v>7.774194893738959</v>
+        <v>7.774195359575069</v>
       </c>
       <c r="E218" t="n">
-        <v>7.915611210128628</v>
+        <v>7.915611684438519</v>
       </c>
       <c r="F218" t="n">
         <v>7652765</v>
@@ -4892,16 +4892,16 @@
         <v>44071</v>
       </c>
       <c r="B224" t="n">
-        <v>8.100444793701172</v>
+        <v>8.100445747375488</v>
       </c>
       <c r="C224" t="n">
-        <v>8.100444793701172</v>
+        <v>8.100445747375488</v>
       </c>
       <c r="D224" t="n">
-        <v>7.960268612170143</v>
+        <v>7.960269549341362</v>
       </c>
       <c r="E224" t="n">
-        <v>8.001206157737258</v>
+        <v>8.0012070997281</v>
       </c>
       <c r="F224" t="n">
         <v>5577388</v>
@@ -5012,16 +5012,16 @@
         <v>44082</v>
       </c>
       <c r="B230" t="n">
-        <v>7.751865386962891</v>
+        <v>7.751865863800049</v>
       </c>
       <c r="C230" t="n">
-        <v>7.833737802061967</v>
+        <v>7.833738283935308</v>
       </c>
       <c r="D230" t="n">
-        <v>7.691081361819436</v>
+        <v>7.691081834917614</v>
       </c>
       <c r="E230" t="n">
-        <v>7.813890431199186</v>
+        <v>7.813890911851665</v>
       </c>
       <c r="F230" t="n">
         <v>7181501</v>
@@ -5032,16 +5032,16 @@
         <v>44083</v>
       </c>
       <c r="B231" t="n">
-        <v>7.709689140319824</v>
+        <v>7.709688663482666</v>
       </c>
       <c r="C231" t="n">
-        <v>7.834980256551466</v>
+        <v>7.834979771965168</v>
       </c>
       <c r="D231" t="n">
-        <v>7.637740405675546</v>
+        <v>7.637739933288351</v>
       </c>
       <c r="E231" t="n">
-        <v>7.792802580260581</v>
+        <v>7.792802098282933</v>
       </c>
       <c r="F231" t="n">
         <v>8282629</v>
@@ -5052,16 +5052,16 @@
         <v>44084</v>
       </c>
       <c r="B232" t="n">
-        <v>8.850946426391602</v>
+        <v>8.850947380065918</v>
       </c>
       <c r="C232" t="n">
-        <v>9.197044227170217</v>
+        <v>9.197045218135978</v>
       </c>
       <c r="D232" t="n">
-        <v>8.62145438702172</v>
+        <v>8.621455315968662</v>
       </c>
       <c r="E232" t="n">
-        <v>9.197044227170217</v>
+        <v>9.197045218135978</v>
       </c>
       <c r="F232" t="n">
         <v>139609921</v>
@@ -5132,16 +5132,16 @@
         <v>44090</v>
       </c>
       <c r="B236" t="n">
-        <v>9.312411308288574</v>
+        <v>9.312410354614258</v>
       </c>
       <c r="C236" t="n">
-        <v>9.375676482213272</v>
+        <v>9.375675522060035</v>
       </c>
       <c r="D236" t="n">
-        <v>9.175957274371282</v>
+        <v>9.175956334671081</v>
       </c>
       <c r="E236" t="n">
-        <v>9.179678544963952</v>
+        <v>9.179677604882659</v>
       </c>
       <c r="F236" t="n">
         <v>13993693</v>
@@ -5212,16 +5212,16 @@
         <v>44096</v>
       </c>
       <c r="B240" t="n">
-        <v>9.326057434082031</v>
+        <v>9.326058387756348</v>
       </c>
       <c r="C240" t="n">
-        <v>9.353348239057649</v>
+        <v>9.353349195522698</v>
       </c>
       <c r="D240" t="n">
-        <v>9.182158188124824</v>
+        <v>9.182159127084132</v>
       </c>
       <c r="E240" t="n">
-        <v>9.192082766997606</v>
+        <v>9.192083706971793</v>
       </c>
       <c r="F240" t="n">
         <v>9315031</v>
@@ -5232,16 +5232,16 @@
         <v>44097</v>
       </c>
       <c r="B241" t="n">
-        <v>8.953908920288086</v>
+        <v>8.95390796661377</v>
       </c>
       <c r="C241" t="n">
-        <v>9.308690312405352</v>
+        <v>9.308689320943529</v>
       </c>
       <c r="D241" t="n">
-        <v>8.934060654104224</v>
+        <v>8.934059702543932</v>
       </c>
       <c r="E241" t="n">
-        <v>9.303728915956151</v>
+        <v>9.303727925022763</v>
       </c>
       <c r="F241" t="n">
         <v>13677251</v>
@@ -5252,16 +5252,16 @@
         <v>44098</v>
       </c>
       <c r="B242" t="n">
-        <v>9.282638549804688</v>
+        <v>9.282639503479004</v>
       </c>
       <c r="C242" t="n">
-        <v>9.463751388941567</v>
+        <v>9.46375236122295</v>
       </c>
       <c r="D242" t="n">
-        <v>8.898084356453305</v>
+        <v>8.898085270619518</v>
       </c>
       <c r="E242" t="n">
-        <v>8.906768809518589</v>
+        <v>8.906769724577019</v>
       </c>
       <c r="F242" t="n">
         <v>18607406</v>
@@ -5272,16 +5272,16 @@
         <v>44099</v>
       </c>
       <c r="B243" t="n">
-        <v>9.184639930725098</v>
+        <v>9.184640884399414</v>
       </c>
       <c r="C243" t="n">
-        <v>9.25410751328763</v>
+        <v>9.254108474175018</v>
       </c>
       <c r="D243" t="n">
-        <v>9.095324084518023</v>
+        <v>9.095325028918353</v>
       </c>
       <c r="E243" t="n">
-        <v>9.220613400863298</v>
+        <v>9.22061435827287</v>
       </c>
       <c r="F243" t="n">
         <v>8201819</v>
@@ -5312,16 +5312,16 @@
         <v>44103</v>
       </c>
       <c r="B245" t="n">
-        <v>8.760391235351562</v>
+        <v>8.760390281677246</v>
       </c>
       <c r="C245" t="n">
-        <v>8.942744221459206</v>
+        <v>8.942743247933565</v>
       </c>
       <c r="D245" t="n">
-        <v>8.68348020897627</v>
+        <v>8.683479263674647</v>
       </c>
       <c r="E245" t="n">
-        <v>8.802568019244504</v>
+        <v>8.802567060978735</v>
       </c>
       <c r="F245" t="n">
         <v>13985386</v>
@@ -5332,16 +5332,16 @@
         <v>44104</v>
       </c>
       <c r="B246" t="n">
-        <v>8.651226043701172</v>
+        <v>8.651226997375488</v>
       </c>
       <c r="C246" t="n">
-        <v>8.841022441256731</v>
+        <v>8.841023415853394</v>
       </c>
       <c r="D246" t="n">
-        <v>8.609049265013768</v>
+        <v>8.609050214038696</v>
       </c>
       <c r="E246" t="n">
-        <v>8.803807058409923</v>
+        <v>8.803808028904122</v>
       </c>
       <c r="F246" t="n">
         <v>11477260</v>
@@ -5412,16 +5412,16 @@
         <v>44110</v>
       </c>
       <c r="B250" t="n">
-        <v>8.497405052185059</v>
+        <v>8.497404098510742</v>
       </c>
       <c r="C250" t="n">
-        <v>8.520974589071102</v>
+        <v>8.520973632751547</v>
       </c>
       <c r="D250" t="n">
-        <v>8.316293085426295</v>
+        <v>8.3162921520784</v>
       </c>
       <c r="E250" t="n">
-        <v>8.488721491571129</v>
+        <v>8.48872053887138</v>
       </c>
       <c r="F250" t="n">
         <v>10544549</v>
@@ -5432,16 +5432,16 @@
         <v>44111</v>
       </c>
       <c r="B251" t="n">
-        <v>8.585480690002441</v>
+        <v>8.585479736328125</v>
       </c>
       <c r="C251" t="n">
-        <v>8.704568498874545</v>
+        <v>8.704567531971968</v>
       </c>
       <c r="D251" t="n">
-        <v>8.440343093036322</v>
+        <v>8.440342155483876</v>
       </c>
       <c r="E251" t="n">
-        <v>8.477557586577683</v>
+        <v>8.477556644891454</v>
       </c>
       <c r="F251" t="n">
         <v>12680345</v>
@@ -5552,16 +5552,16 @@
         <v>44120</v>
       </c>
       <c r="B257" t="n">
-        <v>8.25922966003418</v>
+        <v>8.259230613708496</v>
       </c>
       <c r="C257" t="n">
-        <v>8.267912326486389</v>
+        <v>8.267913281163274</v>
       </c>
       <c r="D257" t="n">
-        <v>8.097964185523827</v>
+        <v>8.097965120577188</v>
       </c>
       <c r="E257" t="n">
-        <v>8.122774739620494</v>
+        <v>8.122775677538673</v>
       </c>
       <c r="F257" t="n">
         <v>10726560</v>
@@ -5612,16 +5612,16 @@
         <v>44125</v>
       </c>
       <c r="B260" t="n">
-        <v>8.275355339050293</v>
+        <v>8.275356292724609</v>
       </c>
       <c r="C260" t="n">
-        <v>8.355987625465389</v>
+        <v>8.355988588431988</v>
       </c>
       <c r="D260" t="n">
-        <v>8.245583390421267</v>
+        <v>8.245584340664582</v>
       </c>
       <c r="E260" t="n">
-        <v>8.354747499881778</v>
+        <v>8.35474846270546</v>
       </c>
       <c r="F260" t="n">
         <v>4665068</v>
@@ -5632,16 +5632,16 @@
         <v>44126</v>
       </c>
       <c r="B261" t="n">
-        <v>8.267911911010742</v>
+        <v>8.267912864685059</v>
       </c>
       <c r="C261" t="n">
-        <v>8.337380386835774</v>
+        <v>8.337381348523031</v>
       </c>
       <c r="D261" t="n">
-        <v>8.168673273460097</v>
+        <v>8.168674215687588</v>
       </c>
       <c r="E261" t="n">
-        <v>8.30636741913896</v>
+        <v>8.306368377248981</v>
       </c>
       <c r="F261" t="n">
         <v>7908034</v>
@@ -5652,16 +5652,16 @@
         <v>44127</v>
       </c>
       <c r="B262" t="n">
-        <v>8.234419822692871</v>
+        <v>8.234420776367188</v>
       </c>
       <c r="C262" t="n">
-        <v>8.312570966783923</v>
+        <v>8.312571929509362</v>
       </c>
       <c r="D262" t="n">
-        <v>8.203406854103131</v>
+        <v>8.203407804185662</v>
       </c>
       <c r="E262" t="n">
-        <v>8.269152274680931</v>
+        <v>8.269153232377807</v>
       </c>
       <c r="F262" t="n">
         <v>5098571</v>
@@ -5712,16 +5712,16 @@
         <v>44132</v>
       </c>
       <c r="B265" t="n">
-        <v>7.825055599212646</v>
+        <v>7.825055122375488</v>
       </c>
       <c r="C265" t="n">
-        <v>8.088040873150774</v>
+        <v>8.088040380288025</v>
       </c>
       <c r="D265" t="n">
-        <v>7.817612164601516</v>
+        <v>7.81761168821794</v>
       </c>
       <c r="E265" t="n">
-        <v>8.078116293669268</v>
+        <v>8.078115801411293</v>
       </c>
       <c r="F265" t="n">
         <v>12369944</v>
@@ -5752,16 +5752,16 @@
         <v>44134</v>
       </c>
       <c r="B267" t="n">
-        <v>7.684878826141357</v>
+        <v>7.684879302978516</v>
       </c>
       <c r="C267" t="n">
-        <v>7.777915944304612</v>
+        <v>7.777916426914608</v>
       </c>
       <c r="D267" t="n">
-        <v>7.574474588649013</v>
+        <v>7.574475058635726</v>
       </c>
       <c r="E267" t="n">
-        <v>7.759308699364413</v>
+        <v>7.759309180819852</v>
       </c>
       <c r="F267" t="n">
         <v>16269207</v>
@@ -5772,16 +5772,16 @@
         <v>44138</v>
       </c>
       <c r="B268" t="n">
-        <v>7.717131614685059</v>
+        <v>7.7171311378479</v>
       </c>
       <c r="C268" t="n">
-        <v>7.852346415863062</v>
+        <v>7.852345930671059</v>
       </c>
       <c r="D268" t="n">
-        <v>7.622854363726927</v>
+        <v>7.622853892715106</v>
       </c>
       <c r="E268" t="n">
-        <v>7.821334338599661</v>
+        <v>7.821333855323877</v>
       </c>
       <c r="F268" t="n">
         <v>9901091</v>
@@ -5812,16 +5812,16 @@
         <v>44140</v>
       </c>
       <c r="B270" t="n">
-        <v>8.119053840637207</v>
+        <v>8.119052886962891</v>
       </c>
       <c r="C270" t="n">
-        <v>8.177356724487632</v>
+        <v>8.177355763964984</v>
       </c>
       <c r="D270" t="n">
-        <v>8.007408575750512</v>
+        <v>8.007407635190189</v>
       </c>
       <c r="E270" t="n">
-        <v>8.039661672128053</v>
+        <v>8.039660727779241</v>
       </c>
       <c r="F270" t="n">
         <v>9820281</v>
@@ -5892,16 +5892,16 @@
         <v>44146</v>
       </c>
       <c r="B274" t="n">
-        <v>8.193483352661133</v>
+        <v>8.193482398986816</v>
       </c>
       <c r="C274" t="n">
-        <v>8.420494274138473</v>
+        <v>8.420493294041393</v>
       </c>
       <c r="D274" t="n">
-        <v>8.193483352661133</v>
+        <v>8.193482398986816</v>
       </c>
       <c r="E274" t="n">
-        <v>8.312572059811611</v>
+        <v>8.312571092276054</v>
       </c>
       <c r="F274" t="n">
         <v>7246451</v>
@@ -5912,16 +5912,16 @@
         <v>44147</v>
       </c>
       <c r="B275" t="n">
-        <v>8.234419822692871</v>
+        <v>8.234420776367188</v>
       </c>
       <c r="C275" t="n">
-        <v>8.398164651520666</v>
+        <v>8.398165624159189</v>
       </c>
       <c r="D275" t="n">
-        <v>8.131458125037573</v>
+        <v>8.13145906678732</v>
       </c>
       <c r="E275" t="n">
-        <v>8.193482275292528</v>
+        <v>8.193483224225638</v>
       </c>
       <c r="F275" t="n">
         <v>11697033</v>
@@ -5932,16 +5932,16 @@
         <v>44148</v>
       </c>
       <c r="B276" t="n">
-        <v>8.633858680725098</v>
+        <v>8.633859634399414</v>
       </c>
       <c r="C276" t="n">
-        <v>8.646264403631776</v>
+        <v>8.646265358676397</v>
       </c>
       <c r="D276" t="n">
-        <v>8.267911744802472</v>
+        <v>8.267912658055211</v>
       </c>
       <c r="E276" t="n">
-        <v>8.322493351742979</v>
+        <v>8.322494271024663</v>
       </c>
       <c r="F276" t="n">
         <v>10854949</v>
@@ -5992,16 +5992,16 @@
         <v>44153</v>
       </c>
       <c r="B279" t="n">
-        <v>8.584239959716797</v>
+        <v>8.584240913391113</v>
       </c>
       <c r="C279" t="n">
-        <v>8.64502398560519</v>
+        <v>8.645024946032365</v>
       </c>
       <c r="D279" t="n">
-        <v>8.516012499566937</v>
+        <v>8.516013445661457</v>
       </c>
       <c r="E279" t="n">
-        <v>8.55818927999508</v>
+        <v>8.558190230775271</v>
       </c>
       <c r="F279" t="n">
         <v>8922310</v>
@@ -6072,16 +6072,16 @@
         <v>44160</v>
       </c>
       <c r="B283" t="n">
-        <v>8.739301681518555</v>
+        <v>8.739302635192871</v>
       </c>
       <c r="C283" t="n">
-        <v>8.920413624337439</v>
+        <v>8.920414597775554</v>
       </c>
       <c r="D283" t="n">
-        <v>8.616491723410208</v>
+        <v>8.616492663682914</v>
       </c>
       <c r="E283" t="n">
-        <v>8.854667312281327</v>
+        <v>8.85466827854489</v>
       </c>
       <c r="F283" t="n">
         <v>6633202</v>
@@ -6112,16 +6112,16 @@
         <v>44162</v>
       </c>
       <c r="B285" t="n">
-        <v>8.615251541137695</v>
+        <v>8.615252494812012</v>
       </c>
       <c r="C285" t="n">
-        <v>8.70828776310049</v>
+        <v>8.708288727073548</v>
       </c>
       <c r="D285" t="n">
-        <v>8.507328451506179</v>
+        <v>8.507329393233835</v>
       </c>
       <c r="E285" t="n">
-        <v>8.566871454869922</v>
+        <v>8.566872403188754</v>
       </c>
       <c r="F285" t="n">
         <v>5230736</v>
@@ -6152,16 +6152,16 @@
         <v>44166</v>
       </c>
       <c r="B287" t="n">
-        <v>8.414291381835938</v>
+        <v>8.414292335510254</v>
       </c>
       <c r="C287" t="n">
-        <v>8.672314340510058</v>
+        <v>8.672315323428652</v>
       </c>
       <c r="D287" t="n">
-        <v>8.360949006055193</v>
+        <v>8.360949953683695</v>
       </c>
       <c r="E287" t="n">
-        <v>8.636339977103933</v>
+        <v>8.636340955945199</v>
       </c>
       <c r="F287" t="n">
         <v>16096259</v>
@@ -6172,16 +6172,16 @@
         <v>44167</v>
       </c>
       <c r="B288" t="n">
-        <v>8.282797813415527</v>
+        <v>8.282798767089844</v>
       </c>
       <c r="C288" t="n">
-        <v>8.461429503764982</v>
+        <v>8.4614304780068</v>
       </c>
       <c r="D288" t="n">
-        <v>8.199685276496087</v>
+        <v>8.199686220600897</v>
       </c>
       <c r="E288" t="n">
-        <v>8.456468108007872</v>
+        <v>8.456469081678438</v>
       </c>
       <c r="F288" t="n">
         <v>15329699</v>
@@ -6212,16 +6212,16 @@
         <v>44169</v>
       </c>
       <c r="B290" t="n">
-        <v>8.772793769836426</v>
+        <v>8.772794723510742</v>
       </c>
       <c r="C290" t="n">
-        <v>8.948944312102428</v>
+        <v>8.948945284925747</v>
       </c>
       <c r="D290" t="n">
-        <v>8.683478819885265</v>
+        <v>8.683479763850318</v>
       </c>
       <c r="E290" t="n">
-        <v>8.886919271932774</v>
+        <v>8.886920238013465</v>
       </c>
       <c r="F290" t="n">
         <v>10446369</v>
@@ -6232,16 +6232,16 @@
         <v>44172</v>
       </c>
       <c r="B291" t="n">
-        <v>8.647505760192871</v>
+        <v>8.647504806518555</v>
       </c>
       <c r="C291" t="n">
-        <v>8.82737759966732</v>
+        <v>8.827376626156168</v>
       </c>
       <c r="D291" t="n">
-        <v>8.621455078573774</v>
+        <v>8.621454127772409</v>
       </c>
       <c r="E291" t="n">
-        <v>8.807529333653388</v>
+        <v>8.807528362331166</v>
       </c>
       <c r="F291" t="n">
         <v>10174485</v>
@@ -6392,16 +6392,16 @@
         <v>44182</v>
       </c>
       <c r="B299" t="n">
-        <v>9.125096321105957</v>
+        <v>9.125097274780273</v>
       </c>
       <c r="C299" t="n">
-        <v>9.233019415311725</v>
+        <v>9.233020380265208</v>
       </c>
       <c r="D299" t="n">
-        <v>9.1052480568353</v>
+        <v>9.105249008435251</v>
       </c>
       <c r="E299" t="n">
-        <v>9.230538270595108</v>
+        <v>9.230539235289285</v>
       </c>
       <c r="F299" t="n">
         <v>5262456</v>
@@ -6452,16 +6452,16 @@
         <v>44187</v>
       </c>
       <c r="B302" t="n">
-        <v>9.018413543701172</v>
+        <v>9.018414497375488</v>
       </c>
       <c r="C302" t="n">
-        <v>9.117653080233614</v>
+        <v>9.117654044402261</v>
       </c>
       <c r="D302" t="n">
-        <v>8.941503416629342</v>
+        <v>8.941504362170608</v>
       </c>
       <c r="E302" t="n">
-        <v>8.974995743895692</v>
+        <v>8.974996692978687</v>
       </c>
       <c r="F302" t="n">
         <v>3700636</v>
@@ -6572,16 +6572,16 @@
         <v>44201</v>
       </c>
       <c r="B308" t="n">
-        <v>9.097805023193359</v>
+        <v>9.097805976867676</v>
       </c>
       <c r="C308" t="n">
-        <v>9.304967640603</v>
+        <v>9.304968615993069</v>
       </c>
       <c r="D308" t="n">
-        <v>9.012210449150441</v>
+        <v>9.012211393852336</v>
       </c>
       <c r="E308" t="n">
-        <v>9.304967640603</v>
+        <v>9.304968615993069</v>
       </c>
       <c r="F308" t="n">
         <v>8306796</v>
@@ -6592,16 +6592,16 @@
         <v>44202</v>
       </c>
       <c r="B309" t="n">
-        <v>9.02337646484375</v>
+        <v>9.023375511169434</v>
       </c>
       <c r="C309" t="n">
-        <v>9.178438642419241</v>
+        <v>9.178437672356514</v>
       </c>
       <c r="D309" t="n">
-        <v>8.883200263463204</v>
+        <v>8.883199324604012</v>
       </c>
       <c r="E309" t="n">
-        <v>9.091603036730099</v>
+        <v>9.091602075844966</v>
       </c>
       <c r="F309" t="n">
         <v>6995714</v>
@@ -6632,16 +6632,16 @@
         <v>44204</v>
       </c>
       <c r="B311" t="n">
-        <v>9.494765281677246</v>
+        <v>9.49476432800293</v>
       </c>
       <c r="C311" t="n">
-        <v>9.533220794103377</v>
+        <v>9.533219836566508</v>
       </c>
       <c r="D311" t="n">
-        <v>9.077957953992263</v>
+        <v>9.077957042182957</v>
       </c>
       <c r="E311" t="n">
-        <v>9.178438515281906</v>
+        <v>9.178437593380119</v>
       </c>
       <c r="F311" t="n">
         <v>10280973</v>
@@ -6732,16 +6732,16 @@
         <v>44211</v>
       </c>
       <c r="B316" t="n">
-        <v>9.479878425598145</v>
+        <v>9.479877471923828</v>
       </c>
       <c r="C316" t="n">
-        <v>9.607649794137002</v>
+        <v>9.607648827608905</v>
       </c>
       <c r="D316" t="n">
-        <v>9.378158631904267</v>
+        <v>9.378157688462947</v>
       </c>
       <c r="E316" t="n">
-        <v>9.589042547490402</v>
+        <v>9.589041582834192</v>
       </c>
       <c r="F316" t="n">
         <v>14334303</v>
@@ -6892,16 +6892,16 @@
         <v>44224</v>
       </c>
       <c r="B324" t="n">
-        <v>9.368232727050781</v>
+        <v>9.368233680725098</v>
       </c>
       <c r="C324" t="n">
-        <v>9.399244800408228</v>
+        <v>9.399245757239534</v>
       </c>
       <c r="D324" t="n">
-        <v>9.102766341339521</v>
+        <v>9.102767267989694</v>
       </c>
       <c r="E324" t="n">
-        <v>9.180917480970056</v>
+        <v>9.180918415575915</v>
       </c>
       <c r="F324" t="n">
         <v>7429217</v>
@@ -6912,16 +6912,16 @@
         <v>44225</v>
       </c>
       <c r="B325" t="n">
-        <v>9.363271713256836</v>
+        <v>9.36327075958252</v>
       </c>
       <c r="C325" t="n">
-        <v>9.571676269761104</v>
+        <v>9.571675294860224</v>
       </c>
       <c r="D325" t="n">
-        <v>9.215652973121827</v>
+        <v>9.215652034482874</v>
       </c>
       <c r="E325" t="n">
-        <v>9.312411369945844</v>
+        <v>9.312410421451789</v>
       </c>
       <c r="F325" t="n">
         <v>11022611</v>
@@ -6952,16 +6952,16 @@
         <v>44229</v>
       </c>
       <c r="B327" t="n">
-        <v>10.13361930847168</v>
+        <v>10.133620262146</v>
       </c>
       <c r="C327" t="n">
-        <v>10.18447964681817</v>
+        <v>10.18448060527895</v>
       </c>
       <c r="D327" t="n">
-        <v>9.832179442109044</v>
+        <v>9.832180367414875</v>
       </c>
       <c r="E327" t="n">
-        <v>10.11004977442547</v>
+        <v>10.11005072588166</v>
       </c>
       <c r="F327" t="n">
         <v>20046878</v>
@@ -6992,16 +6992,16 @@
         <v>44231</v>
       </c>
       <c r="B329" t="n">
-        <v>10.38668251037598</v>
+        <v>10.38668155670166</v>
       </c>
       <c r="C329" t="n">
-        <v>10.38668251037598</v>
+        <v>10.38668155670166</v>
       </c>
       <c r="D329" t="n">
-        <v>10.11749393146458</v>
+        <v>10.11749300250636</v>
       </c>
       <c r="E329" t="n">
-        <v>10.17703872709649</v>
+        <v>10.17703779267104</v>
       </c>
       <c r="F329" t="n">
         <v>12166787</v>
@@ -7012,16 +7012,16 @@
         <v>44232</v>
       </c>
       <c r="B330" t="n">
-        <v>10.55663013458252</v>
+        <v>10.5566291809082</v>
       </c>
       <c r="C330" t="n">
-        <v>10.58144069033415</v>
+        <v>10.58143973441847</v>
       </c>
       <c r="D330" t="n">
-        <v>10.32465782656054</v>
+        <v>10.32465689384235</v>
       </c>
       <c r="E330" t="n">
-        <v>10.41893507933724</v>
+        <v>10.41893413810214</v>
       </c>
       <c r="F330" t="n">
         <v>10745440</v>
@@ -7192,16 +7192,16 @@
         <v>44249</v>
       </c>
       <c r="B339" t="n">
-        <v>11.09376525878906</v>
+        <v>11.09376621246338</v>
       </c>
       <c r="C339" t="n">
-        <v>11.20292847746345</v>
+        <v>11.20292944052197</v>
       </c>
       <c r="D339" t="n">
-        <v>10.63602131403072</v>
+        <v>10.63602222835513</v>
       </c>
       <c r="E339" t="n">
-        <v>10.9399432226141</v>
+        <v>10.93994416306512</v>
       </c>
       <c r="F339" t="n">
         <v>14982292</v>
@@ -7292,16 +7292,16 @@
         <v>44256</v>
       </c>
       <c r="B344" t="n">
-        <v>21.85701751708984</v>
+        <v>21.85701560974121</v>
       </c>
       <c r="C344" t="n">
-        <v>23.99306617161</v>
+        <v>23.99306407785948</v>
       </c>
       <c r="D344" t="n">
-        <v>16.31078752172449</v>
+        <v>16.3107860983666</v>
       </c>
       <c r="E344" t="n">
-        <v>16.86353693074166</v>
+        <v>16.8635354591482</v>
       </c>
       <c r="F344" t="n">
         <v>49361500</v>
@@ -7312,16 +7312,16 @@
         <v>44257</v>
       </c>
       <c r="B345" t="n">
-        <v>21.19184494018555</v>
+        <v>21.19184303283691</v>
       </c>
       <c r="C345" t="n">
-        <v>22.95314685108304</v>
+        <v>22.95314478521037</v>
       </c>
       <c r="D345" t="n">
-        <v>20.69530683439987</v>
+        <v>20.6953049717416</v>
       </c>
       <c r="E345" t="n">
-        <v>22.18491936483229</v>
+        <v>22.18491736810308</v>
       </c>
       <c r="F345" t="n">
         <v>20095700</v>
@@ -7352,16 +7352,16 @@
         <v>44259</v>
       </c>
       <c r="B347" t="n">
-        <v>20.86394309997559</v>
+        <v>20.86394119262695</v>
       </c>
       <c r="C347" t="n">
-        <v>21.52911508897337</v>
+        <v>21.52911312081577</v>
       </c>
       <c r="D347" t="n">
-        <v>20.0113977633286</v>
+        <v>20.01139593391831</v>
       </c>
       <c r="E347" t="n">
-        <v>20.23624470835284</v>
+        <v>20.2362428583874</v>
       </c>
       <c r="F347" t="n">
         <v>8984600</v>
@@ -7732,16 +7732,16 @@
         <v>44286</v>
       </c>
       <c r="B366" t="n">
-        <v>31.08511734008789</v>
+        <v>31.08511924743652</v>
       </c>
       <c r="C366" t="n">
-        <v>32.65904760342265</v>
+        <v>32.65904960734591</v>
       </c>
       <c r="D366" t="n">
-        <v>30.82279682081511</v>
+        <v>30.82279871206804</v>
       </c>
       <c r="E366" t="n">
-        <v>31.95640029207138</v>
+        <v>31.95640225288098</v>
       </c>
       <c r="F366" t="n">
         <v>8195900</v>
@@ -7792,16 +7792,16 @@
         <v>44292</v>
       </c>
       <c r="B369" t="n">
-        <v>30.5792121887207</v>
+        <v>30.57921028137207</v>
       </c>
       <c r="C369" t="n">
-        <v>32.19998498521812</v>
+        <v>32.19998297677536</v>
       </c>
       <c r="D369" t="n">
-        <v>30.48552730465581</v>
+        <v>30.48552540315069</v>
       </c>
       <c r="E369" t="n">
-        <v>31.01953900629401</v>
+        <v>31.01953707148042</v>
       </c>
       <c r="F369" t="n">
         <v>6923500</v>
@@ -7812,16 +7812,16 @@
         <v>44293</v>
       </c>
       <c r="B370" t="n">
-        <v>30.95395660400391</v>
+        <v>30.95395851135254</v>
       </c>
       <c r="C370" t="n">
-        <v>31.36617506706607</v>
+        <v>31.36617699981515</v>
       </c>
       <c r="D370" t="n">
-        <v>30.40120725129495</v>
+        <v>30.40120912458377</v>
       </c>
       <c r="E370" t="n">
-        <v>30.72910789533883</v>
+        <v>30.72910978883253</v>
       </c>
       <c r="F370" t="n">
         <v>4745700</v>
@@ -8012,16 +8012,16 @@
         <v>44308</v>
       </c>
       <c r="B380" t="n">
-        <v>36.30344390869141</v>
+        <v>36.30344772338867</v>
       </c>
       <c r="C380" t="n">
-        <v>38.03663915608288</v>
+        <v>38.03664315290104</v>
       </c>
       <c r="D380" t="n">
-        <v>35.88185481304648</v>
+        <v>35.88185858344396</v>
       </c>
       <c r="E380" t="n">
-        <v>37.12788440974715</v>
+        <v>37.12788831107506</v>
       </c>
       <c r="F380" t="n">
         <v>6756200</v>
@@ -8052,16 +8052,16 @@
         <v>44312</v>
       </c>
       <c r="B382" t="n">
-        <v>35.91933441162109</v>
+        <v>35.91933059692383</v>
       </c>
       <c r="C382" t="n">
-        <v>36.30344817190534</v>
+        <v>36.30344431641451</v>
       </c>
       <c r="D382" t="n">
-        <v>35.51648295890232</v>
+        <v>35.5164791869886</v>
       </c>
       <c r="E382" t="n">
-        <v>35.88185902675205</v>
+        <v>35.88185521603473</v>
       </c>
       <c r="F382" t="n">
         <v>4241900</v>
@@ -8072,16 +8072,16 @@
         <v>44313</v>
       </c>
       <c r="B383" t="n">
-        <v>35.46963500976562</v>
+        <v>35.46963882446289</v>
       </c>
       <c r="C383" t="n">
-        <v>36.2940754796825</v>
+        <v>36.29407938304689</v>
       </c>
       <c r="D383" t="n">
-        <v>35.27289463051181</v>
+        <v>35.27289842405</v>
       </c>
       <c r="E383" t="n">
-        <v>36.05985972137591</v>
+        <v>36.05986359955081</v>
       </c>
       <c r="F383" t="n">
         <v>2386900</v>
@@ -35452,19 +35452,39 @@
         <v>46315</v>
       </c>
       <c r="B1752" t="n">
-        <v>3.12</v>
+        <v>3.119999885559082</v>
       </c>
       <c r="C1752" t="n">
-        <v>3.14</v>
+        <v>3.140000104904175</v>
       </c>
       <c r="D1752" t="n">
-        <v>2.98</v>
+        <v>2.980000019073486</v>
       </c>
       <c r="E1752" t="n">
-        <v>3.02</v>
+        <v>3.019999980926514</v>
       </c>
       <c r="F1752" t="n">
         <v>6363900</v>
+      </c>
+    </row>
+    <row r="1753">
+      <c r="A1753" s="1" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B1753" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="C1753" t="n">
+        <v>3.21</v>
+      </c>
+      <c r="D1753" t="n">
+        <v>3</v>
+      </c>
+      <c r="E1753" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="F1753" t="n">
+        <v>6570300</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1753"/>
+  <dimension ref="A1:F1754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906202316284</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173355102539</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173355102539</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173355102539</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173355102539</v>
+        <v>1.799173951148987</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="C9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="D9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="E9" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="C10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="D10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="E10" t="n">
-        <v>2.72519588470459</v>
+        <v>2.725195169448853</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279500007629395</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279500007629395</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279500007629395</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279500007629395</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359247207642</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652074813843</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461867332458</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461867332458</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461867332458</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461748123169</v>
+        <v>1.922461867332458</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951083660125732</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951083660125732</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951083660125732</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951083660125732</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997222900390625</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997222900390624</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958560943604</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958560943603</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.58793306350708</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="C49" t="n">
-        <v>4.58793306350708</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="D49" t="n">
-        <v>4.58793306350708</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="E49" t="n">
-        <v>4.58793306350708</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489363670349121</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296539306640625</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294586181640625</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589142322540283</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988324165344238</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988324165344238</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988324165344238</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988324165344238</v>
+        <v>8.988326072692871</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257484436035</v>
+        <v>10.33257389068604</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27652168273926</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27652168273926</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27652168273926</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27652168273926</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -1872,16 +1872,16 @@
         <v>43741</v>
       </c>
       <c r="B73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F73" t="n">
         <v>755</v>
@@ -1892,16 +1892,16 @@
         <v>43747</v>
       </c>
       <c r="B74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F74" t="n">
         <v>755</v>
@@ -1952,16 +1952,16 @@
         <v>43773</v>
       </c>
       <c r="B77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F77" t="n">
         <v>1510</v>
@@ -2012,16 +2012,16 @@
         <v>43802</v>
       </c>
       <c r="B80" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C80" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D80" t="n">
-        <v>9.217621990355065</v>
+        <v>9.21762282756219</v>
       </c>
       <c r="E80" t="n">
-        <v>9.217621990355065</v>
+        <v>9.21762282756219</v>
       </c>
       <c r="F80" t="n">
         <v>1510</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610008239746</v>
+        <v>10.60610103607178</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448353456507</v>
+        <v>11.08448453125444</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2432,16 +2432,16 @@
         <v>43894</v>
       </c>
       <c r="B101" t="n">
-        <v>8.692569732666016</v>
+        <v>8.692568778991699</v>
       </c>
       <c r="C101" t="n">
-        <v>8.802247729651036</v>
+        <v>8.80224676394379</v>
       </c>
       <c r="D101" t="n">
-        <v>8.564222836484587</v>
+        <v>8.564221896891393</v>
       </c>
       <c r="E101" t="n">
-        <v>8.734573285204156</v>
+        <v>8.734572326921571</v>
       </c>
       <c r="F101" t="n">
         <v>7583284</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174577261989849</v>
+        <v>7.174576363958773</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269087350174872</v>
+        <v>7.269086440314109</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151755156881</v>
+        <v>7.885151270575596</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395101374897398</v>
+        <v>7.395100920432114</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2532,16 +2532,16 @@
         <v>43901</v>
       </c>
       <c r="B106" t="n">
-        <v>7.280755519866943</v>
+        <v>7.280755043029785</v>
       </c>
       <c r="C106" t="n">
-        <v>7.652961180826241</v>
+        <v>7.652960679612288</v>
       </c>
       <c r="D106" t="n">
-        <v>6.825709192772189</v>
+        <v>6.825708745737296</v>
       </c>
       <c r="E106" t="n">
-        <v>7.467442830172282</v>
+        <v>7.467442341108447</v>
       </c>
       <c r="F106" t="n">
         <v>14927915</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198787689209</v>
+        <v>6.731198310852051</v>
       </c>
       <c r="C107" t="n">
-        <v>6.784870504526766</v>
+        <v>6.78487002388751</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975689474925</v>
+        <v>6.183975251402972</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242314420779493</v>
+        <v>6.242313978574833</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642459392547607</v>
+        <v>7.642458915710449</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934156405738198</v>
+        <v>7.934155910701143</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650690051923714</v>
+        <v>6.650689636966175</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251668627103</v>
+        <v>7.242251216760168</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255535125732</v>
+        <v>7.277255058288574</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292731402749</v>
+        <v>7.641292230712304</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086141684674</v>
+        <v>6.70086097777741</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766202137520195</v>
+        <v>6.766201694169458</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2632,16 +2632,16 @@
         <v>43908</v>
       </c>
       <c r="B111" t="n">
-        <v>6.98555850982666</v>
+        <v>6.985558032989502</v>
       </c>
       <c r="C111" t="n">
-        <v>8.075338544707167</v>
+        <v>8.075337993481165</v>
       </c>
       <c r="D111" t="n">
-        <v>6.71019666955442</v>
+        <v>6.710196211513576</v>
       </c>
       <c r="E111" t="n">
-        <v>7.140741469742403</v>
+        <v>7.140740982312391</v>
       </c>
       <c r="F111" t="n">
         <v>26337960</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314575195312</v>
+        <v>7.844314098358154</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109175099531829</v>
+        <v>8.109174606594431</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235251340767977</v>
+        <v>7.235250900954319</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146673416115</v>
+        <v>7.829146197500977</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2692,16 +2692,16 @@
         <v>43913</v>
       </c>
       <c r="B114" t="n">
-        <v>8.386871337890625</v>
+        <v>8.386870384216309</v>
       </c>
       <c r="C114" t="n">
-        <v>8.386871337890625</v>
+        <v>8.386870384216309</v>
       </c>
       <c r="D114" t="n">
-        <v>7.483777299441991</v>
+        <v>7.48377644845884</v>
       </c>
       <c r="E114" t="n">
-        <v>8.050836190491395</v>
+        <v>8.050835275027762</v>
       </c>
       <c r="F114" t="n">
         <v>25091072</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738136291503906</v>
+        <v>7.738137245178223</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145345142681279</v>
+        <v>8.145346146541403</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298031292473</v>
+        <v>7.690298979071039</v>
       </c>
       <c r="E117" t="n">
-        <v>8.138343991239532</v>
+        <v>8.13834499423681</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775199890137</v>
+        <v>7.469775676727295</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304309853773</v>
+        <v>7.746304804343318</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351929620609467</v>
+        <v>7.351930089923889</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113307020195</v>
+        <v>7.514113786687701</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582952976226807</v>
+        <v>7.582953929901123</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840814016199421</v>
+        <v>7.840815002303775</v>
       </c>
       <c r="D122" t="n">
-        <v>7.38109946741859</v>
+        <v>7.381100395706687</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455773374392843</v>
+        <v>7.455774312072345</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261936187744</v>
+        <v>7.340261459350586</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624921524582</v>
+        <v>7.622624426344595</v>
       </c>
       <c r="D123" t="n">
-        <v>7.215416044404066</v>
+        <v>7.21541557567713</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457642689852</v>
+        <v>7.621457147585694</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672797203063965</v>
+        <v>7.672797679901123</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109175462567777</v>
+        <v>8.109175966524298</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661129456500152</v>
+        <v>7.661129932612202</v>
       </c>
       <c r="E125" t="n">
-        <v>7.84081477047941</v>
+        <v>7.840815257758265</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2952,16 +2952,16 @@
         <v>43930</v>
       </c>
       <c r="B127" t="n">
-        <v>7.385766506195068</v>
+        <v>7.38576602935791</v>
       </c>
       <c r="C127" t="n">
-        <v>7.778973921193609</v>
+        <v>7.778973418970338</v>
       </c>
       <c r="D127" t="n">
-        <v>7.351929706227764</v>
+        <v>7.351929231575166</v>
       </c>
       <c r="E127" t="n">
-        <v>7.778973921193609</v>
+        <v>7.778973418970338</v>
       </c>
       <c r="F127" t="n">
         <v>7590081</v>
@@ -2972,16 +2972,16 @@
         <v>43934</v>
       </c>
       <c r="B128" t="n">
-        <v>7.414936065673828</v>
+        <v>7.41493558883667</v>
       </c>
       <c r="C128" t="n">
-        <v>7.447606428031426</v>
+        <v>7.447605949093313</v>
       </c>
       <c r="D128" t="n">
-        <v>7.22941688022938</v>
+        <v>7.229416415322526</v>
       </c>
       <c r="E128" t="n">
-        <v>7.385766699549943</v>
+        <v>7.385766224588598</v>
       </c>
       <c r="F128" t="n">
         <v>8873976</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500111103057861</v>
+        <v>7.500110626220703</v>
       </c>
       <c r="C129" t="n">
-        <v>7.75097100706328</v>
+        <v>7.750970514277116</v>
       </c>
       <c r="D129" t="n">
-        <v>7.45577383571197</v>
+        <v>7.455773361693658</v>
       </c>
       <c r="E129" t="n">
-        <v>7.494278070349739</v>
+        <v>7.49427759388343</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375264644622803</v>
+        <v>7.375265598297119</v>
       </c>
       <c r="C130" t="n">
-        <v>7.494277495176356</v>
+        <v>7.494278464239883</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343761564324954</v>
+        <v>7.343762513925697</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935003671517</v>
+        <v>7.407935961570344</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566618919372559</v>
+        <v>7.566619396209717</v>
       </c>
       <c r="C131" t="n">
-        <v>7.58878797268838</v>
+        <v>7.5887884509226</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234083960008746</v>
+        <v>7.234084415890043</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444105906916389</v>
+        <v>7.444106376032958</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251523017883301</v>
+        <v>8.251522064208984</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431208332707222</v>
+        <v>8.431207358265677</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3112,16 +3112,16 @@
         <v>43944</v>
       </c>
       <c r="B135" t="n">
-        <v>8.089340209960938</v>
+        <v>8.089339256286621</v>
       </c>
       <c r="C135" t="n">
-        <v>8.574724018558863</v>
+        <v>8.57472300766133</v>
       </c>
       <c r="D135" t="n">
-        <v>7.969160906424007</v>
+        <v>7.969159966917957</v>
       </c>
       <c r="E135" t="n">
-        <v>8.481380364324728</v>
+        <v>8.481379364431731</v>
       </c>
       <c r="F135" t="n">
         <v>13472583</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852481842041016</v>
+        <v>7.852482318878174</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764051870702</v>
+        <v>7.357764498666425</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3152,16 +3152,16 @@
         <v>43948</v>
       </c>
       <c r="B137" t="n">
-        <v>8.105674743652344</v>
+        <v>8.105673789978027</v>
       </c>
       <c r="C137" t="n">
-        <v>8.165180757388045</v>
+        <v>8.16517979671254</v>
       </c>
       <c r="D137" t="n">
-        <v>7.710134423961201</v>
+        <v>7.710133516824237</v>
       </c>
       <c r="E137" t="n">
-        <v>7.93765801086142</v>
+        <v>7.937657076955135</v>
       </c>
       <c r="F137" t="n">
         <v>12260436</v>
@@ -3172,16 +3172,16 @@
         <v>43949</v>
       </c>
       <c r="B138" t="n">
-        <v>7.822145938873291</v>
+        <v>7.822145462036133</v>
       </c>
       <c r="C138" t="n">
-        <v>8.301695873226397</v>
+        <v>8.301695367155927</v>
       </c>
       <c r="D138" t="n">
-        <v>7.804644318877395</v>
+        <v>7.804643843107134</v>
       </c>
       <c r="E138" t="n">
-        <v>8.167515105844055</v>
+        <v>8.167514607953231</v>
       </c>
       <c r="F138" t="n">
         <v>14579753</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484073638916</v>
+        <v>7.887484550476074</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826254468098</v>
+        <v>7.966826736101882</v>
       </c>
       <c r="D139" t="n">
-        <v>7.70079846781684</v>
+        <v>7.700798933367937</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980371125938</v>
+        <v>7.841980845212174</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3252,16 +3252,16 @@
         <v>43956</v>
       </c>
       <c r="B142" t="n">
-        <v>8.114090919494629</v>
+        <v>8.114091873168945</v>
       </c>
       <c r="C142" t="n">
-        <v>8.645023715587479</v>
+        <v>8.645024731663977</v>
       </c>
       <c r="D142" t="n">
-        <v>8.069432995707503</v>
+        <v>8.069433944133035</v>
       </c>
       <c r="E142" t="n">
-        <v>8.286520199683441</v>
+        <v>8.286521173623905</v>
       </c>
       <c r="F142" t="n">
         <v>11843548</v>
@@ -3272,16 +3272,16 @@
         <v>43957</v>
       </c>
       <c r="B143" t="n">
-        <v>8.048345565795898</v>
+        <v>8.048344612121582</v>
       </c>
       <c r="C143" t="n">
-        <v>8.145104858936216</v>
+        <v>8.145103893796581</v>
       </c>
       <c r="D143" t="n">
-        <v>7.963991997516411</v>
+        <v>7.96399105383742</v>
       </c>
       <c r="E143" t="n">
-        <v>8.145104858936216</v>
+        <v>8.145103893796581</v>
       </c>
       <c r="F143" t="n">
         <v>16545622</v>
@@ -3312,16 +3312,16 @@
         <v>43959</v>
       </c>
       <c r="B145" t="n">
-        <v>8.162469863891602</v>
+        <v>8.162470817565918</v>
       </c>
       <c r="C145" t="n">
-        <v>8.184799271833279</v>
+        <v>8.184800228116485</v>
       </c>
       <c r="D145" t="n">
-        <v>7.94786381115636</v>
+        <v>7.947864739756858</v>
       </c>
       <c r="E145" t="n">
-        <v>8.15626744912163</v>
+        <v>8.156268402071278</v>
       </c>
       <c r="F145" t="n">
         <v>8818844</v>
@@ -3352,16 +3352,16 @@
         <v>43963</v>
       </c>
       <c r="B147" t="n">
-        <v>8.085558891296387</v>
+        <v>8.085559844970703</v>
       </c>
       <c r="C147" t="n">
-        <v>8.276595411529883</v>
+        <v>8.276596387736546</v>
       </c>
       <c r="D147" t="n">
-        <v>8.063229483236768</v>
+        <v>8.063230434277379</v>
       </c>
       <c r="E147" t="n">
-        <v>8.187279566215866</v>
+        <v>8.187280531887918</v>
       </c>
       <c r="F147" t="n">
         <v>9953957</v>
@@ -3372,16 +3372,16 @@
         <v>43964</v>
       </c>
       <c r="B148" t="n">
-        <v>7.926775455474854</v>
+        <v>7.926775932312012</v>
       </c>
       <c r="C148" t="n">
-        <v>8.187279557292356</v>
+        <v>8.187280049800203</v>
       </c>
       <c r="D148" t="n">
-        <v>7.885839696513885</v>
+        <v>7.885840170888542</v>
       </c>
       <c r="E148" t="n">
-        <v>8.187279557292356</v>
+        <v>8.187280049800203</v>
       </c>
       <c r="F148" t="n">
         <v>10179016</v>
@@ -3412,16 +3412,16 @@
         <v>43966</v>
       </c>
       <c r="B150" t="n">
-        <v>6.8413405418396</v>
+        <v>6.841341018676758</v>
       </c>
       <c r="C150" t="n">
-        <v>7.421893104642092</v>
+        <v>7.421893621943401</v>
       </c>
       <c r="D150" t="n">
-        <v>6.8413405418396</v>
+        <v>6.841341018676758</v>
       </c>
       <c r="E150" t="n">
-        <v>7.420652532303285</v>
+        <v>7.420653049518127</v>
       </c>
       <c r="F150" t="n">
         <v>26563775</v>
@@ -3452,16 +3452,16 @@
         <v>43970</v>
       </c>
       <c r="B152" t="n">
-        <v>6.831418037414551</v>
+        <v>6.831417560577393</v>
       </c>
       <c r="C152" t="n">
-        <v>7.018732418962401</v>
+        <v>7.018731929050585</v>
       </c>
       <c r="D152" t="n">
-        <v>6.79916449333305</v>
+        <v>6.799164018747209</v>
       </c>
       <c r="E152" t="n">
-        <v>6.966631502251738</v>
+        <v>6.966631015976597</v>
       </c>
       <c r="F152" t="n">
         <v>13463520</v>
@@ -3472,16 +3472,16 @@
         <v>43971</v>
       </c>
       <c r="B153" t="n">
-        <v>6.822733879089355</v>
+        <v>6.822733402252197</v>
       </c>
       <c r="C153" t="n">
-        <v>6.983998022077899</v>
+        <v>6.983997533970078</v>
       </c>
       <c r="D153" t="n">
-        <v>6.810329048105121</v>
+        <v>6.81032857213493</v>
       </c>
       <c r="E153" t="n">
-        <v>6.94678397585636</v>
+        <v>6.946783490349408</v>
       </c>
       <c r="F153" t="n">
         <v>11533147</v>
@@ -3552,16 +3552,16 @@
         <v>43977</v>
       </c>
       <c r="B157" t="n">
-        <v>7.423134803771973</v>
+        <v>7.423134326934814</v>
       </c>
       <c r="C157" t="n">
-        <v>7.560829411371671</v>
+        <v>7.560828925689475</v>
       </c>
       <c r="D157" t="n">
-        <v>7.275515169821428</v>
+        <v>7.275514702466858</v>
       </c>
       <c r="E157" t="n">
-        <v>7.442982622817829</v>
+        <v>7.442982144705714</v>
       </c>
       <c r="F157" t="n">
         <v>12080691</v>
@@ -3612,16 +3612,16 @@
         <v>43980</v>
       </c>
       <c r="B160" t="n">
-        <v>7.812650203704834</v>
+        <v>7.812650680541992</v>
       </c>
       <c r="C160" t="n">
-        <v>7.812650203704834</v>
+        <v>7.812650680541992</v>
       </c>
       <c r="D160" t="n">
-        <v>7.481437043617326</v>
+        <v>7.481437500239227</v>
       </c>
       <c r="E160" t="n">
-        <v>7.519892999404318</v>
+        <v>7.519893458373339</v>
       </c>
       <c r="F160" t="n">
         <v>23712019</v>
@@ -3652,16 +3652,16 @@
         <v>43984</v>
       </c>
       <c r="B162" t="n">
-        <v>8.271634101867676</v>
+        <v>8.271635055541992</v>
       </c>
       <c r="C162" t="n">
-        <v>8.286520076241633</v>
+        <v>8.286521031632221</v>
       </c>
       <c r="D162" t="n">
-        <v>7.976395759027911</v>
+        <v>7.976396678662855</v>
       </c>
       <c r="E162" t="n">
-        <v>8.063229567170044</v>
+        <v>8.063230496816454</v>
       </c>
       <c r="F162" t="n">
         <v>21348142</v>
@@ -3672,16 +3672,16 @@
         <v>43985</v>
       </c>
       <c r="B163" t="n">
-        <v>8.373354911804199</v>
+        <v>8.373353958129883</v>
       </c>
       <c r="C163" t="n">
-        <v>8.800086825192951</v>
+        <v>8.80008582291646</v>
       </c>
       <c r="D163" t="n">
-        <v>8.315052026205343</v>
+        <v>8.315051079171372</v>
       </c>
       <c r="E163" t="n">
-        <v>8.317533171149149</v>
+        <v>8.31753222383259</v>
       </c>
       <c r="F163" t="n">
         <v>31125376</v>
@@ -3752,16 +3752,16 @@
         <v>43991</v>
       </c>
       <c r="B167" t="n">
-        <v>8.296442985534668</v>
+        <v>8.296443939208984</v>
       </c>
       <c r="C167" t="n">
-        <v>8.327455953773208</v>
+        <v>8.32745691101246</v>
       </c>
       <c r="D167" t="n">
-        <v>8.096723794435762</v>
+        <v>8.0967247251524</v>
       </c>
       <c r="E167" t="n">
-        <v>8.137660447910266</v>
+        <v>8.137661383332564</v>
       </c>
       <c r="F167" t="n">
         <v>13675741</v>
@@ -3772,16 +3772,16 @@
         <v>43992</v>
       </c>
       <c r="B168" t="n">
-        <v>8.08928108215332</v>
+        <v>8.089280128479004</v>
       </c>
       <c r="C168" t="n">
-        <v>8.426697131827968</v>
+        <v>8.426696138374464</v>
       </c>
       <c r="D168" t="n">
-        <v>8.0371806131882</v>
+        <v>8.037179665656195</v>
       </c>
       <c r="E168" t="n">
-        <v>8.311330595134894</v>
+        <v>8.311329615282364</v>
       </c>
       <c r="F168" t="n">
         <v>11944749</v>
@@ -3792,16 +3792,16 @@
         <v>43994</v>
       </c>
       <c r="B169" t="n">
-        <v>7.950345993041992</v>
+        <v>7.950345516204834</v>
       </c>
       <c r="C169" t="n">
-        <v>8.084319777785</v>
+        <v>8.084319292912509</v>
       </c>
       <c r="D169" t="n">
-        <v>7.774195424975465</v>
+        <v>7.774194958703272</v>
       </c>
       <c r="E169" t="n">
-        <v>7.877157131822456</v>
+        <v>7.877156659374939</v>
       </c>
       <c r="F169" t="n">
         <v>12251373</v>
@@ -3892,16 +3892,16 @@
         <v>44001</v>
       </c>
       <c r="B174" t="n">
-        <v>8.487480163574219</v>
+        <v>8.487481117248535</v>
       </c>
       <c r="C174" t="n">
-        <v>8.589200838114557</v>
+        <v>8.58920180321846</v>
       </c>
       <c r="D174" t="n">
-        <v>8.203406528896336</v>
+        <v>8.203407450651435</v>
       </c>
       <c r="E174" t="n">
-        <v>8.203406528896336</v>
+        <v>8.203407450651435</v>
       </c>
       <c r="F174" t="n">
         <v>20750754</v>
@@ -3912,16 +3912,16 @@
         <v>44004</v>
       </c>
       <c r="B175" t="n">
-        <v>8.440342903137207</v>
+        <v>8.440341949462891</v>
       </c>
       <c r="C175" t="n">
-        <v>8.729377964833343</v>
+        <v>8.729376978500955</v>
       </c>
       <c r="D175" t="n">
-        <v>8.380798106578508</v>
+        <v>8.380797159632158</v>
       </c>
       <c r="E175" t="n">
-        <v>8.489962226742637</v>
+        <v>8.489961267461833</v>
       </c>
       <c r="F175" t="n">
         <v>12069362</v>
@@ -3952,16 +3952,16 @@
         <v>44006</v>
       </c>
       <c r="B177" t="n">
-        <v>8.594162940979004</v>
+        <v>8.59416389465332</v>
       </c>
       <c r="C177" t="n">
-        <v>8.669832935726904</v>
+        <v>8.669833897798144</v>
       </c>
       <c r="D177" t="n">
-        <v>8.422973795079262</v>
+        <v>8.422974729757115</v>
       </c>
       <c r="E177" t="n">
-        <v>8.571833533486773</v>
+        <v>8.571834484683247</v>
       </c>
       <c r="F177" t="n">
         <v>7388434</v>
@@ -4052,16 +4052,16 @@
         <v>44013</v>
       </c>
       <c r="B182" t="n">
-        <v>9.009730339050293</v>
+        <v>9.009729385375977</v>
       </c>
       <c r="C182" t="n">
-        <v>9.11517229493286</v>
+        <v>9.115171330097578</v>
       </c>
       <c r="D182" t="n">
-        <v>8.731859089723871</v>
+        <v>8.731858165462054</v>
       </c>
       <c r="E182" t="n">
-        <v>8.812491383860499</v>
+        <v>8.812490451063802</v>
       </c>
       <c r="F182" t="n">
         <v>8963093</v>
@@ -4292,16 +4292,16 @@
         <v>44029</v>
       </c>
       <c r="B194" t="n">
-        <v>8.81993293762207</v>
+        <v>8.819933891296387</v>
       </c>
       <c r="C194" t="n">
-        <v>8.919173360420668</v>
+        <v>8.919174324825571</v>
       </c>
       <c r="D194" t="n">
-        <v>8.633858708433587</v>
+        <v>8.633859641988225</v>
       </c>
       <c r="E194" t="n">
-        <v>8.633858708433587</v>
+        <v>8.633859641988225</v>
       </c>
       <c r="F194" t="n">
         <v>9678298</v>
@@ -4432,16 +4432,16 @@
         <v>44040</v>
       </c>
       <c r="B201" t="n">
-        <v>9.641143798828125</v>
+        <v>9.641142845153809</v>
       </c>
       <c r="C201" t="n">
-        <v>9.832180339834917</v>
+        <v>9.832179367263814</v>
       </c>
       <c r="D201" t="n">
-        <v>9.466233359369541</v>
+        <v>9.466232422996864</v>
       </c>
       <c r="E201" t="n">
-        <v>9.675878040270206</v>
+        <v>9.67587708316008</v>
       </c>
       <c r="F201" t="n">
         <v>30127714</v>
@@ -4472,16 +4472,16 @@
         <v>44042</v>
       </c>
       <c r="B203" t="n">
-        <v>9.143704414367676</v>
+        <v>9.143703460693359</v>
       </c>
       <c r="C203" t="n">
-        <v>9.700687950073165</v>
+        <v>9.700686938306321</v>
       </c>
       <c r="D203" t="n">
-        <v>9.097806359971171</v>
+        <v>9.097805411083952</v>
       </c>
       <c r="E203" t="n">
-        <v>9.685801080392711</v>
+        <v>9.685800070178546</v>
       </c>
       <c r="F203" t="n">
         <v>33272500</v>
@@ -4592,16 +4592,16 @@
         <v>44050</v>
       </c>
       <c r="B209" t="n">
-        <v>8.429177284240723</v>
+        <v>8.429178237915039</v>
       </c>
       <c r="C209" t="n">
-        <v>8.429177284240723</v>
+        <v>8.429178237915039</v>
       </c>
       <c r="D209" t="n">
-        <v>8.255506990060143</v>
+        <v>8.25550792408546</v>
       </c>
       <c r="E209" t="n">
-        <v>8.336140169103194</v>
+        <v>8.336141112251321</v>
       </c>
       <c r="F209" t="n">
         <v>22110172</v>
@@ -4612,16 +4612,16 @@
         <v>44053</v>
       </c>
       <c r="B210" t="n">
-        <v>8.259230613708496</v>
+        <v>8.25922966003418</v>
       </c>
       <c r="C210" t="n">
-        <v>8.468874414585619</v>
+        <v>8.468873436704216</v>
       </c>
       <c r="D210" t="n">
-        <v>8.166192588662099</v>
+        <v>8.166191645730668</v>
       </c>
       <c r="E210" t="n">
-        <v>8.435380296706972</v>
+        <v>8.435379322693057</v>
       </c>
       <c r="F210" t="n">
         <v>21920608</v>
@@ -4652,16 +4652,16 @@
         <v>44055</v>
       </c>
       <c r="B212" t="n">
-        <v>8.162469863891602</v>
+        <v>8.162470817565918</v>
       </c>
       <c r="C212" t="n">
-        <v>8.446543498127859</v>
+        <v>8.446544484992341</v>
       </c>
       <c r="D212" t="n">
-        <v>8.078115414787984</v>
+        <v>8.078116358606623</v>
       </c>
       <c r="E212" t="n">
-        <v>8.409329009508031</v>
+        <v>8.409329992024503</v>
       </c>
       <c r="F212" t="n">
         <v>20200945</v>
@@ -4732,16 +4732,16 @@
         <v>44061</v>
       </c>
       <c r="B216" t="n">
-        <v>8.101686477661133</v>
+        <v>8.101685523986816</v>
       </c>
       <c r="C216" t="n">
-        <v>8.143864156905972</v>
+        <v>8.143863198266791</v>
       </c>
       <c r="D216" t="n">
-        <v>7.9788782846482</v>
+        <v>7.978877345430011</v>
       </c>
       <c r="E216" t="n">
-        <v>8.038421298987467</v>
+        <v>8.038420352760289</v>
       </c>
       <c r="F216" t="n">
         <v>10608743</v>
@@ -4752,16 +4752,16 @@
         <v>44062</v>
       </c>
       <c r="B217" t="n">
-        <v>7.926775455474854</v>
+        <v>7.926775932312012</v>
       </c>
       <c r="C217" t="n">
-        <v>8.141381509109719</v>
+        <v>8.141381998856557</v>
       </c>
       <c r="D217" t="n">
-        <v>7.921813166253184</v>
+        <v>7.921813642791834</v>
       </c>
       <c r="E217" t="n">
-        <v>8.141381509109719</v>
+        <v>8.141381998856557</v>
       </c>
       <c r="F217" t="n">
         <v>9466833</v>
@@ -4772,16 +4772,16 @@
         <v>44063</v>
       </c>
       <c r="B218" t="n">
-        <v>7.957788467407227</v>
+        <v>7.957787990570068</v>
       </c>
       <c r="C218" t="n">
-        <v>8.033459366376674</v>
+        <v>8.033458885005254</v>
       </c>
       <c r="D218" t="n">
-        <v>7.774195359575069</v>
+        <v>7.774194893738959</v>
       </c>
       <c r="E218" t="n">
-        <v>7.915611684438519</v>
+        <v>7.915611210128628</v>
       </c>
       <c r="F218" t="n">
         <v>7652765</v>
@@ -4892,16 +4892,16 @@
         <v>44071</v>
       </c>
       <c r="B224" t="n">
-        <v>8.100445747375488</v>
+        <v>8.100444793701172</v>
       </c>
       <c r="C224" t="n">
-        <v>8.100445747375488</v>
+        <v>8.100444793701172</v>
       </c>
       <c r="D224" t="n">
-        <v>7.960269549341362</v>
+        <v>7.960268612170143</v>
       </c>
       <c r="E224" t="n">
-        <v>8.0012070997281</v>
+        <v>8.001206157737258</v>
       </c>
       <c r="F224" t="n">
         <v>5577388</v>
@@ -5012,16 +5012,16 @@
         <v>44082</v>
       </c>
       <c r="B230" t="n">
-        <v>7.751865863800049</v>
+        <v>7.751865386962891</v>
       </c>
       <c r="C230" t="n">
-        <v>7.833738283935308</v>
+        <v>7.833737802061967</v>
       </c>
       <c r="D230" t="n">
-        <v>7.691081834917614</v>
+        <v>7.691081361819436</v>
       </c>
       <c r="E230" t="n">
-        <v>7.813890911851665</v>
+        <v>7.813890431199186</v>
       </c>
       <c r="F230" t="n">
         <v>7181501</v>
@@ -5032,16 +5032,16 @@
         <v>44083</v>
       </c>
       <c r="B231" t="n">
-        <v>7.709688663482666</v>
+        <v>7.709689140319824</v>
       </c>
       <c r="C231" t="n">
-        <v>7.834979771965168</v>
+        <v>7.834980256551466</v>
       </c>
       <c r="D231" t="n">
-        <v>7.637739933288351</v>
+        <v>7.637740405675546</v>
       </c>
       <c r="E231" t="n">
-        <v>7.792802098282933</v>
+        <v>7.792802580260581</v>
       </c>
       <c r="F231" t="n">
         <v>8282629</v>
@@ -5052,16 +5052,16 @@
         <v>44084</v>
       </c>
       <c r="B232" t="n">
-        <v>8.850947380065918</v>
+        <v>8.850946426391602</v>
       </c>
       <c r="C232" t="n">
-        <v>9.197045218135978</v>
+        <v>9.197044227170217</v>
       </c>
       <c r="D232" t="n">
-        <v>8.621455315968662</v>
+        <v>8.62145438702172</v>
       </c>
       <c r="E232" t="n">
-        <v>9.197045218135978</v>
+        <v>9.197044227170217</v>
       </c>
       <c r="F232" t="n">
         <v>139609921</v>
@@ -5132,16 +5132,16 @@
         <v>44090</v>
       </c>
       <c r="B236" t="n">
-        <v>9.312410354614258</v>
+        <v>9.312411308288574</v>
       </c>
       <c r="C236" t="n">
-        <v>9.375675522060035</v>
+        <v>9.375676482213272</v>
       </c>
       <c r="D236" t="n">
-        <v>9.175956334671081</v>
+        <v>9.175957274371282</v>
       </c>
       <c r="E236" t="n">
-        <v>9.179677604882659</v>
+        <v>9.179678544963952</v>
       </c>
       <c r="F236" t="n">
         <v>13993693</v>
@@ -5212,16 +5212,16 @@
         <v>44096</v>
       </c>
       <c r="B240" t="n">
-        <v>9.326058387756348</v>
+        <v>9.326057434082031</v>
       </c>
       <c r="C240" t="n">
-        <v>9.353349195522698</v>
+        <v>9.353348239057649</v>
       </c>
       <c r="D240" t="n">
-        <v>9.182159127084132</v>
+        <v>9.182158188124824</v>
       </c>
       <c r="E240" t="n">
-        <v>9.192083706971793</v>
+        <v>9.192082766997606</v>
       </c>
       <c r="F240" t="n">
         <v>9315031</v>
@@ -5232,16 +5232,16 @@
         <v>44097</v>
       </c>
       <c r="B241" t="n">
-        <v>8.95390796661377</v>
+        <v>8.953908920288086</v>
       </c>
       <c r="C241" t="n">
-        <v>9.308689320943529</v>
+        <v>9.308690312405352</v>
       </c>
       <c r="D241" t="n">
-        <v>8.934059702543932</v>
+        <v>8.934060654104224</v>
       </c>
       <c r="E241" t="n">
-        <v>9.303727925022763</v>
+        <v>9.303728915956151</v>
       </c>
       <c r="F241" t="n">
         <v>13677251</v>
@@ -5252,16 +5252,16 @@
         <v>44098</v>
       </c>
       <c r="B242" t="n">
-        <v>9.282639503479004</v>
+        <v>9.282638549804688</v>
       </c>
       <c r="C242" t="n">
-        <v>9.46375236122295</v>
+        <v>9.463751388941567</v>
       </c>
       <c r="D242" t="n">
-        <v>8.898085270619518</v>
+        <v>8.898084356453305</v>
       </c>
       <c r="E242" t="n">
-        <v>8.906769724577019</v>
+        <v>8.906768809518589</v>
       </c>
       <c r="F242" t="n">
         <v>18607406</v>
@@ -5272,16 +5272,16 @@
         <v>44099</v>
       </c>
       <c r="B243" t="n">
-        <v>9.184640884399414</v>
+        <v>9.184639930725098</v>
       </c>
       <c r="C243" t="n">
-        <v>9.254108474175018</v>
+        <v>9.25410751328763</v>
       </c>
       <c r="D243" t="n">
-        <v>9.095325028918353</v>
+        <v>9.095324084518023</v>
       </c>
       <c r="E243" t="n">
-        <v>9.22061435827287</v>
+        <v>9.220613400863298</v>
       </c>
       <c r="F243" t="n">
         <v>8201819</v>
@@ -5312,16 +5312,16 @@
         <v>44103</v>
       </c>
       <c r="B245" t="n">
-        <v>8.760390281677246</v>
+        <v>8.760391235351562</v>
       </c>
       <c r="C245" t="n">
-        <v>8.942743247933565</v>
+        <v>8.942744221459206</v>
       </c>
       <c r="D245" t="n">
-        <v>8.683479263674647</v>
+        <v>8.68348020897627</v>
       </c>
       <c r="E245" t="n">
-        <v>8.802567060978735</v>
+        <v>8.802568019244504</v>
       </c>
       <c r="F245" t="n">
         <v>13985386</v>
@@ -5332,16 +5332,16 @@
         <v>44104</v>
       </c>
       <c r="B246" t="n">
-        <v>8.651226997375488</v>
+        <v>8.651226043701172</v>
       </c>
       <c r="C246" t="n">
-        <v>8.841023415853394</v>
+        <v>8.841022441256731</v>
       </c>
       <c r="D246" t="n">
-        <v>8.609050214038696</v>
+        <v>8.609049265013768</v>
       </c>
       <c r="E246" t="n">
-        <v>8.803808028904122</v>
+        <v>8.803807058409923</v>
       </c>
       <c r="F246" t="n">
         <v>11477260</v>
@@ -5412,16 +5412,16 @@
         <v>44110</v>
       </c>
       <c r="B250" t="n">
-        <v>8.497404098510742</v>
+        <v>8.497405052185059</v>
       </c>
       <c r="C250" t="n">
-        <v>8.520973632751547</v>
+        <v>8.520974589071102</v>
       </c>
       <c r="D250" t="n">
-        <v>8.3162921520784</v>
+        <v>8.316293085426295</v>
       </c>
       <c r="E250" t="n">
-        <v>8.48872053887138</v>
+        <v>8.488721491571129</v>
       </c>
       <c r="F250" t="n">
         <v>10544549</v>
@@ -5432,16 +5432,16 @@
         <v>44111</v>
       </c>
       <c r="B251" t="n">
-        <v>8.585479736328125</v>
+        <v>8.585480690002441</v>
       </c>
       <c r="C251" t="n">
-        <v>8.704567531971968</v>
+        <v>8.704568498874545</v>
       </c>
       <c r="D251" t="n">
-        <v>8.440342155483876</v>
+        <v>8.440343093036322</v>
       </c>
       <c r="E251" t="n">
-        <v>8.477556644891454</v>
+        <v>8.477557586577683</v>
       </c>
       <c r="F251" t="n">
         <v>12680345</v>
@@ -5552,16 +5552,16 @@
         <v>44120</v>
       </c>
       <c r="B257" t="n">
-        <v>8.259230613708496</v>
+        <v>8.25922966003418</v>
       </c>
       <c r="C257" t="n">
-        <v>8.267913281163274</v>
+        <v>8.267912326486389</v>
       </c>
       <c r="D257" t="n">
-        <v>8.097965120577188</v>
+        <v>8.097964185523827</v>
       </c>
       <c r="E257" t="n">
-        <v>8.122775677538673</v>
+        <v>8.122774739620494</v>
       </c>
       <c r="F257" t="n">
         <v>10726560</v>
@@ -5612,16 +5612,16 @@
         <v>44125</v>
       </c>
       <c r="B260" t="n">
-        <v>8.275356292724609</v>
+        <v>8.275355339050293</v>
       </c>
       <c r="C260" t="n">
-        <v>8.355988588431988</v>
+        <v>8.355987625465389</v>
       </c>
       <c r="D260" t="n">
-        <v>8.245584340664582</v>
+        <v>8.245583390421267</v>
       </c>
       <c r="E260" t="n">
-        <v>8.35474846270546</v>
+        <v>8.354747499881778</v>
       </c>
       <c r="F260" t="n">
         <v>4665068</v>
@@ -5632,16 +5632,16 @@
         <v>44126</v>
       </c>
       <c r="B261" t="n">
-        <v>8.267912864685059</v>
+        <v>8.267911911010742</v>
       </c>
       <c r="C261" t="n">
-        <v>8.337381348523031</v>
+        <v>8.337380386835774</v>
       </c>
       <c r="D261" t="n">
-        <v>8.168674215687588</v>
+        <v>8.168673273460097</v>
       </c>
       <c r="E261" t="n">
-        <v>8.306368377248981</v>
+        <v>8.30636741913896</v>
       </c>
       <c r="F261" t="n">
         <v>7908034</v>
@@ -5652,16 +5652,16 @@
         <v>44127</v>
       </c>
       <c r="B262" t="n">
-        <v>8.234420776367188</v>
+        <v>8.234419822692871</v>
       </c>
       <c r="C262" t="n">
-        <v>8.312571929509362</v>
+        <v>8.312570966783923</v>
       </c>
       <c r="D262" t="n">
-        <v>8.203407804185662</v>
+        <v>8.203406854103131</v>
       </c>
       <c r="E262" t="n">
-        <v>8.269153232377807</v>
+        <v>8.269152274680931</v>
       </c>
       <c r="F262" t="n">
         <v>5098571</v>
@@ -5712,16 +5712,16 @@
         <v>44132</v>
       </c>
       <c r="B265" t="n">
-        <v>7.825055122375488</v>
+        <v>7.825055599212646</v>
       </c>
       <c r="C265" t="n">
-        <v>8.088040380288025</v>
+        <v>8.088040873150774</v>
       </c>
       <c r="D265" t="n">
-        <v>7.81761168821794</v>
+        <v>7.817612164601516</v>
       </c>
       <c r="E265" t="n">
-        <v>8.078115801411293</v>
+        <v>8.078116293669268</v>
       </c>
       <c r="F265" t="n">
         <v>12369944</v>
@@ -5752,16 +5752,16 @@
         <v>44134</v>
       </c>
       <c r="B267" t="n">
-        <v>7.684879302978516</v>
+        <v>7.684878826141357</v>
       </c>
       <c r="C267" t="n">
-        <v>7.777916426914608</v>
+        <v>7.777915944304612</v>
       </c>
       <c r="D267" t="n">
-        <v>7.574475058635726</v>
+        <v>7.574474588649013</v>
       </c>
       <c r="E267" t="n">
-        <v>7.759309180819852</v>
+        <v>7.759308699364413</v>
       </c>
       <c r="F267" t="n">
         <v>16269207</v>
@@ -5772,16 +5772,16 @@
         <v>44138</v>
       </c>
       <c r="B268" t="n">
-        <v>7.7171311378479</v>
+        <v>7.717131614685059</v>
       </c>
       <c r="C268" t="n">
-        <v>7.852345930671059</v>
+        <v>7.852346415863062</v>
       </c>
       <c r="D268" t="n">
-        <v>7.622853892715106</v>
+        <v>7.622854363726927</v>
       </c>
       <c r="E268" t="n">
-        <v>7.821333855323877</v>
+        <v>7.821334338599661</v>
       </c>
       <c r="F268" t="n">
         <v>9901091</v>
@@ -5812,16 +5812,16 @@
         <v>44140</v>
       </c>
       <c r="B270" t="n">
-        <v>8.119052886962891</v>
+        <v>8.119053840637207</v>
       </c>
       <c r="C270" t="n">
-        <v>8.177355763964984</v>
+        <v>8.177356724487632</v>
       </c>
       <c r="D270" t="n">
-        <v>8.007407635190189</v>
+        <v>8.007408575750512</v>
       </c>
       <c r="E270" t="n">
-        <v>8.039660727779241</v>
+        <v>8.039661672128053</v>
       </c>
       <c r="F270" t="n">
         <v>9820281</v>
@@ -5892,16 +5892,16 @@
         <v>44146</v>
       </c>
       <c r="B274" t="n">
-        <v>8.193482398986816</v>
+        <v>8.193483352661133</v>
       </c>
       <c r="C274" t="n">
-        <v>8.420493294041393</v>
+        <v>8.420494274138473</v>
       </c>
       <c r="D274" t="n">
-        <v>8.193482398986816</v>
+        <v>8.193483352661133</v>
       </c>
       <c r="E274" t="n">
-        <v>8.312571092276054</v>
+        <v>8.312572059811611</v>
       </c>
       <c r="F274" t="n">
         <v>7246451</v>
@@ -5912,16 +5912,16 @@
         <v>44147</v>
       </c>
       <c r="B275" t="n">
-        <v>8.234420776367188</v>
+        <v>8.234419822692871</v>
       </c>
       <c r="C275" t="n">
-        <v>8.398165624159189</v>
+        <v>8.398164651520666</v>
       </c>
       <c r="D275" t="n">
-        <v>8.13145906678732</v>
+        <v>8.131458125037573</v>
       </c>
       <c r="E275" t="n">
-        <v>8.193483224225638</v>
+        <v>8.193482275292528</v>
       </c>
       <c r="F275" t="n">
         <v>11697033</v>
@@ -5932,16 +5932,16 @@
         <v>44148</v>
       </c>
       <c r="B276" t="n">
-        <v>8.633859634399414</v>
+        <v>8.633858680725098</v>
       </c>
       <c r="C276" t="n">
-        <v>8.646265358676397</v>
+        <v>8.646264403631776</v>
       </c>
       <c r="D276" t="n">
-        <v>8.267912658055211</v>
+        <v>8.267911744802472</v>
       </c>
       <c r="E276" t="n">
-        <v>8.322494271024663</v>
+        <v>8.322493351742979</v>
       </c>
       <c r="F276" t="n">
         <v>10854949</v>
@@ -5992,16 +5992,16 @@
         <v>44153</v>
       </c>
       <c r="B279" t="n">
-        <v>8.584240913391113</v>
+        <v>8.584239959716797</v>
       </c>
       <c r="C279" t="n">
-        <v>8.645024946032365</v>
+        <v>8.64502398560519</v>
       </c>
       <c r="D279" t="n">
-        <v>8.516013445661457</v>
+        <v>8.516012499566937</v>
       </c>
       <c r="E279" t="n">
-        <v>8.558190230775271</v>
+        <v>8.55818927999508</v>
       </c>
       <c r="F279" t="n">
         <v>8922310</v>
@@ -6072,16 +6072,16 @@
         <v>44160</v>
       </c>
       <c r="B283" t="n">
-        <v>8.739302635192871</v>
+        <v>8.739301681518555</v>
       </c>
       <c r="C283" t="n">
-        <v>8.920414597775554</v>
+        <v>8.920413624337439</v>
       </c>
       <c r="D283" t="n">
-        <v>8.616492663682914</v>
+        <v>8.616491723410208</v>
       </c>
       <c r="E283" t="n">
-        <v>8.85466827854489</v>
+        <v>8.854667312281327</v>
       </c>
       <c r="F283" t="n">
         <v>6633202</v>
@@ -6112,16 +6112,16 @@
         <v>44162</v>
       </c>
       <c r="B285" t="n">
-        <v>8.615252494812012</v>
+        <v>8.615251541137695</v>
       </c>
       <c r="C285" t="n">
-        <v>8.708288727073548</v>
+        <v>8.70828776310049</v>
       </c>
       <c r="D285" t="n">
-        <v>8.507329393233835</v>
+        <v>8.507328451506179</v>
       </c>
       <c r="E285" t="n">
-        <v>8.566872403188754</v>
+        <v>8.566871454869922</v>
       </c>
       <c r="F285" t="n">
         <v>5230736</v>
@@ -6152,16 +6152,16 @@
         <v>44166</v>
       </c>
       <c r="B287" t="n">
-        <v>8.414292335510254</v>
+        <v>8.414291381835938</v>
       </c>
       <c r="C287" t="n">
-        <v>8.672315323428652</v>
+        <v>8.672314340510058</v>
       </c>
       <c r="D287" t="n">
-        <v>8.360949953683695</v>
+        <v>8.360949006055193</v>
       </c>
       <c r="E287" t="n">
-        <v>8.636340955945199</v>
+        <v>8.636339977103933</v>
       </c>
       <c r="F287" t="n">
         <v>16096259</v>
@@ -6172,16 +6172,16 @@
         <v>44167</v>
       </c>
       <c r="B288" t="n">
-        <v>8.282798767089844</v>
+        <v>8.282797813415527</v>
       </c>
       <c r="C288" t="n">
-        <v>8.4614304780068</v>
+        <v>8.461429503764982</v>
       </c>
       <c r="D288" t="n">
-        <v>8.199686220600897</v>
+        <v>8.199685276496087</v>
       </c>
       <c r="E288" t="n">
-        <v>8.456469081678438</v>
+        <v>8.456468108007872</v>
       </c>
       <c r="F288" t="n">
         <v>15329699</v>
@@ -6212,16 +6212,16 @@
         <v>44169</v>
       </c>
       <c r="B290" t="n">
-        <v>8.772794723510742</v>
+        <v>8.772793769836426</v>
       </c>
       <c r="C290" t="n">
-        <v>8.948945284925747</v>
+        <v>8.948944312102428</v>
       </c>
       <c r="D290" t="n">
-        <v>8.683479763850318</v>
+        <v>8.683478819885265</v>
       </c>
       <c r="E290" t="n">
-        <v>8.886920238013465</v>
+        <v>8.886919271932774</v>
       </c>
       <c r="F290" t="n">
         <v>10446369</v>
@@ -6232,16 +6232,16 @@
         <v>44172</v>
       </c>
       <c r="B291" t="n">
-        <v>8.647504806518555</v>
+        <v>8.647505760192871</v>
       </c>
       <c r="C291" t="n">
-        <v>8.827376626156168</v>
+        <v>8.82737759966732</v>
       </c>
       <c r="D291" t="n">
-        <v>8.621454127772409</v>
+        <v>8.621455078573774</v>
       </c>
       <c r="E291" t="n">
-        <v>8.807528362331166</v>
+        <v>8.807529333653388</v>
       </c>
       <c r="F291" t="n">
         <v>10174485</v>
@@ -6392,16 +6392,16 @@
         <v>44182</v>
       </c>
       <c r="B299" t="n">
-        <v>9.125097274780273</v>
+        <v>9.125096321105957</v>
       </c>
       <c r="C299" t="n">
-        <v>9.233020380265208</v>
+        <v>9.233019415311725</v>
       </c>
       <c r="D299" t="n">
-        <v>9.105249008435251</v>
+        <v>9.1052480568353</v>
       </c>
       <c r="E299" t="n">
-        <v>9.230539235289285</v>
+        <v>9.230538270595108</v>
       </c>
       <c r="F299" t="n">
         <v>5262456</v>
@@ -6452,16 +6452,16 @@
         <v>44187</v>
       </c>
       <c r="B302" t="n">
-        <v>9.018414497375488</v>
+        <v>9.018413543701172</v>
       </c>
       <c r="C302" t="n">
-        <v>9.117654044402261</v>
+        <v>9.117653080233614</v>
       </c>
       <c r="D302" t="n">
-        <v>8.941504362170608</v>
+        <v>8.941503416629342</v>
       </c>
       <c r="E302" t="n">
-        <v>8.974996692978687</v>
+        <v>8.974995743895692</v>
       </c>
       <c r="F302" t="n">
         <v>3700636</v>
@@ -6572,16 +6572,16 @@
         <v>44201</v>
       </c>
       <c r="B308" t="n">
-        <v>9.097805976867676</v>
+        <v>9.097805023193359</v>
       </c>
       <c r="C308" t="n">
-        <v>9.304968615993069</v>
+        <v>9.304967640603</v>
       </c>
       <c r="D308" t="n">
-        <v>9.012211393852336</v>
+        <v>9.012210449150441</v>
       </c>
       <c r="E308" t="n">
-        <v>9.304968615993069</v>
+        <v>9.304967640603</v>
       </c>
       <c r="F308" t="n">
         <v>8306796</v>
@@ -6592,16 +6592,16 @@
         <v>44202</v>
       </c>
       <c r="B309" t="n">
-        <v>9.023375511169434</v>
+        <v>9.02337646484375</v>
       </c>
       <c r="C309" t="n">
-        <v>9.178437672356514</v>
+        <v>9.178438642419241</v>
       </c>
       <c r="D309" t="n">
-        <v>8.883199324604012</v>
+        <v>8.883200263463204</v>
       </c>
       <c r="E309" t="n">
-        <v>9.091602075844966</v>
+        <v>9.091603036730099</v>
       </c>
       <c r="F309" t="n">
         <v>6995714</v>
@@ -6632,16 +6632,16 @@
         <v>44204</v>
       </c>
       <c r="B311" t="n">
-        <v>9.49476432800293</v>
+        <v>9.494765281677246</v>
       </c>
       <c r="C311" t="n">
-        <v>9.533219836566508</v>
+        <v>9.533220794103377</v>
       </c>
       <c r="D311" t="n">
-        <v>9.077957042182957</v>
+        <v>9.077957953992263</v>
       </c>
       <c r="E311" t="n">
-        <v>9.178437593380119</v>
+        <v>9.178438515281906</v>
       </c>
       <c r="F311" t="n">
         <v>10280973</v>
@@ -6732,16 +6732,16 @@
         <v>44211</v>
       </c>
       <c r="B316" t="n">
-        <v>9.479877471923828</v>
+        <v>9.479878425598145</v>
       </c>
       <c r="C316" t="n">
-        <v>9.607648827608905</v>
+        <v>9.607649794137002</v>
       </c>
       <c r="D316" t="n">
-        <v>9.378157688462947</v>
+        <v>9.378158631904267</v>
       </c>
       <c r="E316" t="n">
-        <v>9.589041582834192</v>
+        <v>9.589042547490402</v>
       </c>
       <c r="F316" t="n">
         <v>14334303</v>
@@ -6892,16 +6892,16 @@
         <v>44224</v>
       </c>
       <c r="B324" t="n">
-        <v>9.368233680725098</v>
+        <v>9.368232727050781</v>
       </c>
       <c r="C324" t="n">
-        <v>9.399245757239534</v>
+        <v>9.399244800408228</v>
       </c>
       <c r="D324" t="n">
-        <v>9.102767267989694</v>
+        <v>9.102766341339521</v>
       </c>
       <c r="E324" t="n">
-        <v>9.180918415575915</v>
+        <v>9.180917480970056</v>
       </c>
       <c r="F324" t="n">
         <v>7429217</v>
@@ -6912,16 +6912,16 @@
         <v>44225</v>
       </c>
       <c r="B325" t="n">
-        <v>9.36327075958252</v>
+        <v>9.363271713256836</v>
       </c>
       <c r="C325" t="n">
-        <v>9.571675294860224</v>
+        <v>9.571676269761104</v>
       </c>
       <c r="D325" t="n">
-        <v>9.215652034482874</v>
+        <v>9.215652973121827</v>
       </c>
       <c r="E325" t="n">
-        <v>9.312410421451789</v>
+        <v>9.312411369945844</v>
       </c>
       <c r="F325" t="n">
         <v>11022611</v>
@@ -6952,16 +6952,16 @@
         <v>44229</v>
       </c>
       <c r="B327" t="n">
-        <v>10.133620262146</v>
+        <v>10.13361930847168</v>
       </c>
       <c r="C327" t="n">
-        <v>10.18448060527895</v>
+        <v>10.18447964681817</v>
       </c>
       <c r="D327" t="n">
-        <v>9.832180367414875</v>
+        <v>9.832179442109044</v>
       </c>
       <c r="E327" t="n">
-        <v>10.11005072588166</v>
+        <v>10.11004977442547</v>
       </c>
       <c r="F327" t="n">
         <v>20046878</v>
@@ -6992,16 +6992,16 @@
         <v>44231</v>
       </c>
       <c r="B329" t="n">
-        <v>10.38668155670166</v>
+        <v>10.38668251037598</v>
       </c>
       <c r="C329" t="n">
-        <v>10.38668155670166</v>
+        <v>10.38668251037598</v>
       </c>
       <c r="D329" t="n">
-        <v>10.11749300250636</v>
+        <v>10.11749393146458</v>
       </c>
       <c r="E329" t="n">
-        <v>10.17703779267104</v>
+        <v>10.17703872709649</v>
       </c>
       <c r="F329" t="n">
         <v>12166787</v>
@@ -7012,16 +7012,16 @@
         <v>44232</v>
       </c>
       <c r="B330" t="n">
-        <v>10.5566291809082</v>
+        <v>10.55663013458252</v>
       </c>
       <c r="C330" t="n">
-        <v>10.58143973441847</v>
+        <v>10.58144069033415</v>
       </c>
       <c r="D330" t="n">
-        <v>10.32465689384235</v>
+        <v>10.32465782656054</v>
       </c>
       <c r="E330" t="n">
-        <v>10.41893413810214</v>
+        <v>10.41893507933724</v>
       </c>
       <c r="F330" t="n">
         <v>10745440</v>
@@ -7192,16 +7192,16 @@
         <v>44249</v>
       </c>
       <c r="B339" t="n">
-        <v>11.09376621246338</v>
+        <v>11.09376525878906</v>
       </c>
       <c r="C339" t="n">
-        <v>11.20292944052197</v>
+        <v>11.20292847746345</v>
       </c>
       <c r="D339" t="n">
-        <v>10.63602222835513</v>
+        <v>10.63602131403072</v>
       </c>
       <c r="E339" t="n">
-        <v>10.93994416306512</v>
+        <v>10.9399432226141</v>
       </c>
       <c r="F339" t="n">
         <v>14982292</v>
@@ -7292,16 +7292,16 @@
         <v>44256</v>
       </c>
       <c r="B344" t="n">
-        <v>21.85701560974121</v>
+        <v>21.85701751708984</v>
       </c>
       <c r="C344" t="n">
-        <v>23.99306407785948</v>
+        <v>23.99306617161</v>
       </c>
       <c r="D344" t="n">
-        <v>16.3107860983666</v>
+        <v>16.31078752172449</v>
       </c>
       <c r="E344" t="n">
-        <v>16.8635354591482</v>
+        <v>16.86353693074166</v>
       </c>
       <c r="F344" t="n">
         <v>49361500</v>
@@ -7312,16 +7312,16 @@
         <v>44257</v>
       </c>
       <c r="B345" t="n">
-        <v>21.19184303283691</v>
+        <v>21.19184494018555</v>
       </c>
       <c r="C345" t="n">
-        <v>22.95314478521037</v>
+        <v>22.95314685108304</v>
       </c>
       <c r="D345" t="n">
-        <v>20.6953049717416</v>
+        <v>20.69530683439987</v>
       </c>
       <c r="E345" t="n">
-        <v>22.18491736810308</v>
+        <v>22.18491936483229</v>
       </c>
       <c r="F345" t="n">
         <v>20095700</v>
@@ -7352,16 +7352,16 @@
         <v>44259</v>
       </c>
       <c r="B347" t="n">
-        <v>20.86394119262695</v>
+        <v>20.86394309997559</v>
       </c>
       <c r="C347" t="n">
-        <v>21.52911312081577</v>
+        <v>21.52911508897337</v>
       </c>
       <c r="D347" t="n">
-        <v>20.01139593391831</v>
+        <v>20.0113977633286</v>
       </c>
       <c r="E347" t="n">
-        <v>20.2362428583874</v>
+        <v>20.23624470835284</v>
       </c>
       <c r="F347" t="n">
         <v>8984600</v>
@@ -7732,16 +7732,16 @@
         <v>44286</v>
       </c>
       <c r="B366" t="n">
-        <v>31.08511924743652</v>
+        <v>31.08511734008789</v>
       </c>
       <c r="C366" t="n">
-        <v>32.65904960734591</v>
+        <v>32.65904760342265</v>
       </c>
       <c r="D366" t="n">
-        <v>30.82279871206804</v>
+        <v>30.82279682081511</v>
       </c>
       <c r="E366" t="n">
-        <v>31.95640225288098</v>
+        <v>31.95640029207138</v>
       </c>
       <c r="F366" t="n">
         <v>8195900</v>
@@ -7792,16 +7792,16 @@
         <v>44292</v>
       </c>
       <c r="B369" t="n">
-        <v>30.57921028137207</v>
+        <v>30.5792121887207</v>
       </c>
       <c r="C369" t="n">
-        <v>32.19998297677536</v>
+        <v>32.19998498521812</v>
       </c>
       <c r="D369" t="n">
-        <v>30.48552540315069</v>
+        <v>30.48552730465581</v>
       </c>
       <c r="E369" t="n">
-        <v>31.01953707148042</v>
+        <v>31.01953900629401</v>
       </c>
       <c r="F369" t="n">
         <v>6923500</v>
@@ -7812,16 +7812,16 @@
         <v>44293</v>
       </c>
       <c r="B370" t="n">
-        <v>30.95395851135254</v>
+        <v>30.95395660400391</v>
       </c>
       <c r="C370" t="n">
-        <v>31.36617699981515</v>
+        <v>31.36617506706607</v>
       </c>
       <c r="D370" t="n">
-        <v>30.40120912458377</v>
+        <v>30.40120725129495</v>
       </c>
       <c r="E370" t="n">
-        <v>30.72910978883253</v>
+        <v>30.72910789533883</v>
       </c>
       <c r="F370" t="n">
         <v>4745700</v>
@@ -8012,16 +8012,16 @@
         <v>44308</v>
       </c>
       <c r="B380" t="n">
-        <v>36.30344772338867</v>
+        <v>36.30344390869141</v>
       </c>
       <c r="C380" t="n">
-        <v>38.03664315290104</v>
+        <v>38.03663915608288</v>
       </c>
       <c r="D380" t="n">
-        <v>35.88185858344396</v>
+        <v>35.88185481304648</v>
       </c>
       <c r="E380" t="n">
-        <v>37.12788831107506</v>
+        <v>37.12788440974715</v>
       </c>
       <c r="F380" t="n">
         <v>6756200</v>
@@ -8052,16 +8052,16 @@
         <v>44312</v>
       </c>
       <c r="B382" t="n">
-        <v>35.91933059692383</v>
+        <v>35.91933441162109</v>
       </c>
       <c r="C382" t="n">
-        <v>36.30344431641451</v>
+        <v>36.30344817190534</v>
       </c>
       <c r="D382" t="n">
-        <v>35.5164791869886</v>
+        <v>35.51648295890232</v>
       </c>
       <c r="E382" t="n">
-        <v>35.88185521603473</v>
+        <v>35.88185902675205</v>
       </c>
       <c r="F382" t="n">
         <v>4241900</v>
@@ -8072,16 +8072,16 @@
         <v>44313</v>
       </c>
       <c r="B383" t="n">
-        <v>35.46963882446289</v>
+        <v>35.46963500976562</v>
       </c>
       <c r="C383" t="n">
-        <v>36.29407938304689</v>
+        <v>36.2940754796825</v>
       </c>
       <c r="D383" t="n">
-        <v>35.27289842405</v>
+        <v>35.27289463051181</v>
       </c>
       <c r="E383" t="n">
-        <v>36.05986359955081</v>
+        <v>36.05985972137591</v>
       </c>
       <c r="F383" t="n">
         <v>2386900</v>
@@ -35472,19 +35472,39 @@
         <v>46316</v>
       </c>
       <c r="B1753" t="n">
-        <v>3.04</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="C1753" t="n">
-        <v>3.21</v>
+        <v>3.210000038146973</v>
       </c>
       <c r="D1753" t="n">
         <v>3</v>
       </c>
       <c r="E1753" t="n">
-        <v>3.14</v>
+        <v>3.140000104904175</v>
       </c>
       <c r="F1753" t="n">
         <v>6570300</v>
+      </c>
+    </row>
+    <row r="1754">
+      <c r="A1754" s="1" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B1754" t="n">
+        <v>3</v>
+      </c>
+      <c r="C1754" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="D1754" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="E1754" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="F1754" t="n">
+        <v>5206800</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1754"/>
+  <dimension ref="A1:F1755"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906202316284</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173951148987</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853133082389832</v>
+        <v>1.853132605552673</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195169448853</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500007629395</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500007629395</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500007629395</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500007629395</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156946182251</v>
+        <v>2.180156469345093</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359247207642</v>
+        <v>2.152359008789062</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212370872498</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800049</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951084613800048</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997223854064941</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997223854064942</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997223854064942</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997222423553467</v>
+        <v>6.997223854064942</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833183288574</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="C46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="D46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="E46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="C47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="D47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="E47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370965957641602</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363670349121</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="C57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="D57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="E57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733024597168</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142322540283</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156007766723633</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="C64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="D64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="E64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27652168273926</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27652168273926</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27652168273926</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27652168273926</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610103607178</v>
+        <v>10.60610008239746</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448453125444</v>
+        <v>11.08448353456507</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087005615234375</v>
+        <v>8.087006568908691</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167514235155968</v>
+        <v>8.167515198324406</v>
       </c>
       <c r="D103" t="n">
-        <v>7.934155965259957</v>
+        <v>7.93415690090921</v>
       </c>
       <c r="E103" t="n">
-        <v>7.99249553273396</v>
+        <v>7.992496475263009</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174576363958773</v>
+        <v>7.174577261989849</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269086440314109</v>
+        <v>7.269087350174872</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151270575596</v>
+        <v>7.885151755156881</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395100920432114</v>
+        <v>7.395101374897398</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642458915710449</v>
+        <v>7.642459392547607</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934155910701143</v>
+        <v>7.934156405738198</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650689636966175</v>
+        <v>6.650690051923714</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251216760168</v>
+        <v>7.242251668627103</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255058288574</v>
+        <v>7.277255535125732</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292230712304</v>
+        <v>7.641292731402749</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086097777741</v>
+        <v>6.70086141684674</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766201694169458</v>
+        <v>6.766202137520195</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2652,16 +2652,16 @@
         <v>43909</v>
       </c>
       <c r="B112" t="n">
-        <v>7.521113395690918</v>
+        <v>7.521113872528076</v>
       </c>
       <c r="C112" t="n">
-        <v>8.106841959390016</v>
+        <v>8.106842473362253</v>
       </c>
       <c r="D112" t="n">
-        <v>6.356659520848136</v>
+        <v>6.35665992385914</v>
       </c>
       <c r="E112" t="n">
-        <v>6.779036703963478</v>
+        <v>6.779037133753115</v>
       </c>
       <c r="F112" t="n">
         <v>19250108</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314098358154</v>
+        <v>7.844314575195312</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109174606594431</v>
+        <v>8.109175099531829</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235250900954319</v>
+        <v>7.235251340767977</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146197500977</v>
+        <v>7.829146673416115</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738137245178223</v>
+        <v>7.738136291503906</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145346146541403</v>
+        <v>8.145345142681279</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298979071039</v>
+        <v>7.690298031292473</v>
       </c>
       <c r="E117" t="n">
-        <v>8.13834499423681</v>
+        <v>8.138343991239532</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775676727295</v>
+        <v>7.469774723052979</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304804343318</v>
+        <v>7.746303815364229</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351930089923889</v>
+        <v>7.351929151295045</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113786687701</v>
+        <v>7.51411282735269</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2792,16 +2792,16 @@
         <v>43920</v>
       </c>
       <c r="B119" t="n">
-        <v>7.584119319915771</v>
+        <v>7.58411979675293</v>
       </c>
       <c r="C119" t="n">
-        <v>7.677462963028194</v>
+        <v>7.677463445734158</v>
       </c>
       <c r="D119" t="n">
-        <v>7.322759808396101</v>
+        <v>7.322760268800774</v>
       </c>
       <c r="E119" t="n">
-        <v>7.354262888769144</v>
+        <v>7.354263351154514</v>
       </c>
       <c r="F119" t="n">
         <v>7283457</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469455718994</v>
+        <v>7.740469932556152</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757971914786575</v>
+        <v>7.757972392701939</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582953929901123</v>
+        <v>7.582952976226807</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840815002303775</v>
+        <v>7.840814016199421</v>
       </c>
       <c r="D122" t="n">
-        <v>7.381100395706687</v>
+        <v>7.38109946741859</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455774312072345</v>
+        <v>7.455773374392843</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261459350586</v>
+        <v>7.340261936187744</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624426344595</v>
+        <v>7.622624921524582</v>
       </c>
       <c r="D123" t="n">
-        <v>7.21541557567713</v>
+        <v>7.215416044404066</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457147585694</v>
+        <v>7.621457642689852</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613289833068848</v>
+        <v>7.613289356231689</v>
       </c>
       <c r="C124" t="n">
-        <v>7.699632328290281</v>
+        <v>7.699631846045301</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497777973422238</v>
+        <v>7.497777503819842</v>
       </c>
       <c r="E124" t="n">
-        <v>7.584119628270164</v>
+        <v>7.58411915326</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672797679901123</v>
+        <v>7.672796726226807</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109175966524298</v>
+        <v>8.109174958611256</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661129932612202</v>
+        <v>7.661128980388104</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840815257758265</v>
+        <v>7.840814283200555</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798511505127</v>
+        <v>7.700798988342285</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307131173381</v>
+        <v>7.781307612995673</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430533892927</v>
+        <v>7.362430989778177</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629459127295</v>
+        <v>7.678629934591736</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500110626220703</v>
+        <v>7.500111103057861</v>
       </c>
       <c r="C129" t="n">
-        <v>7.750970514277116</v>
+        <v>7.75097100706328</v>
       </c>
       <c r="D129" t="n">
-        <v>7.455773361693658</v>
+        <v>7.45577383571197</v>
       </c>
       <c r="E129" t="n">
-        <v>7.49427759388343</v>
+        <v>7.494278070349739</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265598297119</v>
+        <v>7.375265121459961</v>
       </c>
       <c r="C130" t="n">
-        <v>7.494278464239883</v>
+        <v>7.49427797970812</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762513925697</v>
+        <v>7.343762039125325</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935961570344</v>
+        <v>7.407935482620931</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566619396209717</v>
+        <v>7.566618919372559</v>
       </c>
       <c r="C131" t="n">
-        <v>7.5887884509226</v>
+        <v>7.58878797268838</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234084415890043</v>
+        <v>7.234083960008746</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444106376032958</v>
+        <v>7.444105906916389</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3072,16 +3072,16 @@
         <v>43941</v>
       </c>
       <c r="B133" t="n">
-        <v>7.584119319915771</v>
+        <v>7.58411979675293</v>
       </c>
       <c r="C133" t="n">
-        <v>7.592287750070918</v>
+        <v>7.592288227421651</v>
       </c>
       <c r="D133" t="n">
-        <v>7.316925095374786</v>
+        <v>7.316925555412612</v>
       </c>
       <c r="E133" t="n">
-        <v>7.350762733255134</v>
+        <v>7.350763195420438</v>
       </c>
       <c r="F133" t="n">
         <v>10524157</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251522064208984</v>
+        <v>8.251523017883301</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431207358265677</v>
+        <v>8.431208332707222</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852482318878174</v>
+        <v>7.852481842041016</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764498666425</v>
+        <v>7.357764051870702</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484550476074</v>
+        <v>7.887484073638916</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826736101882</v>
+        <v>7.966826254468098</v>
       </c>
       <c r="D139" t="n">
-        <v>7.700798933367937</v>
+        <v>7.70079846781684</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980845212174</v>
+        <v>7.841980371125938</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726467609405518</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817898699254</v>
+        <v>7.882817412213003</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726467609405518</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311578781807</v>
+        <v>7.816311096399979</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -35495,16 +35495,36 @@
         <v>3</v>
       </c>
       <c r="C1754" t="n">
-        <v>3.04</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="D1754" t="n">
-        <v>2.86</v>
+        <v>2.859999895095825</v>
       </c>
       <c r="E1754" t="n">
-        <v>3.04</v>
+        <v>3.039999961853027</v>
       </c>
       <c r="F1754" t="n">
         <v>5206800</v>
+      </c>
+    </row>
+    <row r="1755">
+      <c r="A1755" s="1" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B1755" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="C1755" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="D1755" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="E1755" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="F1755" t="n">
+        <v>6084100</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1755"/>
+  <dimension ref="A1:F1756"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553905963897705</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553905963897705</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553905963897705</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553905963897705</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132605552673</v>
+        <v>1.853132724761963</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725196123123169</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.279499530792236</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461867332458</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461867332458</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461867332458</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461867332458</v>
+        <v>1.922461152076721</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="C39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="D39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="E39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212370872498</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647354125976562</v>
+        <v>4.647354602813721</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951084613800049</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951084613800048</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833183288574</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370965957641602</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370965957641602</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.075627326965332</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075626850128174</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296540260314941</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296540260314941</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296540260314941</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296540260314941</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589144229888916</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589144229888916</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589144229888916</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589144229888916</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156007766723633</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="C64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="D64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="E64" t="n">
-        <v>9.01476001739502</v>
+        <v>9.014760971069336</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116329193115</v>
+        <v>11.20116138458252</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643836975098</v>
+        <v>10.63643741607666</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610008239746</v>
+        <v>10.60610103607178</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448353456507</v>
+        <v>11.08448453125444</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917695528703431</v>
+        <v>9.917696420478112</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444747924805</v>
+        <v>10.73444843292236</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087006568908691</v>
+        <v>8.087005615234375</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167515198324406</v>
+        <v>8.167514235155968</v>
       </c>
       <c r="D103" t="n">
-        <v>7.93415690090921</v>
+        <v>7.934155965259957</v>
       </c>
       <c r="E103" t="n">
-        <v>7.992496475263009</v>
+        <v>7.99249553273396</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619123935699463</v>
+        <v>7.619122982025146</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174577261989849</v>
+        <v>7.174576363958773</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269087350174872</v>
+        <v>7.269086440314109</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151755156881</v>
+        <v>7.885151270575596</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395101374897398</v>
+        <v>7.395100920432114</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138584136963</v>
+        <v>7.759138107299805</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642459392547607</v>
+        <v>7.642458915710449</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934156405738198</v>
+        <v>7.934155910701143</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650690051923714</v>
+        <v>6.650689636966175</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251668627103</v>
+        <v>7.242251216760168</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255535125732</v>
+        <v>7.277255058288574</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292731402749</v>
+        <v>7.641292230712304</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086141684674</v>
+        <v>6.70086097777741</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766202137520195</v>
+        <v>6.766201694169458</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2652,16 +2652,16 @@
         <v>43909</v>
       </c>
       <c r="B112" t="n">
-        <v>7.521113872528076</v>
+        <v>7.521113395690918</v>
       </c>
       <c r="C112" t="n">
-        <v>8.106842473362253</v>
+        <v>8.106841959390016</v>
       </c>
       <c r="D112" t="n">
-        <v>6.35665992385914</v>
+        <v>6.356659520848136</v>
       </c>
       <c r="E112" t="n">
-        <v>6.779037133753115</v>
+        <v>6.779036703963478</v>
       </c>
       <c r="F112" t="n">
         <v>19250108</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314575195312</v>
+        <v>7.844314098358154</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109175099531829</v>
+        <v>8.109174606594431</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235251340767977</v>
+        <v>7.235250900954319</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146673416115</v>
+        <v>7.829146197500977</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738136291503906</v>
+        <v>7.738137245178223</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145345142681279</v>
+        <v>8.145346146541403</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298031292473</v>
+        <v>7.690298979071039</v>
       </c>
       <c r="E117" t="n">
-        <v>8.138343991239532</v>
+        <v>8.13834499423681</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469774723052979</v>
+        <v>7.469775676727295</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746303815364229</v>
+        <v>7.746304804343318</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351929151295045</v>
+        <v>7.351930089923889</v>
       </c>
       <c r="E118" t="n">
-        <v>7.51411282735269</v>
+        <v>7.514113786687701</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2792,16 +2792,16 @@
         <v>43920</v>
       </c>
       <c r="B119" t="n">
-        <v>7.58411979675293</v>
+        <v>7.584119319915771</v>
       </c>
       <c r="C119" t="n">
-        <v>7.677463445734158</v>
+        <v>7.677462963028194</v>
       </c>
       <c r="D119" t="n">
-        <v>7.322760268800774</v>
+        <v>7.322759808396101</v>
       </c>
       <c r="E119" t="n">
-        <v>7.354263351154514</v>
+        <v>7.354262888769144</v>
       </c>
       <c r="F119" t="n">
         <v>7283457</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469932556152</v>
+        <v>7.740469455718994</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757972392701939</v>
+        <v>7.757971914786575</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452273064071203</v>
+        <v>7.452272604987874</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582952976226807</v>
+        <v>7.582953929901123</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840814016199421</v>
+        <v>7.840815002303775</v>
       </c>
       <c r="D122" t="n">
-        <v>7.38109946741859</v>
+        <v>7.381100395706687</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455773374392843</v>
+        <v>7.455774312072345</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261936187744</v>
+        <v>7.340261459350586</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624921524582</v>
+        <v>7.622624426344595</v>
       </c>
       <c r="D123" t="n">
-        <v>7.215416044404066</v>
+        <v>7.21541557567713</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457642689852</v>
+        <v>7.621457147585694</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613289356231689</v>
+        <v>7.613289833068848</v>
       </c>
       <c r="C124" t="n">
-        <v>7.699631846045301</v>
+        <v>7.699632328290281</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497777503819842</v>
+        <v>7.497777973422238</v>
       </c>
       <c r="E124" t="n">
-        <v>7.58411915326</v>
+        <v>7.584119628270164</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672796726226807</v>
+        <v>7.672797679901123</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109174958611256</v>
+        <v>8.109175966524298</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661128980388104</v>
+        <v>7.661129932612202</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840814283200555</v>
+        <v>7.840815257758265</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798988342285</v>
+        <v>7.700798511505127</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307612995673</v>
+        <v>7.781307131173381</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430989778177</v>
+        <v>7.362430533892927</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629934591736</v>
+        <v>7.678629459127295</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500111103057861</v>
+        <v>7.500110626220703</v>
       </c>
       <c r="C129" t="n">
-        <v>7.75097100706328</v>
+        <v>7.750970514277116</v>
       </c>
       <c r="D129" t="n">
-        <v>7.45577383571197</v>
+        <v>7.455773361693658</v>
       </c>
       <c r="E129" t="n">
-        <v>7.494278070349739</v>
+        <v>7.49427759388343</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265121459961</v>
+        <v>7.375265598297119</v>
       </c>
       <c r="C130" t="n">
-        <v>7.49427797970812</v>
+        <v>7.494278464239883</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762039125325</v>
+        <v>7.343762513925697</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935482620931</v>
+        <v>7.407935961570344</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566618919372559</v>
+        <v>7.566619396209717</v>
       </c>
       <c r="C131" t="n">
-        <v>7.58878797268838</v>
+        <v>7.5887884509226</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234083960008746</v>
+        <v>7.234084415890043</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444105906916389</v>
+        <v>7.444106376032958</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3072,16 +3072,16 @@
         <v>43941</v>
       </c>
       <c r="B133" t="n">
-        <v>7.58411979675293</v>
+        <v>7.584119319915771</v>
       </c>
       <c r="C133" t="n">
-        <v>7.592288227421651</v>
+        <v>7.592287750070918</v>
       </c>
       <c r="D133" t="n">
-        <v>7.316925555412612</v>
+        <v>7.316925095374786</v>
       </c>
       <c r="E133" t="n">
-        <v>7.350763195420438</v>
+        <v>7.350762733255134</v>
       </c>
       <c r="F133" t="n">
         <v>10524157</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251523017883301</v>
+        <v>8.251522064208984</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431208332707222</v>
+        <v>8.431207358265677</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595788766851371</v>
+        <v>7.595787888963902</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852481842041016</v>
+        <v>7.852482318878174</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764051870702</v>
+        <v>7.357764498666425</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002476102599</v>
+        <v>8.052002965055527</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484073638916</v>
+        <v>7.887484550476074</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826254468098</v>
+        <v>7.966826736101882</v>
       </c>
       <c r="D139" t="n">
-        <v>7.70079846781684</v>
+        <v>7.700798933367937</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980371125938</v>
+        <v>7.841980845212174</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726467609405518</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817412213003</v>
+        <v>7.882817898699254</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726467609405518</v>
+        <v>7.726468086242676</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311096399979</v>
+        <v>7.816311578781807</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -35512,19 +35512,39 @@
         <v>46318</v>
       </c>
       <c r="B1755" t="n">
-        <v>3.03</v>
+        <v>3.029999971389771</v>
       </c>
       <c r="C1755" t="n">
-        <v>3.07</v>
+        <v>3.069999933242798</v>
       </c>
       <c r="D1755" t="n">
-        <v>2.92</v>
+        <v>2.920000076293945</v>
       </c>
       <c r="E1755" t="n">
-        <v>3.02</v>
+        <v>3.019999980926514</v>
       </c>
       <c r="F1755" t="n">
         <v>6084100</v>
+      </c>
+    </row>
+    <row r="1756">
+      <c r="A1756" s="1" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B1756" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C1756" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="D1756" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="E1756" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="F1756" t="n">
+        <v>7479700</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1756"/>
+  <dimension ref="A1:F1757"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553905963897705</v>
+        <v>1.553906559944153</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553905963897705</v>
+        <v>1.553906559944153</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553905963897705</v>
+        <v>1.553906559944153</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553905963897705</v>
+        <v>1.553906559944153</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173474311829</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173474311829</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173474311829</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799174070358276</v>
+        <v>1.799173474311829</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132724761963</v>
+        <v>1.853132367134094</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732597351074</v>
+        <v>2.616732835769653</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279499530792236</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156469345093</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652551651001</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486747741699</v>
+        <v>1.75848662853241</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212609291077</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951084136962891</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997223854064941</v>
+        <v>6.997223377227783</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997223377227783</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997223377227783</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997223377227783</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958799362183</v>
+        <v>3.926958322525024</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489363193511963</v>
+        <v>4.489362716674805</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543453216553</v>
+        <v>10.73543357849121</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075627326965332</v>
+        <v>7.075629234313965</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.075629234313966</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.075629234313966</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.075629234313966</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045722961426</v>
+        <v>12.56045818328857</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68733024597168</v>
+        <v>12.68733215332031</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296540260314941</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296540260314941</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296540260314941</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296540260314941</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294587135314941</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589144229888916</v>
+        <v>7.5891432762146</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589144229888916</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589144229888916</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589144229888916</v>
+        <v>7.589143276214599</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156006813049316</v>
+        <v>9.156005859375</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -35532,19 +35532,39 @@
         <v>46321</v>
       </c>
       <c r="B1756" t="n">
-        <v>2.3</v>
+        <v>2.299999952316284</v>
       </c>
       <c r="C1756" t="n">
-        <v>2.49</v>
+        <v>2.490000009536743</v>
       </c>
       <c r="D1756" t="n">
-        <v>2.04</v>
+        <v>2.039999961853027</v>
       </c>
       <c r="E1756" t="n">
-        <v>2.49</v>
+        <v>2.490000009536743</v>
       </c>
       <c r="F1756" t="n">
         <v>7479700</v>
+      </c>
+    </row>
+    <row r="1757">
+      <c r="A1757" s="1" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B1757" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="C1757" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="D1757" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="E1757" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="F1757" t="n">
+        <v>10043900</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1757"/>
+  <dimension ref="A1:F1758"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906559944153</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906559944153</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906559944153</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906559944153</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173474311829</v>
+        <v>1.799174308776855</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173474311829</v>
+        <v>1.799174308776855</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173474311829</v>
+        <v>1.799174308776855</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173474311829</v>
+        <v>1.799174308776855</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132367134094</v>
+        <v>1.853132486343384</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616732835769653</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725196123123169</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.27950119972229</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.27950119972229</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.27950119972229</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500484466553</v>
+        <v>3.27950119972229</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652551651001</v>
+        <v>2.125652313232422</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.92246150970459</v>
       </c>
       <c r="C38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.92246150970459</v>
       </c>
       <c r="D38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.92246150970459</v>
       </c>
       <c r="E38" t="n">
-        <v>1.922461152076721</v>
+        <v>1.92246150970459</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="C39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="D39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="E39" t="n">
-        <v>1.75848662853241</v>
+        <v>1.758486866950989</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212609291077</v>
+        <v>1.838212132453918</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647354602813721</v>
+        <v>4.647353649139404</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926958322525024</v>
+        <v>3.926959276199341</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934017181396</v>
+        <v>4.587934494018555</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295562744140625</v>
+        <v>8.295561790466309</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075629234313965</v>
+        <v>7.075627326965332</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075629234313966</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075629234313966</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075629234313966</v>
+        <v>7.075627326965331</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68733215332031</v>
+        <v>12.687331199646</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296538352966309</v>
+        <v>8.296537399291992</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294587135314941</v>
+        <v>8.294588088989258</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.5891432762146</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589143276214599</v>
+        <v>7.589142799377441</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1652,16 +1652,16 @@
         <v>43396</v>
       </c>
       <c r="B62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="C62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="D62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="E62" t="n">
-        <v>9.156005859375</v>
+        <v>9.156006813049316</v>
       </c>
       <c r="F62" t="n">
         <v>3776</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27651977539062</v>
+        <v>10.27652072906494</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116138458252</v>
+        <v>11.20116233825684</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -1872,16 +1872,16 @@
         <v>43741</v>
       </c>
       <c r="B73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E73" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F73" t="n">
         <v>755</v>
@@ -1892,16 +1892,16 @@
         <v>43747</v>
       </c>
       <c r="B74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E74" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F74" t="n">
         <v>755</v>
@@ -1952,16 +1952,16 @@
         <v>43773</v>
       </c>
       <c r="B77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="E77" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="F77" t="n">
         <v>1510</v>
@@ -2012,16 +2012,16 @@
         <v>43802</v>
       </c>
       <c r="B80" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="C80" t="n">
-        <v>10.49992275238037</v>
+        <v>10.49992179870605</v>
       </c>
       <c r="D80" t="n">
-        <v>9.21762282756219</v>
+        <v>9.217621990355065</v>
       </c>
       <c r="E80" t="n">
-        <v>9.21762282756219</v>
+        <v>9.217621990355065</v>
       </c>
       <c r="F80" t="n">
         <v>1510</v>
@@ -2072,16 +2072,16 @@
         <v>43839</v>
       </c>
       <c r="B83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="C83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="D83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="E83" t="n">
-        <v>10.63643741607666</v>
+        <v>10.63643836975098</v>
       </c>
       <c r="F83" t="n">
         <v>1510</v>
@@ -2092,16 +2092,16 @@
         <v>43840</v>
       </c>
       <c r="B84" t="n">
-        <v>10.60610103607178</v>
+        <v>10.60610008239746</v>
       </c>
       <c r="C84" t="n">
-        <v>11.08448453125444</v>
+        <v>11.08448353456507</v>
       </c>
       <c r="D84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="E84" t="n">
-        <v>9.917696420478112</v>
+        <v>9.917695528703431</v>
       </c>
       <c r="F84" t="n">
         <v>5286</v>
@@ -2172,16 +2172,16 @@
         <v>43850</v>
       </c>
       <c r="B88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="C88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="D88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="E88" t="n">
-        <v>10.73444843292236</v>
+        <v>10.73444747924805</v>
       </c>
       <c r="F88" t="n">
         <v>755</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640079498291</v>
+        <v>10.28640174865723</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2432,16 +2432,16 @@
         <v>43894</v>
       </c>
       <c r="B101" t="n">
-        <v>8.692568778991699</v>
+        <v>8.692569732666016</v>
       </c>
       <c r="C101" t="n">
-        <v>8.80224676394379</v>
+        <v>8.802247729651036</v>
       </c>
       <c r="D101" t="n">
-        <v>8.564221896891393</v>
+        <v>8.564222836484587</v>
       </c>
       <c r="E101" t="n">
-        <v>8.734572326921571</v>
+        <v>8.734573285204156</v>
       </c>
       <c r="F101" t="n">
         <v>7583284</v>
@@ -2492,16 +2492,16 @@
         <v>43899</v>
       </c>
       <c r="B104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="C104" t="n">
-        <v>7.619122982025146</v>
+        <v>7.619123935699463</v>
       </c>
       <c r="D104" t="n">
-        <v>7.174576363958773</v>
+        <v>7.174577261989849</v>
       </c>
       <c r="E104" t="n">
-        <v>7.269086440314109</v>
+        <v>7.269087350174872</v>
       </c>
       <c r="F104" t="n">
         <v>12246842</v>
@@ -2512,16 +2512,16 @@
         <v>43900</v>
       </c>
       <c r="B105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="C105" t="n">
-        <v>7.885151270575596</v>
+        <v>7.885151755156881</v>
       </c>
       <c r="D105" t="n">
-        <v>7.395100920432114</v>
+        <v>7.395101374897398</v>
       </c>
       <c r="E105" t="n">
-        <v>7.759138107299805</v>
+        <v>7.759138584136963</v>
       </c>
       <c r="F105" t="n">
         <v>10993156</v>
@@ -2532,16 +2532,16 @@
         <v>43901</v>
       </c>
       <c r="B106" t="n">
-        <v>7.280755043029785</v>
+        <v>7.280755519866943</v>
       </c>
       <c r="C106" t="n">
-        <v>7.652960679612288</v>
+        <v>7.652961180826241</v>
       </c>
       <c r="D106" t="n">
-        <v>6.825708745737296</v>
+        <v>6.825709192772189</v>
       </c>
       <c r="E106" t="n">
-        <v>7.467442341108447</v>
+        <v>7.467442830172282</v>
       </c>
       <c r="F106" t="n">
         <v>14927915</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198310852051</v>
+        <v>6.731198787689209</v>
       </c>
       <c r="C107" t="n">
-        <v>6.78487002388751</v>
+        <v>6.784870504526766</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975251402972</v>
+        <v>6.183975689474925</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242313978574833</v>
+        <v>6.242314420779493</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2572,16 +2572,16 @@
         <v>43903</v>
       </c>
       <c r="B108" t="n">
-        <v>7.642458915710449</v>
+        <v>7.642459392547607</v>
       </c>
       <c r="C108" t="n">
-        <v>7.934155910701143</v>
+        <v>7.934156405738198</v>
       </c>
       <c r="D108" t="n">
-        <v>6.650689636966175</v>
+        <v>6.650690051923714</v>
       </c>
       <c r="E108" t="n">
-        <v>7.242251216760168</v>
+        <v>7.242251668627103</v>
       </c>
       <c r="F108" t="n">
         <v>14418889</v>
@@ -2592,16 +2592,16 @@
         <v>43906</v>
       </c>
       <c r="B109" t="n">
-        <v>7.277255058288574</v>
+        <v>7.277255535125732</v>
       </c>
       <c r="C109" t="n">
-        <v>7.641292230712304</v>
+        <v>7.641292731402749</v>
       </c>
       <c r="D109" t="n">
-        <v>6.70086097777741</v>
+        <v>6.70086141684674</v>
       </c>
       <c r="E109" t="n">
-        <v>6.766201694169458</v>
+        <v>6.766202137520195</v>
       </c>
       <c r="F109" t="n">
         <v>14140963</v>
@@ -2632,16 +2632,16 @@
         <v>43908</v>
       </c>
       <c r="B111" t="n">
-        <v>6.985558032989502</v>
+        <v>6.98555850982666</v>
       </c>
       <c r="C111" t="n">
-        <v>8.075337993481165</v>
+        <v>8.075338544707167</v>
       </c>
       <c r="D111" t="n">
-        <v>6.710196211513576</v>
+        <v>6.71019666955442</v>
       </c>
       <c r="E111" t="n">
-        <v>7.140740982312391</v>
+        <v>7.140741469742403</v>
       </c>
       <c r="F111" t="n">
         <v>26337960</v>
@@ -2672,16 +2672,16 @@
         <v>43910</v>
       </c>
       <c r="B113" t="n">
-        <v>7.844314098358154</v>
+        <v>7.844314575195312</v>
       </c>
       <c r="C113" t="n">
-        <v>8.109174606594431</v>
+        <v>8.109175099531829</v>
       </c>
       <c r="D113" t="n">
-        <v>7.235250900954319</v>
+        <v>7.235251340767977</v>
       </c>
       <c r="E113" t="n">
-        <v>7.829146197500977</v>
+        <v>7.829146673416115</v>
       </c>
       <c r="F113" t="n">
         <v>18087806</v>
@@ -2692,16 +2692,16 @@
         <v>43913</v>
       </c>
       <c r="B114" t="n">
-        <v>8.386870384216309</v>
+        <v>8.386871337890625</v>
       </c>
       <c r="C114" t="n">
-        <v>8.386870384216309</v>
+        <v>8.386871337890625</v>
       </c>
       <c r="D114" t="n">
-        <v>7.48377644845884</v>
+        <v>7.483777299441991</v>
       </c>
       <c r="E114" t="n">
-        <v>8.050835275027762</v>
+        <v>8.050836190491395</v>
       </c>
       <c r="F114" t="n">
         <v>25091072</v>
@@ -2752,16 +2752,16 @@
         <v>43916</v>
       </c>
       <c r="B117" t="n">
-        <v>7.738137245178223</v>
+        <v>7.738136291503906</v>
       </c>
       <c r="C117" t="n">
-        <v>8.145346146541403</v>
+        <v>8.145345142681279</v>
       </c>
       <c r="D117" t="n">
-        <v>7.690298979071039</v>
+        <v>7.690298031292473</v>
       </c>
       <c r="E117" t="n">
-        <v>8.13834499423681</v>
+        <v>8.138343991239532</v>
       </c>
       <c r="F117" t="n">
         <v>18423129</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775676727295</v>
+        <v>7.469775199890137</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304804343318</v>
+        <v>7.746304309853773</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351930089923889</v>
+        <v>7.351929620609467</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113786687701</v>
+        <v>7.514113307020195</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2852,16 +2852,16 @@
         <v>43923</v>
       </c>
       <c r="B122" t="n">
-        <v>7.582953929901123</v>
+        <v>7.582952976226807</v>
       </c>
       <c r="C122" t="n">
-        <v>7.840815002303775</v>
+        <v>7.840814016199421</v>
       </c>
       <c r="D122" t="n">
-        <v>7.381100395706687</v>
+        <v>7.38109946741859</v>
       </c>
       <c r="E122" t="n">
-        <v>7.455774312072345</v>
+        <v>7.455773374392843</v>
       </c>
       <c r="F122" t="n">
         <v>13357788</v>
@@ -2872,16 +2872,16 @@
         <v>43924</v>
       </c>
       <c r="B123" t="n">
-        <v>7.340261459350586</v>
+        <v>7.340261936187744</v>
       </c>
       <c r="C123" t="n">
-        <v>7.622624426344595</v>
+        <v>7.622624921524582</v>
       </c>
       <c r="D123" t="n">
-        <v>7.21541557567713</v>
+        <v>7.215416044404066</v>
       </c>
       <c r="E123" t="n">
-        <v>7.621457147585694</v>
+        <v>7.621457642689852</v>
       </c>
       <c r="F123" t="n">
         <v>13042101</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672797679901123</v>
+        <v>7.672797203063965</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109175966524298</v>
+        <v>8.109175462567777</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661129932612202</v>
+        <v>7.661129456500152</v>
       </c>
       <c r="E125" t="n">
-        <v>7.840815257758265</v>
+        <v>7.84081477047941</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2952,16 +2952,16 @@
         <v>43930</v>
       </c>
       <c r="B127" t="n">
-        <v>7.38576602935791</v>
+        <v>7.385766506195068</v>
       </c>
       <c r="C127" t="n">
-        <v>7.778973418970338</v>
+        <v>7.778973921193609</v>
       </c>
       <c r="D127" t="n">
-        <v>7.351929231575166</v>
+        <v>7.351929706227764</v>
       </c>
       <c r="E127" t="n">
-        <v>7.778973418970338</v>
+        <v>7.778973921193609</v>
       </c>
       <c r="F127" t="n">
         <v>7590081</v>
@@ -2972,16 +2972,16 @@
         <v>43934</v>
       </c>
       <c r="B128" t="n">
-        <v>7.41493558883667</v>
+        <v>7.414936065673828</v>
       </c>
       <c r="C128" t="n">
-        <v>7.447605949093313</v>
+        <v>7.447606428031426</v>
       </c>
       <c r="D128" t="n">
-        <v>7.229416415322526</v>
+        <v>7.22941688022938</v>
       </c>
       <c r="E128" t="n">
-        <v>7.385766224588598</v>
+        <v>7.385766699549943</v>
       </c>
       <c r="F128" t="n">
         <v>8873976</v>
@@ -2992,16 +2992,16 @@
         <v>43935</v>
       </c>
       <c r="B129" t="n">
-        <v>7.500110626220703</v>
+        <v>7.500111103057861</v>
       </c>
       <c r="C129" t="n">
-        <v>7.750970514277116</v>
+        <v>7.75097100706328</v>
       </c>
       <c r="D129" t="n">
-        <v>7.455773361693658</v>
+        <v>7.45577383571197</v>
       </c>
       <c r="E129" t="n">
-        <v>7.49427759388343</v>
+        <v>7.494278070349739</v>
       </c>
       <c r="F129" t="n">
         <v>16056987</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375265598297119</v>
+        <v>7.375264644622803</v>
       </c>
       <c r="C130" t="n">
-        <v>7.494278464239883</v>
+        <v>7.494277495176356</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343762513925697</v>
+        <v>7.343761564324954</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935961570344</v>
+        <v>7.407935003671517</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3032,16 +3032,16 @@
         <v>43937</v>
       </c>
       <c r="B131" t="n">
-        <v>7.566619396209717</v>
+        <v>7.566618919372559</v>
       </c>
       <c r="C131" t="n">
-        <v>7.5887884509226</v>
+        <v>7.58878797268838</v>
       </c>
       <c r="D131" t="n">
-        <v>7.234084415890043</v>
+        <v>7.234083960008746</v>
       </c>
       <c r="E131" t="n">
-        <v>7.444106376032958</v>
+        <v>7.444105906916389</v>
       </c>
       <c r="F131" t="n">
         <v>11360199</v>
@@ -3092,16 +3092,16 @@
         <v>43943</v>
       </c>
       <c r="B134" t="n">
-        <v>8.251522064208984</v>
+        <v>8.251523017883301</v>
       </c>
       <c r="C134" t="n">
-        <v>8.431207358265677</v>
+        <v>8.431208332707222</v>
       </c>
       <c r="D134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="E134" t="n">
-        <v>7.595787888963902</v>
+        <v>7.595788766851371</v>
       </c>
       <c r="F134" t="n">
         <v>28297787</v>
@@ -3112,16 +3112,16 @@
         <v>43944</v>
       </c>
       <c r="B135" t="n">
-        <v>8.089339256286621</v>
+        <v>8.089340209960938</v>
       </c>
       <c r="C135" t="n">
-        <v>8.57472300766133</v>
+        <v>8.574724018558863</v>
       </c>
       <c r="D135" t="n">
-        <v>7.969159966917957</v>
+        <v>7.969160906424007</v>
       </c>
       <c r="E135" t="n">
-        <v>8.481379364431731</v>
+        <v>8.481380364324728</v>
       </c>
       <c r="F135" t="n">
         <v>13472583</v>
@@ -3132,16 +3132,16 @@
         <v>43945</v>
       </c>
       <c r="B136" t="n">
-        <v>7.852482318878174</v>
+        <v>7.852481842041016</v>
       </c>
       <c r="C136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="D136" t="n">
-        <v>7.357764498666425</v>
+        <v>7.357764051870702</v>
       </c>
       <c r="E136" t="n">
-        <v>8.052002965055527</v>
+        <v>8.052002476102599</v>
       </c>
       <c r="F136" t="n">
         <v>18423884</v>
@@ -3152,16 +3152,16 @@
         <v>43948</v>
       </c>
       <c r="B137" t="n">
-        <v>8.105673789978027</v>
+        <v>8.105674743652344</v>
       </c>
       <c r="C137" t="n">
-        <v>8.16517979671254</v>
+        <v>8.165180757388045</v>
       </c>
       <c r="D137" t="n">
-        <v>7.710133516824237</v>
+        <v>7.710134423961201</v>
       </c>
       <c r="E137" t="n">
-        <v>7.937657076955135</v>
+        <v>7.93765801086142</v>
       </c>
       <c r="F137" t="n">
         <v>12260436</v>
@@ -3172,16 +3172,16 @@
         <v>43949</v>
       </c>
       <c r="B138" t="n">
-        <v>7.822145462036133</v>
+        <v>7.822145938873291</v>
       </c>
       <c r="C138" t="n">
-        <v>8.301695367155927</v>
+        <v>8.301695873226397</v>
       </c>
       <c r="D138" t="n">
-        <v>7.804643843107134</v>
+        <v>7.804644318877395</v>
       </c>
       <c r="E138" t="n">
-        <v>8.167514607953231</v>
+        <v>8.167515105844055</v>
       </c>
       <c r="F138" t="n">
         <v>14579753</v>
@@ -3192,16 +3192,16 @@
         <v>43950</v>
       </c>
       <c r="B139" t="n">
-        <v>7.887484550476074</v>
+        <v>7.887484073638916</v>
       </c>
       <c r="C139" t="n">
-        <v>7.966826736101882</v>
+        <v>7.966826254468098</v>
       </c>
       <c r="D139" t="n">
-        <v>7.700798933367937</v>
+        <v>7.70079846781684</v>
       </c>
       <c r="E139" t="n">
-        <v>7.841980845212174</v>
+        <v>7.841980371125938</v>
       </c>
       <c r="F139" t="n">
         <v>11774822</v>
@@ -3252,16 +3252,16 @@
         <v>43956</v>
       </c>
       <c r="B142" t="n">
-        <v>8.114091873168945</v>
+        <v>8.114090919494629</v>
       </c>
       <c r="C142" t="n">
-        <v>8.645024731663977</v>
+        <v>8.645023715587479</v>
       </c>
       <c r="D142" t="n">
-        <v>8.069433944133035</v>
+        <v>8.069432995707503</v>
       </c>
       <c r="E142" t="n">
-        <v>8.286521173623905</v>
+        <v>8.286520199683441</v>
       </c>
       <c r="F142" t="n">
         <v>11843548</v>
@@ -3272,16 +3272,16 @@
         <v>43957</v>
       </c>
       <c r="B143" t="n">
-        <v>8.048344612121582</v>
+        <v>8.048345565795898</v>
       </c>
       <c r="C143" t="n">
-        <v>8.145103893796581</v>
+        <v>8.145104858936216</v>
       </c>
       <c r="D143" t="n">
-        <v>7.96399105383742</v>
+        <v>7.963991997516411</v>
       </c>
       <c r="E143" t="n">
-        <v>8.145103893796581</v>
+        <v>8.145104858936216</v>
       </c>
       <c r="F143" t="n">
         <v>16545622</v>
@@ -3312,16 +3312,16 @@
         <v>43959</v>
       </c>
       <c r="B145" t="n">
-        <v>8.162470817565918</v>
+        <v>8.162469863891602</v>
       </c>
       <c r="C145" t="n">
-        <v>8.184800228116485</v>
+        <v>8.184799271833279</v>
       </c>
       <c r="D145" t="n">
-        <v>7.947864739756858</v>
+        <v>7.94786381115636</v>
       </c>
       <c r="E145" t="n">
-        <v>8.156268402071278</v>
+        <v>8.15626744912163</v>
       </c>
       <c r="F145" t="n">
         <v>8818844</v>
@@ -3352,16 +3352,16 @@
         <v>43963</v>
       </c>
       <c r="B147" t="n">
-        <v>8.085559844970703</v>
+        <v>8.085558891296387</v>
       </c>
       <c r="C147" t="n">
-        <v>8.276596387736546</v>
+        <v>8.276595411529883</v>
       </c>
       <c r="D147" t="n">
-        <v>8.063230434277379</v>
+        <v>8.063229483236768</v>
       </c>
       <c r="E147" t="n">
-        <v>8.187280531887918</v>
+        <v>8.187279566215866</v>
       </c>
       <c r="F147" t="n">
         <v>9953957</v>
@@ -3372,16 +3372,16 @@
         <v>43964</v>
       </c>
       <c r="B148" t="n">
-        <v>7.926775932312012</v>
+        <v>7.926775455474854</v>
       </c>
       <c r="C148" t="n">
-        <v>8.187280049800203</v>
+        <v>8.187279557292356</v>
       </c>
       <c r="D148" t="n">
-        <v>7.885840170888542</v>
+        <v>7.885839696513885</v>
       </c>
       <c r="E148" t="n">
-        <v>8.187280049800203</v>
+        <v>8.187279557292356</v>
       </c>
       <c r="F148" t="n">
         <v>10179016</v>
@@ -3412,16 +3412,16 @@
         <v>43966</v>
       </c>
       <c r="B150" t="n">
-        <v>6.841341018676758</v>
+        <v>6.8413405418396</v>
       </c>
       <c r="C150" t="n">
-        <v>7.421893621943401</v>
+        <v>7.421893104642092</v>
       </c>
       <c r="D150" t="n">
-        <v>6.841341018676758</v>
+        <v>6.8413405418396</v>
       </c>
       <c r="E150" t="n">
-        <v>7.420653049518127</v>
+        <v>7.420652532303285</v>
       </c>
       <c r="F150" t="n">
         <v>26563775</v>
@@ -3452,16 +3452,16 @@
         <v>43970</v>
       </c>
       <c r="B152" t="n">
-        <v>6.831417560577393</v>
+        <v>6.831418037414551</v>
       </c>
       <c r="C152" t="n">
-        <v>7.018731929050585</v>
+        <v>7.018732418962401</v>
       </c>
       <c r="D152" t="n">
-        <v>6.799164018747209</v>
+        <v>6.79916449333305</v>
       </c>
       <c r="E152" t="n">
-        <v>6.966631015976597</v>
+        <v>6.966631502251738</v>
       </c>
       <c r="F152" t="n">
         <v>13463520</v>
@@ -3472,16 +3472,16 @@
         <v>43971</v>
       </c>
       <c r="B153" t="n">
-        <v>6.822733402252197</v>
+        <v>6.822733879089355</v>
       </c>
       <c r="C153" t="n">
-        <v>6.983997533970078</v>
+        <v>6.983998022077899</v>
       </c>
       <c r="D153" t="n">
-        <v>6.81032857213493</v>
+        <v>6.810329048105121</v>
       </c>
       <c r="E153" t="n">
-        <v>6.946783490349408</v>
+        <v>6.94678397585636</v>
       </c>
       <c r="F153" t="n">
         <v>11533147</v>
@@ -3552,16 +3552,16 @@
         <v>43977</v>
       </c>
       <c r="B157" t="n">
-        <v>7.423134326934814</v>
+        <v>7.423134803771973</v>
       </c>
       <c r="C157" t="n">
-        <v>7.560828925689475</v>
+        <v>7.560829411371671</v>
       </c>
       <c r="D157" t="n">
-        <v>7.275514702466858</v>
+        <v>7.275515169821428</v>
       </c>
       <c r="E157" t="n">
-        <v>7.442982144705714</v>
+        <v>7.442982622817829</v>
       </c>
       <c r="F157" t="n">
         <v>12080691</v>
@@ -3612,16 +3612,16 @@
         <v>43980</v>
       </c>
       <c r="B160" t="n">
-        <v>7.812650680541992</v>
+        <v>7.812650203704834</v>
       </c>
       <c r="C160" t="n">
-        <v>7.812650680541992</v>
+        <v>7.812650203704834</v>
       </c>
       <c r="D160" t="n">
-        <v>7.481437500239227</v>
+        <v>7.481437043617326</v>
       </c>
       <c r="E160" t="n">
-        <v>7.519893458373339</v>
+        <v>7.519892999404318</v>
       </c>
       <c r="F160" t="n">
         <v>23712019</v>
@@ -3652,16 +3652,16 @@
         <v>43984</v>
       </c>
       <c r="B162" t="n">
-        <v>8.271635055541992</v>
+        <v>8.271634101867676</v>
       </c>
       <c r="C162" t="n">
-        <v>8.286521031632221</v>
+        <v>8.286520076241633</v>
       </c>
       <c r="D162" t="n">
-        <v>7.976396678662855</v>
+        <v>7.976395759027911</v>
       </c>
       <c r="E162" t="n">
-        <v>8.063230496816454</v>
+        <v>8.063229567170044</v>
       </c>
       <c r="F162" t="n">
         <v>21348142</v>
@@ -3672,16 +3672,16 @@
         <v>43985</v>
       </c>
       <c r="B163" t="n">
-        <v>8.373353958129883</v>
+        <v>8.373354911804199</v>
       </c>
       <c r="C163" t="n">
-        <v>8.80008582291646</v>
+        <v>8.800086825192951</v>
       </c>
       <c r="D163" t="n">
-        <v>8.315051079171372</v>
+        <v>8.315052026205343</v>
       </c>
       <c r="E163" t="n">
-        <v>8.31753222383259</v>
+        <v>8.317533171149149</v>
       </c>
       <c r="F163" t="n">
         <v>31125376</v>
@@ -3752,16 +3752,16 @@
         <v>43991</v>
       </c>
       <c r="B167" t="n">
-        <v>8.296443939208984</v>
+        <v>8.296442985534668</v>
       </c>
       <c r="C167" t="n">
-        <v>8.32745691101246</v>
+        <v>8.327455953773208</v>
       </c>
       <c r="D167" t="n">
-        <v>8.0967247251524</v>
+        <v>8.096723794435762</v>
       </c>
       <c r="E167" t="n">
-        <v>8.137661383332564</v>
+        <v>8.137660447910266</v>
       </c>
       <c r="F167" t="n">
         <v>13675741</v>
@@ -3772,16 +3772,16 @@
         <v>43992</v>
       </c>
       <c r="B168" t="n">
-        <v>8.089280128479004</v>
+        <v>8.08928108215332</v>
       </c>
       <c r="C168" t="n">
-        <v>8.426696138374464</v>
+        <v>8.426697131827968</v>
       </c>
       <c r="D168" t="n">
-        <v>8.037179665656195</v>
+        <v>8.0371806131882</v>
       </c>
       <c r="E168" t="n">
-        <v>8.311329615282364</v>
+        <v>8.311330595134894</v>
       </c>
       <c r="F168" t="n">
         <v>11944749</v>
@@ -3792,16 +3792,16 @@
         <v>43994</v>
       </c>
       <c r="B169" t="n">
-        <v>7.950345516204834</v>
+        <v>7.950345993041992</v>
       </c>
       <c r="C169" t="n">
-        <v>8.084319292912509</v>
+        <v>8.084319777785</v>
       </c>
       <c r="D169" t="n">
-        <v>7.774194958703272</v>
+        <v>7.774195424975465</v>
       </c>
       <c r="E169" t="n">
-        <v>7.877156659374939</v>
+        <v>7.877157131822456</v>
       </c>
       <c r="F169" t="n">
         <v>12251373</v>
@@ -3892,16 +3892,16 @@
         <v>44001</v>
       </c>
       <c r="B174" t="n">
-        <v>8.487481117248535</v>
+        <v>8.487480163574219</v>
       </c>
       <c r="C174" t="n">
-        <v>8.58920180321846</v>
+        <v>8.589200838114557</v>
       </c>
       <c r="D174" t="n">
-        <v>8.203407450651435</v>
+        <v>8.203406528896336</v>
       </c>
       <c r="E174" t="n">
-        <v>8.203407450651435</v>
+        <v>8.203406528896336</v>
       </c>
       <c r="F174" t="n">
         <v>20750754</v>
@@ -3912,16 +3912,16 @@
         <v>44004</v>
       </c>
       <c r="B175" t="n">
-        <v>8.440341949462891</v>
+        <v>8.440342903137207</v>
       </c>
       <c r="C175" t="n">
-        <v>8.729376978500955</v>
+        <v>8.729377964833343</v>
       </c>
       <c r="D175" t="n">
-        <v>8.380797159632158</v>
+        <v>8.380798106578508</v>
       </c>
       <c r="E175" t="n">
-        <v>8.489961267461833</v>
+        <v>8.489962226742637</v>
       </c>
       <c r="F175" t="n">
         <v>12069362</v>
@@ -3952,16 +3952,16 @@
         <v>44006</v>
       </c>
       <c r="B177" t="n">
-        <v>8.59416389465332</v>
+        <v>8.594162940979004</v>
       </c>
       <c r="C177" t="n">
-        <v>8.669833897798144</v>
+        <v>8.669832935726904</v>
       </c>
       <c r="D177" t="n">
-        <v>8.422974729757115</v>
+        <v>8.422973795079262</v>
       </c>
       <c r="E177" t="n">
-        <v>8.571834484683247</v>
+        <v>8.571833533486773</v>
       </c>
       <c r="F177" t="n">
         <v>7388434</v>
@@ -4052,16 +4052,16 @@
         <v>44013</v>
       </c>
       <c r="B182" t="n">
-        <v>9.009729385375977</v>
+        <v>9.009730339050293</v>
       </c>
       <c r="C182" t="n">
-        <v>9.115171330097578</v>
+        <v>9.11517229493286</v>
       </c>
       <c r="D182" t="n">
-        <v>8.731858165462054</v>
+        <v>8.731859089723871</v>
       </c>
       <c r="E182" t="n">
-        <v>8.812490451063802</v>
+        <v>8.812491383860499</v>
       </c>
       <c r="F182" t="n">
         <v>8963093</v>
@@ -4292,16 +4292,16 @@
         <v>44029</v>
       </c>
       <c r="B194" t="n">
-        <v>8.819933891296387</v>
+        <v>8.81993293762207</v>
       </c>
       <c r="C194" t="n">
-        <v>8.919174324825571</v>
+        <v>8.919173360420668</v>
       </c>
       <c r="D194" t="n">
-        <v>8.633859641988225</v>
+        <v>8.633858708433587</v>
       </c>
       <c r="E194" t="n">
-        <v>8.633859641988225</v>
+        <v>8.633858708433587</v>
       </c>
       <c r="F194" t="n">
         <v>9678298</v>
@@ -4432,16 +4432,16 @@
         <v>44040</v>
       </c>
       <c r="B201" t="n">
-        <v>9.641142845153809</v>
+        <v>9.641143798828125</v>
       </c>
       <c r="C201" t="n">
-        <v>9.832179367263814</v>
+        <v>9.832180339834917</v>
       </c>
       <c r="D201" t="n">
-        <v>9.466232422996864</v>
+        <v>9.466233359369541</v>
       </c>
       <c r="E201" t="n">
-        <v>9.67587708316008</v>
+        <v>9.675878040270206</v>
       </c>
       <c r="F201" t="n">
         <v>30127714</v>
@@ -4472,16 +4472,16 @@
         <v>44042</v>
       </c>
       <c r="B203" t="n">
-        <v>9.143703460693359</v>
+        <v>9.143704414367676</v>
       </c>
       <c r="C203" t="n">
-        <v>9.700686938306321</v>
+        <v>9.700687950073165</v>
       </c>
       <c r="D203" t="n">
-        <v>9.097805411083952</v>
+        <v>9.097806359971171</v>
       </c>
       <c r="E203" t="n">
-        <v>9.685800070178546</v>
+        <v>9.685801080392711</v>
       </c>
       <c r="F203" t="n">
         <v>33272500</v>
@@ -4592,16 +4592,16 @@
         <v>44050</v>
       </c>
       <c r="B209" t="n">
-        <v>8.429178237915039</v>
+        <v>8.429177284240723</v>
       </c>
       <c r="C209" t="n">
-        <v>8.429178237915039</v>
+        <v>8.429177284240723</v>
       </c>
       <c r="D209" t="n">
-        <v>8.25550792408546</v>
+        <v>8.255506990060143</v>
       </c>
       <c r="E209" t="n">
-        <v>8.336141112251321</v>
+        <v>8.336140169103194</v>
       </c>
       <c r="F209" t="n">
         <v>22110172</v>
@@ -4612,16 +4612,16 @@
         <v>44053</v>
       </c>
       <c r="B210" t="n">
-        <v>8.25922966003418</v>
+        <v>8.259230613708496</v>
       </c>
       <c r="C210" t="n">
-        <v>8.468873436704216</v>
+        <v>8.468874414585619</v>
       </c>
       <c r="D210" t="n">
-        <v>8.166191645730668</v>
+        <v>8.166192588662099</v>
       </c>
       <c r="E210" t="n">
-        <v>8.435379322693057</v>
+        <v>8.435380296706972</v>
       </c>
       <c r="F210" t="n">
         <v>21920608</v>
@@ -4652,16 +4652,16 @@
         <v>44055</v>
       </c>
       <c r="B212" t="n">
-        <v>8.162470817565918</v>
+        <v>8.162469863891602</v>
       </c>
       <c r="C212" t="n">
-        <v>8.446544484992341</v>
+        <v>8.446543498127859</v>
       </c>
       <c r="D212" t="n">
-        <v>8.078116358606623</v>
+        <v>8.078115414787984</v>
       </c>
       <c r="E212" t="n">
-        <v>8.409329992024503</v>
+        <v>8.409329009508031</v>
       </c>
       <c r="F212" t="n">
         <v>20200945</v>
@@ -4732,16 +4732,16 @@
         <v>44061</v>
       </c>
       <c r="B216" t="n">
-        <v>8.101685523986816</v>
+        <v>8.101686477661133</v>
       </c>
       <c r="C216" t="n">
-        <v>8.143863198266791</v>
+        <v>8.143864156905972</v>
       </c>
       <c r="D216" t="n">
-        <v>7.978877345430011</v>
+        <v>7.9788782846482</v>
       </c>
       <c r="E216" t="n">
-        <v>8.038420352760289</v>
+        <v>8.038421298987467</v>
       </c>
       <c r="F216" t="n">
         <v>10608743</v>
@@ -4752,16 +4752,16 @@
         <v>44062</v>
       </c>
       <c r="B217" t="n">
-        <v>7.926775932312012</v>
+        <v>7.926775455474854</v>
       </c>
       <c r="C217" t="n">
-        <v>8.141381998856557</v>
+        <v>8.141381509109719</v>
       </c>
       <c r="D217" t="n">
-        <v>7.921813642791834</v>
+        <v>7.921813166253184</v>
       </c>
       <c r="E217" t="n">
-        <v>8.141381998856557</v>
+        <v>8.141381509109719</v>
       </c>
       <c r="F217" t="n">
         <v>9466833</v>
@@ -4772,16 +4772,16 @@
         <v>44063</v>
       </c>
       <c r="B218" t="n">
-        <v>7.957787990570068</v>
+        <v>7.957788467407227</v>
       </c>
       <c r="C218" t="n">
-        <v>8.033458885005254</v>
+        <v>8.033459366376674</v>
       </c>
       <c r="D218" t="n">
-        <v>7.774194893738959</v>
+        <v>7.774195359575069</v>
       </c>
       <c r="E218" t="n">
-        <v>7.915611210128628</v>
+        <v>7.915611684438519</v>
       </c>
       <c r="F218" t="n">
         <v>7652765</v>
@@ -4892,16 +4892,16 @@
         <v>44071</v>
       </c>
       <c r="B224" t="n">
-        <v>8.100444793701172</v>
+        <v>8.100445747375488</v>
       </c>
       <c r="C224" t="n">
-        <v>8.100444793701172</v>
+        <v>8.100445747375488</v>
       </c>
       <c r="D224" t="n">
-        <v>7.960268612170143</v>
+        <v>7.960269549341362</v>
       </c>
       <c r="E224" t="n">
-        <v>8.001206157737258</v>
+        <v>8.0012070997281</v>
       </c>
       <c r="F224" t="n">
         <v>5577388</v>
@@ -5012,16 +5012,16 @@
         <v>44082</v>
       </c>
       <c r="B230" t="n">
-        <v>7.751865386962891</v>
+        <v>7.751865863800049</v>
       </c>
       <c r="C230" t="n">
-        <v>7.833737802061967</v>
+        <v>7.833738283935308</v>
       </c>
       <c r="D230" t="n">
-        <v>7.691081361819436</v>
+        <v>7.691081834917614</v>
       </c>
       <c r="E230" t="n">
-        <v>7.813890431199186</v>
+        <v>7.813890911851665</v>
       </c>
       <c r="F230" t="n">
         <v>7181501</v>
@@ -5032,16 +5032,16 @@
         <v>44083</v>
       </c>
       <c r="B231" t="n">
-        <v>7.709689140319824</v>
+        <v>7.709688663482666</v>
       </c>
       <c r="C231" t="n">
-        <v>7.834980256551466</v>
+        <v>7.834979771965168</v>
       </c>
       <c r="D231" t="n">
-        <v>7.637740405675546</v>
+        <v>7.637739933288351</v>
       </c>
       <c r="E231" t="n">
-        <v>7.792802580260581</v>
+        <v>7.792802098282933</v>
       </c>
       <c r="F231" t="n">
         <v>8282629</v>
@@ -5052,16 +5052,16 @@
         <v>44084</v>
       </c>
       <c r="B232" t="n">
-        <v>8.850946426391602</v>
+        <v>8.850947380065918</v>
       </c>
       <c r="C232" t="n">
-        <v>9.197044227170217</v>
+        <v>9.197045218135978</v>
       </c>
       <c r="D232" t="n">
-        <v>8.62145438702172</v>
+        <v>8.621455315968662</v>
       </c>
       <c r="E232" t="n">
-        <v>9.197044227170217</v>
+        <v>9.197045218135978</v>
       </c>
       <c r="F232" t="n">
         <v>139609921</v>
@@ -5132,16 +5132,16 @@
         <v>44090</v>
       </c>
       <c r="B236" t="n">
-        <v>9.312411308288574</v>
+        <v>9.312410354614258</v>
       </c>
       <c r="C236" t="n">
-        <v>9.375676482213272</v>
+        <v>9.375675522060035</v>
       </c>
       <c r="D236" t="n">
-        <v>9.175957274371282</v>
+        <v>9.175956334671081</v>
       </c>
       <c r="E236" t="n">
-        <v>9.179678544963952</v>
+        <v>9.179677604882659</v>
       </c>
       <c r="F236" t="n">
         <v>13993693</v>
@@ -5212,16 +5212,16 @@
         <v>44096</v>
       </c>
       <c r="B240" t="n">
-        <v>9.326057434082031</v>
+        <v>9.326058387756348</v>
       </c>
       <c r="C240" t="n">
-        <v>9.353348239057649</v>
+        <v>9.353349195522698</v>
       </c>
       <c r="D240" t="n">
-        <v>9.182158188124824</v>
+        <v>9.182159127084132</v>
       </c>
       <c r="E240" t="n">
-        <v>9.192082766997606</v>
+        <v>9.192083706971793</v>
       </c>
       <c r="F240" t="n">
         <v>9315031</v>
@@ -5232,16 +5232,16 @@
         <v>44097</v>
       </c>
       <c r="B241" t="n">
-        <v>8.953908920288086</v>
+        <v>8.95390796661377</v>
       </c>
       <c r="C241" t="n">
-        <v>9.308690312405352</v>
+        <v>9.308689320943529</v>
       </c>
       <c r="D241" t="n">
-        <v>8.934060654104224</v>
+        <v>8.934059702543932</v>
       </c>
       <c r="E241" t="n">
-        <v>9.303728915956151</v>
+        <v>9.303727925022763</v>
       </c>
       <c r="F241" t="n">
         <v>13677251</v>
@@ -5252,16 +5252,16 @@
         <v>44098</v>
       </c>
       <c r="B242" t="n">
-        <v>9.282638549804688</v>
+        <v>9.282639503479004</v>
       </c>
       <c r="C242" t="n">
-        <v>9.463751388941567</v>
+        <v>9.46375236122295</v>
       </c>
       <c r="D242" t="n">
-        <v>8.898084356453305</v>
+        <v>8.898085270619518</v>
       </c>
       <c r="E242" t="n">
-        <v>8.906768809518589</v>
+        <v>8.906769724577019</v>
       </c>
       <c r="F242" t="n">
         <v>18607406</v>
@@ -5272,16 +5272,16 @@
         <v>44099</v>
       </c>
       <c r="B243" t="n">
-        <v>9.184639930725098</v>
+        <v>9.184640884399414</v>
       </c>
       <c r="C243" t="n">
-        <v>9.25410751328763</v>
+        <v>9.254108474175018</v>
       </c>
       <c r="D243" t="n">
-        <v>9.095324084518023</v>
+        <v>9.095325028918353</v>
       </c>
       <c r="E243" t="n">
-        <v>9.220613400863298</v>
+        <v>9.22061435827287</v>
       </c>
       <c r="F243" t="n">
         <v>8201819</v>
@@ -5312,16 +5312,16 @@
         <v>44103</v>
       </c>
       <c r="B245" t="n">
-        <v>8.760391235351562</v>
+        <v>8.760390281677246</v>
       </c>
       <c r="C245" t="n">
-        <v>8.942744221459206</v>
+        <v>8.942743247933565</v>
       </c>
       <c r="D245" t="n">
-        <v>8.68348020897627</v>
+        <v>8.683479263674647</v>
       </c>
       <c r="E245" t="n">
-        <v>8.802568019244504</v>
+        <v>8.802567060978735</v>
       </c>
       <c r="F245" t="n">
         <v>13985386</v>
@@ -5332,16 +5332,16 @@
         <v>44104</v>
       </c>
       <c r="B246" t="n">
-        <v>8.651226043701172</v>
+        <v>8.651226997375488</v>
       </c>
       <c r="C246" t="n">
-        <v>8.841022441256731</v>
+        <v>8.841023415853394</v>
       </c>
       <c r="D246" t="n">
-        <v>8.609049265013768</v>
+        <v>8.609050214038696</v>
       </c>
       <c r="E246" t="n">
-        <v>8.803807058409923</v>
+        <v>8.803808028904122</v>
       </c>
       <c r="F246" t="n">
         <v>11477260</v>
@@ -5412,16 +5412,16 @@
         <v>44110</v>
       </c>
       <c r="B250" t="n">
-        <v>8.497405052185059</v>
+        <v>8.497404098510742</v>
       </c>
       <c r="C250" t="n">
-        <v>8.520974589071102</v>
+        <v>8.520973632751547</v>
       </c>
       <c r="D250" t="n">
-        <v>8.316293085426295</v>
+        <v>8.3162921520784</v>
       </c>
       <c r="E250" t="n">
-        <v>8.488721491571129</v>
+        <v>8.48872053887138</v>
       </c>
       <c r="F250" t="n">
         <v>10544549</v>
@@ -5432,16 +5432,16 @@
         <v>44111</v>
       </c>
       <c r="B251" t="n">
-        <v>8.585480690002441</v>
+        <v>8.585479736328125</v>
       </c>
       <c r="C251" t="n">
-        <v>8.704568498874545</v>
+        <v>8.704567531971968</v>
       </c>
       <c r="D251" t="n">
-        <v>8.440343093036322</v>
+        <v>8.440342155483876</v>
       </c>
       <c r="E251" t="n">
-        <v>8.477557586577683</v>
+        <v>8.477556644891454</v>
       </c>
       <c r="F251" t="n">
         <v>12680345</v>
@@ -5552,16 +5552,16 @@
         <v>44120</v>
       </c>
       <c r="B257" t="n">
-        <v>8.25922966003418</v>
+        <v>8.259230613708496</v>
       </c>
       <c r="C257" t="n">
-        <v>8.267912326486389</v>
+        <v>8.267913281163274</v>
       </c>
       <c r="D257" t="n">
-        <v>8.097964185523827</v>
+        <v>8.097965120577188</v>
       </c>
       <c r="E257" t="n">
-        <v>8.122774739620494</v>
+        <v>8.122775677538673</v>
       </c>
       <c r="F257" t="n">
         <v>10726560</v>
@@ -5612,16 +5612,16 @@
         <v>44125</v>
       </c>
       <c r="B260" t="n">
-        <v>8.275355339050293</v>
+        <v>8.275356292724609</v>
       </c>
       <c r="C260" t="n">
-        <v>8.355987625465389</v>
+        <v>8.355988588431988</v>
       </c>
       <c r="D260" t="n">
-        <v>8.245583390421267</v>
+        <v>8.245584340664582</v>
       </c>
       <c r="E260" t="n">
-        <v>8.354747499881778</v>
+        <v>8.35474846270546</v>
       </c>
       <c r="F260" t="n">
         <v>4665068</v>
@@ -5632,16 +5632,16 @@
         <v>44126</v>
       </c>
       <c r="B261" t="n">
-        <v>8.267911911010742</v>
+        <v>8.267912864685059</v>
       </c>
       <c r="C261" t="n">
-        <v>8.337380386835774</v>
+        <v>8.337381348523031</v>
       </c>
       <c r="D261" t="n">
-        <v>8.168673273460097</v>
+        <v>8.168674215687588</v>
       </c>
       <c r="E261" t="n">
-        <v>8.30636741913896</v>
+        <v>8.306368377248981</v>
       </c>
       <c r="F261" t="n">
         <v>7908034</v>
@@ -5652,16 +5652,16 @@
         <v>44127</v>
       </c>
       <c r="B262" t="n">
-        <v>8.234419822692871</v>
+        <v>8.234420776367188</v>
       </c>
       <c r="C262" t="n">
-        <v>8.312570966783923</v>
+        <v>8.312571929509362</v>
       </c>
       <c r="D262" t="n">
-        <v>8.203406854103131</v>
+        <v>8.203407804185662</v>
       </c>
       <c r="E262" t="n">
-        <v>8.269152274680931</v>
+        <v>8.269153232377807</v>
       </c>
       <c r="F262" t="n">
         <v>5098571</v>
@@ -5712,16 +5712,16 @@
         <v>44132</v>
       </c>
       <c r="B265" t="n">
-        <v>7.825055599212646</v>
+        <v>7.825055122375488</v>
       </c>
       <c r="C265" t="n">
-        <v>8.088040873150774</v>
+        <v>8.088040380288025</v>
       </c>
       <c r="D265" t="n">
-        <v>7.817612164601516</v>
+        <v>7.81761168821794</v>
       </c>
       <c r="E265" t="n">
-        <v>8.078116293669268</v>
+        <v>8.078115801411293</v>
       </c>
       <c r="F265" t="n">
         <v>12369944</v>
@@ -5752,16 +5752,16 @@
         <v>44134</v>
       </c>
       <c r="B267" t="n">
-        <v>7.684878826141357</v>
+        <v>7.684879302978516</v>
       </c>
       <c r="C267" t="n">
-        <v>7.777915944304612</v>
+        <v>7.777916426914608</v>
       </c>
       <c r="D267" t="n">
-        <v>7.574474588649013</v>
+        <v>7.574475058635726</v>
       </c>
       <c r="E267" t="n">
-        <v>7.759308699364413</v>
+        <v>7.759309180819852</v>
       </c>
       <c r="F267" t="n">
         <v>16269207</v>
@@ -5772,16 +5772,16 @@
         <v>44138</v>
       </c>
       <c r="B268" t="n">
-        <v>7.717131614685059</v>
+        <v>7.7171311378479</v>
       </c>
       <c r="C268" t="n">
-        <v>7.852346415863062</v>
+        <v>7.852345930671059</v>
       </c>
       <c r="D268" t="n">
-        <v>7.622854363726927</v>
+        <v>7.622853892715106</v>
       </c>
       <c r="E268" t="n">
-        <v>7.821334338599661</v>
+        <v>7.821333855323877</v>
       </c>
       <c r="F268" t="n">
         <v>9901091</v>
@@ -5812,16 +5812,16 @@
         <v>44140</v>
       </c>
       <c r="B270" t="n">
-        <v>8.119053840637207</v>
+        <v>8.119052886962891</v>
       </c>
       <c r="C270" t="n">
-        <v>8.177356724487632</v>
+        <v>8.177355763964984</v>
       </c>
       <c r="D270" t="n">
-        <v>8.007408575750512</v>
+        <v>8.007407635190189</v>
       </c>
       <c r="E270" t="n">
-        <v>8.039661672128053</v>
+        <v>8.039660727779241</v>
       </c>
       <c r="F270" t="n">
         <v>9820281</v>
@@ -5892,16 +5892,16 @@
         <v>44146</v>
       </c>
       <c r="B274" t="n">
-        <v>8.193483352661133</v>
+        <v>8.193482398986816</v>
       </c>
       <c r="C274" t="n">
-        <v>8.420494274138473</v>
+        <v>8.420493294041393</v>
       </c>
       <c r="D274" t="n">
-        <v>8.193483352661133</v>
+        <v>8.193482398986816</v>
       </c>
       <c r="E274" t="n">
-        <v>8.312572059811611</v>
+        <v>8.312571092276054</v>
       </c>
       <c r="F274" t="n">
         <v>7246451</v>
@@ -5912,16 +5912,16 @@
         <v>44147</v>
       </c>
       <c r="B275" t="n">
-        <v>8.234419822692871</v>
+        <v>8.234420776367188</v>
       </c>
       <c r="C275" t="n">
-        <v>8.398164651520666</v>
+        <v>8.398165624159189</v>
       </c>
       <c r="D275" t="n">
-        <v>8.131458125037573</v>
+        <v>8.13145906678732</v>
       </c>
       <c r="E275" t="n">
-        <v>8.193482275292528</v>
+        <v>8.193483224225638</v>
       </c>
       <c r="F275" t="n">
         <v>11697033</v>
@@ -5932,16 +5932,16 @@
         <v>44148</v>
       </c>
       <c r="B276" t="n">
-        <v>8.633858680725098</v>
+        <v>8.633859634399414</v>
       </c>
       <c r="C276" t="n">
-        <v>8.646264403631776</v>
+        <v>8.646265358676397</v>
       </c>
       <c r="D276" t="n">
-        <v>8.267911744802472</v>
+        <v>8.267912658055211</v>
       </c>
       <c r="E276" t="n">
-        <v>8.322493351742979</v>
+        <v>8.322494271024663</v>
       </c>
       <c r="F276" t="n">
         <v>10854949</v>
@@ -5992,16 +5992,16 @@
         <v>44153</v>
       </c>
       <c r="B279" t="n">
-        <v>8.584239959716797</v>
+        <v>8.584240913391113</v>
       </c>
       <c r="C279" t="n">
-        <v>8.64502398560519</v>
+        <v>8.645024946032365</v>
       </c>
       <c r="D279" t="n">
-        <v>8.516012499566937</v>
+        <v>8.516013445661457</v>
       </c>
       <c r="E279" t="n">
-        <v>8.55818927999508</v>
+        <v>8.558190230775271</v>
       </c>
       <c r="F279" t="n">
         <v>8922310</v>
@@ -6072,16 +6072,16 @@
         <v>44160</v>
       </c>
       <c r="B283" t="n">
-        <v>8.739301681518555</v>
+        <v>8.739302635192871</v>
       </c>
       <c r="C283" t="n">
-        <v>8.920413624337439</v>
+        <v>8.920414597775554</v>
       </c>
       <c r="D283" t="n">
-        <v>8.616491723410208</v>
+        <v>8.616492663682914</v>
       </c>
       <c r="E283" t="n">
-        <v>8.854667312281327</v>
+        <v>8.85466827854489</v>
       </c>
       <c r="F283" t="n">
         <v>6633202</v>
@@ -6112,16 +6112,16 @@
         <v>44162</v>
       </c>
       <c r="B285" t="n">
-        <v>8.615251541137695</v>
+        <v>8.615252494812012</v>
       </c>
       <c r="C285" t="n">
-        <v>8.70828776310049</v>
+        <v>8.708288727073548</v>
       </c>
       <c r="D285" t="n">
-        <v>8.507328451506179</v>
+        <v>8.507329393233835</v>
       </c>
       <c r="E285" t="n">
-        <v>8.566871454869922</v>
+        <v>8.566872403188754</v>
       </c>
       <c r="F285" t="n">
         <v>5230736</v>
@@ -6152,16 +6152,16 @@
         <v>44166</v>
       </c>
       <c r="B287" t="n">
-        <v>8.414291381835938</v>
+        <v>8.414292335510254</v>
       </c>
       <c r="C287" t="n">
-        <v>8.672314340510058</v>
+        <v>8.672315323428652</v>
       </c>
       <c r="D287" t="n">
-        <v>8.360949006055193</v>
+        <v>8.360949953683695</v>
       </c>
       <c r="E287" t="n">
-        <v>8.636339977103933</v>
+        <v>8.636340955945199</v>
       </c>
       <c r="F287" t="n">
         <v>16096259</v>
@@ -6172,16 +6172,16 @@
         <v>44167</v>
       </c>
       <c r="B288" t="n">
-        <v>8.282797813415527</v>
+        <v>8.282798767089844</v>
       </c>
       <c r="C288" t="n">
-        <v>8.461429503764982</v>
+        <v>8.4614304780068</v>
       </c>
       <c r="D288" t="n">
-        <v>8.199685276496087</v>
+        <v>8.199686220600897</v>
       </c>
       <c r="E288" t="n">
-        <v>8.456468108007872</v>
+        <v>8.456469081678438</v>
       </c>
       <c r="F288" t="n">
         <v>15329699</v>
@@ -6212,16 +6212,16 @@
         <v>44169</v>
       </c>
       <c r="B290" t="n">
-        <v>8.772793769836426</v>
+        <v>8.772794723510742</v>
       </c>
       <c r="C290" t="n">
-        <v>8.948944312102428</v>
+        <v>8.948945284925747</v>
       </c>
       <c r="D290" t="n">
-        <v>8.683478819885265</v>
+        <v>8.683479763850318</v>
       </c>
       <c r="E290" t="n">
-        <v>8.886919271932774</v>
+        <v>8.886920238013465</v>
       </c>
       <c r="F290" t="n">
         <v>10446369</v>
@@ -6232,16 +6232,16 @@
         <v>44172</v>
       </c>
       <c r="B291" t="n">
-        <v>8.647505760192871</v>
+        <v>8.647504806518555</v>
       </c>
       <c r="C291" t="n">
-        <v>8.82737759966732</v>
+        <v>8.827376626156168</v>
       </c>
       <c r="D291" t="n">
-        <v>8.621455078573774</v>
+        <v>8.621454127772409</v>
       </c>
       <c r="E291" t="n">
-        <v>8.807529333653388</v>
+        <v>8.807528362331166</v>
       </c>
       <c r="F291" t="n">
         <v>10174485</v>
@@ -6392,16 +6392,16 @@
         <v>44182</v>
       </c>
       <c r="B299" t="n">
-        <v>9.125096321105957</v>
+        <v>9.125097274780273</v>
       </c>
       <c r="C299" t="n">
-        <v>9.233019415311725</v>
+        <v>9.233020380265208</v>
       </c>
       <c r="D299" t="n">
-        <v>9.1052480568353</v>
+        <v>9.105249008435251</v>
       </c>
       <c r="E299" t="n">
-        <v>9.230538270595108</v>
+        <v>9.230539235289285</v>
       </c>
       <c r="F299" t="n">
         <v>5262456</v>
@@ -6452,16 +6452,16 @@
         <v>44187</v>
       </c>
       <c r="B302" t="n">
-        <v>9.018413543701172</v>
+        <v>9.018414497375488</v>
       </c>
       <c r="C302" t="n">
-        <v>9.117653080233614</v>
+        <v>9.117654044402261</v>
       </c>
       <c r="D302" t="n">
-        <v>8.941503416629342</v>
+        <v>8.941504362170608</v>
       </c>
       <c r="E302" t="n">
-        <v>8.974995743895692</v>
+        <v>8.974996692978687</v>
       </c>
       <c r="F302" t="n">
         <v>3700636</v>
@@ -6572,16 +6572,16 @@
         <v>44201</v>
       </c>
       <c r="B308" t="n">
-        <v>9.097805023193359</v>
+        <v>9.097805976867676</v>
       </c>
       <c r="C308" t="n">
-        <v>9.304967640603</v>
+        <v>9.304968615993069</v>
       </c>
       <c r="D308" t="n">
-        <v>9.012210449150441</v>
+        <v>9.012211393852336</v>
       </c>
       <c r="E308" t="n">
-        <v>9.304967640603</v>
+        <v>9.304968615993069</v>
       </c>
       <c r="F308" t="n">
         <v>8306796</v>
@@ -6592,16 +6592,16 @@
         <v>44202</v>
       </c>
       <c r="B309" t="n">
-        <v>9.02337646484375</v>
+        <v>9.023375511169434</v>
       </c>
       <c r="C309" t="n">
-        <v>9.178438642419241</v>
+        <v>9.178437672356514</v>
       </c>
       <c r="D309" t="n">
-        <v>8.883200263463204</v>
+        <v>8.883199324604012</v>
       </c>
       <c r="E309" t="n">
-        <v>9.091603036730099</v>
+        <v>9.091602075844966</v>
       </c>
       <c r="F309" t="n">
         <v>6995714</v>
@@ -6632,16 +6632,16 @@
         <v>44204</v>
       </c>
       <c r="B311" t="n">
-        <v>9.494765281677246</v>
+        <v>9.49476432800293</v>
       </c>
       <c r="C311" t="n">
-        <v>9.533220794103377</v>
+        <v>9.533219836566508</v>
       </c>
       <c r="D311" t="n">
-        <v>9.077957953992263</v>
+        <v>9.077957042182957</v>
       </c>
       <c r="E311" t="n">
-        <v>9.178438515281906</v>
+        <v>9.178437593380119</v>
       </c>
       <c r="F311" t="n">
         <v>10280973</v>
@@ -6732,16 +6732,16 @@
         <v>44211</v>
       </c>
       <c r="B316" t="n">
-        <v>9.479878425598145</v>
+        <v>9.479877471923828</v>
       </c>
       <c r="C316" t="n">
-        <v>9.607649794137002</v>
+        <v>9.607648827608905</v>
       </c>
       <c r="D316" t="n">
-        <v>9.378158631904267</v>
+        <v>9.378157688462947</v>
       </c>
       <c r="E316" t="n">
-        <v>9.589042547490402</v>
+        <v>9.589041582834192</v>
       </c>
       <c r="F316" t="n">
         <v>14334303</v>
@@ -6892,16 +6892,16 @@
         <v>44224</v>
       </c>
       <c r="B324" t="n">
-        <v>9.368232727050781</v>
+        <v>9.368233680725098</v>
       </c>
       <c r="C324" t="n">
-        <v>9.399244800408228</v>
+        <v>9.399245757239534</v>
       </c>
       <c r="D324" t="n">
-        <v>9.102766341339521</v>
+        <v>9.102767267989694</v>
       </c>
       <c r="E324" t="n">
-        <v>9.180917480970056</v>
+        <v>9.180918415575915</v>
       </c>
       <c r="F324" t="n">
         <v>7429217</v>
@@ -6912,16 +6912,16 @@
         <v>44225</v>
       </c>
       <c r="B325" t="n">
-        <v>9.363271713256836</v>
+        <v>9.36327075958252</v>
       </c>
       <c r="C325" t="n">
-        <v>9.571676269761104</v>
+        <v>9.571675294860224</v>
       </c>
       <c r="D325" t="n">
-        <v>9.215652973121827</v>
+        <v>9.215652034482874</v>
       </c>
       <c r="E325" t="n">
-        <v>9.312411369945844</v>
+        <v>9.312410421451789</v>
       </c>
       <c r="F325" t="n">
         <v>11022611</v>
@@ -6952,16 +6952,16 @@
         <v>44229</v>
       </c>
       <c r="B327" t="n">
-        <v>10.13361930847168</v>
+        <v>10.133620262146</v>
       </c>
       <c r="C327" t="n">
-        <v>10.18447964681817</v>
+        <v>10.18448060527895</v>
       </c>
       <c r="D327" t="n">
-        <v>9.832179442109044</v>
+        <v>9.832180367414875</v>
       </c>
       <c r="E327" t="n">
-        <v>10.11004977442547</v>
+        <v>10.11005072588166</v>
       </c>
       <c r="F327" t="n">
         <v>20046878</v>
@@ -6992,16 +6992,16 @@
         <v>44231</v>
       </c>
       <c r="B329" t="n">
-        <v>10.38668251037598</v>
+        <v>10.38668155670166</v>
       </c>
       <c r="C329" t="n">
-        <v>10.38668251037598</v>
+        <v>10.38668155670166</v>
       </c>
       <c r="D329" t="n">
-        <v>10.11749393146458</v>
+        <v>10.11749300250636</v>
       </c>
       <c r="E329" t="n">
-        <v>10.17703872709649</v>
+        <v>10.17703779267104</v>
       </c>
       <c r="F329" t="n">
         <v>12166787</v>
@@ -7012,16 +7012,16 @@
         <v>44232</v>
       </c>
       <c r="B330" t="n">
-        <v>10.55663013458252</v>
+        <v>10.5566291809082</v>
       </c>
       <c r="C330" t="n">
-        <v>10.58144069033415</v>
+        <v>10.58143973441847</v>
       </c>
       <c r="D330" t="n">
-        <v>10.32465782656054</v>
+        <v>10.32465689384235</v>
       </c>
       <c r="E330" t="n">
-        <v>10.41893507933724</v>
+        <v>10.41893413810214</v>
       </c>
       <c r="F330" t="n">
         <v>10745440</v>
@@ -7192,16 +7192,16 @@
         <v>44249</v>
       </c>
       <c r="B339" t="n">
-        <v>11.09376525878906</v>
+        <v>11.09376621246338</v>
       </c>
       <c r="C339" t="n">
-        <v>11.20292847746345</v>
+        <v>11.20292944052197</v>
       </c>
       <c r="D339" t="n">
-        <v>10.63602131403072</v>
+        <v>10.63602222835513</v>
       </c>
       <c r="E339" t="n">
-        <v>10.9399432226141</v>
+        <v>10.93994416306512</v>
       </c>
       <c r="F339" t="n">
         <v>14982292</v>
@@ -7292,16 +7292,16 @@
         <v>44256</v>
       </c>
       <c r="B344" t="n">
-        <v>21.85701751708984</v>
+        <v>21.85701560974121</v>
       </c>
       <c r="C344" t="n">
-        <v>23.99306617161</v>
+        <v>23.99306407785948</v>
       </c>
       <c r="D344" t="n">
-        <v>16.31078752172449</v>
+        <v>16.3107860983666</v>
       </c>
       <c r="E344" t="n">
-        <v>16.86353693074166</v>
+        <v>16.8635354591482</v>
       </c>
       <c r="F344" t="n">
         <v>49361500</v>
@@ -7312,16 +7312,16 @@
         <v>44257</v>
       </c>
       <c r="B345" t="n">
-        <v>21.19184494018555</v>
+        <v>21.19184303283691</v>
       </c>
       <c r="C345" t="n">
-        <v>22.95314685108304</v>
+        <v>22.95314478521037</v>
       </c>
       <c r="D345" t="n">
-        <v>20.69530683439987</v>
+        <v>20.6953049717416</v>
       </c>
       <c r="E345" t="n">
-        <v>22.18491936483229</v>
+        <v>22.18491736810308</v>
       </c>
       <c r="F345" t="n">
         <v>20095700</v>
@@ -7352,16 +7352,16 @@
         <v>44259</v>
       </c>
       <c r="B347" t="n">
-        <v>20.86394309997559</v>
+        <v>20.86394119262695</v>
       </c>
       <c r="C347" t="n">
-        <v>21.52911508897337</v>
+        <v>21.52911312081577</v>
       </c>
       <c r="D347" t="n">
-        <v>20.0113977633286</v>
+        <v>20.01139593391831</v>
       </c>
       <c r="E347" t="n">
-        <v>20.23624470835284</v>
+        <v>20.2362428583874</v>
       </c>
       <c r="F347" t="n">
         <v>8984600</v>
@@ -7732,16 +7732,16 @@
         <v>44286</v>
       </c>
       <c r="B366" t="n">
-        <v>31.08511734008789</v>
+        <v>31.08511924743652</v>
       </c>
       <c r="C366" t="n">
-        <v>32.65904760342265</v>
+        <v>32.65904960734591</v>
       </c>
       <c r="D366" t="n">
-        <v>30.82279682081511</v>
+        <v>30.82279871206804</v>
       </c>
       <c r="E366" t="n">
-        <v>31.95640029207138</v>
+        <v>31.95640225288098</v>
       </c>
       <c r="F366" t="n">
         <v>8195900</v>
@@ -7792,16 +7792,16 @@
         <v>44292</v>
       </c>
       <c r="B369" t="n">
-        <v>30.5792121887207</v>
+        <v>30.57921028137207</v>
       </c>
       <c r="C369" t="n">
-        <v>32.19998498521812</v>
+        <v>32.19998297677536</v>
       </c>
       <c r="D369" t="n">
-        <v>30.48552730465581</v>
+        <v>30.48552540315069</v>
       </c>
       <c r="E369" t="n">
-        <v>31.01953900629401</v>
+        <v>31.01953707148042</v>
       </c>
       <c r="F369" t="n">
         <v>6923500</v>
@@ -7812,16 +7812,16 @@
         <v>44293</v>
       </c>
       <c r="B370" t="n">
-        <v>30.95395660400391</v>
+        <v>30.95395851135254</v>
       </c>
       <c r="C370" t="n">
-        <v>31.36617506706607</v>
+        <v>31.36617699981515</v>
       </c>
       <c r="D370" t="n">
-        <v>30.40120725129495</v>
+        <v>30.40120912458377</v>
       </c>
       <c r="E370" t="n">
-        <v>30.72910789533883</v>
+        <v>30.72910978883253</v>
       </c>
       <c r="F370" t="n">
         <v>4745700</v>
@@ -8012,16 +8012,16 @@
         <v>44308</v>
       </c>
       <c r="B380" t="n">
-        <v>36.30344390869141</v>
+        <v>36.30344772338867</v>
       </c>
       <c r="C380" t="n">
-        <v>38.03663915608288</v>
+        <v>38.03664315290104</v>
       </c>
       <c r="D380" t="n">
-        <v>35.88185481304648</v>
+        <v>35.88185858344396</v>
       </c>
       <c r="E380" t="n">
-        <v>37.12788440974715</v>
+        <v>37.12788831107506</v>
       </c>
       <c r="F380" t="n">
         <v>6756200</v>
@@ -8052,16 +8052,16 @@
         <v>44312</v>
       </c>
       <c r="B382" t="n">
-        <v>35.91933441162109</v>
+        <v>35.91933059692383</v>
       </c>
       <c r="C382" t="n">
-        <v>36.30344817190534</v>
+        <v>36.30344431641451</v>
       </c>
       <c r="D382" t="n">
-        <v>35.51648295890232</v>
+        <v>35.5164791869886</v>
       </c>
       <c r="E382" t="n">
-        <v>35.88185902675205</v>
+        <v>35.88185521603473</v>
       </c>
       <c r="F382" t="n">
         <v>4241900</v>
@@ -8072,16 +8072,16 @@
         <v>44313</v>
       </c>
       <c r="B383" t="n">
-        <v>35.46963500976562</v>
+        <v>35.46963882446289</v>
       </c>
       <c r="C383" t="n">
-        <v>36.2940754796825</v>
+        <v>36.29407938304689</v>
       </c>
       <c r="D383" t="n">
-        <v>35.27289463051181</v>
+        <v>35.27289842405</v>
       </c>
       <c r="E383" t="n">
-        <v>36.05985972137591</v>
+        <v>36.05986359955081</v>
       </c>
       <c r="F383" t="n">
         <v>2386900</v>
@@ -35552,19 +35552,39 @@
         <v>46322</v>
       </c>
       <c r="B1757" t="n">
-        <v>2.23</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="C1757" t="n">
-        <v>2.35</v>
+        <v>2.349999904632568</v>
       </c>
       <c r="D1757" t="n">
-        <v>2.15</v>
+        <v>2.150000095367432</v>
       </c>
       <c r="E1757" t="n">
-        <v>2.32</v>
+        <v>2.319999933242798</v>
       </c>
       <c r="F1757" t="n">
         <v>10043900</v>
+      </c>
+    </row>
+    <row r="1758">
+      <c r="A1758" s="1" t="n">
+        <v>46323</v>
+      </c>
+      <c r="B1758" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="C1758" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="D1758" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="E1758" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="F1758" t="n">
+        <v>6089800</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1758"/>
+  <dimension ref="A1:F1759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906083106995</v>
+        <v>1.553906321525574</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799174308776855</v>
+        <v>1.799173593521118</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799174308776855</v>
+        <v>1.799173593521118</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799174308776855</v>
+        <v>1.799173593521118</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799174308776855</v>
+        <v>1.799173593521118</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132486343384</v>
+        <v>1.853132963180542</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616733074188232</v>
+        <v>2.616731882095337</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616733074188232</v>
+        <v>2.616731882095337</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616733074188232</v>
+        <v>2.616731882095337</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616733074188232</v>
+        <v>2.616731882095337</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195407867432</v>
+        <v>2.725195646286011</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.27950119972229</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="C11" t="n">
-        <v>3.27950119972229</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="D11" t="n">
-        <v>3.27950119972229</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="E11" t="n">
-        <v>3.27950119972229</v>
+        <v>3.279500246047974</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156707763672</v>
+        <v>2.180156230926514</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1132,16 +1132,16 @@
         <v>39350</v>
       </c>
       <c r="B36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="C36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="D36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="E36" t="n">
-        <v>2.152359008789062</v>
+        <v>2.152359485626221</v>
       </c>
       <c r="F36" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125652313232422</v>
+        <v>2.125651597976685</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1172,16 +1172,16 @@
         <v>39661</v>
       </c>
       <c r="B38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="C38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="D38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="E38" t="n">
-        <v>1.92246150970459</v>
+        <v>1.922461748123169</v>
       </c>
       <c r="F38" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758486390113831</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758486390113831</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758486390113831</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486866950989</v>
+        <v>1.758486390113831</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212132453918</v>
+        <v>1.838212251663208</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951084136962891</v>
+        <v>6.951083183288574</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997223377227783</v>
+        <v>6.997223854064941</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997223377227783</v>
+        <v>6.997223854064942</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997223377227783</v>
+        <v>6.997223854064942</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997223377227783</v>
+        <v>6.997223854064942</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294833660125732</v>
+        <v>5.294834136962891</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E46" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="C47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="D47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="E47" t="n">
-        <v>5.370966911315918</v>
+        <v>5.37096643447876</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926959037780762</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959276199341</v>
+        <v>3.926959037780761</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1392,16 +1392,16 @@
         <v>42500</v>
       </c>
       <c r="B49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="C49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="D49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="E49" t="n">
-        <v>4.587934494018555</v>
+        <v>4.587934017181396</v>
       </c>
       <c r="F49" t="n">
         <v>1510</v>
@@ -1412,16 +1412,16 @@
         <v>42738</v>
       </c>
       <c r="B50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E50" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F50" t="n">
         <v>2265</v>
@@ -1432,16 +1432,16 @@
         <v>42766</v>
       </c>
       <c r="B51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="C51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="D51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="E51" t="n">
-        <v>4.489362716674805</v>
+        <v>4.489363193511963</v>
       </c>
       <c r="F51" t="n">
         <v>755</v>
@@ -1452,16 +1452,16 @@
         <v>42767</v>
       </c>
       <c r="B52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="C52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="D52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="E52" t="n">
-        <v>10.73543357849121</v>
+        <v>10.73543453216553</v>
       </c>
       <c r="F52" t="n">
         <v>755</v>
@@ -1472,16 +1472,16 @@
         <v>42823</v>
       </c>
       <c r="B53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E53" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F53" t="n">
         <v>755</v>
@@ -1492,16 +1492,16 @@
         <v>42824</v>
       </c>
       <c r="B54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="C54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="D54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="E54" t="n">
-        <v>8.295561790466309</v>
+        <v>8.295562744140625</v>
       </c>
       <c r="F54" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075627326965332</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075627326965331</v>
+        <v>7.075626373291016</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045818328857</v>
+        <v>12.56045913696289</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733310699463</v>
       </c>
       <c r="C57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733310699463</v>
       </c>
       <c r="D57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733310699463</v>
       </c>
       <c r="E57" t="n">
-        <v>12.687331199646</v>
+        <v>12.68733310699463</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1572,16 +1572,16 @@
         <v>42874</v>
       </c>
       <c r="B58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="C58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="D58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="E58" t="n">
-        <v>8.296537399291992</v>
+        <v>8.296538352966309</v>
       </c>
       <c r="F58" t="n">
         <v>755</v>
@@ -1592,16 +1592,16 @@
         <v>42943</v>
       </c>
       <c r="B59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="C59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="D59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="E59" t="n">
-        <v>8.294588088989258</v>
+        <v>8.294586181640625</v>
       </c>
       <c r="F59" t="n">
         <v>755</v>
@@ -1632,16 +1632,16 @@
         <v>43138</v>
       </c>
       <c r="B61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="C61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="D61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="E61" t="n">
-        <v>8.988326072692871</v>
+        <v>8.988327026367188</v>
       </c>
       <c r="F61" t="n">
         <v>2265</v>
@@ -35572,19 +35572,39 @@
         <v>46323</v>
       </c>
       <c r="B1758" t="n">
-        <v>2.07</v>
+        <v>2.069999933242798</v>
       </c>
       <c r="C1758" t="n">
-        <v>2.23</v>
+        <v>2.230000019073486</v>
       </c>
       <c r="D1758" t="n">
-        <v>2.06</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="E1758" t="n">
-        <v>2.2</v>
+        <v>2.200000047683716</v>
       </c>
       <c r="F1758" t="n">
         <v>6089800</v>
+      </c>
+    </row>
+    <row r="1759">
+      <c r="A1759" s="1" t="n">
+        <v>46324</v>
+      </c>
+      <c r="B1759" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="C1759" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="D1759" t="n">
+        <v>2</v>
+      </c>
+      <c r="E1759" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="F1759" t="n">
+        <v>7604500</v>
       </c>
     </row>
   </sheetData>

--- a/database/PCAR3.xlsx
+++ b/database/PCAR3.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F1759"/>
+  <dimension ref="A1:F1760"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,16 +452,16 @@
         <v>36675</v>
       </c>
       <c r="B2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="C2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="D2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="E2" t="n">
-        <v>1.553906321525574</v>
+        <v>1.553906083106995</v>
       </c>
       <c r="F2" t="n">
         <v>755896</v>
@@ -472,16 +472,16 @@
         <v>36704</v>
       </c>
       <c r="B3" t="n">
-        <v>1.799173593521118</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="C3" t="n">
-        <v>1.799173593521118</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="D3" t="n">
-        <v>1.799173593521118</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="E3" t="n">
-        <v>1.799173593521118</v>
+        <v>1.799174070358276</v>
       </c>
       <c r="F3" t="n">
         <v>755896</v>
@@ -492,16 +492,16 @@
         <v>36705</v>
       </c>
       <c r="B4" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C4" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D4" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E4" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F4" t="n">
         <v>755896</v>
@@ -512,16 +512,16 @@
         <v>36707</v>
       </c>
       <c r="B5" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C5" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D5" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E5" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F5" t="n">
         <v>755896</v>
@@ -532,16 +532,16 @@
         <v>36816</v>
       </c>
       <c r="B6" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="C6" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="D6" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="E6" t="n">
-        <v>1.853132963180542</v>
+        <v>1.853133082389832</v>
       </c>
       <c r="F6" t="n">
         <v>2267689</v>
@@ -552,16 +552,16 @@
         <v>36924</v>
       </c>
       <c r="B7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E7" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F7" t="n">
         <v>2192100</v>
@@ -572,16 +572,16 @@
         <v>36941</v>
       </c>
       <c r="B8" t="n">
-        <v>2.616731882095337</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="C8" t="n">
-        <v>2.616731882095337</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="D8" t="n">
-        <v>2.616731882095337</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="E8" t="n">
-        <v>2.616731882095337</v>
+        <v>2.616733074188232</v>
       </c>
       <c r="F8" t="n">
         <v>151179</v>
@@ -592,16 +592,16 @@
         <v>37021</v>
       </c>
       <c r="B9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E9" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F9" t="n">
         <v>226768</v>
@@ -612,16 +612,16 @@
         <v>37033</v>
       </c>
       <c r="B10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="C10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="D10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="E10" t="n">
-        <v>2.725195646286011</v>
+        <v>2.725195407867432</v>
       </c>
       <c r="F10" t="n">
         <v>226768</v>
@@ -632,16 +632,16 @@
         <v>37572</v>
       </c>
       <c r="B11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="C11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="D11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="E11" t="n">
-        <v>3.279500246047974</v>
+        <v>3.279500484466553</v>
       </c>
       <c r="F11" t="n">
         <v>75589</v>
@@ -652,16 +652,16 @@
         <v>38518</v>
       </c>
       <c r="B12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E12" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F12" t="n">
         <v>755896</v>
@@ -672,16 +672,16 @@
         <v>38765</v>
       </c>
       <c r="B13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E13" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F13" t="n">
         <v>75589</v>
@@ -692,16 +692,16 @@
         <v>38835</v>
       </c>
       <c r="B14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E14" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F14" t="n">
         <v>75589</v>
@@ -712,16 +712,16 @@
         <v>38861</v>
       </c>
       <c r="B15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E15" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F15" t="n">
         <v>75589</v>
@@ -732,16 +732,16 @@
         <v>38896</v>
       </c>
       <c r="B16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E16" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F16" t="n">
         <v>831486</v>
@@ -752,16 +752,16 @@
         <v>38905</v>
       </c>
       <c r="B17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E17" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F17" t="n">
         <v>75589</v>
@@ -772,16 +772,16 @@
         <v>38922</v>
       </c>
       <c r="B18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E18" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F18" t="n">
         <v>151179</v>
@@ -792,16 +792,16 @@
         <v>39042</v>
       </c>
       <c r="B19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E19" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F19" t="n">
         <v>75589</v>
@@ -812,16 +812,16 @@
         <v>39048</v>
       </c>
       <c r="B20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E20" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F20" t="n">
         <v>377948</v>
@@ -832,16 +832,16 @@
         <v>39057</v>
       </c>
       <c r="B21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E21" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F21" t="n">
         <v>226768</v>
@@ -852,16 +852,16 @@
         <v>39070</v>
       </c>
       <c r="B22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E22" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F22" t="n">
         <v>151179</v>
@@ -872,16 +872,16 @@
         <v>39098</v>
       </c>
       <c r="B23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E23" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F23" t="n">
         <v>226768</v>
@@ -892,16 +892,16 @@
         <v>39121</v>
       </c>
       <c r="B24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E24" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F24" t="n">
         <v>226768</v>
@@ -912,16 +912,16 @@
         <v>39127</v>
       </c>
       <c r="B25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E25" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F25" t="n">
         <v>226768</v>
@@ -932,16 +932,16 @@
         <v>39128</v>
       </c>
       <c r="B26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E26" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F26" t="n">
         <v>226768</v>
@@ -952,16 +952,16 @@
         <v>39163</v>
       </c>
       <c r="B27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E27" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F27" t="n">
         <v>75589</v>
@@ -972,16 +972,16 @@
         <v>39189</v>
       </c>
       <c r="B28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E28" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F28" t="n">
         <v>75589</v>
@@ -992,16 +992,16 @@
         <v>39191</v>
       </c>
       <c r="B29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E29" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F29" t="n">
         <v>226768</v>
@@ -1012,16 +1012,16 @@
         <v>39196</v>
       </c>
       <c r="B30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E30" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F30" t="n">
         <v>75589</v>
@@ -1032,16 +1032,16 @@
         <v>39232</v>
       </c>
       <c r="B31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E31" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F31" t="n">
         <v>75589</v>
@@ -1052,16 +1052,16 @@
         <v>39237</v>
       </c>
       <c r="B32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E32" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F32" t="n">
         <v>75589</v>
@@ -1072,16 +1072,16 @@
         <v>39301</v>
       </c>
       <c r="B33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E33" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F33" t="n">
         <v>75589</v>
@@ -1092,16 +1092,16 @@
         <v>39310</v>
       </c>
       <c r="B34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E34" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F34" t="n">
         <v>151179</v>
@@ -1112,16 +1112,16 @@
         <v>39336</v>
       </c>
       <c r="B35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="C35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="D35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="E35" t="n">
-        <v>2.180156230926514</v>
+        <v>2.180156707763672</v>
       </c>
       <c r="F35" t="n">
         <v>755</v>
@@ -1152,16 +1152,16 @@
         <v>39393</v>
       </c>
       <c r="B37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="C37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="D37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="E37" t="n">
-        <v>2.125651597976685</v>
+        <v>2.125652074813843</v>
       </c>
       <c r="F37" t="n">
         <v>755</v>
@@ -1192,16 +1192,16 @@
         <v>39898</v>
       </c>
       <c r="B39" t="n">
-        <v>1.758486390113831</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="C39" t="n">
-        <v>1.758486390113831</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="D39" t="n">
-        <v>1.758486390113831</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="E39" t="n">
-        <v>1.758486390113831</v>
+        <v>1.758486747741699</v>
       </c>
       <c r="F39" t="n">
         <v>755</v>
@@ -1212,16 +1212,16 @@
         <v>39905</v>
       </c>
       <c r="B40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="C40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="D40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="E40" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="F40" t="n">
         <v>755</v>
@@ -1232,16 +1232,16 @@
         <v>39906</v>
       </c>
       <c r="B41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="C41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="D41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="E41" t="n">
-        <v>1.838212251663208</v>
+        <v>1.838212490081787</v>
       </c>
       <c r="F41" t="n">
         <v>755</v>
@@ -1252,16 +1252,16 @@
         <v>40245</v>
       </c>
       <c r="B42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="C42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="D42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="E42" t="n">
-        <v>4.647353649139404</v>
+        <v>4.647354125976562</v>
       </c>
       <c r="F42" t="n">
         <v>755</v>
@@ -1272,16 +1272,16 @@
         <v>42185</v>
       </c>
       <c r="B43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951083660125732</v>
       </c>
       <c r="C43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951083660125732</v>
       </c>
       <c r="D43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951083660125732</v>
       </c>
       <c r="E43" t="n">
-        <v>6.951083183288574</v>
+        <v>6.951083660125732</v>
       </c>
       <c r="F43" t="n">
         <v>755</v>
@@ -1292,16 +1292,16 @@
         <v>42214</v>
       </c>
       <c r="B44" t="n">
-        <v>6.997223854064941</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="C44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="D44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="E44" t="n">
-        <v>6.997223854064942</v>
+        <v>6.997222423553467</v>
       </c>
       <c r="F44" t="n">
         <v>755</v>
@@ -1312,16 +1312,16 @@
         <v>42285</v>
       </c>
       <c r="B45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="C45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="D45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="E45" t="n">
-        <v>5.294834136962891</v>
+        <v>5.294833660125732</v>
       </c>
       <c r="F45" t="n">
         <v>755</v>
@@ -1332,16 +1332,16 @@
         <v>42417</v>
       </c>
       <c r="B46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E46" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F46" t="n">
         <v>755</v>
@@ -1352,16 +1352,16 @@
         <v>42446</v>
       </c>
       <c r="B47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="C47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="D47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="E47" t="n">
-        <v>5.37096643447876</v>
+        <v>5.370966911315918</v>
       </c>
       <c r="F47" t="n">
         <v>755</v>
@@ -1372,16 +1372,16 @@
         <v>42453</v>
       </c>
       <c r="B48" t="n">
-        <v>3.926959037780762</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="C48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="D48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="E48" t="n">
-        <v>3.926959037780761</v>
+        <v>3.926958799362183</v>
       </c>
       <c r="F48" t="n">
         <v>755</v>
@@ -1512,16 +1512,16 @@
         <v>42853</v>
       </c>
       <c r="B55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="C55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="D55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="E55" t="n">
-        <v>7.075626373291016</v>
+        <v>7.075626850128174</v>
       </c>
       <c r="F55" t="n">
         <v>755</v>
@@ -1532,16 +1532,16 @@
         <v>42860</v>
       </c>
       <c r="B56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="C56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="D56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="E56" t="n">
-        <v>12.56045913696289</v>
+        <v>12.56045722961426</v>
       </c>
       <c r="F56" t="n">
         <v>755</v>
@@ -1552,16 +1552,16 @@
         <v>42864</v>
       </c>
       <c r="B57" t="n">
-        <v>12.68733310699463</v>
+        <v>12.68732929229736</v>
       </c>
       <c r="C57" t="n">
-        <v>12.68733310699463</v>
+        <v>12.68732929229736</v>
       </c>
       <c r="D57" t="n">
-        <v>12.68733310699463</v>
+        <v>12.68732929229736</v>
       </c>
       <c r="E57" t="n">
-        <v>12.68733310699463</v>
+        <v>12.68732929229736</v>
       </c>
       <c r="F57" t="n">
         <v>755</v>
@@ -1612,16 +1612,16 @@
         <v>43137</v>
       </c>
       <c r="B60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="C60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="D60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="E60" t="n">
-        <v>7.589142799377441</v>
+        <v>7.589141845703125</v>
       </c>
       <c r="F60" t="n">
         <v>3776</v>
@@ -1672,16 +1672,16 @@
         <v>43493</v>
       </c>
       <c r="B63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="C63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="D63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="E63" t="n">
-        <v>10.33257389068604</v>
+        <v>10.33257484436035</v>
       </c>
       <c r="F63" t="n">
         <v>755</v>
@@ -1692,16 +1692,16 @@
         <v>43507</v>
       </c>
       <c r="B64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="C64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="D64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="E64" t="n">
-        <v>9.014760971069336</v>
+        <v>9.01476001739502</v>
       </c>
       <c r="F64" t="n">
         <v>2265</v>
@@ -1712,16 +1712,16 @@
         <v>43508</v>
       </c>
       <c r="B65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="C65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="D65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="E65" t="n">
-        <v>10.27652072906494</v>
+        <v>10.27651977539062</v>
       </c>
       <c r="F65" t="n">
         <v>755</v>
@@ -1792,16 +1792,16 @@
         <v>43682</v>
       </c>
       <c r="B69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="C69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="D69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="E69" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="F69" t="n">
         <v>1510</v>
@@ -1812,16 +1812,16 @@
         <v>43683</v>
       </c>
       <c r="B70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="C70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="D70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="E70" t="n">
-        <v>11.20116233825684</v>
+        <v>11.20116329193115</v>
       </c>
       <c r="F70" t="n">
         <v>755</v>
@@ -1872,16 +1872,16 @@
         <v>43741</v>
       </c>
       <c r="B73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E73" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F73" t="n">
         <v>755</v>
@@ -1892,16 +1892,16 @@
         <v>43747</v>
       </c>
       <c r="B74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E74" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F74" t="n">
         <v>755</v>
@@ -1952,16 +1952,16 @@
         <v>43773</v>
       </c>
       <c r="B77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="E77" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="F77" t="n">
         <v>1510</v>
@@ -2012,16 +2012,16 @@
         <v>43802</v>
       </c>
       <c r="B80" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="C80" t="n">
-        <v>10.49992179870605</v>
+        <v>10.49992275238037</v>
       </c>
       <c r="D80" t="n">
-        <v>9.217621990355065</v>
+        <v>9.21762282756219</v>
       </c>
       <c r="E80" t="n">
-        <v>9.217621990355065</v>
+        <v>9.21762282756219</v>
       </c>
       <c r="F80" t="n">
         <v>1510</v>
@@ -2332,16 +2332,16 @@
         <v>43879</v>
       </c>
       <c r="B96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="C96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="D96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="E96" t="n">
-        <v>10.28640174865723</v>
+        <v>10.28640079498291</v>
       </c>
       <c r="F96" t="n">
         <v>755</v>
@@ -2432,16 +2432,16 @@
         <v>43894</v>
       </c>
       <c r="B101" t="n">
-        <v>8.692569732666016</v>
+        <v>8.692568778991699</v>
       </c>
       <c r="C101" t="n">
-        <v>8.802247729651036</v>
+        <v>8.80224676394379</v>
       </c>
       <c r="D101" t="n">
-        <v>8.564222836484587</v>
+        <v>8.564221896891393</v>
       </c>
       <c r="E101" t="n">
-        <v>8.734573285204156</v>
+        <v>8.734572326921571</v>
       </c>
       <c r="F101" t="n">
         <v>7583284</v>
@@ -2472,16 +2472,16 @@
         <v>43896</v>
       </c>
       <c r="B103" t="n">
-        <v>8.087005615234375</v>
+        <v>8.087006568908691</v>
       </c>
       <c r="C103" t="n">
-        <v>8.167514235155968</v>
+        <v>8.167515198324406</v>
       </c>
       <c r="D103" t="n">
-        <v>7.934155965259957</v>
+        <v>7.93415690090921</v>
       </c>
       <c r="E103" t="n">
-        <v>7.99249553273396</v>
+        <v>7.992496475263009</v>
       </c>
       <c r="F103" t="n">
         <v>19451755</v>
@@ -2532,16 +2532,16 @@
         <v>43901</v>
       </c>
       <c r="B106" t="n">
-        <v>7.280755519866943</v>
+        <v>7.280755043029785</v>
       </c>
       <c r="C106" t="n">
-        <v>7.652961180826241</v>
+        <v>7.652960679612288</v>
       </c>
       <c r="D106" t="n">
-        <v>6.825709192772189</v>
+        <v>6.825708745737296</v>
       </c>
       <c r="E106" t="n">
-        <v>7.467442830172282</v>
+        <v>7.467442341108447</v>
       </c>
       <c r="F106" t="n">
         <v>14927915</v>
@@ -2552,16 +2552,16 @@
         <v>43902</v>
       </c>
       <c r="B107" t="n">
-        <v>6.731198787689209</v>
+        <v>6.731198310852051</v>
       </c>
       <c r="C107" t="n">
-        <v>6.784870504526766</v>
+        <v>6.78487002388751</v>
       </c>
       <c r="D107" t="n">
-        <v>6.183975689474925</v>
+        <v>6.183975251402972</v>
       </c>
       <c r="E107" t="n">
-        <v>6.242314420779493</v>
+        <v>6.242313978574833</v>
       </c>
       <c r="F107" t="n">
         <v>9643557</v>
@@ -2632,16 +2632,16 @@
         <v>43908</v>
       </c>
       <c r="B111" t="n">
-        <v>6.98555850982666</v>
+        <v>6.985558032989502</v>
       </c>
       <c r="C111" t="n">
-        <v>8.075338544707167</v>
+        <v>8.075337993481165</v>
       </c>
       <c r="D111" t="n">
-        <v>6.71019666955442</v>
+        <v>6.710196211513576</v>
       </c>
       <c r="E111" t="n">
-        <v>7.140741469742403</v>
+        <v>7.140740982312391</v>
       </c>
       <c r="F111" t="n">
         <v>26337960</v>
@@ -2652,16 +2652,16 @@
         <v>43909</v>
       </c>
       <c r="B112" t="n">
-        <v>7.521113395690918</v>
+        <v>7.521113872528076</v>
       </c>
       <c r="C112" t="n">
-        <v>8.106841959390016</v>
+        <v>8.106842473362253</v>
       </c>
       <c r="D112" t="n">
-        <v>6.356659520848136</v>
+        <v>6.35665992385914</v>
       </c>
       <c r="E112" t="n">
-        <v>6.779036703963478</v>
+        <v>6.779037133753115</v>
       </c>
       <c r="F112" t="n">
         <v>19250108</v>
@@ -2692,16 +2692,16 @@
         <v>43913</v>
       </c>
       <c r="B114" t="n">
-        <v>8.386871337890625</v>
+        <v>8.386870384216309</v>
       </c>
       <c r="C114" t="n">
-        <v>8.386871337890625</v>
+        <v>8.386870384216309</v>
       </c>
       <c r="D114" t="n">
-        <v>7.483777299441991</v>
+        <v>7.48377644845884</v>
       </c>
       <c r="E114" t="n">
-        <v>8.050836190491395</v>
+        <v>8.050835275027762</v>
       </c>
       <c r="F114" t="n">
         <v>25091072</v>
@@ -2772,16 +2772,16 @@
         <v>43917</v>
       </c>
       <c r="B118" t="n">
-        <v>7.469775199890137</v>
+        <v>7.469774723052979</v>
       </c>
       <c r="C118" t="n">
-        <v>7.746304309853773</v>
+        <v>7.746303815364229</v>
       </c>
       <c r="D118" t="n">
-        <v>7.351929620609467</v>
+        <v>7.351929151295045</v>
       </c>
       <c r="E118" t="n">
-        <v>7.514113307020195</v>
+        <v>7.51411282735269</v>
       </c>
       <c r="F118" t="n">
         <v>14950572</v>
@@ -2792,16 +2792,16 @@
         <v>43920</v>
       </c>
       <c r="B119" t="n">
-        <v>7.584119319915771</v>
+        <v>7.58411979675293</v>
       </c>
       <c r="C119" t="n">
-        <v>7.677462963028194</v>
+        <v>7.677463445734158</v>
       </c>
       <c r="D119" t="n">
-        <v>7.322759808396101</v>
+        <v>7.322760268800774</v>
       </c>
       <c r="E119" t="n">
-        <v>7.354262888769144</v>
+        <v>7.354263351154514</v>
       </c>
       <c r="F119" t="n">
         <v>7283457</v>
@@ -2812,16 +2812,16 @@
         <v>43921</v>
       </c>
       <c r="B120" t="n">
-        <v>7.740469455718994</v>
+        <v>7.740469932556152</v>
       </c>
       <c r="C120" t="n">
-        <v>7.757971914786575</v>
+        <v>7.757972392701939</v>
       </c>
       <c r="D120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="E120" t="n">
-        <v>7.452272604987874</v>
+        <v>7.452273064071203</v>
       </c>
       <c r="F120" t="n">
         <v>7688261</v>
@@ -2892,16 +2892,16 @@
         <v>43927</v>
       </c>
       <c r="B124" t="n">
-        <v>7.613289833068848</v>
+        <v>7.613289356231689</v>
       </c>
       <c r="C124" t="n">
-        <v>7.699632328290281</v>
+        <v>7.699631846045301</v>
       </c>
       <c r="D124" t="n">
-        <v>7.497777973422238</v>
+        <v>7.497777503819842</v>
       </c>
       <c r="E124" t="n">
-        <v>7.584119628270164</v>
+        <v>7.58411915326</v>
       </c>
       <c r="F124" t="n">
         <v>9888252</v>
@@ -2912,16 +2912,16 @@
         <v>43928</v>
       </c>
       <c r="B125" t="n">
-        <v>7.672797203063965</v>
+        <v>7.672796726226807</v>
       </c>
       <c r="C125" t="n">
-        <v>8.109175462567777</v>
+        <v>8.109174958611256</v>
       </c>
       <c r="D125" t="n">
-        <v>7.661129456500152</v>
+        <v>7.661128980388104</v>
       </c>
       <c r="E125" t="n">
-        <v>7.84081477047941</v>
+        <v>7.840814283200555</v>
       </c>
       <c r="F125" t="n">
         <v>10624603</v>
@@ -2932,16 +2932,16 @@
         <v>43929</v>
       </c>
       <c r="B126" t="n">
-        <v>7.700798511505127</v>
+        <v>7.700798988342285</v>
       </c>
       <c r="C126" t="n">
-        <v>7.781307131173381</v>
+        <v>7.781307612995673</v>
       </c>
       <c r="D126" t="n">
-        <v>7.362430533892927</v>
+        <v>7.362430989778177</v>
       </c>
       <c r="E126" t="n">
-        <v>7.678629459127295</v>
+        <v>7.678629934591736</v>
       </c>
       <c r="F126" t="n">
         <v>12945431</v>
@@ -2952,16 +2952,16 @@
         <v>43930</v>
       </c>
       <c r="B127" t="n">
-        <v>7.385766506195068</v>
+        <v>7.38576602935791</v>
       </c>
       <c r="C127" t="n">
-        <v>7.778973921193609</v>
+        <v>7.778973418970338</v>
       </c>
       <c r="D127" t="n">
-        <v>7.351929706227764</v>
+        <v>7.351929231575166</v>
       </c>
       <c r="E127" t="n">
-        <v>7.778973921193609</v>
+        <v>7.778973418970338</v>
       </c>
       <c r="F127" t="n">
         <v>7590081</v>
@@ -2972,16 +2972,16 @@
         <v>43934</v>
       </c>
       <c r="B128" t="n">
-        <v>7.414936065673828</v>
+        <v>7.41493558883667</v>
       </c>
       <c r="C128" t="n">
-        <v>7.447606428031426</v>
+        <v>7.447605949093313</v>
       </c>
       <c r="D128" t="n">
-        <v>7.22941688022938</v>
+        <v>7.229416415322526</v>
       </c>
       <c r="E128" t="n">
-        <v>7.385766699549943</v>
+        <v>7.385766224588598</v>
       </c>
       <c r="F128" t="n">
         <v>8873976</v>
@@ -3012,16 +3012,16 @@
         <v>43936</v>
       </c>
       <c r="B130" t="n">
-        <v>7.375264644622803</v>
+        <v>7.375265121459961</v>
       </c>
       <c r="C130" t="n">
-        <v>7.494277495176356</v>
+        <v>7.49427797970812</v>
       </c>
       <c r="D130" t="n">
-        <v>7.343761564324954</v>
+        <v>7.343762039125325</v>
       </c>
       <c r="E130" t="n">
-        <v>7.407935003671517</v>
+        <v>7.407935482620931</v>
       </c>
       <c r="F130" t="n">
         <v>8695741</v>
@@ -3072,16 +3072,16 @@
         <v>43941</v>
       </c>
       <c r="B133" t="n">
-        <v>7.584119319915771</v>
+        <v>7.58411979675293</v>
       </c>
       <c r="C133" t="n">
-        <v>7.592287750070918</v>
+        <v>7.592288227421651</v>
       </c>
       <c r="D133" t="n">
-        <v>7.316925095374786</v>
+        <v>7.316925555412612</v>
       </c>
       <c r="E133" t="n">
-        <v>7.350762733255134</v>
+        <v>7.350763195420438</v>
       </c>
       <c r="F133" t="n">
         <v>10524157</v>
@@ -3112,16 +3112,16 @@
         <v>43944</v>
       </c>
       <c r="B135" t="n">
-        <v>8.089340209960938</v>
+        <v>8.089339256286621</v>
       </c>
       <c r="C135" t="n">
-        <v>8.574724018558863</v>
+        <v>8.57472300766133</v>
       </c>
       <c r="D135" t="n">
-        <v>7.969160906424007</v>
+        <v>7.969159966917957</v>
       </c>
       <c r="E135" t="n">
-        <v>8.481380364324728</v>
+        <v>8.481379364431731</v>
       </c>
       <c r="F135" t="n">
         <v>13472583</v>
@@ -3152,16 +3152,16 @@
         <v>43948</v>
       </c>
       <c r="B137" t="n">
-        <v>8.105674743652344</v>
+        <v>8.105673789978027</v>
       </c>
       <c r="C137" t="n">
-        <v>8.165180757388045</v>
+        <v>8.16517979671254</v>
       </c>
       <c r="D137" t="n">
-        <v>7.710134423961201</v>
+        <v>7.710133516824237</v>
       </c>
       <c r="E137" t="n">
-        <v>7.93765801086142</v>
+        <v>7.937657076955135</v>
       </c>
       <c r="F137" t="n">
         <v>12260436</v>
@@ -3172,16 +3172,16 @@
         <v>43949</v>
       </c>
       <c r="B138" t="n">
-        <v>7.822145938873291</v>
+        <v>7.822145462036133</v>
       </c>
       <c r="C138" t="n">
-        <v>8.301695873226397</v>
+        <v>8.301695367155927</v>
       </c>
       <c r="D138" t="n">
-        <v>7.804644318877395</v>
+        <v>7.804643843107134</v>
       </c>
       <c r="E138" t="n">
-        <v>8.167515105844055</v>
+        <v>8.167514607953231</v>
       </c>
       <c r="F138" t="n">
         <v>14579753</v>
@@ -3212,16 +3212,16 @@
         <v>43951</v>
       </c>
       <c r="B140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726467609405518</v>
       </c>
       <c r="C140" t="n">
-        <v>7.882817898699254</v>
+        <v>7.882817412213003</v>
       </c>
       <c r="D140" t="n">
-        <v>7.726468086242676</v>
+        <v>7.726467609405518</v>
       </c>
       <c r="E140" t="n">
-        <v>7.816311578781807</v>
+        <v>7.816311096399979</v>
       </c>
       <c r="F140" t="n">
         <v>11836751</v>
@@ -3252,16 +3252,16 @@
         <v>43956</v>
       </c>
       <c r="B142" t="n">
-        <v>8.114090919494629</v>
+        <v>8.114091873168945</v>
       </c>
       <c r="C142" t="n">
-        <v>8.645023715587479</v>
+        <v>8.645024731663977</v>
       </c>
       <c r="D142" t="n">
-        <v>8.069432995707503</v>
+        <v>8.069433944133035</v>
       </c>
       <c r="E142" t="n">
-        <v>8.286520199683441</v>
+        <v>8.286521173623905</v>
       </c>
       <c r="F142" t="n">
         <v>11843548</v>
@@ -3272,16 +3272,16 @@
         <v>43957</v>
       </c>
       <c r="B143" t="n">
-        <v>8.048345565795898</v>
+        <v>8.048344612121582</v>
       </c>
       <c r="C143" t="n">
-        <v>8.145104858936216</v>
+        <v>8.145103893796581</v>
       </c>
       <c r="D143" t="n">
-        <v>7.963991997516411</v>
+        <v>7.96399105383742</v>
       </c>
       <c r="E143" t="n">
-        <v>8.145104858936216</v>
+        <v>8.145103893796581</v>
       </c>
       <c r="F143" t="n">
         <v>16545622</v>
@@ -3312,16 +3312,16 @@
         <v>43959</v>
       </c>
       <c r="B145" t="n">
-        <v>8.162469863891602</v>
+        <v>8.162470817565918</v>
       </c>
       <c r="C145" t="n">
-        <v>8.184799271833279</v>
+        <v>8.184800228116485</v>
       </c>
       <c r="D145" t="n">
-        <v>7.94786381115636</v>
+        <v>7.947864739756858</v>
       </c>
       <c r="E145" t="n">
-        <v>8.15626744912163</v>
+        <v>8.156268402071278</v>
       </c>
       <c r="F145" t="n">
         <v>8818844</v>
@@ -3352,16 +3352,16 @@
         <v>43963</v>
       </c>
       <c r="B147" t="n">
-        <v>8.085558891296387</v>
+        <v>8.085559844970703</v>
       </c>
       <c r="C147" t="n">
-        <v>8.276595411529883</v>
+        <v>8.276596387736546</v>
       </c>
       <c r="D147" t="n">
-        <v>8.063229483236768</v>
+        <v>8.063230434277379</v>
       </c>
       <c r="E147" t="n">
-        <v>8.187279566215866</v>
+        <v>8.187280531887918</v>
       </c>
       <c r="F147" t="n">
         <v>9953957</v>
@@ -3372,16 +3372,16 @@
         <v>43964</v>
       </c>
       <c r="B148" t="n">
-        <v>7.926775455474854</v>
+        <v>7.926775932312012</v>
       </c>
       <c r="C148" t="n">
-        <v>8.187279557292356</v>
+        <v>8.187280049800203</v>
       </c>
       <c r="D148" t="n">
-        <v>7.885839696513885</v>
+        <v>7.885840170888542</v>
       </c>
       <c r="E148" t="n">
-        <v>8.187279557292356</v>
+        <v>8.187280049800203</v>
       </c>
       <c r="F148" t="n">
         <v>10179016</v>
@@ -3412,16 +3412,16 @@
         <v>43966</v>
       </c>
       <c r="B150" t="n">
-        <v>6.8413405418396</v>
+        <v>6.841341018676758</v>
       </c>
       <c r="C150" t="n">
-        <v>7.421893104642092</v>
+        <v>7.421893621943401</v>
       </c>
       <c r="D150" t="n">
-        <v>6.8413405418396</v>
+        <v>6.841341018676758</v>
       </c>
       <c r="E150" t="n">
-        <v>7.420652532303285</v>
+        <v>7.420653049518127</v>
       </c>
       <c r="F150" t="n">
         <v>26563775</v>
@@ -3452,16 +3452,16 @@
         <v>43970</v>
       </c>
       <c r="B152" t="n">
-        <v>6.831418037414551</v>
+        <v>6.831417560577393</v>
       </c>
       <c r="C152" t="n">
-        <v>7.018732418962401</v>
+        <v>7.018731929050585</v>
       </c>
       <c r="D152" t="n">
-        <v>6.79916449333305</v>
+        <v>6.799164018747209</v>
       </c>
       <c r="E152" t="n">
-        <v>6.966631502251738</v>
+        <v>6.966631015976597</v>
       </c>
       <c r="F152" t="n">
         <v>13463520</v>
@@ -3472,16 +3472,16 @@
         <v>43971</v>
       </c>
       <c r="B153" t="n">
-        <v>6.822733879089355</v>
+        <v>6.822733402252197</v>
       </c>
       <c r="C153" t="n">
-        <v>6.983998022077899</v>
+        <v>6.983997533970078</v>
       </c>
       <c r="D153" t="n">
-        <v>6.810329048105121</v>
+        <v>6.81032857213493</v>
       </c>
       <c r="E153" t="n">
-        <v>6.94678397585636</v>
+        <v>6.946783490349408</v>
       </c>
       <c r="F153" t="n">
         <v>11533147</v>
@@ -3552,16 +3552,16 @@
         <v>43977</v>
       </c>
       <c r="B157" t="n">
-        <v>7.423134803771973</v>
+        <v>7.423134326934814</v>
       </c>
       <c r="C157" t="n">
-        <v>7.560829411371671</v>
+        <v>7.560828925689475</v>
       </c>
       <c r="D157" t="n">
-        <v>7.275515169821428</v>
+        <v>7.275514702466858</v>
       </c>
       <c r="E157" t="n">
-        <v>7.442982622817829</v>
+        <v>7.442982144705714</v>
       </c>
       <c r="F157" t="n">
         <v>12080691</v>
@@ -3612,16 +3612,16 @@
         <v>43980</v>
       </c>
       <c r="B160" t="n">
-        <v>7.812650203704834</v>
+        <v>7.812650680541992</v>
       </c>
       <c r="C160" t="n">
-        <v>7.812650203704834</v>
+        <v>7.812650680541992</v>
       </c>
       <c r="D160" t="n">
-        <v>7.481437043617326</v>
+        <v>7.481437500239227</v>
       </c>
       <c r="E160" t="n">
-        <v>7.519892999404318</v>
+        <v>7.519893458373339</v>
       </c>
       <c r="F160" t="n">
         <v>23712019</v>
@@ -3652,16 +3652,16 @@
         <v>43984</v>
       </c>
       <c r="B162" t="n">
-        <v>8.271634101867676</v>
+        <v>8.271635055541992</v>
       </c>
       <c r="C162" t="n">
-        <v>8.286520076241633</v>
+        <v>8.286521031632221</v>
       </c>
       <c r="D162" t="n">
-        <v>7.976395759027911</v>
+        <v>7.976396678662855</v>
       </c>
       <c r="E162" t="n">
-        <v>8.063229567170044</v>
+        <v>8.063230496816454</v>
       </c>
       <c r="F162" t="n">
         <v>21348142</v>
@@ -3672,16 +3672,16 @@
         <v>43985</v>
       </c>
       <c r="B163" t="n">
-        <v>8.373354911804199</v>
+        <v>8.373353958129883</v>
       </c>
       <c r="C163" t="n">
-        <v>8.800086825192951</v>
+        <v>8.80008582291646</v>
       </c>
       <c r="D163" t="n">
-        <v>8.315052026205343</v>
+        <v>8.315051079171372</v>
       </c>
       <c r="E163" t="n">
-        <v>8.317533171149149</v>
+        <v>8.31753222383259</v>
       </c>
       <c r="F163" t="n">
         <v>31125376</v>
@@ -3752,16 +3752,16 @@
         <v>43991</v>
       </c>
       <c r="B167" t="n">
-        <v>8.296442985534668</v>
+        <v>8.296443939208984</v>
       </c>
       <c r="C167" t="n">
-        <v>8.327455953773208</v>
+        <v>8.32745691101246</v>
       </c>
       <c r="D167" t="n">
-        <v>8.096723794435762</v>
+        <v>8.0967247251524</v>
       </c>
       <c r="E167" t="n">
-        <v>8.137660447910266</v>
+        <v>8.137661383332564</v>
       </c>
       <c r="F167" t="n">
         <v>13675741</v>
@@ -3772,16 +3772,16 @@
         <v>43992</v>
       </c>
       <c r="B168" t="n">
-        <v>8.08928108215332</v>
+        <v>8.089280128479004</v>
       </c>
       <c r="C168" t="n">
-        <v>8.426697131827968</v>
+        <v>8.426696138374464</v>
       </c>
       <c r="D168" t="n">
-        <v>8.0371806131882</v>
+        <v>8.037179665656195</v>
       </c>
       <c r="E168" t="n">
-        <v>8.311330595134894</v>
+        <v>8.311329615282364</v>
       </c>
       <c r="F168" t="n">
         <v>11944749</v>
@@ -3792,16 +3792,16 @@
         <v>43994</v>
       </c>
       <c r="B169" t="n">
-        <v>7.950345993041992</v>
+        <v>7.950345516204834</v>
       </c>
       <c r="C169" t="n">
-        <v>8.084319777785</v>
+        <v>8.084319292912509</v>
       </c>
       <c r="D169" t="n">
-        <v>7.774195424975465</v>
+        <v>7.774194958703272</v>
       </c>
       <c r="E169" t="n">
-        <v>7.877157131822456</v>
+        <v>7.877156659374939</v>
       </c>
       <c r="F169" t="n">
         <v>12251373</v>
@@ -3892,16 +3892,16 @@
         <v>44001</v>
       </c>
       <c r="B174" t="n">
-        <v>8.487480163574219</v>
+        <v>8.487481117248535</v>
       </c>
       <c r="C174" t="n">
-        <v>8.589200838114557</v>
+        <v>8.58920180321846</v>
       </c>
       <c r="D174" t="n">
-        <v>8.203406528896336</v>
+        <v>8.203407450651435</v>
       </c>
       <c r="E174" t="n">
-        <v>8.203406528896336</v>
+        <v>8.203407450651435</v>
       </c>
       <c r="F174" t="n">
         <v>20750754</v>
@@ -3912,16 +3912,16 @@
         <v>44004</v>
       </c>
       <c r="B175" t="n">
-        <v>8.440342903137207</v>
+        <v>8.440341949462891</v>
       </c>
       <c r="C175" t="n">
-        <v>8.729377964833343</v>
+        <v>8.729376978500955</v>
       </c>
       <c r="D175" t="n">
-        <v>8.380798106578508</v>
+        <v>8.380797159632158</v>
       </c>
       <c r="E175" t="n">
-        <v>8.489962226742637</v>
+        <v>8.489961267461833</v>
       </c>
       <c r="F175" t="n">
         <v>12069362</v>
@@ -3952,16 +3952,16 @@
         <v>44006</v>
       </c>
       <c r="B177" t="n">
-        <v>8.594162940979004</v>
+        <v>8.59416389465332</v>
       </c>
       <c r="C177" t="n">
-        <v>8.669832935726904</v>
+        <v>8.669833897798144</v>
       </c>
       <c r="D177" t="n">
-        <v>8.422973795079262</v>
+        <v>8.422974729757115</v>
       </c>
       <c r="E177" t="n">
-        <v>8.571833533486773</v>
+        <v>8.571834484683247</v>
       </c>
       <c r="F177" t="n">
         <v>7388434</v>
@@ -4052,16 +4052,16 @@
         <v>44013</v>
       </c>
       <c r="B182" t="n">
-        <v>9.009730339050293</v>
+        <v>9.009729385375977</v>
       </c>
       <c r="C182" t="n">
-        <v>9.11517229493286</v>
+        <v>9.115171330097578</v>
       </c>
       <c r="D182" t="n">
-        <v>8.731859089723871</v>
+        <v>8.731858165462054</v>
       </c>
       <c r="E182" t="n">
-        <v>8.812491383860499</v>
+        <v>8.812490451063802</v>
       </c>
       <c r="F182" t="n">
         <v>8963093</v>
@@ -4292,16 +4292,16 @@
         <v>44029</v>
       </c>
       <c r="B194" t="n">
-        <v>8.81993293762207</v>
+        <v>8.819933891296387</v>
       </c>
       <c r="C194" t="n">
-        <v>8.919173360420668</v>
+        <v>8.919174324825571</v>
       </c>
       <c r="D194" t="n">
-        <v>8.633858708433587</v>
+        <v>8.633859641988225</v>
       </c>
       <c r="E194" t="n">
-        <v>8.633858708433587</v>
+        <v>8.633859641988225</v>
       </c>
       <c r="F194" t="n">
         <v>9678298</v>
@@ -4432,16 +4432,16 @@
         <v>44040</v>
       </c>
       <c r="B201" t="n">
-        <v>9.641143798828125</v>
+        <v>9.641142845153809</v>
       </c>
       <c r="C201" t="n">
-        <v>9.832180339834917</v>
+        <v>9.832179367263814</v>
       </c>
       <c r="D201" t="n">
-        <v>9.466233359369541</v>
+        <v>9.466232422996864</v>
       </c>
       <c r="E201" t="n">
-        <v>9.675878040270206</v>
+        <v>9.67587708316008</v>
       </c>
       <c r="F201" t="n">
         <v>30127714</v>
@@ -4472,16 +4472,16 @@
         <v>44042</v>
       </c>
       <c r="B203" t="n">
-        <v>9.143704414367676</v>
+        <v>9.143703460693359</v>
       </c>
       <c r="C203" t="n">
-        <v>9.700687950073165</v>
+        <v>9.700686938306321</v>
       </c>
       <c r="D203" t="n">
-        <v>9.097806359971171</v>
+        <v>9.097805411083952</v>
       </c>
       <c r="E203" t="n">
-        <v>9.685801080392711</v>
+        <v>9.685800070178546</v>
       </c>
       <c r="F203" t="n">
         <v>33272500</v>
@@ -4592,16 +4592,16 @@
         <v>44050</v>
       </c>
       <c r="B209" t="n">
-        <v>8.429177284240723</v>
+        <v>8.429178237915039</v>
       </c>
       <c r="C209" t="n">
-        <v>8.429177284240723</v>
+        <v>8.429178237915039</v>
       </c>
       <c r="D209" t="n">
-        <v>8.255506990060143</v>
+        <v>8.25550792408546</v>
       </c>
       <c r="E209" t="n">
-        <v>8.336140169103194</v>
+        <v>8.336141112251321</v>
       </c>
       <c r="F209" t="n">
         <v>22110172</v>
@@ -4612,16 +4612,16 @@
         <v>44053</v>
       </c>
       <c r="B210" t="n">
-        <v>8.259230613708496</v>
+        <v>8.25922966003418</v>
       </c>
       <c r="C210" t="n">
-        <v>8.468874414585619</v>
+        <v>8.468873436704216</v>
       </c>
       <c r="D210" t="n">
-        <v>8.166192588662099</v>
+        <v>8.166191645730668</v>
       </c>
       <c r="E210" t="n">
-        <v>8.435380296706972</v>
+        <v>8.435379322693057</v>
       </c>
       <c r="F210" t="n">
         <v>21920608</v>
@@ -4652,16 +4652,16 @@
         <v>44055</v>
       </c>
       <c r="B212" t="n">
-        <v>8.162469863891602</v>
+        <v>8.162470817565918</v>
       </c>
       <c r="C212" t="n">
-        <v>8.446543498127859</v>
+        <v>8.446544484992341</v>
       </c>
       <c r="D212" t="n">
-        <v>8.078115414787984</v>
+        <v>8.078116358606623</v>
       </c>
       <c r="E212" t="n">
-        <v>8.409329009508031</v>
+        <v>8.409329992024503</v>
       </c>
       <c r="F212" t="n">
         <v>20200945</v>
@@ -4732,16 +4732,16 @@
         <v>44061</v>
       </c>
       <c r="B216" t="n">
-        <v>8.101686477661133</v>
+        <v>8.101685523986816</v>
       </c>
       <c r="C216" t="n">
-        <v>8.143864156905972</v>
+        <v>8.143863198266791</v>
       </c>
       <c r="D216" t="n">
-        <v>7.9788782846482</v>
+        <v>7.978877345430011</v>
       </c>
       <c r="E216" t="n">
-        <v>8.038421298987467</v>
+        <v>8.038420352760289</v>
       </c>
       <c r="F216" t="n">
         <v>10608743</v>
@@ -4752,16 +4752,16 @@
         <v>44062</v>
       </c>
       <c r="B217" t="n">
-        <v>7.926775455474854</v>
+        <v>7.926775932312012</v>
       </c>
       <c r="C217" t="n">
-        <v>8.141381509109719</v>
+        <v>8.141381998856557</v>
       </c>
       <c r="D217" t="n">
-        <v>7.921813166253184</v>
+        <v>7.921813642791834</v>
       </c>
       <c r="E217" t="n">
-        <v>8.141381509109719</v>
+        <v>8.141381998856557</v>
       </c>
       <c r="F217" t="n">
         <v>9466833</v>
@@ -4772,16 +4772,16 @@
         <v>44063</v>
       </c>
       <c r="B218" t="n">
-        <v>7.957788467407227</v>
+        <v>7.957787990570068</v>
       </c>
       <c r="C218" t="n">
-        <v>8.033459366376674</v>
+        <v>8.033458885005254</v>
       </c>
       <c r="D218" t="n">
-        <v>7.774195359575069</v>
+        <v>7.774194893738959</v>
       </c>
       <c r="E218" t="n">
-        <v>7.915611684438519</v>
+        <v>7.915611210128628</v>
       </c>
       <c r="F218" t="n">
         <v>7652765</v>
@@ -4892,16 +4892,16 @@
         <v>44071</v>
       </c>
       <c r="B224" t="n">
-        <v>8.100445747375488</v>
+        <v>8.100444793701172</v>
       </c>
       <c r="C224" t="n">
-        <v>8.100445747375488</v>
+        <v>8.100444793701172</v>
       </c>
       <c r="D224" t="n">
-        <v>7.960269549341362</v>
+        <v>7.960268612170143</v>
       </c>
       <c r="E224" t="n">
-        <v>8.0012070997281</v>
+        <v>8.001206157737258</v>
       </c>
       <c r="F224" t="n">
         <v>5577388</v>
@@ -5012,16 +5012,16 @@
         <v>44082</v>
       </c>
       <c r="B230" t="n">
-        <v>7.751865863800049</v>
+        <v>7.751865386962891</v>
       </c>
       <c r="C230" t="n">
-        <v>7.833738283935308</v>
+        <v>7.833737802061967</v>
       </c>
       <c r="D230" t="n">
-        <v>7.691081834917614</v>
+        <v>7.691081361819436</v>
       </c>
       <c r="E230" t="n">
-        <v>7.813890911851665</v>
+        <v>7.813890431199186</v>
       </c>
       <c r="F230" t="n">
         <v>7181501</v>
@@ -5032,16 +5032,16 @@
         <v>44083</v>
       </c>
       <c r="B231" t="n">
-        <v>7.709688663482666</v>
+        <v>7.709689140319824</v>
       </c>
       <c r="C231" t="n">
-        <v>7.834979771965168</v>
+        <v>7.834980256551466</v>
       </c>
       <c r="D231" t="n">
-        <v>7.637739933288351</v>
+        <v>7.637740405675546</v>
       </c>
       <c r="E231" t="n">
-        <v>7.792802098282933</v>
+        <v>7.792802580260581</v>
       </c>
       <c r="F231" t="n">
         <v>8282629</v>
@@ -5052,16 +5052,16 @@
         <v>44084</v>
       </c>
       <c r="B232" t="n">
-        <v>8.850947380065918</v>
+        <v>8.850946426391602</v>
       </c>
       <c r="C232" t="n">
-        <v>9.197045218135978</v>
+        <v>9.197044227170217</v>
       </c>
       <c r="D232" t="n">
-        <v>8.621455315968662</v>
+        <v>8.62145438702172</v>
       </c>
       <c r="E232" t="n">
-        <v>9.197045218135978</v>
+        <v>9.197044227170217</v>
       </c>
       <c r="F232" t="n">
         <v>139609921</v>
@@ -5132,16 +5132,16 @@
         <v>44090</v>
       </c>
       <c r="B236" t="n">
-        <v>9.312410354614258</v>
+        <v>9.312411308288574</v>
       </c>
       <c r="C236" t="n">
-        <v>9.375675522060035</v>
+        <v>9.375676482213272</v>
       </c>
       <c r="D236" t="n">
-        <v>9.175956334671081</v>
+        <v>9.175957274371282</v>
       </c>
       <c r="E236" t="n">
-        <v>9.179677604882659</v>
+        <v>9.179678544963952</v>
       </c>
       <c r="F236" t="n">
         <v>13993693</v>
@@ -5212,16 +5212,16 @@
         <v>44096</v>
       </c>
       <c r="B240" t="n">
-        <v>9.326058387756348</v>
+        <v>9.326057434082031</v>
       </c>
       <c r="C240" t="n">
-        <v>9.353349195522698</v>
+        <v>9.353348239057649</v>
       </c>
       <c r="D240" t="n">
-        <v>9.182159127084132</v>
+        <v>9.182158188124824</v>
       </c>
       <c r="E240" t="n">
-        <v>9.192083706971793</v>
+        <v>9.192082766997606</v>
       </c>
       <c r="F240" t="n">
         <v>9315031</v>
@@ -5232,16 +5232,16 @@
         <v>44097</v>
       </c>
       <c r="B241" t="n">
-        <v>8.95390796661377</v>
+        <v>8.953908920288086</v>
       </c>
       <c r="C241" t="n">
-        <v>9.308689320943529</v>
+        <v>9.308690312405352</v>
       </c>
       <c r="D241" t="n">
-        <v>8.934059702543932</v>
+        <v>8.934060654104224</v>
       </c>
       <c r="E241" t="n">
-        <v>9.303727925022763</v>
+        <v>9.303728915956151</v>
       </c>
       <c r="F241" t="n">
         <v>13677251</v>
@@ -5252,16 +5252,16 @@
         <v>44098</v>
       </c>
       <c r="B242" t="n">
-        <v>9.282639503479004</v>
+        <v>9.282638549804688</v>
       </c>
       <c r="C242" t="n">
-        <v>9.46375236122295</v>
+        <v>9.463751388941567</v>
       </c>
       <c r="D242" t="n">
-        <v>8.898085270619518</v>
+        <v>8.898084356453305</v>
       </c>
       <c r="E242" t="n">
-        <v>8.906769724577019</v>
+        <v>8.906768809518589</v>
       </c>
       <c r="F242" t="n">
         <v>18607406</v>
@@ -5272,16 +5272,16 @@
         <v>44099</v>
       </c>
       <c r="B243" t="n">
-        <v>9.184640884399414</v>
+        <v>9.184639930725098</v>
       </c>
       <c r="C243" t="n">
-        <v>9.254108474175018</v>
+        <v>9.25410751328763</v>
       </c>
       <c r="D243" t="n">
-        <v>9.095325028918353</v>
+        <v>9.095324084518023</v>
       </c>
       <c r="E243" t="n">
-        <v>9.22061435827287</v>
+        <v>9.220613400863298</v>
       </c>
       <c r="F243" t="n">
         <v>8201819</v>
@@ -5312,16 +5312,16 @@
         <v>44103</v>
       </c>
       <c r="B245" t="n">
-        <v>8.760390281677246</v>
+        <v>8.760391235351562</v>
       </c>
       <c r="C245" t="n">
-        <v>8.942743247933565</v>
+        <v>8.942744221459206</v>
       </c>
       <c r="D245" t="n">
-        <v>8.683479263674647</v>
+        <v>8.68348020897627</v>
       </c>
       <c r="E245" t="n">
-        <v>8.802567060978735</v>
+        <v>8.802568019244504</v>
       </c>
       <c r="F245" t="n">
         <v>13985386</v>
@@ -5332,16 +5332,16 @@
         <v>44104</v>
       </c>
       <c r="B246" t="n">
-        <v>8.651226997375488</v>
+        <v>8.651226043701172</v>
       </c>
       <c r="C246" t="n">
-        <v>8.841023415853394</v>
+        <v>8.841022441256731</v>
       </c>
       <c r="D246" t="n">
-        <v>8.609050214038696</v>
+        <v>8.609049265013768</v>
       </c>
       <c r="E246" t="n">
-        <v>8.803808028904122</v>
+        <v>8.803807058409923</v>
       </c>
       <c r="F246" t="n">
         <v>11477260</v>
@@ -5412,16 +5412,16 @@
         <v>44110</v>
       </c>
       <c r="B250" t="n">
-        <v>8.497404098510742</v>
+        <v>8.497405052185059</v>
       </c>
       <c r="C250" t="n">
-        <v>8.520973632751547</v>
+        <v>8.520974589071102</v>
       </c>
       <c r="D250" t="n">
-        <v>8.3162921520784</v>
+        <v>8.316293085426295</v>
       </c>
       <c r="E250" t="n">
-        <v>8.48872053887138</v>
+        <v>8.488721491571129</v>
       </c>
       <c r="F250" t="n">
         <v>10544549</v>
@@ -5432,16 +5432,16 @@
         <v>44111</v>
       </c>
       <c r="B251" t="n">
-        <v>8.585479736328125</v>
+        <v>8.585480690002441</v>
       </c>
       <c r="C251" t="n">
-        <v>8.704567531971968</v>
+        <v>8.704568498874545</v>
       </c>
       <c r="D251" t="n">
-        <v>8.440342155483876</v>
+        <v>8.440343093036322</v>
       </c>
       <c r="E251" t="n">
-        <v>8.477556644891454</v>
+        <v>8.477557586577683</v>
       </c>
       <c r="F251" t="n">
         <v>12680345</v>
@@ -5552,16 +5552,16 @@
         <v>44120</v>
       </c>
       <c r="B257" t="n">
-        <v>8.259230613708496</v>
+        <v>8.25922966003418</v>
       </c>
       <c r="C257" t="n">
-        <v>8.267913281163274</v>
+        <v>8.267912326486389</v>
       </c>
       <c r="D257" t="n">
-        <v>8.097965120577188</v>
+        <v>8.097964185523827</v>
       </c>
       <c r="E257" t="n">
-        <v>8.122775677538673</v>
+        <v>8.122774739620494</v>
       </c>
       <c r="F257" t="n">
         <v>10726560</v>
@@ -5612,16 +5612,16 @@
         <v>44125</v>
       </c>
       <c r="B260" t="n">
-        <v>8.275356292724609</v>
+        <v>8.275355339050293</v>
       </c>
       <c r="C260" t="n">
-        <v>8.355988588431988</v>
+        <v>8.355987625465389</v>
       </c>
       <c r="D260" t="n">
-        <v>8.245584340664582</v>
+        <v>8.245583390421267</v>
       </c>
       <c r="E260" t="n">
-        <v>8.35474846270546</v>
+        <v>8.354747499881778</v>
       </c>
       <c r="F260" t="n">
         <v>4665068</v>
@@ -5632,16 +5632,16 @@
         <v>44126</v>
       </c>
       <c r="B261" t="n">
-        <v>8.267912864685059</v>
+        <v>8.267911911010742</v>
       </c>
       <c r="C261" t="n">
-        <v>8.337381348523031</v>
+        <v>8.337380386835774</v>
       </c>
       <c r="D261" t="n">
-        <v>8.168674215687588</v>
+        <v>8.168673273460097</v>
       </c>
       <c r="E261" t="n">
-        <v>8.306368377248981</v>
+        <v>8.30636741913896</v>
       </c>
       <c r="F261" t="n">
         <v>7908034</v>
@@ -5652,16 +5652,16 @@
         <v>44127</v>
       </c>
       <c r="B262" t="n">
-        <v>8.234420776367188</v>
+        <v>8.234419822692871</v>
       </c>
       <c r="C262" t="n">
-        <v>8.312571929509362</v>
+        <v>8.312570966783923</v>
       </c>
       <c r="D262" t="n">
-        <v>8.203407804185662</v>
+        <v>8.203406854103131</v>
       </c>
       <c r="E262" t="n">
-        <v>8.269153232377807</v>
+        <v>8.269152274680931</v>
       </c>
       <c r="F262" t="n">
         <v>5098571</v>
@@ -5712,16 +5712,16 @@
         <v>44132</v>
       </c>
       <c r="B265" t="n">
-        <v>7.825055122375488</v>
+        <v>7.825055599212646</v>
       </c>
       <c r="C265" t="n">
-        <v>8.088040380288025</v>
+        <v>8.088040873150774</v>
       </c>
       <c r="D265" t="n">
-        <v>7.81761168821794</v>
+        <v>7.817612164601516</v>
       </c>
       <c r="E265" t="n">
-        <v>8.078115801411293</v>
+        <v>8.078116293669268</v>
       </c>
       <c r="F265" t="n">
         <v>12369944</v>
@@ -5752,16 +5752,16 @@
         <v>44134</v>
       </c>
       <c r="B267" t="n">
-        <v>7.684879302978516</v>
+        <v>7.684878826141357</v>
       </c>
       <c r="C267" t="n">
-        <v>7.777916426914608</v>
+        <v>7.777915944304612</v>
       </c>
       <c r="D267" t="n">
-        <v>7.574475058635726</v>
+        <v>7.574474588649013</v>
       </c>
       <c r="E267" t="n">
-        <v>7.759309180819852</v>
+        <v>7.759308699364413</v>
       </c>
       <c r="F267" t="n">
         <v>16269207</v>
@@ -5772,16 +5772,16 @@
         <v>44138</v>
       </c>
       <c r="B268" t="n">
-        <v>7.7171311378479</v>
+        <v>7.717131614685059</v>
       </c>
       <c r="C268" t="n">
-        <v>7.852345930671059</v>
+        <v>7.852346415863062</v>
       </c>
       <c r="D268" t="n">
-        <v>7.622853892715106</v>
+        <v>7.622854363726927</v>
       </c>
       <c r="E268" t="n">
-        <v>7.821333855323877</v>
+        <v>7.821334338599661</v>
       </c>
       <c r="F268" t="n">
         <v>9901091</v>
@@ -5812,16 +5812,16 @@
         <v>44140</v>
       </c>
       <c r="B270" t="n">
-        <v>8.119052886962891</v>
+        <v>8.119053840637207</v>
       </c>
       <c r="C270" t="n">
-        <v>8.177355763964984</v>
+        <v>8.177356724487632</v>
       </c>
       <c r="D270" t="n">
-        <v>8.007407635190189</v>
+        <v>8.007408575750512</v>
       </c>
       <c r="E270" t="n">
-        <v>8.039660727779241</v>
+        <v>8.039661672128053</v>
       </c>
       <c r="F270" t="n">
         <v>9820281</v>
@@ -5892,16 +5892,16 @@
         <v>44146</v>
       </c>
       <c r="B274" t="n">
-        <v>8.193482398986816</v>
+        <v>8.193483352661133</v>
       </c>
       <c r="C274" t="n">
-        <v>8.420493294041393</v>
+        <v>8.420494274138473</v>
       </c>
       <c r="D274" t="n">
-        <v>8.193482398986816</v>
+        <v>8.193483352661133</v>
       </c>
       <c r="E274" t="n">
-        <v>8.312571092276054</v>
+        <v>8.312572059811611</v>
       </c>
       <c r="F274" t="n">
         <v>7246451</v>
@@ -5912,16 +5912,16 @@
         <v>44147</v>
       </c>
       <c r="B275" t="n">
-        <v>8.234420776367188</v>
+        <v>8.234419822692871</v>
       </c>
       <c r="C275" t="n">
-        <v>8.398165624159189</v>
+        <v>8.398164651520666</v>
       </c>
       <c r="D275" t="n">
-        <v>8.13145906678732</v>
+        <v>8.131458125037573</v>
       </c>
       <c r="E275" t="n">
-        <v>8.193483224225638</v>
+        <v>8.193482275292528</v>
       </c>
       <c r="F275" t="n">
         <v>11697033</v>
@@ -5932,16 +5932,16 @@
         <v>44148</v>
       </c>
       <c r="B276" t="n">
-        <v>8.633859634399414</v>
+        <v>8.633858680725098</v>
       </c>
       <c r="C276" t="n">
-        <v>8.646265358676397</v>
+        <v>8.646264403631776</v>
       </c>
       <c r="D276" t="n">
-        <v>8.267912658055211</v>
+        <v>8.267911744802472</v>
       </c>
       <c r="E276" t="n">
-        <v>8.322494271024663</v>
+        <v>8.322493351742979</v>
       </c>
       <c r="F276" t="n">
         <v>10854949</v>
@@ -5992,16 +5992,16 @@
         <v>44153</v>
       </c>
       <c r="B279" t="n">
-        <v>8.584240913391113</v>
+        <v>8.584239959716797</v>
       </c>
       <c r="C279" t="n">
-        <v>8.645024946032365</v>
+        <v>8.64502398560519</v>
       </c>
       <c r="D279" t="n">
-        <v>8.516013445661457</v>
+        <v>8.516012499566937</v>
       </c>
       <c r="E279" t="n">
-        <v>8.558190230775271</v>
+        <v>8.55818927999508</v>
       </c>
       <c r="F279" t="n">
         <v>8922310</v>
@@ -6072,16 +6072,16 @@
         <v>44160</v>
       </c>
       <c r="B283" t="n">
-        <v>8.739302635192871</v>
+        <v>8.739301681518555</v>
       </c>
       <c r="C283" t="n">
-        <v>8.920414597775554</v>
+        <v>8.920413624337439</v>
       </c>
       <c r="D283" t="n">
-        <v>8.616492663682914</v>
+        <v>8.616491723410208</v>
       </c>
       <c r="E283" t="n">
-        <v>8.85466827854489</v>
+        <v>8.854667312281327</v>
       </c>
       <c r="F283" t="n">
         <v>6633202</v>
@@ -6112,16 +6112,16 @@
         <v>44162</v>
       </c>
       <c r="B285" t="n">
-        <v>8.615252494812012</v>
+        <v>8.615251541137695</v>
       </c>
       <c r="C285" t="n">
-        <v>8.708288727073548</v>
+        <v>8.70828776310049</v>
       </c>
       <c r="D285" t="n">
-        <v>8.507329393233835</v>
+        <v>8.507328451506179</v>
       </c>
       <c r="E285" t="n">
-        <v>8.566872403188754</v>
+        <v>8.566871454869922</v>
       </c>
       <c r="F285" t="n">
         <v>5230736</v>
@@ -6152,16 +6152,16 @@
         <v>44166</v>
       </c>
       <c r="B287" t="n">
-        <v>8.414292335510254</v>
+        <v>8.414291381835938</v>
       </c>
       <c r="C287" t="n">
-        <v>8.672315323428652</v>
+        <v>8.672314340510058</v>
       </c>
       <c r="D287" t="n">
-        <v>8.360949953683695</v>
+        <v>8.360949006055193</v>
       </c>
       <c r="E287" t="n">
-        <v>8.636340955945199</v>
+        <v>8.636339977103933</v>
       </c>
       <c r="F287" t="n">
         <v>16096259</v>
@@ -6172,16 +6172,16 @@
         <v>44167</v>
       </c>
       <c r="B288" t="n">
-        <v>8.282798767089844</v>
+        <v>8.282797813415527</v>
       </c>
       <c r="C288" t="n">
-        <v>8.4614304780068</v>
+        <v>8.461429503764982</v>
       </c>
       <c r="D288" t="n">
-        <v>8.199686220600897</v>
+        <v>8.199685276496087</v>
       </c>
       <c r="E288" t="n">
-        <v>8.456469081678438</v>
+        <v>8.456468108007872</v>
       </c>
       <c r="F288" t="n">
         <v>15329699</v>
@@ -6212,16 +6212,16 @@
         <v>44169</v>
       </c>
       <c r="B290" t="n">
-        <v>8.772794723510742</v>
+        <v>8.772793769836426</v>
       </c>
       <c r="C290" t="n">
-        <v>8.948945284925747</v>
+        <v>8.948944312102428</v>
       </c>
       <c r="D290" t="n">
-        <v>8.683479763850318</v>
+        <v>8.683478819885265</v>
       </c>
       <c r="E290" t="n">
-        <v>8.886920238013465</v>
+        <v>8.886919271932774</v>
       </c>
       <c r="F290" t="n">
         <v>10446369</v>
@@ -6232,16 +6232,16 @@
         <v>44172</v>
       </c>
       <c r="B291" t="n">
-        <v>8.647504806518555</v>
+        <v>8.647505760192871</v>
       </c>
       <c r="C291" t="n">
-        <v>8.827376626156168</v>
+        <v>8.82737759966732</v>
       </c>
       <c r="D291" t="n">
-        <v>8.621454127772409</v>
+        <v>8.621455078573774</v>
       </c>
       <c r="E291" t="n">
-        <v>8.807528362331166</v>
+        <v>8.807529333653388</v>
       </c>
       <c r="F291" t="n">
         <v>10174485</v>
@@ -6392,16 +6392,16 @@
         <v>44182</v>
       </c>
       <c r="B299" t="n">
-        <v>9.125097274780273</v>
+        <v>9.125096321105957</v>
       </c>
       <c r="C299" t="n">
-        <v>9.233020380265208</v>
+        <v>9.233019415311725</v>
       </c>
       <c r="D299" t="n">
-        <v>9.105249008435251</v>
+        <v>9.1052480568353</v>
       </c>
       <c r="E299" t="n">
-        <v>9.230539235289285</v>
+        <v>9.230538270595108</v>
       </c>
       <c r="F299" t="n">
         <v>5262456</v>
@@ -6452,16 +6452,16 @@
         <v>44187</v>
       </c>
       <c r="B302" t="n">
-        <v>9.018414497375488</v>
+        <v>9.018413543701172</v>
       </c>
       <c r="C302" t="n">
-        <v>9.117654044402261</v>
+        <v>9.117653080233614</v>
       </c>
       <c r="D302" t="n">
-        <v>8.941504362170608</v>
+        <v>8.941503416629342</v>
       </c>
       <c r="E302" t="n">
-        <v>8.974996692978687</v>
+        <v>8.974995743895692</v>
       </c>
       <c r="F302" t="n">
         <v>3700636</v>
@@ -6572,16 +6572,16 @@
         <v>44201</v>
       </c>
       <c r="B308" t="n">
-        <v>9.097805976867676</v>
+        <v>9.097805023193359</v>
       </c>
       <c r="C308" t="n">
-        <v>9.304968615993069</v>
+        <v>9.304967640603</v>
       </c>
       <c r="D308" t="n">
-        <v>9.012211393852336</v>
+        <v>9.012210449150441</v>
       </c>
       <c r="E308" t="n">
-        <v>9.304968615993069</v>
+        <v>9.304967640603</v>
       </c>
       <c r="F308" t="n">
         <v>8306796</v>
@@ -6592,16 +6592,16 @@
         <v>44202</v>
       </c>
       <c r="B309" t="n">
-        <v>9.023375511169434</v>
+        <v>9.02337646484375</v>
       </c>
       <c r="C309" t="n">
-        <v>9.178437672356514</v>
+        <v>9.178438642419241</v>
       </c>
       <c r="D309" t="n">
-        <v>8.883199324604012</v>
+        <v>8.883200263463204</v>
       </c>
       <c r="E309" t="n">
-        <v>9.091602075844966</v>
+        <v>9.091603036730099</v>
       </c>
       <c r="F309" t="n">
         <v>6995714</v>
@@ -6632,16 +6632,16 @@
         <v>44204</v>
       </c>
       <c r="B311" t="n">
-        <v>9.49476432800293</v>
+        <v>9.494765281677246</v>
       </c>
       <c r="C311" t="n">
-        <v>9.533219836566508</v>
+        <v>9.533220794103377</v>
       </c>
       <c r="D311" t="n">
-        <v>9.077957042182957</v>
+        <v>9.077957953992263</v>
       </c>
       <c r="E311" t="n">
-        <v>9.178437593380119</v>
+        <v>9.178438515281906</v>
       </c>
       <c r="F311" t="n">
         <v>10280973</v>
@@ -6732,16 +6732,16 @@
         <v>44211</v>
       </c>
       <c r="B316" t="n">
-        <v>9.479877471923828</v>
+        <v>9.479878425598145</v>
       </c>
       <c r="C316" t="n">
-        <v>9.607648827608905</v>
+        <v>9.607649794137002</v>
       </c>
       <c r="D316" t="n">
-        <v>9.378157688462947</v>
+        <v>9.378158631904267</v>
       </c>
       <c r="E316" t="n">
-        <v>9.589041582834192</v>
+        <v>9.589042547490402</v>
       </c>
       <c r="F316" t="n">
         <v>14334303</v>
@@ -6892,16 +6892,16 @@
         <v>44224</v>
       </c>
       <c r="B324" t="n">
-        <v>9.368233680725098</v>
+        <v>9.368232727050781</v>
       </c>
       <c r="C324" t="n">
-        <v>9.399245757239534</v>
+        <v>9.399244800408228</v>
       </c>
       <c r="D324" t="n">
-        <v>9.102767267989694</v>
+        <v>9.102766341339521</v>
       </c>
       <c r="E324" t="n">
-        <v>9.180918415575915</v>
+        <v>9.180917480970056</v>
       </c>
       <c r="F324" t="n">
         <v>7429217</v>
@@ -6912,16 +6912,16 @@
         <v>44225</v>
       </c>
       <c r="B325" t="n">
-        <v>9.36327075958252</v>
+        <v>9.363271713256836</v>
       </c>
       <c r="C325" t="n">
-        <v>9.571675294860224</v>
+        <v>9.571676269761104</v>
       </c>
       <c r="D325" t="n">
-        <v>9.215652034482874</v>
+        <v>9.215652973121827</v>
       </c>
       <c r="E325" t="n">
-        <v>9.312410421451789</v>
+        <v>9.312411369945844</v>
       </c>
       <c r="F325" t="n">
         <v>11022611</v>
@@ -6952,16 +6952,16 @@
         <v>44229</v>
       </c>
       <c r="B327" t="n">
-        <v>10.133620262146</v>
+        <v>10.13361930847168</v>
       </c>
       <c r="C327" t="n">
-        <v>10.18448060527895</v>
+        <v>10.18447964681817</v>
       </c>
       <c r="D327" t="n">
-        <v>9.832180367414875</v>
+        <v>9.832179442109044</v>
       </c>
       <c r="E327" t="n">
-        <v>10.11005072588166</v>
+        <v>10.11004977442547</v>
       </c>
       <c r="F327" t="n">
         <v>20046878</v>
@@ -6992,16 +6992,16 @@
         <v>44231</v>
       </c>
       <c r="B329" t="n">
-        <v>10.38668155670166</v>
+        <v>10.38668251037598</v>
       </c>
       <c r="C329" t="n">
-        <v>10.38668155670166</v>
+        <v>10.38668251037598</v>
       </c>
       <c r="D329" t="n">
-        <v>10.11749300250636</v>
+        <v>10.11749393146458</v>
       </c>
       <c r="E329" t="n">
-        <v>10.17703779267104</v>
+        <v>10.17703872709649</v>
       </c>
       <c r="F329" t="n">
         <v>12166787</v>
@@ -7012,16 +7012,16 @@
         <v>44232</v>
       </c>
       <c r="B330" t="n">
-        <v>10.5566291809082</v>
+        <v>10.55663013458252</v>
       </c>
       <c r="C330" t="n">
-        <v>10.58143973441847</v>
+        <v>10.58144069033415</v>
       </c>
       <c r="D330" t="n">
-        <v>10.32465689384235</v>
+        <v>10.32465782656054</v>
       </c>
       <c r="E330" t="n">
-        <v>10.41893413810214</v>
+        <v>10.41893507933724</v>
       </c>
       <c r="F330" t="n">
         <v>10745440</v>
@@ -7192,16 +7192,16 @@
         <v>44249</v>
       </c>
       <c r="B339" t="n">
-        <v>11.09376621246338</v>
+        <v>11.09376525878906</v>
       </c>
       <c r="C339" t="n">
-        <v>11.20292944052197</v>
+        <v>11.20292847746345</v>
       </c>
       <c r="D339" t="n">
-        <v>10.63602222835513</v>
+        <v>10.63602131403072</v>
       </c>
       <c r="E339" t="n">
-        <v>10.93994416306512</v>
+        <v>10.9399432226141</v>
       </c>
       <c r="F339" t="n">
         <v>14982292</v>
@@ -7292,16 +7292,16 @@
         <v>44256</v>
       </c>
       <c r="B344" t="n">
-        <v>21.85701560974121</v>
+        <v>21.85701751708984</v>
       </c>
       <c r="C344" t="n">
-        <v>23.99306407785948</v>
+        <v>23.99306617161</v>
       </c>
       <c r="D344" t="n">
-        <v>16.3107860983666</v>
+        <v>16.31078752172449</v>
       </c>
       <c r="E344" t="n">
-        <v>16.8635354591482</v>
+        <v>16.86353693074166</v>
       </c>
       <c r="F344" t="n">
         <v>49361500</v>
@@ -7312,16 +7312,16 @@
         <v>44257</v>
       </c>
       <c r="B345" t="n">
-        <v>21.19184303283691</v>
+        <v>21.19184494018555</v>
       </c>
       <c r="C345" t="n">
-        <v>22.95314478521037</v>
+        <v>22.95314685108304</v>
       </c>
       <c r="D345" t="n">
-        <v>20.6953049717416</v>
+        <v>20.69530683439987</v>
       </c>
       <c r="E345" t="n">
-        <v>22.18491736810308</v>
+        <v>22.18491936483229</v>
       </c>
       <c r="F345" t="n">
         <v>20095700</v>
@@ -7352,16 +7352,16 @@
         <v>44259</v>
       </c>
       <c r="B347" t="n">
-        <v>20.86394119262695</v>
+        <v>20.86394309997559</v>
       </c>
       <c r="C347" t="n">
-        <v>21.52911312081577</v>
+        <v>21.52911508897337</v>
       </c>
       <c r="D347" t="n">
-        <v>20.01139593391831</v>
+        <v>20.0113977633286</v>
       </c>
       <c r="E347" t="n">
-        <v>20.2362428583874</v>
+        <v>20.23624470835284</v>
       </c>
       <c r="F347" t="n">
         <v>8984600</v>
@@ -7732,16 +7732,16 @@
         <v>44286</v>
       </c>
       <c r="B366" t="n">
-        <v>31.08511924743652</v>
+        <v>31.08511734008789</v>
       </c>
       <c r="C366" t="n">
-        <v>32.65904960734591</v>
+        <v>32.65904760342265</v>
       </c>
       <c r="D366" t="n">
-        <v>30.82279871206804</v>
+        <v>30.82279682081511</v>
       </c>
       <c r="E366" t="n">
-        <v>31.95640225288098</v>
+        <v>31.95640029207138</v>
       </c>
       <c r="F366" t="n">
         <v>8195900</v>
@@ -7792,16 +7792,16 @@
         <v>44292</v>
       </c>
       <c r="B369" t="n">
-        <v>30.57921028137207</v>
+        <v>30.5792121887207</v>
       </c>
       <c r="C369" t="n">
-        <v>32.19998297677536</v>
+        <v>32.19998498521812</v>
       </c>
       <c r="D369" t="n">
-        <v>30.48552540315069</v>
+        <v>30.48552730465581</v>
       </c>
       <c r="E369" t="n">
-        <v>31.01953707148042</v>
+        <v>31.01953900629401</v>
       </c>
       <c r="F369" t="n">
         <v>6923500</v>
@@ -7812,16 +7812,16 @@
         <v>44293</v>
       </c>
       <c r="B370" t="n">
-        <v>30.95395851135254</v>
+        <v>30.95395660400391</v>
       </c>
       <c r="C370" t="n">
-        <v>31.36617699981515</v>
+        <v>31.36617506706607</v>
       </c>
       <c r="D370" t="n">
-        <v>30.40120912458377</v>
+        <v>30.40120725129495</v>
       </c>
       <c r="E370" t="n">
-        <v>30.72910978883253</v>
+        <v>30.72910789533883</v>
       </c>
       <c r="F370" t="n">
         <v>4745700</v>
@@ -8012,16 +8012,16 @@
         <v>44308</v>
       </c>
       <c r="B380" t="n">
-        <v>36.30344772338867</v>
+        <v>36.30344390869141</v>
       </c>
       <c r="C380" t="n">
-        <v>38.03664315290104</v>
+        <v>38.03663915608288</v>
       </c>
       <c r="D380" t="n">
-        <v>35.88185858344396</v>
+        <v>35.88185481304648</v>
       </c>
       <c r="E380" t="n">
-        <v>37.12788831107506</v>
+        <v>37.12788440974715</v>
       </c>
       <c r="F380" t="n">
         <v>6756200</v>
@@ -8052,16 +8052,16 @@
         <v>44312</v>
       </c>
       <c r="B382" t="n">
-        <v>35.91933059692383</v>
+        <v>35.91933441162109</v>
       </c>
       <c r="C382" t="n">
-        <v>36.30344431641451</v>
+        <v>36.30344817190534</v>
       </c>
       <c r="D382" t="n">
-        <v>35.5164791869886</v>
+        <v>35.51648295890232</v>
       </c>
       <c r="E382" t="n">
-        <v>35.88185521603473</v>
+        <v>35.88185902675205</v>
       </c>
       <c r="F382" t="n">
         <v>4241900</v>
@@ -8072,16 +8072,16 @@
         <v>44313</v>
       </c>
       <c r="B383" t="n">
-        <v>35.46963882446289</v>
+        <v>35.46963500976562</v>
       </c>
       <c r="C383" t="n">
-        <v>36.29407938304689</v>
+        <v>36.2940754796825</v>
       </c>
       <c r="D383" t="n">
-        <v>35.27289842405</v>
+        <v>35.27289463051181</v>
       </c>
       <c r="E383" t="n">
-        <v>36.05986359955081</v>
+        <v>36.05985972137591</v>
       </c>
       <c r="F383" t="n">
         <v>2386900</v>
@@ -35592,19 +35592,39 @@
         <v>46324</v>
       </c>
       <c r="B1759" t="n">
-        <v>2.03</v>
+        <v>2.029999971389771</v>
       </c>
       <c r="C1759" t="n">
-        <v>2.14</v>
+        <v>2.140000104904175</v>
       </c>
       <c r="D1759" t="n">
         <v>2</v>
       </c>
       <c r="E1759" t="n">
-        <v>2.06</v>
+        <v>2.059999942779541</v>
       </c>
       <c r="F1759" t="n">
         <v>7604500</v>
+      </c>
+    </row>
+    <row r="1760">
+      <c r="A1760" s="1" t="n">
+        <v>46325</v>
+      </c>
+      <c r="B1760" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="C1760" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="D1760" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="E1760" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="F1760" t="n">
+        <v>1973800</v>
       </c>
     </row>
   </sheetData>
